--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="2146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="2145">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">15.8714008331299</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3207607269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2397861480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.74582862854</t>
+    <t xml:space="preserve">15.3207635879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.239785194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7458276748657</t>
   </si>
   <si>
     <t xml:space="preserve">14.9644641876221</t>
@@ -62,55 +62,55 @@
     <t xml:space="preserve">15.2964687347412</t>
   </si>
   <si>
-    <t xml:space="preserve">15.498908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.061637878418</t>
+    <t xml:space="preserve">15.4989109039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0616359710693</t>
   </si>
   <si>
     <t xml:space="preserve">14.5028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5433874130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8510980606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870899200439</t>
+    <t xml:space="preserve">14.5433883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8510990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870889663696</t>
   </si>
   <si>
     <t xml:space="preserve">14.9401731491089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.409836769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9239730834961</t>
+    <t xml:space="preserve">15.4098358154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9239749908447</t>
   </si>
   <si>
     <t xml:space="preserve">15.2802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1831045150757</t>
+    <t xml:space="preserve">15.1831026077271</t>
   </si>
   <si>
     <t xml:space="preserve">14.6243629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3936376571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8106098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7296323776245</t>
+    <t xml:space="preserve">15.3936395645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8106088638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7296314239502</t>
   </si>
   <si>
     <t xml:space="preserve">14.8996820449829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5190935134888</t>
+    <t xml:space="preserve">14.5190925598145</t>
   </si>
   <si>
     <t xml:space="preserve">13.73362159729</t>
@@ -119,118 +119,118 @@
     <t xml:space="preserve">13.344934463501</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0980157852173</t>
+    <t xml:space="preserve">14.0980176925659</t>
   </si>
   <si>
     <t xml:space="preserve">13.3206415176392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.474494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8955726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7822065353394</t>
+    <t xml:space="preserve">13.4744968414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8955736160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7822046279907</t>
   </si>
   <si>
     <t xml:space="preserve">14.3328475952148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2194795608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057245254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8348999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5514812469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3409433364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8672933578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1021251678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4827146530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3774480819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017381668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4665203094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4908142089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5232038497925</t>
+    <t xml:space="preserve">14.2194786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057264328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8349027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5514831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3409481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8672924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1021242141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2235898971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3774461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4017391204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4665212631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4908123016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5232009887695</t>
   </si>
   <si>
     <t xml:space="preserve">15.5636911392212</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1426124572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742280960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8390102386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879850387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6365699768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9199886322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8309154510498</t>
+    <t xml:space="preserve">15.1426115036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8390092849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879812240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6365690231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9199876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8309125900269</t>
   </si>
   <si>
     <t xml:space="preserve">15.8794994354248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8228158950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8956956863403</t>
+    <t xml:space="preserve">15.8228149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.895697593689</t>
   </si>
   <si>
     <t xml:space="preserve">16.2762832641602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1224327087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8471088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8875980377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4422273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3855438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086719512939</t>
+    <t xml:space="preserve">16.1224308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.847110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8875951766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4422245025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3855419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086757659912</t>
   </si>
   <si>
     <t xml:space="preserve">16.2276973724365</t>
@@ -239,25 +239,25 @@
     <t xml:space="preserve">16.7135581970215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6568756103516</t>
+    <t xml:space="preserve">16.6568737030029</t>
   </si>
   <si>
     <t xml:space="preserve">16.4301414489746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6120529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9179973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0254936218262</t>
+    <t xml:space="preserve">16.6120548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9179992675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0254917144775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9758815765381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9924182891846</t>
+    <t xml:space="preserve">16.9924201965332</t>
   </si>
   <si>
     <t xml:space="preserve">16.6285915374756</t>
@@ -266,61 +266,61 @@
     <t xml:space="preserve">16.7774314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9841556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1081809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9345359802246</t>
+    <t xml:space="preserve">16.98415184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1081829071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">16.5541725158691</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5955181121826</t>
+    <t xml:space="preserve">16.5955142974854</t>
   </si>
   <si>
     <t xml:space="preserve">16.7608909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.703010559082</t>
+    <t xml:space="preserve">16.7030086517334</t>
   </si>
   <si>
     <t xml:space="preserve">16.8766574859619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4058609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7696895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.009485244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9681434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8606491088867</t>
+    <t xml:space="preserve">17.4058589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0094833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9681415557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8606472015381</t>
   </si>
   <si>
     <t xml:space="preserve">17.7779579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8854522705078</t>
+    <t xml:space="preserve">17.8854503631592</t>
   </si>
   <si>
     <t xml:space="preserve">17.6952686309814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1087093353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9598712921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2658176422119</t>
+    <t xml:space="preserve">18.1087112426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.959867477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2658157348633</t>
   </si>
   <si>
     <t xml:space="preserve">18.1748600006104</t>
@@ -329,25 +329,25 @@
     <t xml:space="preserve">18.282356262207</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2988967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4725399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1831321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1335163116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0425567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8027648925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0921726226807</t>
+    <t xml:space="preserve">18.2988948822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.472541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1831302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1335182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0425605773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8027667999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0921745300293</t>
   </si>
   <si>
     <t xml:space="preserve">17.9185256958008</t>
@@ -359,34 +359,34 @@
     <t xml:space="preserve">17.314905166626</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9097309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8022365570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7366104125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5712375640869</t>
+    <t xml:space="preserve">16.9097328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8022403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7366161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5712394714355</t>
   </si>
   <si>
     <t xml:space="preserve">17.3479785919189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9102573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6694097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1402063369751</t>
+    <t xml:space="preserve">17.9102535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6694078445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8342599868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1402072906494</t>
   </si>
   <si>
     <t xml:space="preserve">15.2559700012207</t>
@@ -395,55 +395,55 @@
     <t xml:space="preserve">16.2399559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2978401184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7272901535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5867214202881</t>
+    <t xml:space="preserve">16.2978363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7272920608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5867223739624</t>
   </si>
   <si>
     <t xml:space="preserve">15.2311611175537</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6115274429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2812976837158</t>
+    <t xml:space="preserve">15.6115303039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2813034057617</t>
   </si>
   <si>
     <t xml:space="preserve">16.4632167816162</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6533966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6864776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6782035827637</t>
+    <t xml:space="preserve">16.6533985137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6864738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.678201675415</t>
   </si>
   <si>
     <t xml:space="preserve">16.7443542480469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6699371337891</t>
+    <t xml:space="preserve">16.6699352264404</t>
   </si>
   <si>
     <t xml:space="preserve">16.8435840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8187770843506</t>
+    <t xml:space="preserve">16.818775177002</t>
   </si>
   <si>
     <t xml:space="preserve">16.9510746002197</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0999126434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.116455078125</t>
+    <t xml:space="preserve">17.0999145507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1164512634277</t>
   </si>
   <si>
     <t xml:space="preserve">17.2983665466309</t>
@@ -452,31 +452,31 @@
     <t xml:space="preserve">17.2404842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0751094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3314418792725</t>
+    <t xml:space="preserve">17.0751113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3314437866211</t>
   </si>
   <si>
     <t xml:space="preserve">17.6208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1004428863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125793457031</t>
+    <t xml:space="preserve">18.1004390716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125831604004</t>
   </si>
   <si>
     <t xml:space="preserve">17.5960445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0756378173828</t>
+    <t xml:space="preserve">18.0756340026855</t>
   </si>
   <si>
     <t xml:space="preserve">17.7944946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8771839141846</t>
+    <t xml:space="preserve">17.8771858215332</t>
   </si>
   <si>
     <t xml:space="preserve">18.1913986206055</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">18.2492790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0839023590088</t>
+    <t xml:space="preserve">18.0839042663574</t>
   </si>
   <si>
     <t xml:space="preserve">18.2906227111816</t>
@@ -497,43 +497,43 @@
     <t xml:space="preserve">17.9929466247559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8441066741943</t>
+    <t xml:space="preserve">17.844108581543</t>
   </si>
   <si>
     <t xml:space="preserve">17.7200756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7283477783203</t>
+    <t xml:space="preserve">17.728343963623</t>
   </si>
   <si>
     <t xml:space="preserve">17.8937187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0673656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3733100891113</t>
+    <t xml:space="preserve">18.0673694610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3733139038086</t>
   </si>
   <si>
     <t xml:space="preserve">18.9438591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4317226409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3572998046875</t>
+    <t xml:space="preserve">19.4317207336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3573036193848</t>
   </si>
   <si>
     <t xml:space="preserve">19.1009693145752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1257762908936</t>
+    <t xml:space="preserve">19.1257724761963</t>
   </si>
   <si>
     <t xml:space="preserve">19.1919250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1753902435303</t>
+    <t xml:space="preserve">19.175386428833</t>
   </si>
   <si>
     <t xml:space="preserve">19.2828845977783</t>
@@ -542,31 +542,31 @@
     <t xml:space="preserve">19.1340446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3490314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978713989258</t>
+    <t xml:space="preserve">19.3490333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978694915771</t>
   </si>
   <si>
     <t xml:space="preserve">19.7624740600586</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6549777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7045917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4647941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0596256256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6461849212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.117504119873</t>
+    <t xml:space="preserve">19.6549797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7045936584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4647960662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0596237182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.646183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1175079345703</t>
   </si>
   <si>
     <t xml:space="preserve">19.1588497161865</t>
@@ -575,49 +575,49 @@
     <t xml:space="preserve">19.0100116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7536811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9025192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0844326019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9934768676758</t>
+    <t xml:space="preserve">18.7536773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9025173187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0844345092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9934749603271</t>
   </si>
   <si>
     <t xml:space="preserve">18.7950229644775</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7867546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7454090118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3319664001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6291179656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8694381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1505813598633</t>
+    <t xml:space="preserve">18.7867527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7454071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3319683074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6291217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.869441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1505794525146</t>
   </si>
   <si>
     <t xml:space="preserve">18.3485069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6627235412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7288703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6875305175781</t>
+    <t xml:space="preserve">18.6627197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7288722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6875267028809</t>
   </si>
   <si>
     <t xml:space="preserve">18.8942470550537</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">18.6709880828857</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9355945587158</t>
+    <t xml:space="preserve">18.9355926513672</t>
   </si>
   <si>
     <t xml:space="preserve">19.4399890899658</t>
@@ -653,34 +653,34 @@
     <t xml:space="preserve">19.6797866821289</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1676483154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8451595306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7790107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1428413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9113140106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1759166717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0022678375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9278507232666</t>
+    <t xml:space="preserve">20.1676425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8451633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7790145874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1428394317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9113101959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1759147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0022659301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.927848815918</t>
   </si>
   <si>
     <t xml:space="preserve">20.0105381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8038158416748</t>
+    <t xml:space="preserve">19.8038196563721</t>
   </si>
   <si>
     <t xml:space="preserve">20.1014976501465</t>
@@ -698,49 +698,49 @@
     <t xml:space="preserve">20.6389656066895</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1345691680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2751426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2172584533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3164844512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2420635223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3330211639404</t>
+    <t xml:space="preserve">20.1345710754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2751407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2172603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3164863586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2420654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3330230712891</t>
   </si>
   <si>
     <t xml:space="preserve">20.2255268096924</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6555080413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5066680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3578319549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4818592071533</t>
+    <t xml:space="preserve">20.6555061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5066699981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3578281402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4818630218506</t>
   </si>
   <si>
     <t xml:space="preserve">20.0849571228027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3991756439209</t>
+    <t xml:space="preserve">20.3991718292236</t>
   </si>
   <si>
     <t xml:space="preserve">20.5645503997803</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5397434234619</t>
+    <t xml:space="preserve">20.5397453308105</t>
   </si>
   <si>
     <t xml:space="preserve">20.6885833740234</t>
@@ -749,16 +749,16 @@
     <t xml:space="preserve">19.894775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4074420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7133865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9697189331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3495597839355</t>
+    <t xml:space="preserve">20.4074401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7133884429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9697227478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3495616912842</t>
   </si>
   <si>
     <t xml:space="preserve">20.423978805542</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">19.8865051269531</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8286266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8534297943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.118034362793</t>
+    <t xml:space="preserve">19.8286285400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8534317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1180324554443</t>
   </si>
   <si>
     <t xml:space="preserve">19.5722942352295</t>
@@ -794,28 +794,28 @@
     <t xml:space="preserve">19.5144100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5474815368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4234561920166</t>
+    <t xml:space="preserve">19.5474853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.423454284668</t>
   </si>
   <si>
     <t xml:space="preserve">19.6136341094971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5640182495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3821105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7376670837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.366096496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9361190795898</t>
+    <t xml:space="preserve">19.564022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3821067810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7376689910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3660984039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9361152648926</t>
   </si>
   <si>
     <t xml:space="preserve">20.200719833374</t>
@@ -824,73 +824,73 @@
     <t xml:space="preserve">20.4901294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7381935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2922077178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1516361236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.085485458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9366474151611</t>
+    <t xml:space="preserve">20.7381954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2922058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1516342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0854835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9366455078125</t>
   </si>
   <si>
     <t xml:space="preserve">20.7795372009277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.457052230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7051200866699</t>
+    <t xml:space="preserve">20.4570541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7051181793213</t>
   </si>
   <si>
     <t xml:space="preserve">21.1268291473389</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0435581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1192493438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8669395446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9846839904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2958679199219</t>
+    <t xml:space="preserve">22.0435562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1192512512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8669414520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9846858978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2958698272705</t>
   </si>
   <si>
     <t xml:space="preserve">22.4724864959717</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2201766967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.262228012085</t>
+    <t xml:space="preserve">22.2201747894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2622241973877</t>
   </si>
   <si>
     <t xml:space="preserve">22.5397701263428</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5734119415283</t>
+    <t xml:space="preserve">22.5734081268311</t>
   </si>
   <si>
     <t xml:space="preserve">22.5986404418945</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8080711364746</t>
+    <t xml:space="preserve">21.808069229126</t>
   </si>
   <si>
     <t xml:space="preserve">21.6987323760986</t>
   </si>
   <si>
-    <t xml:space="preserve">21.084774017334</t>
+    <t xml:space="preserve">21.0847778320312</t>
   </si>
   <si>
     <t xml:space="preserve">21.3202686309814</t>
@@ -899,55 +899,55 @@
     <t xml:space="preserve">20.9502105712891</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6390266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4203586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5549240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4540004730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9670314788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.19411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8576984405518</t>
+    <t xml:space="preserve">20.6390285491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4203567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5549201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4540023803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9670295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1941146850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8576965332031</t>
   </si>
   <si>
     <t xml:space="preserve">21.1688823699951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.832462310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9586181640625</t>
+    <t xml:space="preserve">20.8324642181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9586200714111</t>
   </si>
   <si>
     <t xml:space="preserve">20.8156471252441</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5978107452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2613925933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1015949249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6819114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.614631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8164768218994</t>
+    <t xml:space="preserve">21.5978088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2613945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.101598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6819152832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6146297454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.816478729248</t>
   </si>
   <si>
     <t xml:space="preserve">21.6566791534424</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">21.8248882293701</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5473480224609</t>
+    <t xml:space="preserve">21.5473461151123</t>
   </si>
   <si>
     <t xml:space="preserve">21.5725803375244</t>
@@ -965,52 +965,52 @@
     <t xml:space="preserve">22.0351486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.858528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9258098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7828350067139</t>
+    <t xml:space="preserve">21.8585319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9258136749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7828369140625</t>
   </si>
   <si>
     <t xml:space="preserve">22.3210983276367</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4884738922119</t>
+    <t xml:space="preserve">21.4884757995605</t>
   </si>
   <si>
     <t xml:space="preserve">21.3875484466553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1949424743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8501205444336</t>
+    <t xml:space="preserve">22.1949443817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.850118637085</t>
   </si>
   <si>
     <t xml:space="preserve">22.2454051971436</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0015068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3883838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538146972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5481777191162</t>
+    <t xml:space="preserve">22.0015048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3883819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538166046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5481796264648</t>
   </si>
   <si>
     <t xml:space="preserve">22.5313606262207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7668476104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0696201324463</t>
+    <t xml:space="preserve">22.7668495178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0696220397949</t>
   </si>
   <si>
     <t xml:space="preserve">22.5818214416504</t>
@@ -1022,55 +1022,55 @@
     <t xml:space="preserve">22.5650005340576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1444797515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2117652893066</t>
+    <t xml:space="preserve">22.1444835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.211763381958</t>
   </si>
   <si>
     <t xml:space="preserve">22.1865348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5229473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7920780181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4220237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7500286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9266471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9350547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8593616485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7079772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5902309417725</t>
+    <t xml:space="preserve">22.52294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7920799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.422025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7500267028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9266490936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.93505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8593635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7079753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416191101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5902290344238</t>
   </si>
   <si>
     <t xml:space="preserve">22.2369956970215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8417091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1613006591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3547420501709</t>
+    <t xml:space="preserve">21.8417110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.161304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3547401428223</t>
   </si>
   <si>
     <t xml:space="preserve">22.3042793273926</t>
@@ -1079,22 +1079,22 @@
     <t xml:space="preserve">21.9594535827637</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2285861968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1108436584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9174003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3463325500488</t>
+    <t xml:space="preserve">22.2285842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1108417510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9174022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3463306427002</t>
   </si>
   <si>
     <t xml:space="preserve">22.4304370880127</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8257217407227</t>
+    <t xml:space="preserve">22.825719833374</t>
   </si>
   <si>
     <t xml:space="preserve">23.4649066925049</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">23.6331176757812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6751651763916</t>
+    <t xml:space="preserve">23.6751670837402</t>
   </si>
   <si>
     <t xml:space="preserve">23.6835803985596</t>
@@ -1115,61 +1115,61 @@
     <t xml:space="preserve">23.9106597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9190692901611</t>
+    <t xml:space="preserve">23.9190711975098</t>
   </si>
   <si>
     <t xml:space="preserve">23.750862121582</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8770179748535</t>
+    <t xml:space="preserve">23.8770160675049</t>
   </si>
   <si>
     <t xml:space="preserve">23.9863510131836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8938369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.952709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9779376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8517837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0368137359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4741535186768</t>
+    <t xml:space="preserve">23.8938407897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9527111053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9779396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8517818450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0368099212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4741497039795</t>
   </si>
   <si>
     <t xml:space="preserve">24.3311767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3143577575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0536365509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9358921051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8013248443604</t>
+    <t xml:space="preserve">24.3143558502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0536346435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9358901977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8013229370117</t>
   </si>
   <si>
     <t xml:space="preserve">23.9611206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0199947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1040954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5582580566406</t>
+    <t xml:space="preserve">24.0199928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.104097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.558256149292</t>
   </si>
   <si>
     <t xml:space="preserve">24.5077934265137</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">24.3564071655273</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3984622955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9199028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7937469482422</t>
+    <t xml:space="preserve">24.3984603881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.919900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7937450408936</t>
   </si>
   <si>
     <t xml:space="preserve">24.6928215026855</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">25.2310848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1217498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1890316009521</t>
+    <t xml:space="preserve">25.1217517852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1890296936035</t>
   </si>
   <si>
     <t xml:space="preserve">24.8526210784912</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">24.4489212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5574264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3892154693604</t>
+    <t xml:space="preserve">23.5574226379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.389217376709</t>
   </si>
   <si>
     <t xml:space="preserve">23.5994739532471</t>
@@ -1220,133 +1220,133 @@
     <t xml:space="preserve">23.2125988006592</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9274787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6919918060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.540599822998</t>
+    <t xml:space="preserve">23.9274768829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.691987991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5406017303467</t>
   </si>
   <si>
     <t xml:space="preserve">23.5742435455322</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3808078765869</t>
+    <t xml:space="preserve">23.3808040618896</t>
   </si>
   <si>
     <t xml:space="preserve">23.4144477844238</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5321922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9695301055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9939308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6911563873291</t>
+    <t xml:space="preserve">23.5321884155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9695281982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9939289093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6911582946777</t>
   </si>
   <si>
     <t xml:space="preserve">22.9014167785645</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9771099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0443878173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0275707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.035982131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8930053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6827449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1789569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546501159668</t>
+    <t xml:space="preserve">22.9771060943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0443897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.02756690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0359802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8930034637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.682746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1789588928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546482086182</t>
   </si>
   <si>
     <t xml:space="preserve">23.2210063934326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1621341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.229419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0780334472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8677730560303</t>
+    <t xml:space="preserve">23.1621360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2294178009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.078031539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.867769241333</t>
   </si>
   <si>
     <t xml:space="preserve">23.0107498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1882019042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0031719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1713790893555</t>
+    <t xml:space="preserve">24.1881999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.003173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1713829040527</t>
   </si>
   <si>
     <t xml:space="preserve">24.2218418121338</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3900470733643</t>
+    <t xml:space="preserve">24.3900508880615</t>
   </si>
   <si>
     <t xml:space="preserve">24.4909725189209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8273887634277</t>
+    <t xml:space="preserve">24.8273868560791</t>
   </si>
   <si>
     <t xml:space="preserve">24.5246124267578</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3395881652832</t>
+    <t xml:space="preserve">24.3395824432373</t>
   </si>
   <si>
     <t xml:space="preserve">24.3059463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8686065673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8349647521973</t>
+    <t xml:space="preserve">23.8686084747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8349628448486</t>
   </si>
   <si>
     <t xml:space="preserve">23.2882919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9602890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6070537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4564971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7163867950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4556655883789</t>
+    <t xml:space="preserve">22.9602870941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6070518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4564990997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7163848876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4556636810303</t>
   </si>
   <si>
     <t xml:space="preserve">22.0687885284424</t>
@@ -1355,25 +1355,25 @@
     <t xml:space="preserve">22.1781234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0940189361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9089889526367</t>
+    <t xml:space="preserve">22.0940208435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9089908599854</t>
   </si>
   <si>
     <t xml:space="preserve">21.7996559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6314487457275</t>
+    <t xml:space="preserve">21.6314468383789</t>
   </si>
   <si>
     <t xml:space="preserve">21.7912445068359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.363151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3967914581299</t>
+    <t xml:space="preserve">22.3631496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3967952728271</t>
   </si>
   <si>
     <t xml:space="preserve">22.2874584197998</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">22.0856094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6230411529541</t>
+    <t xml:space="preserve">21.6230430603027</t>
   </si>
   <si>
     <t xml:space="preserve">21.3454990386963</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">21.4043712615967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4464225769043</t>
+    <t xml:space="preserve">21.4464244842529</t>
   </si>
   <si>
     <t xml:space="preserve">21.2950344085693</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3370838165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7407855987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7904148101807</t>
+    <t xml:space="preserve">21.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7407836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7904109954834</t>
   </si>
   <si>
     <t xml:space="preserve">20.3194351196289</t>
@@ -1415,40 +1415,40 @@
     <t xml:space="preserve">20.4035377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5717430114746</t>
+    <t xml:space="preserve">20.5717449188232</t>
   </si>
   <si>
     <t xml:space="preserve">20.7735939025879</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9249820709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8072357177734</t>
+    <t xml:space="preserve">20.9249782562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8072376251221</t>
   </si>
   <si>
     <t xml:space="preserve">21.0288734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8919353485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6351699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6180515289307</t>
+    <t xml:space="preserve">20.8919315338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6351680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.618049621582</t>
   </si>
   <si>
     <t xml:space="preserve">20.7464332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8662528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3883419036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9604034423828</t>
+    <t xml:space="preserve">20.8662548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3883380889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9604015350342</t>
   </si>
   <si>
     <t xml:space="preserve">21.362663269043</t>
@@ -1457,25 +1457,25 @@
     <t xml:space="preserve">21.5081634521484</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8847484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7563667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2270965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9203567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4153900146484</t>
+    <t xml:space="preserve">21.884744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7563648223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2270984649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9203586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4153919219971</t>
   </si>
   <si>
     <t xml:space="preserve">22.4239501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8077182769775</t>
+    <t xml:space="preserve">21.8077201843262</t>
   </si>
   <si>
     <t xml:space="preserve">22.0987148284912</t>
@@ -1484,19 +1484,19 @@
     <t xml:space="preserve">22.1072750091553</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7392501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2428398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.45680809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4054565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9432830810547</t>
+    <t xml:space="preserve">21.7392463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2428417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4568119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4054546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9432849884033</t>
   </si>
   <si>
     <t xml:space="preserve">20.1302013397217</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">20.3698463439941</t>
   </si>
   <si>
-    <t xml:space="preserve">21.268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3968982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.336986541748</t>
+    <t xml:space="preserve">21.2685165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.396900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3369846343994</t>
   </si>
   <si>
     <t xml:space="preserve">21.3797798156738</t>
@@ -1526,16 +1526,16 @@
     <t xml:space="preserve">20.6779632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1743717193604</t>
+    <t xml:space="preserve">21.174373626709</t>
   </si>
   <si>
     <t xml:space="preserve">20.8063449859619</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7977848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9960136413574</t>
+    <t xml:space="preserve">20.7977828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9960117340088</t>
   </si>
   <si>
     <t xml:space="preserve">21.5423984527588</t>
@@ -1547,43 +1547,43 @@
     <t xml:space="preserve">20.9090461730957</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4554347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6509113311768</t>
+    <t xml:space="preserve">20.455436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6509094238281</t>
   </si>
   <si>
     <t xml:space="preserve">19.8563213348389</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8706874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9306011199951</t>
+    <t xml:space="preserve">17.8706893920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9305973052979</t>
   </si>
   <si>
     <t xml:space="preserve">18.2729511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4427490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2558326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9355754852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6260871887207</t>
+    <t xml:space="preserve">17.4427509307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2558345794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9355735778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6260833740234</t>
   </si>
   <si>
     <t xml:space="preserve">18.245418548584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1657428741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1568927764893</t>
+    <t xml:space="preserve">18.1657447814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1568908691406</t>
   </si>
   <si>
     <t xml:space="preserve">18.811990737915</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">19.2103652954102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4139766693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5202083587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5113563537598</t>
+    <t xml:space="preserve">19.4139747619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5202045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5113544464111</t>
   </si>
   <si>
     <t xml:space="preserve">19.5644702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7238178253174</t>
+    <t xml:space="preserve">19.7238216400146</t>
   </si>
   <si>
     <t xml:space="preserve">19.6352920532227</t>
@@ -1628,58 +1628,58 @@
     <t xml:space="preserve">19.4316806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1395435333252</t>
+    <t xml:space="preserve">19.1395416259766</t>
   </si>
   <si>
     <t xml:space="preserve">19.0687198638916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2369194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6972618103027</t>
+    <t xml:space="preserve">19.2369213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6972599029541</t>
   </si>
   <si>
     <t xml:space="preserve">19.7503776550293</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8034934997559</t>
+    <t xml:space="preserve">19.8034915924072</t>
   </si>
   <si>
     <t xml:space="preserve">19.4405326843262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0333118438721</t>
+    <t xml:space="preserve">19.2900371551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0333099365234</t>
   </si>
   <si>
     <t xml:space="preserve">18.5109996795654</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3516483306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8208446502686</t>
+    <t xml:space="preserve">18.3516521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8208427429199</t>
   </si>
   <si>
     <t xml:space="preserve">18.7765789031982</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7942867279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9182243347168</t>
+    <t xml:space="preserve">18.7942848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9182262420654</t>
   </si>
   <si>
     <t xml:space="preserve">19.1129817962646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4847984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6707000732422</t>
+    <t xml:space="preserve">19.4847946166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6707019805908</t>
   </si>
   <si>
     <t xml:space="preserve">19.5733242034912</t>
@@ -1709,46 +1709,46 @@
     <t xml:space="preserve">18.4136180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">18.67919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6880550384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1483936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9890460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0510139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5995254516602</t>
+    <t xml:space="preserve">18.6792011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6880531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1483917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9890441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0510158538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5995292663574</t>
   </si>
   <si>
     <t xml:space="preserve">18.3427963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4313259124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3693580627441</t>
+    <t xml:space="preserve">18.4313220977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3693561553955</t>
   </si>
   <si>
     <t xml:space="preserve">17.7585182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6965484619141</t>
+    <t xml:space="preserve">17.6965503692627</t>
   </si>
   <si>
     <t xml:space="preserve">17.4840869903564</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9001636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4176921844482</t>
+    <t xml:space="preserve">17.9001617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4176902770996</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325965881348</t>
@@ -1757,43 +1757,43 @@
     <t xml:space="preserve">16.6342277526855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4527454376221</t>
+    <t xml:space="preserve">16.4527435302734</t>
   </si>
   <si>
     <t xml:space="preserve">15.9392881393433</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5719013214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.434684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4656686782837</t>
+    <t xml:space="preserve">15.5719022750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346828460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4656715393066</t>
   </si>
   <si>
     <t xml:space="preserve">16.7316074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2712631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7666606903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2133693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1735315322876</t>
+    <t xml:space="preserve">16.2712669372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7666625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2133674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.173529624939</t>
   </si>
   <si>
     <t xml:space="preserve">14.6777782440186</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2262916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7840118408203</t>
+    <t xml:space="preserve">14.2262907028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7840127944946</t>
   </si>
   <si>
     <t xml:space="preserve">14.6290893554688</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">15.0717239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.191237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7179698944092</t>
+    <t xml:space="preserve">15.1912355422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7179679870605</t>
   </si>
   <si>
     <t xml:space="preserve">16.2933979034424</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">15.9171562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8596134185791</t>
+    <t xml:space="preserve">15.8596153259277</t>
   </si>
   <si>
     <t xml:space="preserve">16.0986366271973</t>
@@ -1835,19 +1835,19 @@
     <t xml:space="preserve">15.7887926101685</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4833745956421</t>
+    <t xml:space="preserve">15.4833736419678</t>
   </si>
   <si>
     <t xml:space="preserve">14.6910581588745</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2882604598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.204158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943147659302</t>
+    <t xml:space="preserve">14.2882595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2041597366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943157196045</t>
   </si>
   <si>
     <t xml:space="preserve">13.9739894866943</t>
@@ -1862,40 +1862,40 @@
     <t xml:space="preserve">13.9916954040527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7880830764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6243085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1554689407349</t>
+    <t xml:space="preserve">13.7880821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6243076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1554698944092</t>
   </si>
   <si>
     <t xml:space="preserve">14.3148183822632</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0451688766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254779815674</t>
+    <t xml:space="preserve">15.0451679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254770278931</t>
   </si>
   <si>
     <t xml:space="preserve">14.1112060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.495943069458</t>
+    <t xml:space="preserve">13.4959421157837</t>
   </si>
   <si>
     <t xml:space="preserve">13.3675804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2524929046631</t>
+    <t xml:space="preserve">13.2524938583374</t>
   </si>
   <si>
     <t xml:space="preserve">14.0669441223145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7707319259644</t>
+    <t xml:space="preserve">14.7707328796387</t>
   </si>
   <si>
     <t xml:space="preserve">14.8415546417236</t>
@@ -1904,34 +1904,34 @@
     <t xml:space="preserve">14.6954860687256</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6512203216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8946723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0628719329834</t>
+    <t xml:space="preserve">14.6512184143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8946714401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0628709793091</t>
   </si>
   <si>
     <t xml:space="preserve">14.8813905715942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8282747268677</t>
+    <t xml:space="preserve">14.828275680542</t>
   </si>
   <si>
     <t xml:space="preserve">14.9345073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4479675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7131900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2886171340942</t>
+    <t xml:space="preserve">15.4479637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.713189125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558275222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2886161804199</t>
   </si>
   <si>
     <t xml:space="preserve">15.6958389282227</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">16.4129123687744</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1163444519043</t>
+    <t xml:space="preserve">16.1163425445557</t>
   </si>
   <si>
     <t xml:space="preserve">16.0145359039307</t>
@@ -1961,10 +1961,10 @@
     <t xml:space="preserve">16.479305267334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4748802185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3376598358154</t>
+    <t xml:space="preserve">16.4748764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3376617431641</t>
   </si>
   <si>
     <t xml:space="preserve">16.2181491851807</t>
@@ -1973,52 +1973,52 @@
     <t xml:space="preserve">16.2889709472656</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5811100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5412731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7758712768555</t>
+    <t xml:space="preserve">16.5811080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5412712097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7758731842041</t>
   </si>
   <si>
     <t xml:space="preserve">16.4881572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7935752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298007965088</t>
+    <t xml:space="preserve">16.7935733795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6297988891602</t>
   </si>
   <si>
     <t xml:space="preserve">16.9263648986816</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9481401443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.930438041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9614219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5279960632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5368480682373</t>
+    <t xml:space="preserve">15.9481420516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9304342269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9614238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5279941558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5368461608887</t>
   </si>
   <si>
     <t xml:space="preserve">16.6784896850586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855388641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7138996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1292676925659</t>
+    <t xml:space="preserve">16.5855369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1292667388916</t>
   </si>
   <si>
     <t xml:space="preserve">15.5763273239136</t>
@@ -2027,37 +2027,37 @@
     <t xml:space="preserve">15.8197784423828</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0101108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8905992507935</t>
+    <t xml:space="preserve">16.0101089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8906011581421</t>
   </si>
   <si>
     <t xml:space="preserve">15.8463335037231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3992767333984</t>
+    <t xml:space="preserve">15.3992738723755</t>
   </si>
   <si>
     <t xml:space="preserve">15.2930421829224</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9610662460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.987624168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.885817527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3767871856689</t>
+    <t xml:space="preserve">14.9610643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876251220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8858184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3767862319946</t>
   </si>
   <si>
     <t xml:space="preserve">14.4874467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6069574356079</t>
+    <t xml:space="preserve">14.6069555282593</t>
   </si>
   <si>
     <t xml:space="preserve">14.5626945495605</t>
@@ -2066,28 +2066,28 @@
     <t xml:space="preserve">14.7795848846436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4125547409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.222222328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0540180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9212274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6423692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300804138184</t>
+    <t xml:space="preserve">15.4125518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2222185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0540189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9212284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6423673629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300813674927</t>
   </si>
   <si>
     <t xml:space="preserve">14.8592586517334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1868095397949</t>
+    <t xml:space="preserve">15.1868104934692</t>
   </si>
   <si>
     <t xml:space="preserve">15.0230340957642</t>
@@ -2096,52 +2096,52 @@
     <t xml:space="preserve">14.9477863311768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4476089477539</t>
+    <t xml:space="preserve">14.447606086731</t>
   </si>
   <si>
     <t xml:space="preserve">13.2436408996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.553484916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6552934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6420135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1997337341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4564609527588</t>
+    <t xml:space="preserve">13.5534868240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6552925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6420125961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1997346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4564619064331</t>
   </si>
   <si>
     <t xml:space="preserve">14.4431829452515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.682204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8459815979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2177963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0495948791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2089424133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0318880081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1823835372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4963006973267</t>
+    <t xml:space="preserve">14.6822061538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8459806442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.217794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0495929718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2089414596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0318870544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1823844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.496298789978</t>
   </si>
   <si>
     <t xml:space="preserve">14.1820287704468</t>
@@ -2150,55 +2150,55 @@
     <t xml:space="preserve">15.2000885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1381196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3151741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3063230514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6467943191528</t>
+    <t xml:space="preserve">15.1381177902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3151721954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.306321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6467952728271</t>
   </si>
   <si>
     <t xml:space="preserve">14.3723611831665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8589038848877</t>
+    <t xml:space="preserve">13.858904838562</t>
   </si>
   <si>
     <t xml:space="preserve">13.7748041152954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5977487564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7792310714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5888986587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6774244308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2170829772949</t>
+    <t xml:space="preserve">13.5977478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7792291641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5888977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6774234771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2170839309692</t>
   </si>
   <si>
     <t xml:space="preserve">13.5313539505005</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3502292633057</t>
+    <t xml:space="preserve">14.3502283096313</t>
   </si>
   <si>
     <t xml:space="preserve">14.3192443847656</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2705574035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6999111175537</t>
+    <t xml:space="preserve">14.2705564498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6999101638794</t>
   </si>
   <si>
     <t xml:space="preserve">14.7353219985962</t>
@@ -2210,31 +2210,31 @@
     <t xml:space="preserve">14.6600723266602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7486019134521</t>
+    <t xml:space="preserve">14.7486000061035</t>
   </si>
   <si>
     <t xml:space="preserve">14.9079494476318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2266492843628</t>
+    <t xml:space="preserve">15.2266473770142</t>
   </si>
   <si>
     <t xml:space="preserve">15.5807552337646</t>
   </si>
   <si>
-    <t xml:space="preserve">15.91273021698</t>
+    <t xml:space="preserve">15.9127321243286</t>
   </si>
   <si>
     <t xml:space="preserve">16.0942115783691</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8584671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9808731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675346374512</t>
+    <t xml:space="preserve">15.8584632873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9808712005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675327301025</t>
   </si>
   <si>
     <t xml:space="preserve">16.2302188873291</t>
@@ -2246,52 +2246,52 @@
     <t xml:space="preserve">16.5838375091553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5929050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.66090965271</t>
+    <t xml:space="preserve">16.5929069519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6609115600586</t>
   </si>
   <si>
     <t xml:space="preserve">16.7243804931641</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7425117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4115600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6427745819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9827938079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9419918060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0326614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3092136383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4542865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9646549224854</t>
+    <t xml:space="preserve">16.7425136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4115619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6427726745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9827919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9419898986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0326633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3092098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4542846679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9646606445312</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555912017822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0462627410889</t>
+    <t xml:space="preserve">17.0462608337402</t>
   </si>
   <si>
     <t xml:space="preserve">18.0436515808105</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0935211181641</t>
+    <t xml:space="preserve">18.0935192108154</t>
   </si>
   <si>
     <t xml:space="preserve">18.1116561889648</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">17.1414699554443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7833137512207</t>
+    <t xml:space="preserve">16.7833156585693</t>
   </si>
   <si>
     <t xml:space="preserve">16.9283885955811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5268249511719</t>
+    <t xml:space="preserve">17.5268211364746</t>
   </si>
   <si>
     <t xml:space="preserve">17.1505355834961</t>
@@ -2321,25 +2321,25 @@
     <t xml:space="preserve">16.8875885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9601230621338</t>
+    <t xml:space="preserve">16.9601249694824</t>
   </si>
   <si>
     <t xml:space="preserve">17.3726787567139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7787799835205</t>
+    <t xml:space="preserve">16.7787818908691</t>
   </si>
   <si>
     <t xml:space="preserve">16.7923831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7017097473145</t>
+    <t xml:space="preserve">16.7017116546631</t>
   </si>
   <si>
     <t xml:space="preserve">16.030740737915</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0715427398682</t>
+    <t xml:space="preserve">16.0715465545654</t>
   </si>
   <si>
     <t xml:space="preserve">16.6473083496094</t>
@@ -2348,16 +2348,16 @@
     <t xml:space="preserve">16.8150501251221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5948257446289</t>
+    <t xml:space="preserve">17.5948276519775</t>
   </si>
   <si>
     <t xml:space="preserve">17.3862819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0054607391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9782619476318</t>
+    <t xml:space="preserve">17.0054626464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9782600402832</t>
   </si>
   <si>
     <t xml:space="preserve">17.2774753570557</t>
@@ -2366,52 +2366,52 @@
     <t xml:space="preserve">17.2276058197021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0209827423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0481872558594</t>
+    <t xml:space="preserve">18.0209846496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0481834411621</t>
   </si>
   <si>
     <t xml:space="preserve">18.0073852539062</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2068614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7508907318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2975311279297</t>
+    <t xml:space="preserve">18.206859588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7508888244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2975330352783</t>
   </si>
   <si>
     <t xml:space="preserve">18.3519344329834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2884654998779</t>
+    <t xml:space="preserve">18.2884616851807</t>
   </si>
   <si>
     <t xml:space="preserve">18.4244728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9775695800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.050106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0410385131836</t>
+    <t xml:space="preserve">18.9775676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0501079559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0410404205322</t>
   </si>
   <si>
     <t xml:space="preserve">18.3156642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.771635055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0617847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8804397583008</t>
+    <t xml:space="preserve">17.7716388702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0617866516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8804416656494</t>
   </si>
   <si>
     <t xml:space="preserve">18.0889892578125</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">17.7217655181885</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8623085021973</t>
+    <t xml:space="preserve">17.8623104095459</t>
   </si>
   <si>
     <t xml:space="preserve">17.7126998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0598640441895</t>
+    <t xml:space="preserve">17.0598621368408</t>
   </si>
   <si>
     <t xml:space="preserve">17.0507965087891</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">17.096134185791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8921222686768</t>
+    <t xml:space="preserve">16.8921203613281</t>
   </si>
   <si>
     <t xml:space="preserve">17.2366733551025</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">17.7671012878418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0753841400146</t>
+    <t xml:space="preserve">18.0753860473633</t>
   </si>
   <si>
     <t xml:space="preserve">18.4698085784912</t>
@@ -2462,79 +2462,79 @@
     <t xml:space="preserve">18.5060768127441</t>
   </si>
   <si>
-    <t xml:space="preserve">18.723690032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.71462059021</t>
+    <t xml:space="preserve">18.7236881256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7146224975586</t>
   </si>
   <si>
     <t xml:space="preserve">18.2703285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1887245178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.57861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.959436416626</t>
+    <t xml:space="preserve">18.1887264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5786151885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9594345092773</t>
   </si>
   <si>
     <t xml:space="preserve">18.7690238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7418231964111</t>
+    <t xml:space="preserve">18.7418251037598</t>
   </si>
   <si>
     <t xml:space="preserve">18.7780895233154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2223834991455</t>
+    <t xml:space="preserve">19.2223854064941</t>
   </si>
   <si>
     <t xml:space="preserve">19.7120094299316</t>
   </si>
   <si>
-    <t xml:space="preserve">19.521598815918</t>
+    <t xml:space="preserve">19.5216007232666</t>
   </si>
   <si>
     <t xml:space="preserve">19.8117485046387</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490623474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3130531311035</t>
+    <t xml:space="preserve">19.4490604400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3130550384521</t>
   </si>
   <si>
     <t xml:space="preserve">18.7962245941162</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4970111846924</t>
+    <t xml:space="preserve">18.4970073699951</t>
   </si>
   <si>
     <t xml:space="preserve">17.1732044219971</t>
   </si>
   <si>
-    <t xml:space="preserve">17.422550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8033695220947</t>
+    <t xml:space="preserve">17.4225521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8033714294434</t>
   </si>
   <si>
     <t xml:space="preserve">17.9121761322021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0391178131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9892482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0663166046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8596973419189</t>
+    <t xml:space="preserve">18.039119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9892463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0663185119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8596954345703</t>
   </si>
   <si>
     <t xml:space="preserve">18.9050312042236</t>
@@ -2546,28 +2546,28 @@
     <t xml:space="preserve">18.3791370391846</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4399948120117</t>
+    <t xml:space="preserve">19.4399929046631</t>
   </si>
   <si>
     <t xml:space="preserve">18.9685020446777</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0863761901855</t>
+    <t xml:space="preserve">19.0863742828369</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951808929443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5760021209717</t>
+    <t xml:space="preserve">19.576000213623</t>
   </si>
   <si>
     <t xml:space="preserve">19.6394729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4218578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7392101287842</t>
+    <t xml:space="preserve">19.4218597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7392082214355</t>
   </si>
   <si>
     <t xml:space="preserve">19.94775390625</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">19.8661499023438</t>
   </si>
   <si>
-    <t xml:space="preserve">19.485330581665</t>
+    <t xml:space="preserve">19.4853286743164</t>
   </si>
   <si>
     <t xml:space="preserve">19.6757411956787</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">19.2949180603027</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2677192687988</t>
+    <t xml:space="preserve">19.2677173614502</t>
   </si>
   <si>
     <t xml:space="preserve">19.5941371917725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.857084274292</t>
+    <t xml:space="preserve">19.8570823669434</t>
   </si>
   <si>
     <t xml:space="preserve">19.4127902984619</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">18.6602172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">18.533275604248</t>
+    <t xml:space="preserve">18.5332775115967</t>
   </si>
   <si>
     <t xml:space="preserve">18.9322319030762</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">19.4762630462646</t>
   </si>
   <si>
-    <t xml:space="preserve">20.047492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0112247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9658870697021</t>
+    <t xml:space="preserve">20.0474967956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0112266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.965892791748</t>
   </si>
   <si>
     <t xml:space="preserve">20.3376445770264</t>
@@ -2651,13 +2651,13 @@
     <t xml:space="preserve">22.0332012176514</t>
   </si>
   <si>
-    <t xml:space="preserve">21.697717666626</t>
+    <t xml:space="preserve">21.6977157592773</t>
   </si>
   <si>
     <t xml:space="preserve">22.4049549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8337230682373</t>
+    <t xml:space="preserve">21.8337249755859</t>
   </si>
   <si>
     <t xml:space="preserve">20.981409072876</t>
@@ -2669,37 +2669,37 @@
     <t xml:space="preserve">20.192569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3039894104004</t>
+    <t xml:space="preserve">19.3039875030518</t>
   </si>
   <si>
     <t xml:space="preserve">19.385591506958</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4607429504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6511497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.623950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0300521850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8195838928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4685773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842679977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.811206817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.653223991394</t>
+    <t xml:space="preserve">18.4607391357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6511516571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6239490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.03005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8195819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.468578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6842670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8112077713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6532230377197</t>
   </si>
   <si>
     <t xml:space="preserve">13.741283416748</t>
@@ -2711,25 +2711,25 @@
     <t xml:space="preserve">14.3170480728149</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7341375350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1648292541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6914138793945</t>
+    <t xml:space="preserve">14.7341384887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1648283004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6914129257202</t>
   </si>
   <si>
     <t xml:space="preserve">14.090368270874</t>
   </si>
   <si>
-    <t xml:space="preserve">15.269100189209</t>
+    <t xml:space="preserve">15.2690992355347</t>
   </si>
   <si>
     <t xml:space="preserve">15.0242872238159</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0061502456665</t>
+    <t xml:space="preserve">15.0061492919922</t>
   </si>
   <si>
     <t xml:space="preserve">14.2354440689087</t>
@@ -2738,73 +2738,73 @@
     <t xml:space="preserve">13.8863573074341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2380561828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4783344268799</t>
+    <t xml:space="preserve">13.2380571365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4783363342285</t>
   </si>
   <si>
     <t xml:space="preserve">13.5327386856079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9660415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4511337280273</t>
+    <t xml:space="preserve">12.9660406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.451132774353</t>
   </si>
   <si>
     <t xml:space="preserve">13.8092861175537</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1901082992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2581129074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3695297241211</t>
+    <t xml:space="preserve">14.1901073455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2581119537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3695287704468</t>
   </si>
   <si>
     <t xml:space="preserve">13.8727569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9634275436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7820854187012</t>
+    <t xml:space="preserve">13.9634284973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7820844650269</t>
   </si>
   <si>
     <t xml:space="preserve">14.2943801879883</t>
   </si>
   <si>
-    <t xml:space="preserve">14.448522567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5346603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1512250900269</t>
+    <t xml:space="preserve">14.4485216140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5346593856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1512241363525</t>
   </si>
   <si>
     <t xml:space="preserve">15.3643064498901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6544542312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5683155059814</t>
+    <t xml:space="preserve">15.6544551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5683145523071</t>
   </si>
   <si>
     <t xml:space="preserve">15.346170425415</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6291751861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7768592834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7904634475708</t>
+    <t xml:space="preserve">16.6291732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7768611907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7904615402222</t>
   </si>
   <si>
     <t xml:space="preserve">16.4478282928467</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">17.1097354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0398120880127</t>
+    <t xml:space="preserve">16.0398082733154</t>
   </si>
   <si>
     <t xml:space="preserve">17.2446327209473</t>
@@ -2825,25 +2825,25 @@
     <t xml:space="preserve">16.4030952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8813457489014</t>
+    <t xml:space="preserve">16.8813438415527</t>
   </si>
   <si>
     <t xml:space="preserve">16.7066020965576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2906188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6998920440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9896011352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4515686035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6585063934326</t>
+    <t xml:space="preserve">17.2906169891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.699893951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9896030426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4515705108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.658504486084</t>
   </si>
   <si>
     <t xml:space="preserve">17.6079216003418</t>
@@ -2852,16 +2852,16 @@
     <t xml:space="preserve">17.3549995422363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6309127807617</t>
+    <t xml:space="preserve">17.6309146881104</t>
   </si>
   <si>
     <t xml:space="preserve">17.9850025177002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8884353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6333999633789</t>
+    <t xml:space="preserve">17.8884334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6334018707275</t>
   </si>
   <si>
     <t xml:space="preserve">18.7529640197754</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">18.6701889038086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7090892791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6631050109863</t>
+    <t xml:space="preserve">17.7090873718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6631031036377</t>
   </si>
   <si>
     <t xml:space="preserve">17.4745616912842</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">18.5874137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9093151092529</t>
+    <t xml:space="preserve">18.9093132019043</t>
   </si>
   <si>
     <t xml:space="preserve">18.8173427581787</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">18.7161750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9644985198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7897548675537</t>
+    <t xml:space="preserve">18.9645004272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7897529602051</t>
   </si>
   <si>
     <t xml:space="preserve">19.0104846954346</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">19.0748634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5715084075928</t>
+    <t xml:space="preserve">19.5715065002441</t>
   </si>
   <si>
     <t xml:space="preserve">19.3507785797119</t>
@@ -2924,19 +2924,19 @@
     <t xml:space="preserve">19.9761829376221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9577922821045</t>
+    <t xml:space="preserve">19.9577903747559</t>
   </si>
   <si>
     <t xml:space="preserve">19.6542854309082</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278614044189</t>
+    <t xml:space="preserve">19.7278594970703</t>
   </si>
   <si>
     <t xml:space="preserve">19.930196762085</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4703426361084</t>
+    <t xml:space="preserve">19.4703407287598</t>
   </si>
   <si>
     <t xml:space="preserve">20.0957469940186</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">20.2704925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3256759643555</t>
+    <t xml:space="preserve">20.3256740570068</t>
   </si>
   <si>
     <t xml:space="preserve">21.1534175872803</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9602794647217</t>
+    <t xml:space="preserve">20.960277557373</t>
   </si>
   <si>
     <t xml:space="preserve">21.3281631469727</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">21.0154590606689</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0430526733398</t>
+    <t xml:space="preserve">21.0430488586426</t>
   </si>
   <si>
     <t xml:space="preserve">20.4912242889404</t>
@@ -2975,22 +2975,22 @@
     <t xml:space="preserve">19.8934078216553</t>
   </si>
   <si>
-    <t xml:space="preserve">20.822322845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4176483154297</t>
+    <t xml:space="preserve">20.8223209381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4176464080811</t>
   </si>
   <si>
     <t xml:space="preserve">20.3808574676514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2061100006104</t>
+    <t xml:space="preserve">20.206111907959</t>
   </si>
   <si>
     <t xml:space="preserve">20.5556030273438</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8775005340576</t>
+    <t xml:space="preserve">20.8775024414062</t>
   </si>
   <si>
     <t xml:space="preserve">21.0614452362061</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">20.7303485870361</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7579383850098</t>
+    <t xml:space="preserve">20.7579402923584</t>
   </si>
   <si>
     <t xml:space="preserve">20.7395439147949</t>
@@ -3023,16 +3023,16 @@
     <t xml:space="preserve">21.944372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5580902099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5212993621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0271453857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.604076385498</t>
+    <t xml:space="preserve">21.5580921173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5213012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0271472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6040782928467</t>
   </si>
   <si>
     <t xml:space="preserve">21.8156108856201</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">21.4109382629395</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7420310974121</t>
+    <t xml:space="preserve">21.7420330047607</t>
   </si>
   <si>
     <t xml:space="preserve">22.1191158294678</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5145931243896</t>
+    <t xml:space="preserve">22.514591217041</t>
   </si>
   <si>
     <t xml:space="preserve">22.6341571807861</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">22.6433544158936</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3674373626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4410171508789</t>
+    <t xml:space="preserve">22.3674392700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4410152435303</t>
   </si>
   <si>
     <t xml:space="preserve">22.2294826507568</t>
@@ -3074,40 +3074,40 @@
     <t xml:space="preserve">22.4870014190674</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9008731842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8732795715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8456916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2135753631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2411689758301</t>
+    <t xml:space="preserve">22.9008712768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8732814788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8456897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2135772705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2411670684814</t>
   </si>
   <si>
     <t xml:space="preserve">23.6550369262695</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5262794494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5722637176514</t>
+    <t xml:space="preserve">23.5262775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5722618103027</t>
   </si>
   <si>
     <t xml:space="preserve">24.0045299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7194175720215</t>
+    <t xml:space="preserve">23.7194194793701</t>
   </si>
   <si>
     <t xml:space="preserve">24.3356246948242</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3264312744141</t>
+    <t xml:space="preserve">24.3264293670654</t>
   </si>
   <si>
     <t xml:space="preserve">23.875768661499</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">24.1700782775879</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5998573303223</t>
+    <t xml:space="preserve">23.5998554229736</t>
   </si>
   <si>
     <t xml:space="preserve">22.6525478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7261238098145</t>
+    <t xml:space="preserve">22.7261257171631</t>
   </si>
   <si>
     <t xml:space="preserve">22.9560565948486</t>
@@ -3140,37 +3140,37 @@
     <t xml:space="preserve">21.6500644683838</t>
   </si>
   <si>
-    <t xml:space="preserve">21.466121673584</t>
+    <t xml:space="preserve">21.4661197662354</t>
   </si>
   <si>
     <t xml:space="preserve">22.0823287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5881690979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0413150787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0112380981445</t>
+    <t xml:space="preserve">22.588171005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.041316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0112400054932</t>
   </si>
   <si>
     <t xml:space="preserve">23.1216049194336</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6274471282959</t>
+    <t xml:space="preserve">23.6274490356445</t>
   </si>
   <si>
     <t xml:space="preserve">24.2988376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9677391052246</t>
+    <t xml:space="preserve">23.9677410125732</t>
   </si>
   <si>
     <t xml:space="preserve">23.3607292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8665733337402</t>
+    <t xml:space="preserve">23.8665714263916</t>
   </si>
   <si>
     <t xml:space="preserve">23.9217567443848</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">24.4459934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0965023040771</t>
+    <t xml:space="preserve">24.0965042114258</t>
   </si>
   <si>
     <t xml:space="preserve">24.7403011322021</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">25.2277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8966503143311</t>
+    <t xml:space="preserve">24.8966522216797</t>
   </si>
   <si>
     <t xml:space="preserve">24.4092044830322</t>
@@ -3200,43 +3200,43 @@
     <t xml:space="preserve">24.5471630096436</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0622024536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5655536651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6391315460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6023426055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8874549865723</t>
+    <t xml:space="preserve">25.0622005462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5655555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6391334533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6023445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8874530792236</t>
   </si>
   <si>
     <t xml:space="preserve">25.3105220794678</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5680408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0805950164795</t>
+    <t xml:space="preserve">25.5680446624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0805969238281</t>
   </si>
   <si>
     <t xml:space="preserve">25.3841018676758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.503662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3749046325684</t>
+    <t xml:space="preserve">25.5036640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3749027252197</t>
   </si>
   <si>
     <t xml:space="preserve">25.7151966094971</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9359302520752</t>
+    <t xml:space="preserve">25.9359283447266</t>
   </si>
   <si>
     <t xml:space="preserve">26.6257133483887</t>
@@ -3248,16 +3248,16 @@
     <t xml:space="preserve">26.7452754974365</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8740367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0119953155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5546245574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2811965942383</t>
+    <t xml:space="preserve">26.8740348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0119972229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5546264648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2811985015869</t>
   </si>
   <si>
     <t xml:space="preserve">27.9225101470947</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">26.5521373748779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8715476989746</t>
+    <t xml:space="preserve">25.8715496063232</t>
   </si>
   <si>
     <t xml:space="preserve">26.1106719970703</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">26.0278987884521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7519855499268</t>
+    <t xml:space="preserve">25.7519874572754</t>
   </si>
   <si>
     <t xml:space="preserve">25.6876049041748</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">24.7127094268799</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2804431915283</t>
+    <t xml:space="preserve">24.280445098877</t>
   </si>
   <si>
     <t xml:space="preserve">25.1449737548828</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">25.0346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2369480133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6968059539795</t>
+    <t xml:space="preserve">25.2369499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6968040466309</t>
   </si>
   <si>
     <t xml:space="preserve">26.0462951660156</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">26.1198711395264</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0003108978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9635200500488</t>
+    <t xml:space="preserve">26.0003089904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9635181427002</t>
   </si>
   <si>
     <t xml:space="preserve">25.6600131988525</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">25.0530033111572</t>
   </si>
   <si>
-    <t xml:space="preserve">24.593147277832</t>
+    <t xml:space="preserve">24.5931453704834</t>
   </si>
   <si>
     <t xml:space="preserve">24.390811920166</t>
@@ -3353,16 +3353,16 @@
     <t xml:space="preserve">24.5563583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5195693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0162162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9150485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9058475494385</t>
+    <t xml:space="preserve">24.5195713043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0162143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9150466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9058494567871</t>
   </si>
   <si>
     <t xml:space="preserve">24.0137271881104</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">25.2001571655273</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2620468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6734313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5446720123291</t>
+    <t xml:space="preserve">24.2620487213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.673433303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5446739196777</t>
   </si>
   <si>
     <t xml:space="preserve">23.6918258666992</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">23.3055477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5170783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7838020324707</t>
+    <t xml:space="preserve">23.5170803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7838001251221</t>
   </si>
   <si>
     <t xml:space="preserve">24.1056976318359</t>
@@ -3407,25 +3407,25 @@
     <t xml:space="preserve">24.5287647247314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8138771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8322734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9886226654053</t>
+    <t xml:space="preserve">24.8138790130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8322715759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9886245727539</t>
   </si>
   <si>
     <t xml:space="preserve">25.4852676391602</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7703800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6416187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8414707183838</t>
+    <t xml:space="preserve">25.7703819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6416168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8414688110352</t>
   </si>
   <si>
     <t xml:space="preserve">24.6943168640137</t>
@@ -3434,10 +3434,10 @@
     <t xml:space="preserve">25.1081867218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9518356323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3381156921387</t>
+    <t xml:space="preserve">24.9518337249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.33811378479</t>
   </si>
   <si>
     <t xml:space="preserve">24.4919757843018</t>
@@ -3455,37 +3455,37 @@
     <t xml:space="preserve">23.9585418701172</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4000072479248</t>
+    <t xml:space="preserve">24.4000091552734</t>
   </si>
   <si>
     <t xml:space="preserve">23.949348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7954845428467</t>
+    <t xml:space="preserve">24.7954807281494</t>
   </si>
   <si>
     <t xml:space="preserve">24.2252616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3197193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4693622589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4325733184814</t>
+    <t xml:space="preserve">25.3197212219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4693641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4325752258301</t>
   </si>
   <si>
     <t xml:space="preserve">26.2762203216553</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3323879241943</t>
+    <t xml:space="preserve">26.332389831543</t>
   </si>
   <si>
     <t xml:space="preserve">26.5476913452148</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1826133728027</t>
+    <t xml:space="preserve">26.1826114654541</t>
   </si>
   <si>
     <t xml:space="preserve">26.1919727325439</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">27.5867576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7926979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7084503173828</t>
+    <t xml:space="preserve">27.7926998138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7084522247314</t>
   </si>
   <si>
     <t xml:space="preserve">27.8769493103027</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">27.3340110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2872047424316</t>
+    <t xml:space="preserve">27.2872066497803</t>
   </si>
   <si>
     <t xml:space="preserve">27.3808174133301</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">27.1935977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1655158996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9237499237061</t>
+    <t xml:space="preserve">27.1655139923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9237518310547</t>
   </si>
   <si>
     <t xml:space="preserve">27.8395023345947</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">28.4011611938477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5602970123291</t>
+    <t xml:space="preserve">28.5602989196777</t>
   </si>
   <si>
     <t xml:space="preserve">28.3075523376465</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">28.6819877624512</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2981910705566</t>
+    <t xml:space="preserve">28.298189163208</t>
   </si>
   <si>
     <t xml:space="preserve">28.3169116973877</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">28.7568778991699</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9799194335938</t>
+    <t xml:space="preserve">27.9799175262451</t>
   </si>
   <si>
     <t xml:space="preserve">28.5696582794189</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">28.4198837280273</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4760494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6710071563721</t>
+    <t xml:space="preserve">28.4760513305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6710052490234</t>
   </si>
   <si>
     <t xml:space="preserve">28.1203327178955</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">28.1390552520752</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2888298034668</t>
+    <t xml:space="preserve">28.2888278961182</t>
   </si>
   <si>
     <t xml:space="preserve">28.4854106903076</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">28.3637161254883</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7849597930908</t>
+    <t xml:space="preserve">28.7849617004395</t>
   </si>
   <si>
     <t xml:space="preserve">28.8785705566406</t>
@@ -3638,10 +3638,10 @@
     <t xml:space="preserve">29.3934230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2359085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3201580047607</t>
+    <t xml:space="preserve">30.2359104156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3201560974121</t>
   </si>
   <si>
     <t xml:space="preserve">30.1797466278076</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">29.7585010528564</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8053035736084</t>
+    <t xml:space="preserve">29.805305480957</t>
   </si>
   <si>
     <t xml:space="preserve">29.5806427001953</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">29.8708324432373</t>
   </si>
   <si>
-    <t xml:space="preserve">29.908275604248</t>
+    <t xml:space="preserve">29.9082775115967</t>
   </si>
   <si>
     <t xml:space="preserve">29.8333892822266</t>
@@ -3686,10 +3686,10 @@
     <t xml:space="preserve">30.2171878814697</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4044075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3856868743896</t>
+    <t xml:space="preserve">30.4044055938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.385684967041</t>
   </si>
   <si>
     <t xml:space="preserve">30.8630962371826</t>
@@ -3704,16 +3704,16 @@
     <t xml:space="preserve">30.5448246002197</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4980201721191</t>
+    <t xml:space="preserve">30.4980182647705</t>
   </si>
   <si>
     <t xml:space="preserve">30.4699325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7133197784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1142139434814</t>
+    <t xml:space="preserve">30.713321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1142158508301</t>
   </si>
   <si>
     <t xml:space="preserve">30.1891059875488</t>
@@ -3725,13 +3725,13 @@
     <t xml:space="preserve">29.3185367584229</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0299701690674</t>
+    <t xml:space="preserve">30.029972076416</t>
   </si>
   <si>
     <t xml:space="preserve">30.3482398986816</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6742534637451</t>
+    <t xml:space="preserve">29.6742515563965</t>
   </si>
   <si>
     <t xml:space="preserve">28.9534606933594</t>
@@ -3740,28 +3740,28 @@
     <t xml:space="preserve">28.8130435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2420272827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5212326049805</t>
+    <t xml:space="preserve">28.2420253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5212306976318</t>
   </si>
   <si>
     <t xml:space="preserve">27.4837875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0267200469971</t>
+    <t xml:space="preserve">28.0267219543457</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.661642074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6445465087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.224925994873</t>
+    <t xml:space="preserve">27.6616439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6445484161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2249240875244</t>
   </si>
   <si>
     <t xml:space="preserve">29.2717304229736</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">29.7304191589355</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1610221862793</t>
+    <t xml:space="preserve">30.1610240936279</t>
   </si>
   <si>
     <t xml:space="preserve">30.4792976379395</t>
@@ -3785,19 +3785,19 @@
     <t xml:space="preserve">30.5916271209717</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3669624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6384315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6103496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3030624389648</t>
+    <t xml:space="preserve">30.36696434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6384296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6103477478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7694816589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3030586242676</t>
   </si>
   <si>
     <t xml:space="preserve">30.9286212921143</t>
@@ -3806,10 +3806,10 @@
     <t xml:space="preserve">31.1626472473145</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6681423187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8553504943848</t>
+    <t xml:space="preserve">31.6681385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.855354309082</t>
   </si>
   <si>
     <t xml:space="preserve">31.4341163635254</t>
@@ -3839,22 +3839,22 @@
     <t xml:space="preserve">31.9489650726318</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6962184906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1081008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6945953369141</t>
+    <t xml:space="preserve">31.6962223052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1081047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6945972442627</t>
   </si>
   <si>
     <t xml:space="preserve">31.3124217987061</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7320461273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5822639465332</t>
+    <t xml:space="preserve">30.7320442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5822620391846</t>
   </si>
   <si>
     <t xml:space="preserve">30.8911781311035</t>
@@ -3878,13 +3878,13 @@
     <t xml:space="preserve">30.1516609191895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5525588989258</t>
+    <t xml:space="preserve">29.5525608062744</t>
   </si>
   <si>
     <t xml:space="preserve">29.7023334503174</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7507629394531</t>
+    <t xml:space="preserve">30.7507610321045</t>
   </si>
   <si>
     <t xml:space="preserve">30.9754257202148</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">30.9660663604736</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2936973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2468929290771</t>
+    <t xml:space="preserve">31.293701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2468967437744</t>
   </si>
   <si>
     <t xml:space="preserve">31.2656173706055</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">31.6026096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7804718017578</t>
+    <t xml:space="preserve">31.7804679870605</t>
   </si>
   <si>
     <t xml:space="preserve">31.3779468536377</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">30.5073757171631</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9721832275391</t>
+    <t xml:space="preserve">28.9721813201904</t>
   </si>
   <si>
     <t xml:space="preserve">27.6335620880127</t>
@@ -3950,10 +3950,10 @@
     <t xml:space="preserve">27.118709564209</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9298686981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.042200088501</t>
+    <t xml:space="preserve">25.9298667907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0421981811523</t>
   </si>
   <si>
     <t xml:space="preserve">26.8191585540771</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">26.1077251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5399532318115</t>
+    <t xml:space="preserve">27.5399551391602</t>
   </si>
   <si>
     <t xml:space="preserve">28.5415744781494</t>
@@ -3995,10 +3995,10 @@
     <t xml:space="preserve">27.4463424682617</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9766731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.13743019104</t>
+    <t xml:space="preserve">25.9766712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1374282836914</t>
   </si>
   <si>
     <t xml:space="preserve">26.9502124786377</t>
@@ -4019,10 +4019,10 @@
     <t xml:space="preserve">28.7100734710693</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0377063751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.121955871582</t>
+    <t xml:space="preserve">29.0377082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1219577789307</t>
   </si>
   <si>
     <t xml:space="preserve">29.1406764984131</t>
@@ -4049,13 +4049,13 @@
     <t xml:space="preserve">28.9815406799316</t>
   </si>
   <si>
-    <t xml:space="preserve">29.515115737915</t>
+    <t xml:space="preserve">29.5151176452637</t>
   </si>
   <si>
     <t xml:space="preserve">29.3840618133545</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0531826019287</t>
+    <t xml:space="preserve">27.0531806945801</t>
   </si>
   <si>
     <t xml:space="preserve">27.5586738586426</t>
@@ -4064,16 +4064,16 @@
     <t xml:space="preserve">28.8972930908203</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4666881561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4831771850586</t>
+    <t xml:space="preserve">28.4666862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4831790924072</t>
   </si>
   <si>
     <t xml:space="preserve">29.32204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">28.931209564209</t>
+    <t xml:space="preserve">28.9312076568604</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549480438232</t>
@@ -4085,10 +4085,10 @@
     <t xml:space="preserve">29.2171840667725</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5222225189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7605381011963</t>
+    <t xml:space="preserve">29.5222244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7605361938477</t>
   </si>
   <si>
     <t xml:space="preserve">28.6452312469482</t>
@@ -4127,10 +4127,10 @@
     <t xml:space="preserve">26.96750831604</t>
   </si>
   <si>
-    <t xml:space="preserve">27.215353012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7682399749756</t>
+    <t xml:space="preserve">27.2153549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.768238067627</t>
   </si>
   <si>
     <t xml:space="preserve">27.5299263000488</t>
@@ -4139,10 +4139,10 @@
     <t xml:space="preserve">27.8635654449463</t>
   </si>
   <si>
-    <t xml:space="preserve">27.730110168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2829990386963</t>
+    <t xml:space="preserve">27.7301120758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2829971313477</t>
   </si>
   <si>
     <t xml:space="preserve">28.3592586517334</t>
@@ -4157,10 +4157,10 @@
     <t xml:space="preserve">28.6547660827637</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9207630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2258014678955</t>
+    <t xml:space="preserve">27.9207611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2258033752441</t>
   </si>
   <si>
     <t xml:space="preserve">27.8063697814941</t>
@@ -4178,16 +4178,16 @@
     <t xml:space="preserve">28.4450511932373</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6434020996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3860244750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6243381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7950077056885</t>
+    <t xml:space="preserve">26.643404006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3860263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6243362426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7950057983398</t>
   </si>
   <si>
     <t xml:space="preserve">26.4813499450684</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">25.52809715271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0133399963379</t>
+    <t xml:space="preserve">25.0133419036865</t>
   </si>
   <si>
     <t xml:space="preserve">26.0333213806152</t>
@@ -4211,10 +4211,10 @@
     <t xml:space="preserve">26.3002319335938</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9761257171631</t>
+    <t xml:space="preserve">26.4050884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9761276245117</t>
   </si>
   <si>
     <t xml:space="preserve">24.9847431182861</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">24.765495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3937282562256</t>
+    <t xml:space="preserve">24.393726348877</t>
   </si>
   <si>
     <t xml:space="preserve">24.698766708374</t>
@@ -4235,25 +4235,25 @@
     <t xml:space="preserve">25.3374462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9189300537109</t>
+    <t xml:space="preserve">25.9189319610596</t>
   </si>
   <si>
     <t xml:space="preserve">25.1658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2993202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2230567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4795207977295</t>
+    <t xml:space="preserve">25.2993183135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2230548858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4795188903809</t>
   </si>
   <si>
     <t xml:space="preserve">24.9084815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3469791412354</t>
+    <t xml:space="preserve">25.346981048584</t>
   </si>
   <si>
     <t xml:space="preserve">26.2144393920898</t>
@@ -4280,19 +4280,19 @@
     <t xml:space="preserve">28.7882213592529</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5031623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4745616912842</t>
+    <t xml:space="preserve">29.5031604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4745597839355</t>
   </si>
   <si>
     <t xml:space="preserve">29.5508213043213</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6461486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9044399261475</t>
+    <t xml:space="preserve">29.646146774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9044380187988</t>
   </si>
   <si>
     <t xml:space="preserve">29.9893169403076</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">31.7051696777344</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7995853424072</t>
+    <t xml:space="preserve">30.7995834350586</t>
   </si>
   <si>
     <t xml:space="preserve">31.0283622741699</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">30.2085666656494</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3792381286621</t>
+    <t xml:space="preserve">29.3792362213135</t>
   </si>
   <si>
     <t xml:space="preserve">29.5317573547363</t>
@@ -4367,10 +4367,10 @@
     <t xml:space="preserve">30.5326709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3515529632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.389684677124</t>
+    <t xml:space="preserve">30.3515548706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3896827697754</t>
   </si>
   <si>
     <t xml:space="preserve">30.3038921356201</t>
@@ -4385,28 +4385,28 @@
     <t xml:space="preserve">29.2362499237061</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0160846710205</t>
+    <t xml:space="preserve">28.0160865783691</t>
   </si>
   <si>
     <t xml:space="preserve">28.6166343688965</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6738300323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3020610809326</t>
+    <t xml:space="preserve">28.673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3020629882812</t>
   </si>
   <si>
     <t xml:space="preserve">26.9865741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2353363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4927139282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0560455322266</t>
+    <t xml:space="preserve">28.2353343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.492712020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0560474395752</t>
   </si>
   <si>
     <t xml:space="preserve">29.5126914978027</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">29.6842765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2648468017578</t>
+    <t xml:space="preserve">29.2648487091064</t>
   </si>
   <si>
     <t xml:space="preserve">29.7033424377441</t>
@@ -4436,13 +4436,13 @@
     <t xml:space="preserve">30.5422077178955</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9616355895996</t>
+    <t xml:space="preserve">30.961633682251</t>
   </si>
   <si>
     <t xml:space="preserve">30.4945430755615</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6661243438721</t>
+    <t xml:space="preserve">30.6661262512207</t>
   </si>
   <si>
     <t xml:space="preserve">30.8472461700439</t>
@@ -4451,19 +4451,19 @@
     <t xml:space="preserve">31.1236896514893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9434852600098</t>
+    <t xml:space="preserve">31.9434814453125</t>
   </si>
   <si>
     <t xml:space="preserve">31.981616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7242374420166</t>
+    <t xml:space="preserve">31.7242336273193</t>
   </si>
   <si>
     <t xml:space="preserve">31.5717182159424</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4477958679199</t>
+    <t xml:space="preserve">31.4477977752686</t>
   </si>
   <si>
     <t xml:space="preserve">31.6861095428467</t>
@@ -4475,13 +4475,13 @@
     <t xml:space="preserve">30.5231399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9521026611328</t>
+    <t xml:space="preserve">30.9521045684814</t>
   </si>
   <si>
     <t xml:space="preserve">30.5136051177979</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9425716400146</t>
+    <t xml:space="preserve">30.942569732666</t>
   </si>
   <si>
     <t xml:space="preserve">32.5535697937012</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">31.4763946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">32.191333770752</t>
+    <t xml:space="preserve">32.1913299560547</t>
   </si>
   <si>
     <t xml:space="preserve">32.0769424438477</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">31.9244213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1341400146484</t>
+    <t xml:space="preserve">32.1341361999512</t>
   </si>
   <si>
     <t xml:space="preserve">32.2675895690918</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">33.1064529418945</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8404541015625</t>
+    <t xml:space="preserve">33.8404579162598</t>
   </si>
   <si>
     <t xml:space="preserve">33.5926170349121</t>
@@ -4550,40 +4550,40 @@
     <t xml:space="preserve">33.9167213439941</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9357795715332</t>
+    <t xml:space="preserve">33.9357833862305</t>
   </si>
   <si>
     <t xml:space="preserve">33.1445846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3543014526367</t>
+    <t xml:space="preserve">33.354305267334</t>
   </si>
   <si>
     <t xml:space="preserve">33.6116752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4686889648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6021461486816</t>
+    <t xml:space="preserve">33.468692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6021423339844</t>
   </si>
   <si>
     <t xml:space="preserve">33.3161697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5544853210449</t>
+    <t xml:space="preserve">33.5544815063477</t>
   </si>
   <si>
     <t xml:space="preserve">33.6784057617188</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3066329956055</t>
+    <t xml:space="preserve">33.3066368103027</t>
   </si>
   <si>
     <t xml:space="preserve">33.6593399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0397262573242</t>
+    <t xml:space="preserve">33.039722442627</t>
   </si>
   <si>
     <t xml:space="preserve">33.7260665893555</t>
@@ -4595,13 +4595,13 @@
     <t xml:space="preserve">32.2866554260254</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9729995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3733596801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.953929901123</t>
+    <t xml:space="preserve">32.9729957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.373363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9539337158203</t>
   </si>
   <si>
     <t xml:space="preserve">33.3638305664062</t>
@@ -4610,19 +4610,19 @@
     <t xml:space="preserve">33.4114952087402</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5830764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0311088562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7937088012695</t>
+    <t xml:space="preserve">33.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0311126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7937126159668</t>
   </si>
   <si>
     <t xml:space="preserve">35.0892181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5649261474609</t>
+    <t xml:space="preserve">34.5649299621582</t>
   </si>
   <si>
     <t xml:space="preserve">35.2512741088867</t>
@@ -4637,10 +4637,10 @@
     <t xml:space="preserve">35.5372467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5753784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7469635009766</t>
+    <t xml:space="preserve">35.5753746032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7469596862793</t>
   </si>
   <si>
     <t xml:space="preserve">35.3942604064941</t>
@@ -4649,25 +4649,25 @@
     <t xml:space="preserve">35.6516380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1091995239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9852752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7088279724121</t>
+    <t xml:space="preserve">36.109203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.985279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7088317871094</t>
   </si>
   <si>
     <t xml:space="preserve">35.2036094665527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5944404602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9843597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5563125610352</t>
+    <t xml:space="preserve">35.5944442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9843635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5563087463379</t>
   </si>
   <si>
     <t xml:space="preserve">35.3370628356934</t>
@@ -4676,16 +4676,16 @@
     <t xml:space="preserve">35.8327560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1568603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.937614440918</t>
+    <t xml:space="preserve">36.1568641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9376182556152</t>
   </si>
   <si>
     <t xml:space="preserve">35.270336151123</t>
   </si>
   <si>
-    <t xml:space="preserve">34.831844329834</t>
+    <t xml:space="preserve">34.8318405151367</t>
   </si>
   <si>
     <t xml:space="preserve">34.4410095214844</t>
@@ -4694,13 +4694,13 @@
     <t xml:space="preserve">34.5839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1454963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8413696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6697845458984</t>
+    <t xml:space="preserve">34.1455001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8413734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6697883605957</t>
   </si>
   <si>
     <t xml:space="preserve">34.9557647705078</t>
@@ -4739,7 +4739,7 @@
     <t xml:space="preserve">34.2312927246094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8881187438965</t>
+    <t xml:space="preserve">33.8881225585938</t>
   </si>
   <si>
     <t xml:space="preserve">34.3552131652832</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">35.108283996582</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1178169250488</t>
+    <t xml:space="preserve">35.1178131103516</t>
   </si>
   <si>
     <t xml:space="preserve">34.7746429443359</t>
@@ -4763,25 +4763,25 @@
     <t xml:space="preserve">36.5953559875488</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8908653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2235870361328</t>
+    <t xml:space="preserve">36.8908615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2235908508301</t>
   </si>
   <si>
     <t xml:space="preserve">35.9566802978516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.946231842041</t>
+    <t xml:space="preserve">34.9462280273438</t>
   </si>
   <si>
     <t xml:space="preserve">35.3656616210938</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4037933349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5086517333984</t>
+    <t xml:space="preserve">35.4037895202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5086479187012</t>
   </si>
   <si>
     <t xml:space="preserve">35.3847236633301</t>
@@ -5205,9 +5205,6 @@
   </si>
   <si>
     <t xml:space="preserve">34.9451103210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2235908508301</t>
   </si>
   <si>
     <t xml:space="preserve">36.1945304870605</t>
@@ -59326,7 +59323,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2021" t="s">
-        <v>1731</v>
+        <v>1584</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -59352,7 +59349,7 @@
         <v>37.3699989318848</v>
       </c>
       <c r="G2022" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -59378,7 +59375,7 @@
         <v>38.5200004577637</v>
       </c>
       <c r="G2023" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -59404,7 +59401,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2024" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -59430,7 +59427,7 @@
         <v>38.8699989318848</v>
       </c>
       <c r="G2025" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -59456,7 +59453,7 @@
         <v>38.3199996948242</v>
       </c>
       <c r="G2026" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -59482,7 +59479,7 @@
         <v>39.0699996948242</v>
       </c>
       <c r="G2027" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -59508,7 +59505,7 @@
         <v>39.4900016784668</v>
       </c>
       <c r="G2028" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -59534,7 +59531,7 @@
         <v>39.8400001525879</v>
       </c>
       <c r="G2029" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -59560,7 +59557,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G2030" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -59586,7 +59583,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G2031" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -59612,7 +59609,7 @@
         <v>40.689998626709</v>
       </c>
       <c r="G2032" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -59638,7 +59635,7 @@
         <v>40.9099998474121</v>
       </c>
       <c r="G2033" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -59664,7 +59661,7 @@
         <v>41.2400016784668</v>
       </c>
       <c r="G2034" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -59690,7 +59687,7 @@
         <v>41.1300010681152</v>
       </c>
       <c r="G2035" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -59716,7 +59713,7 @@
         <v>41.1699981689453</v>
       </c>
       <c r="G2036" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -59742,7 +59739,7 @@
         <v>41.6599998474121</v>
       </c>
       <c r="G2037" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -59768,7 +59765,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2038" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -59794,7 +59791,7 @@
         <v>40.310001373291</v>
       </c>
       <c r="G2039" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -59820,7 +59817,7 @@
         <v>40.7400016784668</v>
       </c>
       <c r="G2040" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -59846,7 +59843,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G2041" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -59872,7 +59869,7 @@
         <v>40.9000015258789</v>
       </c>
       <c r="G2042" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -59898,7 +59895,7 @@
         <v>40.4099998474121</v>
       </c>
       <c r="G2043" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -59924,7 +59921,7 @@
         <v>39.810001373291</v>
       </c>
       <c r="G2044" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -59950,7 +59947,7 @@
         <v>41.1800003051758</v>
       </c>
       <c r="G2045" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -59976,7 +59973,7 @@
         <v>40.8400001525879</v>
       </c>
       <c r="G2046" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -60002,7 +59999,7 @@
         <v>40.75</v>
       </c>
       <c r="G2047" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -60028,7 +60025,7 @@
         <v>40.1500015258789</v>
       </c>
       <c r="G2048" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -60054,7 +60051,7 @@
         <v>40.7000007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -60080,7 +60077,7 @@
         <v>40.1300010681152</v>
       </c>
       <c r="G2050" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -60106,7 +60103,7 @@
         <v>40.5400009155273</v>
       </c>
       <c r="G2051" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -60132,7 +60129,7 @@
         <v>40.0699996948242</v>
       </c>
       <c r="G2052" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -60158,7 +60155,7 @@
         <v>40.7799987792969</v>
       </c>
       <c r="G2053" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -60184,7 +60181,7 @@
         <v>40.5499992370605</v>
       </c>
       <c r="G2054" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -60210,7 +60207,7 @@
         <v>41.0400009155273</v>
       </c>
       <c r="G2055" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -60236,7 +60233,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G2056" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -60262,7 +60259,7 @@
         <v>40.9300003051758</v>
       </c>
       <c r="G2057" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -60288,7 +60285,7 @@
         <v>40.9900016784668</v>
       </c>
       <c r="G2058" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -60314,7 +60311,7 @@
         <v>41.1100006103516</v>
       </c>
       <c r="G2059" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -60340,7 +60337,7 @@
         <v>41.2999992370605</v>
       </c>
       <c r="G2060" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -60366,7 +60363,7 @@
         <v>40.9099998474121</v>
       </c>
       <c r="G2061" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -60392,7 +60389,7 @@
         <v>41.7299995422363</v>
       </c>
       <c r="G2062" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -60418,7 +60415,7 @@
         <v>41.7700004577637</v>
       </c>
       <c r="G2063" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -60444,7 +60441,7 @@
         <v>41.7299995422363</v>
       </c>
       <c r="G2064" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -60470,7 +60467,7 @@
         <v>42.0299987792969</v>
       </c>
       <c r="G2065" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -60496,7 +60493,7 @@
         <v>41.9300003051758</v>
       </c>
       <c r="G2066" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -60522,7 +60519,7 @@
         <v>41.1699981689453</v>
       </c>
       <c r="G2067" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -60548,7 +60545,7 @@
         <v>41</v>
       </c>
       <c r="G2068" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -60574,7 +60571,7 @@
         <v>42.9300003051758</v>
       </c>
       <c r="G2069" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -60600,7 +60597,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G2070" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -60626,7 +60623,7 @@
         <v>43.2400016784668</v>
       </c>
       <c r="G2071" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -60652,7 +60649,7 @@
         <v>43.6300010681152</v>
       </c>
       <c r="G2072" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -60678,7 +60675,7 @@
         <v>44.0800018310547</v>
       </c>
       <c r="G2073" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -60704,7 +60701,7 @@
         <v>44.6399993896484</v>
       </c>
       <c r="G2074" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -60730,7 +60727,7 @@
         <v>45.2299995422363</v>
       </c>
       <c r="G2075" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -60756,7 +60753,7 @@
         <v>44.2900009155273</v>
       </c>
       <c r="G2076" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -60782,7 +60779,7 @@
         <v>44.2999992370605</v>
       </c>
       <c r="G2077" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -60808,7 +60805,7 @@
         <v>44.8899993896484</v>
       </c>
       <c r="G2078" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -60834,7 +60831,7 @@
         <v>46.0499992370605</v>
       </c>
       <c r="G2079" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -60860,7 +60857,7 @@
         <v>46.0099983215332</v>
       </c>
       <c r="G2080" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -60886,7 +60883,7 @@
         <v>46.1800003051758</v>
       </c>
       <c r="G2081" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -60912,7 +60909,7 @@
         <v>46.3499984741211</v>
       </c>
       <c r="G2082" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -60938,7 +60935,7 @@
         <v>46.9799995422363</v>
       </c>
       <c r="G2083" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -60964,7 +60961,7 @@
         <v>46.9700012207031</v>
       </c>
       <c r="G2084" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -60990,7 +60987,7 @@
         <v>46.8499984741211</v>
       </c>
       <c r="G2085" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -61016,7 +61013,7 @@
         <v>45.8899993896484</v>
       </c>
       <c r="G2086" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -61042,7 +61039,7 @@
         <v>46.9300003051758</v>
       </c>
       <c r="G2087" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -61068,7 +61065,7 @@
         <v>47.3800010681152</v>
       </c>
       <c r="G2088" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -61094,7 +61091,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G2089" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -61120,7 +61117,7 @@
         <v>47.6100006103516</v>
       </c>
       <c r="G2090" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -61146,7 +61143,7 @@
         <v>47.9599990844727</v>
       </c>
       <c r="G2091" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -61172,7 +61169,7 @@
         <v>48.7200012207031</v>
       </c>
       <c r="G2092" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -61198,7 +61195,7 @@
         <v>49.4099998474121</v>
       </c>
       <c r="G2093" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -61224,7 +61221,7 @@
         <v>49.0099983215332</v>
       </c>
       <c r="G2094" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -61250,7 +61247,7 @@
         <v>49.3899993896484</v>
       </c>
       <c r="G2095" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -61276,7 +61273,7 @@
         <v>49.7799987792969</v>
       </c>
       <c r="G2096" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -61302,7 +61299,7 @@
         <v>49.7200012207031</v>
       </c>
       <c r="G2097" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -61328,7 +61325,7 @@
         <v>48.6800003051758</v>
       </c>
       <c r="G2098" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -61354,7 +61351,7 @@
         <v>48.3899993896484</v>
       </c>
       <c r="G2099" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -61380,7 +61377,7 @@
         <v>47.9199981689453</v>
       </c>
       <c r="G2100" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -61406,7 +61403,7 @@
         <v>48.060001373291</v>
       </c>
       <c r="G2101" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -61432,7 +61429,7 @@
         <v>48.25</v>
       </c>
       <c r="G2102" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -61458,7 +61455,7 @@
         <v>48.2400016784668</v>
       </c>
       <c r="G2103" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -61484,7 +61481,7 @@
         <v>49.1500015258789</v>
       </c>
       <c r="G2104" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -61510,7 +61507,7 @@
         <v>48.3300018310547</v>
       </c>
       <c r="G2105" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -61536,7 +61533,7 @@
         <v>48.5200004577637</v>
       </c>
       <c r="G2106" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -61562,7 +61559,7 @@
         <v>48.2000007629395</v>
       </c>
       <c r="G2107" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -61588,7 +61585,7 @@
         <v>48.5200004577637</v>
       </c>
       <c r="G2108" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -61614,7 +61611,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G2109" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -61640,7 +61637,7 @@
         <v>49.4199981689453</v>
       </c>
       <c r="G2110" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -61666,7 +61663,7 @@
         <v>48.6800003051758</v>
       </c>
       <c r="G2111" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -61692,7 +61689,7 @@
         <v>50.2200012207031</v>
       </c>
       <c r="G2112" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -61718,7 +61715,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G2113" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -61744,7 +61741,7 @@
         <v>49.5800018310547</v>
       </c>
       <c r="G2114" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -61770,7 +61767,7 @@
         <v>49.9700012207031</v>
       </c>
       <c r="G2115" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -61796,7 +61793,7 @@
         <v>50.8199996948242</v>
       </c>
       <c r="G2116" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -61822,7 +61819,7 @@
         <v>49.439998626709</v>
       </c>
       <c r="G2117" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -61848,7 +61845,7 @@
         <v>51.1800003051758</v>
       </c>
       <c r="G2118" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -61874,7 +61871,7 @@
         <v>51.1599998474121</v>
       </c>
       <c r="G2119" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -61900,7 +61897,7 @@
         <v>51.1800003051758</v>
       </c>
       <c r="G2120" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -61926,7 +61923,7 @@
         <v>51.060001373291</v>
       </c>
       <c r="G2121" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -61952,7 +61949,7 @@
         <v>51.5</v>
       </c>
       <c r="G2122" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -61978,7 +61975,7 @@
         <v>52.0400009155273</v>
       </c>
       <c r="G2123" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -62004,7 +62001,7 @@
         <v>52.8600006103516</v>
       </c>
       <c r="G2124" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -62030,7 +62027,7 @@
         <v>52.8400001525879</v>
       </c>
       <c r="G2125" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -62056,7 +62053,7 @@
         <v>54.8199996948242</v>
       </c>
       <c r="G2126" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -62082,7 +62079,7 @@
         <v>56</v>
       </c>
       <c r="G2127" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -62108,7 +62105,7 @@
         <v>55.939998626709</v>
       </c>
       <c r="G2128" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -62134,7 +62131,7 @@
         <v>55.8199996948242</v>
       </c>
       <c r="G2129" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -62160,7 +62157,7 @@
         <v>56.6399993896484</v>
       </c>
       <c r="G2130" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -62186,7 +62183,7 @@
         <v>57.4799995422363</v>
       </c>
       <c r="G2131" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -62212,7 +62209,7 @@
         <v>56.6399993896484</v>
       </c>
       <c r="G2132" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -62238,7 +62235,7 @@
         <v>57.6399993896484</v>
       </c>
       <c r="G2133" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -62264,7 +62261,7 @@
         <v>57.6199989318848</v>
       </c>
       <c r="G2134" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -62290,7 +62287,7 @@
         <v>57.7799987792969</v>
       </c>
       <c r="G2135" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -62316,7 +62313,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G2136" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -62342,7 +62339,7 @@
         <v>59.8199996948242</v>
       </c>
       <c r="G2137" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -62368,7 +62365,7 @@
         <v>60.939998626709</v>
       </c>
       <c r="G2138" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -62394,7 +62391,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G2139" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -62420,7 +62417,7 @@
         <v>58.7599983215332</v>
       </c>
       <c r="G2140" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -62446,7 +62443,7 @@
         <v>59.3199996948242</v>
       </c>
       <c r="G2141" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -62472,7 +62469,7 @@
         <v>60.0200004577637</v>
       </c>
       <c r="G2142" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -62498,7 +62495,7 @@
         <v>60.0800018310547</v>
       </c>
       <c r="G2143" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -62524,7 +62521,7 @@
         <v>58.8800010681152</v>
       </c>
       <c r="G2144" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -62550,7 +62547,7 @@
         <v>58.6199989318848</v>
       </c>
       <c r="G2145" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -62576,7 +62573,7 @@
         <v>59.0400009155273</v>
       </c>
       <c r="G2146" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -62602,7 +62599,7 @@
         <v>58.5200004577637</v>
       </c>
       <c r="G2147" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -62628,7 +62625,7 @@
         <v>57.8800010681152</v>
       </c>
       <c r="G2148" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -62654,7 +62651,7 @@
         <v>56.9599990844727</v>
       </c>
       <c r="G2149" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -62680,7 +62677,7 @@
         <v>57.9799995422363</v>
       </c>
       <c r="G2150" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -62706,7 +62703,7 @@
         <v>56.7400016784668</v>
       </c>
       <c r="G2151" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -62732,7 +62729,7 @@
         <v>56.6399993896484</v>
       </c>
       <c r="G2152" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -62758,7 +62755,7 @@
         <v>56.6399993896484</v>
       </c>
       <c r="G2153" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -62784,7 +62781,7 @@
         <v>57.4799995422363</v>
       </c>
       <c r="G2154" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -62810,7 +62807,7 @@
         <v>57.7400016784668</v>
       </c>
       <c r="G2155" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -62836,7 +62833,7 @@
         <v>58.6199989318848</v>
       </c>
       <c r="G2156" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -62862,7 +62859,7 @@
         <v>57.6399993896484</v>
       </c>
       <c r="G2157" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -62888,7 +62885,7 @@
         <v>58.8800010681152</v>
       </c>
       <c r="G2158" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -62914,7 +62911,7 @@
         <v>58</v>
       </c>
       <c r="G2159" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -62940,7 +62937,7 @@
         <v>58</v>
       </c>
       <c r="G2160" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -62966,7 +62963,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G2161" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -62992,7 +62989,7 @@
         <v>57.8199996948242</v>
       </c>
       <c r="G2162" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -63018,7 +63015,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G2163" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -63044,7 +63041,7 @@
         <v>57.8800010681152</v>
       </c>
       <c r="G2164" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -63070,7 +63067,7 @@
         <v>58.7400016784668</v>
       </c>
       <c r="G2165" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -63096,7 +63093,7 @@
         <v>58.6599998474121</v>
       </c>
       <c r="G2166" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -63122,7 +63119,7 @@
         <v>58.2400016784668</v>
       </c>
       <c r="G2167" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -63148,7 +63145,7 @@
         <v>57.7200012207031</v>
       </c>
       <c r="G2168" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -63174,7 +63171,7 @@
         <v>60</v>
       </c>
       <c r="G2169" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -63200,7 +63197,7 @@
         <v>62.060001373291</v>
       </c>
       <c r="G2170" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -63226,7 +63223,7 @@
         <v>63.0800018310547</v>
       </c>
       <c r="G2171" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -63252,7 +63249,7 @@
         <v>62.6199989318848</v>
       </c>
       <c r="G2172" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -63278,7 +63275,7 @@
         <v>61.4599990844727</v>
       </c>
       <c r="G2173" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -63304,7 +63301,7 @@
         <v>62.7599983215332</v>
       </c>
       <c r="G2174" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -63330,7 +63327,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G2175" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -63356,7 +63353,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G2176" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -63382,7 +63379,7 @@
         <v>61.060001373291</v>
       </c>
       <c r="G2177" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -63408,7 +63405,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G2178" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -63434,7 +63431,7 @@
         <v>63.3800010681152</v>
       </c>
       <c r="G2179" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -63460,7 +63457,7 @@
         <v>63.4599990844727</v>
       </c>
       <c r="G2180" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -63486,7 +63483,7 @@
         <v>61.5</v>
       </c>
       <c r="G2181" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -63512,7 +63509,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G2182" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -63538,7 +63535,7 @@
         <v>62.2599983215332</v>
       </c>
       <c r="G2183" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -63564,7 +63561,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G2184" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -63590,7 +63587,7 @@
         <v>63.5400009155273</v>
       </c>
       <c r="G2185" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -63616,7 +63613,7 @@
         <v>58.0999984741211</v>
       </c>
       <c r="G2186" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -63642,7 +63639,7 @@
         <v>56.8199996948242</v>
       </c>
       <c r="G2187" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -63668,7 +63665,7 @@
         <v>55.8400001525879</v>
       </c>
       <c r="G2188" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -63694,7 +63691,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G2189" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -63720,7 +63717,7 @@
         <v>58.7400016784668</v>
       </c>
       <c r="G2190" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -63746,7 +63743,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G2191" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -63772,7 +63769,7 @@
         <v>58.7200012207031</v>
       </c>
       <c r="G2192" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -63798,7 +63795,7 @@
         <v>59.060001373291</v>
       </c>
       <c r="G2193" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -63824,7 +63821,7 @@
         <v>59.8199996948242</v>
       </c>
       <c r="G2194" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -63850,7 +63847,7 @@
         <v>60.6399993896484</v>
       </c>
       <c r="G2195" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -63876,7 +63873,7 @@
         <v>61.2200012207031</v>
       </c>
       <c r="G2196" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -63902,7 +63899,7 @@
         <v>61.2999992370605</v>
       </c>
       <c r="G2197" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -63928,7 +63925,7 @@
         <v>61.3600006103516</v>
       </c>
       <c r="G2198" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -63954,7 +63951,7 @@
         <v>61.560001373291</v>
       </c>
       <c r="G2199" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -63980,7 +63977,7 @@
         <v>61.8199996948242</v>
       </c>
       <c r="G2200" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -64006,7 +64003,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G2201" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -64032,7 +64029,7 @@
         <v>61.7200012207031</v>
       </c>
       <c r="G2202" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -64058,7 +64055,7 @@
         <v>61.7200012207031</v>
       </c>
       <c r="G2203" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -64084,7 +64081,7 @@
         <v>62.439998626709</v>
       </c>
       <c r="G2204" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -64110,7 +64107,7 @@
         <v>63.1599998474121</v>
       </c>
       <c r="G2205" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -64136,7 +64133,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G2206" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -64162,7 +64159,7 @@
         <v>63.3800010681152</v>
       </c>
       <c r="G2207" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -64188,7 +64185,7 @@
         <v>63.2999992370605</v>
       </c>
       <c r="G2208" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -64214,7 +64211,7 @@
         <v>62</v>
       </c>
       <c r="G2209" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -64240,7 +64237,7 @@
         <v>61.5999984741211</v>
       </c>
       <c r="G2210" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -64266,7 +64263,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G2211" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -64292,7 +64289,7 @@
         <v>60.4599990844727</v>
       </c>
       <c r="G2212" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -64318,7 +64315,7 @@
         <v>60.5800018310547</v>
       </c>
       <c r="G2213" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -64344,7 +64341,7 @@
         <v>60.5800018310547</v>
       </c>
       <c r="G2214" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -64370,7 +64367,7 @@
         <v>61.0200004577637</v>
       </c>
       <c r="G2215" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -64396,7 +64393,7 @@
         <v>61.939998626709</v>
       </c>
       <c r="G2216" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -64422,7 +64419,7 @@
         <v>61.5200004577637</v>
       </c>
       <c r="G2217" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -64448,7 +64445,7 @@
         <v>62.8400001525879</v>
       </c>
       <c r="G2218" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -64474,7 +64471,7 @@
         <v>63.1800003051758</v>
       </c>
       <c r="G2219" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -64500,7 +64497,7 @@
         <v>65.6800003051758</v>
       </c>
       <c r="G2220" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -64526,7 +64523,7 @@
         <v>65.6800003051758</v>
       </c>
       <c r="G2221" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -64552,7 +64549,7 @@
         <v>65.879997253418</v>
       </c>
       <c r="G2222" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -64578,7 +64575,7 @@
         <v>64.4599990844727</v>
       </c>
       <c r="G2223" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -64604,7 +64601,7 @@
         <v>65.8199996948242</v>
       </c>
       <c r="G2224" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -64630,7 +64627,7 @@
         <v>66.5400009155273</v>
       </c>
       <c r="G2225" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -64656,7 +64653,7 @@
         <v>64.8399963378906</v>
       </c>
       <c r="G2226" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -64682,7 +64679,7 @@
         <v>65.1999969482422</v>
       </c>
       <c r="G2227" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -64708,7 +64705,7 @@
         <v>65.1600036621094</v>
       </c>
       <c r="G2228" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -64734,7 +64731,7 @@
         <v>65.5</v>
       </c>
       <c r="G2229" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -64760,7 +64757,7 @@
         <v>64.9800033569336</v>
       </c>
       <c r="G2230" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -64786,7 +64783,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G2231" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -64812,7 +64809,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G2232" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -64838,7 +64835,7 @@
         <v>65.0800018310547</v>
       </c>
       <c r="G2233" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -64864,7 +64861,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G2234" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -64890,7 +64887,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G2235" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -64916,7 +64913,7 @@
         <v>65.7399978637695</v>
       </c>
       <c r="G2236" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -64942,7 +64939,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G2237" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -64968,7 +64965,7 @@
         <v>65.5</v>
       </c>
       <c r="G2238" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -64994,7 +64991,7 @@
         <v>66.2399978637695</v>
       </c>
       <c r="G2239" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -65020,7 +65017,7 @@
         <v>67.6999969482422</v>
       </c>
       <c r="G2240" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -65046,7 +65043,7 @@
         <v>67.9199981689453</v>
       </c>
       <c r="G2241" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -65072,7 +65069,7 @@
         <v>67.5199966430664</v>
       </c>
       <c r="G2242" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -65098,7 +65095,7 @@
         <v>66.5199966430664</v>
       </c>
       <c r="G2243" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -65124,7 +65121,7 @@
         <v>66.120002746582</v>
       </c>
       <c r="G2244" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -65150,7 +65147,7 @@
         <v>66.9400024414062</v>
       </c>
       <c r="G2245" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -65176,7 +65173,7 @@
         <v>68</v>
       </c>
       <c r="G2246" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -65202,7 +65199,7 @@
         <v>68.5599975585938</v>
       </c>
       <c r="G2247" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -65228,7 +65225,7 @@
         <v>67.7799987792969</v>
       </c>
       <c r="G2248" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -65254,7 +65251,7 @@
         <v>65.3600006103516</v>
       </c>
       <c r="G2249" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -65280,7 +65277,7 @@
         <v>64.8199996948242</v>
       </c>
       <c r="G2250" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -65306,7 +65303,7 @@
         <v>64.5999984741211</v>
       </c>
       <c r="G2251" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -65332,7 +65329,7 @@
         <v>63.8600006103516</v>
       </c>
       <c r="G2252" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -65358,7 +65355,7 @@
         <v>64.0800018310547</v>
       </c>
       <c r="G2253" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -65384,7 +65381,7 @@
         <v>63.2000007629395</v>
       </c>
       <c r="G2254" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -65410,7 +65407,7 @@
         <v>60.8199996948242</v>
       </c>
       <c r="G2255" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -65436,7 +65433,7 @@
         <v>62.1599998474121</v>
       </c>
       <c r="G2256" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -65462,7 +65459,7 @@
         <v>64.2200012207031</v>
       </c>
       <c r="G2257" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -65488,7 +65485,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G2258" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -65514,7 +65511,7 @@
         <v>62.2599983215332</v>
       </c>
       <c r="G2259" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -65540,7 +65537,7 @@
         <v>63</v>
       </c>
       <c r="G2260" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -65566,7 +65563,7 @@
         <v>60.9199981689453</v>
       </c>
       <c r="G2261" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -65592,7 +65589,7 @@
         <v>61.2599983215332</v>
       </c>
       <c r="G2262" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -65618,7 +65615,7 @@
         <v>59.939998626709</v>
       </c>
       <c r="G2263" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -65644,7 +65641,7 @@
         <v>60.560001373291</v>
       </c>
       <c r="G2264" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -65670,7 +65667,7 @@
         <v>61.2200012207031</v>
       </c>
       <c r="G2265" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -65696,7 +65693,7 @@
         <v>61.9199981689453</v>
       </c>
       <c r="G2266" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -65722,7 +65719,7 @@
         <v>62.8199996948242</v>
       </c>
       <c r="G2267" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -65748,7 +65745,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G2268" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -65774,7 +65771,7 @@
         <v>62.1599998474121</v>
       </c>
       <c r="G2269" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -65800,7 +65797,7 @@
         <v>62.560001373291</v>
       </c>
       <c r="G2270" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -65826,7 +65823,7 @@
         <v>62.4199981689453</v>
       </c>
       <c r="G2271" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -65852,7 +65849,7 @@
         <v>63.0400009155273</v>
       </c>
       <c r="G2272" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -65878,7 +65875,7 @@
         <v>64.3600006103516</v>
       </c>
       <c r="G2273" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -65904,7 +65901,7 @@
         <v>64.9599990844727</v>
       </c>
       <c r="G2274" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -65930,7 +65927,7 @@
         <v>64.4000015258789</v>
       </c>
       <c r="G2275" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -65956,7 +65953,7 @@
         <v>64.5</v>
       </c>
       <c r="G2276" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -65982,7 +65979,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G2277" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -66008,7 +66005,7 @@
         <v>62.2200012207031</v>
       </c>
       <c r="G2278" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -66034,7 +66031,7 @@
         <v>63.4000015258789</v>
       </c>
       <c r="G2279" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -66060,7 +66057,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -66086,7 +66083,7 @@
         <v>61.6800003051758</v>
       </c>
       <c r="G2281" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -66112,7 +66109,7 @@
         <v>62.4000015258789</v>
       </c>
       <c r="G2282" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -66138,7 +66135,7 @@
         <v>61.0800018310547</v>
       </c>
       <c r="G2283" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -66164,7 +66161,7 @@
         <v>61.8400001525879</v>
       </c>
       <c r="G2284" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -66190,7 +66187,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G2285" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -66216,7 +66213,7 @@
         <v>61.0800018310547</v>
       </c>
       <c r="G2286" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -66242,7 +66239,7 @@
         <v>61.5400009155273</v>
       </c>
       <c r="G2287" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -66268,7 +66265,7 @@
         <v>62.1199989318848</v>
       </c>
       <c r="G2288" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -66294,7 +66291,7 @@
         <v>61.6599998474121</v>
       </c>
       <c r="G2289" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -66320,7 +66317,7 @@
         <v>63.060001373291</v>
       </c>
       <c r="G2290" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -66346,7 +66343,7 @@
         <v>62.8800010681152</v>
       </c>
       <c r="G2291" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -66372,7 +66369,7 @@
         <v>64.0599975585938</v>
       </c>
       <c r="G2292" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -66398,7 +66395,7 @@
         <v>64.0999984741211</v>
       </c>
       <c r="G2293" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -66424,7 +66421,7 @@
         <v>63.9599990844727</v>
       </c>
       <c r="G2294" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -66450,7 +66447,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G2295" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -66476,7 +66473,7 @@
         <v>65.879997253418</v>
       </c>
       <c r="G2296" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -66502,7 +66499,7 @@
         <v>63.8600006103516</v>
       </c>
       <c r="G2297" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -66528,7 +66525,7 @@
         <v>63.9599990844727</v>
       </c>
       <c r="G2298" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -66554,7 +66551,7 @@
         <v>66.7799987792969</v>
       </c>
       <c r="G2299" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -66580,7 +66577,7 @@
         <v>66.8600006103516</v>
       </c>
       <c r="G2300" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -66606,7 +66603,7 @@
         <v>68.620002746582</v>
       </c>
       <c r="G2301" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -66632,7 +66629,7 @@
         <v>69.1600036621094</v>
       </c>
       <c r="G2302" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -66658,7 +66655,7 @@
         <v>68.5</v>
       </c>
       <c r="G2303" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -66684,7 +66681,7 @@
         <v>70.8399963378906</v>
       </c>
       <c r="G2304" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -66710,7 +66707,7 @@
         <v>71.7799987792969</v>
       </c>
       <c r="G2305" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -66736,7 +66733,7 @@
         <v>72</v>
       </c>
       <c r="G2306" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -66762,7 +66759,7 @@
         <v>65.6999969482422</v>
       </c>
       <c r="G2307" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -66788,7 +66785,7 @@
         <v>63.6199989318848</v>
       </c>
       <c r="G2308" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -66814,7 +66811,7 @@
         <v>65.4400024414062</v>
       </c>
       <c r="G2309" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -66840,7 +66837,7 @@
         <v>66.4599990844727</v>
       </c>
       <c r="G2310" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -66866,7 +66863,7 @@
         <v>67.3399963378906</v>
       </c>
       <c r="G2311" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -66892,7 +66889,7 @@
         <v>65.9599990844727</v>
       </c>
       <c r="G2312" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -66918,7 +66915,7 @@
         <v>64.0800018310547</v>
       </c>
       <c r="G2313" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -66944,7 +66941,7 @@
         <v>62.7799987792969</v>
       </c>
       <c r="G2314" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -66970,7 +66967,7 @@
         <v>63.560001373291</v>
       </c>
       <c r="G2315" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66996,7 +66993,7 @@
         <v>63.3800010681152</v>
       </c>
       <c r="G2316" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -67022,7 +67019,7 @@
         <v>64.3000030517578</v>
       </c>
       <c r="G2317" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -67048,7 +67045,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G2318" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -67074,7 +67071,7 @@
         <v>65.7399978637695</v>
       </c>
       <c r="G2319" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -67100,7 +67097,7 @@
         <v>67.4000015258789</v>
       </c>
       <c r="G2320" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -67126,7 +67123,7 @@
         <v>66.879997253418</v>
       </c>
       <c r="G2321" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -67152,7 +67149,7 @@
         <v>68.9800033569336</v>
       </c>
       <c r="G2322" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -67178,7 +67175,7 @@
         <v>69.2600021362305</v>
       </c>
       <c r="G2323" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -67204,7 +67201,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G2324" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -67230,7 +67227,7 @@
         <v>67.9199981689453</v>
       </c>
       <c r="G2325" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -67256,7 +67253,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G2326" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -67282,7 +67279,7 @@
         <v>65.5999984741211</v>
       </c>
       <c r="G2327" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -67308,7 +67305,7 @@
         <v>63.560001373291</v>
       </c>
       <c r="G2328" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -67334,7 +67331,7 @@
         <v>65.0400009155273</v>
       </c>
       <c r="G2329" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -67360,7 +67357,7 @@
         <v>57.1199989318848</v>
       </c>
       <c r="G2330" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -67386,7 +67383,7 @@
         <v>57.0400009155273</v>
       </c>
       <c r="G2331" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -67412,7 +67409,7 @@
         <v>56.1800003051758</v>
       </c>
       <c r="G2332" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -67438,7 +67435,7 @@
         <v>53.3199996948242</v>
       </c>
       <c r="G2333" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -67464,7 +67461,7 @@
         <v>55.9599990844727</v>
       </c>
       <c r="G2334" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -67490,7 +67487,7 @@
         <v>56.0200004577637</v>
       </c>
       <c r="G2335" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -67516,7 +67513,7 @@
         <v>54.2400016784668</v>
       </c>
       <c r="G2336" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -67542,7 +67539,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G2337" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -67568,7 +67565,7 @@
         <v>53.2000007629395</v>
       </c>
       <c r="G2338" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -67594,7 +67591,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G2339" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -67620,7 +67617,7 @@
         <v>55.4199981689453</v>
       </c>
       <c r="G2340" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -67646,7 +67643,7 @@
         <v>56.8400001525879</v>
       </c>
       <c r="G2341" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -67672,7 +67669,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G2342" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -67698,7 +67695,7 @@
         <v>59.4799995422363</v>
       </c>
       <c r="G2343" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -67724,7 +67721,7 @@
         <v>59.6399993896484</v>
       </c>
       <c r="G2344" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -67750,7 +67747,7 @@
         <v>58</v>
       </c>
       <c r="G2345" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -67776,7 +67773,7 @@
         <v>57.7599983215332</v>
       </c>
       <c r="G2346" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -67802,7 +67799,7 @@
         <v>57.5</v>
       </c>
       <c r="G2347" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -67828,7 +67825,7 @@
         <v>56.7599983215332</v>
       </c>
       <c r="G2348" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -67854,7 +67851,7 @@
         <v>53.2400016784668</v>
       </c>
       <c r="G2349" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -67880,7 +67877,7 @@
         <v>54.060001373291</v>
       </c>
       <c r="G2350" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -67906,7 +67903,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G2351" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -67932,7 +67929,7 @@
         <v>50.3600006103516</v>
       </c>
       <c r="G2352" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -67958,7 +67955,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G2353" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67984,7 +67981,7 @@
         <v>50.6399993896484</v>
       </c>
       <c r="G2354" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -68010,7 +68007,7 @@
         <v>47.4599990844727</v>
       </c>
       <c r="G2355" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -68036,7 +68033,7 @@
         <v>43.2099990844727</v>
       </c>
       <c r="G2356" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -68062,7 +68059,7 @@
         <v>41.1199989318848</v>
       </c>
       <c r="G2357" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -68088,7 +68085,7 @@
         <v>41.8199996948242</v>
       </c>
       <c r="G2358" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -68114,7 +68111,7 @@
         <v>40.6500015258789</v>
       </c>
       <c r="G2359" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -68140,7 +68137,7 @@
         <v>43.7000007629395</v>
       </c>
       <c r="G2360" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -68166,7 +68163,7 @@
         <v>43.2700004577637</v>
       </c>
       <c r="G2361" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -68192,7 +68189,7 @@
         <v>44.75</v>
       </c>
       <c r="G2362" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -68218,7 +68215,7 @@
         <v>45.7299995422363</v>
       </c>
       <c r="G2363" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -68244,7 +68241,7 @@
         <v>44.7099990844727</v>
       </c>
       <c r="G2364" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -68270,7 +68267,7 @@
         <v>44.9099998474121</v>
       </c>
       <c r="G2365" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -68296,7 +68293,7 @@
         <v>42.6500015258789</v>
       </c>
       <c r="G2366" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -68322,7 +68319,7 @@
         <v>44.9599990844727</v>
       </c>
       <c r="G2367" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -68348,7 +68345,7 @@
         <v>46.5299987792969</v>
       </c>
       <c r="G2368" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -68374,7 +68371,7 @@
         <v>48.0699996948242</v>
       </c>
       <c r="G2369" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -68400,7 +68397,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G2370" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -68426,7 +68423,7 @@
         <v>47.4799995422363</v>
       </c>
       <c r="G2371" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -68452,7 +68449,7 @@
         <v>47.939998626709</v>
       </c>
       <c r="G2372" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -68478,7 +68475,7 @@
         <v>50.9599990844727</v>
       </c>
       <c r="G2373" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -68504,7 +68501,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G2374" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -68530,7 +68527,7 @@
         <v>50.6599998474121</v>
       </c>
       <c r="G2375" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -68556,7 +68553,7 @@
         <v>50.5400009155273</v>
       </c>
       <c r="G2376" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -68582,7 +68579,7 @@
         <v>53.4799995422363</v>
       </c>
       <c r="G2377" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -68608,7 +68605,7 @@
         <v>52.7599983215332</v>
       </c>
       <c r="G2378" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -68634,7 +68631,7 @@
         <v>54.1599998474121</v>
       </c>
       <c r="G2379" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -68660,7 +68657,7 @@
         <v>55.939998626709</v>
       </c>
       <c r="G2380" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -68686,7 +68683,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G2381" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -68712,7 +68709,7 @@
         <v>55.2200012207031</v>
       </c>
       <c r="G2382" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -68738,7 +68735,7 @@
         <v>54.6399993896484</v>
       </c>
       <c r="G2383" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -68764,7 +68761,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G2384" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -68790,7 +68787,7 @@
         <v>56.0400009155273</v>
       </c>
       <c r="G2385" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -68816,7 +68813,7 @@
         <v>55.2200012207031</v>
       </c>
       <c r="G2386" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -68842,7 +68839,7 @@
         <v>54.4599990844727</v>
       </c>
       <c r="G2387" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -68868,7 +68865,7 @@
         <v>54.2999992370605</v>
       </c>
       <c r="G2388" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -68894,7 +68891,7 @@
         <v>55.2799987792969</v>
       </c>
       <c r="G2389" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -68920,7 +68917,7 @@
         <v>57.7999992370605</v>
       </c>
       <c r="G2390" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -68946,7 +68943,7 @@
         <v>58.3199996948242</v>
       </c>
       <c r="G2391" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68972,7 +68969,7 @@
         <v>57.4199981689453</v>
       </c>
       <c r="G2392" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68998,7 +68995,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G2393" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -69024,7 +69021,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G2394" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -69050,7 +69047,7 @@
         <v>57.5800018310547</v>
       </c>
       <c r="G2395" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -69076,7 +69073,7 @@
         <v>58.8400001525879</v>
       </c>
       <c r="G2396" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -69102,7 +69099,7 @@
         <v>58.2799987792969</v>
       </c>
       <c r="G2397" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -69128,7 +69125,7 @@
         <v>58.5800018310547</v>
       </c>
       <c r="G2398" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -69154,7 +69151,7 @@
         <v>58.0800018310547</v>
       </c>
       <c r="G2399" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -69180,7 +69177,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G2400" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -69206,7 +69203,7 @@
         <v>58.3600006103516</v>
       </c>
       <c r="G2401" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -69232,7 +69229,7 @@
         <v>57.2799987792969</v>
       </c>
       <c r="G2402" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -69258,7 +69255,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G2403" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -69284,7 +69281,7 @@
         <v>57.6399993896484</v>
       </c>
       <c r="G2404" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -69310,7 +69307,7 @@
         <v>56.5400009155273</v>
       </c>
       <c r="G2405" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -69336,7 +69333,7 @@
         <v>56.3400001525879</v>
       </c>
       <c r="G2406" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -69362,7 +69359,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G2407" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -69388,7 +69385,7 @@
         <v>56.2799987792969</v>
       </c>
       <c r="G2408" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -69414,7 +69411,7 @@
         <v>55.560001373291</v>
       </c>
       <c r="G2409" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -69440,7 +69437,7 @@
         <v>57.7599983215332</v>
       </c>
       <c r="G2410" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -69466,7 +69463,7 @@
         <v>57.2799987792969</v>
       </c>
       <c r="G2411" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -69492,7 +69489,7 @@
         <v>57.8400001525879</v>
       </c>
       <c r="G2412" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -69518,7 +69515,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G2413" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -69544,7 +69541,7 @@
         <v>60.0400009155273</v>
       </c>
       <c r="G2414" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -69570,7 +69567,7 @@
         <v>59.4199981689453</v>
       </c>
       <c r="G2415" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -69596,7 +69593,7 @@
         <v>60.1399993896484</v>
       </c>
       <c r="G2416" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -69622,7 +69619,7 @@
         <v>59.9799995422363</v>
       </c>
       <c r="G2417" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -69648,7 +69645,7 @@
         <v>59.3400001525879</v>
       </c>
       <c r="G2418" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -69674,7 +69671,7 @@
         <v>59.3800010681152</v>
       </c>
       <c r="G2419" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -69700,7 +69697,7 @@
         <v>59.5800018310547</v>
       </c>
       <c r="G2420" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -69726,7 +69723,7 @@
         <v>61.1199989318848</v>
       </c>
       <c r="G2421" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -69752,7 +69749,7 @@
         <v>61.3199996948242</v>
       </c>
       <c r="G2422" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -69778,7 +69775,7 @@
         <v>61.0999984741211</v>
       </c>
       <c r="G2423" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -69804,7 +69801,7 @@
         <v>60.8400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -69830,7 +69827,7 @@
         <v>62</v>
       </c>
       <c r="G2425" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -69856,7 +69853,7 @@
         <v>60.8400001525879</v>
       </c>
       <c r="G2426" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -69882,7 +69879,7 @@
         <v>64.1800003051758</v>
       </c>
       <c r="G2427" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -69908,7 +69905,7 @@
         <v>64.620002746582</v>
       </c>
       <c r="G2428" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -69934,7 +69931,7 @@
         <v>64.3199996948242</v>
       </c>
       <c r="G2429" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -69960,7 +69957,7 @@
         <v>62.939998626709</v>
       </c>
       <c r="G2430" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69986,7 +69983,7 @@
         <v>64.4199981689453</v>
       </c>
       <c r="G2431" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -70012,7 +70009,7 @@
         <v>66.5</v>
       </c>
       <c r="G2432" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -70038,7 +70035,7 @@
         <v>65.6800003051758</v>
       </c>
       <c r="G2433" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -70064,7 +70061,7 @@
         <v>66</v>
       </c>
       <c r="G2434" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -70090,7 +70087,7 @@
         <v>66.8199996948242</v>
       </c>
       <c r="G2435" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -70116,7 +70113,7 @@
         <v>68.5</v>
       </c>
       <c r="G2436" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -70142,7 +70139,7 @@
         <v>70.379997253418</v>
       </c>
       <c r="G2437" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -70168,7 +70165,7 @@
         <v>69</v>
       </c>
       <c r="G2438" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -70194,7 +70191,7 @@
         <v>70.3600006103516</v>
       </c>
       <c r="G2439" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -70220,7 +70217,7 @@
         <v>70.0999984741211</v>
       </c>
       <c r="G2440" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -70246,7 +70243,7 @@
         <v>70.6800003051758</v>
       </c>
       <c r="G2441" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -70272,7 +70269,7 @@
         <v>74</v>
       </c>
       <c r="G2442" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -70298,7 +70295,7 @@
         <v>73.9199981689453</v>
       </c>
       <c r="G2443" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -70324,7 +70321,7 @@
         <v>73.3399963378906</v>
       </c>
       <c r="G2444" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -70350,7 +70347,7 @@
         <v>74.9599990844727</v>
       </c>
       <c r="G2445" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -70376,7 +70373,7 @@
         <v>73.9199981689453</v>
       </c>
       <c r="G2446" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -70402,7 +70399,7 @@
         <v>74.620002746582</v>
       </c>
       <c r="G2447" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -70428,7 +70425,7 @@
         <v>75.4800033569336</v>
       </c>
       <c r="G2448" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -70454,7 +70451,7 @@
         <v>76.3199996948242</v>
       </c>
       <c r="G2449" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -70480,7 +70477,7 @@
         <v>73.0599975585938</v>
       </c>
       <c r="G2450" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -70506,7 +70503,7 @@
         <v>73.5800018310547</v>
       </c>
       <c r="G2451" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -70532,7 +70529,7 @@
         <v>75.5</v>
       </c>
       <c r="G2452" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -70558,7 +70555,7 @@
         <v>74.5599975585938</v>
       </c>
       <c r="G2453" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -70584,7 +70581,7 @@
         <v>75.3000030517578</v>
       </c>
       <c r="G2454" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -70610,7 +70607,7 @@
         <v>74.3000030517578</v>
       </c>
       <c r="G2455" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -70636,7 +70633,7 @@
         <v>76.4800033569336</v>
       </c>
       <c r="G2456" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -70662,7 +70659,7 @@
         <v>74.7200012207031</v>
       </c>
       <c r="G2457" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -70688,7 +70685,7 @@
         <v>75.4199981689453</v>
       </c>
       <c r="G2458" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -70714,7 +70711,7 @@
         <v>73.8600006103516</v>
       </c>
       <c r="G2459" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -70740,7 +70737,7 @@
         <v>75.4599990844727</v>
       </c>
       <c r="G2460" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -70766,7 +70763,7 @@
         <v>76</v>
       </c>
       <c r="G2461" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -70792,7 +70789,7 @@
         <v>76.4800033569336</v>
       </c>
       <c r="G2462" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -70818,7 +70815,7 @@
         <v>77.4800033569336</v>
       </c>
       <c r="G2463" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -70844,7 +70841,7 @@
         <v>78.379997253418</v>
       </c>
       <c r="G2464" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -70870,7 +70867,7 @@
         <v>79.8000030517578</v>
       </c>
       <c r="G2465" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -70896,7 +70893,7 @@
         <v>79.2399978637695</v>
       </c>
       <c r="G2466" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -70922,7 +70919,7 @@
         <v>80.5999984741211</v>
       </c>
       <c r="G2467" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -70948,7 +70945,7 @@
         <v>80.620002746582</v>
       </c>
       <c r="G2468" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70974,7 +70971,7 @@
         <v>80.2200012207031</v>
       </c>
       <c r="G2469" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -71000,7 +70997,7 @@
         <v>79.3000030517578</v>
       </c>
       <c r="G2470" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -71026,7 +71023,7 @@
         <v>81.2799987792969</v>
       </c>
       <c r="G2471" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -71052,7 +71049,7 @@
         <v>81.379997253418</v>
       </c>
       <c r="G2472" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -71078,7 +71075,7 @@
         <v>82.3199996948242</v>
       </c>
       <c r="G2473" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -71104,7 +71101,7 @@
         <v>83.6399993896484</v>
       </c>
       <c r="G2474" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -71130,7 +71127,7 @@
         <v>83.120002746582</v>
       </c>
       <c r="G2475" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -71156,7 +71153,7 @@
         <v>81.379997253418</v>
       </c>
       <c r="G2476" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -71182,7 +71179,7 @@
         <v>81.5</v>
       </c>
       <c r="G2477" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -71208,7 +71205,7 @@
         <v>83.2799987792969</v>
       </c>
       <c r="G2478" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -71234,7 +71231,7 @@
         <v>84.1800003051758</v>
       </c>
       <c r="G2479" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -71260,7 +71257,7 @@
         <v>84.2399978637695</v>
       </c>
       <c r="G2480" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -71286,7 +71283,7 @@
         <v>88</v>
       </c>
       <c r="G2481" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -71312,7 +71309,7 @@
         <v>87</v>
       </c>
       <c r="G2482" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -71338,7 +71335,7 @@
         <v>88.4599990844727</v>
       </c>
       <c r="G2483" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -71364,7 +71361,7 @@
         <v>87.4599990844727</v>
       </c>
       <c r="G2484" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -71390,7 +71387,7 @@
         <v>91.1800003051758</v>
       </c>
       <c r="G2485" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -71416,7 +71413,7 @@
         <v>89.8199996948242</v>
       </c>
       <c r="G2486" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -71442,7 +71439,7 @@
         <v>87.9199981689453</v>
       </c>
       <c r="G2487" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -71468,7 +71465,7 @@
         <v>88.620002746582</v>
       </c>
       <c r="G2488" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -71476,7 +71473,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6520949074</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>1148879</v>
@@ -71494,9 +71491,35 @@
         <v>87.879997253418</v>
       </c>
       <c r="G2489" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6500925926</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>819521</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>89.5599975585938</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>88.1999969482422</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>88.620002746582</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>2143</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="2145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="2146">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6851577758789</t>
+    <t xml:space="preserve">15.6851558685303</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">15.239785194397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7458276748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9644641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2964687347412</t>
+    <t xml:space="preserve">14.74582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9644660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2964668273926</t>
   </si>
   <si>
     <t xml:space="preserve">15.4989109039307</t>
@@ -71,28 +71,28 @@
     <t xml:space="preserve">14.5028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5433883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8510990142822</t>
+    <t xml:space="preserve">14.5433893203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8510999679565</t>
   </si>
   <si>
     <t xml:space="preserve">14.1870889663696</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9401731491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4098358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9239749908447</t>
+    <t xml:space="preserve">14.9401702880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4098339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9239778518677</t>
   </si>
   <si>
     <t xml:space="preserve">15.2802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1831026077271</t>
+    <t xml:space="preserve">15.1831035614014</t>
   </si>
   <si>
     <t xml:space="preserve">14.6243629455566</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">15.3936395645142</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8106088638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7296314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8996820449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5190925598145</t>
+    <t xml:space="preserve">14.8106098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7296333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8996829986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5190944671631</t>
   </si>
   <si>
     <t xml:space="preserve">13.73362159729</t>
@@ -119,28 +119,28 @@
     <t xml:space="preserve">13.344934463501</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0980176925659</t>
+    <t xml:space="preserve">14.0980167388916</t>
   </si>
   <si>
     <t xml:space="preserve">13.3206415176392</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4744968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8955736160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7822046279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3328475952148</t>
+    <t xml:space="preserve">13.474494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8955726623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7822074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3328485488892</t>
   </si>
   <si>
     <t xml:space="preserve">14.2194786071777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4057264328003</t>
+    <t xml:space="preserve">14.405725479126</t>
   </si>
   <si>
     <t xml:space="preserve">14.8349027633667</t>
@@ -149,109 +149,109 @@
     <t xml:space="preserve">14.5514831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3409481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8672924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1021242141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235898971558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4827156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3774461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017391204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4665212631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4908123016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5232009887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636911392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742319107056</t>
+    <t xml:space="preserve">14.3409461975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8672904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.102123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2235908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4827136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3774471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4017353057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4665184020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4908103942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5232038497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636920928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426124572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742338180542</t>
   </si>
   <si>
     <t xml:space="preserve">15.8390092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5879812240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6365690231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9199876785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8309125900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8794994354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8228149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.895697593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2762832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1224308013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.847110748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8875951766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4422245025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3855419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086757659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2276973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7135581970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6568737030029</t>
+    <t xml:space="preserve">15.5879831314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.636570930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9199895858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8309106826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8794975280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8228130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8956937789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2762851715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.122428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8471088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8875970840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4422273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3855428695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2276992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7135562896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6568717956543</t>
   </si>
   <si>
     <t xml:space="preserve">16.4301414489746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6120548248291</t>
+    <t xml:space="preserve">16.6120529174805</t>
   </si>
   <si>
     <t xml:space="preserve">16.9179992675781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0254917144775</t>
+    <t xml:space="preserve">17.0254955291748</t>
   </si>
   <si>
     <t xml:space="preserve">16.9758815765381</t>
@@ -260,31 +260,31 @@
     <t xml:space="preserve">16.9924201965332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6285915374756</t>
+    <t xml:space="preserve">16.628589630127</t>
   </si>
   <si>
     <t xml:space="preserve">16.7774314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">16.98415184021</t>
+    <t xml:space="preserve">16.9841499328613</t>
   </si>
   <si>
     <t xml:space="preserve">17.1081829071045</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9345378875732</t>
+    <t xml:space="preserve">16.9345397949219</t>
   </si>
   <si>
     <t xml:space="preserve">16.5541725158691</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5955142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7608909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7030086517334</t>
+    <t xml:space="preserve">16.5955181121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7608890533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.703010559082</t>
   </si>
   <si>
     <t xml:space="preserve">16.8766574859619</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">17.4058589935303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7696914672852</t>
+    <t xml:space="preserve">17.7696876525879</t>
   </si>
   <si>
     <t xml:space="preserve">18.0094833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9681415557861</t>
+    <t xml:space="preserve">17.9681396484375</t>
   </si>
   <si>
     <t xml:space="preserve">17.8606472015381</t>
@@ -311,16 +311,16 @@
     <t xml:space="preserve">17.8854503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6952686309814</t>
+    <t xml:space="preserve">17.6952705383301</t>
   </si>
   <si>
     <t xml:space="preserve">18.1087112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.959867477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2658157348633</t>
+    <t xml:space="preserve">17.9598712921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2658176422119</t>
   </si>
   <si>
     <t xml:space="preserve">18.1748600006104</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">18.2988948822021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.472541809082</t>
+    <t xml:space="preserve">18.4725379943848</t>
   </si>
   <si>
     <t xml:space="preserve">18.1831302642822</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">18.1335182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0425605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8027667999268</t>
+    <t xml:space="preserve">18.0425567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8027629852295</t>
   </si>
   <si>
     <t xml:space="preserve">18.0921745300293</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9185256958008</t>
+    <t xml:space="preserve">17.9185276031494</t>
   </si>
   <si>
     <t xml:space="preserve">18.0012149810791</t>
@@ -359,76 +359,76 @@
     <t xml:space="preserve">17.314905166626</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9097328186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8022403717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7366161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5712394714355</t>
+    <t xml:space="preserve">16.9097309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8022365570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7366142272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5712375640869</t>
   </si>
   <si>
     <t xml:space="preserve">17.3479785919189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9102535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6694078445435</t>
+    <t xml:space="preserve">17.9102573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6694097518921</t>
   </si>
   <si>
     <t xml:space="preserve">14.8342599868774</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1402072906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2978363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7272920608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5867223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2311611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6115303039551</t>
+    <t xml:space="preserve">15.1402063369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2559661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2978401184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7272882461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5867214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2311639785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6115283966064</t>
   </si>
   <si>
     <t xml:space="preserve">16.2813034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4632167816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6533985137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6864738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.678201675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7443542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6699352264404</t>
+    <t xml:space="preserve">16.4632148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6533966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6864757537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6782054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7443561553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6699333190918</t>
   </si>
   <si>
     <t xml:space="preserve">16.8435840606689</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">16.818775177002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9510746002197</t>
+    <t xml:space="preserve">16.9510726928711</t>
   </si>
   <si>
     <t xml:space="preserve">17.0999145507812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1164512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2983665466309</t>
+    <t xml:space="preserve">17.1164531707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2983684539795</t>
   </si>
   <si>
     <t xml:space="preserve">17.2404842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0751113891602</t>
+    <t xml:space="preserve">17.0751075744629</t>
   </si>
   <si>
     <t xml:space="preserve">17.3314437866211</t>
@@ -461,73 +461,73 @@
     <t xml:space="preserve">17.6208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1004390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125831604004</t>
+    <t xml:space="preserve">18.1004428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125793457031</t>
   </si>
   <si>
     <t xml:space="preserve">17.5960445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0756340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7944946289062</t>
+    <t xml:space="preserve">18.0756359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7944965362549</t>
   </si>
   <si>
     <t xml:space="preserve">17.8771858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1913986206055</t>
+    <t xml:space="preserve">18.1913967132568</t>
   </si>
   <si>
     <t xml:space="preserve">18.2492790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0839042663574</t>
+    <t xml:space="preserve">18.0839023590088</t>
   </si>
   <si>
     <t xml:space="preserve">18.2906227111816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1665916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9929466247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.844108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7200756072998</t>
+    <t xml:space="preserve">18.1665897369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9929485321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8441047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7200775146484</t>
   </si>
   <si>
     <t xml:space="preserve">17.728343963623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8937187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0673694610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3733139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9438591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4317207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3573036193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1009693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1257724761963</t>
+    <t xml:space="preserve">17.8937206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0673656463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.37331199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9438610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4317226409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3573055267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1009635925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1257762908936</t>
   </si>
   <si>
     <t xml:space="preserve">19.1919250488281</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">19.175386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2828845977783</t>
+    <t xml:space="preserve">19.2828807830811</t>
   </si>
   <si>
     <t xml:space="preserve">19.1340446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3490333557129</t>
+    <t xml:space="preserve">19.3490352630615</t>
   </si>
   <si>
     <t xml:space="preserve">19.4978694915771</t>
@@ -551,79 +551,79 @@
     <t xml:space="preserve">19.7624740600586</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6549797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7045936584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4647960662842</t>
+    <t xml:space="preserve">19.6549777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4647941589355</t>
   </si>
   <si>
     <t xml:space="preserve">19.0596237182617</t>
   </si>
   <si>
-    <t xml:space="preserve">18.646183013916</t>
+    <t xml:space="preserve">18.6461811065674</t>
   </si>
   <si>
     <t xml:space="preserve">19.1175079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1588497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0100116729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7536773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9025173187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0844345092773</t>
+    <t xml:space="preserve">19.1588516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0100135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7536811828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.902515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0844306945801</t>
   </si>
   <si>
     <t xml:space="preserve">18.9934749603271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7950229644775</t>
+    <t xml:space="preserve">18.7950210571289</t>
   </si>
   <si>
     <t xml:space="preserve">18.7867527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7454071044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3319683074951</t>
+    <t xml:space="preserve">18.7454090118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3319702148438</t>
   </si>
   <si>
     <t xml:space="preserve">17.6291217803955</t>
   </si>
   <si>
-    <t xml:space="preserve">18.869441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1505794525146</t>
+    <t xml:space="preserve">18.8694438934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1505813598633</t>
   </si>
   <si>
     <t xml:space="preserve">18.3485069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6627197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7288722991943</t>
+    <t xml:space="preserve">18.6627178192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.728874206543</t>
   </si>
   <si>
     <t xml:space="preserve">18.6875267028809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8942470550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4229259490967</t>
+    <t xml:space="preserve">18.8942489624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.422924041748</t>
   </si>
   <si>
     <t xml:space="preserve">18.480806350708</t>
@@ -632,58 +632,58 @@
     <t xml:space="preserve">18.2327423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3237018585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0590972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6709880828857</t>
+    <t xml:space="preserve">18.3236999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0590991973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6709899902344</t>
   </si>
   <si>
     <t xml:space="preserve">18.9355926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4399890899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8782367706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6797866821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1676425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8451633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7790145874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1428394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9113101959229</t>
+    <t xml:space="preserve">19.4399871826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8782329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6797828674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1676445007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8451614379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7790126800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1428413391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9113140106201</t>
   </si>
   <si>
     <t xml:space="preserve">20.1759147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0022659301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.927848815918</t>
+    <t xml:space="preserve">20.0022678375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9278507232666</t>
   </si>
   <si>
     <t xml:space="preserve">20.0105381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8038196563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1014976501465</t>
+    <t xml:space="preserve">19.8038177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1014957427979</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263027191162</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">20.1924514770508</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6389656066895</t>
+    <t xml:space="preserve">20.6389675140381</t>
   </si>
   <si>
     <t xml:space="preserve">20.1345710754395</t>
@@ -707,58 +707,58 @@
     <t xml:space="preserve">20.2172603607178</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3164863586426</t>
+    <t xml:space="preserve">20.3164825439453</t>
   </si>
   <si>
     <t xml:space="preserve">20.2420654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3330230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2255268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6555061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5066699981689</t>
+    <t xml:space="preserve">20.3330211639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.225528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6555023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5066680908203</t>
   </si>
   <si>
     <t xml:space="preserve">20.3578281402588</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4818630218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0849571228027</t>
+    <t xml:space="preserve">20.4818592071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0849590301514</t>
   </si>
   <si>
     <t xml:space="preserve">20.3991718292236</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5645503997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5397453308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6885833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.894775390625</t>
+    <t xml:space="preserve">20.5645523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5397415161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6885795593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8947734832764</t>
   </si>
   <si>
     <t xml:space="preserve">20.4074401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7133884429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9697227478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3495616912842</t>
+    <t xml:space="preserve">20.7133865356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9697246551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3495597839355</t>
   </si>
   <si>
     <t xml:space="preserve">20.423978805542</t>
@@ -767,31 +767,31 @@
     <t xml:space="preserve">20.3082180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.754732131958</t>
+    <t xml:space="preserve">20.7547340393066</t>
   </si>
   <si>
     <t xml:space="preserve">19.9609260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8865051269531</t>
+    <t xml:space="preserve">19.8865070343018</t>
   </si>
   <si>
     <t xml:space="preserve">19.8286285400391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8534317016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1180324554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5722942352295</t>
+    <t xml:space="preserve">19.8534297943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1180305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5722904205322</t>
   </si>
   <si>
     <t xml:space="preserve">19.2994194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5144100189209</t>
+    <t xml:space="preserve">19.5144081115723</t>
   </si>
   <si>
     <t xml:space="preserve">19.5474853515625</t>
@@ -809,13 +809,13 @@
     <t xml:space="preserve">19.3821067810059</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7376689910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3660984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9361152648926</t>
+    <t xml:space="preserve">19.7376670837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3661003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9361190795898</t>
   </si>
   <si>
     <t xml:space="preserve">20.200719833374</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">20.4901294708252</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7381954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2922058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1516342163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0854835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9366455078125</t>
+    <t xml:space="preserve">20.7381935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2922019958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1516361236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.085485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9366416931152</t>
   </si>
   <si>
     <t xml:space="preserve">20.7795372009277</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">20.4570541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7051181793213</t>
+    <t xml:space="preserve">20.7051200866699</t>
   </si>
   <si>
     <t xml:space="preserve">21.1268291473389</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">22.0435562133789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1192512512207</t>
+    <t xml:space="preserve">22.1192493438721</t>
   </si>
   <si>
     <t xml:space="preserve">21.8669414520264</t>
@@ -863,31 +863,31 @@
     <t xml:space="preserve">21.9846858978271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2958698272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4724864959717</t>
+    <t xml:space="preserve">22.2958679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.472484588623</t>
   </si>
   <si>
     <t xml:space="preserve">22.2201747894287</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2622241973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5397701263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5734081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.808069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6987323760986</t>
+    <t xml:space="preserve">22.262228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5397682189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5734100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8080673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6987342834473</t>
   </si>
   <si>
     <t xml:space="preserve">21.0847778320312</t>
@@ -899,37 +899,37 @@
     <t xml:space="preserve">20.9502105712891</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6390285491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4203567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5549201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4540023803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9670295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1941146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8576965332031</t>
+    <t xml:space="preserve">20.6390247344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4203605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5549221038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4540004730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9670314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.19411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8576984405518</t>
   </si>
   <si>
     <t xml:space="preserve">21.1688823699951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8324642181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9586200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156471252441</t>
+    <t xml:space="preserve">20.8324661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9586181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8156452178955</t>
   </si>
   <si>
     <t xml:space="preserve">21.5978088378906</t>
@@ -938,76 +938,76 @@
     <t xml:space="preserve">21.2613945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">21.101598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6819152832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6146297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.816478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6566791534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8248882293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5473461151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5725803375244</t>
+    <t xml:space="preserve">21.1015968322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6819133758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.614631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8164806365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.656681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8248901367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.547342300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5725765228271</t>
   </si>
   <si>
     <t xml:space="preserve">22.0351486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8585319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9258136749268</t>
+    <t xml:space="preserve">21.858528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9258117675781</t>
   </si>
   <si>
     <t xml:space="preserve">21.7828369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3210983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4884757995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3875484466553</t>
+    <t xml:space="preserve">22.3211002349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4884719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3875522613525</t>
   </si>
   <si>
     <t xml:space="preserve">22.1949443817139</t>
   </si>
   <si>
-    <t xml:space="preserve">21.850118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2454051971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0015048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3883819580078</t>
+    <t xml:space="preserve">21.8501205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2454071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0015068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3883800506592</t>
   </si>
   <si>
     <t xml:space="preserve">22.2538166046143</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5481796264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5313606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7668495178223</t>
+    <t xml:space="preserve">22.5481815338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5313587188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7668476104736</t>
   </si>
   <si>
     <t xml:space="preserve">23.0696220397949</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">22.5818214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8425407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5650005340576</t>
+    <t xml:space="preserve">22.8425445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.564998626709</t>
   </si>
   <si>
     <t xml:space="preserve">22.1444835662842</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">22.52294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7920799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.422025680542</t>
+    <t xml:space="preserve">22.7920742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4220237731934</t>
   </si>
   <si>
     <t xml:space="preserve">22.7500267028809</t>
@@ -1046,64 +1046,64 @@
     <t xml:space="preserve">22.9266490936279</t>
   </si>
   <si>
-    <t xml:space="preserve">22.93505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8593635559082</t>
+    <t xml:space="preserve">22.9350547790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8593654632568</t>
   </si>
   <si>
     <t xml:space="preserve">22.7079753875732</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7416191101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5902290344238</t>
+    <t xml:space="preserve">22.7416172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5902309417725</t>
   </si>
   <si>
     <t xml:space="preserve">22.2369956970215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8417110443115</t>
+    <t xml:space="preserve">21.8417091369629</t>
   </si>
   <si>
     <t xml:space="preserve">22.161304473877</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3547401428223</t>
+    <t xml:space="preserve">22.3547420501709</t>
   </si>
   <si>
     <t xml:space="preserve">22.3042793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9594535827637</t>
+    <t xml:space="preserve">21.9594554901123</t>
   </si>
   <si>
     <t xml:space="preserve">22.2285842895508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1108417510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9174022674561</t>
+    <t xml:space="preserve">22.11083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9174003601074</t>
   </si>
   <si>
     <t xml:space="preserve">22.3463306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4304370880127</t>
+    <t xml:space="preserve">22.4304351806641</t>
   </si>
   <si>
     <t xml:space="preserve">22.825719833374</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4649066925049</t>
+    <t xml:space="preserve">23.4649085998535</t>
   </si>
   <si>
     <t xml:space="preserve">23.6331176757812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6751670837402</t>
+    <t xml:space="preserve">23.6751651763916</t>
   </si>
   <si>
     <t xml:space="preserve">23.6835803985596</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">23.8097324371338</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9106597900391</t>
+    <t xml:space="preserve">23.9106578826904</t>
   </si>
   <si>
     <t xml:space="preserve">23.9190711975098</t>
@@ -1124,31 +1124,31 @@
     <t xml:space="preserve">23.8770160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9863510131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8938407897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9527111053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9779396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8517818450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0368099212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4741497039795</t>
+    <t xml:space="preserve">23.9863471984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8938388824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9527072906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9779376983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8517875671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0368137359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4741516113281</t>
   </si>
   <si>
     <t xml:space="preserve">24.3311767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3143558502197</t>
+    <t xml:space="preserve">24.3143577575684</t>
   </si>
   <si>
     <t xml:space="preserve">24.0536346435547</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">23.9611206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0199928283691</t>
+    <t xml:space="preserve">24.0199947357178</t>
   </si>
   <si>
     <t xml:space="preserve">24.104097366333</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">24.558256149292</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5077934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3564071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3984603881836</t>
+    <t xml:space="preserve">24.5077953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.356409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3984622955322</t>
   </si>
   <si>
     <t xml:space="preserve">24.919900894165</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">25.2310848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1217517852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1890296936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8526210784912</t>
+    <t xml:space="preserve">25.1217498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1890316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8526191711426</t>
   </si>
   <si>
     <t xml:space="preserve">24.4489212036133</t>
@@ -1211,64 +1211,64 @@
     <t xml:space="preserve">23.5574226379395</t>
   </si>
   <si>
-    <t xml:space="preserve">23.389217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5994739532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2125988006592</t>
+    <t xml:space="preserve">23.3892154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5994758605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2126007080078</t>
   </si>
   <si>
     <t xml:space="preserve">23.9274768829346</t>
   </si>
   <si>
-    <t xml:space="preserve">23.691987991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5406017303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5742435455322</t>
+    <t xml:space="preserve">23.6919898986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5406036376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5742454528809</t>
   </si>
   <si>
     <t xml:space="preserve">23.3808040618896</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4144477844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5321884155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9695281982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9939289093018</t>
+    <t xml:space="preserve">23.4144458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.532190322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9695301055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9939270019531</t>
   </si>
   <si>
     <t xml:space="preserve">22.6911582946777</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9014167785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9771060943604</t>
+    <t xml:space="preserve">22.9014186859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.977108001709</t>
   </si>
   <si>
     <t xml:space="preserve">23.0443897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">23.02756690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0359802246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8930034637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.682746887207</t>
+    <t xml:space="preserve">23.0275688171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0359783172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8930053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6827449798584</t>
   </si>
   <si>
     <t xml:space="preserve">23.1789588928223</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">23.2546482086182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2210063934326</t>
+    <t xml:space="preserve">23.2210083007812</t>
   </si>
   <si>
     <t xml:space="preserve">23.1621360778809</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2294178009033</t>
+    <t xml:space="preserve">23.229419708252</t>
   </si>
   <si>
     <t xml:space="preserve">23.078031539917</t>
   </si>
   <si>
-    <t xml:space="preserve">22.867769241333</t>
+    <t xml:space="preserve">22.8677730560303</t>
   </si>
   <si>
     <t xml:space="preserve">23.0107498168945</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">24.1881999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">24.003173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1713829040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2218418121338</t>
+    <t xml:space="preserve">24.0031700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1713790893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2218399047852</t>
   </si>
   <si>
     <t xml:space="preserve">24.3900508880615</t>
@@ -1319,70 +1319,70 @@
     <t xml:space="preserve">24.5246124267578</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3395824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3059463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8686084747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8349628448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2882919311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9602870941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6070518493652</t>
+    <t xml:space="preserve">24.3395881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.305944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8686046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8349666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2882881164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9602851867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6070556640625</t>
   </si>
   <si>
     <t xml:space="preserve">23.4564990997314</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7163848876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4556636810303</t>
+    <t xml:space="preserve">22.7163867950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4556674957275</t>
   </si>
   <si>
     <t xml:space="preserve">22.0687885284424</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1781234741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0940208435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9089908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7996559143066</t>
+    <t xml:space="preserve">22.1781215667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0940189361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9089946746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.799654006958</t>
   </si>
   <si>
     <t xml:space="preserve">21.6314468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7912445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3631496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3967952728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2874584197998</t>
+    <t xml:space="preserve">21.7912483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3631534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3967933654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2874622344971</t>
   </si>
   <si>
     <t xml:space="preserve">22.0856094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6230430603027</t>
+    <t xml:space="preserve">21.6230392456055</t>
   </si>
   <si>
     <t xml:space="preserve">21.3454990386963</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">21.2950344085693</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3370876312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7407836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7904109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3194351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7988224029541</t>
+    <t xml:space="preserve">21.337085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7407875061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7904148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3194332122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7988262176514</t>
   </si>
   <si>
     <t xml:space="preserve">20.4035377502441</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">20.5717449188232</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7735939025879</t>
+    <t xml:space="preserve">20.7735958099365</t>
   </si>
   <si>
     <t xml:space="preserve">20.9249782562256</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8072376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0288734436035</t>
+    <t xml:space="preserve">20.8072338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0288715362549</t>
   </si>
   <si>
     <t xml:space="preserve">20.8919315338135</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6351680755615</t>
+    <t xml:space="preserve">20.6351699829102</t>
   </si>
   <si>
     <t xml:space="preserve">20.618049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7464332580566</t>
+    <t xml:space="preserve">20.7464351654053</t>
   </si>
   <si>
     <t xml:space="preserve">20.8662548065186</t>
@@ -1451,25 +1451,25 @@
     <t xml:space="preserve">20.9604015350342</t>
   </si>
   <si>
-    <t xml:space="preserve">21.362663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5081634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.884744644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7563648223877</t>
+    <t xml:space="preserve">21.3626594543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5081615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8847465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.756368637085</t>
   </si>
   <si>
     <t xml:space="preserve">22.2270984649658</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9203586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4153919219971</t>
+    <t xml:space="preserve">22.9203605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4153900146484</t>
   </si>
   <si>
     <t xml:space="preserve">22.4239501953125</t>
@@ -1481,61 +1481,61 @@
     <t xml:space="preserve">22.0987148284912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1072750091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7392463684082</t>
+    <t xml:space="preserve">22.1072731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7392501831055</t>
   </si>
   <si>
     <t xml:space="preserve">21.2428417205811</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4568119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4054546356201</t>
+    <t xml:space="preserve">21.4568099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4054565429688</t>
   </si>
   <si>
     <t xml:space="preserve">20.9432849884033</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1302013397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1216411590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3698463439941</t>
+    <t xml:space="preserve">20.1302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1216430664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3698482513428</t>
   </si>
   <si>
     <t xml:space="preserve">21.2685165405273</t>
   </si>
   <si>
-    <t xml:space="preserve">21.396900177002</t>
+    <t xml:space="preserve">21.3968982696533</t>
   </si>
   <si>
     <t xml:space="preserve">21.3369846343994</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3797798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0117530822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779632568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.174373626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8063449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7977828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9960117340088</t>
+    <t xml:space="preserve">21.3797817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.011754989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779613494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1743698120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8063430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7977867126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9960136413574</t>
   </si>
   <si>
     <t xml:space="preserve">21.5423984527588</t>
@@ -1550,16 +1550,16 @@
     <t xml:space="preserve">20.455436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6509094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8563213348389</t>
+    <t xml:space="preserve">19.6509113311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8563232421875</t>
   </si>
   <si>
     <t xml:space="preserve">17.8706893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9305973052979</t>
+    <t xml:space="preserve">17.9306030273438</t>
   </si>
   <si>
     <t xml:space="preserve">18.2729511260986</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">18.2558345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9355735778809</t>
+    <t xml:space="preserve">17.9355754852295</t>
   </si>
   <si>
     <t xml:space="preserve">18.6260833740234</t>
@@ -1595,34 +1595,34 @@
     <t xml:space="preserve">18.997896194458</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9359283447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2988891601562</t>
+    <t xml:space="preserve">18.9359264373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2988872528076</t>
   </si>
   <si>
     <t xml:space="preserve">19.1838035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2103652954102</t>
+    <t xml:space="preserve">19.2103633880615</t>
   </si>
   <si>
     <t xml:space="preserve">19.4139747619629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5202045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5113544464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5644702911377</t>
+    <t xml:space="preserve">19.520206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5113563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5644721984863</t>
   </si>
   <si>
     <t xml:space="preserve">19.7238216400146</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6352920532227</t>
+    <t xml:space="preserve">19.635290145874</t>
   </si>
   <si>
     <t xml:space="preserve">19.4316806793213</t>
@@ -1634,34 +1634,34 @@
     <t xml:space="preserve">19.0687198638916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2369213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6972599029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7503776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8034915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4405326843262</t>
+    <t xml:space="preserve">19.2369174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6972637176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7503757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8034934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4405307769775</t>
   </si>
   <si>
     <t xml:space="preserve">19.2900371551514</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0333099365234</t>
+    <t xml:space="preserve">19.0333080291748</t>
   </si>
   <si>
     <t xml:space="preserve">18.5109996795654</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3516521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8208427429199</t>
+    <t xml:space="preserve">18.3516502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8208446502686</t>
   </si>
   <si>
     <t xml:space="preserve">18.7765789031982</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">18.7942848205566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9182262420654</t>
+    <t xml:space="preserve">18.9182243347168</t>
   </si>
   <si>
     <t xml:space="preserve">19.1129817962646</t>
@@ -1679,64 +1679,64 @@
     <t xml:space="preserve">19.4847946166992</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6707019805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5733242034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2015132904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2192134857178</t>
+    <t xml:space="preserve">19.6707057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5733261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.201509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.219217300415</t>
   </si>
   <si>
     <t xml:space="preserve">19.0952777862549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6969051361084</t>
+    <t xml:space="preserve">18.696907043457</t>
   </si>
   <si>
     <t xml:space="preserve">19.1218357086182</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2546253204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5906734466553</t>
+    <t xml:space="preserve">19.2546272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5906715393066</t>
   </si>
   <si>
     <t xml:space="preserve">18.4136180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6792011260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6880531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1483917236328</t>
+    <t xml:space="preserve">18.6792030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6880550384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1483936309814</t>
   </si>
   <si>
     <t xml:space="preserve">18.9890441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0510158538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5995292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3427963256836</t>
+    <t xml:space="preserve">19.0510139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5995235443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3427982330322</t>
   </si>
   <si>
     <t xml:space="preserve">18.4313220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3693561553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7585182189941</t>
+    <t xml:space="preserve">18.3693580627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7585201263428</t>
   </si>
   <si>
     <t xml:space="preserve">17.6965503692627</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">17.4840869903564</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9001617431641</t>
+    <t xml:space="preserve">17.9001598358154</t>
   </si>
   <si>
     <t xml:space="preserve">17.4176902770996</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">16.6342277526855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4527435302734</t>
+    <t xml:space="preserve">16.4527416229248</t>
   </si>
   <si>
     <t xml:space="preserve">15.9392881393433</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">15.5719022750854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4346828460693</t>
+    <t xml:space="preserve">15.434684753418</t>
   </si>
   <si>
     <t xml:space="preserve">15.4656715393066</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">16.7316074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2712669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7666625976562</t>
+    <t xml:space="preserve">16.2712631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7666606903076</t>
   </si>
   <si>
     <t xml:space="preserve">15.2133674621582</t>
@@ -1787,79 +1787,79 @@
     <t xml:space="preserve">15.173529624939</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6777782440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2262907028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7840127944946</t>
+    <t xml:space="preserve">14.6777772903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2262916564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7840118408203</t>
   </si>
   <si>
     <t xml:space="preserve">14.6290893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9743461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0717239379883</t>
+    <t xml:space="preserve">14.9743452072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.071722984314</t>
   </si>
   <si>
     <t xml:space="preserve">15.1912355422974</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7179679870605</t>
+    <t xml:space="preserve">15.7179698944092</t>
   </si>
   <si>
     <t xml:space="preserve">16.2933979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9171562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8596153259277</t>
+    <t xml:space="preserve">15.9171581268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8596172332764</t>
   </si>
   <si>
     <t xml:space="preserve">16.0986366271973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1030654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7755126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4169816970825</t>
+    <t xml:space="preserve">16.103063583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7755146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4169797897339</t>
   </si>
   <si>
     <t xml:space="preserve">15.7887926101685</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4833736419678</t>
+    <t xml:space="preserve">15.4833765029907</t>
   </si>
   <si>
     <t xml:space="preserve">14.6910581588745</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2882595062256</t>
+    <t xml:space="preserve">14.2882604598999</t>
   </si>
   <si>
     <t xml:space="preserve">14.2041597366333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8943157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9739894866943</t>
+    <t xml:space="preserve">13.8943147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.97398853302</t>
   </si>
   <si>
     <t xml:space="preserve">13.8766098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0802211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9916954040527</t>
+    <t xml:space="preserve">14.0802221298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9916963577271</t>
   </si>
   <si>
     <t xml:space="preserve">13.7880821228027</t>
@@ -1868,28 +1868,28 @@
     <t xml:space="preserve">13.6243076324463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1554698944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3148183822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0451679229736</t>
+    <t xml:space="preserve">14.1554708480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3148193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0451669692993</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254770278931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1112060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4959421157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3675804138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2524938583374</t>
+    <t xml:space="preserve">14.1112051010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4959440231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.367579460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2524948120117</t>
   </si>
   <si>
     <t xml:space="preserve">14.0669441223145</t>
@@ -1898,19 +1898,19 @@
     <t xml:space="preserve">14.7707328796387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8415546417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6954860687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6512184143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8946714401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0628709793091</t>
+    <t xml:space="preserve">14.841552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6954851150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.651219367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8946704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0628728866577</t>
   </si>
   <si>
     <t xml:space="preserve">14.8813905715942</t>
@@ -1919,67 +1919,67 @@
     <t xml:space="preserve">14.828275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9345073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4479637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.713189125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558275222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2886161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6958389282227</t>
+    <t xml:space="preserve">14.9345064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4479646682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7131910324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2886152267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6958379745483</t>
   </si>
   <si>
     <t xml:space="preserve">16.3155288696289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4129123687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1163425445557</t>
+    <t xml:space="preserve">16.4129104614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.116340637207</t>
   </si>
   <si>
     <t xml:space="preserve">16.0145359039307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8020725250244</t>
+    <t xml:space="preserve">15.8020734786987</t>
   </si>
   <si>
     <t xml:space="preserve">16.1340484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2358551025391</t>
+    <t xml:space="preserve">16.2358570098877</t>
   </si>
   <si>
     <t xml:space="preserve">16.479305267334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4748764038086</t>
+    <t xml:space="preserve">16.4748783111572</t>
   </si>
   <si>
     <t xml:space="preserve">16.3376617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2181491851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2889709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5811080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5412712097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7758731842041</t>
+    <t xml:space="preserve">16.218147277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2889728546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5811100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5412731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7758712768555</t>
   </si>
   <si>
     <t xml:space="preserve">16.4881572723389</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">16.7935733795166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6297988891602</t>
+    <t xml:space="preserve">16.6298027038574</t>
   </si>
   <si>
     <t xml:space="preserve">16.9263648986816</t>
@@ -1997,25 +1997,25 @@
     <t xml:space="preserve">15.9481420516968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9304342269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9614238739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5279941558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5368461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6784896850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5855369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7138977050781</t>
+    <t xml:space="preserve">15.9304351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9614219665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5279960632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5368480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.67848777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5855388641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7139015197754</t>
   </si>
   <si>
     <t xml:space="preserve">15.1292667388916</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">15.5763273239136</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8197784423828</t>
+    <t xml:space="preserve">15.8197765350342</t>
   </si>
   <si>
     <t xml:space="preserve">16.0101089477539</t>
@@ -2033,52 +2033,52 @@
     <t xml:space="preserve">15.8906011581421</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8463335037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3992738723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2930421829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9610643386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8858184814453</t>
+    <t xml:space="preserve">15.8463354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3992729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2930402755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9610662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876260757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8858194351196</t>
   </si>
   <si>
     <t xml:space="preserve">14.3767862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4874467849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6069555282593</t>
+    <t xml:space="preserve">14.4874458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6069574356079</t>
   </si>
   <si>
     <t xml:space="preserve">14.5626945495605</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7795848846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4125518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2222185134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0540189743042</t>
+    <t xml:space="preserve">14.7795839309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4125547409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2222194671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0540180206299</t>
   </si>
   <si>
     <t xml:space="preserve">14.9212284088135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6423673629761</t>
+    <t xml:space="preserve">14.6423683166504</t>
   </si>
   <si>
     <t xml:space="preserve">14.9300813674927</t>
@@ -2087,31 +2087,31 @@
     <t xml:space="preserve">14.8592586517334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1868104934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0230340957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9477863311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.447606086731</t>
+    <t xml:space="preserve">15.1868095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0230331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9477844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476070404053</t>
   </si>
   <si>
     <t xml:space="preserve">13.2436408996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5534868240356</t>
+    <t xml:space="preserve">13.5534858703613</t>
   </si>
   <si>
     <t xml:space="preserve">13.6552925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6420125961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1997346878052</t>
+    <t xml:space="preserve">13.6420135498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1997337341309</t>
   </si>
   <si>
     <t xml:space="preserve">14.4564619064331</t>
@@ -2120,58 +2120,58 @@
     <t xml:space="preserve">14.4431829452515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6822061538696</t>
+    <t xml:space="preserve">14.6822071075439</t>
   </si>
   <si>
     <t xml:space="preserve">14.8459806442261</t>
   </si>
   <si>
-    <t xml:space="preserve">15.217794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0495929718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2089414596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0318870544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1823844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.496298789978</t>
+    <t xml:space="preserve">15.2177925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0495910644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2089424133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0318880081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1823835372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4962978363037</t>
   </si>
   <si>
     <t xml:space="preserve">14.1820287704468</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2000885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1381177902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3151721954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.306321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6467952728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3723611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.858904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7748041152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5977478027344</t>
+    <t xml:space="preserve">15.2000875473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1381206512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3151731491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3063230514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6467943191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3723602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589029312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7748031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5977487564087</t>
   </si>
   <si>
     <t xml:space="preserve">13.7792291641235</t>
@@ -2180,64 +2180,64 @@
     <t xml:space="preserve">13.5888977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6774234771729</t>
+    <t xml:space="preserve">13.6774244308472</t>
   </si>
   <si>
     <t xml:space="preserve">13.2170839309692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5313539505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3502283096313</t>
+    <t xml:space="preserve">13.5313549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.350227355957</t>
   </si>
   <si>
     <t xml:space="preserve">14.3192443847656</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2705564498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6999101638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353219985962</t>
+    <t xml:space="preserve">14.2705535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6999092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353229522705</t>
   </si>
   <si>
     <t xml:space="preserve">14.9256553649902</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6600723266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7486000061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9079494476318</t>
+    <t xml:space="preserve">14.6600742340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7486009597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9079504013062</t>
   </si>
   <si>
     <t xml:space="preserve">15.2266473770142</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5807552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9127321243286</t>
+    <t xml:space="preserve">15.5807542800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9127311706543</t>
   </si>
   <si>
     <t xml:space="preserve">16.0942115783691</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8584632873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9808712005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675327301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2302188873291</t>
+    <t xml:space="preserve">15.8584651947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9808721542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675308227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2302169799805</t>
   </si>
   <si>
     <t xml:space="preserve">16.4568977355957</t>
@@ -2246,16 +2246,16 @@
     <t xml:space="preserve">16.5838375091553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5929069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6609115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7243804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425136566162</t>
+    <t xml:space="preserve">16.5929050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.66090965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7243785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7425155639648</t>
   </si>
   <si>
     <t xml:space="preserve">16.4115619659424</t>
@@ -2267,25 +2267,25 @@
     <t xml:space="preserve">16.9827919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9419898986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0326633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3092098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4542846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9646606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9555912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0462608337402</t>
+    <t xml:space="preserve">16.941987991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0326652526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.309211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4542865753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9646587371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9555931091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0462627410889</t>
   </si>
   <si>
     <t xml:space="preserve">18.0436515808105</t>
@@ -2297,19 +2297,19 @@
     <t xml:space="preserve">18.1116561889648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7263011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1414699554443</t>
+    <t xml:space="preserve">17.72629737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1414680480957</t>
   </si>
   <si>
     <t xml:space="preserve">16.7833156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9283885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5268211364746</t>
+    <t xml:space="preserve">16.9283924102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5268249511719</t>
   </si>
   <si>
     <t xml:space="preserve">17.1505355834961</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">16.9601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3726787567139</t>
+    <t xml:space="preserve">17.3726806640625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7787818908691</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">16.7923831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7017116546631</t>
+    <t xml:space="preserve">16.7017097473145</t>
   </si>
   <si>
     <t xml:space="preserve">16.030740737915</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0715465545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6473083496094</t>
+    <t xml:space="preserve">16.0715427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.647310256958</t>
   </si>
   <si>
     <t xml:space="preserve">16.8150501251221</t>
@@ -2351,31 +2351,31 @@
     <t xml:space="preserve">17.5948276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3862819671631</t>
+    <t xml:space="preserve">17.3862838745117</t>
   </si>
   <si>
     <t xml:space="preserve">17.0054626464844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9782600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2774753570557</t>
+    <t xml:space="preserve">16.9782581329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2774772644043</t>
   </si>
   <si>
     <t xml:space="preserve">17.2276058197021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0209846496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0481834411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0073852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.206859588623</t>
+    <t xml:space="preserve">18.0209808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0481853485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0073833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2068614959717</t>
   </si>
   <si>
     <t xml:space="preserve">18.7508888244629</t>
@@ -2387,64 +2387,64 @@
     <t xml:space="preserve">18.3519344329834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2884616851807</t>
+    <t xml:space="preserve">18.2884654998779</t>
   </si>
   <si>
     <t xml:space="preserve">18.4244728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9775676727295</t>
+    <t xml:space="preserve">18.9775695800781</t>
   </si>
   <si>
     <t xml:space="preserve">19.0501079559326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0410404205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3156642913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7716388702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0617866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8804416656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0889892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9756488800049</t>
+    <t xml:space="preserve">19.0410385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3156661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7716369628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0617828369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.880443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0889873504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9756469726562</t>
   </si>
   <si>
     <t xml:space="preserve">17.7353668212891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7217655181885</t>
+    <t xml:space="preserve">17.7217674255371</t>
   </si>
   <si>
     <t xml:space="preserve">17.8623104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7126998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0598621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0507965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.973726272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.096134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8921203613281</t>
+    <t xml:space="preserve">17.7126979827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0598659515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0507984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9737243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0961322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8921184539795</t>
   </si>
   <si>
     <t xml:space="preserve">17.2366733551025</t>
@@ -2474,28 +2474,28 @@
     <t xml:space="preserve">18.1887264251709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5786151885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9594345092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7690238952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7418251037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7780895233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2223854064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7120094299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5216007232666</t>
+    <t xml:space="preserve">18.5786113739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9594326019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.769021987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7418231964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7780876159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2223834991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7120113372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.521598815918</t>
   </si>
   <si>
     <t xml:space="preserve">19.8117485046387</t>
@@ -2504,16 +2504,16 @@
     <t xml:space="preserve">19.4490604400635</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3130550384521</t>
+    <t xml:space="preserve">19.3130531311035</t>
   </si>
   <si>
     <t xml:space="preserve">18.7962245941162</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4970073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1732044219971</t>
+    <t xml:space="preserve">18.4970092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1732063293457</t>
   </si>
   <si>
     <t xml:space="preserve">17.4225521087646</t>
@@ -2522,64 +2522,64 @@
     <t xml:space="preserve">17.8033714294434</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9121761322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.039119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9892463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0663185119629</t>
+    <t xml:space="preserve">17.9121780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0391178131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9892482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0663146972656</t>
   </si>
   <si>
     <t xml:space="preserve">18.8596954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9050312042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7599563598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3791370391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4399929046631</t>
+    <t xml:space="preserve">18.9050331115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7599582672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3791389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4399948120117</t>
   </si>
   <si>
     <t xml:space="preserve">18.9685020446777</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0863742828369</t>
+    <t xml:space="preserve">19.0863761901855</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951808929443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.576000213623</t>
+    <t xml:space="preserve">19.5760021209717</t>
   </si>
   <si>
     <t xml:space="preserve">19.6394729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4218597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7392082214355</t>
+    <t xml:space="preserve">19.4218616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7392120361328</t>
   </si>
   <si>
     <t xml:space="preserve">19.94775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0021553039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8661499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4853286743164</t>
+    <t xml:space="preserve">20.0021572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8661479949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4853267669678</t>
   </si>
   <si>
     <t xml:space="preserve">19.6757411956787</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">19.1679782867432</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3221206665039</t>
+    <t xml:space="preserve">19.3221187591553</t>
   </si>
   <si>
     <t xml:space="preserve">19.0319709777832</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">19.2949180603027</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2677173614502</t>
+    <t xml:space="preserve">19.2677192687988</t>
   </si>
   <si>
     <t xml:space="preserve">19.5941371917725</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">19.8570823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4127902984619</t>
+    <t xml:space="preserve">19.4127922058105</t>
   </si>
   <si>
     <t xml:space="preserve">18.9957027435303</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">18.5332775115967</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9322319030762</t>
+    <t xml:space="preserve">18.9322338104248</t>
   </si>
   <si>
     <t xml:space="preserve">19.4762630462646</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">20.0112266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">19.965892791748</t>
+    <t xml:space="preserve">19.9658908843994</t>
   </si>
   <si>
     <t xml:space="preserve">20.3376445770264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9088745117188</t>
+    <t xml:space="preserve">20.9088726043701</t>
   </si>
   <si>
     <t xml:space="preserve">21.325963973999</t>
@@ -2657,112 +2657,112 @@
     <t xml:space="preserve">22.4049549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8337249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.981409072876</t>
+    <t xml:space="preserve">21.8337230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9814109802246</t>
   </si>
   <si>
     <t xml:space="preserve">19.9930896759033</t>
   </si>
   <si>
-    <t xml:space="preserve">20.192569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3039875030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.385591506958</t>
+    <t xml:space="preserve">20.1925678253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3039894104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3855934143066</t>
   </si>
   <si>
     <t xml:space="preserve">18.4607391357422</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6511516571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6239490509033</t>
+    <t xml:space="preserve">18.6511497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.623950958252</t>
   </si>
   <si>
     <t xml:space="preserve">18.03005027771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8195819854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.468578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8112077713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6532230377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.741283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7775506973267</t>
+    <t xml:space="preserve">16.8195838928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4685764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6842679977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8112058639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.653223991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7412824630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.777551651001</t>
   </si>
   <si>
     <t xml:space="preserve">14.3170480728149</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7341384887695</t>
+    <t xml:space="preserve">14.7341375350952</t>
   </si>
   <si>
     <t xml:space="preserve">15.1648283004761</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6914129257202</t>
+    <t xml:space="preserve">13.6914138793945</t>
   </si>
   <si>
     <t xml:space="preserve">14.090368270874</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2690992355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0242872238159</t>
+    <t xml:space="preserve">15.269100189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0242862701416</t>
   </si>
   <si>
     <t xml:space="preserve">15.0061492919922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2354440689087</t>
+    <t xml:space="preserve">14.2354431152344</t>
   </si>
   <si>
     <t xml:space="preserve">13.8863573074341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2380571365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4783363342285</t>
+    <t xml:space="preserve">13.2380561828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4783344268799</t>
   </si>
   <si>
     <t xml:space="preserve">13.5327386856079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9660406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.451132774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8092861175537</t>
+    <t xml:space="preserve">12.9660396575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4511346817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.809287071228</t>
   </si>
   <si>
     <t xml:space="preserve">14.1901073455811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2581119537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3695287704468</t>
+    <t xml:space="preserve">14.258111000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3695306777954</t>
   </si>
   <si>
     <t xml:space="preserve">13.8727569580078</t>
@@ -2771,49 +2771,49 @@
     <t xml:space="preserve">13.9634284973145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7820844650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2943801879883</t>
+    <t xml:space="preserve">13.7820854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2943811416626</t>
   </si>
   <si>
     <t xml:space="preserve">14.4485216140747</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5346593856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1512241363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3643064498901</t>
+    <t xml:space="preserve">14.5346603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1512260437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3643035888672</t>
   </si>
   <si>
     <t xml:space="preserve">15.6544551849365</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5683145523071</t>
+    <t xml:space="preserve">15.5683174133301</t>
   </si>
   <si>
     <t xml:space="preserve">15.346170425415</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6291732788086</t>
+    <t xml:space="preserve">16.6291751861572</t>
   </si>
   <si>
     <t xml:space="preserve">15.7768611907959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7904615402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4478282928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3752937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1097354888916</t>
+    <t xml:space="preserve">15.7904624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4478302001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3752918243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.109733581543</t>
   </si>
   <si>
     <t xml:space="preserve">16.0398082733154</t>
@@ -2822,10 +2822,10 @@
     <t xml:space="preserve">17.2446327209473</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4030952453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8813438415527</t>
+    <t xml:space="preserve">16.4030933380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8813457489014</t>
   </si>
   <si>
     <t xml:space="preserve">16.7066020965576</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">17.699893951416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9896030426025</t>
+    <t xml:space="preserve">17.9896011352539</t>
   </si>
   <si>
     <t xml:space="preserve">17.4515705108643</t>
@@ -2846,19 +2846,19 @@
     <t xml:space="preserve">17.658504486084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6079216003418</t>
+    <t xml:space="preserve">17.6079196929932</t>
   </si>
   <si>
     <t xml:space="preserve">17.3549995422363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6309146881104</t>
+    <t xml:space="preserve">17.6309127807617</t>
   </si>
   <si>
     <t xml:space="preserve">17.9850025177002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8884334564209</t>
+    <t xml:space="preserve">17.8884353637695</t>
   </si>
   <si>
     <t xml:space="preserve">18.6334018707275</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">18.8081474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6701889038086</t>
+    <t xml:space="preserve">18.67018699646</t>
   </si>
   <si>
     <t xml:space="preserve">17.7090873718262</t>
@@ -2882,28 +2882,28 @@
     <t xml:space="preserve">17.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3482913970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885074615479</t>
+    <t xml:space="preserve">18.3482894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885093688965</t>
   </si>
   <si>
     <t xml:space="preserve">18.5874137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9093132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8173427581787</t>
+    <t xml:space="preserve">18.9093151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8173446655273</t>
   </si>
   <si>
     <t xml:space="preserve">19.222017288208</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7161750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9645004272461</t>
+    <t xml:space="preserve">18.7161731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9644985198975</t>
   </si>
   <si>
     <t xml:space="preserve">18.7897529602051</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">19.0104846954346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0748634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5715065002441</t>
+    <t xml:space="preserve">19.0748615264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5715084075928</t>
   </si>
   <si>
     <t xml:space="preserve">19.3507785797119</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">19.9577903747559</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6542854309082</t>
+    <t xml:space="preserve">19.6542835235596</t>
   </si>
   <si>
     <t xml:space="preserve">19.7278594970703</t>
@@ -2939,22 +2939,22 @@
     <t xml:space="preserve">19.4703407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0957469940186</t>
+    <t xml:space="preserve">20.0957450866699</t>
   </si>
   <si>
     <t xml:space="preserve">20.2704925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3256740570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1534175872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.960277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3281631469727</t>
+    <t xml:space="preserve">20.3256759643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1534156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9602756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.328161239624</t>
   </si>
   <si>
     <t xml:space="preserve">21.0154590606689</t>
@@ -2969,19 +2969,19 @@
     <t xml:space="preserve">20.2245063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2337036132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8934078216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8223209381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4176464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3808574676514</t>
+    <t xml:space="preserve">20.2337017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8934097290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8223190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4176483154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.380859375</t>
   </si>
   <si>
     <t xml:space="preserve">20.206111907959</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">20.5556030273438</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8775024414062</t>
+    <t xml:space="preserve">20.8775043487549</t>
   </si>
   <si>
     <t xml:space="preserve">21.0614452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7303485870361</t>
+    <t xml:space="preserve">20.7303504943848</t>
   </si>
   <si>
     <t xml:space="preserve">20.7579402923584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7395439147949</t>
+    <t xml:space="preserve">20.7395458221436</t>
   </si>
   <si>
     <t xml:space="preserve">20.6291809082031</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">21.2453880310059</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3649520874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4201335906982</t>
+    <t xml:space="preserve">21.3649501800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4201354980469</t>
   </si>
   <si>
     <t xml:space="preserve">21.4937114715576</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">21.5580921173096</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5213012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0271472930908</t>
+    <t xml:space="preserve">21.5213031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0271453857422</t>
   </si>
   <si>
     <t xml:space="preserve">21.6040782928467</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">21.7420330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1191158294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.514591217041</t>
+    <t xml:space="preserve">22.1191139221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5145931243896</t>
   </si>
   <si>
     <t xml:space="preserve">22.6341571807861</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5421848297119</t>
+    <t xml:space="preserve">22.5421867370605</t>
   </si>
   <si>
     <t xml:space="preserve">22.6433544158936</t>
@@ -3065,25 +3065,25 @@
     <t xml:space="preserve">22.4410152435303</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2294826507568</t>
+    <t xml:space="preserve">22.2294807434082</t>
   </si>
   <si>
     <t xml:space="preserve">22.6709442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4870014190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9008712768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8732814788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8456897735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2135772705078</t>
+    <t xml:space="preserve">22.487003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9008731842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8732833862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8456916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2135753631592</t>
   </si>
   <si>
     <t xml:space="preserve">23.2411670684814</t>
@@ -3095,16 +3095,16 @@
     <t xml:space="preserve">23.5262775421143</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5722618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0045299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7194194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3356246948242</t>
+    <t xml:space="preserve">23.5722637176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0045280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7194213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3356227874756</t>
   </si>
   <si>
     <t xml:space="preserve">24.3264293670654</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">23.875768661499</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1700782775879</t>
+    <t xml:space="preserve">24.1700763702393</t>
   </si>
   <si>
     <t xml:space="preserve">23.5998554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6525478363037</t>
+    <t xml:space="preserve">22.6525497436523</t>
   </si>
   <si>
     <t xml:space="preserve">22.7261257171631</t>
@@ -3128,25 +3128,25 @@
     <t xml:space="preserve">22.9560565948486</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1926918029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6684551239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1993999481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6500644683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4661197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0823287963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.588171005249</t>
+    <t xml:space="preserve">22.1926956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.66845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1994018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6500625610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.466121673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0823268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5881690979004</t>
   </si>
   <si>
     <t xml:space="preserve">24.041316986084</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">23.0112400054932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1216049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6274490356445</t>
+    <t xml:space="preserve">23.121603012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6274471282959</t>
   </si>
   <si>
     <t xml:space="preserve">24.2988376617432</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">23.9217567443848</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9033622741699</t>
+    <t xml:space="preserve">23.9033603668213</t>
   </si>
   <si>
     <t xml:space="preserve">24.4459934234619</t>
@@ -3185,19 +3185,19 @@
     <t xml:space="preserve">24.0965042114258</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7403011322021</t>
+    <t xml:space="preserve">24.7402992248535</t>
   </si>
   <si>
     <t xml:space="preserve">25.2277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8966522216797</t>
+    <t xml:space="preserve">24.8966541290283</t>
   </si>
   <si>
     <t xml:space="preserve">24.4092044830322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5471630096436</t>
+    <t xml:space="preserve">24.5471611022949</t>
   </si>
   <si>
     <t xml:space="preserve">25.0622005462646</t>
@@ -3215,28 +3215,28 @@
     <t xml:space="preserve">24.8874530792236</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3105220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5680446624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0805969238281</t>
+    <t xml:space="preserve">25.3105239868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5680408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0805931091309</t>
   </si>
   <si>
     <t xml:space="preserve">25.3841018676758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5036640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3749027252197</t>
+    <t xml:space="preserve">25.503662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3749046325684</t>
   </si>
   <si>
     <t xml:space="preserve">25.7151966094971</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9359283447266</t>
+    <t xml:space="preserve">25.9359264373779</t>
   </si>
   <si>
     <t xml:space="preserve">26.6257133483887</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">26.8740348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0119972229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5546264648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2811985015869</t>
+    <t xml:space="preserve">27.0119934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5546245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2812004089355</t>
   </si>
   <si>
     <t xml:space="preserve">27.9225101470947</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">28.0880584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3957862854004</t>
+    <t xml:space="preserve">26.395788192749</t>
   </si>
   <si>
     <t xml:space="preserve">26.5521373748779</t>
@@ -3278,34 +3278,34 @@
     <t xml:space="preserve">26.1106719970703</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8439559936523</t>
+    <t xml:space="preserve">25.843957901001</t>
   </si>
   <si>
     <t xml:space="preserve">26.0278987884521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7519874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6876049041748</t>
+    <t xml:space="preserve">25.7519836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6876068115234</t>
   </si>
   <si>
     <t xml:space="preserve">24.7127094268799</t>
   </si>
   <si>
-    <t xml:space="preserve">24.280445098877</t>
+    <t xml:space="preserve">24.2804431915283</t>
   </si>
   <si>
     <t xml:space="preserve">25.1449737548828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5011730194092</t>
+    <t xml:space="preserve">24.5011749267578</t>
   </si>
   <si>
     <t xml:space="preserve">25.0346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2369499206543</t>
+    <t xml:space="preserve">25.2369480133057</t>
   </si>
   <si>
     <t xml:space="preserve">25.6968040466309</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">26.0462951660156</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9175357818604</t>
+    <t xml:space="preserve">25.9175338745117</t>
   </si>
   <si>
     <t xml:space="preserve">26.2854194641113</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9267330169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9083366394043</t>
+    <t xml:space="preserve">25.9267311096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9083385467529</t>
   </si>
   <si>
     <t xml:space="preserve">26.1198711395264</t>
@@ -3332,19 +3332,19 @@
     <t xml:space="preserve">26.0003089904785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6600131988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0530033111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5931453704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.390811920166</t>
+    <t xml:space="preserve">25.9635200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6600151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0530014038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.593147277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3908081054688</t>
   </si>
   <si>
     <t xml:space="preserve">24.1608810424805</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">24.5563583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5195713043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0162143707275</t>
+    <t xml:space="preserve">24.5195693969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0162162780762</t>
   </si>
   <si>
     <t xml:space="preserve">24.9150466918945</t>
@@ -3368,22 +3368,22 @@
     <t xml:space="preserve">24.0137271881104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2712478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2001571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2620487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.673433303833</t>
+    <t xml:space="preserve">24.2712459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2001609802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2620506286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6734313964844</t>
   </si>
   <si>
     <t xml:space="preserve">23.5446739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6918258666992</t>
+    <t xml:space="preserve">23.6918277740479</t>
   </si>
   <si>
     <t xml:space="preserve">23.4251098632812</t>
@@ -3392,55 +3392,55 @@
     <t xml:space="preserve">23.3055477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5170803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7838001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1056976318359</t>
+    <t xml:space="preserve">23.5170822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1056995391846</t>
   </si>
   <si>
     <t xml:space="preserve">24.151683807373</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5287647247314</t>
+    <t xml:space="preserve">24.5287666320801</t>
   </si>
   <si>
     <t xml:space="preserve">24.8138790130615</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8322715759277</t>
+    <t xml:space="preserve">24.8322734832764</t>
   </si>
   <si>
     <t xml:space="preserve">24.9886245727539</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4852676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7703819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6416168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8414688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6943168640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1081867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9518337249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.33811378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4919757843018</t>
+    <t xml:space="preserve">25.4852695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7703800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6416187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8414707183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.694314956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1081848144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9518356323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3381156921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4919776916504</t>
   </si>
   <si>
     <t xml:space="preserve">24.5379638671875</t>
@@ -3452,25 +3452,25 @@
     <t xml:space="preserve">23.9861335754395</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9585418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4000091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.949348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7954807281494</t>
+    <t xml:space="preserve">23.9585437774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4000072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9493465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.795482635498</t>
   </si>
   <si>
     <t xml:space="preserve">24.2252616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3197212219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4693641662598</t>
+    <t xml:space="preserve">25.3197231292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4693622589111</t>
   </si>
   <si>
     <t xml:space="preserve">26.4325752258301</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">26.1826114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1919727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5196075439453</t>
+    <t xml:space="preserve">26.1919746398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5196056365967</t>
   </si>
   <si>
     <t xml:space="preserve">26.4259967803955</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">27.3901767730713</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5867576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7926998138428</t>
+    <t xml:space="preserve">27.5867557525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7927017211914</t>
   </si>
   <si>
     <t xml:space="preserve">27.7084522247314</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">27.2872066497803</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3808174133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6990909576416</t>
+    <t xml:space="preserve">27.3808155059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.699089050293</t>
   </si>
   <si>
     <t xml:space="preserve">27.1935977935791</t>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">27.1655139923096</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9237518310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8395023345947</t>
+    <t xml:space="preserve">27.9237537384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8395042419434</t>
   </si>
   <si>
     <t xml:space="preserve">27.8020610809326</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">28.3075523376465</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6819877624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.298189163208</t>
+    <t xml:space="preserve">28.6819896697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2981872558594</t>
   </si>
   <si>
     <t xml:space="preserve">28.3169116973877</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">27.9799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5696582794189</t>
+    <t xml:space="preserve">28.5696601867676</t>
   </si>
   <si>
     <t xml:space="preserve">28.8317642211914</t>
@@ -3593,28 +3593,28 @@
     <t xml:space="preserve">28.4198837280273</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4760513305664</t>
+    <t xml:space="preserve">28.4760494232178</t>
   </si>
   <si>
     <t xml:space="preserve">27.6710052490234</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1203327178955</t>
+    <t xml:space="preserve">28.1203308105469</t>
   </si>
   <si>
     <t xml:space="preserve">27.8301429748535</t>
   </si>
   <si>
-    <t xml:space="preserve">27.989278793335</t>
+    <t xml:space="preserve">27.9892807006836</t>
   </si>
   <si>
     <t xml:space="preserve">28.1671371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2701091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1390552520752</t>
+    <t xml:space="preserve">28.2701072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1390533447266</t>
   </si>
   <si>
     <t xml:space="preserve">28.2888278961182</t>
@@ -3629,10 +3629,10 @@
     <t xml:space="preserve">28.7849617004395</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8785705566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0002632141113</t>
+    <t xml:space="preserve">28.8785724639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0002613067627</t>
   </si>
   <si>
     <t xml:space="preserve">29.3934230804443</t>
@@ -3641,10 +3641,10 @@
     <t xml:space="preserve">30.2359104156494</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3201560974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1797466278076</t>
+    <t xml:space="preserve">30.3201580047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.179744720459</t>
   </si>
   <si>
     <t xml:space="preserve">29.8146667480469</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">29.5806427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8708324432373</t>
+    <t xml:space="preserve">29.8708305358887</t>
   </si>
   <si>
     <t xml:space="preserve">29.9082775115967</t>
@@ -3689,16 +3689,16 @@
     <t xml:space="preserve">30.4044055938721</t>
   </si>
   <si>
-    <t xml:space="preserve">30.385684967041</t>
+    <t xml:space="preserve">30.3856830596924</t>
   </si>
   <si>
     <t xml:space="preserve">30.8630962371826</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8537311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0018863677979</t>
+    <t xml:space="preserve">30.8537330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0018844604492</t>
   </si>
   <si>
     <t xml:space="preserve">30.5448246002197</t>
@@ -3710,7 +3710,7 @@
     <t xml:space="preserve">30.4699325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">30.713321685791</t>
+    <t xml:space="preserve">30.7133197784424</t>
   </si>
   <si>
     <t xml:space="preserve">30.1142158508301</t>
@@ -3722,10 +3722,10 @@
     <t xml:space="preserve">29.6461696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3185367584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.029972076416</t>
+    <t xml:space="preserve">29.3185348510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0299701690674</t>
   </si>
   <si>
     <t xml:space="preserve">30.3482398986816</t>
@@ -3734,28 +3734,28 @@
     <t xml:space="preserve">29.6742515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9534606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8130435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2420253753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5212306976318</t>
+    <t xml:space="preserve">28.9534587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.813045501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2420234680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5212287902832</t>
   </si>
   <si>
     <t xml:space="preserve">27.4837875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0267219543457</t>
+    <t xml:space="preserve">28.0267238616943</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6616439819336</t>
+    <t xml:space="preserve">27.6616458892822</t>
   </si>
   <si>
     <t xml:space="preserve">28.6445484161377</t>
@@ -3779,19 +3779,19 @@
     <t xml:space="preserve">30.1610240936279</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4792976379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5916271209717</t>
+    <t xml:space="preserve">30.4792995452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5916290283203</t>
   </si>
   <si>
     <t xml:space="preserve">30.36696434021</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6384296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6103477478027</t>
+    <t xml:space="preserve">30.6384315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6103496551514</t>
   </si>
   <si>
     <t xml:space="preserve">30.7694816589355</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">31.1626472473145</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6681385040283</t>
+    <t xml:space="preserve">31.6681365966797</t>
   </si>
   <si>
     <t xml:space="preserve">31.855354309082</t>
@@ -3818,10 +3818,10 @@
     <t xml:space="preserve">31.1813678741455</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2749786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8179168701172</t>
+    <t xml:space="preserve">31.2749767303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8179130554199</t>
   </si>
   <si>
     <t xml:space="preserve">31.9302444458008</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">32.763370513916</t>
   </si>
   <si>
-    <t xml:space="preserve">32.641674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9489650726318</t>
+    <t xml:space="preserve">32.6416778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9489631652832</t>
   </si>
   <si>
     <t xml:space="preserve">31.6962223052979</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1081047058105</t>
+    <t xml:space="preserve">32.1081008911133</t>
   </si>
   <si>
     <t xml:space="preserve">30.6945972442627</t>
@@ -3851,13 +3851,13 @@
     <t xml:space="preserve">31.3124217987061</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7320442199707</t>
+    <t xml:space="preserve">30.7320423126221</t>
   </si>
   <si>
     <t xml:space="preserve">30.5822620391846</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8911781311035</t>
+    <t xml:space="preserve">30.8911762237549</t>
   </si>
   <si>
     <t xml:space="preserve">31.7523822784424</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">30.9473457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7039585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3576030731201</t>
+    <t xml:space="preserve">30.7039566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3576011657715</t>
   </si>
   <si>
     <t xml:space="preserve">30.0861339569092</t>
@@ -3881,19 +3881,19 @@
     <t xml:space="preserve">29.5525608062744</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7023334503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7507610321045</t>
+    <t xml:space="preserve">29.702335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7507591247559</t>
   </si>
   <si>
     <t xml:space="preserve">30.9754257202148</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9379825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0690364837646</t>
+    <t xml:space="preserve">30.9379806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.069034576416</t>
   </si>
   <si>
     <t xml:space="preserve">30.9567050933838</t>
@@ -3923,10 +3923,10 @@
     <t xml:space="preserve">31.3779468536377</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5073757171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9721813201904</t>
+    <t xml:space="preserve">30.5073776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9721794128418</t>
   </si>
   <si>
     <t xml:space="preserve">27.6335620880127</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">27.0063781738281</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0454425811768</t>
+    <t xml:space="preserve">28.0454444885254</t>
   </si>
   <si>
     <t xml:space="preserve">26.8378810882568</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">26.8191585540771</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5664119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.248140335083</t>
+    <t xml:space="preserve">26.5664100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2481422424316</t>
   </si>
   <si>
     <t xml:space="preserve">25.7800922393799</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">26.1077251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5399551391602</t>
+    <t xml:space="preserve">27.5399532318115</t>
   </si>
   <si>
     <t xml:space="preserve">28.5415744781494</t>
@@ -3998,13 +3998,13 @@
     <t xml:space="preserve">25.9766712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1374282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9502124786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7287940979004</t>
+    <t xml:space="preserve">27.13743019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9502143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.728796005249</t>
   </si>
   <si>
     <t xml:space="preserve">27.596118927002</t>
@@ -4025,28 +4025,28 @@
     <t xml:space="preserve">29.1219577789307</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1406764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8598480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6071033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2326641082764</t>
+    <t xml:space="preserve">29.1406745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8598499298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6071014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2326622009277</t>
   </si>
   <si>
     <t xml:space="preserve">28.8692111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0096244812012</t>
+    <t xml:space="preserve">29.0096225738525</t>
   </si>
   <si>
     <t xml:space="preserve">29.290454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9815406799316</t>
+    <t xml:space="preserve">28.981538772583</t>
   </si>
   <si>
     <t xml:space="preserve">29.5151176452637</t>
@@ -6447,6 +6447,9 @@
   </si>
   <si>
     <t xml:space="preserve">87.879997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5</t>
   </si>
 </sst>
 </file>
@@ -71499,7 +71502,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6500925926</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>819521</v>
@@ -71520,6 +71523,32 @@
         <v>2143</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6496180556</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>1080138</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>90.6600036621094</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>87.9599990844727</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>88.9599990844727</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>2145</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6851558685303</t>
+    <t xml:space="preserve">15.6851539611816</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
@@ -47,61 +47,61 @@
     <t xml:space="preserve">15.8714008331299</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3207635879517</t>
+    <t xml:space="preserve">15.3207588195801</t>
   </si>
   <si>
     <t xml:space="preserve">15.239785194397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.74582862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9644660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2964668273926</t>
+    <t xml:space="preserve">14.7458295822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9644632339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2964639663696</t>
   </si>
   <si>
     <t xml:space="preserve">15.4989109039307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0616359710693</t>
+    <t xml:space="preserve">15.061637878418</t>
   </si>
   <si>
     <t xml:space="preserve">14.5028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5433893203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8510999679565</t>
+    <t xml:space="preserve">14.5433864593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8511009216309</t>
   </si>
   <si>
     <t xml:space="preserve">14.1870889663696</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9401702880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4098339080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9239778518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1831035614014</t>
+    <t xml:space="preserve">14.9401721954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4098358154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9239768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2802715301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1831026077271</t>
   </si>
   <si>
     <t xml:space="preserve">14.6243629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3936395645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8106098175049</t>
+    <t xml:space="preserve">15.3936414718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8106107711792</t>
   </si>
   <si>
     <t xml:space="preserve">14.7296333312988</t>
@@ -110,43 +110,43 @@
     <t xml:space="preserve">14.8996829986572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5190944671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.73362159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.344934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0980167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3206415176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.474494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8955726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7822074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3328485488892</t>
+    <t xml:space="preserve">14.5190925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7336196899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3449354171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0980176925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3206396102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4744968414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8955755233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7822065353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3328466415405</t>
   </si>
   <si>
     <t xml:space="preserve">14.2194786071777</t>
   </si>
   <si>
-    <t xml:space="preserve">14.405725479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8349027633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5514831542969</t>
+    <t xml:space="preserve">14.4057264328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8348999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5514822006226</t>
   </si>
   <si>
     <t xml:space="preserve">14.3409461975098</t>
@@ -155,22 +155,22 @@
     <t xml:space="preserve">14.8672904968262</t>
   </si>
   <si>
-    <t xml:space="preserve">15.102123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4827136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3774471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017353057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4665184020996</t>
+    <t xml:space="preserve">15.1021251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2235918045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3774461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4017391204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.466516494751</t>
   </si>
   <si>
     <t xml:space="preserve">15.4908103942871</t>
@@ -188,25 +188,25 @@
     <t xml:space="preserve">15.7742338180542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8390092849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879831314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.636570930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9199895858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8309106826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8794975280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8228130340576</t>
+    <t xml:space="preserve">15.8390140533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.587984085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6365718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9199867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8309116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8795013427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8228158950806</t>
   </si>
   <si>
     <t xml:space="preserve">15.8956937789917</t>
@@ -218,70 +218,70 @@
     <t xml:space="preserve">16.122428894043</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8471088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8875970840454</t>
+    <t xml:space="preserve">15.847110748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8875961303711</t>
   </si>
   <si>
     <t xml:space="preserve">15.4422273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3855428695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2276992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7135562896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6568717956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4301414489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6120529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9179992675781</t>
+    <t xml:space="preserve">15.3855438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086757659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2276973724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7135581970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6568737030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.430139541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6120548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9180011749268</t>
   </si>
   <si>
     <t xml:space="preserve">17.0254955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9758815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9924201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.628589630127</t>
+    <t xml:space="preserve">16.9758796691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9924182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6285915374756</t>
   </si>
   <si>
     <t xml:space="preserve">16.7774314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9841499328613</t>
+    <t xml:space="preserve">16.98415184021</t>
   </si>
   <si>
     <t xml:space="preserve">17.1081829071045</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9345397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5541725158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5955181121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7608890533447</t>
+    <t xml:space="preserve">16.9345359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5541744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5955142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.760892868042</t>
   </si>
   <si>
     <t xml:space="preserve">16.703010559082</t>
@@ -290,82 +290,82 @@
     <t xml:space="preserve">16.8766574859619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4058589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7696876525879</t>
+    <t xml:space="preserve">17.4058609008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696857452393</t>
   </si>
   <si>
     <t xml:space="preserve">18.0094833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9681396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8606472015381</t>
+    <t xml:space="preserve">17.9681415557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8606452941895</t>
   </si>
   <si>
     <t xml:space="preserve">17.7779579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8854503631592</t>
+    <t xml:space="preserve">17.8854541778564</t>
   </si>
   <si>
     <t xml:space="preserve">17.6952705383301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1087112426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9598712921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2658176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748600006104</t>
+    <t xml:space="preserve">18.1087093353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9598693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2658195495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1748580932617</t>
   </si>
   <si>
     <t xml:space="preserve">18.282356262207</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2988948822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4725379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1831302642822</t>
+    <t xml:space="preserve">18.2988929748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4725399017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1831321716309</t>
   </si>
   <si>
     <t xml:space="preserve">18.1335182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0425567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8027629852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0921745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9185276031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0012149810791</t>
+    <t xml:space="preserve">18.0425624847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8027648925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0921726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9185256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0012168884277</t>
   </si>
   <si>
     <t xml:space="preserve">17.314905166626</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9097309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8022365570068</t>
+    <t xml:space="preserve">16.9097328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8022384643555</t>
   </si>
   <si>
     <t xml:space="preserve">17.7366142272949</t>
@@ -380,76 +380,76 @@
     <t xml:space="preserve">17.9102573394775</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6694097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8342599868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1402063369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2559661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2978401184082</t>
+    <t xml:space="preserve">15.6694078445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8342571258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1402053833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2559690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399578094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2978382110596</t>
   </si>
   <si>
     <t xml:space="preserve">15.7272882461548</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5867214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2311639785767</t>
+    <t xml:space="preserve">15.5867223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2311611175537</t>
   </si>
   <si>
     <t xml:space="preserve">15.6115283966064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2813034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6533966064453</t>
+    <t xml:space="preserve">16.2812995910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4632167816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6533985137939</t>
   </si>
   <si>
     <t xml:space="preserve">16.6864757537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6782054901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7443561553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6699333190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8435840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.818775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9510726928711</t>
+    <t xml:space="preserve">16.6782035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7443542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6699371337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8435802459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8187732696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9510746002197</t>
   </si>
   <si>
     <t xml:space="preserve">17.0999145507812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1164531707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2983684539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2404842376709</t>
+    <t xml:space="preserve">17.1164512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2983646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2404880523682</t>
   </si>
   <si>
     <t xml:space="preserve">17.0751075744629</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">17.6208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1004428863525</t>
+    <t xml:space="preserve">18.1004409790039</t>
   </si>
   <si>
     <t xml:space="preserve">17.6125793457031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5960445404053</t>
+    <t xml:space="preserve">17.5960426330566</t>
   </si>
   <si>
     <t xml:space="preserve">18.0756359100342</t>
@@ -479,16 +479,16 @@
     <t xml:space="preserve">17.8771858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1913967132568</t>
+    <t xml:space="preserve">18.1913986206055</t>
   </si>
   <si>
     <t xml:space="preserve">18.2492790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0839023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2906227111816</t>
+    <t xml:space="preserve">18.0839004516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2906246185303</t>
   </si>
   <si>
     <t xml:space="preserve">18.1665897369385</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">17.9929485321045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8441047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7200775146484</t>
+    <t xml:space="preserve">17.844108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7200736999512</t>
   </si>
   <si>
     <t xml:space="preserve">17.728343963623</t>
@@ -509,64 +509,64 @@
     <t xml:space="preserve">17.8937206268311</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0673656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.37331199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9438610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4317226409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3573055267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1009635925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1257762908936</t>
+    <t xml:space="preserve">18.0673637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3733139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9438629150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4317207336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3573017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1009654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1257743835449</t>
   </si>
   <si>
     <t xml:space="preserve">19.1919250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">19.175386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2828807830811</t>
+    <t xml:space="preserve">19.1753883361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2828845977783</t>
   </si>
   <si>
     <t xml:space="preserve">19.1340446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3490352630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978694915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7624740600586</t>
+    <t xml:space="preserve">19.3490314483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978733062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7624702453613</t>
   </si>
   <si>
     <t xml:space="preserve">19.6549777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">19.70458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4647941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0596237182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6461811065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1175079345703</t>
+    <t xml:space="preserve">19.7045936584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4647960662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0596256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.646183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1175060272217</t>
   </si>
   <si>
     <t xml:space="preserve">19.1588516235352</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">19.0100135803223</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7536811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.902515411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0844306945801</t>
+    <t xml:space="preserve">18.7536792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9025211334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0844326019287</t>
   </si>
   <si>
     <t xml:space="preserve">18.9934749603271</t>
@@ -593,49 +593,49 @@
     <t xml:space="preserve">18.7867527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7454090118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3319702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6291217803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8694438934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1505813598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3485069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6627178192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.728874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6875267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8942489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.422924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.480806350708</t>
+    <t xml:space="preserve">18.7454071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3319683074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6291198730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8694400787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1505832672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3485088348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6627216339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7288703918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6875286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8942451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4229259490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4808101654053</t>
   </si>
   <si>
     <t xml:space="preserve">18.2327423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3236999511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0590991973877</t>
+    <t xml:space="preserve">18.3236980438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0590972900391</t>
   </si>
   <si>
     <t xml:space="preserve">18.6709899902344</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">19.4399871826172</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8782329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6797828674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1676445007324</t>
+    <t xml:space="preserve">19.8782367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6797847747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1676483154297</t>
   </si>
   <si>
     <t xml:space="preserve">19.8451614379883</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">19.7790126800537</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1428413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9113140106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1759147644043</t>
+    <t xml:space="preserve">20.1428394317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9113121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1759185791016</t>
   </si>
   <si>
     <t xml:space="preserve">20.0022678375244</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9278507232666</t>
+    <t xml:space="preserve">19.927848815918</t>
   </si>
   <si>
     <t xml:space="preserve">20.0105381011963</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">20.1263027191162</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1097640991211</t>
+    <t xml:space="preserve">20.1097660064697</t>
   </si>
   <si>
     <t xml:space="preserve">20.1924514770508</t>
@@ -710,52 +710,52 @@
     <t xml:space="preserve">20.3164825439453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2420654296875</t>
+    <t xml:space="preserve">20.2420616149902</t>
   </si>
   <si>
     <t xml:space="preserve">20.3330211639404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.225528717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6555023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5066680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3578281402588</t>
+    <t xml:space="preserve">20.2255268096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6555061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5066699981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3578300476074</t>
   </si>
   <si>
     <t xml:space="preserve">20.4818592071533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0849590301514</t>
+    <t xml:space="preserve">20.0849571228027</t>
   </si>
   <si>
     <t xml:space="preserve">20.3991718292236</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5645523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5397415161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6885795593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8947734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4074401855469</t>
+    <t xml:space="preserve">20.5645484924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5397396087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6885814666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.894775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4074440002441</t>
   </si>
   <si>
     <t xml:space="preserve">20.7133865356445</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9697246551514</t>
+    <t xml:space="preserve">20.9697227478027</t>
   </si>
   <si>
     <t xml:space="preserve">20.3495597839355</t>
@@ -764,85 +764,85 @@
     <t xml:space="preserve">20.423978805542</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3082180023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7547340393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9609260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8865070343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8286285400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8534297943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1180305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5722904205322</t>
+    <t xml:space="preserve">20.3082141876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.754732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9609279632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8865051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8286266326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8534317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1180324554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5722923278809</t>
   </si>
   <si>
     <t xml:space="preserve">19.2994194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5144081115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.423454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6136341094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.564022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3821067810059</t>
+    <t xml:space="preserve">19.5144062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4234523773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6136379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5640201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3821105957031</t>
   </si>
   <si>
     <t xml:space="preserve">19.7376670837402</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3661003112793</t>
+    <t xml:space="preserve">20.3660984039307</t>
   </si>
   <si>
     <t xml:space="preserve">19.9361190795898</t>
   </si>
   <si>
-    <t xml:space="preserve">20.200719833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4901294708252</t>
+    <t xml:space="preserve">20.2007160186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4901313781738</t>
   </si>
   <si>
     <t xml:space="preserve">20.7381935119629</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2922019958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1516361236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.085485458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9366416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7795372009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4570541381836</t>
+    <t xml:space="preserve">21.2922058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1516342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0854816436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9366455078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7795391082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.457052230835</t>
   </si>
   <si>
     <t xml:space="preserve">20.7051200866699</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">21.1268291473389</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0435562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1192493438721</t>
+    <t xml:space="preserve">22.0435581207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1192512512207</t>
   </si>
   <si>
     <t xml:space="preserve">21.8669414520264</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">22.2958679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">22.472484588623</t>
+    <t xml:space="preserve">22.4724884033203</t>
   </si>
   <si>
     <t xml:space="preserve">22.2201747894287</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">22.262228012085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5397682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5734100341797</t>
+    <t xml:space="preserve">22.5397701263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5734081268311</t>
   </si>
   <si>
     <t xml:space="preserve">22.5986423492432</t>
@@ -887,34 +887,34 @@
     <t xml:space="preserve">21.8080673217773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6987342834473</t>
+    <t xml:space="preserve">21.69873046875</t>
   </si>
   <si>
     <t xml:space="preserve">21.0847778320312</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3202686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9502105712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6390247344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4203605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5549221038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4540004730225</t>
+    <t xml:space="preserve">21.3202667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9502124786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6390266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4203586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5549240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4540023803711</t>
   </si>
   <si>
     <t xml:space="preserve">20.9670314788818</t>
   </si>
   <si>
-    <t xml:space="preserve">21.19411277771</t>
+    <t xml:space="preserve">21.1941108703613</t>
   </si>
   <si>
     <t xml:space="preserve">20.8576984405518</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">20.8324661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9586181640625</t>
+    <t xml:space="preserve">20.9586200714111</t>
   </si>
   <si>
     <t xml:space="preserve">20.8156452178955</t>
@@ -938,37 +938,37 @@
     <t xml:space="preserve">21.2613945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1015968322754</t>
+    <t xml:space="preserve">21.1015949249268</t>
   </si>
   <si>
     <t xml:space="preserve">21.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.614631652832</t>
+    <t xml:space="preserve">21.6146297454834</t>
   </si>
   <si>
     <t xml:space="preserve">21.8164806365967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.656681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8248901367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.547342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5725765228271</t>
+    <t xml:space="preserve">21.6566791534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8248920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5473461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5725784301758</t>
   </si>
   <si>
     <t xml:space="preserve">22.0351486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.858528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9258117675781</t>
+    <t xml:space="preserve">21.8585300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9258098602295</t>
   </si>
   <si>
     <t xml:space="preserve">21.7828369140625</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">22.3211002349854</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4884719848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3875522613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1949443817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8501205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2454071044922</t>
+    <t xml:space="preserve">21.4884738922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3875503540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1949462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8501224517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2454051971436</t>
   </si>
   <si>
     <t xml:space="preserve">22.0015068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3883800506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538166046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5481815338135</t>
+    <t xml:space="preserve">22.3883819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538185119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5481796264648</t>
   </si>
   <si>
     <t xml:space="preserve">22.5313587188721</t>
@@ -1016,25 +1016,25 @@
     <t xml:space="preserve">22.5818214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8425445556641</t>
+    <t xml:space="preserve">22.8425407409668</t>
   </si>
   <si>
     <t xml:space="preserve">22.564998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1444835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.211763381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1865348815918</t>
+    <t xml:space="preserve">22.1444816589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2117652893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1865329742432</t>
   </si>
   <si>
     <t xml:space="preserve">22.52294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7920742034912</t>
+    <t xml:space="preserve">22.7920780181885</t>
   </si>
   <si>
     <t xml:space="preserve">22.4220237731934</t>
@@ -1043,34 +1043,34 @@
     <t xml:space="preserve">22.7500267028809</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9266490936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9350547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8593654632568</t>
+    <t xml:space="preserve">22.9266471862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9350566864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8593635559082</t>
   </si>
   <si>
     <t xml:space="preserve">22.7079753875732</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7416172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5902309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2369956970215</t>
+    <t xml:space="preserve">22.7416210174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5902328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2369976043701</t>
   </si>
   <si>
     <t xml:space="preserve">21.8417091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.161304473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3547420501709</t>
+    <t xml:space="preserve">22.1613025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3547401428223</t>
   </si>
   <si>
     <t xml:space="preserve">22.3042793273926</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">22.2285842895508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.11083984375</t>
+    <t xml:space="preserve">22.1108417510986</t>
   </si>
   <si>
     <t xml:space="preserve">21.9174003601074</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3463306427002</t>
+    <t xml:space="preserve">22.3463325500488</t>
   </si>
   <si>
     <t xml:space="preserve">22.4304351806641</t>
@@ -1103,49 +1103,49 @@
     <t xml:space="preserve">23.6331176757812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6751651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6835803985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8097324371338</t>
+    <t xml:space="preserve">23.6751689910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6835784912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8097343444824</t>
   </si>
   <si>
     <t xml:space="preserve">23.9106578826904</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9190711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.750862121582</t>
+    <t xml:space="preserve">23.9190692901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7508602142334</t>
   </si>
   <si>
     <t xml:space="preserve">23.8770160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9863471984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8938388824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9527072906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9779376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8517875671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0368137359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4741516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3311767578125</t>
+    <t xml:space="preserve">23.986349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8938369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9527111053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9779415130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.85178565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0368118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4741497039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3311748504639</t>
   </si>
   <si>
     <t xml:space="preserve">24.3143577575684</t>
@@ -1172,16 +1172,16 @@
     <t xml:space="preserve">24.558256149292</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5077953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.356409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3984622955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.919900894165</t>
+    <t xml:space="preserve">24.5077972412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3564071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3984603881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9199047088623</t>
   </si>
   <si>
     <t xml:space="preserve">24.7937450408936</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">24.8946685791016</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2310848236084</t>
+    <t xml:space="preserve">25.2310829162598</t>
   </si>
   <si>
     <t xml:space="preserve">25.1217498779297</t>
@@ -1202,25 +1202,25 @@
     <t xml:space="preserve">25.1890316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8526191711426</t>
+    <t xml:space="preserve">24.8526210784912</t>
   </si>
   <si>
     <t xml:space="preserve">24.4489212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5574226379395</t>
+    <t xml:space="preserve">23.5574207305908</t>
   </si>
   <si>
     <t xml:space="preserve">23.3892154693604</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5994758605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2126007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9274768829346</t>
+    <t xml:space="preserve">23.5994739532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2125968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9274806976318</t>
   </si>
   <si>
     <t xml:space="preserve">23.6919898986816</t>
@@ -1229,31 +1229,31 @@
     <t xml:space="preserve">23.5406036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5742454528809</t>
+    <t xml:space="preserve">23.5742416381836</t>
   </si>
   <si>
     <t xml:space="preserve">23.3808040618896</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4144458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.532190322876</t>
+    <t xml:space="preserve">23.4144477844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5321884155273</t>
   </si>
   <si>
     <t xml:space="preserve">23.9695301055908</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9939270019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6911582946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014186859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.977108001709</t>
+    <t xml:space="preserve">22.9939289093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6911544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014148712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9771099090576</t>
   </si>
   <si>
     <t xml:space="preserve">23.0443897247314</t>
@@ -1265,31 +1265,31 @@
     <t xml:space="preserve">23.0359783172607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8930053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6827449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1789588928223</t>
+    <t xml:space="preserve">22.8930072784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6827430725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1789569854736</t>
   </si>
   <si>
     <t xml:space="preserve">23.2546482086182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2210083007812</t>
+    <t xml:space="preserve">23.2210102081299</t>
   </si>
   <si>
     <t xml:space="preserve">23.1621360778809</t>
   </si>
   <si>
-    <t xml:space="preserve">23.229419708252</t>
+    <t xml:space="preserve">23.2294158935547</t>
   </si>
   <si>
     <t xml:space="preserve">23.078031539917</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8677730560303</t>
+    <t xml:space="preserve">22.8677711486816</t>
   </si>
   <si>
     <t xml:space="preserve">23.0107498168945</t>
@@ -1298,88 +1298,88 @@
     <t xml:space="preserve">24.1881999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0031700134277</t>
+    <t xml:space="preserve">24.0031719207764</t>
   </si>
   <si>
     <t xml:space="preserve">24.1713790893555</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2218399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3900508880615</t>
+    <t xml:space="preserve">24.2218418121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3900489807129</t>
   </si>
   <si>
     <t xml:space="preserve">24.4909725189209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8273868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5246124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3395881652832</t>
+    <t xml:space="preserve">24.8273887634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5246143341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3395862579346</t>
   </si>
   <si>
     <t xml:space="preserve">24.305944442749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8686046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8349666595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2882881164551</t>
+    <t xml:space="preserve">23.8686065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8349628448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.288293838501</t>
   </si>
   <si>
     <t xml:space="preserve">22.9602851867676</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6070556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4564990997314</t>
+    <t xml:space="preserve">22.6070518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4564971923828</t>
   </si>
   <si>
     <t xml:space="preserve">22.7163867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4556674957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0687885284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1781215667725</t>
+    <t xml:space="preserve">22.4556636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0687923431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1781234741211</t>
   </si>
   <si>
     <t xml:space="preserve">22.0940189361572</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9089946746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.799654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6314468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7912483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3631534576416</t>
+    <t xml:space="preserve">21.908992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7996578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6314506530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7912445068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">22.3967933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2874622344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0856094360352</t>
+    <t xml:space="preserve">22.2874584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0856113433838</t>
   </si>
   <si>
     <t xml:space="preserve">21.6230392456055</t>
@@ -1391,37 +1391,37 @@
     <t xml:space="preserve">21.4043712615967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4464244842529</t>
+    <t xml:space="preserve">21.446418762207</t>
   </si>
   <si>
     <t xml:space="preserve">21.2950344085693</t>
   </si>
   <si>
-    <t xml:space="preserve">21.337085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7407875061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7904148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3194332122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7988262176514</t>
+    <t xml:space="preserve">21.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7407855987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7904109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3194351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7988243103027</t>
   </si>
   <si>
     <t xml:space="preserve">20.4035377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5717449188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7735958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9249782562256</t>
+    <t xml:space="preserve">20.5717430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7735939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9249801635742</t>
   </si>
   <si>
     <t xml:space="preserve">20.8072338104248</t>
@@ -1433,40 +1433,40 @@
     <t xml:space="preserve">20.8919315338135</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6351699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.618049621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7464351654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8662548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3883380889893</t>
+    <t xml:space="preserve">20.6351680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6180534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7464332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8662528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3883399963379</t>
   </si>
   <si>
     <t xml:space="preserve">20.9604015350342</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3626594543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5081615447998</t>
+    <t xml:space="preserve">21.3626651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5081634521484</t>
   </si>
   <si>
     <t xml:space="preserve">21.8847465515137</t>
   </si>
   <si>
-    <t xml:space="preserve">21.756368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2270984649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9203605651855</t>
+    <t xml:space="preserve">21.7563667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2270965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9203567504883</t>
   </si>
   <si>
     <t xml:space="preserve">22.4153900146484</t>
@@ -1475,25 +1475,25 @@
     <t xml:space="preserve">22.4239501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8077201843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0987148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1072731018066</t>
+    <t xml:space="preserve">21.8077182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0987167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1072769165039</t>
   </si>
   <si>
     <t xml:space="preserve">21.7392501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2428417205811</t>
+    <t xml:space="preserve">21.2428398132324</t>
   </si>
   <si>
     <t xml:space="preserve">21.4568099975586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4054565429688</t>
+    <t xml:space="preserve">21.4054584503174</t>
   </si>
   <si>
     <t xml:space="preserve">20.9432849884033</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">20.1302032470703</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1216430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3698482513428</t>
+    <t xml:space="preserve">20.1216411590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3698463439941</t>
   </si>
   <si>
     <t xml:space="preserve">21.2685165405273</t>
@@ -1514,16 +1514,16 @@
     <t xml:space="preserve">21.3968982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3369846343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3797817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.011754989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779613494873</t>
+    <t xml:space="preserve">21.336986541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3797779083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0117568969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779632568359</t>
   </si>
   <si>
     <t xml:space="preserve">21.1743698120117</t>
@@ -1532,34 +1532,34 @@
     <t xml:space="preserve">20.8063430786133</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7977867126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9960136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5423984527588</t>
+    <t xml:space="preserve">20.7977809906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9960117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5424003601074</t>
   </si>
   <si>
     <t xml:space="preserve">21.1914882659912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9090461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.455436706543</t>
+    <t xml:space="preserve">20.9090442657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4554347991943</t>
   </si>
   <si>
     <t xml:space="preserve">19.6509113311768</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8563232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8706893920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9306030273438</t>
+    <t xml:space="preserve">19.8563213348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8706874847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9306011199951</t>
   </si>
   <si>
     <t xml:space="preserve">18.2729511260986</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">18.2558345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9355754852295</t>
+    <t xml:space="preserve">17.9355735778809</t>
   </si>
   <si>
     <t xml:space="preserve">18.6260833740234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.245418548584</t>
+    <t xml:space="preserve">18.2454166412354</t>
   </si>
   <si>
     <t xml:space="preserve">18.1657447814941</t>
@@ -1586,25 +1586,25 @@
     <t xml:space="preserve">18.1568908691406</t>
   </si>
   <si>
-    <t xml:space="preserve">18.811990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2280673980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.997896194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359264373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2988872528076</t>
+    <t xml:space="preserve">18.8119926452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2280654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9978981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359283447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2988891601562</t>
   </si>
   <si>
     <t xml:space="preserve">19.1838035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2103633880615</t>
+    <t xml:space="preserve">19.2103652954102</t>
   </si>
   <si>
     <t xml:space="preserve">19.4139747619629</t>
@@ -1613,19 +1613,19 @@
     <t xml:space="preserve">19.520206451416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5113563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5644721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7238216400146</t>
+    <t xml:space="preserve">19.5113525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5644702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.723819732666</t>
   </si>
   <si>
     <t xml:space="preserve">19.635290145874</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4316806793213</t>
+    <t xml:space="preserve">19.4316787719727</t>
   </si>
   <si>
     <t xml:space="preserve">19.1395416259766</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">19.2369174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6972637176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7503757476807</t>
+    <t xml:space="preserve">19.6972618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7503776550293</t>
   </si>
   <si>
     <t xml:space="preserve">19.8034934997559</t>
@@ -1649,115 +1649,115 @@
     <t xml:space="preserve">19.4405307769775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2900371551514</t>
+    <t xml:space="preserve">19.2900352478027</t>
   </si>
   <si>
     <t xml:space="preserve">19.0333080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5109996795654</t>
+    <t xml:space="preserve">18.5110015869141</t>
   </si>
   <si>
     <t xml:space="preserve">18.3516502380371</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8208446502686</t>
+    <t xml:space="preserve">18.8208427429199</t>
   </si>
   <si>
     <t xml:space="preserve">18.7765789031982</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7942848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9182243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1129817962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4847946166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6707057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5733261108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.201509475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.219217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0952777862549</t>
+    <t xml:space="preserve">18.7942867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9182262420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1129837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4847965240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6707019805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5733242034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2015113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2192115783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0952758789062</t>
   </si>
   <si>
     <t xml:space="preserve">18.696907043457</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1218357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2546272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5906715393066</t>
+    <t xml:space="preserve">19.1218338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2546253204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5906734466553</t>
   </si>
   <si>
     <t xml:space="preserve">18.4136180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6792030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6880550384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1483936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9890441894531</t>
+    <t xml:space="preserve">18.6791973114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6880531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1483917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9890460968018</t>
   </si>
   <si>
     <t xml:space="preserve">19.0510139465332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5995235443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3427982330322</t>
+    <t xml:space="preserve">18.5995254516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3428001403809</t>
   </si>
   <si>
     <t xml:space="preserve">18.4313220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3693580627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7585201263428</t>
+    <t xml:space="preserve">18.3693561553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7585182189941</t>
   </si>
   <si>
     <t xml:space="preserve">17.6965503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4840869903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9001598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4176902770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0325965881348</t>
+    <t xml:space="preserve">17.4840850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9001617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.417688369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0325984954834</t>
   </si>
   <si>
     <t xml:space="preserve">16.6342277526855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4527416229248</t>
+    <t xml:space="preserve">16.4527473449707</t>
   </si>
   <si>
     <t xml:space="preserve">15.9392881393433</t>
@@ -1769,28 +1769,28 @@
     <t xml:space="preserve">15.434684753418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4656715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7316074371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2712631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7666606903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2133674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.173529624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6777772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2262916564941</t>
+    <t xml:space="preserve">15.4656667709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7316055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2712650299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7666625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2133655548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1735305786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6777791976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2262907028198</t>
   </si>
   <si>
     <t xml:space="preserve">14.7840118408203</t>
@@ -1802,64 +1802,64 @@
     <t xml:space="preserve">14.9743452072144</t>
   </si>
   <si>
-    <t xml:space="preserve">15.071722984314</t>
+    <t xml:space="preserve">15.0717220306396</t>
   </si>
   <si>
     <t xml:space="preserve">15.1912355422974</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7179698944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2933979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171581268311</t>
+    <t xml:space="preserve">15.7179718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2933940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171562194824</t>
   </si>
   <si>
     <t xml:space="preserve">15.8596172332764</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0986366271973</t>
+    <t xml:space="preserve">16.0986347198486</t>
   </si>
   <si>
     <t xml:space="preserve">16.103063583374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7755146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4169797897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7887926101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4833765029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6910581588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2882604598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2041597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.97398853302</t>
+    <t xml:space="preserve">15.7755126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4169816970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7887945175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4833755493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6910562515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2882595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2041606903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943138122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9739904403687</t>
   </si>
   <si>
     <t xml:space="preserve">13.8766098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0802221298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9916963577271</t>
+    <t xml:space="preserve">14.0802211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9916944503784</t>
   </si>
   <si>
     <t xml:space="preserve">13.7880821228027</t>
@@ -1868,136 +1868,136 @@
     <t xml:space="preserve">13.6243076324463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1554708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3148193359375</t>
+    <t xml:space="preserve">14.1554689407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3148183822632</t>
   </si>
   <si>
     <t xml:space="preserve">15.0451669692993</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4254770278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1112051010132</t>
+    <t xml:space="preserve">14.4254779815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1112060546875</t>
   </si>
   <si>
     <t xml:space="preserve">13.4959440231323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.367579460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2524948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0669441223145</t>
+    <t xml:space="preserve">13.3675804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2524938583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0669431686401</t>
   </si>
   <si>
     <t xml:space="preserve">14.7707328796387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.841552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6954851150513</t>
+    <t xml:space="preserve">14.8415536880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.695484161377</t>
   </si>
   <si>
     <t xml:space="preserve">14.651219367981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8946704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0628728866577</t>
+    <t xml:space="preserve">14.8946714401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0628709793091</t>
   </si>
   <si>
     <t xml:space="preserve">14.8813905715942</t>
   </si>
   <si>
-    <t xml:space="preserve">14.828275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9345064163208</t>
+    <t xml:space="preserve">14.8282737731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9345083236694</t>
   </si>
   <si>
     <t xml:space="preserve">15.4479646682739</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7131910324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2886152267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6958379745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3155288696289</t>
+    <t xml:space="preserve">14.7131900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2886161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6958408355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3155307769775</t>
   </si>
   <si>
     <t xml:space="preserve">16.4129104614258</t>
   </si>
   <si>
-    <t xml:space="preserve">16.116340637207</t>
+    <t xml:space="preserve">16.1163425445557</t>
   </si>
   <si>
     <t xml:space="preserve">16.0145359039307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8020734786987</t>
+    <t xml:space="preserve">15.8020706176758</t>
   </si>
   <si>
     <t xml:space="preserve">16.1340484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2358570098877</t>
+    <t xml:space="preserve">16.2358531951904</t>
   </si>
   <si>
     <t xml:space="preserve">16.479305267334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4748783111572</t>
+    <t xml:space="preserve">16.4748802185059</t>
   </si>
   <si>
     <t xml:space="preserve">16.3376617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">16.218147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2889728546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5811100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5412731170654</t>
+    <t xml:space="preserve">16.2181491851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2889709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5811080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5412712097168</t>
   </si>
   <si>
     <t xml:space="preserve">16.7758712768555</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4881572723389</t>
+    <t xml:space="preserve">16.4881553649902</t>
   </si>
   <si>
     <t xml:space="preserve">16.7935733795166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6298027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9263648986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9481420516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9304351806641</t>
+    <t xml:space="preserve">16.6297988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9263668060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9481401443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9304361343384</t>
   </si>
   <si>
     <t xml:space="preserve">15.9614219665527</t>
@@ -2006,97 +2006,97 @@
     <t xml:space="preserve">16.5279960632324</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5368480682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.67848777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5855388641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7139015197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1292667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5763273239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8197765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0101089477539</t>
+    <t xml:space="preserve">16.5368461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6784896850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5855369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7138996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1292657852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5763263702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8197784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0101127624512</t>
   </si>
   <si>
     <t xml:space="preserve">15.8906011581421</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8463354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3992729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2930402755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9610662460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876260757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8858194351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3767862319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4874458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6069574356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5626945495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7795839309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4125547409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2222194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0540180206299</t>
+    <t xml:space="preserve">15.8463335037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3992757797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.293041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9610681533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.885817527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3767881393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4874467849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6069583892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5626955032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7795848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4125537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2222204208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0540189743042</t>
   </si>
   <si>
     <t xml:space="preserve">14.9212284088135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6423683166504</t>
+    <t xml:space="preserve">14.6423692703247</t>
   </si>
   <si>
     <t xml:space="preserve">14.9300813674927</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8592586517334</t>
+    <t xml:space="preserve">14.859260559082</t>
   </si>
   <si>
     <t xml:space="preserve">15.1868095397949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0230331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9477844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476070404053</t>
+    <t xml:space="preserve">15.0230340957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9477872848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476089477539</t>
   </si>
   <si>
     <t xml:space="preserve">13.2436408996582</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">13.5534858703613</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6552925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6420135498047</t>
+    <t xml:space="preserve">13.6552934646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.642014503479</t>
   </si>
   <si>
     <t xml:space="preserve">14.1997337341309</t>
@@ -2117,91 +2117,91 @@
     <t xml:space="preserve">14.4564619064331</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4431829452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6822071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8459806442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2177925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0495910644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2089424133301</t>
+    <t xml:space="preserve">14.4431819915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6822061538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8459815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.217794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0495929718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2089414596558</t>
   </si>
   <si>
     <t xml:space="preserve">15.0318880081177</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1823835372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4962978363037</t>
+    <t xml:space="preserve">15.1823816299438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.496298789978</t>
   </si>
   <si>
     <t xml:space="preserve">14.1820287704468</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2000875473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1381206512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3151731491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3063230514526</t>
+    <t xml:space="preserve">15.2000885009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1381216049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3151741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3063220977783</t>
   </si>
   <si>
     <t xml:space="preserve">14.6467943191528</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3723602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8589029312134</t>
+    <t xml:space="preserve">14.3723611831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589038848877</t>
   </si>
   <si>
     <t xml:space="preserve">13.7748031616211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5977487564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7792291641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5888977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6774244308472</t>
+    <t xml:space="preserve">13.597749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7792301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5888967514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6774225234985</t>
   </si>
   <si>
     <t xml:space="preserve">13.2170839309692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5313549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.350227355957</t>
+    <t xml:space="preserve">13.5313529968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3502292633057</t>
   </si>
   <si>
     <t xml:space="preserve">14.3192443847656</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2705535888672</t>
+    <t xml:space="preserve">14.2705554962158</t>
   </si>
   <si>
     <t xml:space="preserve">14.6999092102051</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7353229522705</t>
+    <t xml:space="preserve">14.7353219985962</t>
   </si>
   <si>
     <t xml:space="preserve">14.9256553649902</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">14.7486009597778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9079504013062</t>
+    <t xml:space="preserve">14.9079494476318</t>
   </si>
   <si>
     <t xml:space="preserve">15.2266473770142</t>
@@ -2222,55 +2222,55 @@
     <t xml:space="preserve">15.5807542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9127311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0942115783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8584651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9808721542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675308227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2302169799805</t>
+    <t xml:space="preserve">15.91273021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0942134857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8584632873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9808712005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675327301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2302188873291</t>
   </si>
   <si>
     <t xml:space="preserve">16.4568977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5838375091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5929050445557</t>
+    <t xml:space="preserve">16.5838413238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.592903137207</t>
   </si>
   <si>
     <t xml:space="preserve">16.66090965271</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7243785858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4115619659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6427726745605</t>
+    <t xml:space="preserve">16.7243804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7425136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4115600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6427764892578</t>
   </si>
   <si>
     <t xml:space="preserve">16.9827919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.941987991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0326652526855</t>
+    <t xml:space="preserve">16.9419918060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0326614379883</t>
   </si>
   <si>
     <t xml:space="preserve">17.309211730957</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">17.4542865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9646587371826</t>
+    <t xml:space="preserve">16.9646606445312</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555931091309</t>
@@ -2288,61 +2288,61 @@
     <t xml:space="preserve">17.0462627410889</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0436515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0935192108154</t>
+    <t xml:space="preserve">18.0436496734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0935211181641</t>
   </si>
   <si>
     <t xml:space="preserve">18.1116561889648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.72629737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1414680480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7833156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9283924102783</t>
+    <t xml:space="preserve">17.7263011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1414699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7833137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9283885955811</t>
   </si>
   <si>
     <t xml:space="preserve">17.5268249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1505355834961</t>
+    <t xml:space="preserve">17.1505393981934</t>
   </si>
   <si>
     <t xml:space="preserve">16.996395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8875885009766</t>
+    <t xml:space="preserve">16.8875865936279</t>
   </si>
   <si>
     <t xml:space="preserve">16.9601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3726806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7787818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7923831939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7017097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.030740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0715427398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.647310256958</t>
+    <t xml:space="preserve">17.3726787567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7787837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7923812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7017135620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0307426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0715446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6473083496094</t>
   </si>
   <si>
     <t xml:space="preserve">16.8150501251221</t>
@@ -2351,28 +2351,28 @@
     <t xml:space="preserve">17.5948276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3862838745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0054626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9782581329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2774772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2276058197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0209808349609</t>
+    <t xml:space="preserve">17.3862800598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0054588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9782600402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2774753570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2276077270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0209827423096</t>
   </si>
   <si>
     <t xml:space="preserve">18.0481853485107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0073833465576</t>
+    <t xml:space="preserve">18.0073852539062</t>
   </si>
   <si>
     <t xml:space="preserve">18.2068614959717</t>
@@ -2381,10 +2381,10 @@
     <t xml:space="preserve">18.7508888244629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2975330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3519344329834</t>
+    <t xml:space="preserve">18.2975311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3519325256348</t>
   </si>
   <si>
     <t xml:space="preserve">18.2884654998779</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">18.9775695800781</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0501079559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0410385131836</t>
+    <t xml:space="preserve">19.050106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0410404205322</t>
   </si>
   <si>
     <t xml:space="preserve">18.3156661987305</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">17.7716369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0617828369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.880443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0889873504639</t>
+    <t xml:space="preserve">18.0617847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8804416656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0889892578125</t>
   </si>
   <si>
     <t xml:space="preserve">17.9756469726562</t>
@@ -2426,25 +2426,25 @@
     <t xml:space="preserve">17.7217674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8623104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7126979827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0598659515381</t>
+    <t xml:space="preserve">17.8623065948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7126998901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0598640441895</t>
   </si>
   <si>
     <t xml:space="preserve">17.0507984161377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9737243652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0961322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8921184539795</t>
+    <t xml:space="preserve">16.973726272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.096134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8921203613281</t>
   </si>
   <si>
     <t xml:space="preserve">17.2366733551025</t>
@@ -2453,46 +2453,46 @@
     <t xml:space="preserve">17.7671012878418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0753860473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4698085784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5060768127441</t>
+    <t xml:space="preserve">18.0753841400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4698066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5060787200928</t>
   </si>
   <si>
     <t xml:space="preserve">18.7236881256104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7146224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2703285217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1887264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5786113739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9594326019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.769021987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7418231964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7780876159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2223834991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7120113372803</t>
+    <t xml:space="preserve">18.71462059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2703304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1887245178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5786151885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.959436416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7690238952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7418251037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7780914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2223815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.712007522583</t>
   </si>
   <si>
     <t xml:space="preserve">19.521598815918</t>
@@ -2501,58 +2501,58 @@
     <t xml:space="preserve">19.8117485046387</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490604400635</t>
+    <t xml:space="preserve">19.4490623474121</t>
   </si>
   <si>
     <t xml:space="preserve">19.3130531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7962245941162</t>
+    <t xml:space="preserve">18.7962265014648</t>
   </si>
   <si>
     <t xml:space="preserve">18.4970092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1732063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4225521087646</t>
+    <t xml:space="preserve">17.1732044219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.422550201416</t>
   </si>
   <si>
     <t xml:space="preserve">17.8033714294434</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9121780395508</t>
+    <t xml:space="preserve">17.9121761322021</t>
   </si>
   <si>
     <t xml:space="preserve">18.0391178131104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9892482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0663146972656</t>
+    <t xml:space="preserve">17.9892501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0663185119629</t>
   </si>
   <si>
     <t xml:space="preserve">18.8596954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9050331115723</t>
+    <t xml:space="preserve">18.9050312042236</t>
   </si>
   <si>
     <t xml:space="preserve">18.7599582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3791389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4399948120117</t>
+    <t xml:space="preserve">18.3791370391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4399929046631</t>
   </si>
   <si>
     <t xml:space="preserve">18.9685020446777</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0863761901855</t>
+    <t xml:space="preserve">19.0863742828369</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951808929443</t>
@@ -2561,25 +2561,25 @@
     <t xml:space="preserve">19.5760021209717</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6394729614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4218616485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7392120361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.94775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0021572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8661479949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4853267669678</t>
+    <t xml:space="preserve">19.6394691467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4218578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7392101287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9477558135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0021553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8661499023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.485330581665</t>
   </si>
   <si>
     <t xml:space="preserve">19.6757411956787</t>
@@ -2588,16 +2588,16 @@
     <t xml:space="preserve">19.2133159637451</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1679782867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3221187591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0319709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2949180603027</t>
+    <t xml:space="preserve">19.1679801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3221206665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0319728851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2949199676514</t>
   </si>
   <si>
     <t xml:space="preserve">19.2677192687988</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">19.5941371917725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8570823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4127922058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9957027435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6602172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5332775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9322338104248</t>
+    <t xml:space="preserve">19.857084274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4127902984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9957046508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6602191925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.533275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9322319030762</t>
   </si>
   <si>
     <t xml:space="preserve">19.4762630462646</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">20.0474967956543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0112266540527</t>
+    <t xml:space="preserve">20.0112247467041</t>
   </si>
   <si>
     <t xml:space="preserve">19.9658908843994</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">20.3376445770264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9088726043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.325963973999</t>
+    <t xml:space="preserve">20.9088745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3259620666504</t>
   </si>
   <si>
     <t xml:space="preserve">21.5526428222656</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">22.0332012176514</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6977157592773</t>
+    <t xml:space="preserve">21.697717666626</t>
   </si>
   <si>
     <t xml:space="preserve">22.4049549102783</t>
@@ -2669,13 +2669,13 @@
     <t xml:space="preserve">20.1925678253174</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3039894104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3855934143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4607391357422</t>
+    <t xml:space="preserve">19.3039875030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.385591506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4607410430908</t>
   </si>
   <si>
     <t xml:space="preserve">18.6511497497559</t>
@@ -2684,34 +2684,34 @@
     <t xml:space="preserve">18.623950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">18.03005027771</t>
+    <t xml:space="preserve">18.0300521850586</t>
   </si>
   <si>
     <t xml:space="preserve">16.8195838928223</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4685764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842679977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8112058639526</t>
+    <t xml:space="preserve">15.4685754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6842670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8112077713013</t>
   </si>
   <si>
     <t xml:space="preserve">12.653223991394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7412824630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.777551651001</t>
+    <t xml:space="preserve">13.741283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7775506973267</t>
   </si>
   <si>
     <t xml:space="preserve">14.3170480728149</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7341375350952</t>
+    <t xml:space="preserve">14.7341384887695</t>
   </si>
   <si>
     <t xml:space="preserve">15.1648283004761</t>
@@ -2726,91 +2726,91 @@
     <t xml:space="preserve">15.269100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0242862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0061492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2354431152344</t>
+    <t xml:space="preserve">15.0242881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0061521530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2354440689087</t>
   </si>
   <si>
     <t xml:space="preserve">13.8863573074341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2380561828613</t>
+    <t xml:space="preserve">13.238055229187</t>
   </si>
   <si>
     <t xml:space="preserve">13.4783344268799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5327386856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9660396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4511346817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.809287071228</t>
+    <t xml:space="preserve">13.5327377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9660406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4511337280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8092851638794</t>
   </si>
   <si>
     <t xml:space="preserve">14.1901073455811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.258111000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3695306777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8727569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9634284973145</t>
+    <t xml:space="preserve">14.2581119537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3695287704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8727579116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9634275436401</t>
   </si>
   <si>
     <t xml:space="preserve">13.7820854187012</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2943811416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4485216140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5346603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1512260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3643035888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6544551849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5683174133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6291751861572</t>
+    <t xml:space="preserve">14.2943801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.448522567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5346593856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1512241363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3643045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6544542312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5683145523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3461694717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6291732788086</t>
   </si>
   <si>
     <t xml:space="preserve">15.7768611907959</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7904624938965</t>
+    <t xml:space="preserve">15.7904634475708</t>
   </si>
   <si>
     <t xml:space="preserve">16.4478302001953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3752918243408</t>
+    <t xml:space="preserve">16.3752937316895</t>
   </si>
   <si>
     <t xml:space="preserve">17.109733581543</t>
@@ -2819,37 +2819,37 @@
     <t xml:space="preserve">16.0398082733154</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2446327209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4030933380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8813457489014</t>
+    <t xml:space="preserve">17.2446346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4030952453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8813438415527</t>
   </si>
   <si>
     <t xml:space="preserve">16.7066020965576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2906169891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.699893951416</t>
+    <t xml:space="preserve">17.2906188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6998901367188</t>
   </si>
   <si>
     <t xml:space="preserve">17.9896011352539</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4515705108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.658504486084</t>
+    <t xml:space="preserve">17.4515686035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6585063934326</t>
   </si>
   <si>
     <t xml:space="preserve">17.6079196929932</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3549995422363</t>
+    <t xml:space="preserve">17.3549976348877</t>
   </si>
   <si>
     <t xml:space="preserve">17.6309127807617</t>
@@ -2861,19 +2861,19 @@
     <t xml:space="preserve">17.8884353637695</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6334018707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7529640197754</t>
+    <t xml:space="preserve">18.6333999633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.752965927124</t>
   </si>
   <si>
     <t xml:space="preserve">18.8081474304199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.67018699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7090873718262</t>
+    <t xml:space="preserve">18.6701889038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7090892791748</t>
   </si>
   <si>
     <t xml:space="preserve">17.6631031036377</t>
@@ -2882,10 +2882,10 @@
     <t xml:space="preserve">17.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3482894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885093688965</t>
+    <t xml:space="preserve">18.3482913970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885074615479</t>
   </si>
   <si>
     <t xml:space="preserve">18.5874137878418</t>
@@ -2894,31 +2894,31 @@
     <t xml:space="preserve">18.9093151092529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8173446655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.222017288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7161731719971</t>
+    <t xml:space="preserve">18.8173427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2220191955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7161769866943</t>
   </si>
   <si>
     <t xml:space="preserve">18.9644985198975</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7897529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0104846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0748615264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5715084075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3507785797119</t>
+    <t xml:space="preserve">18.7897510528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0104827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0748634338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5715103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3507766723633</t>
   </si>
   <si>
     <t xml:space="preserve">19.9761829376221</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">19.9577903747559</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6542835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278594970703</t>
+    <t xml:space="preserve">19.6542854309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278614044189</t>
   </si>
   <si>
     <t xml:space="preserve">19.930196762085</t>
@@ -2945,22 +2945,22 @@
     <t xml:space="preserve">20.2704925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3256759643555</t>
+    <t xml:space="preserve">20.3256740570068</t>
   </si>
   <si>
     <t xml:space="preserve">21.1534156799316</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9602756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.328161239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0154590606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0430488586426</t>
+    <t xml:space="preserve">20.960277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3281631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0154609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0430526733398</t>
   </si>
   <si>
     <t xml:space="preserve">20.4912242889404</t>
@@ -2969,52 +2969,52 @@
     <t xml:space="preserve">20.2245063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2337017059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8934097290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8223190307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4176483154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.380859375</t>
+    <t xml:space="preserve">20.2337036132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8934059143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8223209381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4176464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3808574676514</t>
   </si>
   <si>
     <t xml:space="preserve">20.206111907959</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5556030273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8775043487549</t>
+    <t xml:space="preserve">20.5556049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8775024414062</t>
   </si>
   <si>
     <t xml:space="preserve">21.0614452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7303504943848</t>
+    <t xml:space="preserve">20.7303485870361</t>
   </si>
   <si>
     <t xml:space="preserve">20.7579402923584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7395458221436</t>
+    <t xml:space="preserve">20.7395439147949</t>
   </si>
   <si>
     <t xml:space="preserve">20.6291809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2453880310059</t>
+    <t xml:space="preserve">21.2453899383545</t>
   </si>
   <si>
     <t xml:space="preserve">21.3649501800537</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4201354980469</t>
+    <t xml:space="preserve">21.4201335906982</t>
   </si>
   <si>
     <t xml:space="preserve">21.4937114715576</t>
@@ -3023,19 +3023,19 @@
     <t xml:space="preserve">21.944372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5580921173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5213031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0271453857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6040782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8156108856201</t>
+    <t xml:space="preserve">21.5580902099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5213012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0271472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.604076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8156089782715</t>
   </si>
   <si>
     <t xml:space="preserve">21.4109382629395</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">21.7420330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1191139221191</t>
+    <t xml:space="preserve">22.1191158294678</t>
   </si>
   <si>
     <t xml:space="preserve">22.5145931243896</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6341571807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5421867370605</t>
+    <t xml:space="preserve">22.6341552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5421848297119</t>
   </si>
   <si>
     <t xml:space="preserve">22.6433544158936</t>
@@ -3062,25 +3062,25 @@
     <t xml:space="preserve">22.3674392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4410152435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2294807434082</t>
+    <t xml:space="preserve">22.4410171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2294845581055</t>
   </si>
   <si>
     <t xml:space="preserve">22.6709442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">22.487003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9008731842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8732833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8456916809082</t>
+    <t xml:space="preserve">22.4870014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9008712768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8732795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8456935882568</t>
   </si>
   <si>
     <t xml:space="preserve">23.2135753631592</t>
@@ -3092,34 +3092,34 @@
     <t xml:space="preserve">23.6550369262695</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5262775421143</t>
+    <t xml:space="preserve">23.5262794494629</t>
   </si>
   <si>
     <t xml:space="preserve">23.5722637176514</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0045280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7194213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3356227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3264293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.875768661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1700763702393</t>
+    <t xml:space="preserve">24.0045299530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7194194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3356246948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3264312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8757705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1700782775879</t>
   </si>
   <si>
     <t xml:space="preserve">23.5998554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6525497436523</t>
+    <t xml:space="preserve">22.6525478363037</t>
   </si>
   <si>
     <t xml:space="preserve">22.7261257171631</t>
@@ -3128,10 +3128,10 @@
     <t xml:space="preserve">22.9560565948486</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1926956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.66845703125</t>
+    <t xml:space="preserve">22.1926937103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6684551239014</t>
   </si>
   <si>
     <t xml:space="preserve">21.1994018554688</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">21.466121673584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0823268890381</t>
+    <t xml:space="preserve">22.0823287963867</t>
   </si>
   <si>
     <t xml:space="preserve">22.5881690979004</t>
@@ -3164,25 +3164,25 @@
     <t xml:space="preserve">24.2988376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9677410125732</t>
+    <t xml:space="preserve">23.9677391052246</t>
   </si>
   <si>
     <t xml:space="preserve">23.3607292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8665714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9217567443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9033603668213</t>
+    <t xml:space="preserve">23.8665733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9217548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9033622741699</t>
   </si>
   <si>
     <t xml:space="preserve">24.4459934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0965042114258</t>
+    <t xml:space="preserve">24.0965003967285</t>
   </si>
   <si>
     <t xml:space="preserve">24.7402992248535</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">25.2277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8966541290283</t>
+    <t xml:space="preserve">24.8966503143311</t>
   </si>
   <si>
     <t xml:space="preserve">24.4092044830322</t>
@@ -3200,19 +3200,19 @@
     <t xml:space="preserve">24.5471611022949</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0622005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5655555725098</t>
+    <t xml:space="preserve">25.0622024536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5655536651611</t>
   </si>
   <si>
     <t xml:space="preserve">24.6391334533691</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6023445129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8874530792236</t>
+    <t xml:space="preserve">24.6023426055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8874549865723</t>
   </si>
   <si>
     <t xml:space="preserve">25.3105239868164</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">25.7151966094971</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9359264373779</t>
+    <t xml:space="preserve">25.9359283447266</t>
   </si>
   <si>
     <t xml:space="preserve">26.6257133483887</t>
@@ -3251,43 +3251,43 @@
     <t xml:space="preserve">26.8740348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0119934082031</t>
+    <t xml:space="preserve">27.0119972229004</t>
   </si>
   <si>
     <t xml:space="preserve">27.5546245574951</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2812004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9225101470947</t>
+    <t xml:space="preserve">28.2811985015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9225120544434</t>
   </si>
   <si>
     <t xml:space="preserve">28.0880584716797</t>
   </si>
   <si>
-    <t xml:space="preserve">26.395788192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5521373748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8715496063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1106719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.843957901001</t>
+    <t xml:space="preserve">26.3957862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5521354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8715476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1106739044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8439559936523</t>
   </si>
   <si>
     <t xml:space="preserve">26.0278987884521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7519836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6876068115234</t>
+    <t xml:space="preserve">25.7519874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6876049041748</t>
   </si>
   <si>
     <t xml:space="preserve">24.7127094268799</t>
@@ -3296,19 +3296,19 @@
     <t xml:space="preserve">24.2804431915283</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1449737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5011749267578</t>
+    <t xml:space="preserve">25.1449756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5011730194092</t>
   </si>
   <si>
     <t xml:space="preserve">25.0346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2369480133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6968040466309</t>
+    <t xml:space="preserve">25.236946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6968021392822</t>
   </si>
   <si>
     <t xml:space="preserve">26.0462951660156</t>
@@ -3320,31 +3320,31 @@
     <t xml:space="preserve">26.2854194641113</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9267311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9083385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1198711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0003089904785</t>
+    <t xml:space="preserve">25.9267330169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9083366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.119873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0003108978271</t>
   </si>
   <si>
     <t xml:space="preserve">25.9635200500488</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6600151062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0530014038086</t>
+    <t xml:space="preserve">25.6600112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0530033111572</t>
   </si>
   <si>
     <t xml:space="preserve">24.593147277832</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3908081054688</t>
+    <t xml:space="preserve">24.3908100128174</t>
   </si>
   <si>
     <t xml:space="preserve">24.1608810424805</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">24.5563583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5195693969727</t>
+    <t xml:space="preserve">24.5195713043213</t>
   </si>
   <si>
     <t xml:space="preserve">25.0162162780762</t>
@@ -3368,22 +3368,22 @@
     <t xml:space="preserve">24.0137271881104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2712459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2001609802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2620506286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6734313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5446739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6918277740479</t>
+    <t xml:space="preserve">24.2712478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2001552581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2620468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.673433303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5446720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6918258666992</t>
   </si>
   <si>
     <t xml:space="preserve">23.4251098632812</t>
@@ -3392,22 +3392,22 @@
     <t xml:space="preserve">23.3055477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5170822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7837982177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1056995391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.151683807373</t>
+    <t xml:space="preserve">23.5170783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7838001251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1056976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1516857147217</t>
   </si>
   <si>
     <t xml:space="preserve">24.5287666320801</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8138790130615</t>
+    <t xml:space="preserve">24.8138771057129</t>
   </si>
   <si>
     <t xml:space="preserve">24.8322734832764</t>
@@ -3419,22 +3419,22 @@
     <t xml:space="preserve">25.4852695465088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7703800201416</t>
+    <t xml:space="preserve">25.770378112793</t>
   </si>
   <si>
     <t xml:space="preserve">25.6416187286377</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8414707183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.694314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1081848144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9518356323242</t>
+    <t xml:space="preserve">24.8414688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6943168640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1081867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9518337249756</t>
   </si>
   <si>
     <t xml:space="preserve">25.3381156921387</t>
@@ -3446,52 +3446,52 @@
     <t xml:space="preserve">24.5379638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4367961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9861335754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9585437774658</t>
+    <t xml:space="preserve">24.4367942810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9861354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9585418701172</t>
   </si>
   <si>
     <t xml:space="preserve">24.4000072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9493465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.795482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2252616882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3197231292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4693622589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4325752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2762203216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.332389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5476913452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1826114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1919746398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5196056365967</t>
+    <t xml:space="preserve">23.949348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7954845428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2252597808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3197193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4693641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4325733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2762222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3323879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5476894378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1826133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1919727325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5196075439453</t>
   </si>
   <si>
     <t xml:space="preserve">26.4259967803955</t>
@@ -3506,61 +3506,61 @@
     <t xml:space="preserve">27.3901767730713</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5867557525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7927017211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7084522247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8769493103027</t>
+    <t xml:space="preserve">27.5867595672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7926998138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7084503173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8769474029541</t>
   </si>
   <si>
     <t xml:space="preserve">27.3340110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2872066497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3808155059814</t>
+    <t xml:space="preserve">27.2872047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3808174133301</t>
   </si>
   <si>
     <t xml:space="preserve">27.699089050293</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1935977935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1655139923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9237537384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8395042419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8020610809326</t>
+    <t xml:space="preserve">27.1935958862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1655158996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9237518310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8395023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.802059173584</t>
   </si>
   <si>
     <t xml:space="preserve">28.4011611938477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5602989196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3075523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6819896697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2981872558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3169116973877</t>
+    <t xml:space="preserve">28.5602970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3075504302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6819915771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2981910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3169136047363</t>
   </si>
   <si>
     <t xml:space="preserve">28.5041332244873</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">28.4479656219482</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7568778991699</t>
+    <t xml:space="preserve">28.7568759918213</t>
   </si>
   <si>
     <t xml:space="preserve">27.9799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5696601867676</t>
+    <t xml:space="preserve">28.5696582794189</t>
   </si>
   <si>
     <t xml:space="preserve">28.8317642211914</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">28.6913509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4198837280273</t>
+    <t xml:space="preserve">28.419885635376</t>
   </si>
   <si>
     <t xml:space="preserve">28.4760494232178</t>
@@ -3599,25 +3599,25 @@
     <t xml:space="preserve">27.6710052490234</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1203308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8301429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9892807006836</t>
+    <t xml:space="preserve">28.1203327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8301410675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.989278793335</t>
   </si>
   <si>
     <t xml:space="preserve">28.1671371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2701072692871</t>
+    <t xml:space="preserve">28.2701110839844</t>
   </si>
   <si>
     <t xml:space="preserve">28.1390533447266</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2888278961182</t>
+    <t xml:space="preserve">28.2888298034668</t>
   </si>
   <si>
     <t xml:space="preserve">28.4854106903076</t>
@@ -3629,28 +3629,28 @@
     <t xml:space="preserve">28.7849617004395</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8785724639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0002613067627</t>
+    <t xml:space="preserve">28.8785705566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0002632141113</t>
   </si>
   <si>
     <t xml:space="preserve">29.3934230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2359104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3201580047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.179744720459</t>
+    <t xml:space="preserve">30.2359085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3201599121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1797466278076</t>
   </si>
   <si>
     <t xml:space="preserve">29.8146667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9925270080566</t>
+    <t xml:space="preserve">29.992525100708</t>
   </si>
   <si>
     <t xml:space="preserve">29.9550800323486</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">29.8989162445068</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5619201660156</t>
+    <t xml:space="preserve">29.5619220733643</t>
   </si>
   <si>
     <t xml:space="preserve">29.5057563781738</t>
@@ -3668,37 +3668,37 @@
     <t xml:space="preserve">29.7585010528564</t>
   </si>
   <si>
-    <t xml:space="preserve">29.805305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5806427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8708305358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9082775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8333892822266</t>
+    <t xml:space="preserve">29.8053035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5806446075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8708343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.908275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8333911895752</t>
   </si>
   <si>
     <t xml:space="preserve">30.2171878814697</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4044055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3856830596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8630962371826</t>
+    <t xml:space="preserve">30.4044075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.385684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.863094329834</t>
   </si>
   <si>
     <t xml:space="preserve">30.8537330627441</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0018844604492</t>
+    <t xml:space="preserve">30.0018863677979</t>
   </si>
   <si>
     <t xml:space="preserve">30.5448246002197</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">30.4699325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7133197784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1142158508301</t>
+    <t xml:space="preserve">30.713321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1142139434814</t>
   </si>
   <si>
     <t xml:space="preserve">30.1891059875488</t>
@@ -3722,43 +3722,43 @@
     <t xml:space="preserve">29.6461696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3185348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0299701690674</t>
+    <t xml:space="preserve">29.3185367584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.029972076416</t>
   </si>
   <si>
     <t xml:space="preserve">30.3482398986816</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6742515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9534587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.813045501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2420234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5212287902832</t>
+    <t xml:space="preserve">29.6742534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9534606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8130435943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2420253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5212306976318</t>
   </si>
   <si>
     <t xml:space="preserve">27.4837875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0267238616943</t>
+    <t xml:space="preserve">28.0267219543457</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6616458892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6445484161377</t>
+    <t xml:space="preserve">27.661642074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6445465087891</t>
   </si>
   <si>
     <t xml:space="preserve">29.2249240875244</t>
@@ -3767,22 +3767,22 @@
     <t xml:space="preserve">29.2717304229736</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2623710632324</t>
+    <t xml:space="preserve">29.2623691558838</t>
   </si>
   <si>
     <t xml:space="preserve">29.5244789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7304191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1610240936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4792995452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5916290283203</t>
+    <t xml:space="preserve">29.7304172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1610221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4792957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.591625213623</t>
   </si>
   <si>
     <t xml:space="preserve">30.36696434021</t>
@@ -3794,37 +3794,37 @@
     <t xml:space="preserve">30.6103496551514</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7694816589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3030586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9286212921143</t>
+    <t xml:space="preserve">30.7694854736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3030567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9286231994629</t>
   </si>
   <si>
     <t xml:space="preserve">31.1626472473145</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6681365966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.855354309082</t>
+    <t xml:space="preserve">31.6681385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8553581237793</t>
   </si>
   <si>
     <t xml:space="preserve">31.4341163635254</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1813678741455</t>
+    <t xml:space="preserve">31.1813659667969</t>
   </si>
   <si>
     <t xml:space="preserve">31.2749767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8179130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9302444458008</t>
+    <t xml:space="preserve">31.8179168701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9302406311035</t>
   </si>
   <si>
     <t xml:space="preserve">32.8101768493652</t>
@@ -3836,40 +3836,40 @@
     <t xml:space="preserve">32.6416778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6962223052979</t>
+    <t xml:space="preserve">31.9489688873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6962184906006</t>
   </si>
   <si>
     <t xml:space="preserve">32.1081008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6945972442627</t>
+    <t xml:space="preserve">30.6945953369141</t>
   </si>
   <si>
     <t xml:space="preserve">31.3124217987061</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7320423126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5822620391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8911762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7523822784424</t>
+    <t xml:space="preserve">30.7320461273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5822658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8911800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7523860931396</t>
   </si>
   <si>
     <t xml:space="preserve">30.9473457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7039566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3576011657715</t>
+    <t xml:space="preserve">30.7039585113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3576030731201</t>
   </si>
   <si>
     <t xml:space="preserve">30.0861339569092</t>
@@ -3878,16 +3878,16 @@
     <t xml:space="preserve">30.1516609191895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5525608062744</t>
+    <t xml:space="preserve">29.5525588989258</t>
   </si>
   <si>
     <t xml:space="preserve">29.702335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7507591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9754257202148</t>
+    <t xml:space="preserve">30.7507610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9754276275635</t>
   </si>
   <si>
     <t xml:space="preserve">30.9379806518555</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">30.9660663604736</t>
   </si>
   <si>
-    <t xml:space="preserve">31.293701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2468967437744</t>
+    <t xml:space="preserve">31.2936992645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2468948364258</t>
   </si>
   <si>
     <t xml:space="preserve">31.2656173706055</t>
@@ -3917,43 +3917,43 @@
     <t xml:space="preserve">31.6026096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7804679870605</t>
+    <t xml:space="preserve">31.7804718017578</t>
   </si>
   <si>
     <t xml:space="preserve">31.3779468536377</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5073776245117</t>
+    <t xml:space="preserve">30.5073757171631</t>
   </si>
   <si>
     <t xml:space="preserve">28.9721794128418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6335620880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0063781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0454444885254</t>
+    <t xml:space="preserve">27.6335639953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0063800811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0454425811768</t>
   </si>
   <si>
     <t xml:space="preserve">26.8378810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2045783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0548057556152</t>
+    <t xml:space="preserve">28.2045803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0548076629639</t>
   </si>
   <si>
     <t xml:space="preserve">27.118709564209</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9298667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0421981811523</t>
+    <t xml:space="preserve">25.9298686981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0421962738037</t>
   </si>
   <si>
     <t xml:space="preserve">26.8191585540771</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">26.5664100646973</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2481422424316</t>
+    <t xml:space="preserve">26.248140335083</t>
   </si>
   <si>
     <t xml:space="preserve">25.7800922393799</t>
@@ -3983,16 +3983,16 @@
     <t xml:space="preserve">26.2294178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1077251434326</t>
+    <t xml:space="preserve">26.1077270507812</t>
   </si>
   <si>
     <t xml:space="preserve">27.5399532318115</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5415744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4463424682617</t>
+    <t xml:space="preserve">28.5415725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4463405609131</t>
   </si>
   <si>
     <t xml:space="preserve">25.9766712188721</t>
@@ -4001,79 +4001,79 @@
     <t xml:space="preserve">27.13743019104</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9502143859863</t>
+    <t xml:space="preserve">26.9502124786377</t>
   </si>
   <si>
     <t xml:space="preserve">28.728796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">27.596118927002</t>
+    <t xml:space="preserve">27.5961170196533</t>
   </si>
   <si>
     <t xml:space="preserve">27.8863105773926</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6258239746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7100734710693</t>
+    <t xml:space="preserve">28.625825881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7100715637207</t>
   </si>
   <si>
     <t xml:space="preserve">29.0377082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1219577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1406745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8598499298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6071014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2326622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8692111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0096225738525</t>
+    <t xml:space="preserve">29.121955871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1406764984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8598480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6071033477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2326641082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8692092895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0096244812012</t>
   </si>
   <si>
     <t xml:space="preserve">29.290454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.981538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5151176452637</t>
+    <t xml:space="preserve">28.9815406799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.515115737915</t>
   </si>
   <si>
     <t xml:space="preserve">29.3840618133545</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0531806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5586738586426</t>
+    <t xml:space="preserve">27.0531826019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5586757659912</t>
   </si>
   <si>
     <t xml:space="preserve">28.8972930908203</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4666862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4831790924072</t>
+    <t xml:space="preserve">28.4666900634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4831771850586</t>
   </si>
   <si>
     <t xml:space="preserve">29.32204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9312076568604</t>
+    <t xml:space="preserve">28.931209564209</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549480438232</t>
@@ -4106,10 +4106,10 @@
     <t xml:space="preserve">28.3211250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7482585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0247020721436</t>
+    <t xml:space="preserve">26.7482604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0247058868408</t>
   </si>
   <si>
     <t xml:space="preserve">27.1104965209961</t>
@@ -4121,16 +4121,16 @@
     <t xml:space="preserve">26.7101306915283</t>
   </si>
   <si>
-    <t xml:space="preserve">26.414623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.96750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2153549194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.768238067627</t>
+    <t xml:space="preserve">26.4146213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9675102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.215353012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7682399749756</t>
   </si>
   <si>
     <t xml:space="preserve">27.5299263000488</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">27.8635654449463</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7301120758057</t>
+    <t xml:space="preserve">27.7301082611084</t>
   </si>
   <si>
     <t xml:space="preserve">28.2829971313477</t>
@@ -4151,16 +4151,16 @@
     <t xml:space="preserve">28.9788703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4459629058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6547660827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9207611083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2258033752441</t>
+    <t xml:space="preserve">29.4459648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.654764175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9207630157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2258014678955</t>
   </si>
   <si>
     <t xml:space="preserve">27.8063697814941</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">27.9684238433838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1304779052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4450511932373</t>
+    <t xml:space="preserve">28.1304759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4450492858887</t>
   </si>
   <si>
     <t xml:space="preserve">26.643404006958</t>
@@ -4184,22 +4184,22 @@
     <t xml:space="preserve">26.3860263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6243362426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7950057983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4813499450684</t>
+    <t xml:space="preserve">26.6243381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7950077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.481351852417</t>
   </si>
   <si>
     <t xml:space="preserve">26.2430381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1667766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.52809715271</t>
+    <t xml:space="preserve">26.1667785644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5280990600586</t>
   </si>
   <si>
     <t xml:space="preserve">25.0133419036865</t>
@@ -4211,10 +4211,10 @@
     <t xml:space="preserve">26.3002319335938</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4050884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9761276245117</t>
+    <t xml:space="preserve">26.4050903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9761257171631</t>
   </si>
   <si>
     <t xml:space="preserve">24.9847431182861</t>
@@ -4226,19 +4226,19 @@
     <t xml:space="preserve">24.765495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">24.393726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.698766708374</t>
+    <t xml:space="preserve">24.3937282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6987686157227</t>
   </si>
   <si>
     <t xml:space="preserve">25.3374462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9189319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1658611297607</t>
+    <t xml:space="preserve">25.9189300537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1658592224121</t>
   </si>
   <si>
     <t xml:space="preserve">25.2993183135986</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">25.2230548858643</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4795188903809</t>
+    <t xml:space="preserve">24.4795207977295</t>
   </si>
   <si>
     <t xml:space="preserve">24.9084815979004</t>
@@ -4262,10 +4262,10 @@
     <t xml:space="preserve">25.9093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4908809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0533008575439</t>
+    <t xml:space="preserve">26.4908847808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0532989501953</t>
   </si>
   <si>
     <t xml:space="preserve">27.0437698364258</t>
@@ -4274,22 +4274,22 @@
     <t xml:space="preserve">26.6815338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2630157470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7882213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5031604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4745597839355</t>
+    <t xml:space="preserve">27.2630176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7882232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5031585693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4745616912842</t>
   </si>
   <si>
     <t xml:space="preserve">29.5508213043213</t>
   </si>
   <si>
-    <t xml:space="preserve">29.646146774292</t>
+    <t xml:space="preserve">29.6461486816406</t>
   </si>
   <si>
     <t xml:space="preserve">30.9044380187988</t>
@@ -4304,13 +4304,13 @@
     <t xml:space="preserve">29.8939933776855</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0760250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7051696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7995834350586</t>
+    <t xml:space="preserve">31.0760269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.705171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7995853424072</t>
   </si>
   <si>
     <t xml:space="preserve">31.0283622741699</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">30.4468803405762</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9997653961182</t>
+    <t xml:space="preserve">30.9997673034668</t>
   </si>
   <si>
     <t xml:space="preserve">30.551736831665</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">30.0274486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2371635437012</t>
+    <t xml:space="preserve">30.2371616363525</t>
   </si>
   <si>
     <t xml:space="preserve">30.5993995666504</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">29.1885871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4554977416992</t>
+    <t xml:space="preserve">29.4554958343506</t>
   </si>
   <si>
     <t xml:space="preserve">30.3610877990723</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">31.0664920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5907821655273</t>
+    <t xml:space="preserve">31.5907802581787</t>
   </si>
   <si>
     <t xml:space="preserve">30.5326709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3515548706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3896827697754</t>
+    <t xml:space="preserve">30.3515529632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.389684677124</t>
   </si>
   <si>
     <t xml:space="preserve">30.3038921356201</t>
@@ -4382,31 +4382,31 @@
     <t xml:space="preserve">29.874927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2362499237061</t>
+    <t xml:space="preserve">29.2362480163574</t>
   </si>
   <si>
     <t xml:space="preserve">28.0160865783691</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6166343688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.673828125</t>
+    <t xml:space="preserve">28.6166362762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6738319396973</t>
   </si>
   <si>
     <t xml:space="preserve">28.3020629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9865741729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2353343963623</t>
+    <t xml:space="preserve">26.986572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2353363037109</t>
   </si>
   <si>
     <t xml:space="preserve">28.492712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0560474395752</t>
+    <t xml:space="preserve">30.0560455322266</t>
   </si>
   <si>
     <t xml:space="preserve">29.5126914978027</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">29.7128753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6842765808105</t>
+    <t xml:space="preserve">29.6842784881592</t>
   </si>
   <si>
     <t xml:space="preserve">29.2648487091064</t>
@@ -4424,25 +4424,25 @@
     <t xml:space="preserve">29.7033424377441</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3983039855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7700710296631</t>
+    <t xml:space="preserve">29.3983020782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7700691223145</t>
   </si>
   <si>
     <t xml:space="preserve">29.7510051727295</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5422077178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.961633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4945430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6661262512207</t>
+    <t xml:space="preserve">30.5422058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9616355895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4945411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6661243438721</t>
   </si>
   <si>
     <t xml:space="preserve">30.8472461700439</t>
@@ -4451,16 +4451,16 @@
     <t xml:space="preserve">31.1236896514893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9434814453125</t>
+    <t xml:space="preserve">31.9434833526611</t>
   </si>
   <si>
     <t xml:space="preserve">31.981616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7242336273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5717182159424</t>
+    <t xml:space="preserve">31.7242374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5717163085938</t>
   </si>
   <si>
     <t xml:space="preserve">31.4477977752686</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">30.5231399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9521045684814</t>
+    <t xml:space="preserve">30.9521026611328</t>
   </si>
   <si>
     <t xml:space="preserve">30.5136051177979</t>
@@ -4487,13 +4487,13 @@
     <t xml:space="preserve">32.5535697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6289119720459</t>
+    <t xml:space="preserve">31.6289100646973</t>
   </si>
   <si>
     <t xml:space="preserve">30.8853759765625</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3715343475342</t>
+    <t xml:space="preserve">31.3715324401855</t>
   </si>
   <si>
     <t xml:space="preserve">30.7709846496582</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">31.0950889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">31.037899017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4763946533203</t>
+    <t xml:space="preserve">31.0378971099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.476390838623</t>
   </si>
   <si>
     <t xml:space="preserve">32.1913299560547</t>
@@ -4514,10 +4514,10 @@
     <t xml:space="preserve">32.0769424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">32.105541229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1246032714844</t>
+    <t xml:space="preserve">32.1055374145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1246070861816</t>
   </si>
   <si>
     <t xml:space="preserve">32.143669128418</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">31.8386287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9244213104248</t>
+    <t xml:space="preserve">31.9244251251221</t>
   </si>
   <si>
     <t xml:space="preserve">32.1341361999512</t>
@@ -4538,10 +4538,10 @@
     <t xml:space="preserve">32.8300094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1064529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8404579162598</t>
+    <t xml:space="preserve">33.1064491271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.840461730957</t>
   </si>
   <si>
     <t xml:space="preserve">33.5926170349121</t>
@@ -4556,22 +4556,22 @@
     <t xml:space="preserve">33.1445846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">33.354305267334</t>
+    <t xml:space="preserve">33.3543014526367</t>
   </si>
   <si>
     <t xml:space="preserve">33.6116752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.468692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6021423339844</t>
+    <t xml:space="preserve">33.4686889648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6021461486816</t>
   </si>
   <si>
     <t xml:space="preserve">33.3161697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5544815063477</t>
+    <t xml:space="preserve">33.5544853210449</t>
   </si>
   <si>
     <t xml:space="preserve">33.6784057617188</t>
@@ -4583,10 +4583,10 @@
     <t xml:space="preserve">33.6593399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">33.039722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7260665893555</t>
+    <t xml:space="preserve">33.0397262573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7260704040527</t>
   </si>
   <si>
     <t xml:space="preserve">33.0587921142578</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">32.2866554260254</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9729957580566</t>
+    <t xml:space="preserve">32.9729995727539</t>
   </si>
   <si>
     <t xml:space="preserve">33.373363494873</t>
@@ -4610,7 +4610,7 @@
     <t xml:space="preserve">33.4114952087402</t>
   </si>
   <si>
-    <t xml:space="preserve">33.583080291748</t>
+    <t xml:space="preserve">33.5830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">34.0311126708984</t>
@@ -4625,7 +4625,7 @@
     <t xml:space="preserve">34.5649299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2512741088867</t>
+    <t xml:space="preserve">35.2512702941895</t>
   </si>
   <si>
     <t xml:space="preserve">35.4323883056641</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">35.5753746032715</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7469596862793</t>
+    <t xml:space="preserve">35.7469635009766</t>
   </si>
   <si>
     <t xml:space="preserve">35.3942604064941</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">35.6516380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">36.109203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.985279083252</t>
+    <t xml:space="preserve">36.1091995239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">35.7088317871094</t>
@@ -4661,13 +4661,13 @@
     <t xml:space="preserve">35.2036094665527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5944442749023</t>
+    <t xml:space="preserve">35.5944404602051</t>
   </si>
   <si>
     <t xml:space="preserve">34.9843635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5563087463379</t>
+    <t xml:space="preserve">35.5563125610352</t>
   </si>
   <si>
     <t xml:space="preserve">35.3370628356934</t>
@@ -4676,10 +4676,10 @@
     <t xml:space="preserve">35.8327560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1568641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9376182556152</t>
+    <t xml:space="preserve">36.1568603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.937614440918</t>
   </si>
   <si>
     <t xml:space="preserve">35.270336151123</t>
@@ -4694,28 +4694,28 @@
     <t xml:space="preserve">34.5839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1455001831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8413734436035</t>
+    <t xml:space="preserve">34.1454963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8413696289062</t>
   </si>
   <si>
     <t xml:space="preserve">34.6697883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9557647705078</t>
+    <t xml:space="preserve">34.9557609558105</t>
   </si>
   <si>
     <t xml:space="preserve">34.6888542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1759262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1282653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0615348815918</t>
+    <t xml:space="preserve">36.1759300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1282615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0615386962891</t>
   </si>
   <si>
     <t xml:space="preserve">36.7097473144531</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">34.9748268127441</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6707038879395</t>
+    <t xml:space="preserve">35.6707000732422</t>
   </si>
   <si>
     <t xml:space="preserve">33.7546653747559</t>
@@ -4739,16 +4739,16 @@
     <t xml:space="preserve">34.2312927246094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8881225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3552131652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.108283996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1178131103516</t>
+    <t xml:space="preserve">33.8881187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3552169799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1082878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1178169250488</t>
   </si>
   <si>
     <t xml:space="preserve">34.7746429443359</t>
@@ -4763,37 +4763,37 @@
     <t xml:space="preserve">36.5953559875488</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8908615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2235908508301</t>
+    <t xml:space="preserve">36.8908653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2235870361328</t>
   </si>
   <si>
     <t xml:space="preserve">35.9566802978516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9462280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3656616210938</t>
+    <t xml:space="preserve">34.946231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3656578063965</t>
   </si>
   <si>
     <t xml:space="preserve">35.4037895202637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5086479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3847236633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9471435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9090156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5286293029785</t>
+    <t xml:space="preserve">35.5086517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3847274780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9471473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9090118408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5286254882812</t>
   </si>
   <si>
     <t xml:space="preserve">36.4619026184082</t>
@@ -4814,7 +4814,7 @@
     <t xml:space="preserve">35.0516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9039688110352</t>
+    <t xml:space="preserve">35.9039649963379</t>
   </si>
   <si>
     <t xml:space="preserve">36.2139015197754</t>
@@ -4832,16 +4832,16 @@
     <t xml:space="preserve">36.4947814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6521492004395</t>
+    <t xml:space="preserve">35.6521453857422</t>
   </si>
   <si>
     <t xml:space="preserve">35.3809509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0249938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2477569580078</t>
+    <t xml:space="preserve">34.0249900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2477531433105</t>
   </si>
   <si>
     <t xml:space="preserve">34.6739158630371</t>
@@ -4883,25 +4883,25 @@
     <t xml:space="preserve">33.5794563293457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.664234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3518943786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4995727539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4027252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4705238342285</t>
+    <t xml:space="preserve">34.6642303466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3518981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4995765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4027214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4705200195312</t>
   </si>
   <si>
     <t xml:space="preserve">34.62548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5770606994629</t>
+    <t xml:space="preserve">34.5770645141602</t>
   </si>
   <si>
     <t xml:space="preserve">35.6618309020996</t>
@@ -4919,28 +4919,28 @@
     <t xml:space="preserve">35.9620819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5649757385254</t>
+    <t xml:space="preserve">35.5649795532227</t>
   </si>
   <si>
     <t xml:space="preserve">34.9354209899902</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8579406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8312835693359</t>
+    <t xml:space="preserve">34.8579444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8312797546387</t>
   </si>
   <si>
     <t xml:space="preserve">34.8676261901855</t>
   </si>
   <si>
-    <t xml:space="preserve">35.952392578125</t>
+    <t xml:space="preserve">35.9523963928223</t>
   </si>
   <si>
     <t xml:space="preserve">35.855541229248</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0759086608887</t>
+    <t xml:space="preserve">37.0759048461914</t>
   </si>
   <si>
     <t xml:space="preserve">36.8240852355957</t>
@@ -4955,10 +4955,10 @@
     <t xml:space="preserve">35.1678733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6812057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5456047058105</t>
+    <t xml:space="preserve">35.6812019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5456085205078</t>
   </si>
   <si>
     <t xml:space="preserve">36.5432052612305</t>
@@ -4967,13 +4967,13 @@
     <t xml:space="preserve">36.349494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.894287109375</t>
+    <t xml:space="preserve">35.8942832946777</t>
   </si>
   <si>
     <t xml:space="preserve">35.739315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6230888366699</t>
+    <t xml:space="preserve">35.6230850219727</t>
   </si>
   <si>
     <t xml:space="preserve">35.5359191894531</t>
@@ -4982,7 +4982,7 @@
     <t xml:space="preserve">35.2259864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2550468444824</t>
+    <t xml:space="preserve">35.2550430297852</t>
   </si>
   <si>
     <t xml:space="preserve">34.7513999938965</t>
@@ -5003,19 +5003,19 @@
     <t xml:space="preserve">36.0492515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7029724121094</t>
+    <t xml:space="preserve">34.7029762268066</t>
   </si>
   <si>
     <t xml:space="preserve">34.4802055358887</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5383186340332</t>
+    <t xml:space="preserve">34.5383224487305</t>
   </si>
   <si>
     <t xml:space="preserve">34.2671279907227</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5480003356934</t>
+    <t xml:space="preserve">34.5480041503906</t>
   </si>
   <si>
     <t xml:space="preserve">33.8700256347656</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">34.7901382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1872444152832</t>
+    <t xml:space="preserve">35.1872482299805</t>
   </si>
   <si>
     <t xml:space="preserve">36.4463539123535</t>
@@ -5042,10 +5042,10 @@
     <t xml:space="preserve">36.6013221740723</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5625762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.136417388916</t>
+    <t xml:space="preserve">36.5625801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1364212036133</t>
   </si>
   <si>
     <t xml:space="preserve">36.3010711669922</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">36.3398132324219</t>
   </si>
   <si>
-    <t xml:space="preserve">36.504467010498</t>
+    <t xml:space="preserve">36.5044631958008</t>
   </si>
   <si>
     <t xml:space="preserve">36.7078590393066</t>
@@ -5069,22 +5069,22 @@
     <t xml:space="preserve">36.6497497558594</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7732582092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9282264709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5408058166504</t>
+    <t xml:space="preserve">37.7732620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9282302856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5408096313477</t>
   </si>
   <si>
     <t xml:space="preserve">37.4633255004883</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7635765075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3591842651367</t>
+    <t xml:space="preserve">37.7635726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.359188079834</t>
   </si>
   <si>
     <t xml:space="preserve">36.020191192627</t>
@@ -5096,16 +5096,16 @@
     <t xml:space="preserve">35.061336517334</t>
   </si>
   <si>
-    <t xml:space="preserve">36.291389465332</t>
+    <t xml:space="preserve">36.2913856506348</t>
   </si>
   <si>
     <t xml:space="preserve">36.9499969482422</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0274810791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.119441986084</t>
+    <t xml:space="preserve">37.0274772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1194458007812</t>
   </si>
   <si>
     <t xml:space="preserve">36.0008201599121</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">34.3930358886719</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1000747680664</t>
+    <t xml:space="preserve">35.1000785827637</t>
   </si>
   <si>
     <t xml:space="preserve">34.4608383178711</t>
@@ -5141,13 +5141,13 @@
     <t xml:space="preserve">33.7150573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5310287475586</t>
+    <t xml:space="preserve">33.5310325622559</t>
   </si>
   <si>
     <t xml:space="preserve">32.7755661010742</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7271385192871</t>
+    <t xml:space="preserve">32.7271423339844</t>
   </si>
   <si>
     <t xml:space="preserve">32.7174530029297</t>
@@ -5159,16 +5159,16 @@
     <t xml:space="preserve">34.1799583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8022270202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6836051940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9547920227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7441101074219</t>
+    <t xml:space="preserve">33.8022232055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6836013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9547958374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7441139221191</t>
   </si>
   <si>
     <t xml:space="preserve">33.8990783691406</t>
@@ -5186,16 +5186,16 @@
     <t xml:space="preserve">35.1581878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8482551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3155517578125</t>
+    <t xml:space="preserve">34.8482513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3155555725098</t>
   </si>
   <si>
     <t xml:space="preserve">33.8409652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4729232788086</t>
+    <t xml:space="preserve">33.4729194641113</t>
   </si>
   <si>
     <t xml:space="preserve">34.160587310791</t>
@@ -5210,10 +5210,10 @@
     <t xml:space="preserve">36.1945304870605</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3083610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5795478820801</t>
+    <t xml:space="preserve">37.3083572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5795516967773</t>
   </si>
   <si>
     <t xml:space="preserve">37.6473503112793</t>
@@ -5234,7 +5234,7 @@
     <t xml:space="preserve">39.3713607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3229331970215</t>
+    <t xml:space="preserve">39.3229293823242</t>
   </si>
   <si>
     <t xml:space="preserve">39.410099029541</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">39.4585304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6134986877441</t>
+    <t xml:space="preserve">39.6134948730469</t>
   </si>
   <si>
     <t xml:space="preserve">39.1389083862305</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">39.8846893310547</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5553817749023</t>
+    <t xml:space="preserve">39.5553855895996</t>
   </si>
   <si>
     <t xml:space="preserve">39.4682159423828</t>
@@ -5285,7 +5285,7 @@
     <t xml:space="preserve">38.8870887756348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4197883605957</t>
+    <t xml:space="preserve">39.4197845458984</t>
   </si>
   <si>
     <t xml:space="preserve">38.8677177429199</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">39.264820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8096046447754</t>
+    <t xml:space="preserve">38.8096008300781</t>
   </si>
   <si>
     <t xml:space="preserve">39.4972686767578</t>
@@ -5303,7 +5303,7 @@
     <t xml:space="preserve">39.2745056152344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7490921020508</t>
+    <t xml:space="preserve">39.749095916748</t>
   </si>
   <si>
     <t xml:space="preserve">38.9355125427246</t>
@@ -5312,13 +5312,13 @@
     <t xml:space="preserve">39.6425514221191</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7006683349609</t>
+    <t xml:space="preserve">39.7006645202637</t>
   </si>
   <si>
     <t xml:space="preserve">39.8168907165527</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0009117126465</t>
+    <t xml:space="preserve">40.0009155273438</t>
   </si>
   <si>
     <t xml:space="preserve">40.4173889160156</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">40.707950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6110954284668</t>
+    <t xml:space="preserve">40.6110992431641</t>
   </si>
   <si>
     <t xml:space="preserve">39.7103500366211</t>
@@ -5339,16 +5339,16 @@
     <t xml:space="preserve">41.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3254241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8798942565918</t>
+    <t xml:space="preserve">42.3254203796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8798904418945</t>
   </si>
   <si>
     <t xml:space="preserve">42.257625579834</t>
   </si>
   <si>
-    <t xml:space="preserve">42.693473815918</t>
+    <t xml:space="preserve">42.6934700012207</t>
   </si>
   <si>
     <t xml:space="preserve">43.2358551025391</t>
@@ -5357,7 +5357,7 @@
     <t xml:space="preserve">43.8072967529297</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8968658447266</t>
+    <t xml:space="preserve">42.8968620300293</t>
   </si>
   <si>
     <t xml:space="preserve">42.906551361084</t>
@@ -5366,7 +5366,7 @@
     <t xml:space="preserve">43.4779891967773</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6015014648438</t>
+    <t xml:space="preserve">44.601505279541</t>
   </si>
   <si>
     <t xml:space="preserve">44.5627593994141</t>
@@ -5381,10 +5381,10 @@
     <t xml:space="preserve">45.5022506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4925651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.376335144043</t>
+    <t xml:space="preserve">45.4925689697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3763389587402</t>
   </si>
   <si>
     <t xml:space="preserve">44.4465370178223</t>
@@ -5396,7 +5396,7 @@
     <t xml:space="preserve">45.8896713256836</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5870170593262</t>
+    <t xml:space="preserve">46.5870208740234</t>
   </si>
   <si>
     <t xml:space="preserve">46.112434387207</t>
@@ -5405,7 +5405,7 @@
     <t xml:space="preserve">46.4514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1875190734863</t>
+    <t xml:space="preserve">47.1875228881836</t>
   </si>
   <si>
     <t xml:space="preserve">47.8558158874512</t>
@@ -5414,10 +5414,10 @@
     <t xml:space="preserve">47.4683952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8364410400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2141723632812</t>
+    <t xml:space="preserve">47.8364448547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2141761779785</t>
   </si>
   <si>
     <t xml:space="preserve">48.1560668945312</t>
@@ -5426,28 +5426,28 @@
     <t xml:space="preserve">47.1487770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8678970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4126815795898</t>
+    <t xml:space="preserve">46.8679008483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4126777648926</t>
   </si>
   <si>
     <t xml:space="preserve">46.548282623291</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7323036193848</t>
+    <t xml:space="preserve">46.7322998046875</t>
   </si>
   <si>
     <t xml:space="preserve">46.7226181030273</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6039924621582</t>
+    <t xml:space="preserve">47.6039962768555</t>
   </si>
   <si>
     <t xml:space="preserve">46.8097877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9938087463379</t>
+    <t xml:space="preserve">46.9938125610352</t>
   </si>
   <si>
     <t xml:space="preserve">46.6838760375977</t>
@@ -5459,10 +5459,10 @@
     <t xml:space="preserve">47.8654975891113</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6403350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8146743774414</t>
+    <t xml:space="preserve">48.6403388977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8146781921387</t>
   </si>
   <si>
     <t xml:space="preserve">48.6968154907227</t>
@@ -71528,7 +71528,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6496180556</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>1080138</v>
@@ -71549,6 +71549,32 @@
         <v>2145</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6527430556</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>1099342</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>88.9400024414062</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>87.2200012207031</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>88.6600036621094</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>87.4599990844727</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>2139</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="2146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="2147">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6851539611816</t>
+    <t xml:space="preserve">15.6851577758789</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
@@ -47,202 +47,202 @@
     <t xml:space="preserve">15.8714008331299</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3207588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.239785194397</t>
+    <t xml:space="preserve">15.3207597732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2397832870483</t>
   </si>
   <si>
     <t xml:space="preserve">14.7458295822144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9644632339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2964639663696</t>
+    <t xml:space="preserve">14.9644641876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2964668273926</t>
   </si>
   <si>
     <t xml:space="preserve">15.4989109039307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.061637878418</t>
+    <t xml:space="preserve">15.0616369247437</t>
   </si>
   <si>
     <t xml:space="preserve">14.5028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5433864593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8511009216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9401721954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4098358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9239768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2802715301514</t>
+    <t xml:space="preserve">14.5433883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8510980606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870908737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9401712417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4098377227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9239778518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2802724838257</t>
   </si>
   <si>
     <t xml:space="preserve">15.1831026077271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6243629455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936414718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8106107711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7296333312988</t>
+    <t xml:space="preserve">14.624361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936395645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8106079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7296342849731</t>
   </si>
   <si>
     <t xml:space="preserve">14.8996829986572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5190925598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7336196899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3449354171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0980176925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3206396102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4744968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8955755233765</t>
+    <t xml:space="preserve">14.5190916061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.73362159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3449335098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.098014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3206405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.474494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8955764770508</t>
   </si>
   <si>
     <t xml:space="preserve">13.7822065353394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3328466415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2194786071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057264328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8348999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5514822006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3409461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8672904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1021251678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235918045044</t>
+    <t xml:space="preserve">14.3328485488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2194814682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057273864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8349027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5514831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3409452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8672933578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.102123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2235908508301</t>
   </si>
   <si>
     <t xml:space="preserve">15.4827156066895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3774461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017391204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.466516494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4908103942871</t>
+    <t xml:space="preserve">15.3774480819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4017362594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4665193557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4908113479614</t>
   </si>
   <si>
     <t xml:space="preserve">15.5232038497925</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5636920928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426124572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8390140533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.587984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6365718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9199867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8309116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8795013427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8228158950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8956937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2762851715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.122428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.847110748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8875961303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4422273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3855438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086757659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2276973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7135581970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6568737030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.430139541626</t>
+    <t xml:space="preserve">15.5636901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426115036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8390130996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879831314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6365699768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9199876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8309135437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8795003890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8228130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.895694732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2762832641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1224269866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8471097946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8875951766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4422254562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3855428695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2277011871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7135562896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6568756103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4301376342773</t>
   </si>
   <si>
     <t xml:space="preserve">16.6120548248291</t>
@@ -254,34 +254,34 @@
     <t xml:space="preserve">17.0254955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9758796691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9924182891846</t>
+    <t xml:space="preserve">16.9758815765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9924201965332</t>
   </si>
   <si>
     <t xml:space="preserve">16.6285915374756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7774314880371</t>
+    <t xml:space="preserve">16.7774295806885</t>
   </si>
   <si>
     <t xml:space="preserve">16.98415184021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1081829071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9345359802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5541744232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5955142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.760892868042</t>
+    <t xml:space="preserve">17.1081790924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9345397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5541725158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.595516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7608947753906</t>
   </si>
   <si>
     <t xml:space="preserve">16.703010559082</t>
@@ -290,73 +290,73 @@
     <t xml:space="preserve">16.8766574859619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4058609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7696857452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0094833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9681415557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8606452941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7779579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8854541778564</t>
+    <t xml:space="preserve">17.4058589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0094814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9681396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8606472015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7779560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8854522705078</t>
   </si>
   <si>
     <t xml:space="preserve">17.6952705383301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1087093353271</t>
+    <t xml:space="preserve">18.1087074279785</t>
   </si>
   <si>
     <t xml:space="preserve">17.9598693847656</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2658195495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748580932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.282356262207</t>
+    <t xml:space="preserve">18.2658157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1748600006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2823581695557</t>
   </si>
   <si>
     <t xml:space="preserve">18.2988929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4725399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1831321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1335182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0425624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8027648925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0921726226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9185256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0012168884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.314905166626</t>
+    <t xml:space="preserve">18.4725360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1831283569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1335144042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0425586700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8027629852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.092170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9185276031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0012149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3149013519287</t>
   </si>
   <si>
     <t xml:space="preserve">16.9097328186035</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">16.6368598937988</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8022384643555</t>
+    <t xml:space="preserve">16.8022403717041</t>
   </si>
   <si>
     <t xml:space="preserve">17.7366142272949</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">17.5712375640869</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3479785919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9102573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6694078445435</t>
+    <t xml:space="preserve">17.3479766845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9102592468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6694087982178</t>
   </si>
   <si>
     <t xml:space="preserve">14.8342571258545</t>
@@ -389,67 +389,67 @@
     <t xml:space="preserve">15.1402053833008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2559690475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2978382110596</t>
+    <t xml:space="preserve">15.2559680938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2978401184082</t>
   </si>
   <si>
     <t xml:space="preserve">15.7272882461548</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5867223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2311611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6115283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2812995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4632167816162</t>
+    <t xml:space="preserve">15.5867214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.231162071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6115274429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2813014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4632148742676</t>
   </si>
   <si>
     <t xml:space="preserve">16.6533985137939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6864757537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6782035827637</t>
+    <t xml:space="preserve">16.6864738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6782054901123</t>
   </si>
   <si>
     <t xml:space="preserve">16.7443542480469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6699371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8435802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8187732696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9510746002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0999145507812</t>
+    <t xml:space="preserve">16.6699352264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.843578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8187713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9510765075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.099910736084</t>
   </si>
   <si>
     <t xml:space="preserve">17.1164512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2983646392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2404880523682</t>
+    <t xml:space="preserve">17.2983665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2404823303223</t>
   </si>
   <si>
     <t xml:space="preserve">17.0751075744629</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">18.1004409790039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6125793457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5960426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0756359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7944965362549</t>
+    <t xml:space="preserve">17.6125812530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5960445404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0756340026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7944946289062</t>
   </si>
   <si>
     <t xml:space="preserve">17.8771858215332</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">18.1913986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2492790222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0839004516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2906246185303</t>
+    <t xml:space="preserve">18.2492809295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0839023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2906227111816</t>
   </si>
   <si>
     <t xml:space="preserve">18.1665897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9929485321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.844108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7200736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.728343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8937206268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0673637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3733139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9438629150391</t>
+    <t xml:space="preserve">17.9929466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8441066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7200775146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7283458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8937244415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0673675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.37331199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9438591003418</t>
   </si>
   <si>
     <t xml:space="preserve">19.4317207336426</t>
@@ -524,34 +524,34 @@
     <t xml:space="preserve">19.3573017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1009654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1257743835449</t>
+    <t xml:space="preserve">19.1009674072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1257724761963</t>
   </si>
   <si>
     <t xml:space="preserve">19.1919250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1753883361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2828845977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1340446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3490314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7624702453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549777984619</t>
+    <t xml:space="preserve">19.175386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2828826904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1340427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3490295410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.76247215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549816131592</t>
   </si>
   <si>
     <t xml:space="preserve">19.7045936584473</t>
@@ -560,28 +560,28 @@
     <t xml:space="preserve">19.4647960662842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0596256256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.646183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1175060272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1588516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0100135803223</t>
+    <t xml:space="preserve">19.0596237182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6461811065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1175079345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1588497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0100154876709</t>
   </si>
   <si>
     <t xml:space="preserve">18.7536792755127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9025211334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0844326019287</t>
+    <t xml:space="preserve">18.902515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0844287872314</t>
   </si>
   <si>
     <t xml:space="preserve">18.9934749603271</t>
@@ -590,19 +590,19 @@
     <t xml:space="preserve">18.7950210571289</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7867527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7454071044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3319683074951</t>
+    <t xml:space="preserve">18.7867546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7454109191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3319664001465</t>
   </si>
   <si>
     <t xml:space="preserve">17.6291198730469</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8694400787354</t>
+    <t xml:space="preserve">18.869441986084</t>
   </si>
   <si>
     <t xml:space="preserve">19.1505832672119</t>
@@ -611,31 +611,31 @@
     <t xml:space="preserve">18.3485088348389</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6627216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7288703918457</t>
+    <t xml:space="preserve">18.6627197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.728874206543</t>
   </si>
   <si>
     <t xml:space="preserve">18.6875286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8942451477051</t>
+    <t xml:space="preserve">18.8942470550537</t>
   </si>
   <si>
     <t xml:space="preserve">18.4229259490967</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4808101654053</t>
+    <t xml:space="preserve">18.480806350708</t>
   </si>
   <si>
     <t xml:space="preserve">18.2327423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3236980438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0590972900391</t>
+    <t xml:space="preserve">18.3237018585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0590934753418</t>
   </si>
   <si>
     <t xml:space="preserve">18.6709899902344</t>
@@ -644,19 +644,19 @@
     <t xml:space="preserve">18.9355926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4399871826172</t>
+    <t xml:space="preserve">19.4399929046631</t>
   </si>
   <si>
     <t xml:space="preserve">19.8782367706299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6797847747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1676483154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8451614379883</t>
+    <t xml:space="preserve">19.6797866821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1676425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8451633453369</t>
   </si>
   <si>
     <t xml:space="preserve">19.7790126800537</t>
@@ -668,52 +668,52 @@
     <t xml:space="preserve">19.9113121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1759185791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0022678375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.927848815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0105381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8038177490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1014957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1263027191162</t>
+    <t xml:space="preserve">20.1759166717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.002269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9278507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0105361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8038196563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1014976501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1263008117676</t>
   </si>
   <si>
     <t xml:space="preserve">20.1097660064697</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1924514770508</t>
+    <t xml:space="preserve">20.1924495697021</t>
   </si>
   <si>
     <t xml:space="preserve">20.6389675140381</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1345710754395</t>
+    <t xml:space="preserve">20.1345691680908</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751407623291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2172603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3164825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2420616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3330211639404</t>
+    <t xml:space="preserve">20.2172584533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3164844512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2420654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3330249786377</t>
   </si>
   <si>
     <t xml:space="preserve">20.2255268096924</t>
@@ -722,115 +722,115 @@
     <t xml:space="preserve">20.6555061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5066699981689</t>
+    <t xml:space="preserve">20.5066680908203</t>
   </si>
   <si>
     <t xml:space="preserve">20.3578300476074</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4818592071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0849571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3991718292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645484924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5397396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6885814666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.894775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4074440002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7133865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9697227478027</t>
+    <t xml:space="preserve">20.481861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0849590301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3991737365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5645503997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5397434234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6885795593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8947734832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4074401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7133884429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9697189331055</t>
   </si>
   <si>
     <t xml:space="preserve">20.3495597839355</t>
   </si>
   <si>
-    <t xml:space="preserve">20.423978805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3082141876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.754732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9609279632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8865051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8286266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8534317016602</t>
+    <t xml:space="preserve">20.4239768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3082160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7547302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9609241485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8865032196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8286247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8534278869629</t>
   </si>
   <si>
     <t xml:space="preserve">20.1180324554443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5722923278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2994194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5144062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474834442139</t>
+    <t xml:space="preserve">19.5722942352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2994174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5144081115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474853515625</t>
   </si>
   <si>
     <t xml:space="preserve">19.4234523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6136379241943</t>
+    <t xml:space="preserve">19.6136360168457</t>
   </si>
   <si>
     <t xml:space="preserve">19.5640201568604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3821105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7376670837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3660984039307</t>
+    <t xml:space="preserve">19.3821067810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7376689910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3661022186279</t>
   </si>
   <si>
     <t xml:space="preserve">19.9361190795898</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2007160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4901313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7381935119629</t>
+    <t xml:space="preserve">20.200719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4901294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7381954193115</t>
   </si>
   <si>
     <t xml:space="preserve">21.2922058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1516342163086</t>
+    <t xml:space="preserve">21.15163230896</t>
   </si>
   <si>
     <t xml:space="preserve">21.0854816436768</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">20.9366455078125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7795391082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.457052230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7051200866699</t>
+    <t xml:space="preserve">20.7795372009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4570541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7051181793213</t>
   </si>
   <si>
     <t xml:space="preserve">21.1268291473389</t>
@@ -854,49 +854,49 @@
     <t xml:space="preserve">22.0435581207275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1192512512207</t>
+    <t xml:space="preserve">22.1192474365234</t>
   </si>
   <si>
     <t xml:space="preserve">21.8669414520264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9846858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2958679199219</t>
+    <t xml:space="preserve">21.9846878051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2958698272705</t>
   </si>
   <si>
     <t xml:space="preserve">22.4724884033203</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2201747894287</t>
+    <t xml:space="preserve">22.220178604126</t>
   </si>
   <si>
     <t xml:space="preserve">22.262228012085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5397701263428</t>
+    <t xml:space="preserve">22.5397720336914</t>
   </si>
   <si>
     <t xml:space="preserve">22.5734081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5986423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8080673217773</t>
+    <t xml:space="preserve">22.5986404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8080654144287</t>
   </si>
   <si>
     <t xml:space="preserve">21.69873046875</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0847778320312</t>
+    <t xml:space="preserve">21.0847759246826</t>
   </si>
   <si>
     <t xml:space="preserve">21.3202667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9502124786377</t>
+    <t xml:space="preserve">20.9502086639404</t>
   </si>
   <si>
     <t xml:space="preserve">20.6390266418457</t>
@@ -905,46 +905,46 @@
     <t xml:space="preserve">20.4203586578369</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5549240112305</t>
+    <t xml:space="preserve">20.5549221038818</t>
   </si>
   <si>
     <t xml:space="preserve">20.4540023803711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9670314788818</t>
+    <t xml:space="preserve">20.9670295715332</t>
   </si>
   <si>
     <t xml:space="preserve">21.1941108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8576984405518</t>
+    <t xml:space="preserve">20.8576965332031</t>
   </si>
   <si>
     <t xml:space="preserve">21.1688823699951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8324661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9586200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156452178955</t>
+    <t xml:space="preserve">20.8324642181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9586162567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8156471252441</t>
   </si>
   <si>
     <t xml:space="preserve">21.5978088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2613945007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1015949249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6819133758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6146297454834</t>
+    <t xml:space="preserve">21.2613964080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.101598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6819114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.614631652832</t>
   </si>
   <si>
     <t xml:space="preserve">21.8164806365967</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">21.6566791534424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8248920440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5473461151123</t>
+    <t xml:space="preserve">21.8248901367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.547342300415</t>
   </si>
   <si>
     <t xml:space="preserve">21.5725784301758</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">21.8585300445557</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9258098602295</t>
+    <t xml:space="preserve">21.9258117675781</t>
   </si>
   <si>
     <t xml:space="preserve">21.7828369140625</t>
@@ -986,109 +986,109 @@
     <t xml:space="preserve">22.1949462890625</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8501224517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2454051971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0015068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3883819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538185119629</t>
+    <t xml:space="preserve">21.8501205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2454032897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0015048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3883838653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538146972656</t>
   </si>
   <si>
     <t xml:space="preserve">22.5481796264648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5313587188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7668476104736</t>
+    <t xml:space="preserve">22.5313625335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7668495178223</t>
   </si>
   <si>
     <t xml:space="preserve">23.0696220397949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5818214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8425407409668</t>
+    <t xml:space="preserve">22.5818195343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8425426483154</t>
   </si>
   <si>
     <t xml:space="preserve">22.564998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1444816589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2117652893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1865329742432</t>
+    <t xml:space="preserve">22.1444797515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2117671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1865348815918</t>
   </si>
   <si>
     <t xml:space="preserve">22.52294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7920780181885</t>
+    <t xml:space="preserve">22.7920799255371</t>
   </si>
   <si>
     <t xml:space="preserve">22.4220237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7500267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9266471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9350566864014</t>
+    <t xml:space="preserve">22.7500286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.926643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9350547790527</t>
   </si>
   <si>
     <t xml:space="preserve">22.8593635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7079753875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5902328491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2369976043701</t>
+    <t xml:space="preserve">22.7079772949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5902271270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2369956970215</t>
   </si>
   <si>
     <t xml:space="preserve">21.8417091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1613025665283</t>
+    <t xml:space="preserve">22.1613006591797</t>
   </si>
   <si>
     <t xml:space="preserve">22.3547401428223</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3042793273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9594554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2285842895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1108417510986</t>
+    <t xml:space="preserve">22.3042812347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9594535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2285861968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.11083984375</t>
   </si>
   <si>
     <t xml:space="preserve">21.9174003601074</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3463325500488</t>
+    <t xml:space="preserve">22.3463306427002</t>
   </si>
   <si>
     <t xml:space="preserve">22.4304351806641</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">22.825719833374</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4649085998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6331176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6751689910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6835784912109</t>
+    <t xml:space="preserve">23.4649066925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6331157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6751651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6835765838623</t>
   </si>
   <si>
     <t xml:space="preserve">23.8097343444824</t>
@@ -1118,31 +1118,31 @@
     <t xml:space="preserve">23.9190692901611</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7508602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8770160675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.986349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8938369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9527111053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9779415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.85178565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0368118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4741497039795</t>
+    <t xml:space="preserve">23.750862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8770179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9863510131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8938407897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.952709197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9779396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8517875671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0368137359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4741535186768</t>
   </si>
   <si>
     <t xml:space="preserve">24.3311748504639</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">24.0536346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9358901977539</t>
+    <t xml:space="preserve">23.9358882904053</t>
   </si>
   <si>
     <t xml:space="preserve">23.8013229370117</t>
@@ -1163,82 +1163,82 @@
     <t xml:space="preserve">23.9611206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0199947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.104097366333</t>
+    <t xml:space="preserve">24.0199928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1040992736816</t>
   </si>
   <si>
     <t xml:space="preserve">24.558256149292</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5077972412109</t>
+    <t xml:space="preserve">24.5077953338623</t>
   </si>
   <si>
     <t xml:space="preserve">24.3564071655273</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3984603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9199047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7937450408936</t>
+    <t xml:space="preserve">24.398458480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9199028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7937469482422</t>
   </si>
   <si>
     <t xml:space="preserve">24.6928215026855</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8946685791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2310829162598</t>
+    <t xml:space="preserve">24.8946704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2310848236084</t>
   </si>
   <si>
     <t xml:space="preserve">25.1217498779297</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1890316009521</t>
+    <t xml:space="preserve">25.1890335083008</t>
   </si>
   <si>
     <t xml:space="preserve">24.8526210784912</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4489212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5574207305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3892154693604</t>
+    <t xml:space="preserve">24.4489231109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5574245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.389217376709</t>
   </si>
   <si>
     <t xml:space="preserve">23.5994739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2125968933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9274806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6919898986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5406036376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5742416381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3808040618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4144477844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5321884155273</t>
+    <t xml:space="preserve">23.2125988006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9274787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.691987991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5406017303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5742435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3808059692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4144458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.532190322876</t>
   </si>
   <si>
     <t xml:space="preserve">23.9695301055908</t>
@@ -1247,34 +1247,34 @@
     <t xml:space="preserve">22.9939289093018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6911544799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014148712158</t>
+    <t xml:space="preserve">22.6911563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014167785645</t>
   </si>
   <si>
     <t xml:space="preserve">22.9771099090576</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0443897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0275688171387</t>
+    <t xml:space="preserve">23.0443878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0275707244873</t>
   </si>
   <si>
     <t xml:space="preserve">23.0359783172607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8930072784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6827430725098</t>
+    <t xml:space="preserve">22.8930053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.682746887207</t>
   </si>
   <si>
     <t xml:space="preserve">23.1789569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2546482086182</t>
+    <t xml:space="preserve">23.2546501159668</t>
   </si>
   <si>
     <t xml:space="preserve">23.2210102081299</t>
@@ -1283,22 +1283,22 @@
     <t xml:space="preserve">23.1621360778809</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2294158935547</t>
+    <t xml:space="preserve">23.2294178009033</t>
   </si>
   <si>
     <t xml:space="preserve">23.078031539917</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8677711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0107498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1881999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0031719207764</t>
+    <t xml:space="preserve">22.8677730560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0107479095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1882019042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.003173828125</t>
   </si>
   <si>
     <t xml:space="preserve">24.1713790893555</t>
@@ -1313,103 +1313,103 @@
     <t xml:space="preserve">24.4909725189209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8273887634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5246143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3395862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.305944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8686065673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8349628448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.288293838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9602851867676</t>
+    <t xml:space="preserve">24.8273868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5246162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3395881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3059463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8686046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8349647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2882900238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9602870941162</t>
   </si>
   <si>
     <t xml:space="preserve">22.6070518493652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4564971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7163867950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4556636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0687923431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1781234741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0940189361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.908992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7996578216553</t>
+    <t xml:space="preserve">23.4564952850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7163848876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4556674957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.068790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1781215667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0940208435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9089908599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7996559143066</t>
   </si>
   <si>
     <t xml:space="preserve">21.6314506530762</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7912445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3631496429443</t>
+    <t xml:space="preserve">21.7912483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3631477355957</t>
   </si>
   <si>
     <t xml:space="preserve">22.3967933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2874584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0856113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6230392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3454990386963</t>
+    <t xml:space="preserve">22.2874622344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0856094360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6230430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3455009460449</t>
   </si>
   <si>
     <t xml:space="preserve">21.4043712615967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.446418762207</t>
+    <t xml:space="preserve">21.4464206695557</t>
   </si>
   <si>
     <t xml:space="preserve">21.2950344085693</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3370876312256</t>
+    <t xml:space="preserve">21.337085723877</t>
   </si>
   <si>
     <t xml:space="preserve">21.7407855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7904109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3194351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7988243103027</t>
+    <t xml:space="preserve">20.790412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3194332122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7988224029541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4035377502441</t>
@@ -1418,31 +1418,31 @@
     <t xml:space="preserve">20.5717430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7735939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9249801635742</t>
+    <t xml:space="preserve">20.7735919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9249820709229</t>
   </si>
   <si>
     <t xml:space="preserve">20.8072338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0288715362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8919315338135</t>
+    <t xml:space="preserve">21.0288734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8919334411621</t>
   </si>
   <si>
     <t xml:space="preserve">20.6351680755615</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6180534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7464332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8662528991699</t>
+    <t xml:space="preserve">20.6180515289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7464294433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8662548065186</t>
   </si>
   <si>
     <t xml:space="preserve">21.3883399963379</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">20.9604015350342</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3626651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5081634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8847465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7563667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2270965576172</t>
+    <t xml:space="preserve">21.3626613616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5081596374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8847484588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.756368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2271003723145</t>
   </si>
   <si>
     <t xml:space="preserve">22.9203567504883</t>
@@ -1475,22 +1475,22 @@
     <t xml:space="preserve">22.4239501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8077182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0987167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1072769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7392501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2428398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4568099975586</t>
+    <t xml:space="preserve">21.8077163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0987205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1072750091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7392463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2428436279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.45680809021</t>
   </si>
   <si>
     <t xml:space="preserve">21.4054584503174</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">20.1302032470703</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1216411590576</t>
+    <t xml:space="preserve">20.1216430664062</t>
   </si>
   <si>
     <t xml:space="preserve">20.3698463439941</t>
@@ -1517,34 +1517,34 @@
     <t xml:space="preserve">21.336986541748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3797779083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0117568969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779632568359</t>
+    <t xml:space="preserve">21.3797798156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0117511749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779651641846</t>
   </si>
   <si>
     <t xml:space="preserve">21.1743698120117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8063430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7977809906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9960117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5424003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1914882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9090442657471</t>
+    <t xml:space="preserve">20.8063468933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7977848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9960136413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5423984527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1914901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9090461730957</t>
   </si>
   <si>
     <t xml:space="preserve">20.4554347991943</t>
@@ -1553,52 +1553,52 @@
     <t xml:space="preserve">19.6509113311768</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8563213348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8706874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9306011199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2729511260986</t>
+    <t xml:space="preserve">19.8563194274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8706893920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9305973052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2729473114014</t>
   </si>
   <si>
     <t xml:space="preserve">17.4427509307861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2558345794678</t>
+    <t xml:space="preserve">18.2558326721191</t>
   </si>
   <si>
     <t xml:space="preserve">17.9355735778809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6260833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2454166412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1657447814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1568908691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8119926452637</t>
+    <t xml:space="preserve">18.6260852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.245418548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1657428741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1568870544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.811990737915</t>
   </si>
   <si>
     <t xml:space="preserve">19.2280654907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9978981018066</t>
+    <t xml:space="preserve">18.997896194458</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2988891601562</t>
+    <t xml:space="preserve">19.2988872528076</t>
   </si>
   <si>
     <t xml:space="preserve">19.1838035583496</t>
@@ -1607,25 +1607,25 @@
     <t xml:space="preserve">19.2103652954102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4139747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.520206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5113525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5644702911377</t>
+    <t xml:space="preserve">19.4139766693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5202045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5113544464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5644721984863</t>
   </si>
   <si>
     <t xml:space="preserve">19.723819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.635290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4316787719727</t>
+    <t xml:space="preserve">19.6352939605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4316806793213</t>
   </si>
   <si>
     <t xml:space="preserve">19.1395416259766</t>
@@ -1634,28 +1634,28 @@
     <t xml:space="preserve">19.0687198638916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2369174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6972618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7503776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8034934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4405307769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2900352478027</t>
+    <t xml:space="preserve">19.2369194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6972599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.750373840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8034954071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4405345916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2900390625</t>
   </si>
   <si>
     <t xml:space="preserve">19.0333080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5110015869141</t>
+    <t xml:space="preserve">18.5109977722168</t>
   </si>
   <si>
     <t xml:space="preserve">18.3516502380371</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">18.7942867279053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9182262420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1129837036133</t>
+    <t xml:space="preserve">18.9182243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1129817962646</t>
   </si>
   <si>
     <t xml:space="preserve">19.4847965240479</t>
@@ -1688,16 +1688,16 @@
     <t xml:space="preserve">19.2015113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2192115783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0952758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.696907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1218338012695</t>
+    <t xml:space="preserve">19.219217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0952777862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6969089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1218357086182</t>
   </si>
   <si>
     <t xml:space="preserve">19.2546253204346</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">18.6791973114014</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6880531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1483917236328</t>
+    <t xml:space="preserve">18.6880550384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1483936309814</t>
   </si>
   <si>
     <t xml:space="preserve">18.9890460968018</t>
@@ -1730,19 +1730,19 @@
     <t xml:space="preserve">18.3428001403809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4313220977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3693561553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7585182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6965503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4840850830078</t>
+    <t xml:space="preserve">18.431324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3693542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7585201263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6965484619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4840869903564</t>
   </si>
   <si>
     <t xml:space="preserve">17.9001617431641</t>
@@ -1751,49 +1751,49 @@
     <t xml:space="preserve">17.417688369751</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6342277526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4527473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9392881393433</t>
+    <t xml:space="preserve">17.0325965881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6342258453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4527435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9392890930176</t>
   </si>
   <si>
     <t xml:space="preserve">15.5719022750854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.434684753418</t>
+    <t xml:space="preserve">15.4346866607666</t>
   </si>
   <si>
     <t xml:space="preserve">15.4656667709351</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7316055297852</t>
+    <t xml:space="preserve">16.7316074371338</t>
   </si>
   <si>
     <t xml:space="preserve">16.2712650299072</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7666625976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2133655548096</t>
+    <t xml:space="preserve">15.766658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2133693695068</t>
   </si>
   <si>
     <t xml:space="preserve">15.1735305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6777791976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2262907028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7840118408203</t>
+    <t xml:space="preserve">14.6777801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2262916564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7840127944946</t>
   </si>
   <si>
     <t xml:space="preserve">14.6290893554688</t>
@@ -1802,67 +1802,67 @@
     <t xml:space="preserve">14.9743452072144</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0717220306396</t>
+    <t xml:space="preserve">15.071722984314</t>
   </si>
   <si>
     <t xml:space="preserve">15.1912355422974</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7179718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2933940887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8596172332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0986347198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.103063583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7755126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4169816970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7887945175171</t>
+    <t xml:space="preserve">15.7179698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2933979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171552658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8596153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0986366271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1030654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7755146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4169797897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7887897491455</t>
   </si>
   <si>
     <t xml:space="preserve">15.4833755493164</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6910562515259</t>
+    <t xml:space="preserve">14.6910581588745</t>
   </si>
   <si>
     <t xml:space="preserve">14.2882595062256</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2041606903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943138122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9739904403687</t>
+    <t xml:space="preserve">14.2041597366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9739894866943</t>
   </si>
   <si>
     <t xml:space="preserve">13.8766098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0802211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9916944503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7880821228027</t>
+    <t xml:space="preserve">14.0802221298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9916954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7880830764771</t>
   </si>
   <si>
     <t xml:space="preserve">13.6243076324463</t>
@@ -1877,43 +1877,43 @@
     <t xml:space="preserve">15.0451669692993</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4254779815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1112060546875</t>
+    <t xml:space="preserve">14.4254760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1112051010132</t>
   </si>
   <si>
     <t xml:space="preserve">13.4959440231323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3675804138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2524938583374</t>
+    <t xml:space="preserve">13.3675785064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2524948120117</t>
   </si>
   <si>
     <t xml:space="preserve">14.0669431686401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7707328796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8415536880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.695484161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.651219367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8946714401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0628709793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8813905715942</t>
+    <t xml:space="preserve">14.7707319259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8415546417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6954851150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6512203216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8946704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0628719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8813915252686</t>
   </si>
   <si>
     <t xml:space="preserve">14.8282737731934</t>
@@ -1922,25 +1922,25 @@
     <t xml:space="preserve">14.9345083236694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4479646682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7131900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558246612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2886161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6958408355713</t>
+    <t xml:space="preserve">15.4479627609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.713191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558265686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2886171340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.695837020874</t>
   </si>
   <si>
     <t xml:space="preserve">16.3155307769775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4129104614258</t>
+    <t xml:space="preserve">16.4129085540771</t>
   </si>
   <si>
     <t xml:space="preserve">16.1163425445557</t>
@@ -1949,25 +1949,25 @@
     <t xml:space="preserve">16.0145359039307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8020706176758</t>
+    <t xml:space="preserve">15.8020725250244</t>
   </si>
   <si>
     <t xml:space="preserve">16.1340484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2358531951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.479305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4748802185059</t>
+    <t xml:space="preserve">16.2358551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4793033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4748783111572</t>
   </si>
   <si>
     <t xml:space="preserve">16.3376617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2181491851807</t>
+    <t xml:space="preserve">16.2181510925293</t>
   </si>
   <si>
     <t xml:space="preserve">16.2889709472656</t>
@@ -1976,40 +1976,40 @@
     <t xml:space="preserve">16.5811080932617</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5412712097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7758712768555</t>
+    <t xml:space="preserve">16.5412731170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7758693695068</t>
   </si>
   <si>
     <t xml:space="preserve">16.4881553649902</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7935733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6297988891602</t>
+    <t xml:space="preserve">16.7935752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6298007965088</t>
   </si>
   <si>
     <t xml:space="preserve">16.9263668060303</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9481401443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9304361343384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9614219665527</t>
+    <t xml:space="preserve">15.9481420516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9304370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9614210128784</t>
   </si>
   <si>
     <t xml:space="preserve">16.5279960632324</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5368461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6784896850586</t>
+    <t xml:space="preserve">16.5368480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.67848777771</t>
   </si>
   <si>
     <t xml:space="preserve">16.5855369567871</t>
@@ -2018,46 +2018,46 @@
     <t xml:space="preserve">16.7138996124268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1292657852173</t>
+    <t xml:space="preserve">15.1292667388916</t>
   </si>
   <si>
     <t xml:space="preserve">15.5763263702393</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8197784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0101127624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8906011581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8463335037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3992757797241</t>
+    <t xml:space="preserve">15.8197774887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0101070404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8905973434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8463344573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3992738723755</t>
   </si>
   <si>
     <t xml:space="preserve">15.293041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9610681533813</t>
+    <t xml:space="preserve">14.9610662460327</t>
   </si>
   <si>
     <t xml:space="preserve">14.9876232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">14.885817527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3767881393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4874467849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6069583892822</t>
+    <t xml:space="preserve">14.8858194351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3767871856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4874458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6069564819336</t>
   </si>
   <si>
     <t xml:space="preserve">14.5626955032349</t>
@@ -2069,97 +2069,97 @@
     <t xml:space="preserve">15.4125537872314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2222204208374</t>
+    <t xml:space="preserve">15.2222194671631</t>
   </si>
   <si>
     <t xml:space="preserve">15.0540189743042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9212284088135</t>
+    <t xml:space="preserve">14.9212293624878</t>
   </si>
   <si>
     <t xml:space="preserve">14.6423692703247</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9300813674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.859260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1868095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0230340957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9477872848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476089477539</t>
+    <t xml:space="preserve">14.9300804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8592596054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1868104934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0230321884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9477844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476099014282</t>
   </si>
   <si>
     <t xml:space="preserve">13.2436408996582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5534858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6552934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.642014503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1997337341309</t>
+    <t xml:space="preserve">13.5534868240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6552925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6420125961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1997356414795</t>
   </si>
   <si>
     <t xml:space="preserve">14.4564619064331</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4431819915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6822061538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8459815979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.217794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0495929718018</t>
+    <t xml:space="preserve">14.4431829452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.682204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8459806442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2177925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0495920181274</t>
   </si>
   <si>
     <t xml:space="preserve">15.2089414596558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0318880081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1823816299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.496298789978</t>
+    <t xml:space="preserve">15.031886100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1823835372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4962997436523</t>
   </si>
   <si>
     <t xml:space="preserve">14.1820287704468</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2000885009766</t>
+    <t xml:space="preserve">15.2000904083252</t>
   </si>
   <si>
     <t xml:space="preserve">15.1381216049194</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3151741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3063220977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6467943191528</t>
+    <t xml:space="preserve">15.3151712417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.306321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6467933654785</t>
   </si>
   <si>
     <t xml:space="preserve">14.3723611831665</t>
@@ -2168,28 +2168,28 @@
     <t xml:space="preserve">13.8589038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7748031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.597749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7792301177979</t>
+    <t xml:space="preserve">13.7748050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5977487564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7792291641235</t>
   </si>
   <si>
     <t xml:space="preserve">13.5888967514038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6774225234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2170839309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5313529968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3502292633057</t>
+    <t xml:space="preserve">13.6774234771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2170848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5313549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3502283096313</t>
   </si>
   <si>
     <t xml:space="preserve">14.3192443847656</t>
@@ -2198,67 +2198,67 @@
     <t xml:space="preserve">14.2705554962158</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353219985962</t>
+    <t xml:space="preserve">14.6999101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353229522705</t>
   </si>
   <si>
     <t xml:space="preserve">14.9256553649902</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6600742340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7486009597778</t>
+    <t xml:space="preserve">14.6600732803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7486000061035</t>
   </si>
   <si>
     <t xml:space="preserve">14.9079494476318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2266473770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5807542800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.91273021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0942134857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8584632873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9808712005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675327301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2302188873291</t>
+    <t xml:space="preserve">15.2266454696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.580756187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9127311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0942115783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8584642410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9808731079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675317764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2302207946777</t>
   </si>
   <si>
     <t xml:space="preserve">16.4568977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5838413238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.592903137207</t>
+    <t xml:space="preserve">16.5838375091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5929050445557</t>
   </si>
   <si>
     <t xml:space="preserve">16.66090965271</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7243804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4115600585938</t>
+    <t xml:space="preserve">16.7243785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7425155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4115619659424</t>
   </si>
   <si>
     <t xml:space="preserve">16.6427764892578</t>
@@ -2276,22 +2276,22 @@
     <t xml:space="preserve">17.309211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4542865753174</t>
+    <t xml:space="preserve">17.454288482666</t>
   </si>
   <si>
     <t xml:space="preserve">16.9646606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9555931091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0462627410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0436496734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0935211181641</t>
+    <t xml:space="preserve">16.9555912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0462646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0436515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0935192108154</t>
   </si>
   <si>
     <t xml:space="preserve">18.1116561889648</t>
@@ -2303,22 +2303,22 @@
     <t xml:space="preserve">17.1414699554443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7833137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9283885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5268249511719</t>
+    <t xml:space="preserve">16.7833156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9283905029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5268230438232</t>
   </si>
   <si>
     <t xml:space="preserve">17.1505393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.996395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8875865936279</t>
+    <t xml:space="preserve">16.9963970184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8875885009766</t>
   </si>
   <si>
     <t xml:space="preserve">16.9601249694824</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">17.3726787567139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7787837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7923812866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7017135620117</t>
+    <t xml:space="preserve">16.7787818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7923831939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7017116546631</t>
   </si>
   <si>
     <t xml:space="preserve">16.0307426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0715446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6473083496094</t>
+    <t xml:space="preserve">16.0715427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.647310256958</t>
   </si>
   <si>
     <t xml:space="preserve">16.8150501251221</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">17.2774753570557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2276077270508</t>
+    <t xml:space="preserve">17.2276058197021</t>
   </si>
   <si>
     <t xml:space="preserve">18.0209827423096</t>
@@ -2372,34 +2372,34 @@
     <t xml:space="preserve">18.0481853485107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0073852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2068614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7508888244629</t>
+    <t xml:space="preserve">18.0073833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.206859588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7508907318115</t>
   </si>
   <si>
     <t xml:space="preserve">18.2975311279297</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3519325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2884654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4244728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9775695800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.050106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0410404205322</t>
+    <t xml:space="preserve">18.3519344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2884674072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4244709014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9775676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0501079559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.041036605835</t>
   </si>
   <si>
     <t xml:space="preserve">18.3156661987305</t>
@@ -2408,22 +2408,22 @@
     <t xml:space="preserve">17.7716369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0617847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8804416656494</t>
+    <t xml:space="preserve">18.0617866516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.880443572998</t>
   </si>
   <si>
     <t xml:space="preserve">18.0889892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9756469726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7353668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7217674255371</t>
+    <t xml:space="preserve">17.9756488800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7353687286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7217655181885</t>
   </si>
   <si>
     <t xml:space="preserve">17.8623065948486</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">17.7126998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0598640441895</t>
+    <t xml:space="preserve">17.0598659515381</t>
   </si>
   <si>
     <t xml:space="preserve">17.0507984161377</t>
@@ -2441,13 +2441,13 @@
     <t xml:space="preserve">16.973726272583</t>
   </si>
   <si>
-    <t xml:space="preserve">17.096134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8921203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2366733551025</t>
+    <t xml:space="preserve">17.0961322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8921222686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2366752624512</t>
   </si>
   <si>
     <t xml:space="preserve">17.7671012878418</t>
@@ -2456,13 +2456,13 @@
     <t xml:space="preserve">18.0753841400146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4698066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5060787200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7236881256104</t>
+    <t xml:space="preserve">18.4698085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5060749053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7236862182617</t>
   </si>
   <si>
     <t xml:space="preserve">18.71462059021</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">18.1887245178223</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5786151885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.959436416626</t>
+    <t xml:space="preserve">18.57861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9594345092773</t>
   </si>
   <si>
     <t xml:space="preserve">18.7690238952637</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">18.7418251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7780914306641</t>
+    <t xml:space="preserve">18.7780895233154</t>
   </si>
   <si>
     <t xml:space="preserve">19.2223815917969</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">19.521598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8117485046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4490623474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3130531311035</t>
+    <t xml:space="preserve">19.81174659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4490604400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3130550384521</t>
   </si>
   <si>
     <t xml:space="preserve">18.7962265014648</t>
@@ -2528,25 +2528,25 @@
     <t xml:space="preserve">18.0391178131104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9892501831055</t>
+    <t xml:space="preserve">17.9892482757568</t>
   </si>
   <si>
     <t xml:space="preserve">18.0663185119629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8596954345703</t>
+    <t xml:space="preserve">18.8596973419189</t>
   </si>
   <si>
     <t xml:space="preserve">18.9050312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7599582672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3791370391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4399929046631</t>
+    <t xml:space="preserve">18.7599563598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3791351318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4399948120117</t>
   </si>
   <si>
     <t xml:space="preserve">18.9685020446777</t>
@@ -2555,28 +2555,28 @@
     <t xml:space="preserve">19.0863742828369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5760021209717</t>
+    <t xml:space="preserve">19.195182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.576000213623</t>
   </si>
   <si>
     <t xml:space="preserve">19.6394691467285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4218578338623</t>
+    <t xml:space="preserve">19.4218616485596</t>
   </si>
   <si>
     <t xml:space="preserve">19.7392101287842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9477558135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0021553039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8661499023438</t>
+    <t xml:space="preserve">19.94775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0021572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8661518096924</t>
   </si>
   <si>
     <t xml:space="preserve">19.485330581665</t>
@@ -2591,10 +2591,10 @@
     <t xml:space="preserve">19.1679801940918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3221206665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0319728851318</t>
+    <t xml:space="preserve">19.3221225738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0319690704346</t>
   </si>
   <si>
     <t xml:space="preserve">19.2949199676514</t>
@@ -2615,22 +2615,22 @@
     <t xml:space="preserve">18.9957046508789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6602191925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.533275604248</t>
+    <t xml:space="preserve">18.6602172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5332794189453</t>
   </si>
   <si>
     <t xml:space="preserve">18.9322319030762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4762630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0474967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0112247467041</t>
+    <t xml:space="preserve">19.4762649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.047492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0112266540527</t>
   </si>
   <si>
     <t xml:space="preserve">19.9658908843994</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">20.3376445770264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9088745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3259620666504</t>
+    <t xml:space="preserve">20.9088726043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.325963973999</t>
   </si>
   <si>
     <t xml:space="preserve">21.5526428222656</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">21.697717666626</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8337230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9814109802246</t>
+    <t xml:space="preserve">22.4049530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8337249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9814128875732</t>
   </si>
   <si>
     <t xml:space="preserve">19.9930896759033</t>
@@ -2672,49 +2672,49 @@
     <t xml:space="preserve">19.3039875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.385591506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4607410430908</t>
+    <t xml:space="preserve">19.3855895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4607429504395</t>
   </si>
   <si>
     <t xml:space="preserve">18.6511497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">18.623950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0300521850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8195838928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4685754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8112077713013</t>
+    <t xml:space="preserve">18.6239490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.03005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8195858001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4685773849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6842679977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.811206817627</t>
   </si>
   <si>
     <t xml:space="preserve">12.653223991394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.741283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7775506973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3170480728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7341384887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1648283004761</t>
+    <t xml:space="preserve">13.7412824630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7775526046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3170471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7341375350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1648273468018</t>
   </si>
   <si>
     <t xml:space="preserve">13.6914138793945</t>
@@ -2723,67 +2723,67 @@
     <t xml:space="preserve">14.090368270874</t>
   </si>
   <si>
-    <t xml:space="preserve">15.269100189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0242881774902</t>
+    <t xml:space="preserve">15.2691011428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0242862701416</t>
   </si>
   <si>
     <t xml:space="preserve">15.0061521530151</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2354440689087</t>
+    <t xml:space="preserve">14.2354431152344</t>
   </si>
   <si>
     <t xml:space="preserve">13.8863573074341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.238055229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4783344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5327377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9660406112671</t>
+    <t xml:space="preserve">13.2380561828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4783353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5327386856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9660415649414</t>
   </si>
   <si>
     <t xml:space="preserve">13.4511337280273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8092851638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1901073455811</t>
+    <t xml:space="preserve">13.8092861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1901063919067</t>
   </si>
   <si>
     <t xml:space="preserve">14.2581119537354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3695287704468</t>
+    <t xml:space="preserve">13.3695297241211</t>
   </si>
   <si>
     <t xml:space="preserve">13.8727579116821</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9634275436401</t>
+    <t xml:space="preserve">13.9634284973145</t>
   </si>
   <si>
     <t xml:space="preserve">13.7820854187012</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2943801879883</t>
+    <t xml:space="preserve">14.2943811416626</t>
   </si>
   <si>
     <t xml:space="preserve">14.448522567749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5346593856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1512241363525</t>
+    <t xml:space="preserve">14.5346612930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1512269973755</t>
   </si>
   <si>
     <t xml:space="preserve">15.3643045425415</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">15.6544542312622</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5683145523071</t>
+    <t xml:space="preserve">15.5683155059814</t>
   </si>
   <si>
     <t xml:space="preserve">15.3461694717407</t>
@@ -2801,10 +2801,10 @@
     <t xml:space="preserve">16.6291732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7768611907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7904634475708</t>
+    <t xml:space="preserve">15.7768602371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7904624938965</t>
   </si>
   <si>
     <t xml:space="preserve">16.4478302001953</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">16.4030952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8813438415527</t>
+    <t xml:space="preserve">16.8813457489014</t>
   </si>
   <si>
     <t xml:space="preserve">16.7066020965576</t>
@@ -2834,52 +2834,52 @@
     <t xml:space="preserve">17.2906188964844</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6998901367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9896011352539</t>
+    <t xml:space="preserve">17.699893951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9896030426025</t>
   </si>
   <si>
     <t xml:space="preserve">17.4515686035156</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6585063934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6079196929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3549976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6309127807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9850025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8884353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6333999633789</t>
+    <t xml:space="preserve">17.658504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6079216003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3549995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6309108734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9850044250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8884334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6334018707275</t>
   </si>
   <si>
     <t xml:space="preserve">18.752965927124</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8081474304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6701889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7090892791748</t>
+    <t xml:space="preserve">18.8081493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6701908111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7090854644775</t>
   </si>
   <si>
     <t xml:space="preserve">17.6631031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4745616912842</t>
+    <t xml:space="preserve">17.4745635986328</t>
   </si>
   <si>
     <t xml:space="preserve">18.3482913970947</t>
@@ -2897,25 +2897,25 @@
     <t xml:space="preserve">18.8173427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2220191955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7161769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9644985198975</t>
+    <t xml:space="preserve">19.222017288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7161731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9645004272461</t>
   </si>
   <si>
     <t xml:space="preserve">18.7897510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0104827880859</t>
+    <t xml:space="preserve">19.0104846954346</t>
   </si>
   <si>
     <t xml:space="preserve">19.0748634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5715103149414</t>
+    <t xml:space="preserve">19.5715084075928</t>
   </si>
   <si>
     <t xml:space="preserve">19.3507766723633</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">19.6542854309082</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278614044189</t>
+    <t xml:space="preserve">19.7278633117676</t>
   </si>
   <si>
     <t xml:space="preserve">19.930196762085</t>
@@ -2939,67 +2939,67 @@
     <t xml:space="preserve">19.4703407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0957450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2704925537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3256740570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1534156799316</t>
+    <t xml:space="preserve">20.0957469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2704944610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3256759643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1534175872803</t>
   </si>
   <si>
     <t xml:space="preserve">20.960277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3281631469727</t>
+    <t xml:space="preserve">21.3281650543213</t>
   </si>
   <si>
     <t xml:space="preserve">21.0154609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0430526733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4912242889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2245063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2337036132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8934059143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8223209381104</t>
+    <t xml:space="preserve">21.0430507659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4912223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2245044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2337017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8934078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8223190307617</t>
   </si>
   <si>
     <t xml:space="preserve">20.4176464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3808574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.206111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5556049346924</t>
+    <t xml:space="preserve">20.3808555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2061100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5556011199951</t>
   </si>
   <si>
     <t xml:space="preserve">20.8775024414062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0614452362061</t>
+    <t xml:space="preserve">21.0614471435547</t>
   </si>
   <si>
     <t xml:space="preserve">20.7303485870361</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7579402923584</t>
+    <t xml:space="preserve">20.7579383850098</t>
   </si>
   <si>
     <t xml:space="preserve">20.7395439147949</t>
@@ -3014,46 +3014,46 @@
     <t xml:space="preserve">21.3649501800537</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4201335906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4937114715576</t>
+    <t xml:space="preserve">21.4201354980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4937133789062</t>
   </si>
   <si>
     <t xml:space="preserve">21.944372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5580902099609</t>
+    <t xml:space="preserve">21.5580940246582</t>
   </si>
   <si>
     <t xml:space="preserve">21.5213012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0271472930908</t>
+    <t xml:space="preserve">22.0271453857422</t>
   </si>
   <si>
     <t xml:space="preserve">21.604076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8156089782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4109382629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7420330047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1191158294678</t>
+    <t xml:space="preserve">21.8156108856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4109363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7420310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1191177368164</t>
   </si>
   <si>
     <t xml:space="preserve">22.5145931243896</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6341552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5421848297119</t>
+    <t xml:space="preserve">22.6341590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5421867370605</t>
   </si>
   <si>
     <t xml:space="preserve">22.6433544158936</t>
@@ -3062,25 +3062,25 @@
     <t xml:space="preserve">22.3674392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4410171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2294845581055</t>
+    <t xml:space="preserve">22.4410152435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2294807434082</t>
   </si>
   <si>
     <t xml:space="preserve">22.6709442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4870014190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9008712768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8732795715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8456935882568</t>
+    <t xml:space="preserve">22.487003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9008731842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8732814788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8456916809082</t>
   </si>
   <si>
     <t xml:space="preserve">23.2135753631592</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">23.6550369262695</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5262794494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5722637176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0045299530029</t>
+    <t xml:space="preserve">23.5262775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5722618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0045280456543</t>
   </si>
   <si>
     <t xml:space="preserve">23.7194194793701</t>
@@ -3110,46 +3110,46 @@
     <t xml:space="preserve">24.3264312744141</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8757705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1700782775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5998554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6525478363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7261257171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9560565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1926937103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6684551239014</t>
+    <t xml:space="preserve">23.8757667541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1700801849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5998573303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6525497436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7261276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1926956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.66845703125</t>
   </si>
   <si>
     <t xml:space="preserve">21.1994018554688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6500625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.466121673584</t>
+    <t xml:space="preserve">21.6500644683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4661197662354</t>
   </si>
   <si>
     <t xml:space="preserve">22.0823287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5881690979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.041316986084</t>
+    <t xml:space="preserve">22.5881671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0413188934326</t>
   </si>
   <si>
     <t xml:space="preserve">23.0112400054932</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">23.121603012085</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6274471282959</t>
+    <t xml:space="preserve">23.6274490356445</t>
   </si>
   <si>
     <t xml:space="preserve">24.2988376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9677391052246</t>
+    <t xml:space="preserve">23.9677410125732</t>
   </si>
   <si>
     <t xml:space="preserve">23.3607292175293</t>
@@ -3173,55 +3173,55 @@
     <t xml:space="preserve">23.8665733337402</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9217548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9033622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4459934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0965003967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7402992248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2277488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8966503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4092044830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5471611022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0622024536133</t>
+    <t xml:space="preserve">23.9217567443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9033603668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4459915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0965023040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7403011322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2277526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8966522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4092063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5471591949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0622005462646</t>
   </si>
   <si>
     <t xml:space="preserve">24.5655536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6391334533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6023426055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8874549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3105239868164</t>
+    <t xml:space="preserve">24.6391315460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6023445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8874568939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3105220794678</t>
   </si>
   <si>
     <t xml:space="preserve">25.5680408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0805931091309</t>
+    <t xml:space="preserve">25.0805950164795</t>
   </si>
   <si>
     <t xml:space="preserve">25.3841018676758</t>
@@ -3233,28 +3233,28 @@
     <t xml:space="preserve">25.3749046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7151966094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9359283447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6257133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5613346099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7452754974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8740348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0119972229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5546245574951</t>
+    <t xml:space="preserve">25.7151947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9359302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6257152557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5613327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7452793121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8740367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0119953155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5546226501465</t>
   </si>
   <si>
     <t xml:space="preserve">28.2811985015869</t>
@@ -3269,19 +3269,19 @@
     <t xml:space="preserve">26.3957862854004</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5521354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8715476989746</t>
+    <t xml:space="preserve">26.5521373748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8715496063232</t>
   </si>
   <si>
     <t xml:space="preserve">26.1106739044189</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8439559936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0278987884521</t>
+    <t xml:space="preserve">25.843957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0279006958008</t>
   </si>
   <si>
     <t xml:space="preserve">25.7519874572754</t>
@@ -3299,19 +3299,19 @@
     <t xml:space="preserve">25.1449756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5011730194092</t>
+    <t xml:space="preserve">24.5011749267578</t>
   </si>
   <si>
     <t xml:space="preserve">25.0346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">25.236946105957</t>
+    <t xml:space="preserve">25.2369480133057</t>
   </si>
   <si>
     <t xml:space="preserve">25.6968021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0462951660156</t>
+    <t xml:space="preserve">26.046293258667</t>
   </si>
   <si>
     <t xml:space="preserve">25.9175338745117</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">26.2854194641113</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9267330169678</t>
+    <t xml:space="preserve">25.9267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">25.9083366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">26.119873046875</t>
+    <t xml:space="preserve">26.1198711395264</t>
   </si>
   <si>
     <t xml:space="preserve">26.0003108978271</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">25.9635200500488</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6600112915039</t>
+    <t xml:space="preserve">25.6600151062012</t>
   </si>
   <si>
     <t xml:space="preserve">25.0530033111572</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">24.5563583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5195713043213</t>
+    <t xml:space="preserve">24.5195693969727</t>
   </si>
   <si>
     <t xml:space="preserve">25.0162162780762</t>
@@ -3365,22 +3365,22 @@
     <t xml:space="preserve">24.9058494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0137271881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2712478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2001552581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2620468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.673433303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5446720123291</t>
+    <t xml:space="preserve">24.0137252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2712459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2001571655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2620487213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6734313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5446739196777</t>
   </si>
   <si>
     <t xml:space="preserve">23.6918258666992</t>
@@ -3392,43 +3392,43 @@
     <t xml:space="preserve">23.3055477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5170783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7838001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1056976318359</t>
+    <t xml:space="preserve">23.5170803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7837982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1056957244873</t>
   </si>
   <si>
     <t xml:space="preserve">24.1516857147217</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5287666320801</t>
+    <t xml:space="preserve">24.5287685394287</t>
   </si>
   <si>
     <t xml:space="preserve">24.8138771057129</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8322734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9886245727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4852695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.770378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6416187286377</t>
+    <t xml:space="preserve">24.8322715759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9886207580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4852676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7703819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6416206359863</t>
   </si>
   <si>
     <t xml:space="preserve">24.8414688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6943168640137</t>
+    <t xml:space="preserve">24.694314956665</t>
   </si>
   <si>
     <t xml:space="preserve">25.1081867218018</t>
@@ -3437,28 +3437,28 @@
     <t xml:space="preserve">24.9518337249756</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3381156921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4919776916504</t>
+    <t xml:space="preserve">25.3381118774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4919757843018</t>
   </si>
   <si>
     <t xml:space="preserve">24.5379638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4367942810059</t>
+    <t xml:space="preserve">24.4367923736572</t>
   </si>
   <si>
     <t xml:space="preserve">23.9861354827881</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9585418701172</t>
+    <t xml:space="preserve">23.9585437774658</t>
   </si>
   <si>
     <t xml:space="preserve">24.4000072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">23.949348449707</t>
+    <t xml:space="preserve">23.9493465423584</t>
   </si>
   <si>
     <t xml:space="preserve">24.7954845428467</t>
@@ -3467,28 +3467,28 @@
     <t xml:space="preserve">24.2252597808838</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3197193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4693641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4325733184814</t>
+    <t xml:space="preserve">25.3197231292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4693622589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4325752258301</t>
   </si>
   <si>
     <t xml:space="preserve">26.2762222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3323879241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5476894378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1826133728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1919727325439</t>
+    <t xml:space="preserve">26.332389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5476913452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1826114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1919746398926</t>
   </si>
   <si>
     <t xml:space="preserve">26.5196075439453</t>
@@ -3497,16 +3497,16 @@
     <t xml:space="preserve">26.4259967803955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6693840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753223419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3901767730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5867595672607</t>
+    <t xml:space="preserve">26.6693820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753242492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3901786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5867576599121</t>
   </si>
   <si>
     <t xml:space="preserve">27.7926998138428</t>
@@ -3515,22 +3515,22 @@
     <t xml:space="preserve">27.7084503173828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8769474029541</t>
+    <t xml:space="preserve">27.8769454956055</t>
   </si>
   <si>
     <t xml:space="preserve">27.3340110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2872047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3808174133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.699089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1935958862305</t>
+    <t xml:space="preserve">27.2872066497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3808155059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6990871429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1935977935791</t>
   </si>
   <si>
     <t xml:space="preserve">27.1655158996582</t>
@@ -3539,13 +3539,13 @@
     <t xml:space="preserve">27.9237518310547</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8395023345947</t>
+    <t xml:space="preserve">27.8395042419434</t>
   </si>
   <si>
     <t xml:space="preserve">27.802059173584</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4011611938477</t>
+    <t xml:space="preserve">28.401159286499</t>
   </si>
   <si>
     <t xml:space="preserve">28.5602970123291</t>
@@ -3554,19 +3554,19 @@
     <t xml:space="preserve">28.3075504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6819915771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2981910705566</t>
+    <t xml:space="preserve">28.6819896697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.298189163208</t>
   </si>
   <si>
     <t xml:space="preserve">28.3169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5041332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3824367523193</t>
+    <t xml:space="preserve">28.5041351318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.382438659668</t>
   </si>
   <si>
     <t xml:space="preserve">28.4479656219482</t>
@@ -3578,19 +3578,19 @@
     <t xml:space="preserve">27.9799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5696582794189</t>
+    <t xml:space="preserve">28.5696601867676</t>
   </si>
   <si>
     <t xml:space="preserve">28.8317642211914</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7943229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6913509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.419885635376</t>
+    <t xml:space="preserve">28.7943210601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.691349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4198837280273</t>
   </si>
   <si>
     <t xml:space="preserve">28.4760494232178</t>
@@ -3602,28 +3602,28 @@
     <t xml:space="preserve">28.1203327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8301410675049</t>
+    <t xml:space="preserve">27.8301429748535</t>
   </si>
   <si>
     <t xml:space="preserve">27.989278793335</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1671371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2701110839844</t>
+    <t xml:space="preserve">28.1671352386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2701072692871</t>
   </si>
   <si>
     <t xml:space="preserve">28.1390533447266</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2888298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4854106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3637161254883</t>
+    <t xml:space="preserve">28.2888317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.485408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3637180328369</t>
   </si>
   <si>
     <t xml:space="preserve">28.7849617004395</t>
@@ -3635,55 +3635,55 @@
     <t xml:space="preserve">29.0002632141113</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3934230804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2359085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3201599121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1797466278076</t>
+    <t xml:space="preserve">29.3934211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2359104156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3201580047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.179744720459</t>
   </si>
   <si>
     <t xml:space="preserve">29.8146667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">29.992525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9550800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8989162445068</t>
+    <t xml:space="preserve">29.9925270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9550819396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8989143371582</t>
   </si>
   <si>
     <t xml:space="preserve">29.5619220733643</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5057563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7585010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8053035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5806446075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8708343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.908275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8333911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2171878814697</t>
+    <t xml:space="preserve">29.5057544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7585029602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.805305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5806407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8708324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9082775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8333892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2171859741211</t>
   </si>
   <si>
     <t xml:space="preserve">30.4044075012207</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">30.385684967041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.863094329834</t>
+    <t xml:space="preserve">30.8630962371826</t>
   </si>
   <si>
     <t xml:space="preserve">30.8537330627441</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0018863677979</t>
+    <t xml:space="preserve">30.0018844604492</t>
   </si>
   <si>
     <t xml:space="preserve">30.5448246002197</t>
@@ -3710,34 +3710,34 @@
     <t xml:space="preserve">30.4699325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">30.713321685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1142139434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1891059875488</t>
+    <t xml:space="preserve">30.7133178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1142158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1891040802002</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3185367584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.029972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3482398986816</t>
+    <t xml:space="preserve">29.3185348510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0299682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.348237991333</t>
   </si>
   <si>
     <t xml:space="preserve">29.6742534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9534606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8130435943604</t>
+    <t xml:space="preserve">28.9534587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.813045501709</t>
   </si>
   <si>
     <t xml:space="preserve">28.2420253753662</t>
@@ -3749,13 +3749,13 @@
     <t xml:space="preserve">27.4837875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0267219543457</t>
+    <t xml:space="preserve">28.0267238616943</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.661642074585</t>
+    <t xml:space="preserve">27.6616439819336</t>
   </si>
   <si>
     <t xml:space="preserve">28.6445465087891</t>
@@ -3764,109 +3764,109 @@
     <t xml:space="preserve">29.2249240875244</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2717304229736</t>
+    <t xml:space="preserve">29.2717323303223</t>
   </si>
   <si>
     <t xml:space="preserve">29.2623691558838</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5244789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7304172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1610221862793</t>
+    <t xml:space="preserve">29.5244770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7304191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1610240936279</t>
   </si>
   <si>
     <t xml:space="preserve">30.4792957305908</t>
   </si>
   <si>
-    <t xml:space="preserve">30.591625213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.36696434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6384315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6103496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3030567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9286231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1626472473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6681385040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8553581237793</t>
+    <t xml:space="preserve">30.5916290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3669624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6384296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6103477478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7694835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3030586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9286212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1626453399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.668140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8553562164307</t>
   </si>
   <si>
     <t xml:space="preserve">31.4341163635254</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1813659667969</t>
+    <t xml:space="preserve">31.1813716888428</t>
   </si>
   <si>
     <t xml:space="preserve">31.2749767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8179168701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9302406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8101768493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.763370513916</t>
+    <t xml:space="preserve">31.8179130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9302444458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8101692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7633666992188</t>
   </si>
   <si>
     <t xml:space="preserve">32.6416778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9489688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6962184906006</t>
+    <t xml:space="preserve">31.9489707946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6962203979492</t>
   </si>
   <si>
     <t xml:space="preserve">32.1081008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6945953369141</t>
+    <t xml:space="preserve">30.6945991516113</t>
   </si>
   <si>
     <t xml:space="preserve">31.3124217987061</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7320461273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5822658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8911800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7523860931396</t>
+    <t xml:space="preserve">30.7320423126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5822639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8911762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.752384185791</t>
   </si>
   <si>
     <t xml:space="preserve">30.9473457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7039585113525</t>
+    <t xml:space="preserve">30.7039566040039</t>
   </si>
   <si>
     <t xml:space="preserve">30.3576030731201</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">30.0861339569092</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1516609191895</t>
+    <t xml:space="preserve">30.1516590118408</t>
   </si>
   <si>
     <t xml:space="preserve">29.5525588989258</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">29.702335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7507610321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9754276275635</t>
+    <t xml:space="preserve">30.7507629394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9754257202148</t>
   </si>
   <si>
     <t xml:space="preserve">30.9379806518555</t>
@@ -3896,46 +3896,46 @@
     <t xml:space="preserve">31.069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9567050933838</t>
+    <t xml:space="preserve">30.9567031860352</t>
   </si>
   <si>
     <t xml:space="preserve">30.9941501617432</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9660663604736</t>
+    <t xml:space="preserve">30.9660682678223</t>
   </si>
   <si>
     <t xml:space="preserve">31.2936992645264</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2468948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2656173706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6026096343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7804718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3779468536377</t>
+    <t xml:space="preserve">31.2468929290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2656192779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.602611541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7804679870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3779487609863</t>
   </si>
   <si>
     <t xml:space="preserve">30.5073757171631</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9721794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6335639953613</t>
+    <t xml:space="preserve">28.9721813201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6335620880127</t>
   </si>
   <si>
     <t xml:space="preserve">27.0063800811768</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0454425811768</t>
+    <t xml:space="preserve">28.0454444885254</t>
   </si>
   <si>
     <t xml:space="preserve">26.8378810882568</t>
@@ -3944,28 +3944,28 @@
     <t xml:space="preserve">28.2045803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0548076629639</t>
+    <t xml:space="preserve">28.0548057556152</t>
   </si>
   <si>
     <t xml:space="preserve">27.118709564209</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9298686981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0421962738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8191585540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5664100646973</t>
+    <t xml:space="preserve">25.9298667907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.042200088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8191566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5664119720459</t>
   </si>
   <si>
     <t xml:space="preserve">26.248140335083</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7800922393799</t>
+    <t xml:space="preserve">25.7800941467285</t>
   </si>
   <si>
     <t xml:space="preserve">26.5102462768555</t>
@@ -3977,31 +3977,31 @@
     <t xml:space="preserve">26.9970169067383</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1264476776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2294178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1077270507812</t>
+    <t xml:space="preserve">26.1264457702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.229419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1077251434326</t>
   </si>
   <si>
     <t xml:space="preserve">27.5399532318115</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5415725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4463405609131</t>
+    <t xml:space="preserve">28.541576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4463424682617</t>
   </si>
   <si>
     <t xml:space="preserve">25.9766712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">27.13743019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9502124786377</t>
+    <t xml:space="preserve">27.1374320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9502105712891</t>
   </si>
   <si>
     <t xml:space="preserve">28.728796005249</t>
@@ -4010,43 +4010,43 @@
     <t xml:space="preserve">27.5961170196533</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8863105773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.625825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7100715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0377082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.121955871582</t>
+    <t xml:space="preserve">27.8863086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6258239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7100734710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0377063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1219577789307</t>
   </si>
   <si>
     <t xml:space="preserve">29.1406764984131</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8598480224609</t>
+    <t xml:space="preserve">28.8598499298096</t>
   </si>
   <si>
     <t xml:space="preserve">28.6071033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2326641082764</t>
+    <t xml:space="preserve">28.2326622009277</t>
   </si>
   <si>
     <t xml:space="preserve">28.8692092895508</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0096244812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.290454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9815406799316</t>
+    <t xml:space="preserve">29.0096225738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2904510498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.981538772583</t>
   </si>
   <si>
     <t xml:space="preserve">29.515115737915</t>
@@ -4058,22 +4058,22 @@
     <t xml:space="preserve">27.0531826019287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5586757659912</t>
+    <t xml:space="preserve">27.5586738586426</t>
   </si>
   <si>
     <t xml:space="preserve">28.8972930908203</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4666900634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4831771850586</t>
+    <t xml:space="preserve">28.4666881561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4831790924072</t>
   </si>
   <si>
     <t xml:space="preserve">29.32204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">28.931209564209</t>
+    <t xml:space="preserve">28.9312076568604</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549480438232</t>
@@ -4091,10 +4091,10 @@
     <t xml:space="preserve">29.7605361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6452312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0265350341797</t>
+    <t xml:space="preserve">28.6452331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0265331268311</t>
   </si>
   <si>
     <t xml:space="preserve">29.045597076416</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">26.7482604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0247058868408</t>
+    <t xml:space="preserve">27.0247020721436</t>
   </si>
   <si>
     <t xml:space="preserve">27.1104965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052722930908</t>
+    <t xml:space="preserve">26.6052742004395</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101306915283</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">26.9675102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">27.215353012085</t>
+    <t xml:space="preserve">27.2153549194336</t>
   </si>
   <si>
     <t xml:space="preserve">27.7682399749756</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">27.8635654449463</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7301082611084</t>
+    <t xml:space="preserve">27.730110168457</t>
   </si>
   <si>
     <t xml:space="preserve">28.2829971313477</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">27.9684238433838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1304759979248</t>
+    <t xml:space="preserve">28.1304779052734</t>
   </si>
   <si>
     <t xml:space="preserve">28.4450492858887</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">26.1667785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5280990600586</t>
+    <t xml:space="preserve">25.52809715271</t>
   </si>
   <si>
     <t xml:space="preserve">25.0133419036865</t>
@@ -4226,22 +4226,22 @@
     <t xml:space="preserve">24.765495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3937282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6987686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3374462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9189300537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1658592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2993183135986</t>
+    <t xml:space="preserve">24.393726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.698766708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3374481201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9189319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1658611297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.29931640625</t>
   </si>
   <si>
     <t xml:space="preserve">25.2230548858643</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">24.9084815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">25.346981048584</t>
+    <t xml:space="preserve">25.3469791412354</t>
   </si>
   <si>
     <t xml:space="preserve">26.2144393920898</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">25.9093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4908847808838</t>
+    <t xml:space="preserve">26.4908828735352</t>
   </si>
   <si>
     <t xml:space="preserve">27.0532989501953</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">27.0437698364258</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6815338134766</t>
+    <t xml:space="preserve">26.6815319061279</t>
   </si>
   <si>
     <t xml:space="preserve">27.2630176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7882232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5031585693359</t>
+    <t xml:space="preserve">28.7882213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5031604766846</t>
   </si>
   <si>
     <t xml:space="preserve">29.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5508213043213</t>
+    <t xml:space="preserve">29.5508232116699</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461486816406</t>
@@ -4301,16 +4301,16 @@
     <t xml:space="preserve">29.9797859191895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8939933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0760269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.705171585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7995853424072</t>
+    <t xml:space="preserve">29.8939952850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0760250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7051696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7995834350586</t>
   </si>
   <si>
     <t xml:space="preserve">31.0283622741699</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">30.4468803405762</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9997673034668</t>
+    <t xml:space="preserve">30.9997653961182</t>
   </si>
   <si>
     <t xml:space="preserve">30.551736831665</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">30.0274486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2371616363525</t>
+    <t xml:space="preserve">30.2371635437012</t>
   </si>
   <si>
     <t xml:space="preserve">30.5993995666504</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">29.5317573547363</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1790542602539</t>
+    <t xml:space="preserve">29.1790561676025</t>
   </si>
   <si>
     <t xml:space="preserve">29.1885871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4554958343506</t>
+    <t xml:space="preserve">29.4554977416992</t>
   </si>
   <si>
     <t xml:space="preserve">30.3610877990723</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">31.0664920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5907802581787</t>
+    <t xml:space="preserve">31.590784072876</t>
   </si>
   <si>
     <t xml:space="preserve">30.5326709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3515529632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.389684677124</t>
+    <t xml:space="preserve">30.3515567779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3896827697754</t>
   </si>
   <si>
     <t xml:space="preserve">30.3038921356201</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">29.874927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2362480163574</t>
+    <t xml:space="preserve">29.2362499237061</t>
   </si>
   <si>
     <t xml:space="preserve">28.0160865783691</t>
@@ -4391,34 +4391,34 @@
     <t xml:space="preserve">28.6166362762451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6738319396973</t>
+    <t xml:space="preserve">28.6738300323486</t>
   </si>
   <si>
     <t xml:space="preserve">28.3020629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">26.986572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2353363037109</t>
+    <t xml:space="preserve">26.9865741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2353343963623</t>
   </si>
   <si>
     <t xml:space="preserve">28.492712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0560455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5126914978027</t>
+    <t xml:space="preserve">30.0560474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5126895904541</t>
   </si>
   <si>
     <t xml:space="preserve">29.7128753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6842784881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2648487091064</t>
+    <t xml:space="preserve">29.6842765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2648468017578</t>
   </si>
   <si>
     <t xml:space="preserve">29.7033424377441</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">29.3983020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7700691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7510051727295</t>
+    <t xml:space="preserve">29.7700710296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7510032653809</t>
   </si>
   <si>
     <t xml:space="preserve">30.5422058105469</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">30.9616355895996</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4945411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6661243438721</t>
+    <t xml:space="preserve">30.4945430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6661262512207</t>
   </si>
   <si>
     <t xml:space="preserve">30.8472461700439</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">31.1236896514893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9434833526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.981616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7242374420166</t>
+    <t xml:space="preserve">31.9434814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9816150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7242336273193</t>
   </si>
   <si>
     <t xml:space="preserve">31.5717163085938</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">30.5231399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9521026611328</t>
+    <t xml:space="preserve">30.9521045684814</t>
   </si>
   <si>
     <t xml:space="preserve">30.5136051177979</t>
@@ -4487,13 +4487,13 @@
     <t xml:space="preserve">32.5535697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6289100646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8853759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3715324401855</t>
+    <t xml:space="preserve">31.6289119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8853778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3715343475342</t>
   </si>
   <si>
     <t xml:space="preserve">30.7709846496582</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">31.0950889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0378971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.476390838623</t>
+    <t xml:space="preserve">31.037899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4763946533203</t>
   </si>
   <si>
     <t xml:space="preserve">32.1913299560547</t>
@@ -4514,19 +4514,19 @@
     <t xml:space="preserve">32.0769424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1055374145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1246070861816</t>
+    <t xml:space="preserve">32.105541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1246032714844</t>
   </si>
   <si>
     <t xml:space="preserve">32.143669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8386287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9244251251221</t>
+    <t xml:space="preserve">31.8386325836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9244213104248</t>
   </si>
   <si>
     <t xml:space="preserve">32.1341361999512</t>
@@ -4538,16 +4538,16 @@
     <t xml:space="preserve">32.8300094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1064491271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.840461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5926170349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9167213439941</t>
+    <t xml:space="preserve">33.1064529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8404579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5926132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9167175292969</t>
   </si>
   <si>
     <t xml:space="preserve">33.9357833862305</t>
@@ -4562,16 +4562,16 @@
     <t xml:space="preserve">33.6116752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4686889648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6021461486816</t>
+    <t xml:space="preserve">33.468692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6021423339844</t>
   </si>
   <si>
     <t xml:space="preserve">33.3161697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5544853210449</t>
+    <t xml:space="preserve">33.5544815063477</t>
   </si>
   <si>
     <t xml:space="preserve">33.6784057617188</t>
@@ -4595,25 +4595,25 @@
     <t xml:space="preserve">32.2866554260254</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9729995727539</t>
+    <t xml:space="preserve">32.9729957580566</t>
   </si>
   <si>
     <t xml:space="preserve">33.373363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9539337158203</t>
+    <t xml:space="preserve">32.953929901123</t>
   </si>
   <si>
     <t xml:space="preserve">33.3638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4114952087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5830764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0311126708984</t>
+    <t xml:space="preserve">33.411491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0311088562012</t>
   </si>
   <si>
     <t xml:space="preserve">34.7937126159668</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">35.0892181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5649299621582</t>
+    <t xml:space="preserve">34.5649261474609</t>
   </si>
   <si>
     <t xml:space="preserve">35.2512702941895</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">35.8804168701172</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5372467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5753746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7469635009766</t>
+    <t xml:space="preserve">35.5372428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5753784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7469596862793</t>
   </si>
   <si>
     <t xml:space="preserve">35.3942604064941</t>
@@ -4649,7 +4649,7 @@
     <t xml:space="preserve">35.6516380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1091995239258</t>
+    <t xml:space="preserve">36.109203338623</t>
   </si>
   <si>
     <t xml:space="preserve">35.9852752685547</t>
@@ -4661,13 +4661,13 @@
     <t xml:space="preserve">35.2036094665527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5944404602051</t>
+    <t xml:space="preserve">35.5944442749023</t>
   </si>
   <si>
     <t xml:space="preserve">34.9843635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5563125610352</t>
+    <t xml:space="preserve">35.5563087463379</t>
   </si>
   <si>
     <t xml:space="preserve">35.3370628356934</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">35.8327560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1568603515625</t>
+    <t xml:space="preserve">36.1568641662598</t>
   </si>
   <si>
     <t xml:space="preserve">35.937614440918</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">34.1454963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8413696289062</t>
+    <t xml:space="preserve">34.8413734436035</t>
   </si>
   <si>
     <t xml:space="preserve">34.6697883605957</t>
@@ -4709,16 +4709,16 @@
     <t xml:space="preserve">34.6888542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1759300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1282615661621</t>
+    <t xml:space="preserve">36.1759262084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1282653808594</t>
   </si>
   <si>
     <t xml:space="preserve">36.0615386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7097473144531</t>
+    <t xml:space="preserve">36.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">37.8631858825684</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">34.9748268127441</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6707000732422</t>
+    <t xml:space="preserve">35.6707038879395</t>
   </si>
   <si>
     <t xml:space="preserve">33.7546653747559</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">33.8881187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3552169799805</t>
+    <t xml:space="preserve">34.3552131652832</t>
   </si>
   <si>
     <t xml:space="preserve">35.1082878112793</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">36.3761100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5953559875488</t>
+    <t xml:space="preserve">36.5953598022461</t>
   </si>
   <si>
     <t xml:space="preserve">36.8908653259277</t>
@@ -4775,28 +4775,28 @@
     <t xml:space="preserve">34.946231842041</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3656578063965</t>
+    <t xml:space="preserve">35.3656616210938</t>
   </si>
   <si>
     <t xml:space="preserve">35.4037895202637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5086517333984</t>
+    <t xml:space="preserve">35.5086479187012</t>
   </si>
   <si>
     <t xml:space="preserve">35.3847274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9471473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9090118408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5286254882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4619026184082</t>
+    <t xml:space="preserve">35.9471435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9090156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5286293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4618988037109</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807846069336</t>
@@ -6450,6 +6450,9 @@
   </si>
   <si>
     <t xml:space="preserve">90.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.879997253418</t>
   </si>
 </sst>
 </file>
@@ -71554,7 +71557,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6527430556</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>1099342</v>
@@ -71575,6 +71578,32 @@
         <v>2139</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6506944444</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>656254</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>89.0800018310547</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>88.0199966430664</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>89</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>88.879997253418</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>2146</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="2147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="2148">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6851577758789</t>
+    <t xml:space="preserve">15.6851539611816</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
@@ -50,181 +50,181 @@
     <t xml:space="preserve">15.3207597732544</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2397832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7458295822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9644641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2964668273926</t>
+    <t xml:space="preserve">15.2397842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.74582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9644660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2964677810669</t>
   </si>
   <si>
     <t xml:space="preserve">15.4989109039307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0616369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5028991699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5433883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8510980606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870908737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9401712417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4098377227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9239778518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2802724838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1831026077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.624361038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936395645142</t>
+    <t xml:space="preserve">15.061637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5028972625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5433893203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8511009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870889663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9401721954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4098339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9239740371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2802762985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1831016540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6243629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936414718628</t>
   </si>
   <si>
     <t xml:space="preserve">14.8106079101562</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7296342849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8996829986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5190916061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.73362159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3449335098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.098014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3206405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.474494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8955764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7822065353394</t>
+    <t xml:space="preserve">14.7296314239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8996820449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5190935134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7336225509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.344934463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0980157852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3206396102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4744958877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8955736160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.782205581665</t>
   </si>
   <si>
     <t xml:space="preserve">14.3328485488892</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2194814682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057273864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8349027633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5514831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3409452438354</t>
+    <t xml:space="preserve">14.2194805145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.405725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8349018096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5514850616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3409481048584</t>
   </si>
   <si>
     <t xml:space="preserve">14.8672933578491</t>
   </si>
   <si>
-    <t xml:space="preserve">15.102123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4827156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3774480819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017362594604</t>
+    <t xml:space="preserve">15.1021251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2235889434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4827146530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3774461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4017400741577</t>
   </si>
   <si>
     <t xml:space="preserve">15.4665193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4908113479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5232038497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8390130996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879831314087</t>
+    <t xml:space="preserve">15.4908151626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5232019424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636892318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426105499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8390092849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879821777344</t>
   </si>
   <si>
     <t xml:space="preserve">15.6365699768066</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9199876785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8309135437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8795003890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8228130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.895694732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2762832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1224269866943</t>
+    <t xml:space="preserve">15.9199886322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8309164047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8794975280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8228139877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8956937789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2762851715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1224308013916</t>
   </si>
   <si>
     <t xml:space="preserve">15.8471097946167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8875951766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4422254562378</t>
+    <t xml:space="preserve">15.8875970840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4422245025635</t>
   </si>
   <si>
     <t xml:space="preserve">15.3855428695679</t>
@@ -233,31 +233,31 @@
     <t xml:space="preserve">16.3086738586426</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2277011871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7135562896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6568756103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4301376342773</t>
+    <t xml:space="preserve">16.2276973724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7135581970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6568737030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.430139541626</t>
   </si>
   <si>
     <t xml:space="preserve">16.6120548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9180011749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0254955291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9758815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9924201965332</t>
+    <t xml:space="preserve">16.9179973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0254974365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9758777618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9924182891846</t>
   </si>
   <si>
     <t xml:space="preserve">16.6285915374756</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">16.98415184021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1081790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9345397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5541725158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.595516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7608947753906</t>
+    <t xml:space="preserve">17.1081829071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9345359802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5541744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5955181121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.760892868042</t>
   </si>
   <si>
     <t xml:space="preserve">16.703010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8766574859619</t>
+    <t xml:space="preserve">16.8766593933105</t>
   </si>
   <si>
     <t xml:space="preserve">17.4058589935303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7696914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0094814300537</t>
+    <t xml:space="preserve">17.7696876525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0094833374023</t>
   </si>
   <si>
     <t xml:space="preserve">17.9681396484375</t>
@@ -305,37 +305,37 @@
     <t xml:space="preserve">17.8606472015381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7779560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8854522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6952705383301</t>
+    <t xml:space="preserve">17.7779579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8854503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6952686309814</t>
   </si>
   <si>
     <t xml:space="preserve">18.1087074279785</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9598693847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2658157348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748600006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2823581695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2988929748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4725360870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1831283569336</t>
+    <t xml:space="preserve">17.9598712921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2658195495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1748580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2823543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2988948822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4725399017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1831302642822</t>
   </si>
   <si>
     <t xml:space="preserve">18.1335144042969</t>
@@ -344,28 +344,28 @@
     <t xml:space="preserve">18.0425586700439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8027629852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.092170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9185276031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0012149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3149013519287</t>
+    <t xml:space="preserve">17.8027610778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0921726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9185256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0012168884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.314905166626</t>
   </si>
   <si>
     <t xml:space="preserve">16.9097328186035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6368598937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8022403717041</t>
+    <t xml:space="preserve">16.6368618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8022384643555</t>
   </si>
   <si>
     <t xml:space="preserve">17.7366142272949</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">17.5712375640869</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3479766845703</t>
+    <t xml:space="preserve">17.3479824066162</t>
   </si>
   <si>
     <t xml:space="preserve">17.9102592468262</t>
@@ -386,25 +386,25 @@
     <t xml:space="preserve">14.8342571258545</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1402053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2559680938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2978401184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7272882461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5867214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.231162071228</t>
+    <t xml:space="preserve">15.1402063369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2559719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399578094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2978382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7272911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5867223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2311611175537</t>
   </si>
   <si>
     <t xml:space="preserve">15.6115274429321</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">16.2813014984131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4632148742676</t>
+    <t xml:space="preserve">16.4632129669189</t>
   </si>
   <si>
     <t xml:space="preserve">16.6533985137939</t>
@@ -422,79 +422,79 @@
     <t xml:space="preserve">16.6864738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6782054901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7443542480469</t>
+    <t xml:space="preserve">16.6782035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7443523406982</t>
   </si>
   <si>
     <t xml:space="preserve">16.6699352264404</t>
   </si>
   <si>
-    <t xml:space="preserve">16.843578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8187713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9510765075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.099910736084</t>
+    <t xml:space="preserve">16.8435821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8187732696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.951078414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0999145507812</t>
   </si>
   <si>
     <t xml:space="preserve">17.1164512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2983665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2404823303223</t>
+    <t xml:space="preserve">17.2983684539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2404861450195</t>
   </si>
   <si>
     <t xml:space="preserve">17.0751075744629</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3314437866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6208515167236</t>
+    <t xml:space="preserve">17.3314399719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6208477020264</t>
   </si>
   <si>
     <t xml:space="preserve">18.1004409790039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6125812530518</t>
+    <t xml:space="preserve">17.612585067749</t>
   </si>
   <si>
     <t xml:space="preserve">17.5960445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0756340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7944946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8771858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1913986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2492809295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0839023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2906227111816</t>
+    <t xml:space="preserve">18.0756378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7944984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8771820068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1914005279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2492790222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0839061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.290620803833</t>
   </si>
   <si>
     <t xml:space="preserve">18.1665897369385</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9929466247559</t>
+    <t xml:space="preserve">17.9929447174072</t>
   </si>
   <si>
     <t xml:space="preserve">17.8441066741943</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">17.7200775146484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7283458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8937244415283</t>
+    <t xml:space="preserve">17.7283401489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8937187194824</t>
   </si>
   <si>
     <t xml:space="preserve">18.0673675537109</t>
@@ -515,88 +515,88 @@
     <t xml:space="preserve">18.37331199646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9438591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4317207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3573017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1009674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1257724761963</t>
+    <t xml:space="preserve">18.9438629150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4317226409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3573036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1009693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1257762908936</t>
   </si>
   <si>
     <t xml:space="preserve">19.1919250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">19.175386428833</t>
+    <t xml:space="preserve">19.1753902435303</t>
   </si>
   <si>
     <t xml:space="preserve">19.2828826904297</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1340427398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3490295410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978713989258</t>
+    <t xml:space="preserve">19.1340446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3490333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978694915771</t>
   </si>
   <si>
     <t xml:space="preserve">19.76247215271</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6549816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7045936584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4647960662842</t>
+    <t xml:space="preserve">19.6549797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4647941589355</t>
   </si>
   <si>
     <t xml:space="preserve">19.0596237182617</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6461811065674</t>
+    <t xml:space="preserve">18.646183013916</t>
   </si>
   <si>
     <t xml:space="preserve">19.1175079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1588497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0100154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7536792755127</t>
+    <t xml:space="preserve">19.1588478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0100116729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7536773681641</t>
   </si>
   <si>
     <t xml:space="preserve">18.902515411377</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0844287872314</t>
+    <t xml:space="preserve">19.0844306945801</t>
   </si>
   <si>
     <t xml:space="preserve">18.9934749603271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7950210571289</t>
+    <t xml:space="preserve">18.7950229644775</t>
   </si>
   <si>
     <t xml:space="preserve">18.7867546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7454109191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3319664001465</t>
+    <t xml:space="preserve">18.7454071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3319683074951</t>
   </si>
   <si>
     <t xml:space="preserve">17.6291198730469</t>
@@ -605,46 +605,46 @@
     <t xml:space="preserve">18.869441986084</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1505832672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3485088348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6627197265625</t>
+    <t xml:space="preserve">19.1505794525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3485069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6627235412598</t>
   </si>
   <si>
     <t xml:space="preserve">18.728874206543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6875286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8942470550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4229259490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.480806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2327423095703</t>
+    <t xml:space="preserve">18.6875247955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8942489624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4229278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4808082580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2327442169189</t>
   </si>
   <si>
     <t xml:space="preserve">18.3237018585205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0590934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6709899902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9355926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4399929046631</t>
+    <t xml:space="preserve">18.0590953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.670991897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9355907440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4399909973145</t>
   </si>
   <si>
     <t xml:space="preserve">19.8782367706299</t>
@@ -653,67 +653,67 @@
     <t xml:space="preserve">19.6797866821289</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1676425933838</t>
+    <t xml:space="preserve">20.1676445007324</t>
   </si>
   <si>
     <t xml:space="preserve">19.8451633453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7790126800537</t>
+    <t xml:space="preserve">19.7790107727051</t>
   </si>
   <si>
     <t xml:space="preserve">20.1428394317627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9113121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1759166717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.002269744873</t>
+    <t xml:space="preserve">19.9113159179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1759147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0022678375244</t>
   </si>
   <si>
     <t xml:space="preserve">19.9278507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0105361938477</t>
+    <t xml:space="preserve">20.0105400085449</t>
   </si>
   <si>
     <t xml:space="preserve">19.8038196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1014976501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1263008117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1097660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1924495697021</t>
+    <t xml:space="preserve">20.1014938354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1262989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1097640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1924514770508</t>
   </si>
   <si>
     <t xml:space="preserve">20.6389675140381</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1345691680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2751407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2172584533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3164844512939</t>
+    <t xml:space="preserve">20.1345729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2751426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2172565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3164863586426</t>
   </si>
   <si>
     <t xml:space="preserve">20.2420654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3330249786377</t>
+    <t xml:space="preserve">20.3330230712891</t>
   </si>
   <si>
     <t xml:space="preserve">20.2255268096924</t>
@@ -725,46 +725,46 @@
     <t xml:space="preserve">20.5066680908203</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3578300476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.481861114502</t>
+    <t xml:space="preserve">20.3578281402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4818592071533</t>
   </si>
   <si>
     <t xml:space="preserve">20.0849590301514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3991737365723</t>
+    <t xml:space="preserve">20.3991718292236</t>
   </si>
   <si>
     <t xml:space="preserve">20.5645503997803</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5397434234619</t>
+    <t xml:space="preserve">20.5397453308105</t>
   </si>
   <si>
     <t xml:space="preserve">20.6885795593262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8947734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4074401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7133884429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9697189331055</t>
+    <t xml:space="preserve">19.894775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4074382781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7133903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9697227478027</t>
   </si>
   <si>
     <t xml:space="preserve">20.3495597839355</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4239768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3082160949707</t>
+    <t xml:space="preserve">20.423978805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3082180023193</t>
   </si>
   <si>
     <t xml:space="preserve">20.7547302246094</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">19.8865032196045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8286247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8534278869629</t>
+    <t xml:space="preserve">19.8286266326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8534336090088</t>
   </si>
   <si>
     <t xml:space="preserve">20.1180324554443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5722942352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2994174957275</t>
+    <t xml:space="preserve">19.5722904205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2994194030762</t>
   </si>
   <si>
     <t xml:space="preserve">19.5144081115723</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">19.6136360168457</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5640201568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3821067810059</t>
+    <t xml:space="preserve">19.564022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3821105957031</t>
   </si>
   <si>
     <t xml:space="preserve">19.7376689910889</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3661022186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9361190795898</t>
+    <t xml:space="preserve">20.3660984039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9361171722412</t>
   </si>
   <si>
     <t xml:space="preserve">20.200719833374</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4901294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7381954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2922058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.15163230896</t>
+    <t xml:space="preserve">20.4901313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7381916046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2922039031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1516361236572</t>
   </si>
   <si>
     <t xml:space="preserve">21.0854816436768</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">20.7051181793213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0435581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1192474365234</t>
+    <t xml:space="preserve">21.1268272399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0435562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1192531585693</t>
   </si>
   <si>
     <t xml:space="preserve">21.8669414520264</t>
@@ -863,31 +863,31 @@
     <t xml:space="preserve">21.9846878051758</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2958698272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4724884033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.220178604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.262228012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5397720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5734081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8080654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.69873046875</t>
+    <t xml:space="preserve">22.2958679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4724864959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2201747894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2622261047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5397682189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5734100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.808069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6987323760986</t>
   </si>
   <si>
     <t xml:space="preserve">21.0847759246826</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">21.3202667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9502086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6390266418457</t>
+    <t xml:space="preserve">20.9502124786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6390285491943</t>
   </si>
   <si>
     <t xml:space="preserve">20.4203586578369</t>
@@ -908,55 +908,55 @@
     <t xml:space="preserve">20.5549221038818</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4540023803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9670295715332</t>
+    <t xml:space="preserve">20.4539985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9670314788818</t>
   </si>
   <si>
     <t xml:space="preserve">21.1941108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8576965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1688823699951</t>
+    <t xml:space="preserve">20.8576946258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1688785552979</t>
   </si>
   <si>
     <t xml:space="preserve">20.8324642181396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9586162567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5978088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2613964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.101598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6819114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.614631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8164806365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6566791534424</t>
+    <t xml:space="preserve">20.9586200714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8156452178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5978107452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2613945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1015968322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6819133758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6146297454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8164768218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.656681060791</t>
   </si>
   <si>
     <t xml:space="preserve">21.8248901367188</t>
   </si>
   <si>
-    <t xml:space="preserve">21.547342300415</t>
+    <t xml:space="preserve">21.5473442077637</t>
   </si>
   <si>
     <t xml:space="preserve">21.5725784301758</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">22.0351486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8585300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9258117675781</t>
+    <t xml:space="preserve">21.858528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9258136749268</t>
   </si>
   <si>
     <t xml:space="preserve">21.7828369140625</t>
@@ -980,115 +980,115 @@
     <t xml:space="preserve">21.4884738922119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3875503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1949462890625</t>
+    <t xml:space="preserve">21.3875522613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1949481964111</t>
   </si>
   <si>
     <t xml:space="preserve">21.8501205444336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2454032897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0015048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3883838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538146972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5481796264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5313625335693</t>
+    <t xml:space="preserve">22.2454051971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0015068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3883819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538166046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5481815338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5313587188721</t>
   </si>
   <si>
     <t xml:space="preserve">22.7668495178223</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0696220397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5818195343018</t>
+    <t xml:space="preserve">23.0696201324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5818214416504</t>
   </si>
   <si>
     <t xml:space="preserve">22.8425426483154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.564998626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1444797515869</t>
+    <t xml:space="preserve">22.5650005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1444816589355</t>
   </si>
   <si>
     <t xml:space="preserve">22.2117671966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1865348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.52294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7920799255371</t>
+    <t xml:space="preserve">22.1865329742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5229511260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7920837402344</t>
   </si>
   <si>
     <t xml:space="preserve">22.4220237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7500286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.926643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9350547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8593635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7079772949219</t>
+    <t xml:space="preserve">22.7500267028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9266452789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.93505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8593616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7079753875732</t>
   </si>
   <si>
     <t xml:space="preserve">22.7416172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5902271270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2369956970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8417091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1613006591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3547401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3042812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9594535827637</t>
+    <t xml:space="preserve">22.5902309417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2369995117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8417072296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.161304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3547420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3042774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.959451675415</t>
   </si>
   <si>
     <t xml:space="preserve">22.2285861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.11083984375</t>
+    <t xml:space="preserve">22.1108379364014</t>
   </si>
   <si>
     <t xml:space="preserve">21.9174003601074</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3463306427002</t>
+    <t xml:space="preserve">22.3463287353516</t>
   </si>
   <si>
     <t xml:space="preserve">22.4304351806641</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">22.825719833374</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4649066925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6331157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6751651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6835765838623</t>
+    <t xml:space="preserve">23.4649085998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.633113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6751670837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6835784912109</t>
   </si>
   <si>
     <t xml:space="preserve">23.8097343444824</t>
@@ -1115,19 +1115,19 @@
     <t xml:space="preserve">23.9106578826904</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9190692901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.750862121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8770179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9863510131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8938407897949</t>
+    <t xml:space="preserve">23.9190654754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7508583068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8770141601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.986349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8938388824463</t>
   </si>
   <si>
     <t xml:space="preserve">23.952709197998</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">23.9779396057129</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8517875671387</t>
+    <t xml:space="preserve">23.8517894744873</t>
   </si>
   <si>
     <t xml:space="preserve">24.0368137359619</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">24.3311748504639</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3143577575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0536346435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9358882904053</t>
+    <t xml:space="preserve">24.3143558502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0536365509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9358901977539</t>
   </si>
   <si>
     <t xml:space="preserve">23.8013229370117</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">24.1040992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">24.558256149292</t>
+    <t xml:space="preserve">24.5582580566406</t>
   </si>
   <si>
     <t xml:space="preserve">24.5077953338623</t>
@@ -1184,19 +1184,19 @@
     <t xml:space="preserve">24.9199028015137</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7937469482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6928215026855</t>
+    <t xml:space="preserve">24.7937450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6928195953369</t>
   </si>
   <si>
     <t xml:space="preserve">24.8946704864502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2310848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1217498779297</t>
+    <t xml:space="preserve">25.2310886383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1217479705811</t>
   </si>
   <si>
     <t xml:space="preserve">25.1890335083008</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">24.8526210784912</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4489231109619</t>
+    <t xml:space="preserve">24.4489212036133</t>
   </si>
   <si>
     <t xml:space="preserve">23.5574245452881</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">23.2125988006592</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9274787902832</t>
+    <t xml:space="preserve">23.9274826049805</t>
   </si>
   <si>
     <t xml:space="preserve">23.691987991333</t>
@@ -1235,28 +1235,28 @@
     <t xml:space="preserve">23.3808059692383</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4144458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.532190322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9695301055908</t>
+    <t xml:space="preserve">23.4144477844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5321922302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9695320129395</t>
   </si>
   <si>
     <t xml:space="preserve">22.9939289093018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6911563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014167785645</t>
+    <t xml:space="preserve">22.6911582946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014148712158</t>
   </si>
   <si>
     <t xml:space="preserve">22.9771099090576</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0443878173828</t>
+    <t xml:space="preserve">23.0443935394287</t>
   </si>
   <si>
     <t xml:space="preserve">23.0275707244873</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">23.0359783172607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8930053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.682746887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1789569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546501159668</t>
+    <t xml:space="preserve">22.8930034637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6827449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1789588928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546539306641</t>
   </si>
   <si>
     <t xml:space="preserve">23.2210102081299</t>
@@ -1286,28 +1286,28 @@
     <t xml:space="preserve">23.2294178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">23.078031539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8677730560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0107479095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1882019042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.003173828125</t>
+    <t xml:space="preserve">23.0780296325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8677711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0107498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1881980895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0031719207764</t>
   </si>
   <si>
     <t xml:space="preserve">24.1713790893555</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2218418121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3900489807129</t>
+    <t xml:space="preserve">24.2218456268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3900508880615</t>
   </si>
   <si>
     <t xml:space="preserve">24.4909725189209</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">24.8273868560791</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5246162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3395881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3059463500977</t>
+    <t xml:space="preserve">24.5246143341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3395862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.305944442749</t>
   </si>
   <si>
     <t xml:space="preserve">23.8686046600342</t>
@@ -1331,85 +1331,85 @@
     <t xml:space="preserve">23.8349647521973</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2882900238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9602870941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6070518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4564952850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7163848876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4556674957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.068790435791</t>
+    <t xml:space="preserve">23.2882919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9602890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4564990997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7163867950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4556636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0687885284424</t>
   </si>
   <si>
     <t xml:space="preserve">22.1781215667725</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0940208435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9089908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7996559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6314506530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7912483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3631477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3967933654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2874622344971</t>
+    <t xml:space="preserve">22.0940189361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.908992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7996597290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6314487457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7912464141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3631496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3967952728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2874603271484</t>
   </si>
   <si>
     <t xml:space="preserve">22.0856094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6230430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3455009460449</t>
+    <t xml:space="preserve">21.6230411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3454990386963</t>
   </si>
   <si>
     <t xml:space="preserve">21.4043712615967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4464206695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2950344085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.337085723877</t>
+    <t xml:space="preserve">21.4464244842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2950325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3370838165283</t>
   </si>
   <si>
     <t xml:space="preserve">21.7407855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.790412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3194332122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7988224029541</t>
+    <t xml:space="preserve">20.7904148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3194351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7988243103027</t>
   </si>
   <si>
     <t xml:space="preserve">20.4035377502441</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">20.5717430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7735919952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9249820709229</t>
+    <t xml:space="preserve">20.7735939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9249801635742</t>
   </si>
   <si>
     <t xml:space="preserve">20.8072338104248</t>
@@ -1430,43 +1430,43 @@
     <t xml:space="preserve">21.0288734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8919334411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6351680755615</t>
+    <t xml:space="preserve">20.8919315338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6351699829102</t>
   </si>
   <si>
     <t xml:space="preserve">20.6180515289307</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7464294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8662548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3883399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9604015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3626613616943</t>
+    <t xml:space="preserve">20.746431350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8662528991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3883419036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9603996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.362663269043</t>
   </si>
   <si>
     <t xml:space="preserve">21.5081596374512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8847484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.756368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2271003723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9203567504883</t>
+    <t xml:space="preserve">21.884744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7563648223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2270946502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9203586578369</t>
   </si>
   <si>
     <t xml:space="preserve">22.4153900146484</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">22.4239501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8077163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0987205505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1072750091553</t>
+    <t xml:space="preserve">21.8077182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0987167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1072769165039</t>
   </si>
   <si>
     <t xml:space="preserve">21.7392463684082</t>
@@ -1496,19 +1496,19 @@
     <t xml:space="preserve">21.4054584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9432849884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1216430664062</t>
+    <t xml:space="preserve">20.943286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1302051544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1216449737549</t>
   </si>
   <si>
     <t xml:space="preserve">20.3698463439941</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2685165405273</t>
+    <t xml:space="preserve">21.268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">21.3968982696533</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">21.3797798156738</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0117511749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6779651641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1743698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8063468933105</t>
+    <t xml:space="preserve">21.0117530822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6779613494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1743717193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8063430786133</t>
   </si>
   <si>
     <t xml:space="preserve">20.7977848052979</t>
@@ -1538,73 +1538,73 @@
     <t xml:space="preserve">21.9960136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5423984527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1914901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9090461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4554347991943</t>
+    <t xml:space="preserve">21.5423965454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1914882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9090480804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4554328918457</t>
   </si>
   <si>
     <t xml:space="preserve">19.6509113311768</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8563194274902</t>
+    <t xml:space="preserve">19.8563213348389</t>
   </si>
   <si>
     <t xml:space="preserve">17.8706893920898</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9305973052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2729473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4427509307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2558326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9355735778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6260852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.245418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1657428741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1568870544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.811990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2280654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.997896194458</t>
+    <t xml:space="preserve">17.9305992126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2729511260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4427490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2558364868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9355754852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6260833740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2454204559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1657447814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.156888961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8119926452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2280673980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9978981018066</t>
   </si>
   <si>
     <t xml:space="preserve">18.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2988872528076</t>
+    <t xml:space="preserve">19.2988891601562</t>
   </si>
   <si>
     <t xml:space="preserve">19.1838035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2103652954102</t>
+    <t xml:space="preserve">19.2103614807129</t>
   </si>
   <si>
     <t xml:space="preserve">19.4139766693115</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">19.5202045440674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5113544464111</t>
+    <t xml:space="preserve">19.5113563537598</t>
   </si>
   <si>
     <t xml:space="preserve">19.5644721984863</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">19.4316806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1395416259766</t>
+    <t xml:space="preserve">19.1395435333252</t>
   </si>
   <si>
     <t xml:space="preserve">19.0687198638916</t>
@@ -1637,46 +1637,46 @@
     <t xml:space="preserve">19.2369194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6972599029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.750373840332</t>
+    <t xml:space="preserve">19.6972618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7503757476807</t>
   </si>
   <si>
     <t xml:space="preserve">19.8034954071045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4405345916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0333080291748</t>
+    <t xml:space="preserve">19.4405307769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2900371551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0333099365234</t>
   </si>
   <si>
     <t xml:space="preserve">18.5109977722168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3516502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8208427429199</t>
+    <t xml:space="preserve">18.3516521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8208465576172</t>
   </si>
   <si>
     <t xml:space="preserve">18.7765789031982</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7942867279053</t>
+    <t xml:space="preserve">18.7942848205566</t>
   </si>
   <si>
     <t xml:space="preserve">18.9182243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1129817962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4847965240479</t>
+    <t xml:space="preserve">19.1129837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4847984313965</t>
   </si>
   <si>
     <t xml:space="preserve">19.6707019805908</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">19.5733242034912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2015113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.219217300415</t>
+    <t xml:space="preserve">19.2015075683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2192134857178</t>
   </si>
   <si>
     <t xml:space="preserve">19.0952777862549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6969089508057</t>
+    <t xml:space="preserve">18.696907043457</t>
   </si>
   <si>
     <t xml:space="preserve">19.1218357086182</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2546253204346</t>
+    <t xml:space="preserve">19.2546234130859</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906734466553</t>
@@ -1709,37 +1709,37 @@
     <t xml:space="preserve">18.4136180877686</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6791973114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6880550384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1483936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9890460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0510139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5995254516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3428001403809</t>
+    <t xml:space="preserve">18.67919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6880531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1483955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9890480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0510120391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5995273590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3427963256836</t>
   </si>
   <si>
     <t xml:space="preserve">18.431324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3693542480469</t>
+    <t xml:space="preserve">18.3693561553955</t>
   </si>
   <si>
     <t xml:space="preserve">17.7585201263428</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6965484619141</t>
+    <t xml:space="preserve">17.6965503692627</t>
   </si>
   <si>
     <t xml:space="preserve">17.4840869903564</t>
@@ -1751,46 +1751,46 @@
     <t xml:space="preserve">17.417688369751</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6342258453369</t>
+    <t xml:space="preserve">17.0325984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6342277526855</t>
   </si>
   <si>
     <t xml:space="preserve">16.4527435302734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9392890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5719022750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346866607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4656667709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7316074371338</t>
+    <t xml:space="preserve">15.9392871856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5719032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346876144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4656677246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7316055297852</t>
   </si>
   <si>
     <t xml:space="preserve">16.2712650299072</t>
   </si>
   <si>
-    <t xml:space="preserve">15.766658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2133693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1735305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6777801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2262916564941</t>
+    <t xml:space="preserve">15.7666597366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2133674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.173529624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6777782440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2262907028198</t>
   </si>
   <si>
     <t xml:space="preserve">14.7840127944946</t>
@@ -1799,46 +1799,46 @@
     <t xml:space="preserve">14.6290893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9743452072144</t>
+    <t xml:space="preserve">14.97434425354</t>
   </si>
   <si>
     <t xml:space="preserve">15.071722984314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1912355422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7179698944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2933979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171552658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8596153259277</t>
+    <t xml:space="preserve">15.1912336349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7179689407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.293399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8596124649048</t>
   </si>
   <si>
     <t xml:space="preserve">16.0986366271973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1030654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7755146026611</t>
+    <t xml:space="preserve">16.103063583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7755136489868</t>
   </si>
   <si>
     <t xml:space="preserve">15.4169797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7887897491455</t>
+    <t xml:space="preserve">15.7887916564941</t>
   </si>
   <si>
     <t xml:space="preserve">15.4833755493164</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6910581588745</t>
+    <t xml:space="preserve">14.6910572052002</t>
   </si>
   <si>
     <t xml:space="preserve">14.2882595062256</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">13.8943147659302</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9739894866943</t>
+    <t xml:space="preserve">13.97398853302</t>
   </si>
   <si>
     <t xml:space="preserve">13.8766098022461</t>
@@ -1859,22 +1859,22 @@
     <t xml:space="preserve">14.0802221298218</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9916954040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7880830764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6243076324463</t>
+    <t xml:space="preserve">13.9916944503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7880821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6243085861206</t>
   </si>
   <si>
     <t xml:space="preserve">14.1554689407349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3148183822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0451669692993</t>
+    <t xml:space="preserve">14.3148193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.045166015625</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254760742188</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">13.4959440231323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3675785064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2524948120117</t>
+    <t xml:space="preserve">13.367579460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.252495765686</t>
   </si>
   <si>
     <t xml:space="preserve">14.0669431686401</t>
@@ -1901,43 +1901,43 @@
     <t xml:space="preserve">14.8415546417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6954851150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6512203216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8946704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0628719329834</t>
+    <t xml:space="preserve">14.6954860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.651219367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8946723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0628700256348</t>
   </si>
   <si>
     <t xml:space="preserve">14.8813915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8282737731934</t>
+    <t xml:space="preserve">14.8282747268677</t>
   </si>
   <si>
     <t xml:space="preserve">14.9345083236694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4479627609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.713191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2886171340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.695837020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3155307769775</t>
+    <t xml:space="preserve">15.4479646682739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7131910324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2886161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6958389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3155288696289</t>
   </si>
   <si>
     <t xml:space="preserve">16.4129085540771</t>
@@ -1949,25 +1949,25 @@
     <t xml:space="preserve">16.0145359039307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8020725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1340484619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2358551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4793033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4748783111572</t>
+    <t xml:space="preserve">15.802074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1340503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2358531951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4793014526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4748802185059</t>
   </si>
   <si>
     <t xml:space="preserve">16.3376617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2181510925293</t>
+    <t xml:space="preserve">16.218147277832</t>
   </si>
   <si>
     <t xml:space="preserve">16.2889709472656</t>
@@ -1979,31 +1979,31 @@
     <t xml:space="preserve">16.5412731170654</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7758693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4881553649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7935752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9263668060303</t>
+    <t xml:space="preserve">16.7758674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4881572723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7935733795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6297988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.926362991333</t>
   </si>
   <si>
     <t xml:space="preserve">15.9481420516968</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9304370880127</t>
+    <t xml:space="preserve">15.9304361343384</t>
   </si>
   <si>
     <t xml:space="preserve">15.9614210128784</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5279960632324</t>
+    <t xml:space="preserve">16.5279941558838</t>
   </si>
   <si>
     <t xml:space="preserve">16.5368480682373</t>
@@ -2012,49 +2012,49 @@
     <t xml:space="preserve">16.67848777771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7138996124268</t>
+    <t xml:space="preserve">16.5855350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7139015197754</t>
   </si>
   <si>
     <t xml:space="preserve">15.1292667388916</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5763263702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8197774887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0101070404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8905973434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8463344573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3992738723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.293041229248</t>
+    <t xml:space="preserve">15.5763273239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8197803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0101108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8906002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8463373184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3992748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2930431365967</t>
   </si>
   <si>
     <t xml:space="preserve">14.9610662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9876232147217</t>
+    <t xml:space="preserve">14.987624168396</t>
   </si>
   <si>
     <t xml:space="preserve">14.8858194351196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3767871856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4874458312988</t>
+    <t xml:space="preserve">14.3767881393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4874467849731</t>
   </si>
   <si>
     <t xml:space="preserve">14.6069564819336</t>
@@ -2063,25 +2063,25 @@
     <t xml:space="preserve">14.5626955032349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7795848846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4125537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2222194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0540189743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9212293624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6423692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300804138184</t>
+    <t xml:space="preserve">14.7795839309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4125547409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2222204208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0540170669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9212284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.642370223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.930079460144</t>
   </si>
   <si>
     <t xml:space="preserve">14.8592596054077</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">14.9477844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4476099014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2436408996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5534868240356</t>
+    <t xml:space="preserve">14.4476089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2436418533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5534858703613</t>
   </si>
   <si>
     <t xml:space="preserve">13.6552925109863</t>
@@ -2111,19 +2111,19 @@
     <t xml:space="preserve">13.6420125961304</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1997356414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4564619064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4431829452515</t>
+    <t xml:space="preserve">14.1997337341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4564609527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4431838989258</t>
   </si>
   <si>
     <t xml:space="preserve">14.682204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8459806442261</t>
+    <t xml:space="preserve">14.8459796905518</t>
   </si>
   <si>
     <t xml:space="preserve">15.2177925109863</t>
@@ -2135,49 +2135,49 @@
     <t xml:space="preserve">15.2089414596558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.031886100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1823835372925</t>
+    <t xml:space="preserve">15.0318870544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1823825836182</t>
   </si>
   <si>
     <t xml:space="preserve">14.4962997436523</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1820287704468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2000904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1381216049194</t>
+    <t xml:space="preserve">14.1820278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2000885009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1381187438965</t>
   </si>
   <si>
     <t xml:space="preserve">15.3151712417603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.306321144104</t>
+    <t xml:space="preserve">15.3063220977783</t>
   </si>
   <si>
     <t xml:space="preserve">14.6467933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3723611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8589038848877</t>
+    <t xml:space="preserve">14.3723621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.858904838562</t>
   </si>
   <si>
     <t xml:space="preserve">13.7748050689697</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5977487564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7792291641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5888967514038</t>
+    <t xml:space="preserve">13.597749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7792301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5888986587524</t>
   </si>
   <si>
     <t xml:space="preserve">13.6774234771729</t>
@@ -2186,25 +2186,25 @@
     <t xml:space="preserve">13.2170848846436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5313549041748</t>
+    <t xml:space="preserve">13.5313539505005</t>
   </si>
   <si>
     <t xml:space="preserve">14.3502283096313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3192443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2705554962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6999101638794</t>
+    <t xml:space="preserve">14.3192434310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2705564498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6999092102051</t>
   </si>
   <si>
     <t xml:space="preserve">14.7353229522705</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9256553649902</t>
+    <t xml:space="preserve">14.9256544113159</t>
   </si>
   <si>
     <t xml:space="preserve">14.6600732803345</t>
@@ -2222,22 +2222,22 @@
     <t xml:space="preserve">15.580756187439</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9127311706543</t>
+    <t xml:space="preserve">15.91273021698</t>
   </si>
   <si>
     <t xml:space="preserve">16.0942115783691</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8584642410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9808731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675317764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2302207946777</t>
+    <t xml:space="preserve">15.8584661483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9808702468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675308227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2302188873291</t>
   </si>
   <si>
     <t xml:space="preserve">16.4568977355957</t>
@@ -2246,19 +2246,19 @@
     <t xml:space="preserve">16.5838375091553</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5929050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.66090965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7243785858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4115619659424</t>
+    <t xml:space="preserve">16.5929069519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6609077453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7243766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7425136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4115600585938</t>
   </si>
   <si>
     <t xml:space="preserve">16.6427764892578</t>
@@ -2267,28 +2267,28 @@
     <t xml:space="preserve">16.9827919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9419918060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0326614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.309211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.454288482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9646606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9555912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0462646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0436515808105</t>
+    <t xml:space="preserve">16.9419898986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0326633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3092098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4542865753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9646587371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9555931091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0462627410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0436477661133</t>
   </si>
   <si>
     <t xml:space="preserve">18.0935192108154</t>
@@ -2303,34 +2303,34 @@
     <t xml:space="preserve">17.1414699554443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7833156585693</t>
+    <t xml:space="preserve">16.783317565918</t>
   </si>
   <si>
     <t xml:space="preserve">16.9283905029297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5268230438232</t>
+    <t xml:space="preserve">17.5268249511719</t>
   </si>
   <si>
     <t xml:space="preserve">17.1505393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9963970184326</t>
+    <t xml:space="preserve">16.996395111084</t>
   </si>
   <si>
     <t xml:space="preserve">16.8875885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9601249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3726787567139</t>
+    <t xml:space="preserve">16.9601268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3726806640625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7787818908691</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7923831939697</t>
+    <t xml:space="preserve">16.7923851013184</t>
   </si>
   <si>
     <t xml:space="preserve">16.7017116546631</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">16.0715427398682</t>
   </si>
   <si>
-    <t xml:space="preserve">16.647310256958</t>
+    <t xml:space="preserve">16.6473083496094</t>
   </si>
   <si>
     <t xml:space="preserve">16.8150501251221</t>
@@ -2351,61 +2351,61 @@
     <t xml:space="preserve">17.5948276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3862800598145</t>
+    <t xml:space="preserve">17.3862819671631</t>
   </si>
   <si>
     <t xml:space="preserve">17.0054588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9782600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2774753570557</t>
+    <t xml:space="preserve">16.9782581329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2774772644043</t>
   </si>
   <si>
     <t xml:space="preserve">17.2276058197021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0209827423096</t>
+    <t xml:space="preserve">18.0209846496582</t>
   </si>
   <si>
     <t xml:space="preserve">18.0481853485107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0073833465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.206859588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7508907318115</t>
+    <t xml:space="preserve">18.007381439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2068614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7508888244629</t>
   </si>
   <si>
     <t xml:space="preserve">18.2975311279297</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3519344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2884674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4244709014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9775676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0501079559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.041036605835</t>
+    <t xml:space="preserve">18.3519325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2884635925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4244689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9775657653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.050106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0410385131836</t>
   </si>
   <si>
     <t xml:space="preserve">18.3156661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7716369628906</t>
+    <t xml:space="preserve">17.7716388702393</t>
   </si>
   <si>
     <t xml:space="preserve">18.0617866516113</t>
@@ -2414,25 +2414,25 @@
     <t xml:space="preserve">17.880443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0889892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9756488800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7353687286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7217655181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8623065948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7126998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0598659515381</t>
+    <t xml:space="preserve">18.0889873504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9756469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7353668212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7217674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8623085021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7126979827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0598621368408</t>
   </si>
   <si>
     <t xml:space="preserve">17.0507984161377</t>
@@ -2441,22 +2441,22 @@
     <t xml:space="preserve">16.973726272583</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0961322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8921222686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2366752624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7671012878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0753841400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4698085784912</t>
+    <t xml:space="preserve">17.096134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8921203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2366714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7671031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0753860473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4698104858398</t>
   </si>
   <si>
     <t xml:space="preserve">18.5060749053955</t>
@@ -2465,13 +2465,13 @@
     <t xml:space="preserve">18.7236862182617</t>
   </si>
   <si>
-    <t xml:space="preserve">18.71462059021</t>
+    <t xml:space="preserve">18.7146224975586</t>
   </si>
   <si>
     <t xml:space="preserve">18.2703304290771</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1887245178223</t>
+    <t xml:space="preserve">18.1887264251709</t>
   </si>
   <si>
     <t xml:space="preserve">18.57861328125</t>
@@ -2480,40 +2480,40 @@
     <t xml:space="preserve">18.9594345092773</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7690238952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7418251037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7780895233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2223815917969</t>
+    <t xml:space="preserve">18.7690277099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7418231964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7780933380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2223834991455</t>
   </si>
   <si>
     <t xml:space="preserve">19.712007522583</t>
   </si>
   <si>
-    <t xml:space="preserve">19.521598815918</t>
+    <t xml:space="preserve">19.5216026306152</t>
   </si>
   <si>
     <t xml:space="preserve">19.81174659729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490604400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3130550384521</t>
+    <t xml:space="preserve">19.4490642547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3130512237549</t>
   </si>
   <si>
     <t xml:space="preserve">18.7962265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4970092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1732044219971</t>
+    <t xml:space="preserve">18.4970073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1732025146484</t>
   </si>
   <si>
     <t xml:space="preserve">17.422550201416</t>
@@ -2525,16 +2525,16 @@
     <t xml:space="preserve">17.9121761322021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0391178131104</t>
+    <t xml:space="preserve">18.039119720459</t>
   </si>
   <si>
     <t xml:space="preserve">17.9892482757568</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0663185119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8596973419189</t>
+    <t xml:space="preserve">18.0663166046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8596935272217</t>
   </si>
   <si>
     <t xml:space="preserve">18.9050312042236</t>
@@ -2555,46 +2555,46 @@
     <t xml:space="preserve">19.0863742828369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.195182800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.576000213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6394691467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4218616485596</t>
+    <t xml:space="preserve">19.1951808929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5760021209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6394729614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4218597412109</t>
   </si>
   <si>
     <t xml:space="preserve">19.7392101287842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.94775390625</t>
+    <t xml:space="preserve">19.9477558135986</t>
   </si>
   <si>
     <t xml:space="preserve">20.0021572113037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8661518096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.485330581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6757411956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2133159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1679801940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3221225738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0319690704346</t>
+    <t xml:space="preserve">19.8661499023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4853286743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6757392883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2133178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1679763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3221206665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0319709777832</t>
   </si>
   <si>
     <t xml:space="preserve">19.2949199676514</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">18.9957046508789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6602172851562</t>
+    <t xml:space="preserve">18.6602191925049</t>
   </si>
   <si>
     <t xml:space="preserve">18.5332794189453</t>
@@ -2624,22 +2624,22 @@
     <t xml:space="preserve">18.9322319030762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4762649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.047492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0112266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9658908843994</t>
+    <t xml:space="preserve">19.4762630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0474948883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0112247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9658889770508</t>
   </si>
   <si>
     <t xml:space="preserve">20.3376445770264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9088726043701</t>
+    <t xml:space="preserve">20.9088745117188</t>
   </si>
   <si>
     <t xml:space="preserve">21.325963973999</t>
@@ -2648,28 +2648,28 @@
     <t xml:space="preserve">21.5526428222656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0332012176514</t>
+    <t xml:space="preserve">22.0332050323486</t>
   </si>
   <si>
     <t xml:space="preserve">21.697717666626</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049530029297</t>
+    <t xml:space="preserve">22.4049549102783</t>
   </si>
   <si>
     <t xml:space="preserve">21.8337249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9814128875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9930896759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1925678253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3039875030518</t>
+    <t xml:space="preserve">20.9814109802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9930877685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.192569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3039894104004</t>
   </si>
   <si>
     <t xml:space="preserve">19.3855895996094</t>
@@ -2678,85 +2678,85 @@
     <t xml:space="preserve">18.4607429504395</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6511497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6239490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8195858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4685773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842679977417</t>
+    <t xml:space="preserve">18.6511516571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.623950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0300521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8195838928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4685764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6842670440674</t>
   </si>
   <si>
     <t xml:space="preserve">14.811206817627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.653223991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7412824630737</t>
+    <t xml:space="preserve">12.6532230377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.741283416748</t>
   </si>
   <si>
     <t xml:space="preserve">13.7775526046753</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3170471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7341375350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1648273468018</t>
+    <t xml:space="preserve">14.3170490264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7341384887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1648292541504</t>
   </si>
   <si>
     <t xml:space="preserve">13.6914138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">14.090368270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2691011428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0242862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0061521530151</t>
+    <t xml:space="preserve">14.0903673171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690992355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0242872238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0061502456665</t>
   </si>
   <si>
     <t xml:space="preserve">14.2354431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8863573074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2380561828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4783353805542</t>
+    <t xml:space="preserve">13.8863582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.238055229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4783363342285</t>
   </si>
   <si>
     <t xml:space="preserve">13.5327386856079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9660415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4511337280273</t>
+    <t xml:space="preserve">12.9660406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4511346817017</t>
   </si>
   <si>
     <t xml:space="preserve">13.8092861175537</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1901063919067</t>
+    <t xml:space="preserve">14.1901073455811</t>
   </si>
   <si>
     <t xml:space="preserve">14.2581119537354</t>
@@ -2765,37 +2765,37 @@
     <t xml:space="preserve">13.3695297241211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8727579116821</t>
+    <t xml:space="preserve">13.8727569580078</t>
   </si>
   <si>
     <t xml:space="preserve">13.9634284973145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7820854187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2943811416626</t>
+    <t xml:space="preserve">13.7820844650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2943801879883</t>
   </si>
   <si>
     <t xml:space="preserve">14.448522567749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5346612930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1512269973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3643045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6544542312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5683155059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3461694717407</t>
+    <t xml:space="preserve">14.5346603393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1512279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3643035888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6544551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5683164596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.346170425415</t>
   </si>
   <si>
     <t xml:space="preserve">16.6291732788086</t>
@@ -2804,13 +2804,13 @@
     <t xml:space="preserve">15.7768602371216</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7904624938965</t>
+    <t xml:space="preserve">15.7904615402222</t>
   </si>
   <si>
     <t xml:space="preserve">16.4478302001953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3752937316895</t>
+    <t xml:space="preserve">16.3752918243408</t>
   </si>
   <si>
     <t xml:space="preserve">17.109733581543</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">17.2446346282959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4030952453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8813457489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7066020965576</t>
+    <t xml:space="preserve">16.4030933380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.88134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.706600189209</t>
   </si>
   <si>
     <t xml:space="preserve">17.2906188964844</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">17.699893951416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9896030426025</t>
+    <t xml:space="preserve">17.9896011352539</t>
   </si>
   <si>
     <t xml:space="preserve">17.4515686035156</t>
@@ -2852,40 +2852,40 @@
     <t xml:space="preserve">17.3549995422363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6309108734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9850044250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8884334564209</t>
+    <t xml:space="preserve">17.6309127807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9850025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8884315490723</t>
   </si>
   <si>
     <t xml:space="preserve">18.6334018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.752965927124</t>
+    <t xml:space="preserve">18.7529640197754</t>
   </si>
   <si>
     <t xml:space="preserve">18.8081493377686</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6701908111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7090854644775</t>
+    <t xml:space="preserve">18.6701889038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7090892791748</t>
   </si>
   <si>
     <t xml:space="preserve">17.6631031036377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4745635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3482913970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885074615479</t>
+    <t xml:space="preserve">17.4745616912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3482894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885093688965</t>
   </si>
   <si>
     <t xml:space="preserve">18.5874137878418</t>
@@ -2897,25 +2897,25 @@
     <t xml:space="preserve">18.8173427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.222017288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7161731719971</t>
+    <t xml:space="preserve">19.2220191955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7161750793457</t>
   </si>
   <si>
     <t xml:space="preserve">18.9645004272461</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7897510528564</t>
+    <t xml:space="preserve">18.7897529602051</t>
   </si>
   <si>
     <t xml:space="preserve">19.0104846954346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0748634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5715084075928</t>
+    <t xml:space="preserve">19.0748653411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5715103149414</t>
   </si>
   <si>
     <t xml:space="preserve">19.3507766723633</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">19.9761829376221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9577903747559</t>
+    <t xml:space="preserve">19.9577884674072</t>
   </si>
   <si>
     <t xml:space="preserve">19.6542854309082</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">19.7278633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.930196762085</t>
+    <t xml:space="preserve">19.9301986694336</t>
   </si>
   <si>
     <t xml:space="preserve">19.4703407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0957469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2704944610596</t>
+    <t xml:space="preserve">20.0957450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2704925537109</t>
   </si>
   <si>
     <t xml:space="preserve">20.3256759643555</t>
@@ -2963,16 +2963,16 @@
     <t xml:space="preserve">21.0430507659912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4912223815918</t>
+    <t xml:space="preserve">20.4912242889404</t>
   </si>
   <si>
     <t xml:space="preserve">20.2245044708252</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2337017059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8934078216553</t>
+    <t xml:space="preserve">20.2337036132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8934097290039</t>
   </si>
   <si>
     <t xml:space="preserve">20.8223190307617</t>
@@ -2987,22 +2987,22 @@
     <t xml:space="preserve">20.2061100006104</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5556011199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8775024414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0614471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7303485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7579383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7395439147949</t>
+    <t xml:space="preserve">20.5556049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8775005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0614452362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7303504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7579402923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7395458221436</t>
   </si>
   <si>
     <t xml:space="preserve">20.6291809082031</t>
@@ -3020,67 +3020,67 @@
     <t xml:space="preserve">21.4937133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.944372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5580940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5213012695312</t>
+    <t xml:space="preserve">21.9443740844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5580921173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5213031768799</t>
   </si>
   <si>
     <t xml:space="preserve">22.0271453857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.604076385498</t>
+    <t xml:space="preserve">21.6040782928467</t>
   </si>
   <si>
     <t xml:space="preserve">21.8156108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4109363555908</t>
+    <t xml:space="preserve">21.4109382629395</t>
   </si>
   <si>
     <t xml:space="preserve">21.7420310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1191177368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5145931243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6341590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5421867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6433544158936</t>
+    <t xml:space="preserve">22.1191158294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.514591217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6341571807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5421848297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6433525085449</t>
   </si>
   <si>
     <t xml:space="preserve">22.3674392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4410152435303</t>
+    <t xml:space="preserve">22.4410171508789</t>
   </si>
   <si>
     <t xml:space="preserve">22.2294807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6709442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.487003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9008731842041</t>
+    <t xml:space="preserve">22.6709423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4870014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9008712768555</t>
   </si>
   <si>
     <t xml:space="preserve">22.8732814788818</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8456916809082</t>
+    <t xml:space="preserve">22.8456878662109</t>
   </si>
   <si>
     <t xml:space="preserve">23.2135753631592</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">23.6550369262695</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5262775421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5722618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0045280456543</t>
+    <t xml:space="preserve">23.5262794494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5722637176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0045299530029</t>
   </si>
   <si>
     <t xml:space="preserve">23.7194194793701</t>
@@ -3110,40 +3110,40 @@
     <t xml:space="preserve">24.3264312744141</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8757667541504</t>
+    <t xml:space="preserve">23.875768661499</t>
   </si>
   <si>
     <t xml:space="preserve">24.1700801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5998573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6525497436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7261276245117</t>
+    <t xml:space="preserve">23.599853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6525478363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7261257171631</t>
   </si>
   <si>
     <t xml:space="preserve">22.9560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1926956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.66845703125</t>
+    <t xml:space="preserve">22.1926937103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6684551239014</t>
   </si>
   <si>
     <t xml:space="preserve">21.1994018554688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6500644683838</t>
+    <t xml:space="preserve">21.6500625610352</t>
   </si>
   <si>
     <t xml:space="preserve">21.4661197662354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0823287963867</t>
+    <t xml:space="preserve">22.0823268890381</t>
   </si>
   <si>
     <t xml:space="preserve">22.5881671905518</t>
@@ -3155,13 +3155,13 @@
     <t xml:space="preserve">23.0112400054932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.121603012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6274490356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2988376617432</t>
+    <t xml:space="preserve">23.1216049194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6274471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2988395690918</t>
   </si>
   <si>
     <t xml:space="preserve">23.9677410125732</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">23.3607292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8665733337402</t>
+    <t xml:space="preserve">23.8665752410889</t>
   </si>
   <si>
     <t xml:space="preserve">23.9217567443848</t>
@@ -3185,82 +3185,82 @@
     <t xml:space="preserve">24.0965023040771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7403011322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2277526855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8966522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4092063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5471591949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0622005462646</t>
+    <t xml:space="preserve">24.7403030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2277507781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8966541290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4092044830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5471630096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.062198638916</t>
   </si>
   <si>
     <t xml:space="preserve">24.5655536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6391315460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6023445129395</t>
+    <t xml:space="preserve">24.6391353607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6023426055908</t>
   </si>
   <si>
     <t xml:space="preserve">24.8874568939209</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3105220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5680408477783</t>
+    <t xml:space="preserve">25.3105239868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.568042755127</t>
   </si>
   <si>
     <t xml:space="preserve">25.0805950164795</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3841018676758</t>
+    <t xml:space="preserve">25.3840999603271</t>
   </si>
   <si>
     <t xml:space="preserve">25.503662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3749046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7151947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9359302520752</t>
+    <t xml:space="preserve">25.3749008178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7151966094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9359283447266</t>
   </si>
   <si>
     <t xml:space="preserve">26.6257152557373</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5613327026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7452793121338</t>
+    <t xml:space="preserve">26.5613346099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7452754974365</t>
   </si>
   <si>
     <t xml:space="preserve">26.8740367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0119953155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5546226501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2811985015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9225120544434</t>
+    <t xml:space="preserve">27.0119934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5546245574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2812004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9225101470947</t>
   </si>
   <si>
     <t xml:space="preserve">28.0880584716797</t>
@@ -3275,37 +3275,37 @@
     <t xml:space="preserve">25.8715496063232</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1106739044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.843957901001</t>
+    <t xml:space="preserve">26.1106719970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8439598083496</t>
   </si>
   <si>
     <t xml:space="preserve">26.0279006958008</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7519874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6876049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7127094268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2804431915283</t>
+    <t xml:space="preserve">25.7519855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6876087188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7127113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2804412841797</t>
   </si>
   <si>
     <t xml:space="preserve">25.1449756622314</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5011749267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0346088409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2369480133057</t>
+    <t xml:space="preserve">24.5011730194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0346069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.236946105957</t>
   </si>
   <si>
     <t xml:space="preserve">25.6968021392822</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">25.9267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9083366394043</t>
+    <t xml:space="preserve">25.9083385467529</t>
   </si>
   <si>
     <t xml:space="preserve">26.1198711395264</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">26.0003108978271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9635200500488</t>
+    <t xml:space="preserve">25.9635181427002</t>
   </si>
   <si>
     <t xml:space="preserve">25.6600151062012</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">25.0530033111572</t>
   </si>
   <si>
-    <t xml:space="preserve">24.593147277832</t>
+    <t xml:space="preserve">24.5931453704834</t>
   </si>
   <si>
     <t xml:space="preserve">24.3908100128174</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">24.9058494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0137252807617</t>
+    <t xml:space="preserve">24.0137271881104</t>
   </si>
   <si>
     <t xml:space="preserve">24.2712459564209</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">25.2001571655273</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2620487213135</t>
+    <t xml:space="preserve">24.2620468139648</t>
   </si>
   <si>
     <t xml:space="preserve">23.6734313964844</t>
@@ -3386,37 +3386,37 @@
     <t xml:space="preserve">23.6918258666992</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4251098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3055477142334</t>
+    <t xml:space="preserve">23.4251079559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.305549621582</t>
   </si>
   <si>
     <t xml:space="preserve">23.5170803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7837982177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1056957244873</t>
+    <t xml:space="preserve">23.7838001251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1056976318359</t>
   </si>
   <si>
     <t xml:space="preserve">24.1516857147217</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5287685394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8138771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8322715759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9886207580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4852676391602</t>
+    <t xml:space="preserve">24.5287647247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8138790130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8322734832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9886245727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4852695465088</t>
   </si>
   <si>
     <t xml:space="preserve">25.7703819274902</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">24.8414688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">24.694314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1081867218018</t>
+    <t xml:space="preserve">24.6943130493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1081829071045</t>
   </si>
   <si>
     <t xml:space="preserve">24.9518337249756</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3381118774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4919757843018</t>
+    <t xml:space="preserve">25.33811378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4919776916504</t>
   </si>
   <si>
     <t xml:space="preserve">24.5379638671875</t>
@@ -3449,10 +3449,10 @@
     <t xml:space="preserve">24.4367923736572</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9861354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9585437774658</t>
+    <t xml:space="preserve">23.9861373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9585456848145</t>
   </si>
   <si>
     <t xml:space="preserve">24.4000072479248</t>
@@ -3461,13 +3461,13 @@
     <t xml:space="preserve">23.9493465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7954845428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2252597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3197231292725</t>
+    <t xml:space="preserve">24.795482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2252616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3197212219238</t>
   </si>
   <si>
     <t xml:space="preserve">26.4693622589111</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">26.332389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5476913452148</t>
+    <t xml:space="preserve">26.5476894378662</t>
   </si>
   <si>
     <t xml:space="preserve">26.1826114654541</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">26.8753242492676</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3901786804199</t>
+    <t xml:space="preserve">27.3901767730713</t>
   </si>
   <si>
     <t xml:space="preserve">27.5867576599121</t>
@@ -3515,19 +3515,19 @@
     <t xml:space="preserve">27.7084503173828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8769454956055</t>
+    <t xml:space="preserve">27.8769474029541</t>
   </si>
   <si>
     <t xml:space="preserve">27.3340110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2872066497803</t>
+    <t xml:space="preserve">27.2872047424316</t>
   </si>
   <si>
     <t xml:space="preserve">27.3808155059814</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6990871429443</t>
+    <t xml:space="preserve">27.699089050293</t>
   </si>
   <si>
     <t xml:space="preserve">27.1935977935791</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">27.1655158996582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9237518310547</t>
+    <t xml:space="preserve">27.9237537384033</t>
   </si>
   <si>
     <t xml:space="preserve">27.8395042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">27.802059173584</t>
+    <t xml:space="preserve">27.8020610809326</t>
   </si>
   <si>
     <t xml:space="preserve">28.401159286499</t>
@@ -3563,16 +3563,16 @@
     <t xml:space="preserve">28.3169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5041351318359</t>
+    <t xml:space="preserve">28.5041332244873</t>
   </si>
   <si>
     <t xml:space="preserve">28.382438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4479656219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7568759918213</t>
+    <t xml:space="preserve">28.4479675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7568778991699</t>
   </si>
   <si>
     <t xml:space="preserve">27.9799175262451</t>
@@ -3581,13 +3581,13 @@
     <t xml:space="preserve">28.5696601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8317642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7943210601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.691349029541</t>
+    <t xml:space="preserve">28.83176612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7943229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6913509368896</t>
   </si>
   <si>
     <t xml:space="preserve">28.4198837280273</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">28.2701072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1390533447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2888317108154</t>
+    <t xml:space="preserve">28.1390514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2888298034668</t>
   </si>
   <si>
     <t xml:space="preserve">28.485408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3637180328369</t>
+    <t xml:space="preserve">28.3637161254883</t>
   </si>
   <si>
     <t xml:space="preserve">28.7849617004395</t>
@@ -3632,25 +3632,25 @@
     <t xml:space="preserve">28.8785705566406</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0002632141113</t>
+    <t xml:space="preserve">29.0002613067627</t>
   </si>
   <si>
     <t xml:space="preserve">29.3934211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2359104156494</t>
+    <t xml:space="preserve">30.2359085083008</t>
   </si>
   <si>
     <t xml:space="preserve">30.3201580047607</t>
   </si>
   <si>
-    <t xml:space="preserve">30.179744720459</t>
+    <t xml:space="preserve">30.1797466278076</t>
   </si>
   <si>
     <t xml:space="preserve">29.8146667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9925270080566</t>
+    <t xml:space="preserve">29.992525100708</t>
   </si>
   <si>
     <t xml:space="preserve">29.9550819396973</t>
@@ -3662,19 +3662,19 @@
     <t xml:space="preserve">29.5619220733643</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5057544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7585029602051</t>
+    <t xml:space="preserve">29.5057563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7585048675537</t>
   </si>
   <si>
     <t xml:space="preserve">29.805305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5806407928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8708324432373</t>
+    <t xml:space="preserve">29.5806427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8708305358887</t>
   </si>
   <si>
     <t xml:space="preserve">29.9082775115967</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">30.2171859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4044075012207</t>
+    <t xml:space="preserve">30.4044094085693</t>
   </si>
   <si>
     <t xml:space="preserve">30.385684967041</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">30.8630962371826</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8537330627441</t>
+    <t xml:space="preserve">30.8537311553955</t>
   </si>
   <si>
     <t xml:space="preserve">30.0018844604492</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">30.5448246002197</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4980182647705</t>
+    <t xml:space="preserve">30.4980201721191</t>
   </si>
   <si>
     <t xml:space="preserve">30.4699325561523</t>
@@ -3722,19 +3722,19 @@
     <t xml:space="preserve">29.6461696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3185348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0299682617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.348237991333</t>
+    <t xml:space="preserve">29.3185329437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0299701690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3482398986816</t>
   </si>
   <si>
     <t xml:space="preserve">29.6742534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9534587860107</t>
+    <t xml:space="preserve">28.9534568786621</t>
   </si>
   <si>
     <t xml:space="preserve">28.813045501709</t>
@@ -3746,10 +3746,10 @@
     <t xml:space="preserve">27.5212306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4837875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0267238616943</t>
+    <t xml:space="preserve">27.4837894439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.026725769043</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">29.2249240875244</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2717323303223</t>
+    <t xml:space="preserve">29.2717304229736</t>
   </si>
   <si>
     <t xml:space="preserve">29.2623691558838</t>
@@ -3773,13 +3773,13 @@
     <t xml:space="preserve">29.5244770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7304191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1610240936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4792957305908</t>
+    <t xml:space="preserve">29.7304210662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1610221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4792976379395</t>
   </si>
   <si>
     <t xml:space="preserve">30.5916290283203</t>
@@ -3788,28 +3788,28 @@
     <t xml:space="preserve">30.3669624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6384296417236</t>
+    <t xml:space="preserve">30.6384315490723</t>
   </si>
   <si>
     <t xml:space="preserve">30.6103477478027</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7694835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3030586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9286212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1626453399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.668140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8553562164307</t>
+    <t xml:space="preserve">30.7694816589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3030567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9286193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1626472473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6681365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.855354309082</t>
   </si>
   <si>
     <t xml:space="preserve">31.4341163635254</t>
@@ -3827,31 +3827,31 @@
     <t xml:space="preserve">31.9302444458008</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8101692199707</t>
+    <t xml:space="preserve">32.810173034668</t>
   </si>
   <si>
     <t xml:space="preserve">32.7633666992188</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6416778564453</t>
+    <t xml:space="preserve">32.6416816711426</t>
   </si>
   <si>
     <t xml:space="preserve">31.9489707946777</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6962203979492</t>
+    <t xml:space="preserve">31.6962223052979</t>
   </si>
   <si>
     <t xml:space="preserve">32.1081008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6945991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3124217987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7320423126221</t>
+    <t xml:space="preserve">30.6945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3124237060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7320404052734</t>
   </si>
   <si>
     <t xml:space="preserve">30.5822639465332</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">30.8911762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">31.752384185791</t>
+    <t xml:space="preserve">31.7523860931396</t>
   </si>
   <si>
     <t xml:space="preserve">30.9473457336426</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">30.3576030731201</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0861339569092</t>
+    <t xml:space="preserve">30.0861320495605</t>
   </si>
   <si>
     <t xml:space="preserve">30.1516590118408</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">30.7507629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9754257202148</t>
+    <t xml:space="preserve">30.9754238128662</t>
   </si>
   <si>
     <t xml:space="preserve">30.9379806518555</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">31.2656192779541</t>
   </si>
   <si>
-    <t xml:space="preserve">31.602611541748</t>
+    <t xml:space="preserve">31.6026096343994</t>
   </si>
   <si>
     <t xml:space="preserve">31.7804679870605</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">30.5073757171631</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9721813201904</t>
+    <t xml:space="preserve">28.9721794128418</t>
   </si>
   <si>
     <t xml:space="preserve">27.6335620880127</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">26.8378810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2045803070068</t>
+    <t xml:space="preserve">28.2045783996582</t>
   </si>
   <si>
     <t xml:space="preserve">28.0548057556152</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">26.248140335083</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7800941467285</t>
+    <t xml:space="preserve">25.7800922393799</t>
   </si>
   <si>
     <t xml:space="preserve">26.5102462768555</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3152904510498</t>
+    <t xml:space="preserve">27.3152885437012</t>
   </si>
   <si>
     <t xml:space="preserve">26.9970169067383</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">26.1077251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5399532318115</t>
+    <t xml:space="preserve">27.5399513244629</t>
   </si>
   <si>
     <t xml:space="preserve">28.541576385498</t>
@@ -3998,10 +3998,10 @@
     <t xml:space="preserve">25.9766712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1374320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9502105712891</t>
+    <t xml:space="preserve">27.1374340057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9502124786377</t>
   </si>
   <si>
     <t xml:space="preserve">28.728796005249</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">29.0377063751221</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1219577789307</t>
+    <t xml:space="preserve">29.121955871582</t>
   </si>
   <si>
     <t xml:space="preserve">29.1406764984131</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">28.2326622009277</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8692092895508</t>
+    <t xml:space="preserve">28.8692111968994</t>
   </si>
   <si>
     <t xml:space="preserve">29.0096225738525</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2904510498047</t>
+    <t xml:space="preserve">29.2904529571533</t>
   </si>
   <si>
     <t xml:space="preserve">28.981538772583</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">27.0531826019287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5586738586426</t>
+    <t xml:space="preserve">27.5586757659912</t>
   </si>
   <si>
     <t xml:space="preserve">28.8972930908203</t>
@@ -4091,10 +4091,10 @@
     <t xml:space="preserve">29.7605361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0265331268311</t>
+    <t xml:space="preserve">28.6452312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0265350341797</t>
   </si>
   <si>
     <t xml:space="preserve">29.045597076416</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">28.3211250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7482604980469</t>
+    <t xml:space="preserve">26.7482585906982</t>
   </si>
   <si>
     <t xml:space="preserve">27.0247020721436</t>
@@ -4115,22 +4115,22 @@
     <t xml:space="preserve">27.1104965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052742004395</t>
+    <t xml:space="preserve">26.6052722930908</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101306915283</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4146213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9675102233887</t>
+    <t xml:space="preserve">26.414623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.96750831604</t>
   </si>
   <si>
     <t xml:space="preserve">27.2153549194336</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7682399749756</t>
+    <t xml:space="preserve">27.768238067627</t>
   </si>
   <si>
     <t xml:space="preserve">27.5299263000488</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">27.8635654449463</t>
   </si>
   <si>
-    <t xml:space="preserve">27.730110168457</t>
+    <t xml:space="preserve">27.7301120758057</t>
   </si>
   <si>
     <t xml:space="preserve">28.2829971313477</t>
@@ -4151,16 +4151,16 @@
     <t xml:space="preserve">28.9788703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4459648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.654764175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9207630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2258014678955</t>
+    <t xml:space="preserve">29.4459629058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6547660827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9207611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2258033752441</t>
   </si>
   <si>
     <t xml:space="preserve">27.8063697814941</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">28.1304779052734</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4450492858887</t>
+    <t xml:space="preserve">28.4450511932373</t>
   </si>
   <si>
     <t xml:space="preserve">26.643404006958</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">26.3860263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6243381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7950077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.481351852417</t>
+    <t xml:space="preserve">26.6243362426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7950057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">26.2430381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1667785644531</t>
+    <t xml:space="preserve">26.1667766571045</t>
   </si>
   <si>
     <t xml:space="preserve">25.52809715271</t>
@@ -4211,10 +4211,10 @@
     <t xml:space="preserve">26.3002319335938</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9761257171631</t>
+    <t xml:space="preserve">26.4050884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9761276245117</t>
   </si>
   <si>
     <t xml:space="preserve">24.9847431182861</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">24.698766708374</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3374481201172</t>
+    <t xml:space="preserve">25.3374462127686</t>
   </si>
   <si>
     <t xml:space="preserve">25.9189319610596</t>
@@ -4241,19 +4241,19 @@
     <t xml:space="preserve">25.1658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">25.29931640625</t>
+    <t xml:space="preserve">25.2993183135986</t>
   </si>
   <si>
     <t xml:space="preserve">25.2230548858643</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4795207977295</t>
+    <t xml:space="preserve">24.4795188903809</t>
   </si>
   <si>
     <t xml:space="preserve">24.9084815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3469791412354</t>
+    <t xml:space="preserve">25.346981048584</t>
   </si>
   <si>
     <t xml:space="preserve">26.2144393920898</t>
@@ -4262,19 +4262,19 @@
     <t xml:space="preserve">25.9093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4908828735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0532989501953</t>
+    <t xml:space="preserve">26.4908809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0533008575439</t>
   </si>
   <si>
     <t xml:space="preserve">27.0437698364258</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6815319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2630176544189</t>
+    <t xml:space="preserve">26.6815338134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2630157470703</t>
   </si>
   <si>
     <t xml:space="preserve">28.7882213592529</t>
@@ -4283,13 +4283,13 @@
     <t xml:space="preserve">29.5031604766846</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4745616912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5508232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6461486816406</t>
+    <t xml:space="preserve">29.4745597839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5508213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.646146774292</t>
   </si>
   <si>
     <t xml:space="preserve">30.9044380187988</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">29.9797859191895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8939952850342</t>
+    <t xml:space="preserve">29.8939933776855</t>
   </si>
   <si>
     <t xml:space="preserve">31.0760250091553</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">29.5317573547363</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1790561676025</t>
+    <t xml:space="preserve">29.1790542602539</t>
   </si>
   <si>
     <t xml:space="preserve">29.1885871887207</t>
@@ -4361,13 +4361,13 @@
     <t xml:space="preserve">31.0664920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">31.590784072876</t>
+    <t xml:space="preserve">31.5907821655273</t>
   </si>
   <si>
     <t xml:space="preserve">30.5326709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3515567779541</t>
+    <t xml:space="preserve">30.3515548706055</t>
   </si>
   <si>
     <t xml:space="preserve">30.3896827697754</t>
@@ -4388,10 +4388,10 @@
     <t xml:space="preserve">28.0160865783691</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6166362762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6738300323486</t>
+    <t xml:space="preserve">28.6166343688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.673828125</t>
   </si>
   <si>
     <t xml:space="preserve">28.3020629882812</t>
@@ -4409,7 +4409,7 @@
     <t xml:space="preserve">30.0560474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5126895904541</t>
+    <t xml:space="preserve">29.5126914978027</t>
   </si>
   <si>
     <t xml:space="preserve">29.7128753662109</t>
@@ -4418,25 +4418,25 @@
     <t xml:space="preserve">29.6842765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2648468017578</t>
+    <t xml:space="preserve">29.2648487091064</t>
   </si>
   <si>
     <t xml:space="preserve">29.7033424377441</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3983020782471</t>
+    <t xml:space="preserve">29.3983039855957</t>
   </si>
   <si>
     <t xml:space="preserve">29.7700710296631</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7510032653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5422058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9616355895996</t>
+    <t xml:space="preserve">29.7510051727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5422077178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.961633682251</t>
   </si>
   <si>
     <t xml:space="preserve">30.4945430755615</t>
@@ -4454,13 +4454,13 @@
     <t xml:space="preserve">31.9434814453125</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9816150665283</t>
+    <t xml:space="preserve">31.981616973877</t>
   </si>
   <si>
     <t xml:space="preserve">31.7242336273193</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5717163085938</t>
+    <t xml:space="preserve">31.5717182159424</t>
   </si>
   <si>
     <t xml:space="preserve">31.4477977752686</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">31.6289119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8853778839111</t>
+    <t xml:space="preserve">30.8853759765625</t>
   </si>
   <si>
     <t xml:space="preserve">31.3715343475342</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">32.143669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8386325836182</t>
+    <t xml:space="preserve">31.8386287689209</t>
   </si>
   <si>
     <t xml:space="preserve">31.9244213104248</t>
@@ -4544,10 +4544,10 @@
     <t xml:space="preserve">33.8404579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5926132202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9167175292969</t>
+    <t xml:space="preserve">33.5926170349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9167213439941</t>
   </si>
   <si>
     <t xml:space="preserve">33.9357833862305</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">33.1445846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3543014526367</t>
+    <t xml:space="preserve">33.354305267334</t>
   </si>
   <si>
     <t xml:space="preserve">33.6116752624512</t>
@@ -4583,10 +4583,10 @@
     <t xml:space="preserve">33.6593399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0397262573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7260704040527</t>
+    <t xml:space="preserve">33.039722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7260665893555</t>
   </si>
   <si>
     <t xml:space="preserve">33.0587921142578</t>
@@ -4601,19 +4601,19 @@
     <t xml:space="preserve">33.373363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.953929901123</t>
+    <t xml:space="preserve">32.9539337158203</t>
   </si>
   <si>
     <t xml:space="preserve">33.3638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">33.411491394043</t>
+    <t xml:space="preserve">33.4114952087402</t>
   </si>
   <si>
     <t xml:space="preserve">33.583080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0311088562012</t>
+    <t xml:space="preserve">34.0311126708984</t>
   </si>
   <si>
     <t xml:space="preserve">34.7937126159668</t>
@@ -4622,10 +4622,10 @@
     <t xml:space="preserve">35.0892181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5649261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2512702941895</t>
+    <t xml:space="preserve">34.5649299621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2512741088867</t>
   </si>
   <si>
     <t xml:space="preserve">35.4323883056641</t>
@@ -4634,10 +4634,10 @@
     <t xml:space="preserve">35.8804168701172</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5372428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5753784179688</t>
+    <t xml:space="preserve">35.5372467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5753746032715</t>
   </si>
   <si>
     <t xml:space="preserve">35.7469596862793</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">36.109203338623</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9852752685547</t>
+    <t xml:space="preserve">35.985279083252</t>
   </si>
   <si>
     <t xml:space="preserve">35.7088317871094</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">36.1568641662598</t>
   </si>
   <si>
-    <t xml:space="preserve">35.937614440918</t>
+    <t xml:space="preserve">35.9376182556152</t>
   </si>
   <si>
     <t xml:space="preserve">35.270336151123</t>
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">34.5839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1454963684082</t>
+    <t xml:space="preserve">34.1455001831055</t>
   </si>
   <si>
     <t xml:space="preserve">34.8413734436035</t>
@@ -4703,7 +4703,7 @@
     <t xml:space="preserve">34.6697883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9557609558105</t>
+    <t xml:space="preserve">34.9557647705078</t>
   </si>
   <si>
     <t xml:space="preserve">34.6888542175293</t>
@@ -4715,10 +4715,10 @@
     <t xml:space="preserve">36.1282653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0615386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7097434997559</t>
+    <t xml:space="preserve">36.0615348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7097473144531</t>
   </si>
   <si>
     <t xml:space="preserve">37.8631858825684</t>
@@ -4739,16 +4739,16 @@
     <t xml:space="preserve">34.2312927246094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8881187438965</t>
+    <t xml:space="preserve">33.8881225585938</t>
   </si>
   <si>
     <t xml:space="preserve">34.3552131652832</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1082878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1178169250488</t>
+    <t xml:space="preserve">35.108283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1178131103516</t>
   </si>
   <si>
     <t xml:space="preserve">34.7746429443359</t>
@@ -4760,19 +4760,19 @@
     <t xml:space="preserve">36.3761100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5953598022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8908653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2235870361328</t>
+    <t xml:space="preserve">36.5953559875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8908615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2235908508301</t>
   </si>
   <si>
     <t xml:space="preserve">35.9566802978516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.946231842041</t>
+    <t xml:space="preserve">34.9462280273438</t>
   </si>
   <si>
     <t xml:space="preserve">35.3656616210938</t>
@@ -4784,7 +4784,7 @@
     <t xml:space="preserve">35.5086479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3847274780273</t>
+    <t xml:space="preserve">35.3847236633301</t>
   </si>
   <si>
     <t xml:space="preserve">35.9471435546875</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">36.5286293029785</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4618988037109</t>
+    <t xml:space="preserve">36.4619026184082</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807846069336</t>
@@ -4814,7 +4814,7 @@
     <t xml:space="preserve">35.0516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9039649963379</t>
+    <t xml:space="preserve">35.9039688110352</t>
   </si>
   <si>
     <t xml:space="preserve">36.2139015197754</t>
@@ -4832,16 +4832,16 @@
     <t xml:space="preserve">36.4947814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6521453857422</t>
+    <t xml:space="preserve">35.6521492004395</t>
   </si>
   <si>
     <t xml:space="preserve">35.3809509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0249900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2477531433105</t>
+    <t xml:space="preserve">34.0249938964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2477569580078</t>
   </si>
   <si>
     <t xml:space="preserve">34.6739158630371</t>
@@ -4883,25 +4883,25 @@
     <t xml:space="preserve">33.5794563293457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6642303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3518981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4995765686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4027214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4705200195312</t>
+    <t xml:space="preserve">34.664234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3518943786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4995727539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4027252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4705238342285</t>
   </si>
   <si>
     <t xml:space="preserve">34.62548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5770645141602</t>
+    <t xml:space="preserve">34.5770606994629</t>
   </si>
   <si>
     <t xml:space="preserve">35.6618309020996</t>
@@ -4919,28 +4919,28 @@
     <t xml:space="preserve">35.9620819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5649795532227</t>
+    <t xml:space="preserve">35.5649757385254</t>
   </si>
   <si>
     <t xml:space="preserve">34.9354209899902</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8579444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8312797546387</t>
+    <t xml:space="preserve">34.8579406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8312835693359</t>
   </si>
   <si>
     <t xml:space="preserve">34.8676261901855</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9523963928223</t>
+    <t xml:space="preserve">35.952392578125</t>
   </si>
   <si>
     <t xml:space="preserve">35.855541229248</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0759048461914</t>
+    <t xml:space="preserve">37.0759086608887</t>
   </si>
   <si>
     <t xml:space="preserve">36.8240852355957</t>
@@ -4955,10 +4955,10 @@
     <t xml:space="preserve">35.1678733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6812019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5456085205078</t>
+    <t xml:space="preserve">35.6812057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5456047058105</t>
   </si>
   <si>
     <t xml:space="preserve">36.5432052612305</t>
@@ -4967,13 +4967,13 @@
     <t xml:space="preserve">36.349494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8942832946777</t>
+    <t xml:space="preserve">35.894287109375</t>
   </si>
   <si>
     <t xml:space="preserve">35.739315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6230850219727</t>
+    <t xml:space="preserve">35.6230888366699</t>
   </si>
   <si>
     <t xml:space="preserve">35.5359191894531</t>
@@ -4982,7 +4982,7 @@
     <t xml:space="preserve">35.2259864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2550430297852</t>
+    <t xml:space="preserve">35.2550468444824</t>
   </si>
   <si>
     <t xml:space="preserve">34.7513999938965</t>
@@ -5003,19 +5003,19 @@
     <t xml:space="preserve">36.0492515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7029762268066</t>
+    <t xml:space="preserve">34.7029724121094</t>
   </si>
   <si>
     <t xml:space="preserve">34.4802055358887</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5383224487305</t>
+    <t xml:space="preserve">34.5383186340332</t>
   </si>
   <si>
     <t xml:space="preserve">34.2671279907227</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5480041503906</t>
+    <t xml:space="preserve">34.5480003356934</t>
   </si>
   <si>
     <t xml:space="preserve">33.8700256347656</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">34.7901382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1872482299805</t>
+    <t xml:space="preserve">35.1872444152832</t>
   </si>
   <si>
     <t xml:space="preserve">36.4463539123535</t>
@@ -5042,10 +5042,10 @@
     <t xml:space="preserve">36.6013221740723</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5625801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1364212036133</t>
+    <t xml:space="preserve">36.5625762939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.136417388916</t>
   </si>
   <si>
     <t xml:space="preserve">36.3010711669922</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">36.3398132324219</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5044631958008</t>
+    <t xml:space="preserve">36.504467010498</t>
   </si>
   <si>
     <t xml:space="preserve">36.7078590393066</t>
@@ -5069,22 +5069,22 @@
     <t xml:space="preserve">36.6497497558594</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7732620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9282302856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5408096313477</t>
+    <t xml:space="preserve">37.7732582092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9282264709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5408058166504</t>
   </si>
   <si>
     <t xml:space="preserve">37.4633255004883</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7635726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.359188079834</t>
+    <t xml:space="preserve">37.7635765075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3591842651367</t>
   </si>
   <si>
     <t xml:space="preserve">36.020191192627</t>
@@ -5096,16 +5096,16 @@
     <t xml:space="preserve">35.061336517334</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2913856506348</t>
+    <t xml:space="preserve">36.291389465332</t>
   </si>
   <si>
     <t xml:space="preserve">36.9499969482422</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0274772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1194458007812</t>
+    <t xml:space="preserve">37.0274810791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.119441986084</t>
   </si>
   <si>
     <t xml:space="preserve">36.0008201599121</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">34.3930358886719</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1000785827637</t>
+    <t xml:space="preserve">35.1000747680664</t>
   </si>
   <si>
     <t xml:space="preserve">34.4608383178711</t>
@@ -5141,13 +5141,13 @@
     <t xml:space="preserve">33.7150573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5310325622559</t>
+    <t xml:space="preserve">33.5310287475586</t>
   </si>
   <si>
     <t xml:space="preserve">32.7755661010742</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7271423339844</t>
+    <t xml:space="preserve">32.7271385192871</t>
   </si>
   <si>
     <t xml:space="preserve">32.7174530029297</t>
@@ -5159,16 +5159,16 @@
     <t xml:space="preserve">34.1799583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8022232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6836013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9547958374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7441139221191</t>
+    <t xml:space="preserve">33.8022270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6836051940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9547920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7441101074219</t>
   </si>
   <si>
     <t xml:space="preserve">33.8990783691406</t>
@@ -5186,16 +5186,16 @@
     <t xml:space="preserve">35.1581878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8482513427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3155555725098</t>
+    <t xml:space="preserve">34.8482551574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3155517578125</t>
   </si>
   <si>
     <t xml:space="preserve">33.8409652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4729194641113</t>
+    <t xml:space="preserve">33.4729232788086</t>
   </si>
   <si>
     <t xml:space="preserve">34.160587310791</t>
@@ -5210,10 +5210,10 @@
     <t xml:space="preserve">36.1945304870605</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3083572387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5795516967773</t>
+    <t xml:space="preserve">37.3083610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5795478820801</t>
   </si>
   <si>
     <t xml:space="preserve">37.6473503112793</t>
@@ -5234,7 +5234,7 @@
     <t xml:space="preserve">39.3713607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3229293823242</t>
+    <t xml:space="preserve">39.3229331970215</t>
   </si>
   <si>
     <t xml:space="preserve">39.410099029541</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">39.4585304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6134948730469</t>
+    <t xml:space="preserve">39.6134986877441</t>
   </si>
   <si>
     <t xml:space="preserve">39.1389083862305</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">39.8846893310547</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5553855895996</t>
+    <t xml:space="preserve">39.5553817749023</t>
   </si>
   <si>
     <t xml:space="preserve">39.4682159423828</t>
@@ -5285,7 +5285,7 @@
     <t xml:space="preserve">38.8870887756348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4197845458984</t>
+    <t xml:space="preserve">39.4197883605957</t>
   </si>
   <si>
     <t xml:space="preserve">38.8677177429199</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">39.264820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8096008300781</t>
+    <t xml:space="preserve">38.8096046447754</t>
   </si>
   <si>
     <t xml:space="preserve">39.4972686767578</t>
@@ -5303,7 +5303,7 @@
     <t xml:space="preserve">39.2745056152344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.749095916748</t>
+    <t xml:space="preserve">39.7490921020508</t>
   </si>
   <si>
     <t xml:space="preserve">38.9355125427246</t>
@@ -5312,13 +5312,13 @@
     <t xml:space="preserve">39.6425514221191</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7006645202637</t>
+    <t xml:space="preserve">39.7006683349609</t>
   </si>
   <si>
     <t xml:space="preserve">39.8168907165527</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0009155273438</t>
+    <t xml:space="preserve">40.0009117126465</t>
   </si>
   <si>
     <t xml:space="preserve">40.4173889160156</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">40.707950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6110992431641</t>
+    <t xml:space="preserve">40.6110954284668</t>
   </si>
   <si>
     <t xml:space="preserve">39.7103500366211</t>
@@ -5339,16 +5339,16 @@
     <t xml:space="preserve">41.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3254203796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8798904418945</t>
+    <t xml:space="preserve">42.3254241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8798942565918</t>
   </si>
   <si>
     <t xml:space="preserve">42.257625579834</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6934700012207</t>
+    <t xml:space="preserve">42.693473815918</t>
   </si>
   <si>
     <t xml:space="preserve">43.2358551025391</t>
@@ -5357,7 +5357,7 @@
     <t xml:space="preserve">43.8072967529297</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8968620300293</t>
+    <t xml:space="preserve">42.8968658447266</t>
   </si>
   <si>
     <t xml:space="preserve">42.906551361084</t>
@@ -5366,7 +5366,7 @@
     <t xml:space="preserve">43.4779891967773</t>
   </si>
   <si>
-    <t xml:space="preserve">44.601505279541</t>
+    <t xml:space="preserve">44.6015014648438</t>
   </si>
   <si>
     <t xml:space="preserve">44.5627593994141</t>
@@ -5381,10 +5381,10 @@
     <t xml:space="preserve">45.5022506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4925689697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3763389587402</t>
+    <t xml:space="preserve">45.4925651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.376335144043</t>
   </si>
   <si>
     <t xml:space="preserve">44.4465370178223</t>
@@ -5396,7 +5396,7 @@
     <t xml:space="preserve">45.8896713256836</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5870208740234</t>
+    <t xml:space="preserve">46.5870170593262</t>
   </si>
   <si>
     <t xml:space="preserve">46.112434387207</t>
@@ -5405,7 +5405,7 @@
     <t xml:space="preserve">46.4514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1875228881836</t>
+    <t xml:space="preserve">47.1875190734863</t>
   </si>
   <si>
     <t xml:space="preserve">47.8558158874512</t>
@@ -5414,10 +5414,10 @@
     <t xml:space="preserve">47.4683952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8364448547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2141761779785</t>
+    <t xml:space="preserve">47.8364410400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2141723632812</t>
   </si>
   <si>
     <t xml:space="preserve">48.1560668945312</t>
@@ -5426,28 +5426,28 @@
     <t xml:space="preserve">47.1487770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8679008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4126777648926</t>
+    <t xml:space="preserve">46.8678970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4126815795898</t>
   </si>
   <si>
     <t xml:space="preserve">46.548282623291</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7322998046875</t>
+    <t xml:space="preserve">46.7323036193848</t>
   </si>
   <si>
     <t xml:space="preserve">46.7226181030273</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6039962768555</t>
+    <t xml:space="preserve">47.6039924621582</t>
   </si>
   <si>
     <t xml:space="preserve">46.8097877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9938125610352</t>
+    <t xml:space="preserve">46.9938087463379</t>
   </si>
   <si>
     <t xml:space="preserve">46.6838760375977</t>
@@ -5459,10 +5459,10 @@
     <t xml:space="preserve">47.8654975891113</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6403388977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8146781921387</t>
+    <t xml:space="preserve">48.6403350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8146743774414</t>
   </si>
   <si>
     <t xml:space="preserve">48.6968154907227</t>
@@ -6453,6 +6453,9 @@
   </si>
   <si>
     <t xml:space="preserve">88.879997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5999984741211</t>
   </si>
 </sst>
 </file>
@@ -71583,7 +71586,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6506944444</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>656254</v>
@@ -71604,6 +71607,32 @@
         <v>2146</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6511921296</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>606905</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>89.3199996948242</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>88.1600036621094</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>88.879997253418</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>88.5999984741211</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>2147</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="2148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="2149">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6851539611816</t>
+    <t xml:space="preserve">15.6851577758789</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8714008331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3207597732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2397842407227</t>
+    <t xml:space="preserve">15.8714017868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.320761680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2397861480713</t>
   </si>
   <si>
     <t xml:space="preserve">14.74582862854</t>
@@ -59,79 +59,79 @@
     <t xml:space="preserve">14.9644660949707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2964677810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4989109039307</t>
+    <t xml:space="preserve">15.2964696884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.498908996582</t>
   </si>
   <si>
     <t xml:space="preserve">15.061637878418</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5028972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5433893203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8511009216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9401721954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4098339080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9239740371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2802762985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1831016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6243629455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936414718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8106079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7296314239502</t>
+    <t xml:space="preserve">14.5029020309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5433883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8510971069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870908737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9401712417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4098377227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9239749908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1831026077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6243619918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936395645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8106088638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7296342849731</t>
   </si>
   <si>
     <t xml:space="preserve">14.8996820449829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5190935134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7336225509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.344934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0980157852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3206396102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4744958877563</t>
+    <t xml:space="preserve">14.5190944671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7336206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3449354171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0980176925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3206415176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.474494934082</t>
   </si>
   <si>
     <t xml:space="preserve">13.8955736160278</t>
   </si>
   <si>
-    <t xml:space="preserve">13.782205581665</t>
+    <t xml:space="preserve">13.7822065353394</t>
   </si>
   <si>
     <t xml:space="preserve">14.3328485488892</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">14.405725479126</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8349018096924</t>
+    <t xml:space="preserve">14.8349027633667</t>
   </si>
   <si>
     <t xml:space="preserve">14.5514850616455</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3409481048584</t>
+    <t xml:space="preserve">14.3409471511841</t>
   </si>
   <si>
     <t xml:space="preserve">14.8672933578491</t>
@@ -158,40 +158,40 @@
     <t xml:space="preserve">15.1021251678467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2235889434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4827146530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3774461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017400741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4665193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4908151626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5232019424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636892318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426105499268</t>
+    <t xml:space="preserve">15.2235918045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4827127456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3774471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4017372131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4665212631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4908123016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5232009887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636911392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426115036011</t>
   </si>
   <si>
     <t xml:space="preserve">15.7742319107056</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8390092849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879821777344</t>
+    <t xml:space="preserve">15.8390121459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.587986946106</t>
   </si>
   <si>
     <t xml:space="preserve">15.6365699768066</t>
@@ -200,67 +200,67 @@
     <t xml:space="preserve">15.9199886322021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8309164047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8794975280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8228139877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8956937789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2762851715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1224308013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8471097946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8875970840454</t>
+    <t xml:space="preserve">15.8309154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8794994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8228178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8956956863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2762832641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1224327087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8471069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8875942230225</t>
   </si>
   <si>
     <t xml:space="preserve">15.4422245025635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3855428695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2276973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7135581970215</t>
+    <t xml:space="preserve">15.3855419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086757659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2276992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7135562896729</t>
   </si>
   <si>
     <t xml:space="preserve">16.6568737030029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.430139541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6120548248291</t>
+    <t xml:space="preserve">16.4301414489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6120567321777</t>
   </si>
   <si>
     <t xml:space="preserve">16.9179973602295</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0254974365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9758777618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9924182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6285915374756</t>
+    <t xml:space="preserve">17.0254955291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9758815765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9924201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.628589630127</t>
   </si>
   <si>
     <t xml:space="preserve">16.7774295806885</t>
@@ -272,37 +272,37 @@
     <t xml:space="preserve">17.1081829071045</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9345359802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5541744232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5955181121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.760892868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.703010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8766593933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4058589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7696876525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0094833374023</t>
+    <t xml:space="preserve">16.9345378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5541725158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.595516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7608909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7030124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8766555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4058609008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.009485244751</t>
   </si>
   <si>
     <t xml:space="preserve">17.9681396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8606472015381</t>
+    <t xml:space="preserve">17.8606491088867</t>
   </si>
   <si>
     <t xml:space="preserve">17.7779579162598</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">17.8854503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6952686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1087074279785</t>
+    <t xml:space="preserve">17.6952705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1087112426758</t>
   </si>
   <si>
     <t xml:space="preserve">17.9598712921143</t>
@@ -323,37 +323,37 @@
     <t xml:space="preserve">18.2658195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1748580932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2823543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2988948822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4725399017334</t>
+    <t xml:space="preserve">18.1748600006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.282356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2988929748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4725379943848</t>
   </si>
   <si>
     <t xml:space="preserve">18.1831302642822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1335144042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0425586700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8027610778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0921726226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9185256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0012168884277</t>
+    <t xml:space="preserve">18.1335182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0425624847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8027648925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0921745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9185237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0012149810791</t>
   </si>
   <si>
     <t xml:space="preserve">17.314905166626</t>
@@ -365,43 +365,43 @@
     <t xml:space="preserve">16.6368618011475</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8022384643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7366142272949</t>
+    <t xml:space="preserve">16.8022403717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7366123199463</t>
   </si>
   <si>
     <t xml:space="preserve">17.5712375640869</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3479824066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9102592468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6694087982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8342571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1402063369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2559719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399578094482</t>
+    <t xml:space="preserve">17.3479766845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9102611541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6694059371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8342580795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1402053833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2559661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399597167969</t>
   </si>
   <si>
     <t xml:space="preserve">16.2978382110596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7272911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5867223739624</t>
+    <t xml:space="preserve">15.7272901535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5867233276367</t>
   </si>
   <si>
     <t xml:space="preserve">15.2311611175537</t>
@@ -410,22 +410,22 @@
     <t xml:space="preserve">15.6115274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2813014984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4632129669189</t>
+    <t xml:space="preserve">16.2813034057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4632148742676</t>
   </si>
   <si>
     <t xml:space="preserve">16.6533985137939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6864738464355</t>
+    <t xml:space="preserve">16.6864719390869</t>
   </si>
   <si>
     <t xml:space="preserve">16.6782035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7443523406982</t>
+    <t xml:space="preserve">16.7443561553955</t>
   </si>
   <si>
     <t xml:space="preserve">16.6699352264404</t>
@@ -437,148 +437,148 @@
     <t xml:space="preserve">16.8187732696533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.951078414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0999145507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1164512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2983684539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2404861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0751075744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3314399719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6208477020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1004409790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.612585067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5960445404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0756378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7944984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8771820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1914005279541</t>
+    <t xml:space="preserve">16.9510746002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.099910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1164531707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2983665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2404842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0751094818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3314418792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6208534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1004428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5960426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0756340026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7944946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8771839141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1913986206055</t>
   </si>
   <si>
     <t xml:space="preserve">18.2492790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0839061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.290620803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1665897369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9929447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8441066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7200775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7283401489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8937187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0673675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.37331199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9438629150391</t>
+    <t xml:space="preserve">18.0839023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2906227111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1665954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9929466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.844108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7200756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7283458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8937206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0673656463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3733139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9438591003418</t>
   </si>
   <si>
     <t xml:space="preserve">19.4317226409912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3573036193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1009693145752</t>
+    <t xml:space="preserve">19.3572998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1009674072266</t>
   </si>
   <si>
     <t xml:space="preserve">19.1257762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1919250488281</t>
+    <t xml:space="preserve">19.1919231414795</t>
   </si>
   <si>
     <t xml:space="preserve">19.1753902435303</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2828826904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1340446472168</t>
+    <t xml:space="preserve">19.2828845977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1340427398682</t>
   </si>
   <si>
     <t xml:space="preserve">19.3490333557129</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978694915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.76247215271</t>
+    <t xml:space="preserve">19.4978675842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7624740600586</t>
   </si>
   <si>
     <t xml:space="preserve">19.6549797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">19.70458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4647941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0596237182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.646183013916</t>
+    <t xml:space="preserve">19.7045917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4647960662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.059627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6461887359619</t>
   </si>
   <si>
     <t xml:space="preserve">19.1175079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1588478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0100116729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7536773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.902515411377</t>
+    <t xml:space="preserve">19.1588516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0100135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7536792755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9025192260742</t>
   </si>
   <si>
     <t xml:space="preserve">19.0844306945801</t>
@@ -587,49 +587,49 @@
     <t xml:space="preserve">18.9934749603271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7950229644775</t>
+    <t xml:space="preserve">18.7950210571289</t>
   </si>
   <si>
     <t xml:space="preserve">18.7867546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7454071044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3319683074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6291198730469</t>
+    <t xml:space="preserve">18.7454109191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3319702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6291236877441</t>
   </si>
   <si>
     <t xml:space="preserve">18.869441986084</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1505794525146</t>
+    <t xml:space="preserve">19.1505832672119</t>
   </si>
   <si>
     <t xml:space="preserve">18.3485069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6627235412598</t>
+    <t xml:space="preserve">18.6627197265625</t>
   </si>
   <si>
     <t xml:space="preserve">18.728874206543</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6875247955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8942489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4229278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4808082580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2327442169189</t>
+    <t xml:space="preserve">18.6875286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8942470550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4229259490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.480806350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2327423095703</t>
   </si>
   <si>
     <t xml:space="preserve">18.3237018585205</t>
@@ -638,43 +638,43 @@
     <t xml:space="preserve">18.0590953826904</t>
   </si>
   <si>
-    <t xml:space="preserve">18.670991897583</t>
+    <t xml:space="preserve">18.6709899902344</t>
   </si>
   <si>
     <t xml:space="preserve">18.9355907440186</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4399909973145</t>
+    <t xml:space="preserve">19.4399890899658</t>
   </si>
   <si>
     <t xml:space="preserve">19.8782367706299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6797866821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1676445007324</t>
+    <t xml:space="preserve">19.6797828674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1676483154297</t>
   </si>
   <si>
     <t xml:space="preserve">19.8451633453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7790107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1428394317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9113159179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1759147644043</t>
+    <t xml:space="preserve">19.7790126800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1428413391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9113121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1759185791016</t>
   </si>
   <si>
     <t xml:space="preserve">20.0022678375244</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9278507232666</t>
+    <t xml:space="preserve">19.9278469085693</t>
   </si>
   <si>
     <t xml:space="preserve">20.0105400085449</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">19.8038196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1014938354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1262989044189</t>
+    <t xml:space="preserve">20.1014957427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1263027191162</t>
   </si>
   <si>
     <t xml:space="preserve">20.1097640991211</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">20.6389675140381</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1345729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2751426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2172565460205</t>
+    <t xml:space="preserve">20.1345710754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2751407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2172603607178</t>
   </si>
   <si>
     <t xml:space="preserve">20.3164863586426</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2420654296875</t>
+    <t xml:space="preserve">20.2420616149902</t>
   </si>
   <si>
     <t xml:space="preserve">20.3330230712891</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2255268096924</t>
+    <t xml:space="preserve">20.225528717041</t>
   </si>
   <si>
     <t xml:space="preserve">20.6555061340332</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">20.5066680908203</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3578281402588</t>
+    <t xml:space="preserve">20.3578319549561</t>
   </si>
   <si>
     <t xml:space="preserve">20.4818592071533</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">20.0849590301514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3991718292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645503997803</t>
+    <t xml:space="preserve">20.3991737365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5645484924316</t>
   </si>
   <si>
     <t xml:space="preserve">20.5397453308105</t>
@@ -749,55 +749,55 @@
     <t xml:space="preserve">19.894775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4074382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7133903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9697227478027</t>
+    <t xml:space="preserve">20.4074401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7133846282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9697208404541</t>
   </si>
   <si>
     <t xml:space="preserve">20.3495597839355</t>
   </si>
   <si>
-    <t xml:space="preserve">20.423978805542</t>
+    <t xml:space="preserve">20.4239807128906</t>
   </si>
   <si>
     <t xml:space="preserve">20.3082180023193</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7547302246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9609241485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8865032196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8286266326904</t>
+    <t xml:space="preserve">20.754732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9609260559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8865089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8286247253418</t>
   </si>
   <si>
     <t xml:space="preserve">19.8534336090088</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1180324554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5722904205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2994194030762</t>
+    <t xml:space="preserve">20.1180362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5722923278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2994213104248</t>
   </si>
   <si>
     <t xml:space="preserve">19.5144081115723</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5474853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4234523773193</t>
+    <t xml:space="preserve">19.5474834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.423454284668</t>
   </si>
   <si>
     <t xml:space="preserve">19.6136360168457</t>
@@ -809,22 +809,22 @@
     <t xml:space="preserve">19.3821105957031</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7376689910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3660984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9361171722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.200719833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4901313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7381916046143</t>
+    <t xml:space="preserve">19.7376670837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3661003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9361209869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2007217407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4901332855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7381954193115</t>
   </si>
   <si>
     <t xml:space="preserve">21.2922039031982</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">20.9366455078125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7795372009277</t>
+    <t xml:space="preserve">20.779541015625</t>
   </si>
   <si>
     <t xml:space="preserve">20.4570541381836</t>
@@ -848,28 +848,28 @@
     <t xml:space="preserve">20.7051181793213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1268272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0435562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1192531585693</t>
+    <t xml:space="preserve">21.1268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0435600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1192493438721</t>
   </si>
   <si>
     <t xml:space="preserve">21.8669414520264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9846878051758</t>
+    <t xml:space="preserve">21.9846858978271</t>
   </si>
   <si>
     <t xml:space="preserve">22.2958679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4724864959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2201747894287</t>
+    <t xml:space="preserve">22.4724884033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2201728820801</t>
   </si>
   <si>
     <t xml:space="preserve">22.2622261047363</t>
@@ -881,67 +881,67 @@
     <t xml:space="preserve">22.5734100341797</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5986423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.808069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6987323760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0847759246826</t>
+    <t xml:space="preserve">22.5986404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8080654144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6987342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0847778320312</t>
   </si>
   <si>
     <t xml:space="preserve">21.3202667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9502124786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6390285491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4203586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5549221038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4539985656738</t>
+    <t xml:space="preserve">20.9502086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6390247344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4203605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5549240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4540004730225</t>
   </si>
   <si>
     <t xml:space="preserve">20.9670314788818</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1941108703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8576946258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1688785552979</t>
+    <t xml:space="preserve">21.19411277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8576984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1688823699951</t>
   </si>
   <si>
     <t xml:space="preserve">20.8324642181396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9586200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156452178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5978107452393</t>
+    <t xml:space="preserve">20.9586181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8156433105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5978088378906</t>
   </si>
   <si>
     <t xml:space="preserve">21.2613945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1015968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6819133758545</t>
+    <t xml:space="preserve">21.101598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6819114685059</t>
   </si>
   <si>
     <t xml:space="preserve">21.6146297454834</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">21.656681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8248901367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5473442077637</t>
+    <t xml:space="preserve">21.8248882293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5473461151123</t>
   </si>
   <si>
     <t xml:space="preserve">21.5725784301758</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">22.0351486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.858528137207</t>
+    <t xml:space="preserve">21.8585300445557</t>
   </si>
   <si>
     <t xml:space="preserve">21.9258136749268</t>
@@ -974,103 +974,103 @@
     <t xml:space="preserve">21.7828369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3211002349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4884738922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3875522613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1949481964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8501205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2454051971436</t>
+    <t xml:space="preserve">22.321102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4884757995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3875484466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1949424743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.850118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2454071044922</t>
   </si>
   <si>
     <t xml:space="preserve">22.0015068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3883819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538166046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5481815338135</t>
+    <t xml:space="preserve">22.3883838653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538185119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5481777191162</t>
   </si>
   <si>
     <t xml:space="preserve">22.5313587188721</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7668495178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0696201324463</t>
+    <t xml:space="preserve">22.7668476104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0696220397949</t>
   </si>
   <si>
     <t xml:space="preserve">22.5818214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8425426483154</t>
+    <t xml:space="preserve">22.8425407409668</t>
   </si>
   <si>
     <t xml:space="preserve">22.5650005340576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1444816589355</t>
+    <t xml:space="preserve">22.1444835662842</t>
   </si>
   <si>
     <t xml:space="preserve">22.2117671966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1865329742432</t>
+    <t xml:space="preserve">22.1865348815918</t>
   </si>
   <si>
     <t xml:space="preserve">22.5229511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7920837402344</t>
+    <t xml:space="preserve">22.7920799255371</t>
   </si>
   <si>
     <t xml:space="preserve">22.4220237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7500267028809</t>
+    <t xml:space="preserve">22.7500286102295</t>
   </si>
   <si>
     <t xml:space="preserve">22.9266452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.93505859375</t>
+    <t xml:space="preserve">22.9350566864014</t>
   </si>
   <si>
     <t xml:space="preserve">22.8593616485596</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7079753875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5902309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2369995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8417072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.161304473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3547420501709</t>
+    <t xml:space="preserve">22.7079734802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416191101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5902328491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2369976043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8417091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1613025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3547439575195</t>
   </si>
   <si>
     <t xml:space="preserve">22.3042774200439</t>
@@ -1079,70 +1079,70 @@
     <t xml:space="preserve">21.959451675415</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2285861968994</t>
+    <t xml:space="preserve">22.228588104248</t>
   </si>
   <si>
     <t xml:space="preserve">22.1108379364014</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9174003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3463287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4304351806641</t>
+    <t xml:space="preserve">21.9174022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3463325500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4304313659668</t>
   </si>
   <si>
     <t xml:space="preserve">22.825719833374</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4649085998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.633113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6751670837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6835784912109</t>
+    <t xml:space="preserve">23.4649066925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6331157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6751689910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6835803985596</t>
   </si>
   <si>
     <t xml:space="preserve">23.8097343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9106578826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9190654754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7508583068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8770141601562</t>
+    <t xml:space="preserve">23.9106616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9190673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7508602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8770179748535</t>
   </si>
   <si>
     <t xml:space="preserve">23.986349105835</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8938388824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.952709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9779396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8517894744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0368137359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4741535186768</t>
+    <t xml:space="preserve">23.8938369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9527111053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9779415130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8517837524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0368118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4741516113281</t>
   </si>
   <si>
     <t xml:space="preserve">24.3311748504639</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">24.3143558502197</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0536365509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9358901977539</t>
+    <t xml:space="preserve">24.0536346435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9358882904053</t>
   </si>
   <si>
     <t xml:space="preserve">23.8013229370117</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">24.0199928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1040992736816</t>
+    <t xml:space="preserve">24.104097366333</t>
   </si>
   <si>
     <t xml:space="preserve">24.5582580566406</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5077953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3564071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.398458480835</t>
+    <t xml:space="preserve">24.5077934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.356409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3984603881836</t>
   </si>
   <si>
     <t xml:space="preserve">24.9199028015137</t>
@@ -1187,19 +1187,19 @@
     <t xml:space="preserve">24.7937450408936</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6928195953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8946704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2310886383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1217479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1890335083008</t>
+    <t xml:space="preserve">24.6928215026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8946685791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2310829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1217517852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1890316009521</t>
   </si>
   <si>
     <t xml:space="preserve">24.8526210784912</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">23.5574245452881</t>
   </si>
   <si>
-    <t xml:space="preserve">23.389217376709</t>
+    <t xml:space="preserve">23.3892192840576</t>
   </si>
   <si>
     <t xml:space="preserve">23.5994739532471</t>
@@ -1220,25 +1220,25 @@
     <t xml:space="preserve">23.2125988006592</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9274826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.691987991333</t>
+    <t xml:space="preserve">23.9274787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6919898986816</t>
   </si>
   <si>
     <t xml:space="preserve">23.5406017303467</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5742435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3808059692383</t>
+    <t xml:space="preserve">23.5742416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3808078765869</t>
   </si>
   <si>
     <t xml:space="preserve">23.4144477844238</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5321922302246</t>
+    <t xml:space="preserve">23.5321941375732</t>
   </si>
   <si>
     <t xml:space="preserve">23.9695320129395</t>
@@ -1247,64 +1247,64 @@
     <t xml:space="preserve">22.9939289093018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6911582946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014148712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9771099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0443935394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0275707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0359783172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8930034637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6827449798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1789588928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2210102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1621360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2294178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0780296325684</t>
+    <t xml:space="preserve">22.6911544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014167785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.977108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0443916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.02756690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0359802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8930053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6827430725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1789569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2210121154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1621341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.229419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0780353546143</t>
   </si>
   <si>
     <t xml:space="preserve">22.8677711486816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0107498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1881980895996</t>
+    <t xml:space="preserve">23.0107517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1882019042969</t>
   </si>
   <si>
     <t xml:space="preserve">24.0031719207764</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1713790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2218456268311</t>
+    <t xml:space="preserve">24.1713771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2218418121338</t>
   </si>
   <si>
     <t xml:space="preserve">24.3900508880615</t>
@@ -1313,70 +1313,70 @@
     <t xml:space="preserve">24.4909725189209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8273868560791</t>
+    <t xml:space="preserve">24.8273887634277</t>
   </si>
   <si>
     <t xml:space="preserve">24.5246143341064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3395862579346</t>
+    <t xml:space="preserve">24.3395843505859</t>
   </si>
   <si>
     <t xml:space="preserve">24.305944442749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8686046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8349647521973</t>
+    <t xml:space="preserve">23.8686065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8349666595459</t>
   </si>
   <si>
     <t xml:space="preserve">23.2882919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9602890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6070537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4564990997314</t>
+    <t xml:space="preserve">22.9602870941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6070518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4564971923828</t>
   </si>
   <si>
     <t xml:space="preserve">22.7163867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4556636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0687885284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1781215667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0940189361572</t>
+    <t xml:space="preserve">22.4556617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0687942504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1781234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0940208435059</t>
   </si>
   <si>
     <t xml:space="preserve">21.908992767334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7996597290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6314487457275</t>
+    <t xml:space="preserve">21.7996578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6314506530762</t>
   </si>
   <si>
     <t xml:space="preserve">21.7912464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3631496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3967952728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2874603271484</t>
+    <t xml:space="preserve">22.3631477355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3967933654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2874584197998</t>
   </si>
   <si>
     <t xml:space="preserve">22.0856094360352</t>
@@ -1385,34 +1385,34 @@
     <t xml:space="preserve">21.6230411529541</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3454990386963</t>
+    <t xml:space="preserve">21.3455009460449</t>
   </si>
   <si>
     <t xml:space="preserve">21.4043712615967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4464244842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2950325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3370838165283</t>
+    <t xml:space="preserve">21.4464206695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2950344085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3370876312256</t>
   </si>
   <si>
     <t xml:space="preserve">21.7407855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7904148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3194351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7988243103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4035377502441</t>
+    <t xml:space="preserve">20.7904109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3194313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7988224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4035396575928</t>
   </si>
   <si>
     <t xml:space="preserve">20.5717430114746</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">20.8072338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0288734436035</t>
+    <t xml:space="preserve">21.0288715362549</t>
   </si>
   <si>
     <t xml:space="preserve">20.8919315338135</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">20.6351699829102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6180515289307</t>
+    <t xml:space="preserve">20.618049621582</t>
   </si>
   <si>
     <t xml:space="preserve">20.746431350708</t>
@@ -1448,28 +1448,28 @@
     <t xml:space="preserve">21.3883419036865</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9603996276855</t>
+    <t xml:space="preserve">20.9604034423828</t>
   </si>
   <si>
     <t xml:space="preserve">21.362663269043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5081596374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.884744644165</t>
+    <t xml:space="preserve">21.5081634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8847484588623</t>
   </si>
   <si>
     <t xml:space="preserve">21.7563648223877</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2270946502686</t>
+    <t xml:space="preserve">22.2270965576172</t>
   </si>
   <si>
     <t xml:space="preserve">22.9203586578369</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4153900146484</t>
+    <t xml:space="preserve">22.4153919219971</t>
   </si>
   <si>
     <t xml:space="preserve">22.4239501953125</t>
@@ -1481,115 +1481,115 @@
     <t xml:space="preserve">22.0987167358398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1072769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7392463684082</t>
+    <t xml:space="preserve">22.1072731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7392501831055</t>
   </si>
   <si>
     <t xml:space="preserve">21.2428436279297</t>
   </si>
   <si>
-    <t xml:space="preserve">21.45680809021</t>
+    <t xml:space="preserve">21.4568099975586</t>
   </si>
   <si>
     <t xml:space="preserve">21.4054584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.943286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1302051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1216449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3698463439941</t>
+    <t xml:space="preserve">20.9432830810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1302013397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.121639251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3698444366455</t>
   </si>
   <si>
     <t xml:space="preserve">21.268518447876</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3968982696533</t>
+    <t xml:space="preserve">21.396900177002</t>
   </si>
   <si>
     <t xml:space="preserve">21.336986541748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3797798156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0117530822754</t>
+    <t xml:space="preserve">21.3797817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0117511749268</t>
   </si>
   <si>
     <t xml:space="preserve">20.6779613494873</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1743717193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8063430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7977848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9960136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5423965454102</t>
+    <t xml:space="preserve">21.1743698120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8063449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7977828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9960117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5424003601074</t>
   </si>
   <si>
     <t xml:space="preserve">21.1914882659912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9090480804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4554328918457</t>
+    <t xml:space="preserve">20.909049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4554347991943</t>
   </si>
   <si>
     <t xml:space="preserve">19.6509113311768</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8563213348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8706893920898</t>
+    <t xml:space="preserve">19.8563232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8706874847412</t>
   </si>
   <si>
     <t xml:space="preserve">17.9305992126465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2729511260986</t>
+    <t xml:space="preserve">18.2729530334473</t>
   </si>
   <si>
     <t xml:space="preserve">17.4427490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2558364868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9355754852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6260833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2454204559326</t>
+    <t xml:space="preserve">18.2558307647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9355735778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6260852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2454166412354</t>
   </si>
   <si>
     <t xml:space="preserve">18.1657447814941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.156888961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8119926452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2280673980713</t>
+    <t xml:space="preserve">18.1568927764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8119888305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2280654907227</t>
   </si>
   <si>
     <t xml:space="preserve">18.9978981018066</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">19.1838035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2103614807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4139766693115</t>
+    <t xml:space="preserve">19.2103633880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4139747619629</t>
   </si>
   <si>
     <t xml:space="preserve">19.5202045440674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5113563537598</t>
+    <t xml:space="preserve">19.5113525390625</t>
   </si>
   <si>
     <t xml:space="preserve">19.5644721984863</t>
@@ -1625,46 +1625,46 @@
     <t xml:space="preserve">19.6352939605713</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4316806793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1395435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0687198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2369194030762</t>
+    <t xml:space="preserve">19.4316787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1395416259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0687217712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2369213104248</t>
   </si>
   <si>
     <t xml:space="preserve">19.6972618103027</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7503757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8034954071045</t>
+    <t xml:space="preserve">19.7503776550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8034934997559</t>
   </si>
   <si>
     <t xml:space="preserve">19.4405307769775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2900371551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5109977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3516521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8208465576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7765789031982</t>
+    <t xml:space="preserve">19.2900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0333080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5109996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3516502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8208427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7765808105469</t>
   </si>
   <si>
     <t xml:space="preserve">18.7942848205566</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">18.9182243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1129837036133</t>
+    <t xml:space="preserve">19.1129817962646</t>
   </si>
   <si>
     <t xml:space="preserve">19.4847984313965</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">19.5733242034912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2015075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2192134857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0952777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.696907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1218357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2546234130859</t>
+    <t xml:space="preserve">19.2015113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2192153930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0952758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6969051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1218338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2546253204346</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906734466553</t>
@@ -1712,22 +1712,22 @@
     <t xml:space="preserve">18.67919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6880531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1483955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9890480041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0510120391846</t>
+    <t xml:space="preserve">18.6880512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1483917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9890460968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0510139465332</t>
   </si>
   <si>
     <t xml:space="preserve">18.5995273590088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3427963256836</t>
+    <t xml:space="preserve">18.3427982330322</t>
   </si>
   <si>
     <t xml:space="preserve">18.431324005127</t>
@@ -1745,49 +1745,49 @@
     <t xml:space="preserve">17.4840869903564</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9001617431641</t>
+    <t xml:space="preserve">17.9001636505127</t>
   </si>
   <si>
     <t xml:space="preserve">17.417688369751</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325984954834</t>
+    <t xml:space="preserve">17.0325965881348</t>
   </si>
   <si>
     <t xml:space="preserve">16.6342277526855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4527435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9392871856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5719032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346876144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4656677246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7316055297852</t>
+    <t xml:space="preserve">16.4527473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9392881393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5719013214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.434684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4656686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7316036224365</t>
   </si>
   <si>
     <t xml:space="preserve">16.2712650299072</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7666597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2133674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.173529624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6777782440186</t>
+    <t xml:space="preserve">15.7666625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2133665084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1735305786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6777801513672</t>
   </si>
   <si>
     <t xml:space="preserve">14.2262907028198</t>
@@ -1796,28 +1796,28 @@
     <t xml:space="preserve">14.7840127944946</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6290893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.97434425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.071722984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1912336349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7179689407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.293399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8596124649048</t>
+    <t xml:space="preserve">14.6290884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743452072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0717239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.191237449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7179718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2933979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171581268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8596172332764</t>
   </si>
   <si>
     <t xml:space="preserve">16.0986366271973</t>
@@ -1826,25 +1826,25 @@
     <t xml:space="preserve">16.103063583374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7755136489868</t>
+    <t xml:space="preserve">15.7755146026611</t>
   </si>
   <si>
     <t xml:space="preserve">15.4169797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7887916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4833755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6910572052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2882595062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2041597366333</t>
+    <t xml:space="preserve">15.7887945175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4833745956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6910581588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2882604598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2041606903076</t>
   </si>
   <si>
     <t xml:space="preserve">13.8943147659302</t>
@@ -1853,34 +1853,34 @@
     <t xml:space="preserve">13.97398853302</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8766098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0802221298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9916944503784</t>
+    <t xml:space="preserve">13.8766107559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0802211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9916954040527</t>
   </si>
   <si>
     <t xml:space="preserve">13.7880821228027</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6243085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1554689407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3148193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.045166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254760742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1112051010132</t>
+    <t xml:space="preserve">13.6243076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1554698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3148174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0451679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254770278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1112060546875</t>
   </si>
   <si>
     <t xml:space="preserve">13.4959440231323</t>
@@ -1889,22 +1889,22 @@
     <t xml:space="preserve">13.367579460144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.252495765686</t>
+    <t xml:space="preserve">13.2524938583374</t>
   </si>
   <si>
     <t xml:space="preserve">14.0669431686401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7707319259644</t>
+    <t xml:space="preserve">14.7707328796387</t>
   </si>
   <si>
     <t xml:space="preserve">14.8415546417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6954860687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.651219367981</t>
+    <t xml:space="preserve">14.695484161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6512203216553</t>
   </si>
   <si>
     <t xml:space="preserve">14.8946723937988</t>
@@ -1916,13 +1916,13 @@
     <t xml:space="preserve">14.8813915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8282747268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9345083236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4479646682739</t>
+    <t xml:space="preserve">14.828275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9345064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4479656219482</t>
   </si>
   <si>
     <t xml:space="preserve">14.7131910324097</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">15.1558246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2886161804199</t>
+    <t xml:space="preserve">15.2886142730713</t>
   </si>
   <si>
     <t xml:space="preserve">15.6958389282227</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">16.3155288696289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4129085540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1163425445557</t>
+    <t xml:space="preserve">16.4129123687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.116340637207</t>
   </si>
   <si>
     <t xml:space="preserve">16.0145359039307</t>
@@ -1952,154 +1952,154 @@
     <t xml:space="preserve">15.802074432373</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1340503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2358531951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4793014526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4748802185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3376617431641</t>
+    <t xml:space="preserve">16.1340484619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2358551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4793033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4748783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3376598358154</t>
   </si>
   <si>
     <t xml:space="preserve">16.218147277832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2889709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5811080932617</t>
+    <t xml:space="preserve">16.288969039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5811100006104</t>
   </si>
   <si>
     <t xml:space="preserve">16.5412731170654</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7758674621582</t>
+    <t xml:space="preserve">16.7758693695068</t>
   </si>
   <si>
     <t xml:space="preserve">16.4881572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7935733795166</t>
+    <t xml:space="preserve">16.7935752868652</t>
   </si>
   <si>
     <t xml:space="preserve">16.6297988891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.926362991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9481420516968</t>
+    <t xml:space="preserve">16.9263668060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9481401443481</t>
   </si>
   <si>
     <t xml:space="preserve">15.9304361343384</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9614210128784</t>
+    <t xml:space="preserve">15.9614219665527</t>
   </si>
   <si>
     <t xml:space="preserve">16.5279941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5368480682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.67848777771</t>
+    <t xml:space="preserve">16.5368461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6784896850586</t>
   </si>
   <si>
     <t xml:space="preserve">16.5855350494385</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7139015197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1292667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5763273239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8197803497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0101108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8906002044678</t>
+    <t xml:space="preserve">16.7138977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1292676925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5763263702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8197784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0101070404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8906011581421</t>
   </si>
   <si>
     <t xml:space="preserve">15.8463373184204</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3992748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2930431365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9610662460327</t>
+    <t xml:space="preserve">15.3992767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.293041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9610652923584</t>
   </si>
   <si>
     <t xml:space="preserve">14.987624168396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8858194351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3767881393433</t>
+    <t xml:space="preserve">14.8858184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3767862319946</t>
   </si>
   <si>
     <t xml:space="preserve">14.4874467849731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6069564819336</t>
+    <t xml:space="preserve">14.6069574356079</t>
   </si>
   <si>
     <t xml:space="preserve">14.5626955032349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7795839309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4125547409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2222204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0540170669556</t>
+    <t xml:space="preserve">14.7795858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4125528335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2222194671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0540180206299</t>
   </si>
   <si>
     <t xml:space="preserve">14.9212284088135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.642370223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.930079460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8592596054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1868104934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0230321884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9477844238281</t>
+    <t xml:space="preserve">14.6423673629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300813674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8592586517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1868095397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0230340957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9477863311768</t>
   </si>
   <si>
     <t xml:space="preserve">14.4476089477539</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2436418533325</t>
+    <t xml:space="preserve">13.2436408996582</t>
   </si>
   <si>
     <t xml:space="preserve">13.5534858703613</t>
@@ -2111,82 +2111,82 @@
     <t xml:space="preserve">13.6420125961304</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1997337341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4564609527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4431838989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.682204246521</t>
+    <t xml:space="preserve">14.1997346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4564619064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4431829452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6822052001953</t>
   </si>
   <si>
     <t xml:space="preserve">14.8459796905518</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2177925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0495920181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2089414596558</t>
+    <t xml:space="preserve">15.217794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0495910644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2089395523071</t>
   </si>
   <si>
     <t xml:space="preserve">15.0318870544434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1823825836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4962997436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1820278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2000885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1381187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3151712417603</t>
+    <t xml:space="preserve">15.1823835372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.496298789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1820268630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2000875473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1381196975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3151721954346</t>
   </si>
   <si>
     <t xml:space="preserve">15.3063220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6467933654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3723621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.858904838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7748050689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.597749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7792301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5888986587524</t>
+    <t xml:space="preserve">14.6467952728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3723611831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7748041152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5977487564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7792291641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5888977050781</t>
   </si>
   <si>
     <t xml:space="preserve">13.6774234771729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2170848846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5313539505005</t>
+    <t xml:space="preserve">13.2170839309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5313529968262</t>
   </si>
   <si>
     <t xml:space="preserve">14.3502283096313</t>
@@ -2195,25 +2195,25 @@
     <t xml:space="preserve">14.3192434310913</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2705564498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353229522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9256544113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6600732803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7486000061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9079494476318</t>
+    <t xml:space="preserve">14.2705554962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6999101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353239059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9256553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6600713729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7486028671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9079504013062</t>
   </si>
   <si>
     <t xml:space="preserve">15.2266454696655</t>
@@ -2225,34 +2225,34 @@
     <t xml:space="preserve">15.91273021698</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0942115783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8584661483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9808702468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675308227539</t>
+    <t xml:space="preserve">16.0942134857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8584632873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9808712005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675327301025</t>
   </si>
   <si>
     <t xml:space="preserve">16.2302188873291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4568977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5838375091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5929069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6609077453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7243766784668</t>
+    <t xml:space="preserve">16.4568958282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5838394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5929050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.66090965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7243804931641</t>
   </si>
   <si>
     <t xml:space="preserve">16.7425136566162</t>
@@ -2261,37 +2261,37 @@
     <t xml:space="preserve">16.4115600585938</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6427764892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9827919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9419898986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0326633453369</t>
+    <t xml:space="preserve">16.6427745819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.982795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9419918060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0326614379883</t>
   </si>
   <si>
     <t xml:space="preserve">17.3092098236084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4542865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9646587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9555931091309</t>
+    <t xml:space="preserve">17.4542846679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.964656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9555912017822</t>
   </si>
   <si>
     <t xml:space="preserve">17.0462627410889</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0436477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0935192108154</t>
+    <t xml:space="preserve">18.0436515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0935211181641</t>
   </si>
   <si>
     <t xml:space="preserve">18.1116561889648</t>
@@ -2303,34 +2303,34 @@
     <t xml:space="preserve">17.1414699554443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.783317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9283905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5268249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1505393981934</t>
+    <t xml:space="preserve">16.7833156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9283885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5268211364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1505374908447</t>
   </si>
   <si>
     <t xml:space="preserve">16.996395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8875885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9601268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3726806640625</t>
+    <t xml:space="preserve">16.8875904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9601249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3726787567139</t>
   </si>
   <si>
     <t xml:space="preserve">16.7787818908691</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7923851013184</t>
+    <t xml:space="preserve">16.7923831939697</t>
   </si>
   <si>
     <t xml:space="preserve">16.7017116546631</t>
@@ -2339,28 +2339,28 @@
     <t xml:space="preserve">16.0307426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0715427398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6473083496094</t>
+    <t xml:space="preserve">16.0715446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.647310256958</t>
   </si>
   <si>
     <t xml:space="preserve">16.8150501251221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5948276519775</t>
+    <t xml:space="preserve">17.5948295593262</t>
   </si>
   <si>
     <t xml:space="preserve">17.3862819671631</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0054588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9782581329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2774772644043</t>
+    <t xml:space="preserve">17.0054626464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9782600402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2774753570557</t>
   </si>
   <si>
     <t xml:space="preserve">17.2276058197021</t>
@@ -2372,10 +2372,10 @@
     <t xml:space="preserve">18.0481853485107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.007381439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2068614959717</t>
+    <t xml:space="preserve">18.0073833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.206859588623</t>
   </si>
   <si>
     <t xml:space="preserve">18.7508888244629</t>
@@ -2384,43 +2384,43 @@
     <t xml:space="preserve">18.2975311279297</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3519325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2884635925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4244689941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9775657653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.050106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0410385131836</t>
+    <t xml:space="preserve">18.351936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2884654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4244728088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9775676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0501041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0410404205322</t>
   </si>
   <si>
     <t xml:space="preserve">18.3156661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7716388702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0617866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.880443572998</t>
+    <t xml:space="preserve">17.7716369628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0617847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8804416656494</t>
   </si>
   <si>
     <t xml:space="preserve">18.0889873504639</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9756469726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7353668212891</t>
+    <t xml:space="preserve">17.9756507873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7353649139404</t>
   </si>
   <si>
     <t xml:space="preserve">17.7217674255371</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">17.8623085021973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7126979827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0598621368408</t>
+    <t xml:space="preserve">17.7126998901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0598640441895</t>
   </si>
   <si>
     <t xml:space="preserve">17.0507984161377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.973726272583</t>
+    <t xml:space="preserve">16.9737243652344</t>
   </si>
   <si>
     <t xml:space="preserve">17.096134185791</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">16.8921203613281</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2366714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7671031951904</t>
+    <t xml:space="preserve">17.2366752624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7671012878418</t>
   </si>
   <si>
     <t xml:space="preserve">18.0753860473633</t>
@@ -2462,73 +2462,73 @@
     <t xml:space="preserve">18.5060749053955</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7236862182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7146224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2703304290771</t>
+    <t xml:space="preserve">18.723690032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.71462059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2703285217285</t>
   </si>
   <si>
     <t xml:space="preserve">18.1887264251709</t>
   </si>
   <si>
-    <t xml:space="preserve">18.57861328125</t>
+    <t xml:space="preserve">18.5786151885986</t>
   </si>
   <si>
     <t xml:space="preserve">18.9594345092773</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7690277099609</t>
+    <t xml:space="preserve">18.7690258026123</t>
   </si>
   <si>
     <t xml:space="preserve">18.7418231964111</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7780933380127</t>
+    <t xml:space="preserve">18.7780895233154</t>
   </si>
   <si>
     <t xml:space="preserve">19.2223834991455</t>
   </si>
   <si>
-    <t xml:space="preserve">19.712007522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5216026306152</t>
+    <t xml:space="preserve">19.7120094299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5216007232666</t>
   </si>
   <si>
     <t xml:space="preserve">19.81174659729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490642547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3130512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7962265014648</t>
+    <t xml:space="preserve">19.4490604400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3130531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7962245941162</t>
   </si>
   <si>
     <t xml:space="preserve">18.4970073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1732025146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.422550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8033714294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9121761322021</t>
+    <t xml:space="preserve">17.1732044219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4225521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8033695220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9121742248535</t>
   </si>
   <si>
     <t xml:space="preserve">18.039119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9892482757568</t>
+    <t xml:space="preserve">17.9892501831055</t>
   </si>
   <si>
     <t xml:space="preserve">18.0663166046143</t>
@@ -2537,10 +2537,10 @@
     <t xml:space="preserve">18.8596935272217</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9050312042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7599563598633</t>
+    <t xml:space="preserve">18.905029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7599582672119</t>
   </si>
   <si>
     <t xml:space="preserve">18.3791351318359</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">19.0863742828369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951808929443</t>
+    <t xml:space="preserve">19.1951789855957</t>
   </si>
   <si>
     <t xml:space="preserve">19.5760021209717</t>
@@ -2564,91 +2564,91 @@
     <t xml:space="preserve">19.6394729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4218597412109</t>
+    <t xml:space="preserve">19.4218578338623</t>
   </si>
   <si>
     <t xml:space="preserve">19.7392101287842</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9477558135986</t>
+    <t xml:space="preserve">19.94775390625</t>
   </si>
   <si>
     <t xml:space="preserve">20.0021572113037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8661499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4853286743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6757392883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2133178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1679763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3221206665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0319709777832</t>
+    <t xml:space="preserve">19.8661479949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.485330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6757411956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2133140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1679801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3221225738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0319728851318</t>
   </si>
   <si>
     <t xml:space="preserve">19.2949199676514</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2677192687988</t>
+    <t xml:space="preserve">19.2677154541016</t>
   </si>
   <si>
     <t xml:space="preserve">19.5941371917725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.857084274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4127902984619</t>
+    <t xml:space="preserve">19.8570804595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4127922058105</t>
   </si>
   <si>
     <t xml:space="preserve">18.9957046508789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6602191925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5332794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9322319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4762630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0474948883057</t>
+    <t xml:space="preserve">18.6602172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5332775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9322338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4762649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.047492980957</t>
   </si>
   <si>
     <t xml:space="preserve">20.0112247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9658889770508</t>
+    <t xml:space="preserve">19.9658908843994</t>
   </si>
   <si>
     <t xml:space="preserve">20.3376445770264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9088745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.325963973999</t>
+    <t xml:space="preserve">20.9088726043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3259658813477</t>
   </si>
   <si>
     <t xml:space="preserve">21.5526428222656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0332050323486</t>
+    <t xml:space="preserve">22.0332012176514</t>
   </si>
   <si>
     <t xml:space="preserve">21.697717666626</t>
@@ -2657,97 +2657,97 @@
     <t xml:space="preserve">22.4049549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8337249755859</t>
+    <t xml:space="preserve">21.8337230682373</t>
   </si>
   <si>
     <t xml:space="preserve">20.9814109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9930877685547</t>
+    <t xml:space="preserve">19.9930896759033</t>
   </si>
   <si>
     <t xml:space="preserve">20.192569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3039894104004</t>
+    <t xml:space="preserve">19.3039855957031</t>
   </si>
   <si>
     <t xml:space="preserve">19.3855895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4607429504395</t>
+    <t xml:space="preserve">18.4607391357422</t>
   </si>
   <si>
     <t xml:space="preserve">18.6511516571045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.623950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0300521850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8195838928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4685764312744</t>
+    <t xml:space="preserve">18.6239490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.03005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8195819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.468578338623</t>
   </si>
   <si>
     <t xml:space="preserve">14.6842670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">14.811206817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6532230377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.741283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7775526046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3170490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7341384887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1648292541504</t>
+    <t xml:space="preserve">14.8112077713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.653223991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7412824630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.777551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3170480728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7341365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1648273468018</t>
   </si>
   <si>
     <t xml:space="preserve">13.6914138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0903673171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690992355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0242872238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0061502456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2354431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8863582611084</t>
+    <t xml:space="preserve">14.090368270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.269100189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0242862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0061511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2354440689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8863573074341</t>
   </si>
   <si>
     <t xml:space="preserve">13.238055229187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4783363342285</t>
+    <t xml:space="preserve">13.4783344268799</t>
   </si>
   <si>
     <t xml:space="preserve">13.5327386856079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9660406112671</t>
+    <t xml:space="preserve">12.9660415649414</t>
   </si>
   <si>
     <t xml:space="preserve">13.4511346817017</t>
@@ -2756,10 +2756,10 @@
     <t xml:space="preserve">13.8092861175537</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1901073455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2581119537354</t>
+    <t xml:space="preserve">14.1901082992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.258111000061</t>
   </si>
   <si>
     <t xml:space="preserve">13.3695297241211</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">13.8727569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9634284973145</t>
+    <t xml:space="preserve">13.9634275436401</t>
   </si>
   <si>
     <t xml:space="preserve">13.7820844650269</t>
@@ -2777,31 +2777,31 @@
     <t xml:space="preserve">14.2943801879883</t>
   </si>
   <si>
-    <t xml:space="preserve">14.448522567749</t>
+    <t xml:space="preserve">14.4485235214233</t>
   </si>
   <si>
     <t xml:space="preserve">14.5346603393555</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1512279510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3643035888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6544551849365</t>
+    <t xml:space="preserve">15.1512269973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3643064498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6544532775879</t>
   </si>
   <si>
     <t xml:space="preserve">15.5683164596558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.346170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6291732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7768602371216</t>
+    <t xml:space="preserve">15.3461713790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6291751861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7768573760986</t>
   </si>
   <si>
     <t xml:space="preserve">15.7904615402222</t>
@@ -2810,31 +2810,31 @@
     <t xml:space="preserve">16.4478302001953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3752918243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.109733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0398082733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2446346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4030933380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.88134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.706600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2906188964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.699893951416</t>
+    <t xml:space="preserve">16.3752899169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1097354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0398101806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2446327209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4030952453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8813457489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7066040039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2906169891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6998920440674</t>
   </si>
   <si>
     <t xml:space="preserve">17.9896011352539</t>
@@ -2843,22 +2843,22 @@
     <t xml:space="preserve">17.4515686035156</t>
   </si>
   <si>
-    <t xml:space="preserve">17.658504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6079216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3549995422363</t>
+    <t xml:space="preserve">17.6585083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6079196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.355001449585</t>
   </si>
   <si>
     <t xml:space="preserve">17.6309127807617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9850025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8884315490723</t>
+    <t xml:space="preserve">17.9850044250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8884353637695</t>
   </si>
   <si>
     <t xml:space="preserve">18.6334018707275</t>
@@ -2867,31 +2867,31 @@
     <t xml:space="preserve">18.7529640197754</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8081493377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6701889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7090892791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6631031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4745616912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3482894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885093688965</t>
+    <t xml:space="preserve">18.8081474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.67018699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7090873718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6631050109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4745597839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3482913970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885055541992</t>
   </si>
   <si>
     <t xml:space="preserve">18.5874137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9093151092529</t>
+    <t xml:space="preserve">18.9093132019043</t>
   </si>
   <si>
     <t xml:space="preserve">18.8173427581787</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">18.7161750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9645004272461</t>
+    <t xml:space="preserve">18.9644985198975</t>
   </si>
   <si>
     <t xml:space="preserve">18.7897529602051</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">19.0104846954346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0748653411865</t>
+    <t xml:space="preserve">19.0748634338379</t>
   </si>
   <si>
     <t xml:space="preserve">19.5715103149414</t>
@@ -2927,52 +2927,52 @@
     <t xml:space="preserve">19.9577884674072</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6542854309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9301986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4703407287598</t>
+    <t xml:space="preserve">19.6542835235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278614044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.930196762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4703388214111</t>
   </si>
   <si>
     <t xml:space="preserve">20.0957450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2704925537109</t>
+    <t xml:space="preserve">20.2704906463623</t>
   </si>
   <si>
     <t xml:space="preserve">20.3256759643555</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1534175872803</t>
+    <t xml:space="preserve">21.1534156799316</t>
   </si>
   <si>
     <t xml:space="preserve">20.960277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3281650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0154609680176</t>
+    <t xml:space="preserve">21.3281631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0154628753662</t>
   </si>
   <si>
     <t xml:space="preserve">21.0430507659912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4912242889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2245044708252</t>
+    <t xml:space="preserve">20.4912223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2245063781738</t>
   </si>
   <si>
     <t xml:space="preserve">20.2337036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8934097290039</t>
+    <t xml:space="preserve">19.8934078216553</t>
   </si>
   <si>
     <t xml:space="preserve">20.8223190307617</t>
@@ -2981,28 +2981,28 @@
     <t xml:space="preserve">20.4176464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3808555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2061100006104</t>
+    <t xml:space="preserve">20.380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2061138153076</t>
   </si>
   <si>
     <t xml:space="preserve">20.5556049346924</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8775005340576</t>
+    <t xml:space="preserve">20.8775024414062</t>
   </si>
   <si>
     <t xml:space="preserve">21.0614452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7303504943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7579402923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7395458221436</t>
+    <t xml:space="preserve">20.7303466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7579383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7395439147949</t>
   </si>
   <si>
     <t xml:space="preserve">20.6291809082031</t>
@@ -3017,22 +3017,22 @@
     <t xml:space="preserve">21.4201354980469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4937133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9443740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5580921173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5213031768799</t>
+    <t xml:space="preserve">21.4937114715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9443683624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5580902099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5213012695312</t>
   </si>
   <si>
     <t xml:space="preserve">22.0271453857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6040782928467</t>
+    <t xml:space="preserve">21.604076385498</t>
   </si>
   <si>
     <t xml:space="preserve">21.8156108856201</t>
@@ -3041,19 +3041,19 @@
     <t xml:space="preserve">21.4109382629395</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7420310974121</t>
+    <t xml:space="preserve">21.7420330047607</t>
   </si>
   <si>
     <t xml:space="preserve">22.1191158294678</t>
   </si>
   <si>
-    <t xml:space="preserve">22.514591217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6341571807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5421848297119</t>
+    <t xml:space="preserve">22.5145931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6341552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5421867370605</t>
   </si>
   <si>
     <t xml:space="preserve">22.6433525085449</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">22.4410171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2294807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6709423065186</t>
+    <t xml:space="preserve">22.2294826507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6709442138672</t>
   </si>
   <si>
     <t xml:space="preserve">22.4870014190674</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">22.8732814788818</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8456878662109</t>
+    <t xml:space="preserve">22.8456935882568</t>
   </si>
   <si>
     <t xml:space="preserve">23.2135753631592</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2411670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6550369262695</t>
+    <t xml:space="preserve">23.2411689758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6550388336182</t>
   </si>
   <si>
     <t xml:space="preserve">23.5262794494629</t>
@@ -3107,16 +3107,16 @@
     <t xml:space="preserve">24.3356246948242</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3264312744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.875768661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1700801849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.599853515625</t>
+    <t xml:space="preserve">24.3264293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8757705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1700782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5998554229736</t>
   </si>
   <si>
     <t xml:space="preserve">22.6525478363037</t>
@@ -3128,25 +3128,25 @@
     <t xml:space="preserve">22.9560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1926937103271</t>
+    <t xml:space="preserve">22.1926918029785</t>
   </si>
   <si>
     <t xml:space="preserve">21.6684551239014</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1994018554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6500625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4661197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0823268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5881671905518</t>
+    <t xml:space="preserve">21.1993999481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6500644683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.466121673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0823287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5881690979004</t>
   </si>
   <si>
     <t xml:space="preserve">24.0413188934326</t>
@@ -3155,64 +3155,64 @@
     <t xml:space="preserve">23.0112400054932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1216049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6274471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2988395690918</t>
+    <t xml:space="preserve">23.121603012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2988414764404</t>
   </si>
   <si>
     <t xml:space="preserve">23.9677410125732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3607292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8665752410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9217567443848</t>
+    <t xml:space="preserve">23.3607311248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8665714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9217548370361</t>
   </si>
   <si>
     <t xml:space="preserve">23.9033603668213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4459915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0965023040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7403030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2277507781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8966541290283</t>
+    <t xml:space="preserve">24.4459934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0965003967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7403011322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2277488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8966503143311</t>
   </si>
   <si>
     <t xml:space="preserve">24.4092044830322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5471630096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.062198638916</t>
+    <t xml:space="preserve">24.5471611022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0622005462646</t>
   </si>
   <si>
     <t xml:space="preserve">24.5655536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6391353607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6023426055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8874568939209</t>
+    <t xml:space="preserve">24.6391334533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6023445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8874530792236</t>
   </si>
   <si>
     <t xml:space="preserve">25.3105239868164</t>
@@ -3227,40 +3227,40 @@
     <t xml:space="preserve">25.3840999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.503662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3749008178711</t>
+    <t xml:space="preserve">25.5036640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3749027252197</t>
   </si>
   <si>
     <t xml:space="preserve">25.7151966094971</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9359283447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6257152557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5613346099854</t>
+    <t xml:space="preserve">25.9359264373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6257133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5613327026367</t>
   </si>
   <si>
     <t xml:space="preserve">26.7452754974365</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8740367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0119934082031</t>
+    <t xml:space="preserve">26.8740348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0119953155518</t>
   </si>
   <si>
     <t xml:space="preserve">27.5546245574951</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2812004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9225101470947</t>
+    <t xml:space="preserve">28.2811985015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9225120544434</t>
   </si>
   <si>
     <t xml:space="preserve">28.0880584716797</t>
@@ -3272,37 +3272,37 @@
     <t xml:space="preserve">26.5521373748779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8715496063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1106719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8439598083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0279006958008</t>
+    <t xml:space="preserve">25.8715476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1106739044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8439559936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0279026031494</t>
   </si>
   <si>
     <t xml:space="preserve">25.7519855499268</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6876087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7127113342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2804412841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1449756622314</t>
+    <t xml:space="preserve">25.6876049041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7127094268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2804431915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1449737548828</t>
   </si>
   <si>
     <t xml:space="preserve">24.5011730194092</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0346069335938</t>
+    <t xml:space="preserve">25.0346088409424</t>
   </si>
   <si>
     <t xml:space="preserve">25.236946105957</t>
@@ -3311,49 +3311,49 @@
     <t xml:space="preserve">25.6968021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">26.046293258667</t>
+    <t xml:space="preserve">26.0462951660156</t>
   </si>
   <si>
     <t xml:space="preserve">25.9175338745117</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2854194641113</t>
+    <t xml:space="preserve">26.28542137146</t>
   </si>
   <si>
     <t xml:space="preserve">25.9267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9083385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1198711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0003108978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6600151062012</t>
+    <t xml:space="preserve">25.9083366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.119873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0003089904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9635200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6600131988525</t>
   </si>
   <si>
     <t xml:space="preserve">25.0530033111572</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5931453704834</t>
+    <t xml:space="preserve">24.593147277832</t>
   </si>
   <si>
     <t xml:space="preserve">24.3908100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1608810424805</t>
+    <t xml:space="preserve">24.1608791351318</t>
   </si>
   <si>
     <t xml:space="preserve">24.5563583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5195693969727</t>
+    <t xml:space="preserve">24.5195713043213</t>
   </si>
   <si>
     <t xml:space="preserve">25.0162162780762</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">24.0137271881104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2712459564209</t>
+    <t xml:space="preserve">24.2712478637695</t>
   </si>
   <si>
     <t xml:space="preserve">25.2001571655273</t>
@@ -3380,16 +3380,16 @@
     <t xml:space="preserve">23.6734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5446739196777</t>
+    <t xml:space="preserve">23.5446720123291</t>
   </si>
   <si>
     <t xml:space="preserve">23.6918258666992</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4251079559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.305549621582</t>
+    <t xml:space="preserve">23.4251098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3055477142334</t>
   </si>
   <si>
     <t xml:space="preserve">23.5170803070068</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">24.1056976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1516857147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5287647247314</t>
+    <t xml:space="preserve">24.151683807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5287685394287</t>
   </si>
   <si>
     <t xml:space="preserve">24.8138790130615</t>
@@ -3413,46 +3413,46 @@
     <t xml:space="preserve">24.8322734832764</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9886245727539</t>
+    <t xml:space="preserve">24.9886264801025</t>
   </si>
   <si>
     <t xml:space="preserve">25.4852695465088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7703819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6416206359863</t>
+    <t xml:space="preserve">25.7703800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6416187286377</t>
   </si>
   <si>
     <t xml:space="preserve">24.8414688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6943130493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1081829071045</t>
+    <t xml:space="preserve">24.6943168640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1081867218018</t>
   </si>
   <si>
     <t xml:space="preserve">24.9518337249756</t>
   </si>
   <si>
-    <t xml:space="preserve">25.33811378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4919776916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5379638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4367923736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9861373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9585456848145</t>
+    <t xml:space="preserve">25.3381156921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4919757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5379619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4367961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9861354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9585437774658</t>
   </si>
   <si>
     <t xml:space="preserve">24.4000072479248</t>
@@ -3464,13 +3464,13 @@
     <t xml:space="preserve">24.795482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2252616882324</t>
+    <t xml:space="preserve">24.2252635955811</t>
   </si>
   <si>
     <t xml:space="preserve">25.3197212219238</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4693622589111</t>
+    <t xml:space="preserve">26.4693641662598</t>
   </si>
   <si>
     <t xml:space="preserve">26.4325752258301</t>
@@ -3479,16 +3479,16 @@
     <t xml:space="preserve">26.2762222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">26.332389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5476894378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1826114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1919746398926</t>
+    <t xml:space="preserve">26.3323879241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5476913452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1826133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1919727325439</t>
   </si>
   <si>
     <t xml:space="preserve">26.5196075439453</t>
@@ -3497,16 +3497,16 @@
     <t xml:space="preserve">26.4259967803955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6693820953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753242492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3901767730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5867576599121</t>
+    <t xml:space="preserve">26.6693840026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753223419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3901786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5867595672607</t>
   </si>
   <si>
     <t xml:space="preserve">27.7926998138428</t>
@@ -3527,49 +3527,49 @@
     <t xml:space="preserve">27.3808155059814</t>
   </si>
   <si>
-    <t xml:space="preserve">27.699089050293</t>
+    <t xml:space="preserve">27.6990909576416</t>
   </si>
   <si>
     <t xml:space="preserve">27.1935977935791</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1655158996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9237537384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8395042419434</t>
+    <t xml:space="preserve">27.1655139923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9237518310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8395023345947</t>
   </si>
   <si>
     <t xml:space="preserve">27.8020610809326</t>
   </si>
   <si>
-    <t xml:space="preserve">28.401159286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5602970123291</t>
+    <t xml:space="preserve">28.4011611938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5602989196777</t>
   </si>
   <si>
     <t xml:space="preserve">28.3075504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6819896697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.298189163208</t>
+    <t xml:space="preserve">28.6819915771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2981910705566</t>
   </si>
   <si>
     <t xml:space="preserve">28.3169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5041332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.382438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4479675292969</t>
+    <t xml:space="preserve">28.5041313171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3824367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4479656219482</t>
   </si>
   <si>
     <t xml:space="preserve">28.7568778991699</t>
@@ -3578,22 +3578,22 @@
     <t xml:space="preserve">27.9799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5696601867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.83176612854</t>
+    <t xml:space="preserve">28.5696563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8317642211914</t>
   </si>
   <si>
     <t xml:space="preserve">28.7943229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6913509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4198837280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4760494232178</t>
+    <t xml:space="preserve">28.691349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.419885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4760475158691</t>
   </si>
   <si>
     <t xml:space="preserve">27.6710052490234</t>
@@ -3602,16 +3602,16 @@
     <t xml:space="preserve">28.1203327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8301429748535</t>
+    <t xml:space="preserve">27.8301410675049</t>
   </si>
   <si>
     <t xml:space="preserve">27.989278793335</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1671352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2701072692871</t>
+    <t xml:space="preserve">28.1671371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2701091766357</t>
   </si>
   <si>
     <t xml:space="preserve">28.1390514373779</t>
@@ -3620,13 +3620,13 @@
     <t xml:space="preserve">28.2888298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.485408782959</t>
+    <t xml:space="preserve">28.4854106903076</t>
   </si>
   <si>
     <t xml:space="preserve">28.3637161254883</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7849617004395</t>
+    <t xml:space="preserve">28.7849597930908</t>
   </si>
   <si>
     <t xml:space="preserve">28.8785705566406</t>
@@ -3635,10 +3635,10 @@
     <t xml:space="preserve">29.0002613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3934211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2359085083008</t>
+    <t xml:space="preserve">29.3934230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2359104156494</t>
   </si>
   <si>
     <t xml:space="preserve">30.3201580047607</t>
@@ -3647,16 +3647,16 @@
     <t xml:space="preserve">30.1797466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8146667480469</t>
+    <t xml:space="preserve">29.8146648406982</t>
   </si>
   <si>
     <t xml:space="preserve">29.992525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9550819396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8989143371582</t>
+    <t xml:space="preserve">29.9550800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8989162445068</t>
   </si>
   <si>
     <t xml:space="preserve">29.5619220733643</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">29.5057563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7585048675537</t>
+    <t xml:space="preserve">29.7585010528564</t>
   </si>
   <si>
     <t xml:space="preserve">29.805305480957</t>
@@ -3674,19 +3674,19 @@
     <t xml:space="preserve">29.5806427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8708305358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9082775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8333892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2171859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4044094085693</t>
+    <t xml:space="preserve">29.8708343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.908275604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8333911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2171878814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4044075012207</t>
   </si>
   <si>
     <t xml:space="preserve">30.385684967041</t>
@@ -3695,34 +3695,34 @@
     <t xml:space="preserve">30.8630962371826</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8537311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0018844604492</t>
+    <t xml:space="preserve">30.8537330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0018863677979</t>
   </si>
   <si>
     <t xml:space="preserve">30.5448246002197</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4980201721191</t>
+    <t xml:space="preserve">30.4980182647705</t>
   </si>
   <si>
     <t xml:space="preserve">30.4699325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7133178710938</t>
+    <t xml:space="preserve">30.713321685791</t>
   </si>
   <si>
     <t xml:space="preserve">30.1142158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1891040802002</t>
+    <t xml:space="preserve">30.1891059875488</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3185329437256</t>
+    <t xml:space="preserve">29.3185367584229</t>
   </si>
   <si>
     <t xml:space="preserve">30.0299701690674</t>
@@ -3734,10 +3734,10 @@
     <t xml:space="preserve">29.6742534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9534568786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.813045501709</t>
+    <t xml:space="preserve">28.9534587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8130435943604</t>
   </si>
   <si>
     <t xml:space="preserve">28.2420253753662</t>
@@ -3746,22 +3746,22 @@
     <t xml:space="preserve">27.5212306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4837894439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.026725769043</t>
+    <t xml:space="preserve">27.4837875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0267219543457</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6616439819336</t>
+    <t xml:space="preserve">27.661642074585</t>
   </si>
   <si>
     <t xml:space="preserve">28.6445465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2249240875244</t>
+    <t xml:space="preserve">29.224925994873</t>
   </si>
   <si>
     <t xml:space="preserve">29.2717304229736</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">29.5244770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7304210662842</t>
+    <t xml:space="preserve">29.7304172515869</t>
   </si>
   <si>
     <t xml:space="preserve">30.1610221862793</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">30.4792976379395</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5916290283203</t>
+    <t xml:space="preserve">30.5916271209717</t>
   </si>
   <si>
     <t xml:space="preserve">30.3669624328613</t>
@@ -3791,22 +3791,22 @@
     <t xml:space="preserve">30.6384315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6103477478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694816589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3030567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9286193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1626472473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6681365966797</t>
+    <t xml:space="preserve">30.6103496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7694835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3030586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9286231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1626491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6681385040283</t>
   </si>
   <si>
     <t xml:space="preserve">31.855354309082</t>
@@ -3815,64 +3815,64 @@
     <t xml:space="preserve">31.4341163635254</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1813716888428</t>
+    <t xml:space="preserve">31.1813659667969</t>
   </si>
   <si>
     <t xml:space="preserve">31.2749767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8179130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9302444458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.810173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7633666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6416816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9489707946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6962223052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1081008911133</t>
+    <t xml:space="preserve">31.8179168701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9302406311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8101768493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.763370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6416778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9489688873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6962184906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1081047058105</t>
   </si>
   <si>
     <t xml:space="preserve">30.6945972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3124237060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7320404052734</t>
+    <t xml:space="preserve">31.3124198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7320442199707</t>
   </si>
   <si>
     <t xml:space="preserve">30.5822639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8911762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7523860931396</t>
+    <t xml:space="preserve">30.8911781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7523822784424</t>
   </si>
   <si>
     <t xml:space="preserve">30.9473457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7039566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3576030731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0861320495605</t>
+    <t xml:space="preserve">30.7039585113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3576049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0861339569092</t>
   </si>
   <si>
     <t xml:space="preserve">30.1516590118408</t>
@@ -3884,82 +3884,82 @@
     <t xml:space="preserve">29.702335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7507629394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9754238128662</t>
+    <t xml:space="preserve">30.7507610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9754276275635</t>
   </si>
   <si>
     <t xml:space="preserve">30.9379806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">31.069034576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9567031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9941501617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9660682678223</t>
+    <t xml:space="preserve">31.0690364837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9567050933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9941463470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9660663604736</t>
   </si>
   <si>
     <t xml:space="preserve">31.2936992645264</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2468929290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2656192779541</t>
+    <t xml:space="preserve">31.2468948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2656173706055</t>
   </si>
   <si>
     <t xml:space="preserve">31.6026096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7804679870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3779487609863</t>
+    <t xml:space="preserve">31.7804718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.377950668335</t>
   </si>
   <si>
     <t xml:space="preserve">30.5073757171631</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9721794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6335620880127</t>
+    <t xml:space="preserve">28.9721813201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6335639953613</t>
   </si>
   <si>
     <t xml:space="preserve">27.0063800811768</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0454444885254</t>
+    <t xml:space="preserve">28.0454425811768</t>
   </si>
   <si>
     <t xml:space="preserve">26.8378810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2045783996582</t>
+    <t xml:space="preserve">28.2045803070068</t>
   </si>
   <si>
     <t xml:space="preserve">28.0548057556152</t>
   </si>
   <si>
-    <t xml:space="preserve">27.118709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9298667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.042200088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8191566467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5664119720459</t>
+    <t xml:space="preserve">27.1187076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9298686981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0421962738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8191604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5664100646973</t>
   </si>
   <si>
     <t xml:space="preserve">26.248140335083</t>
@@ -3968,37 +3968,37 @@
     <t xml:space="preserve">25.7800922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5102462768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3152885437012</t>
+    <t xml:space="preserve">26.5102481842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3152904510498</t>
   </si>
   <si>
     <t xml:space="preserve">26.9970169067383</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1264457702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.229419708252</t>
+    <t xml:space="preserve">26.1264495849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2294178009033</t>
   </si>
   <si>
     <t xml:space="preserve">26.1077251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5399513244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.541576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4463424682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9766712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1374340057373</t>
+    <t xml:space="preserve">27.5399532318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5415744781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4463405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9766731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1374282836914</t>
   </si>
   <si>
     <t xml:space="preserve">26.9502124786377</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">27.5961170196533</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8863086700439</t>
+    <t xml:space="preserve">27.8863105773926</t>
   </si>
   <si>
     <t xml:space="preserve">28.6258239746094</t>
@@ -4019,34 +4019,34 @@
     <t xml:space="preserve">28.7100734710693</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0377063751221</t>
+    <t xml:space="preserve">29.0377082824707</t>
   </si>
   <si>
     <t xml:space="preserve">29.121955871582</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1406764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8598499298096</t>
+    <t xml:space="preserve">29.1406784057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8598480224609</t>
   </si>
   <si>
     <t xml:space="preserve">28.6071033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2326622009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8692111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0096225738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2904529571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.981538772583</t>
+    <t xml:space="preserve">28.2326641082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8692092895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0096244812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.290454864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9815406799316</t>
   </si>
   <si>
     <t xml:space="preserve">29.515115737915</t>
@@ -4058,22 +4058,22 @@
     <t xml:space="preserve">27.0531826019287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5586757659912</t>
+    <t xml:space="preserve">27.5586776733398</t>
   </si>
   <si>
     <t xml:space="preserve">28.8972930908203</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4666881561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4831790924072</t>
+    <t xml:space="preserve">28.4666900634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4831771850586</t>
   </si>
   <si>
     <t xml:space="preserve">29.32204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9312076568604</t>
+    <t xml:space="preserve">28.931209564209</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549480438232</t>
@@ -4082,19 +4082,19 @@
     <t xml:space="preserve">29.1981182098389</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2171840667725</t>
+    <t xml:space="preserve">29.2171821594238</t>
   </si>
   <si>
     <t xml:space="preserve">29.5222244262695</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7605361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6452312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0265350341797</t>
+    <t xml:space="preserve">29.7605381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6452331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0265331268311</t>
   </si>
   <si>
     <t xml:space="preserve">29.045597076416</t>
@@ -4106,40 +4106,40 @@
     <t xml:space="preserve">28.3211250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7482585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0247020721436</t>
+    <t xml:space="preserve">26.7482604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0247039794922</t>
   </si>
   <si>
     <t xml:space="preserve">27.1104965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052722930908</t>
+    <t xml:space="preserve">26.6052742004395</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101306915283</t>
   </si>
   <si>
-    <t xml:space="preserve">26.414623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.96750831604</t>
+    <t xml:space="preserve">26.4146213531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9675102233887</t>
   </si>
   <si>
     <t xml:space="preserve">27.2153549194336</t>
   </si>
   <si>
-    <t xml:space="preserve">27.768238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5299263000488</t>
+    <t xml:space="preserve">27.7682399749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5299282073975</t>
   </si>
   <si>
     <t xml:space="preserve">27.8635654449463</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7301120758057</t>
+    <t xml:space="preserve">27.7301082611084</t>
   </si>
   <si>
     <t xml:space="preserve">28.2829971313477</t>
@@ -4151,16 +4151,16 @@
     <t xml:space="preserve">28.9788703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4459629058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6547660827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9207611083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2258033752441</t>
+    <t xml:space="preserve">29.4459648132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6547622680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9207630157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2258014678955</t>
   </si>
   <si>
     <t xml:space="preserve">27.8063697814941</t>
@@ -4169,34 +4169,34 @@
     <t xml:space="preserve">28.397388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9684238433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1304779052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4450511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.643404006958</t>
+    <t xml:space="preserve">27.9684257507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1304759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4450492858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6434020996094</t>
   </si>
   <si>
     <t xml:space="preserve">26.3860263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6243362426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7950057983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4813499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2430381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1667766571045</t>
+    <t xml:space="preserve">26.6243381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7950077056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.481351852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2430362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1667785644531</t>
   </si>
   <si>
     <t xml:space="preserve">25.52809715271</t>
@@ -4211,16 +4211,16 @@
     <t xml:space="preserve">26.3002319335938</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4050884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9761276245117</t>
+    <t xml:space="preserve">26.4050903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9761257171631</t>
   </si>
   <si>
     <t xml:space="preserve">24.9847431182861</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7464294433594</t>
+    <t xml:space="preserve">24.746431350708</t>
   </si>
   <si>
     <t xml:space="preserve">24.765495300293</t>
@@ -4229,10 +4229,10 @@
     <t xml:space="preserve">24.393726348877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.698766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3374462127686</t>
+    <t xml:space="preserve">24.6987686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3374481201172</t>
   </si>
   <si>
     <t xml:space="preserve">25.9189319610596</t>
@@ -4247,13 +4247,13 @@
     <t xml:space="preserve">25.2230548858643</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4795188903809</t>
+    <t xml:space="preserve">24.4795207977295</t>
   </si>
   <si>
     <t xml:space="preserve">24.9084815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">25.346981048584</t>
+    <t xml:space="preserve">25.3469791412354</t>
   </si>
   <si>
     <t xml:space="preserve">26.2144393920898</t>
@@ -4262,19 +4262,19 @@
     <t xml:space="preserve">25.9093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4908809661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0533008575439</t>
+    <t xml:space="preserve">26.4908828735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0532989501953</t>
   </si>
   <si>
     <t xml:space="preserve">27.0437698364258</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6815338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2630157470703</t>
+    <t xml:space="preserve">26.6815319061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2630176544189</t>
   </si>
   <si>
     <t xml:space="preserve">28.7882213592529</t>
@@ -4283,13 +4283,13 @@
     <t xml:space="preserve">29.5031604766846</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4745597839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5508213043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.646146774292</t>
+    <t xml:space="preserve">29.4745616912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5508232116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6461486816406</t>
   </si>
   <si>
     <t xml:space="preserve">30.9044380187988</t>
@@ -4298,16 +4298,16 @@
     <t xml:space="preserve">29.9893169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9797859191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8939933776855</t>
+    <t xml:space="preserve">29.9797878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8939952850342</t>
   </si>
   <si>
     <t xml:space="preserve">31.0760250091553</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7051696777344</t>
+    <t xml:space="preserve">31.7051734924316</t>
   </si>
   <si>
     <t xml:space="preserve">30.7995834350586</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">30.4468803405762</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9997653961182</t>
+    <t xml:space="preserve">30.9997673034668</t>
   </si>
   <si>
     <t xml:space="preserve">30.551736831665</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">30.0274486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2371635437012</t>
+    <t xml:space="preserve">30.2371616363525</t>
   </si>
   <si>
     <t xml:space="preserve">30.5993995666504</t>
@@ -4340,10 +4340,10 @@
     <t xml:space="preserve">29.3792362213135</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5317573547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1790542602539</t>
+    <t xml:space="preserve">29.5317554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1790561676025</t>
   </si>
   <si>
     <t xml:space="preserve">29.1885871887207</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">29.4554977416992</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3610877990723</t>
+    <t xml:space="preserve">30.3610858917236</t>
   </si>
   <si>
     <t xml:space="preserve">30.7328567504883</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">31.0664920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5907821655273</t>
+    <t xml:space="preserve">31.5907802581787</t>
   </si>
   <si>
     <t xml:space="preserve">30.5326709747314</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">30.3515548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3896827697754</t>
+    <t xml:space="preserve">30.389684677124</t>
   </si>
   <si>
     <t xml:space="preserve">30.3038921356201</t>
@@ -4388,25 +4388,25 @@
     <t xml:space="preserve">28.0160865783691</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6166343688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.673828125</t>
+    <t xml:space="preserve">28.6166362762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6738319396973</t>
   </si>
   <si>
     <t xml:space="preserve">28.3020629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9865741729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2353343963623</t>
+    <t xml:space="preserve">26.986572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2353363037109</t>
   </si>
   <si>
     <t xml:space="preserve">28.492712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0560474395752</t>
+    <t xml:space="preserve">30.0560455322266</t>
   </si>
   <si>
     <t xml:space="preserve">29.5126914978027</t>
@@ -4418,28 +4418,28 @@
     <t xml:space="preserve">29.6842765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2648487091064</t>
+    <t xml:space="preserve">29.2648468017578</t>
   </si>
   <si>
     <t xml:space="preserve">29.7033424377441</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3983039855957</t>
+    <t xml:space="preserve">29.3983020782471</t>
   </si>
   <si>
     <t xml:space="preserve">29.7700710296631</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7510051727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5422077178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.961633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4945430755615</t>
+    <t xml:space="preserve">29.7510032653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5422058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9616355895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4945411682129</t>
   </si>
   <si>
     <t xml:space="preserve">30.6661262512207</t>
@@ -4454,13 +4454,13 @@
     <t xml:space="preserve">31.9434814453125</t>
   </si>
   <si>
-    <t xml:space="preserve">31.981616973877</t>
+    <t xml:space="preserve">31.9816188812256</t>
   </si>
   <si>
     <t xml:space="preserve">31.7242336273193</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5717182159424</t>
+    <t xml:space="preserve">31.5717163085938</t>
   </si>
   <si>
     <t xml:space="preserve">31.4477977752686</t>
@@ -4475,10 +4475,10 @@
     <t xml:space="preserve">30.5231399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9521045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5136051177979</t>
+    <t xml:space="preserve">30.9521026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">30.942569732666</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">31.6289119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8853759765625</t>
+    <t xml:space="preserve">30.8853778839111</t>
   </si>
   <si>
     <t xml:space="preserve">31.3715343475342</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">31.037899017334</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4763946533203</t>
+    <t xml:space="preserve">31.476390838623</t>
   </si>
   <si>
     <t xml:space="preserve">32.1913299560547</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">32.0769424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">32.105541229248</t>
+    <t xml:space="preserve">32.1055374145508</t>
   </si>
   <si>
     <t xml:space="preserve">32.1246032714844</t>
@@ -4529,22 +4529,22 @@
     <t xml:space="preserve">31.9244213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1341361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2675895690918</t>
+    <t xml:space="preserve">32.1341323852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2675933837891</t>
   </si>
   <si>
     <t xml:space="preserve">32.8300094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1064529418945</t>
+    <t xml:space="preserve">33.1064491271973</t>
   </si>
   <si>
     <t xml:space="preserve">33.8404579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5926170349121</t>
+    <t xml:space="preserve">33.5926132202148</t>
   </si>
   <si>
     <t xml:space="preserve">33.9167213439941</t>
@@ -4553,10 +4553,10 @@
     <t xml:space="preserve">33.9357833862305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1445846557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.354305267334</t>
+    <t xml:space="preserve">33.144588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3542976379395</t>
   </si>
   <si>
     <t xml:space="preserve">33.6116752624512</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">33.3161697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5544815063477</t>
+    <t xml:space="preserve">33.5544853210449</t>
   </si>
   <si>
     <t xml:space="preserve">33.6784057617188</t>
@@ -4580,13 +4580,13 @@
     <t xml:space="preserve">33.3066368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6593399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.039722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7260665893555</t>
+    <t xml:space="preserve">33.6593437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0397262573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7260704040527</t>
   </si>
   <si>
     <t xml:space="preserve">33.0587921142578</t>
@@ -4595,13 +4595,13 @@
     <t xml:space="preserve">32.2866554260254</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9729957580566</t>
+    <t xml:space="preserve">32.9729995727539</t>
   </si>
   <si>
     <t xml:space="preserve">33.373363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9539337158203</t>
+    <t xml:space="preserve">32.953929901123</t>
   </si>
   <si>
     <t xml:space="preserve">33.3638305664062</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">33.583080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0311126708984</t>
+    <t xml:space="preserve">34.0311088562012</t>
   </si>
   <si>
     <t xml:space="preserve">34.7937126159668</t>
@@ -4622,10 +4622,10 @@
     <t xml:space="preserve">35.0892181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5649299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2512741088867</t>
+    <t xml:space="preserve">34.5649261474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2512702941895</t>
   </si>
   <si>
     <t xml:space="preserve">35.4323883056641</t>
@@ -4637,7 +4637,7 @@
     <t xml:space="preserve">35.5372467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5753746032715</t>
+    <t xml:space="preserve">35.5753784179688</t>
   </si>
   <si>
     <t xml:space="preserve">35.7469596862793</t>
@@ -4649,10 +4649,10 @@
     <t xml:space="preserve">35.6516380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">36.109203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.985279083252</t>
+    <t xml:space="preserve">36.1091995239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9852752685547</t>
   </si>
   <si>
     <t xml:space="preserve">35.7088317871094</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">35.2036094665527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5944442749023</t>
+    <t xml:space="preserve">35.5944404602051</t>
   </si>
   <si>
     <t xml:space="preserve">34.9843635559082</t>
@@ -4673,13 +4673,13 @@
     <t xml:space="preserve">35.3370628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8327560424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1568641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9376182556152</t>
+    <t xml:space="preserve">35.8327522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1568603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9376106262207</t>
   </si>
   <si>
     <t xml:space="preserve">35.270336151123</t>
@@ -4694,16 +4694,16 @@
     <t xml:space="preserve">34.5839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1455001831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8413734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6697883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9557647705078</t>
+    <t xml:space="preserve">34.1454963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8413696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6697845458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9557609558105</t>
   </si>
   <si>
     <t xml:space="preserve">34.6888542175293</t>
@@ -4712,13 +4712,13 @@
     <t xml:space="preserve">36.1759262084961</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1282653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0615348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7097473144531</t>
+    <t xml:space="preserve">36.1282615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0615386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">37.8631858825684</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">33.7546653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2312927246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8881225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3552131652832</t>
+    <t xml:space="preserve">34.2312889099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8881187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3552169799805</t>
   </si>
   <si>
     <t xml:space="preserve">35.108283996582</t>
@@ -4757,46 +4757,46 @@
     <t xml:space="preserve">34.8509063720703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3761100769043</t>
+    <t xml:space="preserve">36.376106262207</t>
   </si>
   <si>
     <t xml:space="preserve">36.5953559875488</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8908615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2235908508301</t>
+    <t xml:space="preserve">36.890869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2235870361328</t>
   </si>
   <si>
     <t xml:space="preserve">35.9566802978516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9462280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3656616210938</t>
+    <t xml:space="preserve">34.946231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3656578063965</t>
   </si>
   <si>
     <t xml:space="preserve">35.4037895202637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5086479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3847236633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9471435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9090156555176</t>
+    <t xml:space="preserve">35.5086517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3847274780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9471473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9090118408203</t>
   </si>
   <si>
     <t xml:space="preserve">36.5286293029785</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4619026184082</t>
+    <t xml:space="preserve">36.4618988037109</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807846069336</t>
@@ -4814,7 +4814,7 @@
     <t xml:space="preserve">35.0516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9039688110352</t>
+    <t xml:space="preserve">35.9039649963379</t>
   </si>
   <si>
     <t xml:space="preserve">36.2139015197754</t>
@@ -4832,16 +4832,16 @@
     <t xml:space="preserve">36.4947814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6521492004395</t>
+    <t xml:space="preserve">35.6521453857422</t>
   </si>
   <si>
     <t xml:space="preserve">35.3809509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0249938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2477569580078</t>
+    <t xml:space="preserve">34.0249900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2477531433105</t>
   </si>
   <si>
     <t xml:space="preserve">34.6739158630371</t>
@@ -4883,25 +4883,25 @@
     <t xml:space="preserve">33.5794563293457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.664234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3518943786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4995727539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4027252197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4705238342285</t>
+    <t xml:space="preserve">34.6642303466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3518981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4995765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4027214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4705200195312</t>
   </si>
   <si>
     <t xml:space="preserve">34.62548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5770606994629</t>
+    <t xml:space="preserve">34.5770645141602</t>
   </si>
   <si>
     <t xml:space="preserve">35.6618309020996</t>
@@ -4919,28 +4919,28 @@
     <t xml:space="preserve">35.9620819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5649757385254</t>
+    <t xml:space="preserve">35.5649795532227</t>
   </si>
   <si>
     <t xml:space="preserve">34.9354209899902</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8579406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8312835693359</t>
+    <t xml:space="preserve">34.8579444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8312797546387</t>
   </si>
   <si>
     <t xml:space="preserve">34.8676261901855</t>
   </si>
   <si>
-    <t xml:space="preserve">35.952392578125</t>
+    <t xml:space="preserve">35.9523963928223</t>
   </si>
   <si>
     <t xml:space="preserve">35.855541229248</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0759086608887</t>
+    <t xml:space="preserve">37.0759048461914</t>
   </si>
   <si>
     <t xml:space="preserve">36.8240852355957</t>
@@ -4955,10 +4955,10 @@
     <t xml:space="preserve">35.1678733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6812057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5456047058105</t>
+    <t xml:space="preserve">35.6812019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5456085205078</t>
   </si>
   <si>
     <t xml:space="preserve">36.5432052612305</t>
@@ -4967,13 +4967,13 @@
     <t xml:space="preserve">36.349494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.894287109375</t>
+    <t xml:space="preserve">35.8942832946777</t>
   </si>
   <si>
     <t xml:space="preserve">35.739315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6230888366699</t>
+    <t xml:space="preserve">35.6230850219727</t>
   </si>
   <si>
     <t xml:space="preserve">35.5359191894531</t>
@@ -4982,7 +4982,7 @@
     <t xml:space="preserve">35.2259864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2550468444824</t>
+    <t xml:space="preserve">35.2550430297852</t>
   </si>
   <si>
     <t xml:space="preserve">34.7513999938965</t>
@@ -5003,19 +5003,19 @@
     <t xml:space="preserve">36.0492515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7029724121094</t>
+    <t xml:space="preserve">34.7029762268066</t>
   </si>
   <si>
     <t xml:space="preserve">34.4802055358887</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5383186340332</t>
+    <t xml:space="preserve">34.5383224487305</t>
   </si>
   <si>
     <t xml:space="preserve">34.2671279907227</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5480003356934</t>
+    <t xml:space="preserve">34.5480041503906</t>
   </si>
   <si>
     <t xml:space="preserve">33.8700256347656</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">34.7901382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1872444152832</t>
+    <t xml:space="preserve">35.1872482299805</t>
   </si>
   <si>
     <t xml:space="preserve">36.4463539123535</t>
@@ -5042,10 +5042,10 @@
     <t xml:space="preserve">36.6013221740723</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5625762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.136417388916</t>
+    <t xml:space="preserve">36.5625801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1364212036133</t>
   </si>
   <si>
     <t xml:space="preserve">36.3010711669922</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">36.3398132324219</t>
   </si>
   <si>
-    <t xml:space="preserve">36.504467010498</t>
+    <t xml:space="preserve">36.5044631958008</t>
   </si>
   <si>
     <t xml:space="preserve">36.7078590393066</t>
@@ -5069,22 +5069,22 @@
     <t xml:space="preserve">36.6497497558594</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7732582092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9282264709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5408058166504</t>
+    <t xml:space="preserve">37.7732620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9282302856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5408096313477</t>
   </si>
   <si>
     <t xml:space="preserve">37.4633255004883</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7635765075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3591842651367</t>
+    <t xml:space="preserve">37.7635726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.359188079834</t>
   </si>
   <si>
     <t xml:space="preserve">36.020191192627</t>
@@ -5096,16 +5096,16 @@
     <t xml:space="preserve">35.061336517334</t>
   </si>
   <si>
-    <t xml:space="preserve">36.291389465332</t>
+    <t xml:space="preserve">36.2913856506348</t>
   </si>
   <si>
     <t xml:space="preserve">36.9499969482422</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0274810791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.119441986084</t>
+    <t xml:space="preserve">37.0274772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1194458007812</t>
   </si>
   <si>
     <t xml:space="preserve">36.0008201599121</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">34.3930358886719</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1000747680664</t>
+    <t xml:space="preserve">35.1000785827637</t>
   </si>
   <si>
     <t xml:space="preserve">34.4608383178711</t>
@@ -5141,13 +5141,13 @@
     <t xml:space="preserve">33.7150573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5310287475586</t>
+    <t xml:space="preserve">33.5310325622559</t>
   </si>
   <si>
     <t xml:space="preserve">32.7755661010742</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7271385192871</t>
+    <t xml:space="preserve">32.7271423339844</t>
   </si>
   <si>
     <t xml:space="preserve">32.7174530029297</t>
@@ -5159,16 +5159,16 @@
     <t xml:space="preserve">34.1799583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8022270202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6836051940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9547920227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7441101074219</t>
+    <t xml:space="preserve">33.8022232055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6836013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9547958374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7441139221191</t>
   </si>
   <si>
     <t xml:space="preserve">33.8990783691406</t>
@@ -5186,16 +5186,16 @@
     <t xml:space="preserve">35.1581878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8482551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3155517578125</t>
+    <t xml:space="preserve">34.8482513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3155555725098</t>
   </si>
   <si>
     <t xml:space="preserve">33.8409652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4729232788086</t>
+    <t xml:space="preserve">33.4729194641113</t>
   </si>
   <si>
     <t xml:space="preserve">34.160587310791</t>
@@ -5210,10 +5210,10 @@
     <t xml:space="preserve">36.1945304870605</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3083610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5795478820801</t>
+    <t xml:space="preserve">37.3083572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5795516967773</t>
   </si>
   <si>
     <t xml:space="preserve">37.6473503112793</t>
@@ -5234,7 +5234,7 @@
     <t xml:space="preserve">39.3713607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3229331970215</t>
+    <t xml:space="preserve">39.3229293823242</t>
   </si>
   <si>
     <t xml:space="preserve">39.410099029541</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">39.4585304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6134986877441</t>
+    <t xml:space="preserve">39.6134948730469</t>
   </si>
   <si>
     <t xml:space="preserve">39.1389083862305</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">39.8846893310547</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5553817749023</t>
+    <t xml:space="preserve">39.5553855895996</t>
   </si>
   <si>
     <t xml:space="preserve">39.4682159423828</t>
@@ -5285,7 +5285,7 @@
     <t xml:space="preserve">38.8870887756348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4197883605957</t>
+    <t xml:space="preserve">39.4197845458984</t>
   </si>
   <si>
     <t xml:space="preserve">38.8677177429199</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">39.264820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8096046447754</t>
+    <t xml:space="preserve">38.8096008300781</t>
   </si>
   <si>
     <t xml:space="preserve">39.4972686767578</t>
@@ -5303,7 +5303,7 @@
     <t xml:space="preserve">39.2745056152344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7490921020508</t>
+    <t xml:space="preserve">39.749095916748</t>
   </si>
   <si>
     <t xml:space="preserve">38.9355125427246</t>
@@ -5312,13 +5312,13 @@
     <t xml:space="preserve">39.6425514221191</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7006683349609</t>
+    <t xml:space="preserve">39.7006645202637</t>
   </si>
   <si>
     <t xml:space="preserve">39.8168907165527</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0009117126465</t>
+    <t xml:space="preserve">40.0009155273438</t>
   </si>
   <si>
     <t xml:space="preserve">40.4173889160156</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">40.707950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6110954284668</t>
+    <t xml:space="preserve">40.6110992431641</t>
   </si>
   <si>
     <t xml:space="preserve">39.7103500366211</t>
@@ -5339,16 +5339,16 @@
     <t xml:space="preserve">41.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3254241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8798942565918</t>
+    <t xml:space="preserve">42.3254203796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8798904418945</t>
   </si>
   <si>
     <t xml:space="preserve">42.257625579834</t>
   </si>
   <si>
-    <t xml:space="preserve">42.693473815918</t>
+    <t xml:space="preserve">42.6934700012207</t>
   </si>
   <si>
     <t xml:space="preserve">43.2358551025391</t>
@@ -5357,7 +5357,7 @@
     <t xml:space="preserve">43.8072967529297</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8968658447266</t>
+    <t xml:space="preserve">42.8968620300293</t>
   </si>
   <si>
     <t xml:space="preserve">42.906551361084</t>
@@ -5366,7 +5366,7 @@
     <t xml:space="preserve">43.4779891967773</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6015014648438</t>
+    <t xml:space="preserve">44.601505279541</t>
   </si>
   <si>
     <t xml:space="preserve">44.5627593994141</t>
@@ -5381,10 +5381,10 @@
     <t xml:space="preserve">45.5022506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4925651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.376335144043</t>
+    <t xml:space="preserve">45.4925689697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3763389587402</t>
   </si>
   <si>
     <t xml:space="preserve">44.4465370178223</t>
@@ -5396,7 +5396,7 @@
     <t xml:space="preserve">45.8896713256836</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5870170593262</t>
+    <t xml:space="preserve">46.5870208740234</t>
   </si>
   <si>
     <t xml:space="preserve">46.112434387207</t>
@@ -5405,7 +5405,7 @@
     <t xml:space="preserve">46.4514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1875190734863</t>
+    <t xml:space="preserve">47.1875228881836</t>
   </si>
   <si>
     <t xml:space="preserve">47.8558158874512</t>
@@ -5414,10 +5414,10 @@
     <t xml:space="preserve">47.4683952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8364410400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2141723632812</t>
+    <t xml:space="preserve">47.8364448547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2141761779785</t>
   </si>
   <si>
     <t xml:space="preserve">48.1560668945312</t>
@@ -5426,28 +5426,28 @@
     <t xml:space="preserve">47.1487770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8678970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4126815795898</t>
+    <t xml:space="preserve">46.8679008483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4126777648926</t>
   </si>
   <si>
     <t xml:space="preserve">46.548282623291</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7323036193848</t>
+    <t xml:space="preserve">46.7322998046875</t>
   </si>
   <si>
     <t xml:space="preserve">46.7226181030273</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6039924621582</t>
+    <t xml:space="preserve">47.6039962768555</t>
   </si>
   <si>
     <t xml:space="preserve">46.8097877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9938087463379</t>
+    <t xml:space="preserve">46.9938125610352</t>
   </si>
   <si>
     <t xml:space="preserve">46.6838760375977</t>
@@ -5459,10 +5459,10 @@
     <t xml:space="preserve">47.8654975891113</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6403350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8146743774414</t>
+    <t xml:space="preserve">48.6403388977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8146781921387</t>
   </si>
   <si>
     <t xml:space="preserve">48.6968154907227</t>
@@ -6456,6 +6456,9 @@
   </si>
   <si>
     <t xml:space="preserve">88.5999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.120002746582</t>
   </si>
 </sst>
 </file>
@@ -71612,7 +71615,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6511921296</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>606905</v>
@@ -71633,6 +71636,32 @@
         <v>2147</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6519097222</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>1340727</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>90.5800018310547</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>85.5999984741211</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>88.879997253418</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>86.120002746582</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>2148</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6851577758789</t>
+    <t xml:space="preserve">15.685154914856</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8714017868042</t>
+    <t xml:space="preserve">15.8714008331299</t>
   </si>
   <si>
     <t xml:space="preserve">15.320761680603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2397861480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.74582862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9644660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2964696884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.498908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.061637878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5029020309448</t>
+    <t xml:space="preserve">15.239785194397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7458267211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9644641876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2964677810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.498911857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0616369247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5029001235962</t>
   </si>
   <si>
     <t xml:space="preserve">14.5433883666992</t>
@@ -80,160 +80,160 @@
     <t xml:space="preserve">14.1870908737183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9401712417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4098377227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9239749908447</t>
+    <t xml:space="preserve">14.9401721954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4098358154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.923975944519</t>
   </si>
   <si>
     <t xml:space="preserve">15.2802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1831026077271</t>
+    <t xml:space="preserve">15.1831016540527</t>
   </si>
   <si>
     <t xml:space="preserve">14.6243619918823</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3936395645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8106088638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7296342849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8996820449829</t>
+    <t xml:space="preserve">15.3936386108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8106079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7296314239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8996829986572</t>
   </si>
   <si>
     <t xml:space="preserve">14.5190944671631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7336206436157</t>
+    <t xml:space="preserve">13.73362159729</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449354171753</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0980176925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3206415176392</t>
+    <t xml:space="preserve">14.0980157852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3206396102905</t>
   </si>
   <si>
     <t xml:space="preserve">13.474494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8955736160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7822065353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3328485488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2194805145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.405725479126</t>
+    <t xml:space="preserve">13.8955755233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.782205581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3328475952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2194795608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057273864746</t>
   </si>
   <si>
     <t xml:space="preserve">14.8349027633667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5514850616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3409471511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8672933578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1021251678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235918045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4827127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3774471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4665212631226</t>
+    <t xml:space="preserve">14.5514841079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3409461975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8672914505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1021242141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2235908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4827136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3774452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4017391204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4665193557739</t>
   </si>
   <si>
     <t xml:space="preserve">15.4908123016357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5232009887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636911392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742319107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8390121459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.587986946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6365699768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9199886322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8309154510498</t>
+    <t xml:space="preserve">15.5232028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636920928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426124572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742300033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8390130996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.587984085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.636568069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9199876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8309125900269</t>
   </si>
   <si>
     <t xml:space="preserve">15.8794994354248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8228178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8956956863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2762832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1224327087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8471069335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8875942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4422245025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3855419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086757659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2276992797852</t>
+    <t xml:space="preserve">15.8228168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.895694732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2762851715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.122428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8471117019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8875961303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4422273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3855428695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2276973724365</t>
   </si>
   <si>
     <t xml:space="preserve">16.7135562896729</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">16.6568737030029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4301414489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6120567321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9179973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0254955291748</t>
+    <t xml:space="preserve">16.4301376342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6120529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9180011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0254936218262</t>
   </si>
   <si>
     <t xml:space="preserve">16.9758815765381</t>
@@ -260,55 +260,55 @@
     <t xml:space="preserve">16.9924201965332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.628589630127</t>
+    <t xml:space="preserve">16.6285934448242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7774295806885</t>
   </si>
   <si>
-    <t xml:space="preserve">16.98415184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1081829071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9345378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5541725158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.595516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7608909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7030124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8766555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4058609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7696914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.009485244751</t>
+    <t xml:space="preserve">16.9841499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1081809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9345397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5541763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5955200195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.760892868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7030143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8766536712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4058628082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0094833374023</t>
   </si>
   <si>
     <t xml:space="preserve">17.9681396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8606491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7779579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8854503631592</t>
+    <t xml:space="preserve">17.8606472015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7779560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8854522705078</t>
   </si>
   <si>
     <t xml:space="preserve">17.6952705383301</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">18.1087112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9598712921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2658195495605</t>
+    <t xml:space="preserve">17.9598731994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2658157348633</t>
   </si>
   <si>
     <t xml:space="preserve">18.1748600006104</t>
@@ -332,94 +332,94 @@
     <t xml:space="preserve">18.2988929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4725379943848</t>
+    <t xml:space="preserve">18.4725399017334</t>
   </si>
   <si>
     <t xml:space="preserve">18.1831302642822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1335182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0425624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8027648925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0921745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9185237884521</t>
+    <t xml:space="preserve">18.1335144042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0425605773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8027629852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0921726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9185256958008</t>
   </si>
   <si>
     <t xml:space="preserve">18.0012149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.314905166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9097328186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8022403717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7366123199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5712375640869</t>
+    <t xml:space="preserve">17.3149032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9097309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8022384643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7366161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5712394714355</t>
   </si>
   <si>
     <t xml:space="preserve">17.3479766845703</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9102611541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6694059371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8342580795288</t>
+    <t xml:space="preserve">17.9102573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6694087982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8342571258545</t>
   </si>
   <si>
     <t xml:space="preserve">15.1402053833008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2559661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2978382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7272901535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5867233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2311611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6115274429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2813034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6533985137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6864719390869</t>
+    <t xml:space="preserve">15.2559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2978401184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7272930145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5867214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2311601638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6115245819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2813014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4632129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6533946990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6864738464355</t>
   </si>
   <si>
     <t xml:space="preserve">16.6782035827637</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">16.6699352264404</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8435821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8187732696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9510746002197</t>
+    <t xml:space="preserve">16.8435802459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.818775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9510765075684</t>
   </si>
   <si>
     <t xml:space="preserve">17.099910736084</t>
@@ -452,73 +452,73 @@
     <t xml:space="preserve">17.2404842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0751094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3314418792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6208534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1004428863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125793457031</t>
+    <t xml:space="preserve">17.0751056671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3314399719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6208515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1004409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125812530518</t>
   </si>
   <si>
     <t xml:space="preserve">17.5960426330566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0756340026855</t>
+    <t xml:space="preserve">18.0756378173828</t>
   </si>
   <si>
     <t xml:space="preserve">17.7944946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8771839141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1913986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2492790222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0839023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2906227111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1665954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9929466247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.844108581543</t>
+    <t xml:space="preserve">17.8771858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1914024353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2492809295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0839042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2906265258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1665897369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9929504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8441104888916</t>
   </si>
   <si>
     <t xml:space="preserve">17.7200756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7283458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8937206268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0673656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3733139038086</t>
+    <t xml:space="preserve">17.7283420562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8937225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0673675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3733100891113</t>
   </si>
   <si>
     <t xml:space="preserve">18.9438591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4317226409912</t>
+    <t xml:space="preserve">19.4317207336426</t>
   </si>
   <si>
     <t xml:space="preserve">19.3572998046875</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">19.1257762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1919231414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1753902435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2828845977783</t>
+    <t xml:space="preserve">19.1919250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1753883361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2828826904297</t>
   </si>
   <si>
     <t xml:space="preserve">19.1340427398682</t>
@@ -554,31 +554,31 @@
     <t xml:space="preserve">19.6549797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7045917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4647960662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.059627532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6461887359619</t>
+    <t xml:space="preserve">19.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4647941589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0596237182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.646183013916</t>
   </si>
   <si>
     <t xml:space="preserve">19.1175079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1588516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0100135803223</t>
+    <t xml:space="preserve">19.1588497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.010009765625</t>
   </si>
   <si>
     <t xml:space="preserve">18.7536792755127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9025192260742</t>
+    <t xml:space="preserve">18.9025173187256</t>
   </si>
   <si>
     <t xml:space="preserve">19.0844306945801</t>
@@ -590,43 +590,43 @@
     <t xml:space="preserve">18.7950210571289</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7867546081543</t>
+    <t xml:space="preserve">18.7867527008057</t>
   </si>
   <si>
     <t xml:space="preserve">18.7454109191895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3319702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6291236877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.869441986084</t>
+    <t xml:space="preserve">18.3319683074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6291217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8694438934326</t>
   </si>
   <si>
     <t xml:space="preserve">19.1505832672119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3485069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6627197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.728874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6875286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8942470550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4229259490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.480806350708</t>
+    <t xml:space="preserve">18.348503112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6627235412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7288722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6875267028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8942489624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.422924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4808082580566</t>
   </si>
   <si>
     <t xml:space="preserve">18.2327423095703</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">18.3237018585205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0590953826904</t>
+    <t xml:space="preserve">18.0590991973877</t>
   </si>
   <si>
     <t xml:space="preserve">18.6709899902344</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">19.4399890899658</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8782367706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6797828674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1676483154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8451633453369</t>
+    <t xml:space="preserve">19.8782348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6797847747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1676445007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8451614379883</t>
   </si>
   <si>
     <t xml:space="preserve">19.7790126800537</t>
@@ -668,28 +668,28 @@
     <t xml:space="preserve">19.9113121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1759185791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0022678375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9278469085693</t>
+    <t xml:space="preserve">20.1759128570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.002269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9278507232666</t>
   </si>
   <si>
     <t xml:space="preserve">20.0105400085449</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8038196563721</t>
+    <t xml:space="preserve">19.8038215637207</t>
   </si>
   <si>
     <t xml:space="preserve">20.1014957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1263027191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1097640991211</t>
+    <t xml:space="preserve">20.1263008117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1097660064697</t>
   </si>
   <si>
     <t xml:space="preserve">20.1924514770508</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">20.6389675140381</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1345710754395</t>
+    <t xml:space="preserve">20.1345691680908</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751407623291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2172603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3164863586426</t>
+    <t xml:space="preserve">20.2172622680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3164844512939</t>
   </si>
   <si>
     <t xml:space="preserve">20.2420616149902</t>
@@ -716,61 +716,61 @@
     <t xml:space="preserve">20.3330230712891</t>
   </si>
   <si>
-    <t xml:space="preserve">20.225528717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6555061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5066680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3578319549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4818592071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0849590301514</t>
+    <t xml:space="preserve">20.2255306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6555080413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5066699981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3578300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4818630218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0849552154541</t>
   </si>
   <si>
     <t xml:space="preserve">20.3991737365723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5645484924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5397453308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6885795593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.894775390625</t>
+    <t xml:space="preserve">20.5645523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5397434234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6885814666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8947734832764</t>
   </si>
   <si>
     <t xml:space="preserve">20.4074401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7133846282959</t>
+    <t xml:space="preserve">20.7133865356445</t>
   </si>
   <si>
     <t xml:space="preserve">20.9697208404541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3495597839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4239807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3082180023193</t>
+    <t xml:space="preserve">20.3495616912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.423978805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3082141876221</t>
   </si>
   <si>
     <t xml:space="preserve">20.754732131958</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9609260559082</t>
+    <t xml:space="preserve">19.9609241485596</t>
   </si>
   <si>
     <t xml:space="preserve">19.8865089416504</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">19.8286247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8534336090088</t>
+    <t xml:space="preserve">19.8534297943115</t>
   </si>
   <si>
     <t xml:space="preserve">20.1180362701416</t>
@@ -788,31 +788,31 @@
     <t xml:space="preserve">19.5722923278809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2994213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5144081115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.423454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6136360168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.564022064209</t>
+    <t xml:space="preserve">19.2994194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5144100189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474872589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4234504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6136341094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5640239715576</t>
   </si>
   <si>
     <t xml:space="preserve">19.3821105957031</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7376670837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3661003112793</t>
+    <t xml:space="preserve">19.7376689910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3660984039307</t>
   </si>
   <si>
     <t xml:space="preserve">19.9361209869385</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">20.2007217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4901332855225</t>
+    <t xml:space="preserve">20.4901275634766</t>
   </si>
   <si>
     <t xml:space="preserve">20.7381954193115</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2922039031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1516361236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0854816436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9366455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.779541015625</t>
+    <t xml:space="preserve">21.2922077178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1516342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0854835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9366474151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7795372009277</t>
   </si>
   <si>
     <t xml:space="preserve">20.4570541381836</t>
@@ -848,49 +848,49 @@
     <t xml:space="preserve">20.7051181793213</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1268291473389</t>
+    <t xml:space="preserve">21.1268310546875</t>
   </si>
   <si>
     <t xml:space="preserve">22.0435600280762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1192493438721</t>
+    <t xml:space="preserve">22.1192512512207</t>
   </si>
   <si>
     <t xml:space="preserve">21.8669414520264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9846858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2958679199219</t>
+    <t xml:space="preserve">21.9846878051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2958698272705</t>
   </si>
   <si>
     <t xml:space="preserve">22.4724884033203</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2201728820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2622261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5397682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5734100341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8080654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6987342834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0847778320312</t>
+    <t xml:space="preserve">22.2201747894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.262228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5397720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5734062194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8080673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6987323760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0847759246826</t>
   </si>
   <si>
     <t xml:space="preserve">21.3202667236328</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">20.4203605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5549240112305</t>
+    <t xml:space="preserve">20.5549221038818</t>
   </si>
   <si>
     <t xml:space="preserve">20.4540004730225</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">20.9670314788818</t>
   </si>
   <si>
-    <t xml:space="preserve">21.19411277771</t>
+    <t xml:space="preserve">21.1941108703613</t>
   </si>
   <si>
     <t xml:space="preserve">20.8576984405518</t>
@@ -923,31 +923,31 @@
     <t xml:space="preserve">21.1688823699951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8324642181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9586181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156433105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5978088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2613945007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.101598739624</t>
+    <t xml:space="preserve">20.8324680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9586219787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8156452178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5978107452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2613964080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1015968322754</t>
   </si>
   <si>
     <t xml:space="preserve">21.6819114685059</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6146297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8164768218994</t>
+    <t xml:space="preserve">21.6146278381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8164749145508</t>
   </si>
   <si>
     <t xml:space="preserve">21.656681060791</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">21.8248882293701</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5473461151123</t>
+    <t xml:space="preserve">21.5473480224609</t>
   </si>
   <si>
     <t xml:space="preserve">21.5725784301758</t>
@@ -968,28 +968,28 @@
     <t xml:space="preserve">21.8585300445557</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9258136749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7828369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.321102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4884757995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3875484466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1949424743652</t>
+    <t xml:space="preserve">21.9258117675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7828388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3210983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4884738922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3875503540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1949443817139</t>
   </si>
   <si>
     <t xml:space="preserve">21.850118637085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2454071044922</t>
+    <t xml:space="preserve">22.2454051971436</t>
   </si>
   <si>
     <t xml:space="preserve">22.0015068054199</t>
@@ -998,28 +998,28 @@
     <t xml:space="preserve">22.3883838653564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2538185119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5481777191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5313587188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7668476104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0696220397949</t>
+    <t xml:space="preserve">22.2538166046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5481758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5313568115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7668495178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0696201324463</t>
   </si>
   <si>
     <t xml:space="preserve">22.5818214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8425407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5650005340576</t>
+    <t xml:space="preserve">22.8425445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5649967193604</t>
   </si>
   <si>
     <t xml:space="preserve">22.1444835662842</t>
@@ -1028,34 +1028,34 @@
     <t xml:space="preserve">22.2117671966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1865348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5229511260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7920799255371</t>
+    <t xml:space="preserve">22.1865329742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.52294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7920818328857</t>
   </si>
   <si>
     <t xml:space="preserve">22.4220237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7500286102295</t>
+    <t xml:space="preserve">22.7500305175781</t>
   </si>
   <si>
     <t xml:space="preserve">22.9266452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9350566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8593616485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7079734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416191101074</t>
+    <t xml:space="preserve">22.93505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8593635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7079792022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416152954102</t>
   </si>
   <si>
     <t xml:space="preserve">22.5902328491211</t>
@@ -1070,118 +1070,118 @@
     <t xml:space="preserve">22.1613025665283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3547439575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3042774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.959451675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.228588104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1108379364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9174022674561</t>
+    <t xml:space="preserve">22.3547420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3042793273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9594535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2285861968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.11083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9174003601074</t>
   </si>
   <si>
     <t xml:space="preserve">22.3463325500488</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4304313659668</t>
+    <t xml:space="preserve">22.4304332733154</t>
   </si>
   <si>
     <t xml:space="preserve">22.825719833374</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4649066925049</t>
+    <t xml:space="preserve">23.4649105072021</t>
   </si>
   <si>
     <t xml:space="preserve">23.6331157684326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6751689910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6835803985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8097343444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9106616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9190673828125</t>
+    <t xml:space="preserve">23.6751670837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6835784912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8097324371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9106597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9190654754639</t>
   </si>
   <si>
     <t xml:space="preserve">23.7508602142334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8770179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.986349105835</t>
+    <t xml:space="preserve">23.8770160675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9863510131836</t>
   </si>
   <si>
     <t xml:space="preserve">23.8938369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9527111053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9779415130615</t>
+    <t xml:space="preserve">23.952709197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9779357910156</t>
   </si>
   <si>
     <t xml:space="preserve">23.8517837524414</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0368118286133</t>
+    <t xml:space="preserve">24.0368137359619</t>
   </si>
   <si>
     <t xml:space="preserve">24.4741516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3311748504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3143558502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0536346435547</t>
+    <t xml:space="preserve">24.3311786651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3143577575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0536365509033</t>
   </si>
   <si>
     <t xml:space="preserve">23.9358882904053</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8013229370117</t>
+    <t xml:space="preserve">23.8013210296631</t>
   </si>
   <si>
     <t xml:space="preserve">23.9611206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0199928283691</t>
+    <t xml:space="preserve">24.0199909210205</t>
   </si>
   <si>
     <t xml:space="preserve">24.104097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5582580566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5077934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.356409072876</t>
+    <t xml:space="preserve">24.5582542419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5077953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3564071655273</t>
   </si>
   <si>
     <t xml:space="preserve">24.3984603881836</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9199028015137</t>
+    <t xml:space="preserve">24.919900894165</t>
   </si>
   <si>
     <t xml:space="preserve">24.7937450408936</t>
@@ -1190,16 +1190,16 @@
     <t xml:space="preserve">24.6928215026855</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8946685791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2310829162598</t>
+    <t xml:space="preserve">24.8946704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2310848236084</t>
   </si>
   <si>
     <t xml:space="preserve">25.1217517852783</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1890316009521</t>
+    <t xml:space="preserve">25.1890335083008</t>
   </si>
   <si>
     <t xml:space="preserve">24.8526210784912</t>
@@ -1208,31 +1208,31 @@
     <t xml:space="preserve">24.4489212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5574245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3892192840576</t>
+    <t xml:space="preserve">23.5574226379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3892154693604</t>
   </si>
   <si>
     <t xml:space="preserve">23.5994739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2125988006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9274787902832</t>
+    <t xml:space="preserve">23.2125968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9274768829346</t>
   </si>
   <si>
     <t xml:space="preserve">23.6919898986816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5406017303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5742416381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3808078765869</t>
+    <t xml:space="preserve">23.540599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5742435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3808059692383</t>
   </si>
   <si>
     <t xml:space="preserve">23.4144477844238</t>
@@ -1247,16 +1247,16 @@
     <t xml:space="preserve">22.9939289093018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6911544799805</t>
+    <t xml:space="preserve">22.6911563873291</t>
   </si>
   <si>
     <t xml:space="preserve">22.9014167785645</t>
   </si>
   <si>
-    <t xml:space="preserve">22.977108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0443916320801</t>
+    <t xml:space="preserve">22.9771099090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0443878173828</t>
   </si>
   <si>
     <t xml:space="preserve">23.02756690979</t>
@@ -1268,16 +1268,16 @@
     <t xml:space="preserve">22.8930053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6827430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1789569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546501159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2210121154785</t>
+    <t xml:space="preserve">22.6827449798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.178955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546482086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2210102081299</t>
   </si>
   <si>
     <t xml:space="preserve">23.1621341705322</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">23.229419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0780353546143</t>
+    <t xml:space="preserve">23.078031539917</t>
   </si>
   <si>
     <t xml:space="preserve">22.8677711486816</t>
@@ -1295,43 +1295,43 @@
     <t xml:space="preserve">23.0107517242432</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1882019042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0031719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1713771820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2218418121338</t>
+    <t xml:space="preserve">24.1881980895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0031700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1713790893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2218456268311</t>
   </si>
   <si>
     <t xml:space="preserve">24.3900508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4909725189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8273887634277</t>
+    <t xml:space="preserve">24.4909706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8273906707764</t>
   </si>
   <si>
     <t xml:space="preserve">24.5246143341064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3395843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.305944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8686065673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8349666595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2882919311523</t>
+    <t xml:space="preserve">24.3395881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3059463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8686046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8349647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2882900238037</t>
   </si>
   <si>
     <t xml:space="preserve">22.9602870941162</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">22.7163867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4556617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0687942504883</t>
+    <t xml:space="preserve">22.4556636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.068790435791</t>
   </si>
   <si>
     <t xml:space="preserve">22.1781234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0940208435059</t>
+    <t xml:space="preserve">22.0940227508545</t>
   </si>
   <si>
     <t xml:space="preserve">21.908992767334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7996578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6314506530762</t>
+    <t xml:space="preserve">21.7996559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6314487457275</t>
   </si>
   <si>
     <t xml:space="preserve">21.7912464141846</t>
@@ -1373,19 +1373,19 @@
     <t xml:space="preserve">22.3631477355957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3967933654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2874584197998</t>
+    <t xml:space="preserve">22.3967914581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2874603271484</t>
   </si>
   <si>
     <t xml:space="preserve">22.0856094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6230411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3455009460449</t>
+    <t xml:space="preserve">21.6230392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3454990386963</t>
   </si>
   <si>
     <t xml:space="preserve">21.4043712615967</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">21.4464206695557</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2950344085693</t>
+    <t xml:space="preserve">21.295036315918</t>
   </si>
   <si>
     <t xml:space="preserve">21.3370876312256</t>
@@ -1403,31 +1403,31 @@
     <t xml:space="preserve">21.7407855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7904109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3194313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7988224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4035396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5717430114746</t>
+    <t xml:space="preserve">20.7904148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3194332122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7988262176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4035377502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5717468261719</t>
   </si>
   <si>
     <t xml:space="preserve">20.7735939025879</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9249801635742</t>
+    <t xml:space="preserve">20.9249782562256</t>
   </si>
   <si>
     <t xml:space="preserve">20.8072338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0288715362549</t>
+    <t xml:space="preserve">21.0288734436035</t>
   </si>
   <si>
     <t xml:space="preserve">20.8919315338135</t>
@@ -1439,31 +1439,31 @@
     <t xml:space="preserve">20.618049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">20.746431350708</t>
+    <t xml:space="preserve">20.7464294433594</t>
   </si>
   <si>
     <t xml:space="preserve">20.8662528991699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3883419036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9604034423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.362663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5081634521484</t>
+    <t xml:space="preserve">21.3883361816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9604015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3626594543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5081596374512</t>
   </si>
   <si>
     <t xml:space="preserve">21.8847484588623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7563648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2270965576172</t>
+    <t xml:space="preserve">21.7563667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2270984649658</t>
   </si>
   <si>
     <t xml:space="preserve">22.9203586578369</t>
@@ -1478,37 +1478,37 @@
     <t xml:space="preserve">21.8077182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0987167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1072731018066</t>
+    <t xml:space="preserve">22.0987186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1072750091553</t>
   </si>
   <si>
     <t xml:space="preserve">21.7392501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2428436279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4568099975586</t>
+    <t xml:space="preserve">21.2428417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.45680809021</t>
   </si>
   <si>
     <t xml:space="preserve">21.4054584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9432830810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1302013397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.121639251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3698444366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.268518447876</t>
+    <t xml:space="preserve">20.9432849884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1216411590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3698482513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2685165405273</t>
   </si>
   <si>
     <t xml:space="preserve">21.396900177002</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">21.3797817230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0117511749268</t>
+    <t xml:space="preserve">21.011754989624</t>
   </si>
   <si>
     <t xml:space="preserve">20.6779613494873</t>
@@ -1529,19 +1529,19 @@
     <t xml:space="preserve">21.1743698120117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8063449859619</t>
+    <t xml:space="preserve">20.8063411712646</t>
   </si>
   <si>
     <t xml:space="preserve">20.7977828979492</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9960117340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5424003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1914882659912</t>
+    <t xml:space="preserve">21.9960098266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5423984527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1914863586426</t>
   </si>
   <si>
     <t xml:space="preserve">20.909049987793</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">20.4554347991943</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6509113311768</t>
+    <t xml:space="preserve">19.6509132385254</t>
   </si>
   <si>
     <t xml:space="preserve">19.8563232421875</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">17.8706874847412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9305992126465</t>
+    <t xml:space="preserve">17.9306011199951</t>
   </si>
   <si>
     <t xml:space="preserve">18.2729530334473</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">17.4427490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2558307647705</t>
+    <t xml:space="preserve">18.2558345794678</t>
   </si>
   <si>
     <t xml:space="preserve">17.9355735778809</t>
@@ -1583,61 +1583,61 @@
     <t xml:space="preserve">18.1657447814941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1568927764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8119888305664</t>
+    <t xml:space="preserve">18.1568908691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.811990737915</t>
   </si>
   <si>
     <t xml:space="preserve">19.2280654907227</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9978981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359283447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2988891601562</t>
+    <t xml:space="preserve">18.997896194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359264373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2988910675049</t>
   </si>
   <si>
     <t xml:space="preserve">19.1838035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2103633880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4139747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5202045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5113525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5644721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.723819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6352939605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4316787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1395416259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0687217712402</t>
+    <t xml:space="preserve">19.2103614807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4139766693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.520206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5113563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5644702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7238178253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6352920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4316806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1395397186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0687198638916</t>
   </si>
   <si>
     <t xml:space="preserve">19.2369213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6972618103027</t>
+    <t xml:space="preserve">19.6972637176514</t>
   </si>
   <si>
     <t xml:space="preserve">19.7503776550293</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">19.8034934997559</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4405307769775</t>
+    <t xml:space="preserve">19.4405326843262</t>
   </si>
   <si>
     <t xml:space="preserve">19.2900390625</t>
@@ -1658,25 +1658,25 @@
     <t xml:space="preserve">18.5109996795654</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3516502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8208427429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7765808105469</t>
+    <t xml:space="preserve">18.3516483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8208446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7765789031982</t>
   </si>
   <si>
     <t xml:space="preserve">18.7942848205566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9182243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1129817962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4847984313965</t>
+    <t xml:space="preserve">18.9182224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1129837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4847965240479</t>
   </si>
   <si>
     <t xml:space="preserve">19.6707019805908</t>
@@ -1685,139 +1685,139 @@
     <t xml:space="preserve">19.5733242034912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2015113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2192153930664</t>
+    <t xml:space="preserve">19.2015132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.219217300415</t>
   </si>
   <si>
     <t xml:space="preserve">19.0952758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6969051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1218338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2546253204346</t>
+    <t xml:space="preserve">18.696907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1218357086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2546272277832</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906734466553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4136180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.67919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6880512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1483917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9890460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0510139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5995273590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3427982330322</t>
+    <t xml:space="preserve">18.4136199951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6792030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6880493164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1483936309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9890480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0510101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5995254516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3427963256836</t>
   </si>
   <si>
     <t xml:space="preserve">18.431324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3693561553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7585201263428</t>
+    <t xml:space="preserve">18.3693580627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7585182189941</t>
   </si>
   <si>
     <t xml:space="preserve">17.6965503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4840869903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9001636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.417688369751</t>
+    <t xml:space="preserve">17.4840850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9001617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4176864624023</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6342277526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4527473449707</t>
+    <t xml:space="preserve">16.6342258453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4527435302734</t>
   </si>
   <si>
     <t xml:space="preserve">15.9392881393433</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5719013214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.434684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4656686782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7316036224365</t>
+    <t xml:space="preserve">15.5719032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346857070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.465669631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7316055297852</t>
   </si>
   <si>
     <t xml:space="preserve">16.2712650299072</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7666625976562</t>
+    <t xml:space="preserve">15.7666606903076</t>
   </si>
   <si>
     <t xml:space="preserve">15.2133665084839</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1735305786133</t>
+    <t xml:space="preserve">15.173529624939</t>
   </si>
   <si>
     <t xml:space="preserve">14.6777801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2262907028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7840127944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6290884017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9743452072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0717239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.191237449646</t>
+    <t xml:space="preserve">14.2262916564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7840137481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6290893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0717248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1912364959717</t>
   </si>
   <si>
     <t xml:space="preserve">15.7179718017578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2933979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171581268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8596172332764</t>
+    <t xml:space="preserve">16.2933959960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171590805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8596181869507</t>
   </si>
   <si>
     <t xml:space="preserve">16.0986366271973</t>
@@ -1829,28 +1829,28 @@
     <t xml:space="preserve">15.7755146026611</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4169797897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7887945175171</t>
+    <t xml:space="preserve">15.4169807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7887935638428</t>
   </si>
   <si>
     <t xml:space="preserve">15.4833745956421</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6910581588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2882604598999</t>
+    <t xml:space="preserve">14.6910591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2882595062256</t>
   </si>
   <si>
     <t xml:space="preserve">14.2041606903076</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8943147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.97398853302</t>
+    <t xml:space="preserve">13.8943157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9739904403687</t>
   </si>
   <si>
     <t xml:space="preserve">13.8766107559204</t>
@@ -1859,22 +1859,22 @@
     <t xml:space="preserve">14.0802211761475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9916954040527</t>
+    <t xml:space="preserve">13.9916934967041</t>
   </si>
   <si>
     <t xml:space="preserve">13.7880821228027</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6243076324463</t>
+    <t xml:space="preserve">13.624306678772</t>
   </si>
   <si>
     <t xml:space="preserve">14.1554698944092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3148174285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0451679229736</t>
+    <t xml:space="preserve">14.3148193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0451669692993</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254770278931</t>
@@ -1886,76 +1886,76 @@
     <t xml:space="preserve">13.4959440231323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.367579460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2524938583374</t>
+    <t xml:space="preserve">13.3675804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2524948120117</t>
   </si>
   <si>
     <t xml:space="preserve">14.0669431686401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7707328796387</t>
+    <t xml:space="preserve">14.7707319259644</t>
   </si>
   <si>
     <t xml:space="preserve">14.8415546417236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.695484161377</t>
+    <t xml:space="preserve">14.6954860687256</t>
   </si>
   <si>
     <t xml:space="preserve">14.6512203216553</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8946723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0628700256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8813915252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.828275680542</t>
+    <t xml:space="preserve">14.8946704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0628719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8813924789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8282766342163</t>
   </si>
   <si>
     <t xml:space="preserve">14.9345064163208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4479656219482</t>
+    <t xml:space="preserve">15.4479646682739</t>
   </si>
   <si>
     <t xml:space="preserve">14.7131910324097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1558246612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2886142730713</t>
+    <t xml:space="preserve">15.1558237075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2886152267456</t>
   </si>
   <si>
     <t xml:space="preserve">15.6958389282227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3155288696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4129123687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.116340637207</t>
+    <t xml:space="preserve">16.3155307769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4129104614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1163425445557</t>
   </si>
   <si>
     <t xml:space="preserve">16.0145359039307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.802074432373</t>
+    <t xml:space="preserve">15.8020734786987</t>
   </si>
   <si>
     <t xml:space="preserve">16.1340484619141</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2358551025391</t>
+    <t xml:space="preserve">16.2358531951904</t>
   </si>
   <si>
     <t xml:space="preserve">16.4793033599854</t>
@@ -1964,22 +1964,22 @@
     <t xml:space="preserve">16.4748783111572</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3376598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.218147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.288969039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5811100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5412731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7758693695068</t>
+    <t xml:space="preserve">16.3376617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2181491851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2889709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5811080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5412693023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7758712768555</t>
   </si>
   <si>
     <t xml:space="preserve">16.4881572723389</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">16.7935752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6297988891602</t>
+    <t xml:space="preserve">16.6297969818115</t>
   </si>
   <si>
     <t xml:space="preserve">16.9263668060303</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9481401443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9304361343384</t>
+    <t xml:space="preserve">15.9481430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9304399490356</t>
   </si>
   <si>
     <t xml:space="preserve">15.9614219665527</t>
@@ -2006,88 +2006,88 @@
     <t xml:space="preserve">16.5279941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5368461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6784896850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5855350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7138977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1292676925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5763263702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8197784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0101070404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8906011581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8463373184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3992767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.293041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9610652923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.987624168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8858184814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3767862319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4874467849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6069574356079</t>
+    <t xml:space="preserve">16.5368480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6784915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5855369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7138996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1292695999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5763273239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8197793960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0101089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8906002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8463382720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3992748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2930431365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9610633850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.885817527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3767871856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4874458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6069583892822</t>
   </si>
   <si>
     <t xml:space="preserve">14.5626955032349</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7795858383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4125528335571</t>
+    <t xml:space="preserve">14.7795848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4125537872314</t>
   </si>
   <si>
     <t xml:space="preserve">15.2222194671631</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0540180206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9212284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6423673629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300813674927</t>
+    <t xml:space="preserve">15.0540170669556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9212255477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6423692703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300804138184</t>
   </si>
   <si>
     <t xml:space="preserve">14.8592586517334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1868095397949</t>
+    <t xml:space="preserve">15.1868114471436</t>
   </si>
   <si>
     <t xml:space="preserve">15.0230340957642</t>
@@ -2096,10 +2096,10 @@
     <t xml:space="preserve">14.9477863311768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4476089477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2436408996582</t>
+    <t xml:space="preserve">14.4476099014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2436418533325</t>
   </si>
   <si>
     <t xml:space="preserve">13.5534858703613</t>
@@ -2111,34 +2111,34 @@
     <t xml:space="preserve">13.6420125961304</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1997346878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4564619064331</t>
+    <t xml:space="preserve">14.1997327804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4564628601074</t>
   </si>
   <si>
     <t xml:space="preserve">14.4431829452515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6822052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8459796905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.217794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0495910644531</t>
+    <t xml:space="preserve">14.682204246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8459806442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2177963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0495920181274</t>
   </si>
   <si>
     <t xml:space="preserve">15.2089395523071</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0318870544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1823835372925</t>
+    <t xml:space="preserve">15.031886100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1823816299438</t>
   </si>
   <si>
     <t xml:space="preserve">14.496298789978</t>
@@ -2153,22 +2153,22 @@
     <t xml:space="preserve">15.1381196975708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3151721954346</t>
+    <t xml:space="preserve">15.3151712417603</t>
   </si>
   <si>
     <t xml:space="preserve">15.3063220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6467952728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3723611831665</t>
+    <t xml:space="preserve">14.6467962265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3723602294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.8589038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7748041152954</t>
+    <t xml:space="preserve">13.7748050689697</t>
   </si>
   <si>
     <t xml:space="preserve">13.5977487564087</t>
@@ -2177,52 +2177,52 @@
     <t xml:space="preserve">13.7792291641235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5888977050781</t>
+    <t xml:space="preserve">13.5888967514038</t>
   </si>
   <si>
     <t xml:space="preserve">13.6774234771729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2170839309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5313529968262</t>
+    <t xml:space="preserve">13.2170848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5313549041748</t>
   </si>
   <si>
     <t xml:space="preserve">14.3502283096313</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3192434310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2705554962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6999101638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353239059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9256553649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6600713729858</t>
+    <t xml:space="preserve">14.3192443847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2705564498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6999092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353229522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9256563186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6600732803345</t>
   </si>
   <si>
     <t xml:space="preserve">14.7486028671265</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9079504013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2266454696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.580756187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.91273021698</t>
+    <t xml:space="preserve">14.9079475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2266473770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5807552337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9127321243286</t>
   </si>
   <si>
     <t xml:space="preserve">16.0942134857178</t>
@@ -2231,55 +2231,55 @@
     <t xml:space="preserve">15.8584632873535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9808712005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675327301025</t>
+    <t xml:space="preserve">15.9808721542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675308227539</t>
   </si>
   <si>
     <t xml:space="preserve">16.2302188873291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4568958282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5838394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5929050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.66090965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7243804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4115600585938</t>
+    <t xml:space="preserve">16.4568996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5838375091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5929069519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6609115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7243785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7425117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.411563873291</t>
   </si>
   <si>
     <t xml:space="preserve">16.6427745819092</t>
   </si>
   <si>
-    <t xml:space="preserve">16.982795715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9419918060303</t>
+    <t xml:space="preserve">16.9827919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.941987991333</t>
   </si>
   <si>
     <t xml:space="preserve">17.0326614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3092098236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4542846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.964656829834</t>
+    <t xml:space="preserve">17.309211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4542865753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9646587371826</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555912017822</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">17.0462627410889</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0436515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0935211181641</t>
+    <t xml:space="preserve">18.0436496734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0935192108154</t>
   </si>
   <si>
     <t xml:space="preserve">18.1116561889648</t>
@@ -2306,37 +2306,37 @@
     <t xml:space="preserve">16.7833156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9283885955811</t>
+    <t xml:space="preserve">16.9283905029297</t>
   </si>
   <si>
     <t xml:space="preserve">17.5268211364746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1505374908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.996395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8875904083252</t>
+    <t xml:space="preserve">17.1505355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9963932037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8875885009766</t>
   </si>
   <si>
     <t xml:space="preserve">16.9601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3726787567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7787818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7923831939697</t>
+    <t xml:space="preserve">17.3726806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7787799835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7923851013184</t>
   </si>
   <si>
     <t xml:space="preserve">16.7017116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0307426452637</t>
+    <t xml:space="preserve">16.030740737915</t>
   </si>
   <si>
     <t xml:space="preserve">16.0715446472168</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">16.8150501251221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5948295593262</t>
+    <t xml:space="preserve">17.5948257446289</t>
   </si>
   <si>
     <t xml:space="preserve">17.3862819671631</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">17.0054626464844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9782600402832</t>
+    <t xml:space="preserve">16.9782581329346</t>
   </si>
   <si>
     <t xml:space="preserve">17.2774753570557</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">18.0073833465576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.206859588623</t>
+    <t xml:space="preserve">18.2068614959717</t>
   </si>
   <si>
     <t xml:space="preserve">18.7508888244629</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">18.2975311279297</t>
   </si>
   <si>
-    <t xml:space="preserve">18.351936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2884654998779</t>
+    <t xml:space="preserve">18.3519344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2884616851807</t>
   </si>
   <si>
     <t xml:space="preserve">18.4244728088379</t>
@@ -2411,22 +2411,22 @@
     <t xml:space="preserve">18.0617847442627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8804416656494</t>
+    <t xml:space="preserve">17.8804397583008</t>
   </si>
   <si>
     <t xml:space="preserve">18.0889873504639</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9756507873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7353649139404</t>
+    <t xml:space="preserve">17.9756488800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7353668212891</t>
   </si>
   <si>
     <t xml:space="preserve">17.7217674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8623085021973</t>
+    <t xml:space="preserve">17.8623104095459</t>
   </si>
   <si>
     <t xml:space="preserve">17.7126998901367</t>
@@ -2435,34 +2435,34 @@
     <t xml:space="preserve">17.0598640441895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0507984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9737243652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.096134185791</t>
+    <t xml:space="preserve">17.0507946014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.973726272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0961322784424</t>
   </si>
   <si>
     <t xml:space="preserve">16.8921203613281</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2366752624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7671012878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0753860473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4698104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5060749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.723690032959</t>
+    <t xml:space="preserve">17.2366733551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7671031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0753841400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4698085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5060768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7236881256104</t>
   </si>
   <si>
     <t xml:space="preserve">18.71462059021</t>
@@ -2471,10 +2471,10 @@
     <t xml:space="preserve">18.2703285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1887264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5786151885986</t>
+    <t xml:space="preserve">18.1887245178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.57861328125</t>
   </si>
   <si>
     <t xml:space="preserve">18.9594345092773</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">18.7690258026123</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7418231964111</t>
+    <t xml:space="preserve">18.7418212890625</t>
   </si>
   <si>
     <t xml:space="preserve">18.7780895233154</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">19.2223834991455</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7120094299316</t>
+    <t xml:space="preserve">19.7120113372803</t>
   </si>
   <si>
     <t xml:space="preserve">19.5216007232666</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">19.81174659729</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490604400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3130531311035</t>
+    <t xml:space="preserve">19.4490623474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3130512237549</t>
   </si>
   <si>
     <t xml:space="preserve">18.7962245941162</t>
@@ -2513,31 +2513,31 @@
     <t xml:space="preserve">18.4970073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1732044219971</t>
+    <t xml:space="preserve">17.1732063293457</t>
   </si>
   <si>
     <t xml:space="preserve">17.4225521087646</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8033695220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9121742248535</t>
+    <t xml:space="preserve">17.8033714294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9121761322021</t>
   </si>
   <si>
     <t xml:space="preserve">18.039119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9892501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0663166046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8596935272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.905029296875</t>
+    <t xml:space="preserve">17.9892463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0663223266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8596954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9050312042236</t>
   </si>
   <si>
     <t xml:space="preserve">18.7599582672119</t>
@@ -2552,31 +2552,31 @@
     <t xml:space="preserve">18.9685020446777</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0863742828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1951789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5760021209717</t>
+    <t xml:space="preserve">19.0863723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1951808929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5760059356689</t>
   </si>
   <si>
     <t xml:space="preserve">19.6394729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4218578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7392101287842</t>
+    <t xml:space="preserve">19.4218597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7392120361328</t>
   </si>
   <si>
     <t xml:space="preserve">19.94775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0021572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8661479949951</t>
+    <t xml:space="preserve">20.0021553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8661499023438</t>
   </si>
   <si>
     <t xml:space="preserve">19.485330581665</t>
@@ -2588,28 +2588,28 @@
     <t xml:space="preserve">19.2133140563965</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1679801940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3221225738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0319728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2949199676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2677154541016</t>
+    <t xml:space="preserve">19.1679782867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3221206665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0319709777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2677192687988</t>
   </si>
   <si>
     <t xml:space="preserve">19.5941371917725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8570804595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4127922058105</t>
+    <t xml:space="preserve">19.8570823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4127941131592</t>
   </si>
   <si>
     <t xml:space="preserve">18.9957046508789</t>
@@ -2618,82 +2618,82 @@
     <t xml:space="preserve">18.6602172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5332775115967</t>
+    <t xml:space="preserve">18.5332794189453</t>
   </si>
   <si>
     <t xml:space="preserve">18.9322338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4762649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.047492980957</t>
+    <t xml:space="preserve">19.4762630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0474948883057</t>
   </si>
   <si>
     <t xml:space="preserve">20.0112247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9658908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3376445770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9088726043701</t>
+    <t xml:space="preserve">19.9658889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.337646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9088745117188</t>
   </si>
   <si>
     <t xml:space="preserve">21.3259658813477</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5526428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0332012176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.697717666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4049549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8337230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9814109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9930896759033</t>
+    <t xml:space="preserve">21.5526447296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0331993103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6977195739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4049530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8337249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9814128875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.993091583252</t>
   </si>
   <si>
     <t xml:space="preserve">20.192569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3039855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3855895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4607391357422</t>
+    <t xml:space="preserve">19.3039875030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.385591506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4607410430908</t>
   </si>
   <si>
     <t xml:space="preserve">18.6511516571045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6239490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8195819854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.468578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842670440674</t>
+    <t xml:space="preserve">18.623950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0300521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8195838928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4685773849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6842679977417</t>
   </si>
   <si>
     <t xml:space="preserve">14.8112077713013</t>
@@ -2711,28 +2711,28 @@
     <t xml:space="preserve">14.3170480728149</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7341365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1648273468018</t>
+    <t xml:space="preserve">14.7341384887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1648263931274</t>
   </si>
   <si>
     <t xml:space="preserve">13.6914138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">14.090368270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.269100189209</t>
+    <t xml:space="preserve">14.0903673171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2690982818604</t>
   </si>
   <si>
     <t xml:space="preserve">15.0242862701416</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0061511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2354440689087</t>
+    <t xml:space="preserve">15.0061521530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2354431152344</t>
   </si>
   <si>
     <t xml:space="preserve">13.8863573074341</t>
@@ -2741,25 +2741,25 @@
     <t xml:space="preserve">13.238055229187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4783344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5327386856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9660415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4511346817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8092861175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1901082992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.258111000061</t>
+    <t xml:space="preserve">13.4783353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5327396392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9660425186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4511337280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.809287071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1901063919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2581119537354</t>
   </si>
   <si>
     <t xml:space="preserve">13.3695297241211</t>
@@ -2768,25 +2768,25 @@
     <t xml:space="preserve">13.8727569580078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9634275436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7820844650269</t>
+    <t xml:space="preserve">13.9634284973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7820854187012</t>
   </si>
   <si>
     <t xml:space="preserve">14.2943801879883</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4485235214233</t>
+    <t xml:space="preserve">14.4485216140747</t>
   </si>
   <si>
     <t xml:space="preserve">14.5346603393555</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1512269973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3643064498901</t>
+    <t xml:space="preserve">15.1512260437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3643035888672</t>
   </si>
   <si>
     <t xml:space="preserve">15.6544532775879</t>
@@ -2795,28 +2795,28 @@
     <t xml:space="preserve">15.5683164596558</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3461713790894</t>
+    <t xml:space="preserve">15.346170425415</t>
   </si>
   <si>
     <t xml:space="preserve">16.6291751861572</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7768573760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7904615402222</t>
+    <t xml:space="preserve">15.7768583297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7904644012451</t>
   </si>
   <si>
     <t xml:space="preserve">16.4478302001953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3752899169922</t>
+    <t xml:space="preserve">16.3752937316895</t>
   </si>
   <si>
     <t xml:space="preserve">17.1097354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0398101806641</t>
+    <t xml:space="preserve">16.0398082733154</t>
   </si>
   <si>
     <t xml:space="preserve">17.2446327209473</t>
@@ -2825,13 +2825,13 @@
     <t xml:space="preserve">16.4030952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8813457489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7066040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2906169891357</t>
+    <t xml:space="preserve">16.88134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7066020965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2906188964844</t>
   </si>
   <si>
     <t xml:space="preserve">17.6998920440674</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">17.6585083007812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6079196929932</t>
+    <t xml:space="preserve">17.6079177856445</t>
   </si>
   <si>
     <t xml:space="preserve">17.355001449585</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6309127807617</t>
+    <t xml:space="preserve">17.6309146881104</t>
   </si>
   <si>
     <t xml:space="preserve">17.9850044250488</t>
@@ -2864,40 +2864,40 @@
     <t xml:space="preserve">18.6334018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7529640197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8081474304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.67018699646</t>
+    <t xml:space="preserve">18.7529621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8081455230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6701889038086</t>
   </si>
   <si>
     <t xml:space="preserve">17.7090873718262</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6631050109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4745597839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3482913970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885055541992</t>
+    <t xml:space="preserve">17.6631011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4745616912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3482894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885093688965</t>
   </si>
   <si>
     <t xml:space="preserve">18.5874137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9093132019043</t>
+    <t xml:space="preserve">18.9093151092529</t>
   </si>
   <si>
     <t xml:space="preserve">18.8173427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2220191955566</t>
+    <t xml:space="preserve">19.222017288208</t>
   </si>
   <si>
     <t xml:space="preserve">18.7161750793457</t>
@@ -2906,25 +2906,25 @@
     <t xml:space="preserve">18.9644985198975</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7897529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0104846954346</t>
+    <t xml:space="preserve">18.7897510528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0104827880859</t>
   </si>
   <si>
     <t xml:space="preserve">19.0748634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5715103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3507766723633</t>
+    <t xml:space="preserve">19.57151222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3507785797119</t>
   </si>
   <si>
     <t xml:space="preserve">19.9761829376221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9577884674072</t>
+    <t xml:space="preserve">19.9577903747559</t>
   </si>
   <si>
     <t xml:space="preserve">19.6542835235596</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">19.7278614044189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.930196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4703388214111</t>
+    <t xml:space="preserve">19.9301986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4703407287598</t>
   </si>
   <si>
     <t xml:space="preserve">20.0957450866699</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">20.2704906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3256759643555</t>
+    <t xml:space="preserve">20.3256721496582</t>
   </si>
   <si>
     <t xml:space="preserve">21.1534156799316</t>
@@ -2957,10 +2957,10 @@
     <t xml:space="preserve">21.3281631469727</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0154628753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0430507659912</t>
+    <t xml:space="preserve">21.0154590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0430488586426</t>
   </si>
   <si>
     <t xml:space="preserve">20.4912223815918</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">20.2245063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2337036132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8934078216553</t>
+    <t xml:space="preserve">20.2337017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8934097290039</t>
   </si>
   <si>
     <t xml:space="preserve">20.8223190307617</t>
@@ -2981,46 +2981,46 @@
     <t xml:space="preserve">20.4176464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">20.380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2061138153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5556049346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8775024414062</t>
+    <t xml:space="preserve">20.3808555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.206111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5556030273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8775043487549</t>
   </si>
   <si>
     <t xml:space="preserve">21.0614452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7303466796875</t>
+    <t xml:space="preserve">20.7303485870361</t>
   </si>
   <si>
     <t xml:space="preserve">20.7579383850098</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7395439147949</t>
+    <t xml:space="preserve">20.7395458221436</t>
   </si>
   <si>
     <t xml:space="preserve">20.6291809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2453899383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3649501800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4201354980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4937114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9443683624268</t>
+    <t xml:space="preserve">21.2453880310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3649520874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4201374053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4937133789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9443702697754</t>
   </si>
   <si>
     <t xml:space="preserve">21.5580902099609</t>
@@ -3029,46 +3029,46 @@
     <t xml:space="preserve">21.5213012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0271453857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.604076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8156108856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4109382629395</t>
+    <t xml:space="preserve">22.0271472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6040782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8156089782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4109363555908</t>
   </si>
   <si>
     <t xml:space="preserve">21.7420330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1191158294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5145931243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6341552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5421867370605</t>
+    <t xml:space="preserve">22.1191177368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.514591217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6341571807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5421848297119</t>
   </si>
   <si>
     <t xml:space="preserve">22.6433525085449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3674392700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4410171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2294826507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6709442138672</t>
+    <t xml:space="preserve">22.3674373626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4410133361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2294807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6709423065186</t>
   </si>
   <si>
     <t xml:space="preserve">22.4870014190674</t>
@@ -3077,16 +3077,16 @@
     <t xml:space="preserve">22.9008712768555</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8732814788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8456935882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2135753631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2411689758301</t>
+    <t xml:space="preserve">22.8732833862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8456897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2135772705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2411670684814</t>
   </si>
   <si>
     <t xml:space="preserve">23.6550388336182</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">24.0045299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7194194793701</t>
+    <t xml:space="preserve">23.7194175720215</t>
   </si>
   <si>
     <t xml:space="preserve">24.3356246948242</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">23.8757705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1700782775879</t>
+    <t xml:space="preserve">24.1700801849365</t>
   </si>
   <si>
     <t xml:space="preserve">23.5998554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6525478363037</t>
+    <t xml:space="preserve">22.6525497436523</t>
   </si>
   <si>
     <t xml:space="preserve">22.7261257171631</t>
@@ -3128,19 +3128,19 @@
     <t xml:space="preserve">22.9560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1926918029785</t>
+    <t xml:space="preserve">22.1926956176758</t>
   </si>
   <si>
     <t xml:space="preserve">21.6684551239014</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1993999481201</t>
+    <t xml:space="preserve">21.1994018554688</t>
   </si>
   <si>
     <t xml:space="preserve">21.6500644683838</t>
   </si>
   <si>
-    <t xml:space="preserve">21.466121673584</t>
+    <t xml:space="preserve">21.4661197662354</t>
   </si>
   <si>
     <t xml:space="preserve">22.0823287963867</t>
@@ -3149,40 +3149,40 @@
     <t xml:space="preserve">22.5881690979004</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0413188934326</t>
+    <t xml:space="preserve">24.0413208007812</t>
   </si>
   <si>
     <t xml:space="preserve">23.0112400054932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.121603012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6274452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2988414764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9677410125732</t>
+    <t xml:space="preserve">23.1216049194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6274471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2988395690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9677429199219</t>
   </si>
   <si>
     <t xml:space="preserve">23.3607311248779</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8665714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9217548370361</t>
+    <t xml:space="preserve">23.8665733337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9217567443848</t>
   </si>
   <si>
     <t xml:space="preserve">23.9033603668213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4459934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0965003967285</t>
+    <t xml:space="preserve">24.4459915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0965042114258</t>
   </si>
   <si>
     <t xml:space="preserve">24.7403011322021</t>
@@ -3191,16 +3191,16 @@
     <t xml:space="preserve">25.2277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8966503143311</t>
+    <t xml:space="preserve">24.8966522216797</t>
   </si>
   <si>
     <t xml:space="preserve">24.4092044830322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5471611022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0622005462646</t>
+    <t xml:space="preserve">24.5471591949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.062198638916</t>
   </si>
   <si>
     <t xml:space="preserve">24.5655536651611</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">24.6391334533691</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6023445129395</t>
+    <t xml:space="preserve">24.6023426055908</t>
   </si>
   <si>
     <t xml:space="preserve">24.8874530792236</t>
@@ -3224,10 +3224,10 @@
     <t xml:space="preserve">25.0805950164795</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3840999603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5036640167236</t>
+    <t xml:space="preserve">25.3841018676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.503662109375</t>
   </si>
   <si>
     <t xml:space="preserve">25.3749027252197</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">25.7151966094971</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9359264373779</t>
+    <t xml:space="preserve">25.9359283447266</t>
   </si>
   <si>
     <t xml:space="preserve">26.6257133483887</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">26.8740348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0119953155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5546245574951</t>
+    <t xml:space="preserve">27.0119934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5546226501465</t>
   </si>
   <si>
     <t xml:space="preserve">28.2811985015869</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">27.9225120544434</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0880584716797</t>
+    <t xml:space="preserve">28.0880603790283</t>
   </si>
   <si>
     <t xml:space="preserve">26.3957862854004</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">25.8715476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1106739044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8439559936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0279026031494</t>
+    <t xml:space="preserve">26.1106719970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.843957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0279006958008</t>
   </si>
   <si>
     <t xml:space="preserve">25.7519855499268</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">24.7127094268799</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2804431915283</t>
+    <t xml:space="preserve">24.280445098877</t>
   </si>
   <si>
     <t xml:space="preserve">25.1449737548828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5011730194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0346088409424</t>
+    <t xml:space="preserve">24.5011749267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0346069335938</t>
   </si>
   <si>
     <t xml:space="preserve">25.236946105957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6968021392822</t>
+    <t xml:space="preserve">25.6968059539795</t>
   </si>
   <si>
     <t xml:space="preserve">26.0462951660156</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">26.28542137146</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9267311096191</t>
+    <t xml:space="preserve">25.9267330169678</t>
   </si>
   <si>
     <t xml:space="preserve">25.9083366394043</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">26.0003089904785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9635200500488</t>
+    <t xml:space="preserve">25.9635181427002</t>
   </si>
   <si>
     <t xml:space="preserve">25.6600131988525</t>
@@ -3341,31 +3341,31 @@
     <t xml:space="preserve">25.0530033111572</t>
   </si>
   <si>
-    <t xml:space="preserve">24.593147277832</t>
+    <t xml:space="preserve">24.5931453704834</t>
   </si>
   <si>
     <t xml:space="preserve">24.3908100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1608791351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5563583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5195713043213</t>
+    <t xml:space="preserve">24.1608810424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.556360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.519567489624</t>
   </si>
   <si>
     <t xml:space="preserve">25.0162162780762</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9150466918945</t>
+    <t xml:space="preserve">24.9150447845459</t>
   </si>
   <si>
     <t xml:space="preserve">24.9058494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0137271881104</t>
+    <t xml:space="preserve">24.013729095459</t>
   </si>
   <si>
     <t xml:space="preserve">24.2712478637695</t>
@@ -3374,16 +3374,16 @@
     <t xml:space="preserve">25.2001571655273</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2620468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6734313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5446720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6918258666992</t>
+    <t xml:space="preserve">24.2620487213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.673433303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5446739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6918277740479</t>
   </si>
   <si>
     <t xml:space="preserve">23.4251098632812</t>
@@ -3395,67 +3395,67 @@
     <t xml:space="preserve">23.5170803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7838001251221</t>
+    <t xml:space="preserve">23.7838020324707</t>
   </si>
   <si>
     <t xml:space="preserve">24.1056976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">24.151683807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5287685394287</t>
+    <t xml:space="preserve">24.1516857147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5287666320801</t>
   </si>
   <si>
     <t xml:space="preserve">24.8138790130615</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8322734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9886264801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4852695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7703800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6416187286377</t>
+    <t xml:space="preserve">24.8322715759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9886226654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4852676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7703819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6416206359863</t>
   </si>
   <si>
     <t xml:space="preserve">24.8414688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6943168640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1081867218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9518337249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3381156921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4919757843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5379619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4367961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9861354827881</t>
+    <t xml:space="preserve">24.694314956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1081848144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9518356323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.33811378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4919738769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5379638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4367942810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9861373901367</t>
   </si>
   <si>
     <t xml:space="preserve">23.9585437774658</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4000072479248</t>
+    <t xml:space="preserve">24.4000053405762</t>
   </si>
   <si>
     <t xml:space="preserve">23.9493465423584</t>
@@ -3467,16 +3467,16 @@
     <t xml:space="preserve">24.2252635955811</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3197212219238</t>
+    <t xml:space="preserve">25.3197193145752</t>
   </si>
   <si>
     <t xml:space="preserve">26.4693641662598</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4325752258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2762222290039</t>
+    <t xml:space="preserve">26.4325733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2762241363525</t>
   </si>
   <si>
     <t xml:space="preserve">26.3323879241943</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">26.1826133728027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1919727325439</t>
+    <t xml:space="preserve">26.1919746398926</t>
   </si>
   <si>
     <t xml:space="preserve">26.5196075439453</t>
@@ -3497,16 +3497,16 @@
     <t xml:space="preserve">26.4259967803955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6693840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753223419189</t>
+    <t xml:space="preserve">26.6693820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753242492676</t>
   </si>
   <si>
     <t xml:space="preserve">27.3901786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5867595672607</t>
+    <t xml:space="preserve">27.5867576599121</t>
   </si>
   <si>
     <t xml:space="preserve">27.7926998138428</t>
@@ -3521,16 +3521,16 @@
     <t xml:space="preserve">27.3340110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2872047424316</t>
+    <t xml:space="preserve">27.2872066497803</t>
   </si>
   <si>
     <t xml:space="preserve">27.3808155059814</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6990909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1935977935791</t>
+    <t xml:space="preserve">27.699089050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1935958862305</t>
   </si>
   <si>
     <t xml:space="preserve">27.1655139923096</t>
@@ -3539,19 +3539,19 @@
     <t xml:space="preserve">27.9237518310547</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8395023345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8020610809326</t>
+    <t xml:space="preserve">27.8395042419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.802059173584</t>
   </si>
   <si>
     <t xml:space="preserve">28.4011611938477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5602989196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3075504302979</t>
+    <t xml:space="preserve">28.5603008270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3075523376465</t>
   </si>
   <si>
     <t xml:space="preserve">28.6819915771484</t>
@@ -3563,22 +3563,22 @@
     <t xml:space="preserve">28.3169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5041313171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3824367523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4479656219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7568778991699</t>
+    <t xml:space="preserve">28.5041332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.382438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4479637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7568759918213</t>
   </si>
   <si>
     <t xml:space="preserve">27.9799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5696563720703</t>
+    <t xml:space="preserve">28.5696582794189</t>
   </si>
   <si>
     <t xml:space="preserve">28.8317642211914</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">28.419885635376</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4760475158691</t>
+    <t xml:space="preserve">28.4760494232178</t>
   </si>
   <si>
     <t xml:space="preserve">27.6710052490234</t>
@@ -3614,46 +3614,46 @@
     <t xml:space="preserve">28.2701091766357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1390514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2888298034668</t>
+    <t xml:space="preserve">28.1390533447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2888278961182</t>
   </si>
   <si>
     <t xml:space="preserve">28.4854106903076</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3637161254883</t>
+    <t xml:space="preserve">28.3637180328369</t>
   </si>
   <si>
     <t xml:space="preserve">28.7849597930908</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8785705566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0002613067627</t>
+    <t xml:space="preserve">28.8785724639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0002632141113</t>
   </si>
   <si>
     <t xml:space="preserve">29.3934230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2359104156494</t>
+    <t xml:space="preserve">30.2359085083008</t>
   </si>
   <si>
     <t xml:space="preserve">30.3201580047607</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1797466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8146648406982</t>
+    <t xml:space="preserve">30.179744720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8146667480469</t>
   </si>
   <si>
     <t xml:space="preserve">29.992525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9550800323486</t>
+    <t xml:space="preserve">29.9550819396973</t>
   </si>
   <si>
     <t xml:space="preserve">29.8989162445068</t>
@@ -3662,13 +3662,13 @@
     <t xml:space="preserve">29.5619220733643</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5057563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7585010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.805305480957</t>
+    <t xml:space="preserve">29.5057544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7585029602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8053073883057</t>
   </si>
   <si>
     <t xml:space="preserve">29.5806427001953</t>
@@ -3677,10 +3677,10 @@
     <t xml:space="preserve">29.8708343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">29.908275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8333911895752</t>
+    <t xml:space="preserve">29.9082775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8333892822266</t>
   </si>
   <si>
     <t xml:space="preserve">30.2171878814697</t>
@@ -3698,13 +3698,13 @@
     <t xml:space="preserve">30.8537330627441</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0018863677979</t>
+    <t xml:space="preserve">30.0018844604492</t>
   </si>
   <si>
     <t xml:space="preserve">30.5448246002197</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4980182647705</t>
+    <t xml:space="preserve">30.4980163574219</t>
   </si>
   <si>
     <t xml:space="preserve">30.4699325561523</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">30.0299701690674</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3482398986816</t>
+    <t xml:space="preserve">30.348237991333</t>
   </si>
   <si>
     <t xml:space="preserve">29.6742534637451</t>
@@ -3740,22 +3740,22 @@
     <t xml:space="preserve">28.8130435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2420253753662</t>
+    <t xml:space="preserve">28.2420272827148</t>
   </si>
   <si>
     <t xml:space="preserve">27.5212306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4837875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0267219543457</t>
+    <t xml:space="preserve">27.4837856292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0267238616943</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.661642074585</t>
+    <t xml:space="preserve">27.6616439819336</t>
   </si>
   <si>
     <t xml:space="preserve">28.6445465087891</t>
@@ -3764,19 +3764,19 @@
     <t xml:space="preserve">29.224925994873</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2717304229736</t>
+    <t xml:space="preserve">29.2717323303223</t>
   </si>
   <si>
     <t xml:space="preserve">29.2623691558838</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5244770050049</t>
+    <t xml:space="preserve">29.5244789123535</t>
   </si>
   <si>
     <t xml:space="preserve">29.7304172515869</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1610221862793</t>
+    <t xml:space="preserve">30.1610240936279</t>
   </si>
   <si>
     <t xml:space="preserve">30.4792976379395</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">30.5916271209717</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3669624328613</t>
+    <t xml:space="preserve">30.36696434021</t>
   </si>
   <si>
     <t xml:space="preserve">30.6384315490723</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">30.6103496551514</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7694835662842</t>
+    <t xml:space="preserve">30.7694854736328</t>
   </si>
   <si>
     <t xml:space="preserve">31.3030586242676</t>
@@ -3809,49 +3809,49 @@
     <t xml:space="preserve">31.6681385040283</t>
   </si>
   <si>
-    <t xml:space="preserve">31.855354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4341163635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1813659667969</t>
+    <t xml:space="preserve">31.8553581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4341144561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1813678741455</t>
   </si>
   <si>
     <t xml:space="preserve">31.2749767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8179168701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9302406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8101768493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.763370513916</t>
+    <t xml:space="preserve">31.8179149627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9302444458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.810173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7633666992188</t>
   </si>
   <si>
     <t xml:space="preserve">32.6416778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9489688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6962184906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1081047058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6945972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3124198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7320442199707</t>
+    <t xml:space="preserve">31.9489669799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6962203979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1081008911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6945953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3124179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7320423126221</t>
   </si>
   <si>
     <t xml:space="preserve">30.5822639465332</t>
@@ -3860,25 +3860,25 @@
     <t xml:space="preserve">30.8911781311035</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7523822784424</t>
+    <t xml:space="preserve">31.752384185791</t>
   </si>
   <si>
     <t xml:space="preserve">30.9473457336426</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7039585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3576049804688</t>
+    <t xml:space="preserve">30.7039566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3576030731201</t>
   </si>
   <si>
     <t xml:space="preserve">30.0861339569092</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1516590118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5525588989258</t>
+    <t xml:space="preserve">30.1516609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5525608062744</t>
   </si>
   <si>
     <t xml:space="preserve">29.702335357666</t>
@@ -3896,43 +3896,43 @@
     <t xml:space="preserve">31.0690364837646</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9567050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9941463470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9660663604736</t>
+    <t xml:space="preserve">30.9567031860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9941482543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9660682678223</t>
   </si>
   <si>
     <t xml:space="preserve">31.2936992645264</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2468948364258</t>
+    <t xml:space="preserve">31.2468967437744</t>
   </si>
   <si>
     <t xml:space="preserve">31.2656173706055</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6026096343994</t>
+    <t xml:space="preserve">31.602611541748</t>
   </si>
   <si>
     <t xml:space="preserve">31.7804718017578</t>
   </si>
   <si>
-    <t xml:space="preserve">31.377950668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5073757171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9721813201904</t>
+    <t xml:space="preserve">31.3779487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5073776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9721794128418</t>
   </si>
   <si>
     <t xml:space="preserve">27.6335639953613</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0063800811768</t>
+    <t xml:space="preserve">27.0063781738281</t>
   </si>
   <si>
     <t xml:space="preserve">28.0454425811768</t>
@@ -3944,19 +3944,19 @@
     <t xml:space="preserve">28.2045803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0548057556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1187076568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9298686981201</t>
+    <t xml:space="preserve">28.0548038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.118709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9298667907715</t>
   </si>
   <si>
     <t xml:space="preserve">26.0421962738037</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8191604614258</t>
+    <t xml:space="preserve">26.8191585540771</t>
   </si>
   <si>
     <t xml:space="preserve">26.5664100646973</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">26.9970169067383</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1264495849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2294178009033</t>
+    <t xml:space="preserve">26.1264476776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.229419708252</t>
   </si>
   <si>
     <t xml:space="preserve">26.1077251434326</t>
@@ -3998,19 +3998,19 @@
     <t xml:space="preserve">25.9766731262207</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1374282836914</t>
+    <t xml:space="preserve">27.13743019104</t>
   </si>
   <si>
     <t xml:space="preserve">26.9502124786377</t>
   </si>
   <si>
-    <t xml:space="preserve">28.728796005249</t>
+    <t xml:space="preserve">28.7287940979004</t>
   </si>
   <si>
     <t xml:space="preserve">27.5961170196533</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8863105773926</t>
+    <t xml:space="preserve">27.8863086700439</t>
   </si>
   <si>
     <t xml:space="preserve">28.6258239746094</t>
@@ -4022,34 +4022,34 @@
     <t xml:space="preserve">29.0377082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.121955871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1406784057617</t>
+    <t xml:space="preserve">29.1219577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1406764984131</t>
   </si>
   <si>
     <t xml:space="preserve">28.8598480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6071033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2326641082764</t>
+    <t xml:space="preserve">28.6071014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2326622009277</t>
   </si>
   <si>
     <t xml:space="preserve">28.8692092895508</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0096244812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.290454864502</t>
+    <t xml:space="preserve">29.0096225738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2904529571533</t>
   </si>
   <si>
     <t xml:space="preserve">28.9815406799316</t>
   </si>
   <si>
-    <t xml:space="preserve">29.515115737915</t>
+    <t xml:space="preserve">29.5151176452637</t>
   </si>
   <si>
     <t xml:space="preserve">29.3840618133545</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">27.0531826019287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5586776733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8972930908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4666900634766</t>
+    <t xml:space="preserve">27.5586757659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8972911834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4666881561279</t>
   </si>
   <si>
     <t xml:space="preserve">28.4831771850586</t>
@@ -4082,19 +4082,19 @@
     <t xml:space="preserve">29.1981182098389</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2171821594238</t>
+    <t xml:space="preserve">29.2171840667725</t>
   </si>
   <si>
     <t xml:space="preserve">29.5222244262695</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7605381011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0265331268311</t>
+    <t xml:space="preserve">29.7605361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6452312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0265350341797</t>
   </si>
   <si>
     <t xml:space="preserve">29.045597076416</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">26.7482604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0247039794922</t>
+    <t xml:space="preserve">27.0247058868408</t>
   </si>
   <si>
     <t xml:space="preserve">27.1104965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052742004395</t>
+    <t xml:space="preserve">26.6052722930908</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101306915283</t>
@@ -4127,13 +4127,13 @@
     <t xml:space="preserve">26.9675102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2153549194336</t>
+    <t xml:space="preserve">27.215353012085</t>
   </si>
   <si>
     <t xml:space="preserve">27.7682399749756</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5299282073975</t>
+    <t xml:space="preserve">27.5299263000488</t>
   </si>
   <si>
     <t xml:space="preserve">27.8635654449463</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">29.4459648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6547622680664</t>
+    <t xml:space="preserve">28.654764175415</t>
   </si>
   <si>
     <t xml:space="preserve">27.9207630157471</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">28.397388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9684257507324</t>
+    <t xml:space="preserve">27.9684238433838</t>
   </si>
   <si>
     <t xml:space="preserve">28.1304759979248</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">28.4450492858887</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6434020996094</t>
+    <t xml:space="preserve">26.643404006958</t>
   </si>
   <si>
     <t xml:space="preserve">26.3860263824463</t>
@@ -4193,13 +4193,13 @@
     <t xml:space="preserve">26.481351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2430362701416</t>
+    <t xml:space="preserve">26.2430381774902</t>
   </si>
   <si>
     <t xml:space="preserve">26.1667785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.52809715271</t>
+    <t xml:space="preserve">25.5280990600586</t>
   </si>
   <si>
     <t xml:space="preserve">25.0133419036865</t>
@@ -4220,25 +4220,25 @@
     <t xml:space="preserve">24.9847431182861</t>
   </si>
   <si>
-    <t xml:space="preserve">24.746431350708</t>
+    <t xml:space="preserve">24.7464294433594</t>
   </si>
   <si>
     <t xml:space="preserve">24.765495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">24.393726348877</t>
+    <t xml:space="preserve">24.3937282562256</t>
   </si>
   <si>
     <t xml:space="preserve">24.6987686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3374481201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9189319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1658611297607</t>
+    <t xml:space="preserve">25.3374462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9189300537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1658592224121</t>
   </si>
   <si>
     <t xml:space="preserve">25.2993183135986</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">24.9084815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3469791412354</t>
+    <t xml:space="preserve">25.346981048584</t>
   </si>
   <si>
     <t xml:space="preserve">26.2144393920898</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">25.9093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4908828735352</t>
+    <t xml:space="preserve">26.4908847808838</t>
   </si>
   <si>
     <t xml:space="preserve">27.0532989501953</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">27.0437698364258</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6815319061279</t>
+    <t xml:space="preserve">26.6815338134766</t>
   </si>
   <si>
     <t xml:space="preserve">27.2630176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7882213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5031604766846</t>
+    <t xml:space="preserve">28.7882232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5031585693359</t>
   </si>
   <si>
     <t xml:space="preserve">29.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5508232116699</t>
+    <t xml:space="preserve">29.5508213043213</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461486816406</t>
@@ -4298,19 +4298,19 @@
     <t xml:space="preserve">29.9893169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9797878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8939952850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0760250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7051734924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7995834350586</t>
+    <t xml:space="preserve">29.9797859191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8939933776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0760269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.705171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7995853424072</t>
   </si>
   <si>
     <t xml:space="preserve">31.0283622741699</t>
@@ -4340,19 +4340,19 @@
     <t xml:space="preserve">29.3792362213135</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5317554473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1790561676025</t>
+    <t xml:space="preserve">29.5317573547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1790542602539</t>
   </si>
   <si>
     <t xml:space="preserve">29.1885871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4554977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3610858917236</t>
+    <t xml:space="preserve">29.4554958343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3610877990723</t>
   </si>
   <si>
     <t xml:space="preserve">30.7328567504883</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">30.5326709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3515548706055</t>
+    <t xml:space="preserve">30.3515529632568</t>
   </si>
   <si>
     <t xml:space="preserve">30.389684677124</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">29.874927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2362499237061</t>
+    <t xml:space="preserve">29.2362480163574</t>
   </si>
   <si>
     <t xml:space="preserve">28.0160865783691</t>
@@ -4415,10 +4415,10 @@
     <t xml:space="preserve">29.7128753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6842765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2648468017578</t>
+    <t xml:space="preserve">29.6842784881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2648487091064</t>
   </si>
   <si>
     <t xml:space="preserve">29.7033424377441</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">29.3983020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7700710296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7510032653809</t>
+    <t xml:space="preserve">29.7700691223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7510051727295</t>
   </si>
   <si>
     <t xml:space="preserve">30.5422058105469</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">30.4945411682129</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6661262512207</t>
+    <t xml:space="preserve">30.6661243438721</t>
   </si>
   <si>
     <t xml:space="preserve">30.8472461700439</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">31.1236896514893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9434814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9816188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7242336273193</t>
+    <t xml:space="preserve">31.9434833526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.981616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7242374420166</t>
   </si>
   <si>
     <t xml:space="preserve">31.5717163085938</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">30.9521026611328</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5136070251465</t>
+    <t xml:space="preserve">30.5136051177979</t>
   </si>
   <si>
     <t xml:space="preserve">30.942569732666</t>
@@ -4487,13 +4487,13 @@
     <t xml:space="preserve">32.5535697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6289119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8853778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3715343475342</t>
+    <t xml:space="preserve">31.6289100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8853759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3715324401855</t>
   </si>
   <si>
     <t xml:space="preserve">30.7709846496582</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">31.0950889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">31.037899017334</t>
+    <t xml:space="preserve">31.0378971099854</t>
   </si>
   <si>
     <t xml:space="preserve">31.476390838623</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">32.1055374145508</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1246032714844</t>
+    <t xml:space="preserve">32.1246070861816</t>
   </si>
   <si>
     <t xml:space="preserve">32.143669128418</t>
@@ -4526,13 +4526,13 @@
     <t xml:space="preserve">31.8386287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9244213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1341323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2675933837891</t>
+    <t xml:space="preserve">31.9244251251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1341361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2675895690918</t>
   </si>
   <si>
     <t xml:space="preserve">32.8300094604492</t>
@@ -4541,10 +4541,10 @@
     <t xml:space="preserve">33.1064491271973</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8404579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5926132202148</t>
+    <t xml:space="preserve">33.840461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5926170349121</t>
   </si>
   <si>
     <t xml:space="preserve">33.9167213439941</t>
@@ -4553,19 +4553,19 @@
     <t xml:space="preserve">33.9357833862305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.144588470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3542976379395</t>
+    <t xml:space="preserve">33.1445846557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3543014526367</t>
   </si>
   <si>
     <t xml:space="preserve">33.6116752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.468692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6021423339844</t>
+    <t xml:space="preserve">33.4686889648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6021461486816</t>
   </si>
   <si>
     <t xml:space="preserve">33.3161697387695</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">33.3066368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6593437194824</t>
+    <t xml:space="preserve">33.6593399047852</t>
   </si>
   <si>
     <t xml:space="preserve">33.0397262573242</t>
@@ -4601,7 +4601,7 @@
     <t xml:space="preserve">33.373363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.953929901123</t>
+    <t xml:space="preserve">32.9539337158203</t>
   </si>
   <si>
     <t xml:space="preserve">33.3638305664062</t>
@@ -4610,10 +4610,10 @@
     <t xml:space="preserve">33.4114952087402</t>
   </si>
   <si>
-    <t xml:space="preserve">33.583080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0311088562012</t>
+    <t xml:space="preserve">33.5830764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0311126708984</t>
   </si>
   <si>
     <t xml:space="preserve">34.7937126159668</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">35.0892181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5649261474609</t>
+    <t xml:space="preserve">34.5649299621582</t>
   </si>
   <si>
     <t xml:space="preserve">35.2512702941895</t>
@@ -4637,10 +4637,10 @@
     <t xml:space="preserve">35.5372467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5753784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7469596862793</t>
+    <t xml:space="preserve">35.5753746032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7469635009766</t>
   </si>
   <si>
     <t xml:space="preserve">35.3942604064941</t>
@@ -4667,19 +4667,19 @@
     <t xml:space="preserve">34.9843635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5563087463379</t>
+    <t xml:space="preserve">35.5563125610352</t>
   </si>
   <si>
     <t xml:space="preserve">35.3370628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8327522277832</t>
+    <t xml:space="preserve">35.8327560424805</t>
   </si>
   <si>
     <t xml:space="preserve">36.1568603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9376106262207</t>
+    <t xml:space="preserve">35.937614440918</t>
   </si>
   <si>
     <t xml:space="preserve">35.270336151123</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">34.8413696289062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6697845458984</t>
+    <t xml:space="preserve">34.6697883605957</t>
   </si>
   <si>
     <t xml:space="preserve">34.9557609558105</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">34.6888542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1759262084961</t>
+    <t xml:space="preserve">36.1759300231934</t>
   </si>
   <si>
     <t xml:space="preserve">36.1282615661621</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">36.0615386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7097434997559</t>
+    <t xml:space="preserve">36.7097473144531</t>
   </si>
   <si>
     <t xml:space="preserve">37.8631858825684</t>
@@ -4730,13 +4730,13 @@
     <t xml:space="preserve">34.9748268127441</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6707038879395</t>
+    <t xml:space="preserve">35.6707000732422</t>
   </si>
   <si>
     <t xml:space="preserve">33.7546653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2312889099121</t>
+    <t xml:space="preserve">34.2312927246094</t>
   </si>
   <si>
     <t xml:space="preserve">33.8881187438965</t>
@@ -4745,10 +4745,10 @@
     <t xml:space="preserve">34.3552169799805</t>
   </si>
   <si>
-    <t xml:space="preserve">35.108283996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1178131103516</t>
+    <t xml:space="preserve">35.1082878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1178169250488</t>
   </si>
   <si>
     <t xml:space="preserve">34.7746429443359</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">34.8509063720703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.376106262207</t>
+    <t xml:space="preserve">36.3761100769043</t>
   </si>
   <si>
     <t xml:space="preserve">36.5953559875488</t>
   </si>
   <si>
-    <t xml:space="preserve">36.890869140625</t>
+    <t xml:space="preserve">36.8908653259277</t>
   </si>
   <si>
     <t xml:space="preserve">36.2235870361328</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">35.9090118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5286293029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4618988037109</t>
+    <t xml:space="preserve">36.5286254882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4619026184082</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807846069336</t>
@@ -71641,7 +71641,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6519097222</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>1340727</v>
@@ -71662,6 +71662,32 @@
         <v>2148</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6501157407</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>918826</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>88.9199981689453</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>86.3000030517578</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>86.7799987792969</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>88.620002746582</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>2143</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="2149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="2150">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,85 +38,85 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.685154914856</t>
+    <t xml:space="preserve">15.6851568222046</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8714008331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.320761680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.239785194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7458267211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9644641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2964677810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.498911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0616369247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5029001235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5433883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8510971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870908737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9401721954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4098358154297</t>
+    <t xml:space="preserve">15.8714027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3207597732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2397832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7458305358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9644651412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2964668273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4989137649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0616388320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5028991699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5433874130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8510990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870880126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9401712417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4098339080811</t>
   </si>
   <si>
     <t xml:space="preserve">14.923975944519</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1831016540527</t>
+    <t xml:space="preserve">15.2802753448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1831045150757</t>
   </si>
   <si>
     <t xml:space="preserve">14.6243619918823</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3936386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8106079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7296314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8996829986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5190944671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.73362159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3449354171753</t>
+    <t xml:space="preserve">15.3936414718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8106098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7296333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8996810913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5190935134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7336225509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.344934463501</t>
   </si>
   <si>
     <t xml:space="preserve">14.0980157852173</t>
@@ -125,55 +125,55 @@
     <t xml:space="preserve">13.3206396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">13.474494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8955755233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.782205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3328475952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2194795608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057273864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8349027633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5514841079712</t>
+    <t xml:space="preserve">13.4744958877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8955745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7822046279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3328485488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2194814682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057245254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8348999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5514860153198</t>
   </si>
   <si>
     <t xml:space="preserve">14.3409461975098</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8672914505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1021242141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4827136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3774452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017391204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4665193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4908123016357</t>
+    <t xml:space="preserve">14.8672943115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1021223068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2235879898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4827146530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3774461746216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4017372131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4665203094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4908151626587</t>
   </si>
   <si>
     <t xml:space="preserve">15.5232028961182</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">15.5636920928955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1426124572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742300033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8390130996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.587984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.636568069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9199876785278</t>
+    <t xml:space="preserve">15.1426115036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8390111923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879812240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6365699768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9199857711792</t>
   </si>
   <si>
     <t xml:space="preserve">15.8309125900269</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">15.8794994354248</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8228168487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.895694732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2762851715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.122428894043</t>
+    <t xml:space="preserve">15.8228139877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8956966400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2762832641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1224308013916</t>
   </si>
   <si>
     <t xml:space="preserve">15.8471117019653</t>
@@ -224,19 +224,19 @@
     <t xml:space="preserve">15.8875961303711</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4422273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3855428695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2276973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7135562896729</t>
+    <t xml:space="preserve">15.4422245025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3855438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086757659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2276992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7135581970215</t>
   </si>
   <si>
     <t xml:space="preserve">16.6568737030029</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">16.4301376342773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6120529174805</t>
+    <t xml:space="preserve">16.6120548248291</t>
   </si>
   <si>
     <t xml:space="preserve">16.9180011749268</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">16.9758815765381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9924201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6285934448242</t>
+    <t xml:space="preserve">16.9924182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6285915374756</t>
   </si>
   <si>
     <t xml:space="preserve">16.7774295806885</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">17.1081809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9345397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5541763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5955200195312</t>
+    <t xml:space="preserve">16.9345378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5541725158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.595516204834</t>
   </si>
   <si>
     <t xml:space="preserve">16.760892868042</t>
@@ -287,25 +287,25 @@
     <t xml:space="preserve">16.7030143737793</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8766536712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4058628082275</t>
+    <t xml:space="preserve">16.8766574859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4058609008789</t>
   </si>
   <si>
     <t xml:space="preserve">17.7696895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0094833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9681396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8606472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7779560089111</t>
+    <t xml:space="preserve">18.009485244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9681415557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8606491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7779579162598</t>
   </si>
   <si>
     <t xml:space="preserve">17.8854522705078</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">17.6952705383301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1087112426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9598731994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2658157348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748600006104</t>
+    <t xml:space="preserve">18.1087093353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9598712921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2658176422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.174861907959</t>
   </si>
   <si>
     <t xml:space="preserve">18.282356262207</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">18.2988929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4725399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1831302642822</t>
+    <t xml:space="preserve">18.472541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1831283569336</t>
   </si>
   <si>
     <t xml:space="preserve">18.1335144042969</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">18.0425605773926</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8027629852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0921726226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9185256958008</t>
+    <t xml:space="preserve">17.8027648925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0921745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.918529510498</t>
   </si>
   <si>
     <t xml:space="preserve">18.0012149810791</t>
@@ -362,64 +362,64 @@
     <t xml:space="preserve">16.9097309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6368637084961</t>
+    <t xml:space="preserve">16.6368618011475</t>
   </si>
   <si>
     <t xml:space="preserve">16.8022384643555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7366161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5712394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3479766845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9102573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6694087982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8342571258545</t>
+    <t xml:space="preserve">17.7366142272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5712375640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3479785919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9102592468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6694078445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8342580795288</t>
   </si>
   <si>
     <t xml:space="preserve">15.1402053833008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399559020996</t>
+    <t xml:space="preserve">15.2559690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399578094482</t>
   </si>
   <si>
     <t xml:space="preserve">16.2978401184082</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7272930145264</t>
+    <t xml:space="preserve">15.7272911071777</t>
   </si>
   <si>
     <t xml:space="preserve">15.5867214202881</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2311601638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6115245819092</t>
+    <t xml:space="preserve">15.231162071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6115283966064</t>
   </si>
   <si>
     <t xml:space="preserve">16.2813014984131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4632129669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6533946990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6864738464355</t>
+    <t xml:space="preserve">16.4632148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6534004211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6864719390869</t>
   </si>
   <si>
     <t xml:space="preserve">16.6782035827637</t>
@@ -428,37 +428,37 @@
     <t xml:space="preserve">16.7443561553955</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6699352264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8435802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.818775177002</t>
+    <t xml:space="preserve">16.6699371337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8435821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8187732696533</t>
   </si>
   <si>
     <t xml:space="preserve">16.9510765075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.099910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1164531707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2983665466309</t>
+    <t xml:space="preserve">17.0999126434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1164512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2983684539795</t>
   </si>
   <si>
     <t xml:space="preserve">17.2404842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0751056671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3314399719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6208515167236</t>
+    <t xml:space="preserve">17.0751075744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3314418792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6208477020264</t>
   </si>
   <si>
     <t xml:space="preserve">18.1004409790039</t>
@@ -476,52 +476,52 @@
     <t xml:space="preserve">17.7944946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8771858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1914024353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2492809295654</t>
+    <t xml:space="preserve">17.8771839141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1913986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2492828369141</t>
   </si>
   <si>
     <t xml:space="preserve">18.0839042663574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2906265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1665897369385</t>
+    <t xml:space="preserve">18.2906246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1665935516357</t>
   </si>
   <si>
     <t xml:space="preserve">17.9929504394531</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8441104888916</t>
+    <t xml:space="preserve">17.8441066741943</t>
   </si>
   <si>
     <t xml:space="preserve">17.7200756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7283420562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8937225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0673675537109</t>
+    <t xml:space="preserve">17.728343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8937206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0673637390137</t>
   </si>
   <si>
     <t xml:space="preserve">18.3733100891113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9438591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4317207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3572998046875</t>
+    <t xml:space="preserve">18.9438610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4317226409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3573017120361</t>
   </si>
   <si>
     <t xml:space="preserve">19.1009674072266</t>
@@ -530,34 +530,34 @@
     <t xml:space="preserve">19.1257762908936</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1919250488281</t>
+    <t xml:space="preserve">19.1919269561768</t>
   </si>
   <si>
     <t xml:space="preserve">19.1753883361816</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2828826904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1340427398682</t>
+    <t xml:space="preserve">19.2828807830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1340446472168</t>
   </si>
   <si>
     <t xml:space="preserve">19.3490333557129</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978675842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7624740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.70458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4647941589355</t>
+    <t xml:space="preserve">19.4978733062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7624759674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7045879364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4647960662842</t>
   </si>
   <si>
     <t xml:space="preserve">19.0596237182617</t>
@@ -566,22 +566,22 @@
     <t xml:space="preserve">18.646183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1175079345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1588497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.010009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7536792755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9025173187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0844306945801</t>
+    <t xml:space="preserve">19.1175060272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1588535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0100135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7536754608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.902515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0844287872314</t>
   </si>
   <si>
     <t xml:space="preserve">18.9934749603271</t>
@@ -593,28 +593,28 @@
     <t xml:space="preserve">18.7867527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7454109191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3319683074951</t>
+    <t xml:space="preserve">18.7454090118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3319664001465</t>
   </si>
   <si>
     <t xml:space="preserve">17.6291217803955</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8694438934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1505832672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.348503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6627235412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7288722991943</t>
+    <t xml:space="preserve">18.869441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1505794525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3485069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6627197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7288703918457</t>
   </si>
   <si>
     <t xml:space="preserve">18.6875267028809</t>
@@ -629,16 +629,16 @@
     <t xml:space="preserve">18.4808082580566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2327423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3237018585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0590991973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6709899902344</t>
+    <t xml:space="preserve">18.2327442169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3236999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0590972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6709880828857</t>
   </si>
   <si>
     <t xml:space="preserve">18.9355907440186</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">19.8782348632812</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6797847747803</t>
+    <t xml:space="preserve">19.6797866821289</t>
   </si>
   <si>
     <t xml:space="preserve">20.1676445007324</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8451614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7790126800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1428413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9113121032715</t>
+    <t xml:space="preserve">19.8451633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7790145874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1428356170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9113140106201</t>
   </si>
   <si>
     <t xml:space="preserve">20.1759128570557</t>
@@ -674,37 +674,37 @@
     <t xml:space="preserve">20.002269744873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9278507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0105400085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8038215637207</t>
+    <t xml:space="preserve">19.9278469085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0105361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8038196563721</t>
   </si>
   <si>
     <t xml:space="preserve">20.1014957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1263008117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1097660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1924514770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6389675140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1345691680908</t>
+    <t xml:space="preserve">20.1262989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1097602844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1924495697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6389694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1345710754395</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751407623291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2172622680664</t>
+    <t xml:space="preserve">20.2172584533691</t>
   </si>
   <si>
     <t xml:space="preserve">20.3164844512939</t>
@@ -716,40 +716,40 @@
     <t xml:space="preserve">20.3330230712891</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2255306243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6555080413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5066699981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3578300476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4818630218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0849552154541</t>
+    <t xml:space="preserve">20.2255268096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6555061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5066680908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3578281402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4818592071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0849571228027</t>
   </si>
   <si>
     <t xml:space="preserve">20.3991737365723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5645523071289</t>
+    <t xml:space="preserve">20.5645503997803</t>
   </si>
   <si>
     <t xml:space="preserve">20.5397434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6885814666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8947734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4074401855469</t>
+    <t xml:space="preserve">20.6885852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8947772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4074420928955</t>
   </si>
   <si>
     <t xml:space="preserve">20.7133865356445</t>
@@ -758,34 +758,34 @@
     <t xml:space="preserve">20.9697208404541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3495616912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.423978805542</t>
+    <t xml:space="preserve">20.3495597839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4239807128906</t>
   </si>
   <si>
     <t xml:space="preserve">20.3082141876221</t>
   </si>
   <si>
-    <t xml:space="preserve">20.754732131958</t>
+    <t xml:space="preserve">20.7547359466553</t>
   </si>
   <si>
     <t xml:space="preserve">19.9609241485596</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8865089416504</t>
+    <t xml:space="preserve">19.8865032196045</t>
   </si>
   <si>
     <t xml:space="preserve">19.8286247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8534297943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1180362701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5722923278809</t>
+    <t xml:space="preserve">19.8534317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.118034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5722885131836</t>
   </si>
   <si>
     <t xml:space="preserve">19.2994194030762</t>
@@ -794,22 +794,22 @@
     <t xml:space="preserve">19.5144100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5474872589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4234504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6136341094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5640239715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3821105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7376689910889</t>
+    <t xml:space="preserve">19.5474853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.423454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6136360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.564022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3821125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7376670837402</t>
   </si>
   <si>
     <t xml:space="preserve">20.3660984039307</t>
@@ -821,46 +821,46 @@
     <t xml:space="preserve">20.2007217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4901275634766</t>
+    <t xml:space="preserve">20.4901313781738</t>
   </si>
   <si>
     <t xml:space="preserve">20.7381954193115</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2922077178955</t>
+    <t xml:space="preserve">21.2922058105469</t>
   </si>
   <si>
     <t xml:space="preserve">21.1516342163086</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0854835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9366474151611</t>
+    <t xml:space="preserve">21.0854816436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9366455078125</t>
   </si>
   <si>
     <t xml:space="preserve">20.7795372009277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4570541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7051181793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1268310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0435600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1192512512207</t>
+    <t xml:space="preserve">20.4570560455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7051200866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0435581207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1192493438721</t>
   </si>
   <si>
     <t xml:space="preserve">21.8669414520264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9846878051758</t>
+    <t xml:space="preserve">21.9846858978271</t>
   </si>
   <si>
     <t xml:space="preserve">22.2958698272705</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">22.262228012085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5397720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5734062194824</t>
+    <t xml:space="preserve">22.5397682189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5734081268311</t>
   </si>
   <si>
     <t xml:space="preserve">22.5986423492432</t>
@@ -890,22 +890,22 @@
     <t xml:space="preserve">21.6987323760986</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0847759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3202667236328</t>
+    <t xml:space="preserve">21.0847778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3202648162842</t>
   </si>
   <si>
     <t xml:space="preserve">20.9502086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6390247344971</t>
+    <t xml:space="preserve">20.6390266418457</t>
   </si>
   <si>
     <t xml:space="preserve">20.4203605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5549221038818</t>
+    <t xml:space="preserve">20.5549240112305</t>
   </si>
   <si>
     <t xml:space="preserve">20.4540004730225</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">20.9670314788818</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1941108703613</t>
+    <t xml:space="preserve">21.19411277771</t>
   </si>
   <si>
     <t xml:space="preserve">20.8576984405518</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">21.1688823699951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8324680328369</t>
+    <t xml:space="preserve">20.8324661254883</t>
   </si>
   <si>
     <t xml:space="preserve">20.9586219787598</t>
@@ -932,40 +932,40 @@
     <t xml:space="preserve">20.8156452178955</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5978107452393</t>
+    <t xml:space="preserve">21.5978088378906</t>
   </si>
   <si>
     <t xml:space="preserve">21.2613964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1015968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6819114685059</t>
+    <t xml:space="preserve">21.101598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6819133758545</t>
   </si>
   <si>
     <t xml:space="preserve">21.6146278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8164749145508</t>
+    <t xml:space="preserve">21.816478729248</t>
   </si>
   <si>
     <t xml:space="preserve">21.656681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8248882293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5473480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5725784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0351486206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8585300445557</t>
+    <t xml:space="preserve">21.8248901367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5473461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5725765228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0351505279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8585319519043</t>
   </si>
   <si>
     <t xml:space="preserve">21.9258117675781</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">22.3210983276367</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4884738922119</t>
+    <t xml:space="preserve">21.4884757995605</t>
   </si>
   <si>
     <t xml:space="preserve">21.3875503540039</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1949443817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.850118637085</t>
+    <t xml:space="preserve">22.1949481964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8501205444336</t>
   </si>
   <si>
     <t xml:space="preserve">22.2454051971436</t>
@@ -995,25 +995,25 @@
     <t xml:space="preserve">22.0015068054199</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3883838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538166046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5481758117676</t>
+    <t xml:space="preserve">22.3883819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538185119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5481815338135</t>
   </si>
   <si>
     <t xml:space="preserve">22.5313568115234</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7668495178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0696201324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5818214416504</t>
+    <t xml:space="preserve">22.7668476104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0696220397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5818195343018</t>
   </si>
   <si>
     <t xml:space="preserve">22.8425445556641</t>
@@ -1022,40 +1022,40 @@
     <t xml:space="preserve">22.5649967193604</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1444835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2117671966553</t>
+    <t xml:space="preserve">22.1444797515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2117652893066</t>
   </si>
   <si>
     <t xml:space="preserve">22.1865329742432</t>
   </si>
   <si>
-    <t xml:space="preserve">22.52294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7920818328857</t>
+    <t xml:space="preserve">22.5229473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7920799255371</t>
   </si>
   <si>
     <t xml:space="preserve">22.4220237731934</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7500305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9266452789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.93505859375</t>
+    <t xml:space="preserve">22.7500286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9266471862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9350547790527</t>
   </si>
   <si>
     <t xml:space="preserve">22.8593635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7079792022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416152954102</t>
+    <t xml:space="preserve">22.7079753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416172027588</t>
   </si>
   <si>
     <t xml:space="preserve">22.5902328491211</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">21.8417091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1613025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3547420501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3042793273926</t>
+    <t xml:space="preserve">22.1613006591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3547401428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3042774200439</t>
   </si>
   <si>
     <t xml:space="preserve">21.9594535827637</t>
@@ -1082,49 +1082,49 @@
     <t xml:space="preserve">22.2285861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.11083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9174003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3463325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4304332733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.825719833374</t>
+    <t xml:space="preserve">22.1108417510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9174022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3463306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4304351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8257179260254</t>
   </si>
   <si>
     <t xml:space="preserve">23.4649105072021</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6331157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6751670837402</t>
+    <t xml:space="preserve">23.6331176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6751708984375</t>
   </si>
   <si>
     <t xml:space="preserve">23.6835784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8097324371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9106597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9190654754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7508602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8770160675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9863510131836</t>
+    <t xml:space="preserve">23.8097362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9106578826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9190673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7508583068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8770179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9863471984863</t>
   </si>
   <si>
     <t xml:space="preserve">23.8938369750977</t>
@@ -1133,49 +1133,49 @@
     <t xml:space="preserve">23.952709197998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9779357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8517837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0368137359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4741516113281</t>
+    <t xml:space="preserve">23.9779396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.85178565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0368156433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4741554260254</t>
   </si>
   <si>
     <t xml:space="preserve">24.3311786651611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3143577575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0536365509033</t>
+    <t xml:space="preserve">24.3143558502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0536346435547</t>
   </si>
   <si>
     <t xml:space="preserve">23.9358882904053</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8013210296631</t>
+    <t xml:space="preserve">23.8013229370117</t>
   </si>
   <si>
     <t xml:space="preserve">23.9611206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0199909210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.104097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5582542419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5077953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3564071655273</t>
+    <t xml:space="preserve">24.0199928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1040992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5582580566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5077934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3564052581787</t>
   </si>
   <si>
     <t xml:space="preserve">24.3984603881836</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">24.7937450408936</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6928215026855</t>
+    <t xml:space="preserve">24.6928195953369</t>
   </si>
   <si>
     <t xml:space="preserve">24.8946704864502</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">25.2310848236084</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1217517852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1890335083008</t>
+    <t xml:space="preserve">25.1217498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1890316009521</t>
   </si>
   <si>
     <t xml:space="preserve">24.8526210784912</t>
@@ -1208,61 +1208,61 @@
     <t xml:space="preserve">24.4489212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5574226379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3892154693604</t>
+    <t xml:space="preserve">23.5574245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3892135620117</t>
   </si>
   <si>
     <t xml:space="preserve">23.5994739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2125968933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9274768829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6919898986816</t>
+    <t xml:space="preserve">23.2125988006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9274806976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.691987991333</t>
   </si>
   <si>
     <t xml:space="preserve">23.540599822998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5742435455322</t>
+    <t xml:space="preserve">23.5742416381836</t>
   </si>
   <si>
     <t xml:space="preserve">23.3808059692383</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4144477844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5321941375732</t>
+    <t xml:space="preserve">23.4144458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.532190322876</t>
   </si>
   <si>
     <t xml:space="preserve">23.9695320129395</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9939289093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6911563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014167785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9771099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0443878173828</t>
+    <t xml:space="preserve">22.9939308166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6911544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014148712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.977108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0443916320801</t>
   </si>
   <si>
     <t xml:space="preserve">23.02756690979</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0359802246094</t>
+    <t xml:space="preserve">23.035982131958</t>
   </si>
   <si>
     <t xml:space="preserve">22.8930053710938</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">22.6827449798584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.178955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546482086182</t>
+    <t xml:space="preserve">23.1789588928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546501159668</t>
   </si>
   <si>
     <t xml:space="preserve">23.2210102081299</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">23.1621341705322</t>
   </si>
   <si>
-    <t xml:space="preserve">23.229419708252</t>
+    <t xml:space="preserve">23.2294178009033</t>
   </si>
   <si>
     <t xml:space="preserve">23.078031539917</t>
@@ -1298,40 +1298,40 @@
     <t xml:space="preserve">24.1881980895996</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0031700134277</t>
+    <t xml:space="preserve">24.0031719207764</t>
   </si>
   <si>
     <t xml:space="preserve">24.1713790893555</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2218456268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3900508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4909706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8273906707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5246143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3395881652832</t>
+    <t xml:space="preserve">24.2218437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3900489807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4909725189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8273849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5246124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3395862579346</t>
   </si>
   <si>
     <t xml:space="preserve">24.3059463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8686046600342</t>
+    <t xml:space="preserve">23.8686065673828</t>
   </si>
   <si>
     <t xml:space="preserve">23.8349647521973</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2882900238037</t>
+    <t xml:space="preserve">23.2882919311523</t>
   </si>
   <si>
     <t xml:space="preserve">22.9602870941162</t>
@@ -1343,61 +1343,61 @@
     <t xml:space="preserve">23.4564971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7163867950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4556636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.068790435791</t>
+    <t xml:space="preserve">22.7163887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4556655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0687923431396</t>
   </si>
   <si>
     <t xml:space="preserve">22.1781234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0940227508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.908992767334</t>
+    <t xml:space="preserve">22.0940189361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9089908599854</t>
   </si>
   <si>
     <t xml:space="preserve">21.7996559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6314487457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7912464141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3631477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3967914581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2874603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0856094360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6230392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3454990386963</t>
+    <t xml:space="preserve">21.6314506530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7912483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3631496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3967933654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2874622344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0856113433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6230449676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3454971313477</t>
   </si>
   <si>
     <t xml:space="preserve">21.4043712615967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4464206695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.295036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3370876312256</t>
+    <t xml:space="preserve">21.4464225769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2950344085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.337085723877</t>
   </si>
   <si>
     <t xml:space="preserve">21.7407855987549</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">20.3194332122803</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7988262176514</t>
+    <t xml:space="preserve">20.7988224029541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4035377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5717468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7735939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9249782562256</t>
+    <t xml:space="preserve">20.5717430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7735919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9249801635742</t>
   </si>
   <si>
     <t xml:space="preserve">20.8072338104248</t>
@@ -1430,94 +1430,94 @@
     <t xml:space="preserve">21.0288734436035</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8919315338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6351699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.618049621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7464294433594</t>
+    <t xml:space="preserve">20.8919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6351680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6180515289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.746431350708</t>
   </si>
   <si>
     <t xml:space="preserve">20.8662528991699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3883361816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9604015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3626594543457</t>
+    <t xml:space="preserve">21.3883380889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9603996276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3626651763916</t>
   </si>
   <si>
     <t xml:space="preserve">21.5081596374512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8847484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7563667297363</t>
+    <t xml:space="preserve">21.8847465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7563648223877</t>
   </si>
   <si>
     <t xml:space="preserve">22.2270984649658</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9203586578369</t>
+    <t xml:space="preserve">22.9203567504883</t>
   </si>
   <si>
     <t xml:space="preserve">22.4153919219971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4239501953125</t>
+    <t xml:space="preserve">22.4239521026611</t>
   </si>
   <si>
     <t xml:space="preserve">21.8077182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0987186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1072750091553</t>
+    <t xml:space="preserve">22.0987167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1072731018066</t>
   </si>
   <si>
     <t xml:space="preserve">21.7392501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2428417205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.45680809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4054584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9432849884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1216411590576</t>
+    <t xml:space="preserve">21.2428436279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4568099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.405460357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.943286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1302051544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1216449737549</t>
   </si>
   <si>
     <t xml:space="preserve">20.3698482513428</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2685165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.396900177002</t>
+    <t xml:space="preserve">21.268518447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3968982696533</t>
   </si>
   <si>
     <t xml:space="preserve">21.336986541748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3797817230225</t>
+    <t xml:space="preserve">21.3797798156738</t>
   </si>
   <si>
     <t xml:space="preserve">21.011754989624</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">21.1743698120117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8063411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7977828979492</t>
+    <t xml:space="preserve">20.8063449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7977867126465</t>
   </si>
   <si>
     <t xml:space="preserve">21.9960098266602</t>
@@ -1541,28 +1541,28 @@
     <t xml:space="preserve">21.5423984527588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1914863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.909049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4554347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6509132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8563232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8706874847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9306011199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2729530334473</t>
+    <t xml:space="preserve">21.1914882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9090480804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.455436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6509113311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8563213348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8706912994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9306030273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2729511260986</t>
   </si>
   <si>
     <t xml:space="preserve">17.4427490234375</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">17.9355735778809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6260852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2454166412354</t>
+    <t xml:space="preserve">18.6260833740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.245418548584</t>
   </si>
   <si>
     <t xml:space="preserve">18.1657447814941</t>
@@ -1589,28 +1589,28 @@
     <t xml:space="preserve">18.811990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2280654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.997896194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359264373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2988910675049</t>
+    <t xml:space="preserve">19.228063583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9978981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2988872528076</t>
   </si>
   <si>
     <t xml:space="preserve">19.1838035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2103614807129</t>
+    <t xml:space="preserve">19.2103633880615</t>
   </si>
   <si>
     <t xml:space="preserve">19.4139766693115</t>
   </si>
   <si>
-    <t xml:space="preserve">19.520206451416</t>
+    <t xml:space="preserve">19.5202083587646</t>
   </si>
   <si>
     <t xml:space="preserve">19.5113563537598</t>
@@ -1619,25 +1619,25 @@
     <t xml:space="preserve">19.5644702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7238178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6352920532227</t>
+    <t xml:space="preserve">19.7238216400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.635290145874</t>
   </si>
   <si>
     <t xml:space="preserve">19.4316806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1395397186279</t>
+    <t xml:space="preserve">19.1395435333252</t>
   </si>
   <si>
     <t xml:space="preserve">19.0687198638916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2369213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6972637176514</t>
+    <t xml:space="preserve">19.2369194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6972599029541</t>
   </si>
   <si>
     <t xml:space="preserve">19.7503776550293</t>
@@ -1646,25 +1646,25 @@
     <t xml:space="preserve">19.8034934997559</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4405326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0333080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5109996795654</t>
+    <t xml:space="preserve">19.4405288696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2900371551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0333099365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5109958648682</t>
   </si>
   <si>
     <t xml:space="preserve">18.3516483306885</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8208446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7765789031982</t>
+    <t xml:space="preserve">18.8208427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7765808105469</t>
   </si>
   <si>
     <t xml:space="preserve">18.7942848205566</t>
@@ -1673,10 +1673,10 @@
     <t xml:space="preserve">18.9182224273682</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1129837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4847965240479</t>
+    <t xml:space="preserve">19.1129817962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4847946166992</t>
   </si>
   <si>
     <t xml:space="preserve">19.6707019805908</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">19.5733242034912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2015132904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.219217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0952758789062</t>
+    <t xml:space="preserve">19.201509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2192134857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0952739715576</t>
   </si>
   <si>
     <t xml:space="preserve">18.696907043457</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1218357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2546272277832</t>
+    <t xml:space="preserve">19.1218376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2546253204346</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906734466553</t>
@@ -1709,46 +1709,46 @@
     <t xml:space="preserve">18.4136199951172</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6792030334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6880493164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1483936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9890480041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0510101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5995254516602</t>
+    <t xml:space="preserve">18.67919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6880512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1483955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9890441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0510120391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5995273590088</t>
   </si>
   <si>
     <t xml:space="preserve">18.3427963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">18.431324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3693580627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7585182189941</t>
+    <t xml:space="preserve">18.4313259124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3693561553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7585163116455</t>
   </si>
   <si>
     <t xml:space="preserve">17.6965503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4840850830078</t>
+    <t xml:space="preserve">17.4840869903564</t>
   </si>
   <si>
     <t xml:space="preserve">17.9001617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4176864624023</t>
+    <t xml:space="preserve">17.4176902770996</t>
   </si>
   <si>
     <t xml:space="preserve">17.0325965881348</t>
@@ -1757,43 +1757,43 @@
     <t xml:space="preserve">16.6342258453369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4527435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9392881393433</t>
+    <t xml:space="preserve">16.4527416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9392890930176</t>
   </si>
   <si>
     <t xml:space="preserve">15.5719032287598</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4346857070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.465669631958</t>
+    <t xml:space="preserve">15.4346828460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4656686782837</t>
   </si>
   <si>
     <t xml:space="preserve">16.7316055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2712650299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7666606903076</t>
+    <t xml:space="preserve">16.2712631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.766658782959</t>
   </si>
   <si>
     <t xml:space="preserve">15.2133665084839</t>
   </si>
   <si>
-    <t xml:space="preserve">15.173529624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6777801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2262916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7840137481689</t>
+    <t xml:space="preserve">15.1735315322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6777791976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2262897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7840118408203</t>
   </si>
   <si>
     <t xml:space="preserve">14.6290893554688</t>
@@ -1802,28 +1802,28 @@
     <t xml:space="preserve">14.9743461608887</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0717248916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1912364959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7179718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2933959960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171590805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8596181869507</t>
+    <t xml:space="preserve">15.0717239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.191234588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7179698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2933979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171571731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8596153259277</t>
   </si>
   <si>
     <t xml:space="preserve">16.0986366271973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.103063583374</t>
+    <t xml:space="preserve">16.1030654907227</t>
   </si>
   <si>
     <t xml:space="preserve">15.7755146026611</t>
@@ -1838,55 +1838,55 @@
     <t xml:space="preserve">15.4833745956421</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6910591125488</t>
+    <t xml:space="preserve">14.6910572052002</t>
   </si>
   <si>
     <t xml:space="preserve">14.2882595062256</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2041606903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9739904403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8766107559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0802211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9916934967041</t>
+    <t xml:space="preserve">14.204158782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9739894866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8766098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0802221298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9916954040527</t>
   </si>
   <si>
     <t xml:space="preserve">13.7880821228027</t>
   </si>
   <si>
-    <t xml:space="preserve">13.624306678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1554698944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3148193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0451669692993</t>
+    <t xml:space="preserve">13.6243085861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1554689407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3148183822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.045166015625</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254770278931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1112060546875</t>
+    <t xml:space="preserve">14.1112070083618</t>
   </si>
   <si>
     <t xml:space="preserve">13.4959440231323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3675804138184</t>
+    <t xml:space="preserve">13.3675785064697</t>
   </si>
   <si>
     <t xml:space="preserve">13.2524948120117</t>
@@ -1895,40 +1895,40 @@
     <t xml:space="preserve">14.0669431686401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7707319259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8415546417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6954860687256</t>
+    <t xml:space="preserve">14.7707328796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.841552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6954851150513</t>
   </si>
   <si>
     <t xml:space="preserve">14.6512203216553</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8946704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0628719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8813924789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8282766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9345064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4479646682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7131910324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558237075806</t>
+    <t xml:space="preserve">14.8946685791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0628690719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8813905715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8282747268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9345083236694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4479665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7131900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558256149292</t>
   </si>
   <si>
     <t xml:space="preserve">15.2886152267456</t>
@@ -1937,34 +1937,34 @@
     <t xml:space="preserve">15.6958389282227</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3155307769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4129104614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1163425445557</t>
+    <t xml:space="preserve">16.3155326843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4129066467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1163444519043</t>
   </si>
   <si>
     <t xml:space="preserve">16.0145359039307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8020734786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1340484619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2358531951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4793033599854</t>
+    <t xml:space="preserve">15.8020725250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1340522766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2358551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.479305267334</t>
   </si>
   <si>
     <t xml:space="preserve">16.4748783111572</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3376617431641</t>
+    <t xml:space="preserve">16.3376598358154</t>
   </si>
   <si>
     <t xml:space="preserve">16.2181491851807</t>
@@ -1973,13 +1973,13 @@
     <t xml:space="preserve">16.2889709472656</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5811080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5412693023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7758712768555</t>
+    <t xml:space="preserve">16.5811100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5412750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7758693695068</t>
   </si>
   <si>
     <t xml:space="preserve">16.4881572723389</t>
@@ -1988,19 +1988,19 @@
     <t xml:space="preserve">16.7935752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6297969818115</t>
+    <t xml:space="preserve">16.6297988891602</t>
   </si>
   <si>
     <t xml:space="preserve">16.9263668060303</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9481430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9304399490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9614219665527</t>
+    <t xml:space="preserve">15.9481401443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9304370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9614229202271</t>
   </si>
   <si>
     <t xml:space="preserve">16.5279941558838</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">16.5368480682373</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6784915924072</t>
+    <t xml:space="preserve">16.6784896850586</t>
   </si>
   <si>
     <t xml:space="preserve">16.5855369567871</t>
@@ -2018,103 +2018,103 @@
     <t xml:space="preserve">16.7138996124268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1292695999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5763273239136</t>
+    <t xml:space="preserve">15.1292686462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5763282775879</t>
   </si>
   <si>
     <t xml:space="preserve">15.8197793960571</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0101089477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8906002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8463382720947</t>
+    <t xml:space="preserve">16.0101108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8906011581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8463363647461</t>
   </si>
   <si>
     <t xml:space="preserve">15.3992748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2930431365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9610633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876232147217</t>
+    <t xml:space="preserve">15.2930421829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9610652923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876251220703</t>
   </si>
   <si>
     <t xml:space="preserve">14.885817527771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3767871856689</t>
+    <t xml:space="preserve">14.3767881393433</t>
   </si>
   <si>
     <t xml:space="preserve">14.4874458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6069583892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5626955032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7795848846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4125537872314</t>
+    <t xml:space="preserve">14.6069564819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5626945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7795839309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4125556945801</t>
   </si>
   <si>
     <t xml:space="preserve">15.2222194671631</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0540170669556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9212255477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6423692703247</t>
+    <t xml:space="preserve">15.0540189743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9212284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6423683166504</t>
   </si>
   <si>
     <t xml:space="preserve">14.9300804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8592586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1868114471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0230340957642</t>
+    <t xml:space="preserve">14.8592596054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1868104934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0230360031128</t>
   </si>
   <si>
     <t xml:space="preserve">14.9477863311768</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4476099014282</t>
+    <t xml:space="preserve">14.4476089477539</t>
   </si>
   <si>
     <t xml:space="preserve">13.2436418533325</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5534858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6552925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6420125961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1997327804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4564628601074</t>
+    <t xml:space="preserve">13.5534868240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.655291557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6420116424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1997346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4564619064331</t>
   </si>
   <si>
     <t xml:space="preserve">14.4431829452515</t>
@@ -2123,19 +2123,19 @@
     <t xml:space="preserve">14.682204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8459806442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2177963256836</t>
+    <t xml:space="preserve">14.8459796905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.217794418335</t>
   </si>
   <si>
     <t xml:space="preserve">15.0495920181274</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2089395523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.031886100769</t>
+    <t xml:space="preserve">15.2089414596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0318870544434</t>
   </si>
   <si>
     <t xml:space="preserve">15.1823816299438</t>
@@ -2144,31 +2144,31 @@
     <t xml:space="preserve">14.496298789978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1820268630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2000875473022</t>
+    <t xml:space="preserve">14.1820278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2000894546509</t>
   </si>
   <si>
     <t xml:space="preserve">15.1381196975708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3151712417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3063220977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6467962265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3723602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8589038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7748050689697</t>
+    <t xml:space="preserve">15.3151721954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3063230514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6467943191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3723621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589029312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7748022079468</t>
   </si>
   <si>
     <t xml:space="preserve">13.5977487564087</t>
@@ -2177,19 +2177,19 @@
     <t xml:space="preserve">13.7792291641235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5888967514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6774234771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2170848846436</t>
+    <t xml:space="preserve">13.5888957977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6774225234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2170839309692</t>
   </si>
   <si>
     <t xml:space="preserve">13.5313549041748</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3502283096313</t>
+    <t xml:space="preserve">14.350227355957</t>
   </si>
   <si>
     <t xml:space="preserve">14.3192443847656</t>
@@ -2198,76 +2198,76 @@
     <t xml:space="preserve">14.2705564498901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353229522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9256563186646</t>
+    <t xml:space="preserve">14.6999111175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353239059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9256553649902</t>
   </si>
   <si>
     <t xml:space="preserve">14.6600732803345</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7486028671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9079475402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2266473770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5807552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9127321243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0942134857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8584632873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9808721542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675308227539</t>
+    <t xml:space="preserve">14.7486009597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9079504013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2266454696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.580756187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9127311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0942115783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8584661483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9808731079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675317764282</t>
   </si>
   <si>
     <t xml:space="preserve">16.2302188873291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5838375091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5929069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6609115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7243785858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.411563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6427745819092</t>
+    <t xml:space="preserve">16.456901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5838394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.592903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.66090965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7243766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7425155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4115619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6427726745605</t>
   </si>
   <si>
     <t xml:space="preserve">16.9827919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.941987991333</t>
+    <t xml:space="preserve">16.9419898986816</t>
   </si>
   <si>
     <t xml:space="preserve">17.0326614379883</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">17.4542865753174</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9646587371826</t>
+    <t xml:space="preserve">16.964656829834</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555912017822</t>
@@ -2288,55 +2288,55 @@
     <t xml:space="preserve">17.0462627410889</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0436496734619</t>
+    <t xml:space="preserve">18.0436515808105</t>
   </si>
   <si>
     <t xml:space="preserve">18.0935192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1116561889648</t>
+    <t xml:space="preserve">18.1116542816162</t>
   </si>
   <si>
     <t xml:space="preserve">17.7263011932373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1414699554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7833156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9283905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5268211364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1505355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9963932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8875885009766</t>
+    <t xml:space="preserve">17.1414680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7833137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9283885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5268230438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1505374908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.996395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8875846862793</t>
   </si>
   <si>
     <t xml:space="preserve">16.9601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3726806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7787799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7923851013184</t>
+    <t xml:space="preserve">17.3726787567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7787818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7923831939697</t>
   </si>
   <si>
     <t xml:space="preserve">16.7017116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">16.030740737915</t>
+    <t xml:space="preserve">16.0307426452637</t>
   </si>
   <si>
     <t xml:space="preserve">16.0715446472168</t>
@@ -2348,70 +2348,70 @@
     <t xml:space="preserve">16.8150501251221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5948257446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3862819671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0054626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9782581329346</t>
+    <t xml:space="preserve">17.5948276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3862838745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0054607391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9782600402832</t>
   </si>
   <si>
     <t xml:space="preserve">17.2774753570557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2276058197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0209846496582</t>
+    <t xml:space="preserve">17.2276077270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0209827423096</t>
   </si>
   <si>
     <t xml:space="preserve">18.0481853485107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0073833465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2068614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7508888244629</t>
+    <t xml:space="preserve">18.0073852539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.206859588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7508907318115</t>
   </si>
   <si>
     <t xml:space="preserve">18.2975311279297</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3519344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2884616851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4244728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9775676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0501041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0410404205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3156661987305</t>
+    <t xml:space="preserve">18.3519325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2884654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4244689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9775695800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.050106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0410385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3156681060791</t>
   </si>
   <si>
     <t xml:space="preserve">17.7716369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0617847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8804397583008</t>
+    <t xml:space="preserve">18.06178855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8804416656494</t>
   </si>
   <si>
     <t xml:space="preserve">18.0889873504639</t>
@@ -2426,19 +2426,19 @@
     <t xml:space="preserve">17.7217674255371</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8623104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7126998901367</t>
+    <t xml:space="preserve">17.8623085021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7126979827881</t>
   </si>
   <si>
     <t xml:space="preserve">17.0598640441895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0507946014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.973726272583</t>
+    <t xml:space="preserve">17.0507984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9737281799316</t>
   </si>
   <si>
     <t xml:space="preserve">17.0961322784424</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">16.8921203613281</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2366733551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7671031951904</t>
+    <t xml:space="preserve">17.2366752624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7671012878418</t>
   </si>
   <si>
     <t xml:space="preserve">18.0753841400146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4698085784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5060768127441</t>
+    <t xml:space="preserve">18.4698104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5060749053955</t>
   </si>
   <si>
     <t xml:space="preserve">18.7236881256104</t>
@@ -2468,19 +2468,19 @@
     <t xml:space="preserve">18.71462059021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2703285217285</t>
+    <t xml:space="preserve">18.2703304290771</t>
   </si>
   <si>
     <t xml:space="preserve">18.1887245178223</t>
   </si>
   <si>
-    <t xml:space="preserve">18.57861328125</t>
+    <t xml:space="preserve">18.5786151885986</t>
   </si>
   <si>
     <t xml:space="preserve">18.9594345092773</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7690258026123</t>
+    <t xml:space="preserve">18.7690238952637</t>
   </si>
   <si>
     <t xml:space="preserve">18.7418212890625</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">18.7780895233154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2223834991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7120113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5216007232666</t>
+    <t xml:space="preserve">19.2223815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7120094299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.521598815918</t>
   </si>
   <si>
     <t xml:space="preserve">19.81174659729</t>
@@ -2504,85 +2504,85 @@
     <t xml:space="preserve">19.4490623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3130512237549</t>
+    <t xml:space="preserve">19.3130550384521</t>
   </si>
   <si>
     <t xml:space="preserve">18.7962245941162</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4970073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1732063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4225521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8033714294434</t>
+    <t xml:space="preserve">18.4970111846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1732025146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.422550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.803373336792</t>
   </si>
   <si>
     <t xml:space="preserve">17.9121761322021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.039119720459</t>
+    <t xml:space="preserve">18.0391159057617</t>
   </si>
   <si>
     <t xml:space="preserve">17.9892463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0663223266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8596954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9050312042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7599582672119</t>
+    <t xml:space="preserve">18.0663166046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8596973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9050331115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7599563598633</t>
   </si>
   <si>
     <t xml:space="preserve">18.3791351318359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4399948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9685020446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0863723754883</t>
+    <t xml:space="preserve">19.4399929046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9685001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0863761901855</t>
   </si>
   <si>
     <t xml:space="preserve">19.1951808929443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5760059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6394729614258</t>
+    <t xml:space="preserve">19.5760021209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6394710540771</t>
   </si>
   <si>
     <t xml:space="preserve">19.4218597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7392120361328</t>
+    <t xml:space="preserve">19.7392101287842</t>
   </si>
   <si>
     <t xml:space="preserve">19.94775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0021553039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8661499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.485330581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6757411956787</t>
+    <t xml:space="preserve">20.0021533966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8661518096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4853286743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6757431030273</t>
   </si>
   <si>
     <t xml:space="preserve">19.2133140563965</t>
@@ -2597,28 +2597,28 @@
     <t xml:space="preserve">19.0319709777832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.294921875</t>
+    <t xml:space="preserve">19.2949199676514</t>
   </si>
   <si>
     <t xml:space="preserve">19.2677192687988</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5941371917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8570823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4127941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9957046508789</t>
+    <t xml:space="preserve">19.5941352844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.857084274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4127922058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9957008361816</t>
   </si>
   <si>
     <t xml:space="preserve">18.6602172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5332794189453</t>
+    <t xml:space="preserve">18.5332775115967</t>
   </si>
   <si>
     <t xml:space="preserve">18.9322338104248</t>
@@ -2636,34 +2636,34 @@
     <t xml:space="preserve">19.9658889770508</t>
   </si>
   <si>
-    <t xml:space="preserve">20.337646484375</t>
+    <t xml:space="preserve">20.3376426696777</t>
   </si>
   <si>
     <t xml:space="preserve">20.9088745117188</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3259658813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5526447296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0331993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6977195739746</t>
+    <t xml:space="preserve">21.325963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5526428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0332012176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.697717666626</t>
   </si>
   <si>
     <t xml:space="preserve">22.4049530029297</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8337249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9814128875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.993091583252</t>
+    <t xml:space="preserve">21.8337230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.981409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9930896759033</t>
   </si>
   <si>
     <t xml:space="preserve">20.192569732666</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">19.3039875030518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.385591506958</t>
+    <t xml:space="preserve">19.3855895996094</t>
   </si>
   <si>
     <t xml:space="preserve">18.4607410430908</t>
@@ -2681,22 +2681,22 @@
     <t xml:space="preserve">18.6511516571045</t>
   </si>
   <si>
-    <t xml:space="preserve">18.623950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0300521850586</t>
+    <t xml:space="preserve">18.6239490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.03005027771</t>
   </si>
   <si>
     <t xml:space="preserve">16.8195838928223</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4685773849487</t>
+    <t xml:space="preserve">15.4685764312744</t>
   </si>
   <si>
     <t xml:space="preserve">14.6842679977417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8112077713013</t>
+    <t xml:space="preserve">14.811206817627</t>
   </si>
   <si>
     <t xml:space="preserve">12.653223991394</t>
@@ -2705,37 +2705,37 @@
     <t xml:space="preserve">13.7412824630737</t>
   </si>
   <si>
-    <t xml:space="preserve">13.777551651001</t>
+    <t xml:space="preserve">13.7775526046753</t>
   </si>
   <si>
     <t xml:space="preserve">14.3170480728149</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7341384887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1648263931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6914138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0903673171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690982818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0242862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0061521530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2354431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8863573074341</t>
+    <t xml:space="preserve">14.7341365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1648283004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6914148330688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0903692245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.269100189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0242872238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0061502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2354421615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">13.238055229187</t>
@@ -2744,19 +2744,19 @@
     <t xml:space="preserve">13.4783353805542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5327396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9660425186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4511337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.809287071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1901063919067</t>
+    <t xml:space="preserve">13.5327386856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9660415649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4511346817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8092851638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1901073455811</t>
   </si>
   <si>
     <t xml:space="preserve">14.2581119537354</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">13.3695297241211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8727569580078</t>
+    <t xml:space="preserve">13.8727579116821</t>
   </si>
   <si>
     <t xml:space="preserve">13.9634284973145</t>
@@ -2780,28 +2780,28 @@
     <t xml:space="preserve">14.4485216140747</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5346603393555</t>
+    <t xml:space="preserve">14.5346593856812</t>
   </si>
   <si>
     <t xml:space="preserve">15.1512260437012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3643035888672</t>
+    <t xml:space="preserve">15.3643045425415</t>
   </si>
   <si>
     <t xml:space="preserve">15.6544532775879</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5683164596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346170425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6291751861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7768583297729</t>
+    <t xml:space="preserve">15.5683174133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3461685180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6291732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7768602371216</t>
   </si>
   <si>
     <t xml:space="preserve">15.7904644012451</t>
@@ -2810,10 +2810,10 @@
     <t xml:space="preserve">16.4478302001953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3752937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1097354888916</t>
+    <t xml:space="preserve">16.3752918243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.109733581543</t>
   </si>
   <si>
     <t xml:space="preserve">16.0398082733154</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">16.4030952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.88134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7066020965576</t>
+    <t xml:space="preserve">16.8813457489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7066040039062</t>
   </si>
   <si>
     <t xml:space="preserve">17.2906188964844</t>
@@ -2840,19 +2840,19 @@
     <t xml:space="preserve">17.9896011352539</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4515686035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6585083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6079177856445</t>
+    <t xml:space="preserve">17.4515705108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6585063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6079196929932</t>
   </si>
   <si>
     <t xml:space="preserve">17.355001449585</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6309146881104</t>
+    <t xml:space="preserve">17.6309127807617</t>
   </si>
   <si>
     <t xml:space="preserve">17.9850044250488</t>
@@ -2864,37 +2864,37 @@
     <t xml:space="preserve">18.6334018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7529621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8081455230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6701889038086</t>
+    <t xml:space="preserve">18.752965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8081474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.67018699646</t>
   </si>
   <si>
     <t xml:space="preserve">17.7090873718262</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6631011962891</t>
+    <t xml:space="preserve">17.6631031036377</t>
   </si>
   <si>
     <t xml:space="preserve">17.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3482894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885093688965</t>
+    <t xml:space="preserve">18.3482913970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885055541992</t>
   </si>
   <si>
     <t xml:space="preserve">18.5874137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9093151092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8173427581787</t>
+    <t xml:space="preserve">18.9093132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8173408508301</t>
   </si>
   <si>
     <t xml:space="preserve">19.222017288208</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">18.7161750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9644985198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7897510528564</t>
+    <t xml:space="preserve">18.9644966125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7897529602051</t>
   </si>
   <si>
     <t xml:space="preserve">19.0104827880859</t>
@@ -2915,13 +2915,13 @@
     <t xml:space="preserve">19.0748634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.57151222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3507785797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9761829376221</t>
+    <t xml:space="preserve">19.5715084075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3507766723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9761810302734</t>
   </si>
   <si>
     <t xml:space="preserve">19.9577903747559</t>
@@ -2930,40 +2930,40 @@
     <t xml:space="preserve">19.6542835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278614044189</t>
+    <t xml:space="preserve">19.7278633117676</t>
   </si>
   <si>
     <t xml:space="preserve">19.9301986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4703407287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0957450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2704906463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3256721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1534156799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.960277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3281631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0154590606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0430488586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4912223815918</t>
+    <t xml:space="preserve">19.4703388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0957431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2704925537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3256740570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1534175872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9602756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3281650543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0154609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0430507659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4912242889404</t>
   </si>
   <si>
     <t xml:space="preserve">20.2245063781738</t>
@@ -2972,25 +2972,25 @@
     <t xml:space="preserve">20.2337017059326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8934097290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8223190307617</t>
+    <t xml:space="preserve">19.8934078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8223209381104</t>
   </si>
   <si>
     <t xml:space="preserve">20.4176464080811</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3808555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.206111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5556030273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8775043487549</t>
+    <t xml:space="preserve">20.3808574676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2061100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5556049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8775024414062</t>
   </si>
   <si>
     <t xml:space="preserve">21.0614452362061</t>
@@ -3002,19 +3002,19 @@
     <t xml:space="preserve">20.7579383850098</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7395458221436</t>
+    <t xml:space="preserve">20.7395439147949</t>
   </si>
   <si>
     <t xml:space="preserve">20.6291809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2453880310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3649520874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4201374053955</t>
+    <t xml:space="preserve">21.2453899383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3649501800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4201354980469</t>
   </si>
   <si>
     <t xml:space="preserve">21.4937133789062</t>
@@ -3029,10 +3029,10 @@
     <t xml:space="preserve">21.5213012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0271472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6040782928467</t>
+    <t xml:space="preserve">22.0271453857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.604076385498</t>
   </si>
   <si>
     <t xml:space="preserve">21.8156089782715</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">21.7420330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1191177368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.514591217041</t>
+    <t xml:space="preserve">22.1191158294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5145950317383</t>
   </si>
   <si>
     <t xml:space="preserve">22.6341571807861</t>
@@ -3059,49 +3059,49 @@
     <t xml:space="preserve">22.6433525085449</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3674373626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4410133361816</t>
+    <t xml:space="preserve">22.3674392700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4410152435303</t>
   </si>
   <si>
     <t xml:space="preserve">22.2294807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6709423065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4870014190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9008712768555</t>
+    <t xml:space="preserve">22.6709442138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.487003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9008731842041</t>
   </si>
   <si>
     <t xml:space="preserve">22.8732833862305</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8456897735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2135772705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2411670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6550388336182</t>
+    <t xml:space="preserve">22.8456935882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2135734558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2411651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6550350189209</t>
   </si>
   <si>
     <t xml:space="preserve">23.5262794494629</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5722637176514</t>
+    <t xml:space="preserve">23.5722618103027</t>
   </si>
   <si>
     <t xml:space="preserve">24.0045299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7194175720215</t>
+    <t xml:space="preserve">23.7194194793701</t>
   </si>
   <si>
     <t xml:space="preserve">24.3356246948242</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">24.3264293670654</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8757705688477</t>
+    <t xml:space="preserve">23.875768661499</t>
   </si>
   <si>
     <t xml:space="preserve">24.1700801849365</t>
@@ -3122,19 +3122,19 @@
     <t xml:space="preserve">22.6525497436523</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7261257171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1926956176758</t>
+    <t xml:space="preserve">22.7261276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9560565948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1926937103271</t>
   </si>
   <si>
     <t xml:space="preserve">21.6684551239014</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1994018554688</t>
+    <t xml:space="preserve">21.1993999481201</t>
   </si>
   <si>
     <t xml:space="preserve">21.6500644683838</t>
@@ -3143,31 +3143,31 @@
     <t xml:space="preserve">21.4661197662354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0823287963867</t>
+    <t xml:space="preserve">22.0823268890381</t>
   </si>
   <si>
     <t xml:space="preserve">22.5881690979004</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0413208007812</t>
+    <t xml:space="preserve">24.041316986084</t>
   </si>
   <si>
     <t xml:space="preserve">23.0112400054932</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1216049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6274471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2988395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9677429199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3607311248779</t>
+    <t xml:space="preserve">23.121603012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2988376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9677391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3607273101807</t>
   </si>
   <si>
     <t xml:space="preserve">23.8665733337402</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">24.4459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0965042114258</t>
+    <t xml:space="preserve">24.0965003967285</t>
   </si>
   <si>
     <t xml:space="preserve">24.7403011322021</t>
@@ -3191,31 +3191,31 @@
     <t xml:space="preserve">25.2277488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8966522216797</t>
+    <t xml:space="preserve">24.8966503143311</t>
   </si>
   <si>
     <t xml:space="preserve">24.4092044830322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5471591949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.062198638916</t>
+    <t xml:space="preserve">24.5471611022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0622005462646</t>
   </si>
   <si>
     <t xml:space="preserve">24.5655536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6391334533691</t>
+    <t xml:space="preserve">24.6391315460205</t>
   </si>
   <si>
     <t xml:space="preserve">24.6023426055908</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8874530792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3105239868164</t>
+    <t xml:space="preserve">24.8874568939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3105201721191</t>
   </si>
   <si>
     <t xml:space="preserve">25.568042755127</t>
@@ -3224,10 +3224,10 @@
     <t xml:space="preserve">25.0805950164795</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3841018676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.503662109375</t>
+    <t xml:space="preserve">25.3840999603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5036602020264</t>
   </si>
   <si>
     <t xml:space="preserve">25.3749027252197</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">25.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6257133483887</t>
+    <t xml:space="preserve">26.6257152557373</t>
   </si>
   <si>
     <t xml:space="preserve">26.5613327026367</t>
@@ -3248,13 +3248,13 @@
     <t xml:space="preserve">26.7452754974365</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8740348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0119934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5546226501465</t>
+    <t xml:space="preserve">26.8740367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0119953155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5546245574951</t>
   </si>
   <si>
     <t xml:space="preserve">28.2811985015869</t>
@@ -3272,43 +3272,43 @@
     <t xml:space="preserve">26.5521373748779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8715476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1106719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.843957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0279006958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7519855499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6876049041748</t>
+    <t xml:space="preserve">25.8715496063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1106739044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8439540863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0278968811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7519874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6876068115234</t>
   </si>
   <si>
     <t xml:space="preserve">24.7127094268799</t>
   </si>
   <si>
-    <t xml:space="preserve">24.280445098877</t>
+    <t xml:space="preserve">24.2804431915283</t>
   </si>
   <si>
     <t xml:space="preserve">25.1449737548828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5011749267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0346069335938</t>
+    <t xml:space="preserve">24.5011768341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0346088409424</t>
   </si>
   <si>
     <t xml:space="preserve">25.236946105957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6968059539795</t>
+    <t xml:space="preserve">25.6968021392822</t>
   </si>
   <si>
     <t xml:space="preserve">26.0462951660156</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">25.9175338745117</t>
   </si>
   <si>
-    <t xml:space="preserve">26.28542137146</t>
+    <t xml:space="preserve">26.2854194641113</t>
   </si>
   <si>
     <t xml:space="preserve">25.9267330169678</t>
@@ -3326,16 +3326,16 @@
     <t xml:space="preserve">25.9083366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">26.119873046875</t>
+    <t xml:space="preserve">26.1198711395264</t>
   </si>
   <si>
     <t xml:space="preserve">26.0003089904785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6600131988525</t>
+    <t xml:space="preserve">25.9635200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6600170135498</t>
   </si>
   <si>
     <t xml:space="preserve">25.0530033111572</t>
@@ -3350,28 +3350,28 @@
     <t xml:space="preserve">24.1608810424805</t>
   </si>
   <si>
-    <t xml:space="preserve">24.556360244751</t>
+    <t xml:space="preserve">24.5563583374023</t>
   </si>
   <si>
     <t xml:space="preserve">24.519567489624</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0162162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9150447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9058494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.013729095459</t>
+    <t xml:space="preserve">25.0162143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9150485992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9058475494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0137252807617</t>
   </si>
   <si>
     <t xml:space="preserve">24.2712478637695</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2001571655273</t>
+    <t xml:space="preserve">25.2001552581787</t>
   </si>
   <si>
     <t xml:space="preserve">24.2620487213135</t>
@@ -3380,10 +3380,10 @@
     <t xml:space="preserve">23.673433303833</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5446739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6918277740479</t>
+    <t xml:space="preserve">23.5446720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6918258666992</t>
   </si>
   <si>
     <t xml:space="preserve">23.4251098632812</t>
@@ -3395,52 +3395,52 @@
     <t xml:space="preserve">23.5170803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7838020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1056976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1516857147217</t>
+    <t xml:space="preserve">23.7838001251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1056957244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.151683807373</t>
   </si>
   <si>
     <t xml:space="preserve">24.5287666320801</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8138790130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8322715759277</t>
+    <t xml:space="preserve">24.8138771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8322734832764</t>
   </si>
   <si>
     <t xml:space="preserve">24.9886226654053</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4852676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7703819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6416206359863</t>
+    <t xml:space="preserve">25.4852695465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7703800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6416187286377</t>
   </si>
   <si>
     <t xml:space="preserve">24.8414688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">24.694314956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1081848144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9518356323242</t>
+    <t xml:space="preserve">24.6943168640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1081867218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9518337249756</t>
   </si>
   <si>
     <t xml:space="preserve">25.33811378479</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4919738769531</t>
+    <t xml:space="preserve">24.4919757843018</t>
   </si>
   <si>
     <t xml:space="preserve">24.5379638671875</t>
@@ -3449,34 +3449,34 @@
     <t xml:space="preserve">24.4367942810059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9861373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9585437774658</t>
+    <t xml:space="preserve">23.9861335754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9585418701172</t>
   </si>
   <si>
     <t xml:space="preserve">24.4000053405762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9493465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.795482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2252635955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3197193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4693641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4325733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2762241363525</t>
+    <t xml:space="preserve">23.949348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7954845428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2252597808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3197212219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4693603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4325752258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2762203216553</t>
   </si>
   <si>
     <t xml:space="preserve">26.3323879241943</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">26.1826133728027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1919746398926</t>
+    <t xml:space="preserve">26.1919727325439</t>
   </si>
   <si>
     <t xml:space="preserve">26.5196075439453</t>
@@ -3500,13 +3500,13 @@
     <t xml:space="preserve">26.6693820953369</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8753242492676</t>
+    <t xml:space="preserve">26.8753223419189</t>
   </si>
   <si>
     <t xml:space="preserve">27.3901786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5867576599121</t>
+    <t xml:space="preserve">27.5867557525635</t>
   </si>
   <si>
     <t xml:space="preserve">27.7926998138428</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">27.7084503173828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8769474029541</t>
+    <t xml:space="preserve">27.8769493103027</t>
   </si>
   <si>
     <t xml:space="preserve">27.3340110778809</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">27.1935958862305</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1655139923096</t>
+    <t xml:space="preserve">27.1655158996582</t>
   </si>
   <si>
     <t xml:space="preserve">27.9237518310547</t>
@@ -3542,34 +3542,34 @@
     <t xml:space="preserve">27.8395042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">27.802059173584</t>
+    <t xml:space="preserve">27.8020610809326</t>
   </si>
   <si>
     <t xml:space="preserve">28.4011611938477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5603008270264</t>
+    <t xml:space="preserve">28.5602989196777</t>
   </si>
   <si>
     <t xml:space="preserve">28.3075523376465</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6819915771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2981910705566</t>
+    <t xml:space="preserve">28.6819877624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.298189163208</t>
   </si>
   <si>
     <t xml:space="preserve">28.3169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5041332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.382438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4479637145996</t>
+    <t xml:space="preserve">28.5041313171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3824367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4479656219482</t>
   </si>
   <si>
     <t xml:space="preserve">28.7568759918213</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">27.9799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5696582794189</t>
+    <t xml:space="preserve">28.5696601867676</t>
   </si>
   <si>
     <t xml:space="preserve">28.8317642211914</t>
@@ -3587,34 +3587,34 @@
     <t xml:space="preserve">28.7943229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">28.691349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.419885635376</t>
+    <t xml:space="preserve">28.6913509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4198837280273</t>
   </si>
   <si>
     <t xml:space="preserve">28.4760494232178</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6710052490234</t>
+    <t xml:space="preserve">27.6710071563721</t>
   </si>
   <si>
     <t xml:space="preserve">28.1203327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8301410675049</t>
+    <t xml:space="preserve">27.8301429748535</t>
   </si>
   <si>
     <t xml:space="preserve">27.989278793335</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1671371459961</t>
+    <t xml:space="preserve">28.1671352386475</t>
   </si>
   <si>
     <t xml:space="preserve">28.2701091766357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1390533447266</t>
+    <t xml:space="preserve">28.1390552520752</t>
   </si>
   <si>
     <t xml:space="preserve">28.2888278961182</t>
@@ -3626,10 +3626,10 @@
     <t xml:space="preserve">28.3637180328369</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7849597930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8785724639893</t>
+    <t xml:space="preserve">28.7849617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8785705566406</t>
   </si>
   <si>
     <t xml:space="preserve">29.0002632141113</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">29.3934230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2359085083008</t>
+    <t xml:space="preserve">30.2359104156494</t>
   </si>
   <si>
     <t xml:space="preserve">30.3201580047607</t>
@@ -3647,25 +3647,25 @@
     <t xml:space="preserve">30.179744720459</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8146667480469</t>
+    <t xml:space="preserve">29.8146686553955</t>
   </si>
   <si>
     <t xml:space="preserve">29.992525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9550819396973</t>
+    <t xml:space="preserve">29.9550800323486</t>
   </si>
   <si>
     <t xml:space="preserve">29.8989162445068</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5619220733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5057544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7585029602051</t>
+    <t xml:space="preserve">29.5619201660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5057563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7585010528564</t>
   </si>
   <si>
     <t xml:space="preserve">29.8053073883057</t>
@@ -3674,25 +3674,25 @@
     <t xml:space="preserve">29.5806427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8708343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9082775115967</t>
+    <t xml:space="preserve">29.8708324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.908275604248</t>
   </si>
   <si>
     <t xml:space="preserve">29.8333892822266</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2171878814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4044075012207</t>
+    <t xml:space="preserve">30.2171859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4044055938721</t>
   </si>
   <si>
     <t xml:space="preserve">30.385684967041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8630962371826</t>
+    <t xml:space="preserve">30.8630981445312</t>
   </si>
   <si>
     <t xml:space="preserve">30.8537330627441</t>
@@ -3704,25 +3704,25 @@
     <t xml:space="preserve">30.5448246002197</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4980163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4699325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.713321685791</t>
+    <t xml:space="preserve">30.4980201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.469934463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7133197784424</t>
   </si>
   <si>
     <t xml:space="preserve">30.1142158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1891059875488</t>
+    <t xml:space="preserve">30.1891040802002</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3185367584229</t>
+    <t xml:space="preserve">29.3185348510742</t>
   </si>
   <si>
     <t xml:space="preserve">30.0299701690674</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">30.348237991333</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6742534637451</t>
+    <t xml:space="preserve">29.6742515563965</t>
   </si>
   <si>
     <t xml:space="preserve">28.9534587860107</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">28.8130435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2420272827148</t>
+    <t xml:space="preserve">28.2420234680176</t>
   </si>
   <si>
     <t xml:space="preserve">27.5212306976318</t>
@@ -3749,79 +3749,79 @@
     <t xml:space="preserve">27.4837856292725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0267238616943</t>
+    <t xml:space="preserve">28.0267219543457</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6616439819336</t>
+    <t xml:space="preserve">27.6616458892822</t>
   </si>
   <si>
     <t xml:space="preserve">28.6445465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">29.224925994873</t>
+    <t xml:space="preserve">29.2249240875244</t>
   </si>
   <si>
     <t xml:space="preserve">29.2717323303223</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2623691558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5244789123535</t>
+    <t xml:space="preserve">29.2623710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5244770050049</t>
   </si>
   <si>
     <t xml:space="preserve">29.7304172515869</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1610240936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4792976379395</t>
+    <t xml:space="preserve">30.1610260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4792957305908</t>
   </si>
   <si>
     <t xml:space="preserve">30.5916271209717</t>
   </si>
   <si>
-    <t xml:space="preserve">30.36696434021</t>
+    <t xml:space="preserve">30.3669624328613</t>
   </si>
   <si>
     <t xml:space="preserve">30.6384315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6103496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3030586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9286231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1626491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6681385040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8553581237793</t>
+    <t xml:space="preserve">30.6103477478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7694835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3030605316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9286212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1626453399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.668140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8553524017334</t>
   </si>
   <si>
     <t xml:space="preserve">31.4341144561768</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1813678741455</t>
+    <t xml:space="preserve">31.1813659667969</t>
   </si>
   <si>
     <t xml:space="preserve">31.2749767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8179149627686</t>
+    <t xml:space="preserve">31.8179168701172</t>
   </si>
   <si>
     <t xml:space="preserve">31.9302444458008</t>
@@ -3830,10 +3830,10 @@
     <t xml:space="preserve">32.810173034668</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7633666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6416778564453</t>
+    <t xml:space="preserve">32.763370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.641674041748</t>
   </si>
   <si>
     <t xml:space="preserve">31.9489669799805</t>
@@ -3845,37 +3845,37 @@
     <t xml:space="preserve">32.1081008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6945953369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3124179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7320423126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5822639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8911781311035</t>
+    <t xml:space="preserve">30.6945991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3124217987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7320442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5822620391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8911762237549</t>
   </si>
   <si>
     <t xml:space="preserve">31.752384185791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9473457336426</t>
+    <t xml:space="preserve">30.9473438262939</t>
   </si>
   <si>
     <t xml:space="preserve">30.7039566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3576030731201</t>
+    <t xml:space="preserve">30.3576011657715</t>
   </si>
   <si>
     <t xml:space="preserve">30.0861339569092</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1516609191895</t>
+    <t xml:space="preserve">30.1516628265381</t>
   </si>
   <si>
     <t xml:space="preserve">29.5525608062744</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">30.9754276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9379806518555</t>
+    <t xml:space="preserve">30.9379787445068</t>
   </si>
   <si>
     <t xml:space="preserve">31.0690364837646</t>
@@ -3902,22 +3902,22 @@
     <t xml:space="preserve">30.9941482543945</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9660682678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2936992645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2468967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2656173706055</t>
+    <t xml:space="preserve">30.9660663604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2937030792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2468948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2656192779541</t>
   </si>
   <si>
     <t xml:space="preserve">31.602611541748</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7804718017578</t>
+    <t xml:space="preserve">31.7804679870605</t>
   </si>
   <si>
     <t xml:space="preserve">31.3779487609863</t>
@@ -3926,16 +3926,16 @@
     <t xml:space="preserve">30.5073776245117</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9721794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6335639953613</t>
+    <t xml:space="preserve">28.9721813201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6335620880127</t>
   </si>
   <si>
     <t xml:space="preserve">27.0063781738281</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0454425811768</t>
+    <t xml:space="preserve">28.0454444885254</t>
   </si>
   <si>
     <t xml:space="preserve">26.8378810882568</t>
@@ -3944,34 +3944,34 @@
     <t xml:space="preserve">28.2045803070068</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0548038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.118709564209</t>
+    <t xml:space="preserve">28.0548057556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1187076568604</t>
   </si>
   <si>
     <t xml:space="preserve">25.9298667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0421962738037</t>
+    <t xml:space="preserve">26.042200088501</t>
   </si>
   <si>
     <t xml:space="preserve">26.8191585540771</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5664100646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.248140335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7800922393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5102481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3152904510498</t>
+    <t xml:space="preserve">26.5664119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2481422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7800941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5102462768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3152923583984</t>
   </si>
   <si>
     <t xml:space="preserve">26.9970169067383</t>
@@ -3980,22 +3980,22 @@
     <t xml:space="preserve">26.1264476776123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.229419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1077251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5399532318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5415744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4463405609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9766731262207</t>
+    <t xml:space="preserve">26.2294178009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.107723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5399551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.541576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4463443756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9766693115234</t>
   </si>
   <si>
     <t xml:space="preserve">27.13743019104</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">27.5961170196533</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8863086700439</t>
+    <t xml:space="preserve">27.8863105773926</t>
   </si>
   <si>
     <t xml:space="preserve">28.6258239746094</t>
@@ -4034,22 +4034,22 @@
     <t xml:space="preserve">28.6071014404297</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2326622009277</t>
+    <t xml:space="preserve">28.2326641082764</t>
   </si>
   <si>
     <t xml:space="preserve">28.8692092895508</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0096225738525</t>
+    <t xml:space="preserve">29.0096244812012</t>
   </si>
   <si>
     <t xml:space="preserve">29.2904529571533</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9815406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5151176452637</t>
+    <t xml:space="preserve">28.981538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.515115737915</t>
   </si>
   <si>
     <t xml:space="preserve">29.3840618133545</t>
@@ -4058,22 +4058,22 @@
     <t xml:space="preserve">27.0531826019287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5586757659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8972911834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4666881561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4831771850586</t>
+    <t xml:space="preserve">27.5586738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8972930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4666862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4831790924072</t>
   </si>
   <si>
     <t xml:space="preserve">29.32204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">28.931209564209</t>
+    <t xml:space="preserve">28.9312076568604</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549480438232</t>
@@ -4091,10 +4091,10 @@
     <t xml:space="preserve">29.7605361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6452312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0265350341797</t>
+    <t xml:space="preserve">28.6452331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0265331268311</t>
   </si>
   <si>
     <t xml:space="preserve">29.045597076416</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">26.7482604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0247058868408</t>
+    <t xml:space="preserve">27.0247020721436</t>
   </si>
   <si>
     <t xml:space="preserve">27.1104965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052722930908</t>
+    <t xml:space="preserve">26.6052742004395</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101306915283</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">26.9675102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">27.215353012085</t>
+    <t xml:space="preserve">27.2153549194336</t>
   </si>
   <si>
     <t xml:space="preserve">27.7682399749756</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">27.8635654449463</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7301082611084</t>
+    <t xml:space="preserve">27.730110168457</t>
   </si>
   <si>
     <t xml:space="preserve">28.2829971313477</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">27.9684238433838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1304759979248</t>
+    <t xml:space="preserve">28.1304779052734</t>
   </si>
   <si>
     <t xml:space="preserve">28.4450492858887</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">26.1667785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5280990600586</t>
+    <t xml:space="preserve">25.52809715271</t>
   </si>
   <si>
     <t xml:space="preserve">25.0133419036865</t>
@@ -4226,22 +4226,22 @@
     <t xml:space="preserve">24.765495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3937282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6987686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3374462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9189300537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1658592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2993183135986</t>
+    <t xml:space="preserve">24.393726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.698766708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3374481201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9189319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1658611297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.29931640625</t>
   </si>
   <si>
     <t xml:space="preserve">25.2230548858643</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">24.9084815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">25.346981048584</t>
+    <t xml:space="preserve">25.3469791412354</t>
   </si>
   <si>
     <t xml:space="preserve">26.2144393920898</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">25.9093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4908847808838</t>
+    <t xml:space="preserve">26.4908828735352</t>
   </si>
   <si>
     <t xml:space="preserve">27.0532989501953</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">27.0437698364258</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6815338134766</t>
+    <t xml:space="preserve">26.6815319061279</t>
   </si>
   <si>
     <t xml:space="preserve">27.2630176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7882232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5031585693359</t>
+    <t xml:space="preserve">28.7882213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5031604766846</t>
   </si>
   <si>
     <t xml:space="preserve">29.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5508213043213</t>
+    <t xml:space="preserve">29.5508232116699</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461486816406</t>
@@ -4301,16 +4301,16 @@
     <t xml:space="preserve">29.9797859191895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8939933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0760269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.705171585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7995853424072</t>
+    <t xml:space="preserve">29.8939952850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0760250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7051696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7995834350586</t>
   </si>
   <si>
     <t xml:space="preserve">31.0283622741699</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">30.4468803405762</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9997673034668</t>
+    <t xml:space="preserve">30.9997653961182</t>
   </si>
   <si>
     <t xml:space="preserve">30.551736831665</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">30.0274486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2371616363525</t>
+    <t xml:space="preserve">30.2371635437012</t>
   </si>
   <si>
     <t xml:space="preserve">30.5993995666504</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">29.5317573547363</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1790542602539</t>
+    <t xml:space="preserve">29.1790561676025</t>
   </si>
   <si>
     <t xml:space="preserve">29.1885871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4554958343506</t>
+    <t xml:space="preserve">29.4554977416992</t>
   </si>
   <si>
     <t xml:space="preserve">30.3610877990723</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">31.0664920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5907802581787</t>
+    <t xml:space="preserve">31.590784072876</t>
   </si>
   <si>
     <t xml:space="preserve">30.5326709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3515529632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.389684677124</t>
+    <t xml:space="preserve">30.3515567779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3896827697754</t>
   </si>
   <si>
     <t xml:space="preserve">30.3038921356201</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">29.874927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2362480163574</t>
+    <t xml:space="preserve">29.2362499237061</t>
   </si>
   <si>
     <t xml:space="preserve">28.0160865783691</t>
@@ -4391,34 +4391,34 @@
     <t xml:space="preserve">28.6166362762451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6738319396973</t>
+    <t xml:space="preserve">28.6738300323486</t>
   </si>
   <si>
     <t xml:space="preserve">28.3020629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">26.986572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2353363037109</t>
+    <t xml:space="preserve">26.9865741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2353343963623</t>
   </si>
   <si>
     <t xml:space="preserve">28.492712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0560455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5126914978027</t>
+    <t xml:space="preserve">30.0560474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5126895904541</t>
   </si>
   <si>
     <t xml:space="preserve">29.7128753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6842784881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2648487091064</t>
+    <t xml:space="preserve">29.6842765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2648468017578</t>
   </si>
   <si>
     <t xml:space="preserve">29.7033424377441</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">29.3983020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7700691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7510051727295</t>
+    <t xml:space="preserve">29.7700710296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7510032653809</t>
   </si>
   <si>
     <t xml:space="preserve">30.5422058105469</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">30.9616355895996</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4945411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6661243438721</t>
+    <t xml:space="preserve">30.4945430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6661262512207</t>
   </si>
   <si>
     <t xml:space="preserve">30.8472461700439</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">31.1236896514893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9434833526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.981616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7242374420166</t>
+    <t xml:space="preserve">31.9434814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9816150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7242336273193</t>
   </si>
   <si>
     <t xml:space="preserve">31.5717163085938</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">30.5231399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9521026611328</t>
+    <t xml:space="preserve">30.9521045684814</t>
   </si>
   <si>
     <t xml:space="preserve">30.5136051177979</t>
@@ -4487,13 +4487,13 @@
     <t xml:space="preserve">32.5535697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6289100646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8853759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3715324401855</t>
+    <t xml:space="preserve">31.6289119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8853778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3715343475342</t>
   </si>
   <si>
     <t xml:space="preserve">30.7709846496582</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">31.0950889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0378971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.476390838623</t>
+    <t xml:space="preserve">31.037899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4763946533203</t>
   </si>
   <si>
     <t xml:space="preserve">32.1913299560547</t>
@@ -4514,19 +4514,19 @@
     <t xml:space="preserve">32.0769424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1055374145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1246070861816</t>
+    <t xml:space="preserve">32.105541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1246032714844</t>
   </si>
   <si>
     <t xml:space="preserve">32.143669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8386287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9244251251221</t>
+    <t xml:space="preserve">31.8386325836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9244213104248</t>
   </si>
   <si>
     <t xml:space="preserve">32.1341361999512</t>
@@ -4538,16 +4538,16 @@
     <t xml:space="preserve">32.8300094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1064491271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.840461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5926170349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9167213439941</t>
+    <t xml:space="preserve">33.1064529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8404579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5926132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9167175292969</t>
   </si>
   <si>
     <t xml:space="preserve">33.9357833862305</t>
@@ -4562,16 +4562,16 @@
     <t xml:space="preserve">33.6116752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4686889648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6021461486816</t>
+    <t xml:space="preserve">33.468692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6021423339844</t>
   </si>
   <si>
     <t xml:space="preserve">33.3161697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5544853210449</t>
+    <t xml:space="preserve">33.5544815063477</t>
   </si>
   <si>
     <t xml:space="preserve">33.6784057617188</t>
@@ -4595,25 +4595,25 @@
     <t xml:space="preserve">32.2866554260254</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9729995727539</t>
+    <t xml:space="preserve">32.9729957580566</t>
   </si>
   <si>
     <t xml:space="preserve">33.373363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9539337158203</t>
+    <t xml:space="preserve">32.953929901123</t>
   </si>
   <si>
     <t xml:space="preserve">33.3638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4114952087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5830764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0311126708984</t>
+    <t xml:space="preserve">33.411491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0311088562012</t>
   </si>
   <si>
     <t xml:space="preserve">34.7937126159668</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">35.0892181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5649299621582</t>
+    <t xml:space="preserve">34.5649261474609</t>
   </si>
   <si>
     <t xml:space="preserve">35.2512702941895</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">35.8804168701172</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5372467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5753746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7469635009766</t>
+    <t xml:space="preserve">35.5372428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5753784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7469596862793</t>
   </si>
   <si>
     <t xml:space="preserve">35.3942604064941</t>
@@ -4649,7 +4649,7 @@
     <t xml:space="preserve">35.6516380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1091995239258</t>
+    <t xml:space="preserve">36.109203338623</t>
   </si>
   <si>
     <t xml:space="preserve">35.9852752685547</t>
@@ -4661,13 +4661,13 @@
     <t xml:space="preserve">35.2036094665527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5944404602051</t>
+    <t xml:space="preserve">35.5944442749023</t>
   </si>
   <si>
     <t xml:space="preserve">34.9843635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5563125610352</t>
+    <t xml:space="preserve">35.5563087463379</t>
   </si>
   <si>
     <t xml:space="preserve">35.3370628356934</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">35.8327560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1568603515625</t>
+    <t xml:space="preserve">36.1568641662598</t>
   </si>
   <si>
     <t xml:space="preserve">35.937614440918</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">34.1454963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8413696289062</t>
+    <t xml:space="preserve">34.8413734436035</t>
   </si>
   <si>
     <t xml:space="preserve">34.6697883605957</t>
@@ -4709,16 +4709,16 @@
     <t xml:space="preserve">34.6888542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1759300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1282615661621</t>
+    <t xml:space="preserve">36.1759262084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1282653808594</t>
   </si>
   <si>
     <t xml:space="preserve">36.0615386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7097473144531</t>
+    <t xml:space="preserve">36.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">37.8631858825684</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">34.9748268127441</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6707000732422</t>
+    <t xml:space="preserve">35.6707038879395</t>
   </si>
   <si>
     <t xml:space="preserve">33.7546653747559</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">33.8881187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3552169799805</t>
+    <t xml:space="preserve">34.3552131652832</t>
   </si>
   <si>
     <t xml:space="preserve">35.1082878112793</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">36.3761100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5953559875488</t>
+    <t xml:space="preserve">36.5953598022461</t>
   </si>
   <si>
     <t xml:space="preserve">36.8908653259277</t>
@@ -4775,28 +4775,28 @@
     <t xml:space="preserve">34.946231842041</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3656578063965</t>
+    <t xml:space="preserve">35.3656616210938</t>
   </si>
   <si>
     <t xml:space="preserve">35.4037895202637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5086517333984</t>
+    <t xml:space="preserve">35.5086479187012</t>
   </si>
   <si>
     <t xml:space="preserve">35.3847274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9471473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9090118408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5286254882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4619026184082</t>
+    <t xml:space="preserve">35.9471435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9090156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5286293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4618988037109</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807846069336</t>
@@ -6459,6 +6459,9 @@
   </si>
   <si>
     <t xml:space="preserve">86.120002746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9599990844727</t>
   </si>
 </sst>
 </file>
@@ -71667,7 +71670,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6501157407</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>918826</v>
@@ -71688,6 +71691,32 @@
         <v>2143</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6494907407</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>566158</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>89.9599990844727</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>88.3199996948242</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>89.4000015258789</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>89.9599990844727</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>2149</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -38,109 +38,109 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6851568222046</t>
+    <t xml:space="preserve">15.6851558685303</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8714027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3207597732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2397832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7458305358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9644651412964</t>
+    <t xml:space="preserve">15.8713998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3207607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2397842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.74582862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9644641876221</t>
   </si>
   <si>
     <t xml:space="preserve">15.2964668273926</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4989137649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0616388320923</t>
+    <t xml:space="preserve">15.4989099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0616369247437</t>
   </si>
   <si>
     <t xml:space="preserve">14.5028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5433874130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8510990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870880126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9401712417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4098339080811</t>
+    <t xml:space="preserve">14.5433883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8511009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.187087059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9401741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4098329544067</t>
   </si>
   <si>
     <t xml:space="preserve">14.923975944519</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2802753448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1831045150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6243619918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936414718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8106098175049</t>
+    <t xml:space="preserve">15.2802715301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1830997467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6243629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936395645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8106088638306</t>
   </si>
   <si>
     <t xml:space="preserve">14.7296333312988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8996810913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5190935134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7336225509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.344934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0980157852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3206396102905</t>
+    <t xml:space="preserve">14.8996839523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5190925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7336206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3449335098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.098014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3206415176392</t>
   </si>
   <si>
     <t xml:space="preserve">13.4744958877563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8955745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7822046279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3328485488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2194814682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057245254517</t>
+    <t xml:space="preserve">13.8955755233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7822074890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3328495025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2194786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057283401489</t>
   </si>
   <si>
     <t xml:space="preserve">14.8348999023438</t>
@@ -149,58 +149,58 @@
     <t xml:space="preserve">14.5514860153198</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3409461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8672943115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1021223068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4827146530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3774461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017372131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4665203094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4908151626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5232028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636920928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426115036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742319107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8390111923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879812240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6365699768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9199857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8309125900269</t>
+    <t xml:space="preserve">14.3409471511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8672933578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.102123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2235908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4827165603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3774452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4017391204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4665212631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4908123016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5232038497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636892318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426105499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742300033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8390102386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6365671157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9199876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8309116363525</t>
   </si>
   <si>
     <t xml:space="preserve">15.8794994354248</t>
@@ -209,148 +209,148 @@
     <t xml:space="preserve">15.8228139877319</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8956966400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2762832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1224308013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8471117019653</t>
+    <t xml:space="preserve">15.8956956863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2762851715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.122428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8471078872681</t>
   </si>
   <si>
     <t xml:space="preserve">15.8875961303711</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4422245025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3855438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086757659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2276992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7135581970215</t>
+    <t xml:space="preserve">15.4422254562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3855428695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086738586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2276973724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7135562896729</t>
   </si>
   <si>
     <t xml:space="preserve">16.6568737030029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4301376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6120548248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9180011749268</t>
+    <t xml:space="preserve">16.430139541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6120510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9179992675781</t>
   </si>
   <si>
     <t xml:space="preserve">17.0254936218262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9758815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9924182891846</t>
+    <t xml:space="preserve">16.9758777618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9924163818359</t>
   </si>
   <si>
     <t xml:space="preserve">16.6285915374756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7774295806885</t>
+    <t xml:space="preserve">16.7774314880371</t>
   </si>
   <si>
     <t xml:space="preserve">16.9841499328613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1081809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9345378875732</t>
+    <t xml:space="preserve">17.1081848144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9345359802246</t>
   </si>
   <si>
     <t xml:space="preserve">16.5541725158691</t>
   </si>
   <si>
-    <t xml:space="preserve">16.595516204834</t>
+    <t xml:space="preserve">16.5955142974854</t>
   </si>
   <si>
     <t xml:space="preserve">16.760892868042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7030143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8766574859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4058609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7696895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.009485244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9681415557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8606491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7779579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8854522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6952705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1087093353271</t>
+    <t xml:space="preserve">16.703010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8766593933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4058589935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696857452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0094814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9681377410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8606452941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7779598236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8854541778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6952686309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1087074279785</t>
   </si>
   <si>
     <t xml:space="preserve">17.9598712921143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2658176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.174861907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.282356262207</t>
+    <t xml:space="preserve">18.2658157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1748600006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2823581695557</t>
   </si>
   <si>
     <t xml:space="preserve">18.2988929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1831283569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1335144042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0425605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8027648925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0921745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.918529510498</t>
+    <t xml:space="preserve">18.4725379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1831302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1335163116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0425586700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8027629852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0921726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9185237884521</t>
   </si>
   <si>
     <t xml:space="preserve">18.0012149810791</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">17.3149032592773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9097309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8022384643555</t>
+    <t xml:space="preserve">16.9097290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8022403717041</t>
   </si>
   <si>
     <t xml:space="preserve">17.7366142272949</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5712375640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3479785919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9102592468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6694078445435</t>
+    <t xml:space="preserve">17.5712356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3479804992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9102554321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6694068908691</t>
   </si>
   <si>
     <t xml:space="preserve">14.8342580795288</t>
@@ -389,25 +389,25 @@
     <t xml:space="preserve">15.1402053833008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2559690475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2978401184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7272911071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5867214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.231162071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6115283966064</t>
+    <t xml:space="preserve">15.2559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399616241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2978363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7272920608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5867223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2311611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6115264892578</t>
   </si>
   <si>
     <t xml:space="preserve">16.2813014984131</t>
@@ -416,64 +416,64 @@
     <t xml:space="preserve">16.4632148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6534004211426</t>
+    <t xml:space="preserve">16.6533966064453</t>
   </si>
   <si>
     <t xml:space="preserve">16.6864719390869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6782035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7443561553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6699371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8435821533203</t>
+    <t xml:space="preserve">16.6782054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7443542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6699352264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8435802459717</t>
   </si>
   <si>
     <t xml:space="preserve">16.8187732696533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9510765075684</t>
+    <t xml:space="preserve">16.9510746002197</t>
   </si>
   <si>
     <t xml:space="preserve">17.0999126434326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1164512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2983684539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2404842376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0751075744629</t>
+    <t xml:space="preserve">17.1164531707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2983665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2404823303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0751094818115</t>
   </si>
   <si>
     <t xml:space="preserve">17.3314418792725</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6208477020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1004409790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125812530518</t>
+    <t xml:space="preserve">17.620849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1004428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125831604004</t>
   </si>
   <si>
     <t xml:space="preserve">17.5960426330566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0756378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7944946289062</t>
+    <t xml:space="preserve">18.0756340026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7944965362549</t>
   </si>
   <si>
     <t xml:space="preserve">17.8771839141846</t>
@@ -482,85 +482,85 @@
     <t xml:space="preserve">18.1913986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2492828369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0839042663574</t>
+    <t xml:space="preserve">18.2492809295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0839023590088</t>
   </si>
   <si>
     <t xml:space="preserve">18.2906246185303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1665935516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9929504394531</t>
+    <t xml:space="preserve">18.1665897369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9929466247559</t>
   </si>
   <si>
     <t xml:space="preserve">17.8441066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7200756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.728343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8937206268311</t>
+    <t xml:space="preserve">17.7200736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7283458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8937225341797</t>
   </si>
   <si>
     <t xml:space="preserve">18.0673637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3733100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9438610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4317226409912</t>
+    <t xml:space="preserve">18.37331199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9438591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4317188262939</t>
   </si>
   <si>
     <t xml:space="preserve">19.3573017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1009674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1257762908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1919269561768</t>
+    <t xml:space="preserve">19.1009654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1257781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1919250488281</t>
   </si>
   <si>
     <t xml:space="preserve">19.1753883361816</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2828807830811</t>
+    <t xml:space="preserve">19.2828845977783</t>
   </si>
   <si>
     <t xml:space="preserve">19.1340446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3490333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7624759674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7045879364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4647960662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0596237182617</t>
+    <t xml:space="preserve">19.3490314483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.76247215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4647941589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0596199035645</t>
   </si>
   <si>
     <t xml:space="preserve">18.646183013916</t>
@@ -569,28 +569,28 @@
     <t xml:space="preserve">19.1175060272217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1588535308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0100135803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7536754608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.902515411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0844287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9934749603271</t>
+    <t xml:space="preserve">19.1588497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.010009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7536773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9025173187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0844326019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9934730529785</t>
   </si>
   <si>
     <t xml:space="preserve">18.7950210571289</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7867527008057</t>
+    <t xml:space="preserve">18.7867546081543</t>
   </si>
   <si>
     <t xml:space="preserve">18.7454090118408</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">18.3319664001465</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6291217803955</t>
+    <t xml:space="preserve">17.6291179656982</t>
   </si>
   <si>
     <t xml:space="preserve">18.869441986084</t>
@@ -611,148 +611,148 @@
     <t xml:space="preserve">18.3485069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6627197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7288703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6875267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8942489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.422924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4808082580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2327442169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3236999511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0590972900391</t>
+    <t xml:space="preserve">18.6627216339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.728874206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6875286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8942451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4229221343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.480806350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2327423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3237018585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0590953826904</t>
   </si>
   <si>
     <t xml:space="preserve">18.6709880828857</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9355907440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4399890899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8782348632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6797866821289</t>
+    <t xml:space="preserve">18.9355888366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4399871826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8782367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6797847747803</t>
   </si>
   <si>
     <t xml:space="preserve">20.1676445007324</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8451633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7790145874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1428356170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9113140106201</t>
+    <t xml:space="preserve">19.8451595306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7790126800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1428394317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9113121032715</t>
   </si>
   <si>
     <t xml:space="preserve">20.1759128570557</t>
   </si>
   <si>
-    <t xml:space="preserve">20.002269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9278469085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0105361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8038196563721</t>
+    <t xml:space="preserve">20.0022659301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9278450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0105381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8038158416748</t>
   </si>
   <si>
     <t xml:space="preserve">20.1014957427979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1262989044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1097602844238</t>
+    <t xml:space="preserve">20.1263008117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1097640991211</t>
   </si>
   <si>
     <t xml:space="preserve">20.1924495697021</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6389694213867</t>
+    <t xml:space="preserve">20.6389675140381</t>
   </si>
   <si>
     <t xml:space="preserve">20.1345710754395</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2751407623291</t>
+    <t xml:space="preserve">20.2751388549805</t>
   </si>
   <si>
     <t xml:space="preserve">20.2172584533691</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3164844512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2420616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3330230712891</t>
+    <t xml:space="preserve">20.3164825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2420635223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3330211639404</t>
   </si>
   <si>
     <t xml:space="preserve">20.2255268096924</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6555061340332</t>
+    <t xml:space="preserve">20.6555023193359</t>
   </si>
   <si>
     <t xml:space="preserve">20.5066680908203</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3578281402588</t>
+    <t xml:space="preserve">20.3578300476074</t>
   </si>
   <si>
     <t xml:space="preserve">20.4818592071533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0849571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3991737365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645503997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5397434234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6885852813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8947772979736</t>
+    <t xml:space="preserve">20.0849552154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3991718292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.564546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5397415161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6885795593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.894775390625</t>
   </si>
   <si>
     <t xml:space="preserve">20.4074420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7133865356445</t>
+    <t xml:space="preserve">20.7133884429932</t>
   </si>
   <si>
     <t xml:space="preserve">20.9697208404541</t>
@@ -764,91 +764,91 @@
     <t xml:space="preserve">20.4239807128906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3082141876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7547359466553</t>
+    <t xml:space="preserve">20.3082180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7547302246094</t>
   </si>
   <si>
     <t xml:space="preserve">19.9609241485596</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8865032196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8286247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8534317016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.118034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5722885131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2994194030762</t>
+    <t xml:space="preserve">19.8865051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8286266326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8534297943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1180324554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5722904205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2994174957275</t>
   </si>
   <si>
     <t xml:space="preserve">19.5144100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5474853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.423454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6136360168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.564022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3821125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7376670837402</t>
+    <t xml:space="preserve">19.5474815368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4234523773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6136341094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5640201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3821067810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7376689910889</t>
   </si>
   <si>
     <t xml:space="preserve">20.3660984039307</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9361209869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2007217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4901313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7381954193115</t>
+    <t xml:space="preserve">19.9361171722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.200719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4901275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7381935119629</t>
   </si>
   <si>
     <t xml:space="preserve">21.2922058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1516342163086</t>
+    <t xml:space="preserve">21.15163230896</t>
   </si>
   <si>
     <t xml:space="preserve">21.0854816436768</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9366455078125</t>
+    <t xml:space="preserve">20.9366436004639</t>
   </si>
   <si>
     <t xml:space="preserve">20.7795372009277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4570560455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7051200866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1268291473389</t>
+    <t xml:space="preserve">20.4570541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7051162719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1268272399902</t>
   </si>
   <si>
     <t xml:space="preserve">22.0435581207275</t>
@@ -857,31 +857,31 @@
     <t xml:space="preserve">22.1192493438721</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8669414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9846858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2958698272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4724884033203</t>
+    <t xml:space="preserve">21.8669395446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9846839904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2958679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4724864959717</t>
   </si>
   <si>
     <t xml:space="preserve">22.2201747894287</t>
   </si>
   <si>
-    <t xml:space="preserve">22.262228012085</t>
+    <t xml:space="preserve">22.2622261047363</t>
   </si>
   <si>
     <t xml:space="preserve">22.5397682189941</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5734081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986423492432</t>
+    <t xml:space="preserve">22.5734100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986442565918</t>
   </si>
   <si>
     <t xml:space="preserve">21.8080673217773</t>
@@ -902,43 +902,43 @@
     <t xml:space="preserve">20.6390266418457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4203605651855</t>
+    <t xml:space="preserve">20.4203586578369</t>
   </si>
   <si>
     <t xml:space="preserve">20.5549240112305</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4540004730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9670314788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.19411277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8576984405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1688823699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8324661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9586219787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156452178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5978088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2613964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.101598739624</t>
+    <t xml:space="preserve">20.4539985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9670276641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1941089630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8576965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1688804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8324642181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9586200714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8156433105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.597806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2613925933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1015968322754</t>
   </si>
   <si>
     <t xml:space="preserve">21.6819133758545</t>
@@ -947,91 +947,91 @@
     <t xml:space="preserve">21.6146278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.816478729248</t>
+    <t xml:space="preserve">21.8164768218994</t>
   </si>
   <si>
     <t xml:space="preserve">21.656681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8248901367188</t>
+    <t xml:space="preserve">21.8248882293701</t>
   </si>
   <si>
     <t xml:space="preserve">21.5473461151123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5725765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0351505279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8585319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9258117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7828388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3210983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4884757995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3875503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1949481964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8501205444336</t>
+    <t xml:space="preserve">21.5725784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0351486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.858528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9258098602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7828369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3211002349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4884719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3875484466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1949462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.850118637085</t>
   </si>
   <si>
     <t xml:space="preserve">22.2454051971436</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0015068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3883819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538185119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5481815338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5313568115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7668476104736</t>
+    <t xml:space="preserve">22.0015048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3883800506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538166046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5481796264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5313587188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7668495178223</t>
   </si>
   <si>
     <t xml:space="preserve">23.0696220397949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5818195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8425445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5649967193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1444797515869</t>
+    <t xml:space="preserve">22.5818214416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8425426483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5650005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1444816589355</t>
   </si>
   <si>
     <t xml:space="preserve">22.2117652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1865329742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5229473114014</t>
+    <t xml:space="preserve">22.1865348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.52294921875</t>
   </si>
   <si>
     <t xml:space="preserve">22.7920799255371</t>
@@ -1043,22 +1043,22 @@
     <t xml:space="preserve">22.7500286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9266471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9350547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8593635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7079753875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5902328491211</t>
+    <t xml:space="preserve">22.9266452789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9350566864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8593616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7079772949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416191101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5902309417725</t>
   </si>
   <si>
     <t xml:space="preserve">22.2369976043701</t>
@@ -1073,19 +1073,19 @@
     <t xml:space="preserve">22.3547401428223</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3042774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9594535827637</t>
+    <t xml:space="preserve">22.3042793273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.959451675415</t>
   </si>
   <si>
     <t xml:space="preserve">22.2285861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1108417510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9174022674561</t>
+    <t xml:space="preserve">22.1108379364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9174003601074</t>
   </si>
   <si>
     <t xml:space="preserve">22.3463306427002</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">22.4304351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8257179260254</t>
+    <t xml:space="preserve">22.8257217407227</t>
   </si>
   <si>
     <t xml:space="preserve">23.4649105072021</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">23.6835784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8097362518311</t>
+    <t xml:space="preserve">23.8097324371338</t>
   </si>
   <si>
     <t xml:space="preserve">23.9106578826904</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">23.9190673828125</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7508583068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8770179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9863471984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8938369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.952709197998</t>
+    <t xml:space="preserve">23.750862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8770160675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9863529205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8938388824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9527072906494</t>
   </si>
   <si>
     <t xml:space="preserve">23.9779396057129</t>
@@ -1139,34 +1139,34 @@
     <t xml:space="preserve">23.85178565979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0368156433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4741554260254</t>
+    <t xml:space="preserve">24.0368137359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4741516113281</t>
   </si>
   <si>
     <t xml:space="preserve">24.3311786651611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3143558502197</t>
+    <t xml:space="preserve">24.3143577575684</t>
   </si>
   <si>
     <t xml:space="preserve">24.0536346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9358882904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8013229370117</t>
+    <t xml:space="preserve">23.9358901977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8013248443604</t>
   </si>
   <si>
     <t xml:space="preserve">23.9611206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0199928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1040992736816</t>
+    <t xml:space="preserve">24.0199966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1040954589844</t>
   </si>
   <si>
     <t xml:space="preserve">24.5582580566406</t>
@@ -1175,61 +1175,61 @@
     <t xml:space="preserve">24.5077934265137</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3564052581787</t>
+    <t xml:space="preserve">24.356409072876</t>
   </si>
   <si>
     <t xml:space="preserve">24.3984603881836</t>
   </si>
   <si>
-    <t xml:space="preserve">24.919900894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7937450408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6928195953369</t>
+    <t xml:space="preserve">24.9199028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7937488555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6928215026855</t>
   </si>
   <si>
     <t xml:space="preserve">24.8946704864502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2310848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1217498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1890316009521</t>
+    <t xml:space="preserve">25.2310829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1217517852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1890335083008</t>
   </si>
   <si>
     <t xml:space="preserve">24.8526210784912</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4489212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5574245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3892135620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5994739532471</t>
+    <t xml:space="preserve">24.4489192962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5574226379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.389217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5994777679443</t>
   </si>
   <si>
     <t xml:space="preserve">23.2125988006592</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9274806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.691987991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.540599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5742416381836</t>
+    <t xml:space="preserve">23.9274826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6919918060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5406036376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5742454528809</t>
   </si>
   <si>
     <t xml:space="preserve">23.3808059692383</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">23.4144458770752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.532190322876</t>
+    <t xml:space="preserve">23.5321922302246</t>
   </si>
   <si>
     <t xml:space="preserve">23.9695320129395</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">22.9939308166504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6911544799805</t>
+    <t xml:space="preserve">22.6911582946777</t>
   </si>
   <si>
     <t xml:space="preserve">22.9014148712158</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">23.0443916320801</t>
   </si>
   <si>
-    <t xml:space="preserve">23.02756690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.035982131958</t>
+    <t xml:space="preserve">23.0275688171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0359802246094</t>
   </si>
   <si>
     <t xml:space="preserve">22.8930053710938</t>
@@ -1271,64 +1271,64 @@
     <t xml:space="preserve">22.6827449798584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1789588928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546501159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2210102081299</t>
+    <t xml:space="preserve">23.1789569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546482086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2210083007812</t>
   </si>
   <si>
     <t xml:space="preserve">23.1621341705322</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2294178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.078031539917</t>
+    <t xml:space="preserve">23.229419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0780334472656</t>
   </si>
   <si>
     <t xml:space="preserve">22.8677711486816</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0107517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1881980895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0031719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1713790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2218437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3900489807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4909725189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8273849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5246124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3395862579346</t>
+    <t xml:space="preserve">23.0107498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1881999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.003173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1713809967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2218418121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3900508880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4909744262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8273906707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5246162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3395881652832</t>
   </si>
   <si>
     <t xml:space="preserve">24.3059463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8686065673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8349647521973</t>
+    <t xml:space="preserve">23.8686046600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8349666595459</t>
   </si>
   <si>
     <t xml:space="preserve">23.2882919311523</t>
@@ -1343,46 +1343,46 @@
     <t xml:space="preserve">23.4564971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7163887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4556655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0687923431396</t>
+    <t xml:space="preserve">22.7163867950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4556636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0687885284424</t>
   </si>
   <si>
     <t xml:space="preserve">22.1781234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0940189361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9089908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7996559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6314506530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7912483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3631496429443</t>
+    <t xml:space="preserve">22.0940208435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9089889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7996578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6314487457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7912464141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.363151550293</t>
   </si>
   <si>
     <t xml:space="preserve">22.3967933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2874622344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0856113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6230449676514</t>
+    <t xml:space="preserve">22.2874603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0856075286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6230411529541</t>
   </si>
   <si>
     <t xml:space="preserve">21.3454971313477</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">21.4043712615967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4464225769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2950344085693</t>
+    <t xml:space="preserve">21.446418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2950325012207</t>
   </si>
   <si>
     <t xml:space="preserve">21.337085723877</t>
@@ -1403,40 +1403,40 @@
     <t xml:space="preserve">21.7407855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7904148101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3194332122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7988224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4035377502441</t>
+    <t xml:space="preserve">20.790412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3194313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7988243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4035396575928</t>
   </si>
   <si>
     <t xml:space="preserve">20.5717430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7735919952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9249801635742</t>
+    <t xml:space="preserve">20.7735939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9249782562256</t>
   </si>
   <si>
     <t xml:space="preserve">20.8072338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0288734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8919296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6351680755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6180515289307</t>
+    <t xml:space="preserve">21.0288715362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8919315338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6351661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.618049621582</t>
   </si>
   <si>
     <t xml:space="preserve">20.746431350708</t>
@@ -1445,25 +1445,25 @@
     <t xml:space="preserve">20.8662528991699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3883380889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9603996276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3626651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5081596374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8847465515137</t>
+    <t xml:space="preserve">21.3883419036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9604015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.362663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5081634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8847484588623</t>
   </si>
   <si>
     <t xml:space="preserve">21.7563648223877</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2270984649658</t>
+    <t xml:space="preserve">22.2270965576172</t>
   </si>
   <si>
     <t xml:space="preserve">22.9203567504883</t>
@@ -1472,49 +1472,49 @@
     <t xml:space="preserve">22.4153919219971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4239521026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8077182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0987167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1072731018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7392501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2428436279297</t>
+    <t xml:space="preserve">22.4239501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8077163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0987148284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1072769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7392482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2428398132324</t>
   </si>
   <si>
     <t xml:space="preserve">21.4568099975586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.405460357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.943286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1302051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1216449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3698482513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.268518447876</t>
+    <t xml:space="preserve">21.4054584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9432849884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.130199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1216411590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3698444366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2685165405273</t>
   </si>
   <si>
     <t xml:space="preserve">21.3968982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">21.336986541748</t>
+    <t xml:space="preserve">21.3369846343994</t>
   </si>
   <si>
     <t xml:space="preserve">21.3797798156738</t>
@@ -1532,25 +1532,25 @@
     <t xml:space="preserve">20.8063449859619</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7977867126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9960098266602</t>
+    <t xml:space="preserve">20.7977828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9960136413574</t>
   </si>
   <si>
     <t xml:space="preserve">21.5423984527588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1914882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9090480804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.455436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6509113311768</t>
+    <t xml:space="preserve">21.1914863586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.909049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4554347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6509094238281</t>
   </si>
   <si>
     <t xml:space="preserve">19.8563213348389</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">17.8706912994385</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9306030273438</t>
+    <t xml:space="preserve">17.9306011199951</t>
   </si>
   <si>
     <t xml:space="preserve">18.2729511260986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4427490234375</t>
+    <t xml:space="preserve">17.4427509307861</t>
   </si>
   <si>
     <t xml:space="preserve">18.2558345794678</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">17.9355735778809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6260833740234</t>
+    <t xml:space="preserve">18.6260852813721</t>
   </si>
   <si>
     <t xml:space="preserve">18.245418548584</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">18.1657447814941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1568908691406</t>
+    <t xml:space="preserve">18.1568927764893</t>
   </si>
   <si>
     <t xml:space="preserve">18.811990737915</t>
@@ -1595,31 +1595,31 @@
     <t xml:space="preserve">18.9978981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9359302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2988872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1838035583496</t>
+    <t xml:space="preserve">18.9359264373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2988891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1838054656982</t>
   </si>
   <si>
     <t xml:space="preserve">19.2103633880615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4139766693115</t>
+    <t xml:space="preserve">19.4139747619629</t>
   </si>
   <si>
     <t xml:space="preserve">19.5202083587646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5113563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5644702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7238216400146</t>
+    <t xml:space="preserve">19.5113544464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5644721984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7238178253174</t>
   </si>
   <si>
     <t xml:space="preserve">19.635290145874</t>
@@ -1628,55 +1628,55 @@
     <t xml:space="preserve">19.4316806793213</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1395435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0687198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2369194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6972599029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7503776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8034934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4405288696289</t>
+    <t xml:space="preserve">19.1395416259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0687217712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2369213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6972579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7503757476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8034915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4405326843262</t>
   </si>
   <si>
     <t xml:space="preserve">19.2900371551514</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0333099365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5109958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3516483306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8208427429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7765808105469</t>
+    <t xml:space="preserve">19.0333080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5109996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3516502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8208446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7765789031982</t>
   </si>
   <si>
     <t xml:space="preserve">18.7942848205566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9182224273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1129817962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4847946166992</t>
+    <t xml:space="preserve">18.9182243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1129837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4847984313965</t>
   </si>
   <si>
     <t xml:space="preserve">19.6707019805908</t>
@@ -1688,49 +1688,49 @@
     <t xml:space="preserve">19.201509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2192134857178</t>
+    <t xml:space="preserve">19.2192115783691</t>
   </si>
   <si>
     <t xml:space="preserve">19.0952739715576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.696907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1218376159668</t>
+    <t xml:space="preserve">18.6969089508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1218357086182</t>
   </si>
   <si>
     <t xml:space="preserve">19.2546253204346</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5906734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4136199951172</t>
+    <t xml:space="preserve">18.5906715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4136180877686</t>
   </si>
   <si>
     <t xml:space="preserve">18.67919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6880512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1483955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9890441894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0510120391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5995273590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3427963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4313259124756</t>
+    <t xml:space="preserve">18.6880531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1483936309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9890460968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0510158538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5995254516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3427982330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.431324005127</t>
   </si>
   <si>
     <t xml:space="preserve">18.3693561553955</t>
@@ -1739,76 +1739,76 @@
     <t xml:space="preserve">17.7585163116455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6965503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4840869903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9001617431641</t>
+    <t xml:space="preserve">17.6965522766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4840850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9001598358154</t>
   </si>
   <si>
     <t xml:space="preserve">17.4176902770996</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325965881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6342258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4527416229248</t>
+    <t xml:space="preserve">17.0325984954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6342277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4527454376221</t>
   </si>
   <si>
     <t xml:space="preserve">15.9392890930176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5719032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346828460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4656686782837</t>
+    <t xml:space="preserve">15.5719041824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346857070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4656677246094</t>
   </si>
   <si>
     <t xml:space="preserve">16.7316055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2712631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.766658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2133665084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1735315322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6777791976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2262897491455</t>
+    <t xml:space="preserve">16.2712669372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7666606903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2133693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.173529624939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6777801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2262916564941</t>
   </si>
   <si>
     <t xml:space="preserve">14.7840118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6290893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9743461608887</t>
+    <t xml:space="preserve">14.6290884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743452072144</t>
   </si>
   <si>
     <t xml:space="preserve">15.0717239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.191234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7179698944092</t>
+    <t xml:space="preserve">15.1912355422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7179718017578</t>
   </si>
   <si>
     <t xml:space="preserve">16.2933979034424</t>
@@ -1817,22 +1817,22 @@
     <t xml:space="preserve">15.9171571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8596153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0986366271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1030654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7755146026611</t>
+    <t xml:space="preserve">15.8596134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0986385345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1030616760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7755117416382</t>
   </si>
   <si>
     <t xml:space="preserve">15.4169807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7887935638428</t>
+    <t xml:space="preserve">15.7887945175171</t>
   </si>
   <si>
     <t xml:space="preserve">15.4833745956421</t>
@@ -1841,28 +1841,28 @@
     <t xml:space="preserve">14.6910572052002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2882595062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.204158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9739894866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8766098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0802221298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9916954040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7880821228027</t>
+    <t xml:space="preserve">14.2882604598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2041597366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9739904403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8766088485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0802211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9916944503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7880830764771</t>
   </si>
   <si>
     <t xml:space="preserve">13.6243085861206</t>
@@ -1874,133 +1874,133 @@
     <t xml:space="preserve">14.3148183822632</t>
   </si>
   <si>
-    <t xml:space="preserve">15.045166015625</t>
+    <t xml:space="preserve">15.0451669692993</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254770278931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1112070083618</t>
+    <t xml:space="preserve">14.1112051010132</t>
   </si>
   <si>
     <t xml:space="preserve">13.4959440231323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3675785064697</t>
+    <t xml:space="preserve">13.367579460144</t>
   </si>
   <si>
     <t xml:space="preserve">13.2524948120117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0669431686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7707328796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.841552734375</t>
+    <t xml:space="preserve">14.0669422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7707319259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8415536880493</t>
   </si>
   <si>
     <t xml:space="preserve">14.6954851150513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6512203216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8946685791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0628690719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8813905715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8282747268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9345083236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4479665756226</t>
+    <t xml:space="preserve">14.651219367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8946695327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0628709793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8813896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.828275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9345092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4479646682739</t>
   </si>
   <si>
     <t xml:space="preserve">14.7131900787354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1558256149292</t>
+    <t xml:space="preserve">15.1558246612549</t>
   </si>
   <si>
     <t xml:space="preserve">15.2886152267456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6958389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3155326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4129066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1163444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0145359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8020725250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1340522766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2358551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.479305267334</t>
+    <t xml:space="preserve">15.6958408355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3155269622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4129104614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1163425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0145378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8020753860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1340484619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2358531951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4793033599854</t>
   </si>
   <si>
     <t xml:space="preserve">16.4748783111572</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3376598358154</t>
+    <t xml:space="preserve">16.3376617431641</t>
   </si>
   <si>
     <t xml:space="preserve">16.2181491851807</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2889709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5811100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5412750244141</t>
+    <t xml:space="preserve">16.2889728546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5811080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5412731170654</t>
   </si>
   <si>
     <t xml:space="preserve">16.7758693695068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4881572723389</t>
+    <t xml:space="preserve">16.4881534576416</t>
   </si>
   <si>
     <t xml:space="preserve">16.7935752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6297988891602</t>
+    <t xml:space="preserve">16.6298007965088</t>
   </si>
   <si>
     <t xml:space="preserve">16.9263668060303</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9481401443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9304370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9614229202271</t>
+    <t xml:space="preserve">15.9481382369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.930438041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9614219665527</t>
   </si>
   <si>
     <t xml:space="preserve">16.5279941558838</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">16.5368480682373</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6784896850586</t>
+    <t xml:space="preserve">16.67848777771</t>
   </si>
   <si>
     <t xml:space="preserve">16.5855369567871</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">16.7138996124268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1292686462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5763282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8197793960571</t>
+    <t xml:space="preserve">15.1292676925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5763301849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8197784423828</t>
   </si>
   <si>
     <t xml:space="preserve">16.0101108551025</t>
@@ -2033,22 +2033,22 @@
     <t xml:space="preserve">15.8906011581421</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8463363647461</t>
+    <t xml:space="preserve">15.8463344573975</t>
   </si>
   <si>
     <t xml:space="preserve">15.3992748260498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2930421829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9610652923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.885817527771</t>
+    <t xml:space="preserve">15.293041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9610662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8858184814453</t>
   </si>
   <si>
     <t xml:space="preserve">14.3767881393433</t>
@@ -2060,91 +2060,91 @@
     <t xml:space="preserve">14.6069564819336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5626945495605</t>
+    <t xml:space="preserve">14.5626955032349</t>
   </si>
   <si>
     <t xml:space="preserve">14.7795839309692</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4125556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2222194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0540189743042</t>
+    <t xml:space="preserve">15.4125528335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2222204208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0540199279785</t>
   </si>
   <si>
     <t xml:space="preserve">14.9212284088135</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6423683166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300804138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8592596054077</t>
+    <t xml:space="preserve">14.6423692703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.930082321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8592586517334</t>
   </si>
   <si>
     <t xml:space="preserve">15.1868104934692</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0230360031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9477863311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476089477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2436418533325</t>
+    <t xml:space="preserve">15.0230350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9477882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476079940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2436408996582</t>
   </si>
   <si>
     <t xml:space="preserve">13.5534868240356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.655291557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6420116424561</t>
+    <t xml:space="preserve">13.6552925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6420125961304</t>
   </si>
   <si>
     <t xml:space="preserve">14.1997346878052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4564619064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4431829452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.682204246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8459796905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.217794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0495920181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2089414596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0318870544434</t>
+    <t xml:space="preserve">14.4564628601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4431819915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6822061538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8459825515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2177963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0495929718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2089424133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.031886100769</t>
   </si>
   <si>
     <t xml:space="preserve">15.1823816299438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.496298789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1820278167725</t>
+    <t xml:space="preserve">14.4962978363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1820287704468</t>
   </si>
   <si>
     <t xml:space="preserve">15.2000894546509</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">15.1381196975708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3151721954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3063230514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6467943191528</t>
+    <t xml:space="preserve">15.3151731491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3063220977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6467952728271</t>
   </si>
   <si>
     <t xml:space="preserve">14.3723621368408</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">13.8589029312134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7748022079468</t>
+    <t xml:space="preserve">13.7748031616211</t>
   </si>
   <si>
     <t xml:space="preserve">13.5977487564087</t>
@@ -2177,49 +2177,49 @@
     <t xml:space="preserve">13.7792291641235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5888957977295</t>
+    <t xml:space="preserve">13.5888967514038</t>
   </si>
   <si>
     <t xml:space="preserve">13.6774225234985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2170839309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5313549041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.350227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3192443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2705564498901</t>
+    <t xml:space="preserve">13.2170829772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5313539505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3502283096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3192434310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2705554962158</t>
   </si>
   <si>
     <t xml:space="preserve">14.6999111175537</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7353239059448</t>
+    <t xml:space="preserve">14.7353219985962</t>
   </si>
   <si>
     <t xml:space="preserve">14.9256553649902</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6600732803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7486009597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9079504013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2266454696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.580756187439</t>
+    <t xml:space="preserve">14.6600742340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7486000061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9079484939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2266464233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5807571411133</t>
   </si>
   <si>
     <t xml:space="preserve">15.9127311706543</t>
@@ -2228,67 +2228,67 @@
     <t xml:space="preserve">16.0942115783691</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8584661483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9808731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675317764282</t>
+    <t xml:space="preserve">15.8584651947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9808702468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675327301025</t>
   </si>
   <si>
     <t xml:space="preserve">16.2302188873291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.456901550293</t>
+    <t xml:space="preserve">16.4568958282471</t>
   </si>
   <si>
     <t xml:space="preserve">16.5838394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">16.592903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.66090965271</t>
+    <t xml:space="preserve">16.5929050445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6609115600586</t>
   </si>
   <si>
     <t xml:space="preserve">16.7243766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7425155639648</t>
+    <t xml:space="preserve">16.7425136566162</t>
   </si>
   <si>
     <t xml:space="preserve">16.4115619659424</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6427726745605</t>
+    <t xml:space="preserve">16.6427745819092</t>
   </si>
   <si>
     <t xml:space="preserve">16.9827919006348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9419898986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0326614379883</t>
+    <t xml:space="preserve">16.9419918060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0326633453369</t>
   </si>
   <si>
     <t xml:space="preserve">17.309211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4542865753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.964656829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9555912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0462627410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0436515808105</t>
+    <t xml:space="preserve">17.4542846679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9646587371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9555931091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0462646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0436496734619</t>
   </si>
   <si>
     <t xml:space="preserve">18.0935192108154</t>
@@ -2297,16 +2297,16 @@
     <t xml:space="preserve">18.1116542816162</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7263011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1414680480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7833137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9283885955811</t>
+    <t xml:space="preserve">17.7262992858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.141471862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.783317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9283924102783</t>
   </si>
   <si>
     <t xml:space="preserve">17.5268230438232</t>
@@ -2315,16 +2315,16 @@
     <t xml:space="preserve">17.1505374908447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.996395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8875846862793</t>
+    <t xml:space="preserve">16.9963932037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8875865936279</t>
   </si>
   <si>
     <t xml:space="preserve">16.9601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3726787567139</t>
+    <t xml:space="preserve">17.3726806640625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7787818908691</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">16.7923831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7017116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0307426452637</t>
+    <t xml:space="preserve">16.7017097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.030740737915</t>
   </si>
   <si>
     <t xml:space="preserve">16.0715446472168</t>
@@ -2348,31 +2348,31 @@
     <t xml:space="preserve">16.8150501251221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5948276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3862838745117</t>
+    <t xml:space="preserve">17.5948257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3862819671631</t>
   </si>
   <si>
     <t xml:space="preserve">17.0054607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9782600402832</t>
+    <t xml:space="preserve">16.9782581329346</t>
   </si>
   <si>
     <t xml:space="preserve">17.2774753570557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2276077270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0209827423096</t>
+    <t xml:space="preserve">17.2276058197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0209846496582</t>
   </si>
   <si>
     <t xml:space="preserve">18.0481853485107</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0073852539062</t>
+    <t xml:space="preserve">18.0073833465576</t>
   </si>
   <si>
     <t xml:space="preserve">18.206859588623</t>
@@ -2381,19 +2381,19 @@
     <t xml:space="preserve">18.7508907318115</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2975311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3519325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2884654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4244689941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9775695800781</t>
+    <t xml:space="preserve">18.2975330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3519344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2884635925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4244728088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9775714874268</t>
   </si>
   <si>
     <t xml:space="preserve">19.050106048584</t>
@@ -2402,13 +2402,13 @@
     <t xml:space="preserve">19.0410385131836</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3156681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7716369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.06178855896</t>
+    <t xml:space="preserve">18.3156661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7716388702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0617847442627</t>
   </si>
   <si>
     <t xml:space="preserve">17.8804416656494</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">17.7353668212891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7217674255371</t>
+    <t xml:space="preserve">17.7217655181885</t>
   </si>
   <si>
     <t xml:space="preserve">17.8623085021973</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">17.7126979827881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0598640441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0507984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9737281799316</t>
+    <t xml:space="preserve">17.0598678588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0508003234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.973726272583</t>
   </si>
   <si>
     <t xml:space="preserve">17.0961322784424</t>
@@ -2450,31 +2450,31 @@
     <t xml:space="preserve">17.2366752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7671012878418</t>
+    <t xml:space="preserve">17.7671031951904</t>
   </si>
   <si>
     <t xml:space="preserve">18.0753841400146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4698104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5060749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7236881256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.71462059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2703304290771</t>
+    <t xml:space="preserve">18.4698085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5060768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7236862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7146224975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2703285217285</t>
   </si>
   <si>
     <t xml:space="preserve">18.1887245178223</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5786151885986</t>
+    <t xml:space="preserve">18.5786113739014</t>
   </si>
   <si>
     <t xml:space="preserve">18.9594345092773</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">18.7418212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7780895233154</t>
+    <t xml:space="preserve">18.7780933380127</t>
   </si>
   <si>
     <t xml:space="preserve">19.2223815917969</t>
@@ -2495,16 +2495,16 @@
     <t xml:space="preserve">19.7120094299316</t>
   </si>
   <si>
-    <t xml:space="preserve">19.521598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.81174659729</t>
+    <t xml:space="preserve">19.5216007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8117485046387</t>
   </si>
   <si>
     <t xml:space="preserve">19.4490623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3130550384521</t>
+    <t xml:space="preserve">19.3130531311035</t>
   </si>
   <si>
     <t xml:space="preserve">18.7962245941162</t>
@@ -2516,46 +2516,46 @@
     <t xml:space="preserve">17.1732025146484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.422550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.803373336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9121761322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0391159057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9892463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0663166046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8596973419189</t>
+    <t xml:space="preserve">17.4225521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8033714294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9121780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0391178131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9892482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0663185119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8596935272217</t>
   </si>
   <si>
     <t xml:space="preserve">18.9050331115723</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7599563598633</t>
+    <t xml:space="preserve">18.7599582672119</t>
   </si>
   <si>
     <t xml:space="preserve">18.3791351318359</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4399929046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9685001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0863761901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1951808929443</t>
+    <t xml:space="preserve">19.4399948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9685020446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0863742828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1951789855957</t>
   </si>
   <si>
     <t xml:space="preserve">19.5760021209717</t>
@@ -2564,25 +2564,25 @@
     <t xml:space="preserve">19.6394710540771</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4218597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7392101287842</t>
+    <t xml:space="preserve">19.4218578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7392120361328</t>
   </si>
   <si>
     <t xml:space="preserve">19.94775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0021533966064</t>
+    <t xml:space="preserve">20.0021591186523</t>
   </si>
   <si>
     <t xml:space="preserve">19.8661518096924</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4853286743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6757431030273</t>
+    <t xml:space="preserve">19.485330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6757392883301</t>
   </si>
   <si>
     <t xml:space="preserve">19.2133140563965</t>
@@ -2591,37 +2591,37 @@
     <t xml:space="preserve">19.1679782867432</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3221206665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0319709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2949199676514</t>
+    <t xml:space="preserve">19.3221187591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0319728851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2949180603027</t>
   </si>
   <si>
     <t xml:space="preserve">19.2677192687988</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5941352844238</t>
+    <t xml:space="preserve">19.5941371917725</t>
   </si>
   <si>
     <t xml:space="preserve">19.857084274292</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4127922058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9957008361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6602172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5332775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9322338104248</t>
+    <t xml:space="preserve">19.4127902984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9957065582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6602191925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5332794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9322299957275</t>
   </si>
   <si>
     <t xml:space="preserve">19.4762630462646</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">20.0112247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9658889770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3376426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9088745117188</t>
+    <t xml:space="preserve">19.9658908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3376445770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9088726043701</t>
   </si>
   <si>
     <t xml:space="preserve">21.325963973999</t>
@@ -2657,31 +2657,31 @@
     <t xml:space="preserve">22.4049530029297</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8337230682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.981409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9930896759033</t>
+    <t xml:space="preserve">21.8337249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9814109802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.993091583252</t>
   </si>
   <si>
     <t xml:space="preserve">20.192569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3039875030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3855895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4607410430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6511516571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6239490509033</t>
+    <t xml:space="preserve">19.3039855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.385591506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4607391357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6511497497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.623950958252</t>
   </si>
   <si>
     <t xml:space="preserve">18.03005027771</t>
@@ -2693,10 +2693,10 @@
     <t xml:space="preserve">15.4685764312744</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6842679977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.811206817627</t>
+    <t xml:space="preserve">14.6842670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8112077713013</t>
   </si>
   <si>
     <t xml:space="preserve">12.653223991394</t>
@@ -2705,43 +2705,43 @@
     <t xml:space="preserve">13.7412824630737</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7775526046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3170480728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7341365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1648283004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6914148330688</t>
+    <t xml:space="preserve">13.777551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3170490264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7341394424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1648263931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6914138793945</t>
   </si>
   <si>
     <t xml:space="preserve">14.0903692245483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.269100189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0242872238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0061502456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2354421615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8863563537598</t>
+    <t xml:space="preserve">15.2690992355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0242862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0061511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2354440689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8863573074341</t>
   </si>
   <si>
     <t xml:space="preserve">13.238055229187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4783353805542</t>
+    <t xml:space="preserve">13.4783344268799</t>
   </si>
   <si>
     <t xml:space="preserve">13.5327386856079</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">13.4511346817017</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8092851638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1901073455811</t>
+    <t xml:space="preserve">13.809287071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1901082992554</t>
   </si>
   <si>
     <t xml:space="preserve">14.2581119537354</t>
@@ -2765,34 +2765,34 @@
     <t xml:space="preserve">13.3695297241211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8727579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9634284973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7820854187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2943801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4485216140747</t>
+    <t xml:space="preserve">13.8727569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9634265899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7820844650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.294379234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.448522567749</t>
   </si>
   <si>
     <t xml:space="preserve">14.5346593856812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1512260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3643045425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6544532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5683174133301</t>
+    <t xml:space="preserve">15.1512250900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3643035888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6544542312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5683164596558</t>
   </si>
   <si>
     <t xml:space="preserve">15.3461685180664</t>
@@ -2801,22 +2801,22 @@
     <t xml:space="preserve">16.6291732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7768602371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7904644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4478302001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3752918243408</t>
+    <t xml:space="preserve">15.7768630981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7904624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4478321075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3752937316895</t>
   </si>
   <si>
     <t xml:space="preserve">17.109733581543</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0398082733154</t>
+    <t xml:space="preserve">16.0398101806641</t>
   </si>
   <si>
     <t xml:space="preserve">17.2446327209473</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">16.4030952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8813457489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7066040039062</t>
+    <t xml:space="preserve">16.8813438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7066020965576</t>
   </si>
   <si>
     <t xml:space="preserve">17.2906188964844</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">17.4515705108643</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6585063934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6079196929932</t>
+    <t xml:space="preserve">17.658504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6079216003418</t>
   </si>
   <si>
     <t xml:space="preserve">17.355001449585</t>
@@ -2855,19 +2855,19 @@
     <t xml:space="preserve">17.6309127807617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9850044250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8884353637695</t>
+    <t xml:space="preserve">17.9850025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8884334564209</t>
   </si>
   <si>
     <t xml:space="preserve">18.6334018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.752965927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8081474304199</t>
+    <t xml:space="preserve">18.7529640197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8081455230713</t>
   </si>
   <si>
     <t xml:space="preserve">18.67018699646</t>
@@ -2882,67 +2882,67 @@
     <t xml:space="preserve">17.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3482913970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5874137878418</t>
+    <t xml:space="preserve">18.3482894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885093688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5874156951904</t>
   </si>
   <si>
     <t xml:space="preserve">18.9093132019043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8173408508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.222017288208</t>
+    <t xml:space="preserve">18.8173446655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2220191955566</t>
   </si>
   <si>
     <t xml:space="preserve">18.7161750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9644966125488</t>
+    <t xml:space="preserve">18.9645004272461</t>
   </si>
   <si>
     <t xml:space="preserve">18.7897529602051</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0104827880859</t>
+    <t xml:space="preserve">19.0104846954346</t>
   </si>
   <si>
     <t xml:space="preserve">19.0748634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5715084075928</t>
+    <t xml:space="preserve">19.5715103149414</t>
   </si>
   <si>
     <t xml:space="preserve">19.3507766723633</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9761810302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9577903747559</t>
+    <t xml:space="preserve">19.9761829376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9577865600586</t>
   </si>
   <si>
     <t xml:space="preserve">19.6542835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7278633117676</t>
+    <t xml:space="preserve">19.7278614044189</t>
   </si>
   <si>
     <t xml:space="preserve">19.9301986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4703388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0957431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2704925537109</t>
+    <t xml:space="preserve">19.4703407287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0957450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2704906463623</t>
   </si>
   <si>
     <t xml:space="preserve">20.3256740570068</t>
@@ -2969,25 +2969,25 @@
     <t xml:space="preserve">20.2245063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2337017059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8934078216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8223209381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4176464080811</t>
+    <t xml:space="preserve">20.2337036132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8934097290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8223190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4176483154297</t>
   </si>
   <si>
     <t xml:space="preserve">20.3808574676514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2061100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5556049346924</t>
+    <t xml:space="preserve">20.206111907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5556030273438</t>
   </si>
   <si>
     <t xml:space="preserve">20.8775024414062</t>
@@ -2996,19 +2996,19 @@
     <t xml:space="preserve">21.0614452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7303485870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7579383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7395439147949</t>
+    <t xml:space="preserve">20.7303504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7579402923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7395458221436</t>
   </si>
   <si>
     <t xml:space="preserve">20.6291809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2453899383545</t>
+    <t xml:space="preserve">21.2453880310059</t>
   </si>
   <si>
     <t xml:space="preserve">21.3649501800537</t>
@@ -3020,58 +3020,58 @@
     <t xml:space="preserve">21.4937133789062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9443702697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5580902099609</t>
+    <t xml:space="preserve">21.944372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5580921173096</t>
   </si>
   <si>
     <t xml:space="preserve">21.5213012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0271453857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.604076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8156089782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4109363555908</t>
+    <t xml:space="preserve">22.0271472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6040782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8156108856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4109382629395</t>
   </si>
   <si>
     <t xml:space="preserve">21.7420330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1191158294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5145950317383</t>
+    <t xml:space="preserve">22.1191177368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5145931243896</t>
   </si>
   <si>
     <t xml:space="preserve">22.6341571807861</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5421848297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6433525085449</t>
+    <t xml:space="preserve">22.5421867370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6433544158936</t>
   </si>
   <si>
     <t xml:space="preserve">22.3674392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4410152435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2294807434082</t>
+    <t xml:space="preserve">22.4410171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2294826507568</t>
   </si>
   <si>
     <t xml:space="preserve">22.6709442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">22.487003326416</t>
+    <t xml:space="preserve">22.4870014190674</t>
   </si>
   <si>
     <t xml:space="preserve">22.9008731842041</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">22.8732833862305</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8456935882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2135734558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2411651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6550350189209</t>
+    <t xml:space="preserve">22.8456916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2135753631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2411670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6550388336182</t>
   </si>
   <si>
     <t xml:space="preserve">23.5262794494629</t>
@@ -3116,28 +3116,28 @@
     <t xml:space="preserve">24.1700801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5998554229736</t>
+    <t xml:space="preserve">23.599853515625</t>
   </si>
   <si>
     <t xml:space="preserve">22.6525497436523</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7261276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9560565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1926937103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6684551239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1993999481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6500644683838</t>
+    <t xml:space="preserve">22.7261257171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1926956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.66845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1994018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6500625610352</t>
   </si>
   <si>
     <t xml:space="preserve">21.4661197662354</t>
@@ -3149,28 +3149,28 @@
     <t xml:space="preserve">22.5881690979004</t>
   </si>
   <si>
-    <t xml:space="preserve">24.041316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0112400054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.121603012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6274452209473</t>
+    <t xml:space="preserve">24.0413188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0112380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1216049194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6274471282959</t>
   </si>
   <si>
     <t xml:space="preserve">24.2988376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9677391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3607273101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8665733337402</t>
+    <t xml:space="preserve">23.9677410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3607292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8665752410889</t>
   </si>
   <si>
     <t xml:space="preserve">23.9217567443848</t>
@@ -3182,22 +3182,22 @@
     <t xml:space="preserve">24.4459915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0965003967285</t>
+    <t xml:space="preserve">24.0965023040771</t>
   </si>
   <si>
     <t xml:space="preserve">24.7403011322021</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2277488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8966503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4092044830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5471611022949</t>
+    <t xml:space="preserve">25.2277507781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8966541290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4092063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5471630096436</t>
   </si>
   <si>
     <t xml:space="preserve">25.0622005462646</t>
@@ -3206,19 +3206,19 @@
     <t xml:space="preserve">24.5655536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6391315460205</t>
+    <t xml:space="preserve">24.6391334533691</t>
   </si>
   <si>
     <t xml:space="preserve">24.6023426055908</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8874568939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3105201721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.568042755127</t>
+    <t xml:space="preserve">24.8874530792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3105239868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5680446624756</t>
   </si>
   <si>
     <t xml:space="preserve">25.0805950164795</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">25.3840999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5036602020264</t>
+    <t xml:space="preserve">25.503662109375</t>
   </si>
   <si>
     <t xml:space="preserve">25.3749027252197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7151966094971</t>
+    <t xml:space="preserve">25.7151947021484</t>
   </si>
   <si>
     <t xml:space="preserve">25.9359283447266</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">26.5613327026367</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7452754974365</t>
+    <t xml:space="preserve">26.7452774047852</t>
   </si>
   <si>
     <t xml:space="preserve">26.8740367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0119953155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5546245574951</t>
+    <t xml:space="preserve">27.0119934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5546226501465</t>
   </si>
   <si>
     <t xml:space="preserve">28.2811985015869</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">27.9225120544434</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0880603790283</t>
+    <t xml:space="preserve">28.0880584716797</t>
   </si>
   <si>
     <t xml:space="preserve">26.3957862854004</t>
@@ -3272,34 +3272,34 @@
     <t xml:space="preserve">26.5521373748779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8715496063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1106739044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8439540863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0278968811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7519874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6876068115234</t>
+    <t xml:space="preserve">25.8715476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1106758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.843957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0278987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7519855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6876049041748</t>
   </si>
   <si>
     <t xml:space="preserve">24.7127094268799</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2804431915283</t>
+    <t xml:space="preserve">24.2804412841797</t>
   </si>
   <si>
     <t xml:space="preserve">25.1449737548828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5011768341064</t>
+    <t xml:space="preserve">24.5011749267578</t>
   </si>
   <si>
     <t xml:space="preserve">25.0346088409424</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">25.236946105957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6968021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0462951660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9175338745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2854194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9267330169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9083366394043</t>
+    <t xml:space="preserve">25.6968040466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.046293258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9175357818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.28542137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9267311096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9083385467529</t>
   </si>
   <si>
     <t xml:space="preserve">26.1198711395264</t>
@@ -3332,37 +3332,37 @@
     <t xml:space="preserve">26.0003089904785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9635200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6600170135498</t>
+    <t xml:space="preserve">25.9635181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6600151062012</t>
   </si>
   <si>
     <t xml:space="preserve">25.0530033111572</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5931453704834</t>
+    <t xml:space="preserve">24.593147277832</t>
   </si>
   <si>
     <t xml:space="preserve">24.3908100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1608810424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5563583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.519567489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0162143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9150485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9058475494385</t>
+    <t xml:space="preserve">24.1608791351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.556360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5195693969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0162162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9150447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9058513641357</t>
   </si>
   <si>
     <t xml:space="preserve">24.0137252807617</t>
@@ -3374,40 +3374,40 @@
     <t xml:space="preserve">25.2001552581787</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2620487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.673433303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5446720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6918258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4251098632812</t>
+    <t xml:space="preserve">24.2620468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6734313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5446739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6918277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4251079559326</t>
   </si>
   <si>
     <t xml:space="preserve">23.3055477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5170803070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7838001251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1056957244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.151683807373</t>
+    <t xml:space="preserve">23.5170822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7838020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1056976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1516857147217</t>
   </si>
   <si>
     <t xml:space="preserve">24.5287666320801</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8138771057129</t>
+    <t xml:space="preserve">24.8138790130615</t>
   </si>
   <si>
     <t xml:space="preserve">24.8322734832764</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">25.4852695465088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7703800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6416187286377</t>
+    <t xml:space="preserve">25.7703819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6416168212891</t>
   </si>
   <si>
     <t xml:space="preserve">24.8414688110352</t>
@@ -3443,34 +3443,34 @@
     <t xml:space="preserve">24.4919757843018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5379638671875</t>
+    <t xml:space="preserve">24.5379619598389</t>
   </si>
   <si>
     <t xml:space="preserve">24.4367942810059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9861335754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9585418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4000053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.949348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7954845428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2252597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3197212219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4693603515625</t>
+    <t xml:space="preserve">23.9861354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9585456848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4000072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9493465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7954807281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2252616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3197231292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4693622589111</t>
   </si>
   <si>
     <t xml:space="preserve">26.4325752258301</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">26.1826133728027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1919727325439</t>
+    <t xml:space="preserve">26.1919746398926</t>
   </si>
   <si>
     <t xml:space="preserve">26.5196075439453</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">26.4259967803955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6693820953369</t>
+    <t xml:space="preserve">26.6693840026855</t>
   </si>
   <si>
     <t xml:space="preserve">26.8753223419189</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">27.3901786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5867557525635</t>
+    <t xml:space="preserve">27.5867576599121</t>
   </si>
   <si>
     <t xml:space="preserve">27.7926998138428</t>
@@ -3515,10 +3515,10 @@
     <t xml:space="preserve">27.7084503173828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8769493103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3340110778809</t>
+    <t xml:space="preserve">27.8769454956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3340129852295</t>
   </si>
   <si>
     <t xml:space="preserve">27.2872066497803</t>
@@ -3533,43 +3533,43 @@
     <t xml:space="preserve">27.1935958862305</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1655158996582</t>
+    <t xml:space="preserve">27.1655139923096</t>
   </si>
   <si>
     <t xml:space="preserve">27.9237518310547</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8395042419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8020610809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4011611938477</t>
+    <t xml:space="preserve">27.8395023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.802059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.401159286499</t>
   </si>
   <si>
     <t xml:space="preserve">28.5602989196777</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3075523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6819877624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.298189163208</t>
+    <t xml:space="preserve">28.3075504302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6819915771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2981910705566</t>
   </si>
   <si>
     <t xml:space="preserve">28.3169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5041313171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3824367523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4479656219482</t>
+    <t xml:space="preserve">28.5041332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.382438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4479637145996</t>
   </si>
   <si>
     <t xml:space="preserve">28.7568759918213</t>
@@ -3578,67 +3578,67 @@
     <t xml:space="preserve">27.9799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5696601867676</t>
+    <t xml:space="preserve">28.5696582794189</t>
   </si>
   <si>
     <t xml:space="preserve">28.8317642211914</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7943229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6913509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4198837280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4760494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6710071563721</t>
+    <t xml:space="preserve">28.7943210601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.691349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.419885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4760475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6710052490234</t>
   </si>
   <si>
     <t xml:space="preserve">28.1203327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8301429748535</t>
+    <t xml:space="preserve">27.8301410675049</t>
   </si>
   <si>
     <t xml:space="preserve">27.989278793335</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1671352386475</t>
+    <t xml:space="preserve">28.1671371459961</t>
   </si>
   <si>
     <t xml:space="preserve">28.2701091766357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1390552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2888278961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4854106903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3637180328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7849617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8785705566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0002632141113</t>
+    <t xml:space="preserve">28.1390533447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2888298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4854125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3637161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7849597930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8785724639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0002613067627</t>
   </si>
   <si>
     <t xml:space="preserve">29.3934230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2359104156494</t>
+    <t xml:space="preserve">30.2359085083008</t>
   </si>
   <si>
     <t xml:space="preserve">30.3201580047607</t>
@@ -3653,46 +3653,46 @@
     <t xml:space="preserve">29.992525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9550800323486</t>
+    <t xml:space="preserve">29.9550819396973</t>
   </si>
   <si>
     <t xml:space="preserve">29.8989162445068</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5619201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5057563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7585010528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8053073883057</t>
+    <t xml:space="preserve">29.5619220733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5057544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7585029602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.805305480957</t>
   </si>
   <si>
     <t xml:space="preserve">29.5806427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8708324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.908275604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8333892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2171859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4044055938721</t>
+    <t xml:space="preserve">29.8708343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9082775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8333911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2171878814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4044075012207</t>
   </si>
   <si>
     <t xml:space="preserve">30.385684967041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8630981445312</t>
+    <t xml:space="preserve">30.8630962371826</t>
   </si>
   <si>
     <t xml:space="preserve">30.8537330627441</t>
@@ -3704,19 +3704,19 @@
     <t xml:space="preserve">30.5448246002197</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4980201721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.469934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7133197784424</t>
+    <t xml:space="preserve">30.4980182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4699325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.713321685791</t>
   </si>
   <si>
     <t xml:space="preserve">30.1142158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1891040802002</t>
+    <t xml:space="preserve">30.1891059875488</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461696624756</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">29.3185348510742</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0299701690674</t>
+    <t xml:space="preserve">30.029972076416</t>
   </si>
   <si>
     <t xml:space="preserve">30.348237991333</t>
@@ -3740,22 +3740,22 @@
     <t xml:space="preserve">28.8130435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2420234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5212306976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4837856292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0267219543457</t>
+    <t xml:space="preserve">28.2420253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5212287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4837875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0267238616943</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6616458892822</t>
+    <t xml:space="preserve">27.661642074585</t>
   </si>
   <si>
     <t xml:space="preserve">28.6445465087891</t>
@@ -3767,73 +3767,73 @@
     <t xml:space="preserve">29.2717323303223</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2623710632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5244770050049</t>
+    <t xml:space="preserve">29.2623691558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5244789123535</t>
   </si>
   <si>
     <t xml:space="preserve">29.7304172515869</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1610260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4792957305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5916271209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3669624328613</t>
+    <t xml:space="preserve">30.1610221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4792976379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.591625213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.36696434021</t>
   </si>
   <si>
     <t xml:space="preserve">30.6384315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6103477478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3030605316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9286212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1626453399658</t>
+    <t xml:space="preserve">30.6103496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7694854736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3030567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9286231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1626472473145</t>
   </si>
   <si>
     <t xml:space="preserve">31.668140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8553524017334</t>
+    <t xml:space="preserve">31.8553581237793</t>
   </si>
   <si>
     <t xml:space="preserve">31.4341144561768</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1813659667969</t>
+    <t xml:space="preserve">31.1813678741455</t>
   </si>
   <si>
     <t xml:space="preserve">31.2749767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8179168701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9302444458008</t>
+    <t xml:space="preserve">31.8179187774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9302406311035</t>
   </si>
   <si>
     <t xml:space="preserve">32.810173034668</t>
   </si>
   <si>
-    <t xml:space="preserve">32.763370513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.641674041748</t>
+    <t xml:space="preserve">32.7633666992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6416778564453</t>
   </si>
   <si>
     <t xml:space="preserve">31.9489669799805</t>
@@ -3845,19 +3845,19 @@
     <t xml:space="preserve">32.1081008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6945991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3124217987061</t>
+    <t xml:space="preserve">30.6945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3124198913574</t>
   </si>
   <si>
     <t xml:space="preserve">30.7320442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5822620391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8911762237549</t>
+    <t xml:space="preserve">30.5822658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8911800384521</t>
   </si>
   <si>
     <t xml:space="preserve">31.752384185791</t>
@@ -3875,127 +3875,127 @@
     <t xml:space="preserve">30.0861339569092</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1516628265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5525608062744</t>
+    <t xml:space="preserve">30.1516609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5525588989258</t>
   </si>
   <si>
     <t xml:space="preserve">29.702335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7507610321045</t>
+    <t xml:space="preserve">30.7507629394531</t>
   </si>
   <si>
     <t xml:space="preserve">30.9754276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0690364837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9567031860352</t>
+    <t xml:space="preserve">30.9379806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.069034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9567050933838</t>
   </si>
   <si>
     <t xml:space="preserve">30.9941482543945</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9660663604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2937030792236</t>
+    <t xml:space="preserve">30.9660682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2936992645264</t>
   </si>
   <si>
     <t xml:space="preserve">31.2468948364258</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2656192779541</t>
+    <t xml:space="preserve">31.2656154632568</t>
   </si>
   <si>
     <t xml:space="preserve">31.602611541748</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7804679870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3779487609863</t>
+    <t xml:space="preserve">31.7804718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3779468536377</t>
   </si>
   <si>
     <t xml:space="preserve">30.5073776245117</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9721813201904</t>
+    <t xml:space="preserve">28.9721794128418</t>
   </si>
   <si>
     <t xml:space="preserve">27.6335620880127</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0063781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0454444885254</t>
+    <t xml:space="preserve">27.0063800811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0454425811768</t>
   </si>
   <si>
     <t xml:space="preserve">26.8378810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2045803070068</t>
+    <t xml:space="preserve">28.2045822143555</t>
   </si>
   <si>
     <t xml:space="preserve">28.0548057556152</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1187076568604</t>
+    <t xml:space="preserve">27.118709564209</t>
   </si>
   <si>
     <t xml:space="preserve">25.9298667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">26.042200088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8191585540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5664119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2481422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7800941467285</t>
+    <t xml:space="preserve">26.0421962738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8191566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5664100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.248140335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7800922393799</t>
   </si>
   <si>
     <t xml:space="preserve">26.5102462768555</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3152923583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9970169067383</t>
+    <t xml:space="preserve">27.3152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9970149993896</t>
   </si>
   <si>
     <t xml:space="preserve">26.1264476776123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2294178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.107723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5399551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.541576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4463443756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9766693115234</t>
+    <t xml:space="preserve">26.229419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1077251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5399532318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5415744781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4463405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9766712188721</t>
   </si>
   <si>
     <t xml:space="preserve">27.13743019104</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">26.9502124786377</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7287940979004</t>
+    <t xml:space="preserve">28.728796005249</t>
   </si>
   <si>
     <t xml:space="preserve">27.5961170196533</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">29.0377082824707</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1219577789307</t>
+    <t xml:space="preserve">29.121955871582</t>
   </si>
   <si>
     <t xml:space="preserve">29.1406764984131</t>
@@ -4031,22 +4031,22 @@
     <t xml:space="preserve">28.8598480224609</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6071014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2326641082764</t>
+    <t xml:space="preserve">28.6071033477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2326622009277</t>
   </si>
   <si>
     <t xml:space="preserve">28.8692092895508</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0096244812012</t>
+    <t xml:space="preserve">29.0096225738525</t>
   </si>
   <si>
     <t xml:space="preserve">29.2904529571533</t>
   </si>
   <si>
-    <t xml:space="preserve">28.981538772583</t>
+    <t xml:space="preserve">28.9815406799316</t>
   </si>
   <si>
     <t xml:space="preserve">29.515115737915</t>
@@ -4058,22 +4058,22 @@
     <t xml:space="preserve">27.0531826019287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5586738586426</t>
+    <t xml:space="preserve">27.5586757659912</t>
   </si>
   <si>
     <t xml:space="preserve">28.8972930908203</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4666862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4831790924072</t>
+    <t xml:space="preserve">28.4666900634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4831771850586</t>
   </si>
   <si>
     <t xml:space="preserve">29.32204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9312076568604</t>
+    <t xml:space="preserve">28.931209564209</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549480438232</t>
@@ -4091,10 +4091,10 @@
     <t xml:space="preserve">29.7605361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0265331268311</t>
+    <t xml:space="preserve">28.6452312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0265350341797</t>
   </si>
   <si>
     <t xml:space="preserve">29.045597076416</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">26.7482604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0247020721436</t>
+    <t xml:space="preserve">27.0247058868408</t>
   </si>
   <si>
     <t xml:space="preserve">27.1104965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052742004395</t>
+    <t xml:space="preserve">26.6052722930908</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101306915283</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">26.9675102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2153549194336</t>
+    <t xml:space="preserve">27.215353012085</t>
   </si>
   <si>
     <t xml:space="preserve">27.7682399749756</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">27.8635654449463</t>
   </si>
   <si>
-    <t xml:space="preserve">27.730110168457</t>
+    <t xml:space="preserve">27.7301082611084</t>
   </si>
   <si>
     <t xml:space="preserve">28.2829971313477</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">27.9684238433838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1304779052734</t>
+    <t xml:space="preserve">28.1304759979248</t>
   </si>
   <si>
     <t xml:space="preserve">28.4450492858887</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">26.1667785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.52809715271</t>
+    <t xml:space="preserve">25.5280990600586</t>
   </si>
   <si>
     <t xml:space="preserve">25.0133419036865</t>
@@ -4226,22 +4226,22 @@
     <t xml:space="preserve">24.765495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">24.393726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.698766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3374481201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9189319610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1658611297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.29931640625</t>
+    <t xml:space="preserve">24.3937282562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6987686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3374462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9189300537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1658592224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2993183135986</t>
   </si>
   <si>
     <t xml:space="preserve">25.2230548858643</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">24.9084815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3469791412354</t>
+    <t xml:space="preserve">25.346981048584</t>
   </si>
   <si>
     <t xml:space="preserve">26.2144393920898</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">25.9093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4908828735352</t>
+    <t xml:space="preserve">26.4908847808838</t>
   </si>
   <si>
     <t xml:space="preserve">27.0532989501953</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">27.0437698364258</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6815319061279</t>
+    <t xml:space="preserve">26.6815338134766</t>
   </si>
   <si>
     <t xml:space="preserve">27.2630176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7882213592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5031604766846</t>
+    <t xml:space="preserve">28.7882232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5031585693359</t>
   </si>
   <si>
     <t xml:space="preserve">29.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5508232116699</t>
+    <t xml:space="preserve">29.5508213043213</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461486816406</t>
@@ -4301,16 +4301,16 @@
     <t xml:space="preserve">29.9797859191895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8939952850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0760250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7051696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7995834350586</t>
+    <t xml:space="preserve">29.8939933776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0760269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.705171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7995853424072</t>
   </si>
   <si>
     <t xml:space="preserve">31.0283622741699</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">30.4468803405762</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9997653961182</t>
+    <t xml:space="preserve">30.9997673034668</t>
   </si>
   <si>
     <t xml:space="preserve">30.551736831665</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">30.0274486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2371635437012</t>
+    <t xml:space="preserve">30.2371616363525</t>
   </si>
   <si>
     <t xml:space="preserve">30.5993995666504</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">29.5317573547363</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1790561676025</t>
+    <t xml:space="preserve">29.1790542602539</t>
   </si>
   <si>
     <t xml:space="preserve">29.1885871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4554977416992</t>
+    <t xml:space="preserve">29.4554958343506</t>
   </si>
   <si>
     <t xml:space="preserve">30.3610877990723</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">31.0664920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">31.590784072876</t>
+    <t xml:space="preserve">31.5907802581787</t>
   </si>
   <si>
     <t xml:space="preserve">30.5326709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3515567779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3896827697754</t>
+    <t xml:space="preserve">30.3515529632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.389684677124</t>
   </si>
   <si>
     <t xml:space="preserve">30.3038921356201</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">29.874927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2362499237061</t>
+    <t xml:space="preserve">29.2362480163574</t>
   </si>
   <si>
     <t xml:space="preserve">28.0160865783691</t>
@@ -4391,34 +4391,34 @@
     <t xml:space="preserve">28.6166362762451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6738300323486</t>
+    <t xml:space="preserve">28.6738319396973</t>
   </si>
   <si>
     <t xml:space="preserve">28.3020629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9865741729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2353343963623</t>
+    <t xml:space="preserve">26.986572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2353363037109</t>
   </si>
   <si>
     <t xml:space="preserve">28.492712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0560474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5126895904541</t>
+    <t xml:space="preserve">30.0560455322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5126914978027</t>
   </si>
   <si>
     <t xml:space="preserve">29.7128753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6842765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2648468017578</t>
+    <t xml:space="preserve">29.6842784881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2648487091064</t>
   </si>
   <si>
     <t xml:space="preserve">29.7033424377441</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">29.3983020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7700710296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7510032653809</t>
+    <t xml:space="preserve">29.7700691223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7510051727295</t>
   </si>
   <si>
     <t xml:space="preserve">30.5422058105469</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">30.9616355895996</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4945430755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6661262512207</t>
+    <t xml:space="preserve">30.4945411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6661243438721</t>
   </si>
   <si>
     <t xml:space="preserve">30.8472461700439</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">31.1236896514893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9434814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9816150665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7242336273193</t>
+    <t xml:space="preserve">31.9434833526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.981616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7242374420166</t>
   </si>
   <si>
     <t xml:space="preserve">31.5717163085938</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">30.5231399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9521045684814</t>
+    <t xml:space="preserve">30.9521026611328</t>
   </si>
   <si>
     <t xml:space="preserve">30.5136051177979</t>
@@ -4487,13 +4487,13 @@
     <t xml:space="preserve">32.5535697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6289119720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8853778839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3715343475342</t>
+    <t xml:space="preserve">31.6289100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8853759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3715324401855</t>
   </si>
   <si>
     <t xml:space="preserve">30.7709846496582</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">31.0950889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">31.037899017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4763946533203</t>
+    <t xml:space="preserve">31.0378971099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.476390838623</t>
   </si>
   <si>
     <t xml:space="preserve">32.1913299560547</t>
@@ -4514,19 +4514,19 @@
     <t xml:space="preserve">32.0769424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">32.105541229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1246032714844</t>
+    <t xml:space="preserve">32.1055374145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1246070861816</t>
   </si>
   <si>
     <t xml:space="preserve">32.143669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8386325836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9244213104248</t>
+    <t xml:space="preserve">31.8386287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9244251251221</t>
   </si>
   <si>
     <t xml:space="preserve">32.1341361999512</t>
@@ -4538,16 +4538,16 @@
     <t xml:space="preserve">32.8300094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1064529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8404579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5926132202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9167175292969</t>
+    <t xml:space="preserve">33.1064491271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.840461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5926170349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9167213439941</t>
   </si>
   <si>
     <t xml:space="preserve">33.9357833862305</t>
@@ -4562,16 +4562,16 @@
     <t xml:space="preserve">33.6116752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.468692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6021423339844</t>
+    <t xml:space="preserve">33.4686889648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6021461486816</t>
   </si>
   <si>
     <t xml:space="preserve">33.3161697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5544815063477</t>
+    <t xml:space="preserve">33.5544853210449</t>
   </si>
   <si>
     <t xml:space="preserve">33.6784057617188</t>
@@ -4595,25 +4595,25 @@
     <t xml:space="preserve">32.2866554260254</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9729957580566</t>
+    <t xml:space="preserve">32.9729995727539</t>
   </si>
   <si>
     <t xml:space="preserve">33.373363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.953929901123</t>
+    <t xml:space="preserve">32.9539337158203</t>
   </si>
   <si>
     <t xml:space="preserve">33.3638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">33.411491394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.583080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0311088562012</t>
+    <t xml:space="preserve">33.4114952087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5830764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0311126708984</t>
   </si>
   <si>
     <t xml:space="preserve">34.7937126159668</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">35.0892181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5649261474609</t>
+    <t xml:space="preserve">34.5649299621582</t>
   </si>
   <si>
     <t xml:space="preserve">35.2512702941895</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">35.8804168701172</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5372428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5753784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7469596862793</t>
+    <t xml:space="preserve">35.5372467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5753746032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7469635009766</t>
   </si>
   <si>
     <t xml:space="preserve">35.3942604064941</t>
@@ -4649,7 +4649,7 @@
     <t xml:space="preserve">35.6516380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">36.109203338623</t>
+    <t xml:space="preserve">36.1091995239258</t>
   </si>
   <si>
     <t xml:space="preserve">35.9852752685547</t>
@@ -4661,13 +4661,13 @@
     <t xml:space="preserve">35.2036094665527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5944442749023</t>
+    <t xml:space="preserve">35.5944404602051</t>
   </si>
   <si>
     <t xml:space="preserve">34.9843635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5563087463379</t>
+    <t xml:space="preserve">35.5563125610352</t>
   </si>
   <si>
     <t xml:space="preserve">35.3370628356934</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">35.8327560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1568641662598</t>
+    <t xml:space="preserve">36.1568603515625</t>
   </si>
   <si>
     <t xml:space="preserve">35.937614440918</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">34.1454963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8413734436035</t>
+    <t xml:space="preserve">34.8413696289062</t>
   </si>
   <si>
     <t xml:space="preserve">34.6697883605957</t>
@@ -4709,16 +4709,16 @@
     <t xml:space="preserve">34.6888542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1759262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1282653808594</t>
+    <t xml:space="preserve">36.1759300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1282615661621</t>
   </si>
   <si>
     <t xml:space="preserve">36.0615386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7097434997559</t>
+    <t xml:space="preserve">36.7097473144531</t>
   </si>
   <si>
     <t xml:space="preserve">37.8631858825684</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">34.9748268127441</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6707038879395</t>
+    <t xml:space="preserve">35.6707000732422</t>
   </si>
   <si>
     <t xml:space="preserve">33.7546653747559</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">33.8881187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3552131652832</t>
+    <t xml:space="preserve">34.3552169799805</t>
   </si>
   <si>
     <t xml:space="preserve">35.1082878112793</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">36.3761100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5953598022461</t>
+    <t xml:space="preserve">36.5953559875488</t>
   </si>
   <si>
     <t xml:space="preserve">36.8908653259277</t>
@@ -4775,28 +4775,28 @@
     <t xml:space="preserve">34.946231842041</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3656616210938</t>
+    <t xml:space="preserve">35.3656578063965</t>
   </si>
   <si>
     <t xml:space="preserve">35.4037895202637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5086479187012</t>
+    <t xml:space="preserve">35.5086517333984</t>
   </si>
   <si>
     <t xml:space="preserve">35.3847274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9471435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9090156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5286293029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4618988037109</t>
+    <t xml:space="preserve">35.9471473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9090118408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5286254882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4619026184082</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807846069336</t>
@@ -71696,7 +71696,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6494907407</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>566158</v>
@@ -71717,6 +71717,32 @@
         <v>2149</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912962963</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>730474</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>91.6999969482422</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>89.8600006103516</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>90.7200012207031</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>2145</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2150" uniqueCount="2150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="2151">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6851558685303</t>
+    <t xml:space="preserve">15.6851577758789</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8713998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3207607269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2397842407227</t>
+    <t xml:space="preserve">15.8714008331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3207597732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.239785194397</t>
   </si>
   <si>
     <t xml:space="preserve">14.74582862854</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9644641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2964668273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4989099502563</t>
+    <t xml:space="preserve">14.964467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2964649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4989109039307</t>
   </si>
   <si>
     <t xml:space="preserve">15.0616369247437</t>
@@ -71,31 +71,31 @@
     <t xml:space="preserve">14.5028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5433883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8511009216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.187087059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9401741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4098329544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.923975944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2802715301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1830997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6243629455566</t>
+    <t xml:space="preserve">14.5433893203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8510980606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870880126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9401721954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.409836769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9239768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2802724838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1831026077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6243648529053</t>
   </si>
   <si>
     <t xml:space="preserve">15.3936395645142</t>
@@ -104,94 +104,94 @@
     <t xml:space="preserve">14.8106088638306</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7296333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8996839523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5190925598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7336206436157</t>
+    <t xml:space="preserve">14.7296342849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8996829986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5190944671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.73362159729</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449335098267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.098014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3206415176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4744958877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8955755233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7822074890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3328495025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2194786071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057283401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8348999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5514860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3409471511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8672933578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.102123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4827165603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3774452209473</t>
+    <t xml:space="preserve">14.0980176925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3206405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.474494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8955736160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7822065353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3328485488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2194795608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057264328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8349018096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5514831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3409452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8672924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1021242141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2235927581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3774461746216</t>
   </si>
   <si>
     <t xml:space="preserve">15.4017391204834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4665212631226</t>
+    <t xml:space="preserve">15.4665193557739</t>
   </si>
   <si>
     <t xml:space="preserve">15.4908123016357</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5232038497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636892318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426105499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742300033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8390102386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5879821777344</t>
+    <t xml:space="preserve">15.5232028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426124572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742290496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8390111923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879812240601</t>
   </si>
   <si>
     <t xml:space="preserve">15.6365671157837</t>
@@ -203,31 +203,31 @@
     <t xml:space="preserve">15.8309116363525</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8794994354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8228139877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8956956863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2762851715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.122428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8471078872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8875961303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4422254562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3855428695679</t>
+    <t xml:space="preserve">15.8795003890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8228168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8956928253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2762813568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1224269866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8471097946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8875970840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4422273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3855419158936</t>
   </si>
   <si>
     <t xml:space="preserve">16.3086738586426</t>
@@ -236,133 +236,133 @@
     <t xml:space="preserve">16.2276973724365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7135562896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6568737030029</t>
+    <t xml:space="preserve">16.7135543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6568756103516</t>
   </si>
   <si>
     <t xml:space="preserve">16.430139541626</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6120510101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9179992675781</t>
+    <t xml:space="preserve">16.6120548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.918004989624</t>
   </si>
   <si>
     <t xml:space="preserve">17.0254936218262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9758777618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9924163818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6285915374756</t>
+    <t xml:space="preserve">16.9758815765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9924201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.628589630127</t>
   </si>
   <si>
     <t xml:space="preserve">16.7774314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9841499328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1081848144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9345359802246</t>
+    <t xml:space="preserve">16.98415184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1081809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9345397949219</t>
   </si>
   <si>
     <t xml:space="preserve">16.5541725158691</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5955142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.760892868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.703010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8766593933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4058589935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7696857452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0094814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9681377410889</t>
+    <t xml:space="preserve">16.595516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7608909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7030124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8766555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4058609008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.009485244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9681396484375</t>
   </si>
   <si>
     <t xml:space="preserve">17.8606452941895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7779598236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8854541778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6952686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1087074279785</t>
+    <t xml:space="preserve">17.7779560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8854503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6952705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1087093353271</t>
   </si>
   <si>
     <t xml:space="preserve">17.9598712921143</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2658157348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1748600006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2823581695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2988929748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4725379943848</t>
+    <t xml:space="preserve">18.2658195495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.174861907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2823600769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2988910675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4725360870361</t>
   </si>
   <si>
     <t xml:space="preserve">18.1831302642822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1335163116455</t>
+    <t xml:space="preserve">18.1335144042969</t>
   </si>
   <si>
     <t xml:space="preserve">18.0425586700439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8027629852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0921726226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9185237884521</t>
+    <t xml:space="preserve">17.8027648925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.092170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9185276031494</t>
   </si>
   <si>
     <t xml:space="preserve">18.0012149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3149032592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9097290039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368598937988</t>
+    <t xml:space="preserve">17.3149013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9097309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368637084961</t>
   </si>
   <si>
     <t xml:space="preserve">16.8022403717041</t>
@@ -371,43 +371,43 @@
     <t xml:space="preserve">17.7366142272949</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5712356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3479804992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9102554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6694068908691</t>
+    <t xml:space="preserve">17.5712394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3479785919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9102592468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6694087982178</t>
   </si>
   <si>
     <t xml:space="preserve">14.8342580795288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1402053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399616241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2978363037109</t>
+    <t xml:space="preserve">15.1402044296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2559680938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2978420257568</t>
   </si>
   <si>
     <t xml:space="preserve">15.7272920608521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5867223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2311611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6115264892578</t>
+    <t xml:space="preserve">15.5867233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2311592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6115293502808</t>
   </si>
   <si>
     <t xml:space="preserve">16.2813014984131</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">16.4632148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6533966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6864719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6782054901123</t>
+    <t xml:space="preserve">16.6533985137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6864738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6782035827637</t>
   </si>
   <si>
     <t xml:space="preserve">16.7443542480469</t>
@@ -437,52 +437,52 @@
     <t xml:space="preserve">16.8187732696533</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9510746002197</t>
+    <t xml:space="preserve">16.9510765075684</t>
   </si>
   <si>
     <t xml:space="preserve">17.0999126434326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1164531707764</t>
+    <t xml:space="preserve">17.116455078125</t>
   </si>
   <si>
     <t xml:space="preserve">17.2983665466309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2404823303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0751094818115</t>
+    <t xml:space="preserve">17.2404842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0751113891602</t>
   </si>
   <si>
     <t xml:space="preserve">17.3314418792725</t>
   </si>
   <si>
-    <t xml:space="preserve">17.620849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1004428863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125831604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5960426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0756340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7944965362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8771839141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1913986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2492809295654</t>
+    <t xml:space="preserve">17.6208477020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1004409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125812530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5960445404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0756359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7944946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8771858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1914005279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2492828369141</t>
   </si>
   <si>
     <t xml:space="preserve">18.0839023590088</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">18.2906246185303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1665897369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9929466247559</t>
+    <t xml:space="preserve">18.1665916442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9929447174072</t>
   </si>
   <si>
     <t xml:space="preserve">17.8441066741943</t>
@@ -503,40 +503,40 @@
     <t xml:space="preserve">17.7200736999512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7283458709717</t>
+    <t xml:space="preserve">17.728343963623</t>
   </si>
   <si>
     <t xml:space="preserve">17.8937225341797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0673637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.37331199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9438591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4317188262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3573017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1009654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1257781982422</t>
+    <t xml:space="preserve">18.0673675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3733139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9438629150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4317226409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3573036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1009693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1257743835449</t>
   </si>
   <si>
     <t xml:space="preserve">19.1919250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1753883361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2828845977783</t>
+    <t xml:space="preserve">19.175386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2828826904297</t>
   </si>
   <si>
     <t xml:space="preserve">19.1340446472168</t>
@@ -545,49 +545,49 @@
     <t xml:space="preserve">19.3490314483643</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.76247215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.70458984375</t>
+    <t xml:space="preserve">19.4978733062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7624740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7045917510986</t>
   </si>
   <si>
     <t xml:space="preserve">19.4647941589355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0596199035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.646183013916</t>
+    <t xml:space="preserve">19.0596256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6461811065674</t>
   </si>
   <si>
     <t xml:space="preserve">19.1175060272217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1588497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.010009765625</t>
+    <t xml:space="preserve">19.1588516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0100135803223</t>
   </si>
   <si>
     <t xml:space="preserve">18.7536773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9025173187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0844326019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9934730529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7950210571289</t>
+    <t xml:space="preserve">18.9025192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0844306945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9934749603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7950229644775</t>
   </si>
   <si>
     <t xml:space="preserve">18.7867546081543</t>
@@ -599,22 +599,22 @@
     <t xml:space="preserve">18.3319664001465</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6291179656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.869441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1505794525146</t>
+    <t xml:space="preserve">17.6291217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8694400787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1505813598633</t>
   </si>
   <si>
     <t xml:space="preserve">18.3485069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6627216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.728874206543</t>
+    <t xml:space="preserve">18.6627197265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7288703918457</t>
   </si>
   <si>
     <t xml:space="preserve">18.6875286102295</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">18.8942451477051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4229221343994</t>
+    <t xml:space="preserve">18.4229259490967</t>
   </si>
   <si>
     <t xml:space="preserve">18.480806350708</t>
@@ -638,160 +638,160 @@
     <t xml:space="preserve">18.0590953826904</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6709880828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9355888366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4399871826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8782367706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6797847747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1676445007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8451595306396</t>
+    <t xml:space="preserve">18.670991897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9355926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4399909973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8782386779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6797866821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1676425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8451614379883</t>
   </si>
   <si>
     <t xml:space="preserve">19.7790126800537</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1428394317627</t>
+    <t xml:space="preserve">20.1428375244141</t>
   </si>
   <si>
     <t xml:space="preserve">19.9113121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1759128570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0022659301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9278450012207</t>
+    <t xml:space="preserve">20.1759166717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.002269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9278526306152</t>
   </si>
   <si>
     <t xml:space="preserve">20.0105381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8038158416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1014957427979</t>
+    <t xml:space="preserve">19.8038177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1014938354492</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263008117676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1097640991211</t>
+    <t xml:space="preserve">20.1097660064697</t>
   </si>
   <si>
     <t xml:space="preserve">20.1924495697021</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6389675140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1345710754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2751388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2172584533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3164825439453</t>
+    <t xml:space="preserve">20.6389713287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1345691680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2751407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2172603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3164863586426</t>
   </si>
   <si>
     <t xml:space="preserve">20.2420635223389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3330211639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2255268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6555023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5066680908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3578300476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4818592071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0849552154541</t>
+    <t xml:space="preserve">20.3330230712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2255306243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6555061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5066661834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3578319549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4818630218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0849590301514</t>
   </si>
   <si>
     <t xml:space="preserve">20.3991718292236</t>
   </si>
   <si>
-    <t xml:space="preserve">20.564546585083</t>
+    <t xml:space="preserve">20.5645484924316</t>
   </si>
   <si>
     <t xml:space="preserve">20.5397415161133</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6885795593262</t>
+    <t xml:space="preserve">20.6885776519775</t>
   </si>
   <si>
     <t xml:space="preserve">19.894775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4074420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7133884429932</t>
+    <t xml:space="preserve">20.4074382781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7133846282959</t>
   </si>
   <si>
     <t xml:space="preserve">20.9697208404541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3495597839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4239807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3082180023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7547302246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9609241485596</t>
+    <t xml:space="preserve">20.3495616912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.423978805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3082160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.754732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9609260559082</t>
   </si>
   <si>
     <t xml:space="preserve">19.8865051269531</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8286266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8534297943115</t>
+    <t xml:space="preserve">19.8286247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8534278869629</t>
   </si>
   <si>
     <t xml:space="preserve">20.1180324554443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5722904205322</t>
+    <t xml:space="preserve">19.5722923278809</t>
   </si>
   <si>
     <t xml:space="preserve">19.2994174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5144100189209</t>
+    <t xml:space="preserve">19.5144081115723</t>
   </si>
   <si>
     <t xml:space="preserve">19.5474815368652</t>
@@ -800,28 +800,28 @@
     <t xml:space="preserve">19.4234523773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6136341094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5640201568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3821067810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7376689910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3660984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9361171722412</t>
+    <t xml:space="preserve">19.6136379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.564022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3821105957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7376670837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3661003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9361190795898</t>
   </si>
   <si>
     <t xml:space="preserve">20.200719833374</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4901275634766</t>
+    <t xml:space="preserve">20.4901313781738</t>
   </si>
   <si>
     <t xml:space="preserve">20.7381935119629</t>
@@ -830,61 +830,61 @@
     <t xml:space="preserve">21.2922058105469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.15163230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0854816436768</t>
+    <t xml:space="preserve">21.1516342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.085485458374</t>
   </si>
   <si>
     <t xml:space="preserve">20.9366436004639</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7795372009277</t>
+    <t xml:space="preserve">20.779541015625</t>
   </si>
   <si>
     <t xml:space="preserve">20.4570541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7051162719727</t>
+    <t xml:space="preserve">20.7051200866699</t>
   </si>
   <si>
     <t xml:space="preserve">21.1268272399902</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0435581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1192493438721</t>
+    <t xml:space="preserve">22.0435562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1192512512207</t>
   </si>
   <si>
     <t xml:space="preserve">21.8669395446777</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9846839904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2958679199219</t>
+    <t xml:space="preserve">21.9846858978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2958698272705</t>
   </si>
   <si>
     <t xml:space="preserve">22.4724864959717</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2201747894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2622261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5397682189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5734100341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8080673217773</t>
+    <t xml:space="preserve">22.2201766967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.262228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5397701263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5734081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.808069229126</t>
   </si>
   <si>
     <t xml:space="preserve">21.6987323760986</t>
@@ -893,100 +893,100 @@
     <t xml:space="preserve">21.0847778320312</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3202648162842</t>
+    <t xml:space="preserve">21.3202667236328</t>
   </si>
   <si>
     <t xml:space="preserve">20.9502086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6390266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4203586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5549240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4539985656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9670276641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1941089630127</t>
+    <t xml:space="preserve">20.6390285491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4203605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5549221038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4540004730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9670314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1941108703613</t>
   </si>
   <si>
     <t xml:space="preserve">20.8576965332031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1688804626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8324642181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9586200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156433105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.597806930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2613925933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1015968322754</t>
+    <t xml:space="preserve">21.1688823699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8324661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9586181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8156452178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5978088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2613964080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1016006469727</t>
   </si>
   <si>
     <t xml:space="preserve">21.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6146278381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8164768218994</t>
+    <t xml:space="preserve">21.614631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.816478729248</t>
   </si>
   <si>
     <t xml:space="preserve">21.656681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8248882293701</t>
+    <t xml:space="preserve">21.8248920440674</t>
   </si>
   <si>
     <t xml:space="preserve">21.5473461151123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5725784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0351486206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.858528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9258098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7828369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3211002349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4884719848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3875484466553</t>
+    <t xml:space="preserve">21.5725803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0351505279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8585300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9258117675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7828388214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3210983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4884738922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3875522613525</t>
   </si>
   <si>
     <t xml:space="preserve">22.1949462890625</t>
   </si>
   <si>
-    <t xml:space="preserve">21.850118637085</t>
+    <t xml:space="preserve">21.8501224517822</t>
   </si>
   <si>
     <t xml:space="preserve">22.2454051971436</t>
@@ -995,31 +995,31 @@
     <t xml:space="preserve">22.0015048980713</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3883800506592</t>
+    <t xml:space="preserve">22.3883857727051</t>
   </si>
   <si>
     <t xml:space="preserve">22.2538166046143</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5481796264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5313587188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7668495178223</t>
+    <t xml:space="preserve">22.5481815338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5313606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7668476104736</t>
   </si>
   <si>
     <t xml:space="preserve">23.0696220397949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5818214416504</t>
+    <t xml:space="preserve">22.5818176269531</t>
   </si>
   <si>
     <t xml:space="preserve">22.8425426483154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5650005340576</t>
+    <t xml:space="preserve">22.564998626709</t>
   </si>
   <si>
     <t xml:space="preserve">22.1444816589355</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">22.2117652893066</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1865348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.52294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7920799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4220237731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7500286102295</t>
+    <t xml:space="preserve">22.1865329742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5229511260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7920780181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4220218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7500267028809</t>
   </si>
   <si>
     <t xml:space="preserve">22.9266452789307</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">22.7079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7416191101074</t>
+    <t xml:space="preserve">22.7416172027588</t>
   </si>
   <si>
     <t xml:space="preserve">22.5902309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2369976043701</t>
+    <t xml:space="preserve">22.2369956970215</t>
   </si>
   <si>
     <t xml:space="preserve">21.8417091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1613006591797</t>
+    <t xml:space="preserve">22.1612987518311</t>
   </si>
   <si>
     <t xml:space="preserve">22.3547401428223</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">22.3042793273926</t>
   </si>
   <si>
-    <t xml:space="preserve">21.959451675415</t>
+    <t xml:space="preserve">21.9594535827637</t>
   </si>
   <si>
     <t xml:space="preserve">22.2285861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1108379364014</t>
+    <t xml:space="preserve">22.11083984375</t>
   </si>
   <si>
     <t xml:space="preserve">21.9174003601074</t>
@@ -1097,19 +1097,19 @@
     <t xml:space="preserve">22.8257217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4649105072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6331176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6751708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6835784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8097324371338</t>
+    <t xml:space="preserve">23.4649085998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6331157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6751689910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6835765838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8097343444824</t>
   </si>
   <si>
     <t xml:space="preserve">23.9106578826904</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">23.9190673828125</t>
   </si>
   <si>
-    <t xml:space="preserve">23.750862121582</t>
+    <t xml:space="preserve">23.7508602142334</t>
   </si>
   <si>
     <t xml:space="preserve">23.8770160675049</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">23.9779396057129</t>
   </si>
   <si>
-    <t xml:space="preserve">23.85178565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0368137359619</t>
+    <t xml:space="preserve">23.8517875671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0368118286133</t>
   </si>
   <si>
     <t xml:space="preserve">24.4741516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3311786651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3143577575684</t>
+    <t xml:space="preserve">24.3311767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3143558502197</t>
   </si>
   <si>
     <t xml:space="preserve">24.0536346435547</t>
@@ -1163,82 +1163,82 @@
     <t xml:space="preserve">23.9611206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0199966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1040954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5582580566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5077934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.356409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3984603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9199028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7937488555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6928215026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8946704864502</t>
+    <t xml:space="preserve">24.0199928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1040992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.558256149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5077953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3564071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.398458480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.919900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7937469482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6928234100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8946666717529</t>
   </si>
   <si>
     <t xml:space="preserve">25.2310829162598</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1217517852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1890335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8526210784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4489192962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5574226379395</t>
+    <t xml:space="preserve">25.1217498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1890316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8526191711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4489231109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5574245452881</t>
   </si>
   <si>
     <t xml:space="preserve">23.389217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5994777679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2125988006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9274826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6919918060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5406036376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5742454528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3808059692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4144458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5321922302246</t>
+    <t xml:space="preserve">23.5994720458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2125968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9274787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6919860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5406017303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5742435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3808078765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4144477844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.532190322876</t>
   </si>
   <si>
     <t xml:space="preserve">23.9695320129395</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">22.9014148712158</t>
   </si>
   <si>
-    <t xml:space="preserve">22.977108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0443916320801</t>
+    <t xml:space="preserve">22.9771099090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0443878173828</t>
   </si>
   <si>
     <t xml:space="preserve">23.0275688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0359802246094</t>
+    <t xml:space="preserve">23.0359783172607</t>
   </si>
   <si>
     <t xml:space="preserve">22.8930053710938</t>
@@ -1271,67 +1271,67 @@
     <t xml:space="preserve">22.6827449798584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1789569854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2546482086182</t>
+    <t xml:space="preserve">23.1789588928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2546501159668</t>
   </si>
   <si>
     <t xml:space="preserve">23.2210083007812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1621341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.229419708252</t>
+    <t xml:space="preserve">23.1621360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2294178009033</t>
   </si>
   <si>
     <t xml:space="preserve">23.0780334472656</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8677711486816</t>
+    <t xml:space="preserve">22.8677730560303</t>
   </si>
   <si>
     <t xml:space="preserve">23.0107498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1881999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.003173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1713809967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2218418121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3900508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4909744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8273906707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5246162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3395881652832</t>
+    <t xml:space="preserve">24.1881980895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0031700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1713790893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2218437194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3900489807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4909725189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8273868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5246143341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3395900726318</t>
   </si>
   <si>
     <t xml:space="preserve">24.3059463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8686046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8349666595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2882919311523</t>
+    <t xml:space="preserve">23.8686065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8349628448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2882881164551</t>
   </si>
   <si>
     <t xml:space="preserve">22.9602870941162</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">22.6070518493652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4564971923828</t>
+    <t xml:space="preserve">23.4564952850342</t>
   </si>
   <si>
     <t xml:space="preserve">22.7163867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4556636810303</t>
+    <t xml:space="preserve">22.4556674957275</t>
   </si>
   <si>
     <t xml:space="preserve">22.0687885284424</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">22.1781234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0940208435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9089889526367</t>
+    <t xml:space="preserve">22.0940189361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9089908599854</t>
   </si>
   <si>
     <t xml:space="preserve">21.7996578216553</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">21.6314487457275</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7912464141846</t>
+    <t xml:space="preserve">21.7912483215332</t>
   </si>
   <si>
     <t xml:space="preserve">22.363151550293</t>
@@ -1379,58 +1379,58 @@
     <t xml:space="preserve">22.2874603271484</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0856075286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6230411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3454971313477</t>
+    <t xml:space="preserve">22.0856094360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6230430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3454990386963</t>
   </si>
   <si>
     <t xml:space="preserve">21.4043712615967</t>
   </si>
   <si>
-    <t xml:space="preserve">21.446418762207</t>
+    <t xml:space="preserve">21.4464206695557</t>
   </si>
   <si>
     <t xml:space="preserve">21.2950325012207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.337085723877</t>
+    <t xml:space="preserve">21.3370876312256</t>
   </si>
   <si>
     <t xml:space="preserve">21.7407855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.790412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3194313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7988243103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4035396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5717430114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7735939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9249782562256</t>
+    <t xml:space="preserve">20.7904109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3194332122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7988204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4035358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5717468261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7735919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9249820709229</t>
   </si>
   <si>
     <t xml:space="preserve">20.8072338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0288715362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8919315338135</t>
+    <t xml:space="preserve">21.0288734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8919334411621</t>
   </si>
   <si>
     <t xml:space="preserve">20.6351661682129</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">20.746431350708</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8662528991699</t>
+    <t xml:space="preserve">20.8662548065186</t>
   </si>
   <si>
     <t xml:space="preserve">21.3883419036865</t>
@@ -1454,40 +1454,40 @@
     <t xml:space="preserve">21.362663269043</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5081634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8847484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7563648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2270965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9203567504883</t>
+    <t xml:space="preserve">21.5081615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8847503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7563667297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2270984649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9203586578369</t>
   </si>
   <si>
     <t xml:space="preserve">22.4153919219971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4239501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8077163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0987148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1072769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7392482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2428398132324</t>
+    <t xml:space="preserve">22.4239521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8077182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0987186431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1072731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7392501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2428436279297</t>
   </si>
   <si>
     <t xml:space="preserve">21.4568099975586</t>
@@ -1499,31 +1499,31 @@
     <t xml:space="preserve">20.9432849884033</t>
   </si>
   <si>
-    <t xml:space="preserve">20.130199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1216411590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3698444366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2685165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3968982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3369846343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3797798156738</t>
+    <t xml:space="preserve">20.1302032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1216449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3698482513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.268518447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3968963623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.336986541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3797779083252</t>
   </si>
   <si>
     <t xml:space="preserve">21.011754989624</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779613494873</t>
+    <t xml:space="preserve">20.6779651641846</t>
   </si>
   <si>
     <t xml:space="preserve">21.1743698120117</t>
@@ -1532,37 +1532,37 @@
     <t xml:space="preserve">20.8063449859619</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7977828979492</t>
+    <t xml:space="preserve">20.7977867126465</t>
   </si>
   <si>
     <t xml:space="preserve">21.9960136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5423984527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1914863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.909049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4554347991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6509094238281</t>
+    <t xml:space="preserve">21.5424003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1914882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9090461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4554328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6509132385254</t>
   </si>
   <si>
     <t xml:space="preserve">19.8563213348389</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8706912994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9306011199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2729511260986</t>
+    <t xml:space="preserve">17.8706893920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9305992126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.27294921875</t>
   </si>
   <si>
     <t xml:space="preserve">17.4427509307861</t>
@@ -1580,49 +1580,49 @@
     <t xml:space="preserve">18.245418548584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1657447814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1568927764893</t>
+    <t xml:space="preserve">18.1657428741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.156888961792</t>
   </si>
   <si>
     <t xml:space="preserve">18.811990737915</t>
   </si>
   <si>
-    <t xml:space="preserve">19.228063583374</t>
+    <t xml:space="preserve">19.2280673980713</t>
   </si>
   <si>
     <t xml:space="preserve">18.9978981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9359264373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2988891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1838054656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2103633880615</t>
+    <t xml:space="preserve">18.9359283447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2988872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1838035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2103614807129</t>
   </si>
   <si>
     <t xml:space="preserve">19.4139747619629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5202083587646</t>
+    <t xml:space="preserve">19.5202045440674</t>
   </si>
   <si>
     <t xml:space="preserve">19.5113544464111</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5644721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7238178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.635290145874</t>
+    <t xml:space="preserve">19.5644702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.723819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6352920532227</t>
   </si>
   <si>
     <t xml:space="preserve">19.4316806793213</t>
@@ -1634,34 +1634,34 @@
     <t xml:space="preserve">19.0687217712402</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2369213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6972579956055</t>
+    <t xml:space="preserve">19.2369194030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6972618103027</t>
   </si>
   <si>
     <t xml:space="preserve">19.7503757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8034915924072</t>
+    <t xml:space="preserve">19.8034954071045</t>
   </si>
   <si>
     <t xml:space="preserve">19.4405326843262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2900371551514</t>
+    <t xml:space="preserve">19.2900390625</t>
   </si>
   <si>
     <t xml:space="preserve">19.0333080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5109996795654</t>
+    <t xml:space="preserve">18.5109977722168</t>
   </si>
   <si>
     <t xml:space="preserve">18.3516502380371</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8208446502686</t>
+    <t xml:space="preserve">18.8208408355713</t>
   </si>
   <si>
     <t xml:space="preserve">18.7765789031982</t>
@@ -1673,10 +1673,10 @@
     <t xml:space="preserve">18.9182243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1129837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4847984313965</t>
+    <t xml:space="preserve">19.1129817962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4847965240479</t>
   </si>
   <si>
     <t xml:space="preserve">19.6707019805908</t>
@@ -1688,127 +1688,127 @@
     <t xml:space="preserve">19.201509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2192115783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0952739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6969089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1218357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2546253204346</t>
+    <t xml:space="preserve">19.219217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0952777862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.696907043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1218338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2546234130859</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906715393066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4136180877686</t>
+    <t xml:space="preserve">18.4136199951172</t>
   </si>
   <si>
     <t xml:space="preserve">18.67919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6880531311035</t>
+    <t xml:space="preserve">18.6880550384521</t>
   </si>
   <si>
     <t xml:space="preserve">19.1483936309814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9890460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0510158538818</t>
+    <t xml:space="preserve">18.9890441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0510139465332</t>
   </si>
   <si>
     <t xml:space="preserve">18.5995254516602</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3427982330322</t>
+    <t xml:space="preserve">18.3428001403809</t>
   </si>
   <si>
     <t xml:space="preserve">18.431324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3693561553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7585163116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6965522766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4840850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9001598358154</t>
+    <t xml:space="preserve">18.3693542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7585182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6965503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4840869903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9001617431641</t>
   </si>
   <si>
     <t xml:space="preserve">17.4176902770996</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325984954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6342277526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4527454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9392890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5719041824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346857070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4656677246094</t>
+    <t xml:space="preserve">17.0325965881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6342258453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4527435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9392871856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5719022750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346828460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4656705856323</t>
   </si>
   <si>
     <t xml:space="preserve">16.7316055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2712669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7666606903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2133693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.173529624939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6777801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2262916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7840118408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6290884017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9743452072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0717239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1912355422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7179718017578</t>
+    <t xml:space="preserve">16.2712631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.766658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2133674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1735305786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6777811050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2262907028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7840127944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6290903091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.071722984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1912326812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7179698944092</t>
   </si>
   <si>
     <t xml:space="preserve">16.2933979034424</t>
@@ -1817,46 +1817,46 @@
     <t xml:space="preserve">15.9171571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8596134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0986385345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1030616760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7755117416382</t>
+    <t xml:space="preserve">15.8596153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0986366271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1030654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7755146026611</t>
   </si>
   <si>
     <t xml:space="preserve">15.4169807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7887945175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4833745956421</t>
+    <t xml:space="preserve">15.7887897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4833755493164</t>
   </si>
   <si>
     <t xml:space="preserve">14.6910572052002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2882604598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2041597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9739904403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8766088485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0802211761475</t>
+    <t xml:space="preserve">14.2882595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.204158782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943138122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9739894866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8766098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0802221298218</t>
   </si>
   <si>
     <t xml:space="preserve">13.9916944503784</t>
@@ -1865,22 +1865,22 @@
     <t xml:space="preserve">13.7880830764771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6243085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1554689407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3148183822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0451669692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254770278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1112051010132</t>
+    <t xml:space="preserve">13.6243076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1554698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3148174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0451650619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1112060546875</t>
   </si>
   <si>
     <t xml:space="preserve">13.4959440231323</t>
@@ -1889,10 +1889,10 @@
     <t xml:space="preserve">13.367579460144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2524948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0669422149658</t>
+    <t xml:space="preserve">13.252495765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0669441223145</t>
   </si>
   <si>
     <t xml:space="preserve">14.7707319259644</t>
@@ -1907,55 +1907,55 @@
     <t xml:space="preserve">14.651219367981</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8946695327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0628709793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8813896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.828275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9345092773438</t>
+    <t xml:space="preserve">14.8946704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0628719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8813915252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8282737731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9345064163208</t>
   </si>
   <si>
     <t xml:space="preserve">15.4479646682739</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7131900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558246612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2886152267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6958408355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3155269622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4129104614258</t>
+    <t xml:space="preserve">14.7131910324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558237075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2886171340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6958389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3155307769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4129085540771</t>
   </si>
   <si>
     <t xml:space="preserve">16.1163425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0145378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8020753860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1340484619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2358531951904</t>
+    <t xml:space="preserve">16.0145359039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8020706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1340503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2358551025391</t>
   </si>
   <si>
     <t xml:space="preserve">16.4793033599854</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">16.3376617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2181491851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2889728546143</t>
+    <t xml:space="preserve">16.2181510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2889709472656</t>
   </si>
   <si>
     <t xml:space="preserve">16.5811080932617</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">16.7758693695068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4881534576416</t>
+    <t xml:space="preserve">16.4881572723389</t>
   </si>
   <si>
     <t xml:space="preserve">16.7935752868652</t>
@@ -1991,52 +1991,52 @@
     <t xml:space="preserve">16.6298007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9263668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9481382369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.930438041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9614219665527</t>
+    <t xml:space="preserve">16.9263648986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9481401443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9304370880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9614229202271</t>
   </si>
   <si>
     <t xml:space="preserve">16.5279941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5368480682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.67848777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5855369567871</t>
+    <t xml:space="preserve">16.5368461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6784896850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5855350494385</t>
   </si>
   <si>
     <t xml:space="preserve">16.7138996124268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1292676925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5763301849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8197784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0101108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8906011581421</t>
+    <t xml:space="preserve">15.1292667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5763282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8197774887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0101089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8905992507935</t>
   </si>
   <si>
     <t xml:space="preserve">15.8463344573975</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3992748260498</t>
+    <t xml:space="preserve">15.3992757797241</t>
   </si>
   <si>
     <t xml:space="preserve">15.293041229248</t>
@@ -2045,13 +2045,13 @@
     <t xml:space="preserve">14.9610662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9876232147217</t>
+    <t xml:space="preserve">14.9876260757446</t>
   </si>
   <si>
     <t xml:space="preserve">14.8858184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3767881393433</t>
+    <t xml:space="preserve">14.3767871856689</t>
   </si>
   <si>
     <t xml:space="preserve">14.4874458312988</t>
@@ -2060,40 +2060,40 @@
     <t xml:space="preserve">14.6069564819336</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5626955032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7795839309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4125528335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2222204208374</t>
+    <t xml:space="preserve">14.5626945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7795848846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4125518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2222194671631</t>
   </si>
   <si>
     <t xml:space="preserve">15.0540199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9212284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6423692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.930082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8592586517334</t>
+    <t xml:space="preserve">14.9212293624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6423683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300813674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8592596054077</t>
   </si>
   <si>
     <t xml:space="preserve">15.1868104934692</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9477882385254</t>
+    <t xml:space="preserve">15.0230331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9477863311768</t>
   </si>
   <si>
     <t xml:space="preserve">14.4476079940796</t>
@@ -2108,58 +2108,58 @@
     <t xml:space="preserve">13.6552925109863</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6420125961304</t>
+    <t xml:space="preserve">13.6420135498047</t>
   </si>
   <si>
     <t xml:space="preserve">14.1997346878052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4564628601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4431819915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6822061538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8459825515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2177963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0495929718018</t>
+    <t xml:space="preserve">14.4564619064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4431829452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6822032928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8459806442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2177934646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0495920181274</t>
   </si>
   <si>
     <t xml:space="preserve">15.2089424133301</t>
   </si>
   <si>
-    <t xml:space="preserve">15.031886100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1823816299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4962978363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1820287704468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2000894546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1381196975708</t>
+    <t xml:space="preserve">15.0318880081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1823825836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.496298789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1820268630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2000885009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1381216049194</t>
   </si>
   <si>
     <t xml:space="preserve">15.3151731491089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3063220977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6467952728271</t>
+    <t xml:space="preserve">15.3063230514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6467933654785</t>
   </si>
   <si>
     <t xml:space="preserve">14.3723621368408</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">13.8589029312134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7748031616211</t>
+    <t xml:space="preserve">13.7748041152954</t>
   </si>
   <si>
     <t xml:space="preserve">13.5977487564087</t>
@@ -2183,43 +2183,43 @@
     <t xml:space="preserve">13.6774225234985</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2170829772949</t>
+    <t xml:space="preserve">13.2170848846436</t>
   </si>
   <si>
     <t xml:space="preserve">13.5313539505005</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3502283096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3192434310913</t>
+    <t xml:space="preserve">14.350227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3192453384399</t>
   </si>
   <si>
     <t xml:space="preserve">14.2705554962158</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6999111175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353219985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9256553649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6600742340088</t>
+    <t xml:space="preserve">14.6999130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353229522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9256544113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6600723266602</t>
   </si>
   <si>
     <t xml:space="preserve">14.7486000061035</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9079484939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2266464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5807571411133</t>
+    <t xml:space="preserve">14.9079504013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2266454696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5807542800903</t>
   </si>
   <si>
     <t xml:space="preserve">15.9127311706543</t>
@@ -2228,40 +2228,40 @@
     <t xml:space="preserve">16.0942115783691</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8584651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9808702468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675327301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2302188873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4568958282471</t>
+    <t xml:space="preserve">15.8584642410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9808712005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675317764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2302207946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4568977355957</t>
   </si>
   <si>
     <t xml:space="preserve">16.5838394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5929050445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6609115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7243766784668</t>
+    <t xml:space="preserve">16.5929012298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.66090965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7243785858154</t>
   </si>
   <si>
     <t xml:space="preserve">16.7425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4115619659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6427745819092</t>
+    <t xml:space="preserve">16.4115600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6427764892578</t>
   </si>
   <si>
     <t xml:space="preserve">16.9827919006348</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">16.9419918060303</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0326633453369</t>
+    <t xml:space="preserve">17.0326614379883</t>
   </si>
   <si>
     <t xml:space="preserve">17.309211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4542846679688</t>
+    <t xml:space="preserve">17.4542865753174</t>
   </si>
   <si>
     <t xml:space="preserve">16.9646587371826</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">17.0462646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0436496734619</t>
+    <t xml:space="preserve">18.0436534881592</t>
   </si>
   <si>
     <t xml:space="preserve">18.0935192108154</t>
@@ -2297,34 +2297,34 @@
     <t xml:space="preserve">18.1116542816162</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7262992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.141471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.783317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9283924102783</t>
+    <t xml:space="preserve">17.7263011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1414699554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7833156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9283905029297</t>
   </si>
   <si>
     <t xml:space="preserve">17.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1505374908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9963932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8875865936279</t>
+    <t xml:space="preserve">17.1505355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.996395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8875885009766</t>
   </si>
   <si>
     <t xml:space="preserve">16.9601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3726806640625</t>
+    <t xml:space="preserve">17.3726787567139</t>
   </si>
   <si>
     <t xml:space="preserve">16.7787818908691</t>
@@ -2336,13 +2336,13 @@
     <t xml:space="preserve">16.7017097473145</t>
   </si>
   <si>
-    <t xml:space="preserve">16.030740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0715446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.647310256958</t>
+    <t xml:space="preserve">16.0307426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0715427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6473121643066</t>
   </si>
   <si>
     <t xml:space="preserve">16.8150501251221</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">17.0054607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9782581329346</t>
+    <t xml:space="preserve">16.9782638549805</t>
   </si>
   <si>
     <t xml:space="preserve">17.2774753570557</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">17.2276058197021</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0209846496582</t>
+    <t xml:space="preserve">18.0209827423096</t>
   </si>
   <si>
     <t xml:space="preserve">18.0481853485107</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">18.0073833465576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.206859588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7508907318115</t>
+    <t xml:space="preserve">18.2068614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7508926391602</t>
   </si>
   <si>
     <t xml:space="preserve">18.2975330352783</t>
@@ -2387,25 +2387,25 @@
     <t xml:space="preserve">18.3519344329834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2884635925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4244728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9775714874268</t>
+    <t xml:space="preserve">18.2884654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4244709014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9775695800781</t>
   </si>
   <si>
     <t xml:space="preserve">19.050106048584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0410385131836</t>
+    <t xml:space="preserve">19.041036605835</t>
   </si>
   <si>
     <t xml:space="preserve">18.3156661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7716388702393</t>
+    <t xml:space="preserve">17.7716369628906</t>
   </si>
   <si>
     <t xml:space="preserve">18.0617847442627</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">17.8804416656494</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0889873504639</t>
+    <t xml:space="preserve">18.0889892578125</t>
   </si>
   <si>
     <t xml:space="preserve">17.9756488800049</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">17.7217655181885</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8623085021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7126979827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0598678588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0508003234863</t>
+    <t xml:space="preserve">17.8623104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7127017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0598640441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0507984161377</t>
   </si>
   <si>
     <t xml:space="preserve">16.973726272583</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">17.2366752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7671031951904</t>
+    <t xml:space="preserve">17.7671012878418</t>
   </si>
   <si>
     <t xml:space="preserve">18.0753841400146</t>
@@ -2462,19 +2462,19 @@
     <t xml:space="preserve">18.5060768127441</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7236862182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7146224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2703285217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1887245178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5786113739014</t>
+    <t xml:space="preserve">18.7236881256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.71462059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2703323364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1887226104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.57861328125</t>
   </si>
   <si>
     <t xml:space="preserve">18.9594345092773</t>
@@ -2483,49 +2483,49 @@
     <t xml:space="preserve">18.7690238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7418212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7780933380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2223815917969</t>
+    <t xml:space="preserve">18.7418231964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7780895233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2223796844482</t>
   </si>
   <si>
     <t xml:space="preserve">19.7120094299316</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5216007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8117485046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4490623474121</t>
+    <t xml:space="preserve">19.521598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8117446899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4490604400635</t>
   </si>
   <si>
     <t xml:space="preserve">19.3130531311035</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7962245941162</t>
+    <t xml:space="preserve">18.7962265014648</t>
   </si>
   <si>
     <t xml:space="preserve">18.4970111846924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1732025146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4225521087646</t>
+    <t xml:space="preserve">17.1732044219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4225482940674</t>
   </si>
   <si>
     <t xml:space="preserve">17.8033714294434</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9121780395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0391178131104</t>
+    <t xml:space="preserve">17.9121742248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0391159057617</t>
   </si>
   <si>
     <t xml:space="preserve">17.9892482757568</t>
@@ -2534,13 +2534,13 @@
     <t xml:space="preserve">18.0663185119629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8596935272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9050331115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7599582672119</t>
+    <t xml:space="preserve">18.8596973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9050312042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7599563598633</t>
   </si>
   <si>
     <t xml:space="preserve">18.3791351318359</t>
@@ -2555,49 +2555,49 @@
     <t xml:space="preserve">19.0863742828369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1951789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5760021209717</t>
+    <t xml:space="preserve">19.195182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.576000213623</t>
   </si>
   <si>
     <t xml:space="preserve">19.6394710540771</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4218578338623</t>
+    <t xml:space="preserve">19.4218597412109</t>
   </si>
   <si>
     <t xml:space="preserve">19.7392120361328</t>
   </si>
   <si>
-    <t xml:space="preserve">19.94775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0021591186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8661518096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.485330581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6757392883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2133140563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1679782867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3221187591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0319728851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2949180603027</t>
+    <t xml:space="preserve">19.9477558135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0021572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.866153717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4853324890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6757411956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2133159637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1679801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3221225738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0319709777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2949199676514</t>
   </si>
   <si>
     <t xml:space="preserve">19.2677192687988</t>
@@ -2606,13 +2606,13 @@
     <t xml:space="preserve">19.5941371917725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.857084274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4127902984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9957065582275</t>
+    <t xml:space="preserve">19.8570823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4127941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9957027435303</t>
   </si>
   <si>
     <t xml:space="preserve">18.6602191925049</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">18.5332794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9322299957275</t>
+    <t xml:space="preserve">18.9322338104248</t>
   </si>
   <si>
     <t xml:space="preserve">19.4762630462646</t>
@@ -2630,22 +2630,22 @@
     <t xml:space="preserve">20.0474948883057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0112247467041</t>
+    <t xml:space="preserve">20.0112266540527</t>
   </si>
   <si>
     <t xml:space="preserve">19.9658908843994</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3376445770264</t>
+    <t xml:space="preserve">20.3376426696777</t>
   </si>
   <si>
     <t xml:space="preserve">20.9088726043701</t>
   </si>
   <si>
-    <t xml:space="preserve">21.325963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5526428222656</t>
+    <t xml:space="preserve">21.3259620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.552640914917</t>
   </si>
   <si>
     <t xml:space="preserve">22.0332012176514</t>
@@ -2654,40 +2654,40 @@
     <t xml:space="preserve">21.697717666626</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4049530029297</t>
+    <t xml:space="preserve">22.4049549102783</t>
   </si>
   <si>
     <t xml:space="preserve">21.8337249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9814109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.993091583252</t>
+    <t xml:space="preserve">20.9814128875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9930896759033</t>
   </si>
   <si>
     <t xml:space="preserve">20.192569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3039855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.385591506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4607391357422</t>
+    <t xml:space="preserve">19.3039894104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3855895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4607410430908</t>
   </si>
   <si>
     <t xml:space="preserve">18.6511497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">18.623950958252</t>
+    <t xml:space="preserve">18.6239490509033</t>
   </si>
   <si>
     <t xml:space="preserve">18.03005027771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8195838928223</t>
+    <t xml:space="preserve">16.8195819854736</t>
   </si>
   <si>
     <t xml:space="preserve">15.4685764312744</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">14.6842670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8112077713013</t>
+    <t xml:space="preserve">14.811206817627</t>
   </si>
   <si>
     <t xml:space="preserve">12.653223991394</t>
@@ -2705,25 +2705,25 @@
     <t xml:space="preserve">13.7412824630737</t>
   </si>
   <si>
-    <t xml:space="preserve">13.777551651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3170490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7341394424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1648263931274</t>
+    <t xml:space="preserve">13.7775526046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3170471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7341375350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1648283004761</t>
   </si>
   <si>
     <t xml:space="preserve">13.6914138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0903692245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690992355347</t>
+    <t xml:space="preserve">14.090368270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2691011428833</t>
   </si>
   <si>
     <t xml:space="preserve">15.0242862701416</t>
@@ -2732,91 +2732,91 @@
     <t xml:space="preserve">15.0061511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2354440689087</t>
+    <t xml:space="preserve">14.2354431152344</t>
   </si>
   <si>
     <t xml:space="preserve">13.8863573074341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.238055229187</t>
+    <t xml:space="preserve">13.2380561828613</t>
   </si>
   <si>
     <t xml:space="preserve">13.4783344268799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5327386856079</t>
+    <t xml:space="preserve">13.5327377319336</t>
   </si>
   <si>
     <t xml:space="preserve">12.9660415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4511346817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.809287071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1901082992554</t>
+    <t xml:space="preserve">13.4511337280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8092861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1901073455811</t>
   </si>
   <si>
     <t xml:space="preserve">14.2581119537354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3695297241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8727569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9634265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7820844650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.294379234314</t>
+    <t xml:space="preserve">13.3695306777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8727579116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9634284973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7820854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2943801879883</t>
   </si>
   <si>
     <t xml:space="preserve">14.448522567749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5346593856812</t>
+    <t xml:space="preserve">14.5346603393555</t>
   </si>
   <si>
     <t xml:space="preserve">15.1512250900269</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3643035888672</t>
+    <t xml:space="preserve">15.3643026351929</t>
   </si>
   <si>
     <t xml:space="preserve">15.6544542312622</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5683164596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3461685180664</t>
+    <t xml:space="preserve">15.5683155059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3461694717407</t>
   </si>
   <si>
     <t xml:space="preserve">16.6291732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7768630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7904624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4478321075439</t>
+    <t xml:space="preserve">15.7768602371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7904644012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4478302001953</t>
   </si>
   <si>
     <t xml:space="preserve">16.3752937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.109733581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0398101806641</t>
+    <t xml:space="preserve">17.1097354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0398082733154</t>
   </si>
   <si>
     <t xml:space="preserve">17.2446327209473</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">16.4030952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8813438415527</t>
+    <t xml:space="preserve">16.8813457489014</t>
   </si>
   <si>
     <t xml:space="preserve">16.7066020965576</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">17.6998920440674</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9896011352539</t>
+    <t xml:space="preserve">17.9896030426025</t>
   </si>
   <si>
     <t xml:space="preserve">17.4515705108643</t>
@@ -2849,55 +2849,55 @@
     <t xml:space="preserve">17.6079216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">17.355001449585</t>
+    <t xml:space="preserve">17.3549995422363</t>
   </si>
   <si>
     <t xml:space="preserve">17.6309127807617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9850025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8884334564209</t>
+    <t xml:space="preserve">17.9850044250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8884353637695</t>
   </si>
   <si>
     <t xml:space="preserve">18.6334018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7529640197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8081455230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.67018699646</t>
+    <t xml:space="preserve">18.752965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8081493377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6701889038086</t>
   </si>
   <si>
     <t xml:space="preserve">17.7090873718262</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6631031036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4745616912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3482894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885093688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5874156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9093132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8173446655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2220191955566</t>
+    <t xml:space="preserve">17.6631050109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4745635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3482913970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5874137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9093151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8173427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.222017288208</t>
   </si>
   <si>
     <t xml:space="preserve">18.7161750793457</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">18.7897529602051</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0104846954346</t>
+    <t xml:space="preserve">19.0104827880859</t>
   </si>
   <si>
     <t xml:space="preserve">19.0748634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5715103149414</t>
+    <t xml:space="preserve">19.5715084075928</t>
   </si>
   <si>
     <t xml:space="preserve">19.3507766723633</t>
@@ -2924,25 +2924,25 @@
     <t xml:space="preserve">19.9761829376221</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9577865600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6542835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278614044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9301986694336</t>
+    <t xml:space="preserve">19.9577903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6542873382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.930196762085</t>
   </si>
   <si>
     <t xml:space="preserve">19.4703407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0957450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2704906463623</t>
+    <t xml:space="preserve">20.0957469940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2704925537109</t>
   </si>
   <si>
     <t xml:space="preserve">20.3256740570068</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">20.9602756500244</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3281650543213</t>
+    <t xml:space="preserve">21.3281631469727</t>
   </si>
   <si>
     <t xml:space="preserve">21.0154609680176</t>
@@ -2963,31 +2963,31 @@
     <t xml:space="preserve">21.0430507659912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4912242889404</t>
+    <t xml:space="preserve">20.4912223815918</t>
   </si>
   <si>
     <t xml:space="preserve">20.2245063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2337036132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8934097290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8223190307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4176483154297</t>
+    <t xml:space="preserve">20.2337017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8934078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8223209381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4176464080811</t>
   </si>
   <si>
     <t xml:space="preserve">20.3808574676514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.206111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5556030273438</t>
+    <t xml:space="preserve">20.2061100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5556011199951</t>
   </si>
   <si>
     <t xml:space="preserve">20.8775024414062</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">21.0614452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7303504943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7579402923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7395458221436</t>
+    <t xml:space="preserve">20.7303485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7579383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7395439147949</t>
   </si>
   <si>
     <t xml:space="preserve">20.6291809082031</t>
@@ -3029,28 +3029,28 @@
     <t xml:space="preserve">21.5213012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0271472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6040782928467</t>
+    <t xml:space="preserve">22.0271453857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.604076385498</t>
   </si>
   <si>
     <t xml:space="preserve">21.8156108856201</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4109382629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7420330047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1191177368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5145931243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6341571807861</t>
+    <t xml:space="preserve">21.4109363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7420310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1191158294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5145950317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6341590881348</t>
   </si>
   <si>
     <t xml:space="preserve">22.5421867370605</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">22.3674392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4410171508789</t>
+    <t xml:space="preserve">22.4410152435303</t>
   </si>
   <si>
     <t xml:space="preserve">22.2294826507568</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">22.6709442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4870014190674</t>
+    <t xml:space="preserve">22.487003326416</t>
   </si>
   <si>
     <t xml:space="preserve">22.9008731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8732833862305</t>
+    <t xml:space="preserve">22.8732814788818</t>
   </si>
   <si>
     <t xml:space="preserve">22.8456916809082</t>
@@ -3089,16 +3089,16 @@
     <t xml:space="preserve">23.2411670684814</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6550388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5262794494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5722618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0045299530029</t>
+    <t xml:space="preserve">23.6550369262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5262775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5722637176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0045280456543</t>
   </si>
   <si>
     <t xml:space="preserve">23.7194194793701</t>
@@ -3107,25 +3107,25 @@
     <t xml:space="preserve">24.3356246948242</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3264293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.875768661499</t>
+    <t xml:space="preserve">24.3264312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8757667541504</t>
   </si>
   <si>
     <t xml:space="preserve">24.1700801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">23.599853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6525497436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7261257171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9560546875</t>
+    <t xml:space="preserve">23.5998573303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6525478363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7261276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9560565948486</t>
   </si>
   <si>
     <t xml:space="preserve">22.1926956176758</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">21.1994018554688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6500625610352</t>
+    <t xml:space="preserve">21.6500644683838</t>
   </si>
   <si>
     <t xml:space="preserve">21.4661197662354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0823268890381</t>
+    <t xml:space="preserve">22.0823287963867</t>
   </si>
   <si>
     <t xml:space="preserve">22.5881690979004</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">24.0413188934326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0112380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1216049194336</t>
+    <t xml:space="preserve">23.0112400054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.121603012085</t>
   </si>
   <si>
     <t xml:space="preserve">23.6274471282959</t>
@@ -3164,13 +3164,13 @@
     <t xml:space="preserve">24.2988376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9677410125732</t>
+    <t xml:space="preserve">23.9677391052246</t>
   </si>
   <si>
     <t xml:space="preserve">23.3607292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8665752410889</t>
+    <t xml:space="preserve">23.8665733337402</t>
   </si>
   <si>
     <t xml:space="preserve">23.9217567443848</t>
@@ -3191,13 +3191,13 @@
     <t xml:space="preserve">25.2277507781982</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8966541290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4092063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5471630096436</t>
+    <t xml:space="preserve">24.8966522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4092044830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5471611022949</t>
   </si>
   <si>
     <t xml:space="preserve">25.0622005462646</t>
@@ -3206,19 +3206,19 @@
     <t xml:space="preserve">24.5655536651611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6391334533691</t>
+    <t xml:space="preserve">24.6391315460205</t>
   </si>
   <si>
     <t xml:space="preserve">24.6023426055908</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8874530792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3105239868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5680446624756</t>
+    <t xml:space="preserve">24.8874549865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3105220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5680408477783</t>
   </si>
   <si>
     <t xml:space="preserve">25.0805950164795</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">25.503662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3749027252197</t>
+    <t xml:space="preserve">25.3749046325684</t>
   </si>
   <si>
     <t xml:space="preserve">25.7151947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9359283447266</t>
+    <t xml:space="preserve">25.9359302520752</t>
   </si>
   <si>
     <t xml:space="preserve">26.6257152557373</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">26.8740367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0119934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5546226501465</t>
+    <t xml:space="preserve">27.0119953155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5546245574951</t>
   </si>
   <si>
     <t xml:space="preserve">28.2811985015869</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">27.9225120544434</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0880584716797</t>
+    <t xml:space="preserve">28.0880603790283</t>
   </si>
   <si>
     <t xml:space="preserve">26.3957862854004</t>
@@ -3272,19 +3272,19 @@
     <t xml:space="preserve">26.5521373748779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8715476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1106758117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.843957901001</t>
+    <t xml:space="preserve">25.8715496063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1106739044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8439559936523</t>
   </si>
   <si>
     <t xml:space="preserve">26.0278987884521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7519855499268</t>
+    <t xml:space="preserve">25.7519874572754</t>
   </si>
   <si>
     <t xml:space="preserve">25.6876049041748</t>
@@ -3293,10 +3293,10 @@
     <t xml:space="preserve">24.7127094268799</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2804412841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1449737548828</t>
+    <t xml:space="preserve">24.2804431915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1449756622314</t>
   </si>
   <si>
     <t xml:space="preserve">24.5011749267578</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">25.0346088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">25.236946105957</t>
+    <t xml:space="preserve">25.2369480133057</t>
   </si>
   <si>
     <t xml:space="preserve">25.6968040466309</t>
@@ -3314,25 +3314,25 @@
     <t xml:space="preserve">26.046293258667</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9175357818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.28542137146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9267311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9083385467529</t>
+    <t xml:space="preserve">25.9175319671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2854194641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9267330169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9083366394043</t>
   </si>
   <si>
     <t xml:space="preserve">26.1198711395264</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0003089904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9635181427002</t>
+    <t xml:space="preserve">26.0003108978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9635200500488</t>
   </si>
   <si>
     <t xml:space="preserve">25.6600151062012</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">24.593147277832</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3908100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1608791351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.556360244751</t>
+    <t xml:space="preserve">24.390811920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1608810424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5563583374023</t>
   </si>
   <si>
     <t xml:space="preserve">24.5195693969727</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">25.0162162780762</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9150447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9058513641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0137252807617</t>
+    <t xml:space="preserve">24.9150466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9058494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0137271881104</t>
   </si>
   <si>
     <t xml:space="preserve">24.2712478637695</t>
@@ -3374,40 +3374,40 @@
     <t xml:space="preserve">25.2001552581787</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2620468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6734313964844</t>
+    <t xml:space="preserve">24.2620487213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.673433303833</t>
   </si>
   <si>
     <t xml:space="preserve">23.5446739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6918277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4251079559326</t>
+    <t xml:space="preserve">23.6918258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4251098632812</t>
   </si>
   <si>
     <t xml:space="preserve">23.3055477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5170822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7838020324707</t>
+    <t xml:space="preserve">23.5170803070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7837982177734</t>
   </si>
   <si>
     <t xml:space="preserve">24.1056976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1516857147217</t>
+    <t xml:space="preserve">24.151683807373</t>
   </si>
   <si>
     <t xml:space="preserve">24.5287666320801</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8138790130615</t>
+    <t xml:space="preserve">24.8138771057129</t>
   </si>
   <si>
     <t xml:space="preserve">24.8322734832764</t>
@@ -3416,25 +3416,25 @@
     <t xml:space="preserve">24.9886226654053</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4852695465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7703819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6416168212891</t>
+    <t xml:space="preserve">25.4852676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7703800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6416206359863</t>
   </si>
   <si>
     <t xml:space="preserve">24.8414688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6943168640137</t>
+    <t xml:space="preserve">24.694314956665</t>
   </si>
   <si>
     <t xml:space="preserve">25.1081867218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9518337249756</t>
+    <t xml:space="preserve">24.9518356323242</t>
   </si>
   <si>
     <t xml:space="preserve">25.33811378479</t>
@@ -3443,31 +3443,31 @@
     <t xml:space="preserve">24.4919757843018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5379619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4367942810059</t>
+    <t xml:space="preserve">24.5379638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4367923736572</t>
   </si>
   <si>
     <t xml:space="preserve">23.9861354827881</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9585456848145</t>
+    <t xml:space="preserve">23.9585437774658</t>
   </si>
   <si>
     <t xml:space="preserve">24.4000072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9493465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7954807281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2252616882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3197231292725</t>
+    <t xml:space="preserve">23.949348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7954845428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2252578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3197212219238</t>
   </si>
   <si>
     <t xml:space="preserve">26.4693622589111</t>
@@ -3476,16 +3476,16 @@
     <t xml:space="preserve">26.4325752258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2762203216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3323879241943</t>
+    <t xml:space="preserve">26.2762222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.332389831543</t>
   </si>
   <si>
     <t xml:space="preserve">26.5476913452148</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1826133728027</t>
+    <t xml:space="preserve">26.1826114654541</t>
   </si>
   <si>
     <t xml:space="preserve">26.1919746398926</t>
@@ -3497,10 +3497,10 @@
     <t xml:space="preserve">26.4259967803955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6693840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8753223419189</t>
+    <t xml:space="preserve">26.6693820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8753242492676</t>
   </si>
   <si>
     <t xml:space="preserve">27.3901786804199</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">27.8769454956055</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3340129852295</t>
+    <t xml:space="preserve">27.3340110778809</t>
   </si>
   <si>
     <t xml:space="preserve">27.2872066497803</t>
@@ -3527,19 +3527,19 @@
     <t xml:space="preserve">27.3808155059814</t>
   </si>
   <si>
-    <t xml:space="preserve">27.699089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1935958862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1655139923096</t>
+    <t xml:space="preserve">27.6990871429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1935977935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1655158996582</t>
   </si>
   <si>
     <t xml:space="preserve">27.9237518310547</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8395023345947</t>
+    <t xml:space="preserve">27.8395042419434</t>
   </si>
   <si>
     <t xml:space="preserve">27.802059173584</t>
@@ -3548,28 +3548,28 @@
     <t xml:space="preserve">28.401159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5602989196777</t>
+    <t xml:space="preserve">28.5602970123291</t>
   </si>
   <si>
     <t xml:space="preserve">28.3075504302979</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6819915771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2981910705566</t>
+    <t xml:space="preserve">28.6819896697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.298189163208</t>
   </si>
   <si>
     <t xml:space="preserve">28.3169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5041332244873</t>
+    <t xml:space="preserve">28.5041351318359</t>
   </si>
   <si>
     <t xml:space="preserve">28.382438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4479637145996</t>
+    <t xml:space="preserve">28.4479656219482</t>
   </si>
   <si>
     <t xml:space="preserve">28.7568759918213</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">27.9799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5696582794189</t>
+    <t xml:space="preserve">28.5696601867676</t>
   </si>
   <si>
     <t xml:space="preserve">28.8317642211914</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">28.691349029541</t>
   </si>
   <si>
-    <t xml:space="preserve">28.419885635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4760475158691</t>
+    <t xml:space="preserve">28.4198837280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4760494232178</t>
   </si>
   <si>
     <t xml:space="preserve">27.6710052490234</t>
@@ -3602,43 +3602,43 @@
     <t xml:space="preserve">28.1203327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8301410675049</t>
+    <t xml:space="preserve">27.8301429748535</t>
   </si>
   <si>
     <t xml:space="preserve">27.989278793335</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1671371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2701091766357</t>
+    <t xml:space="preserve">28.1671352386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2701072692871</t>
   </si>
   <si>
     <t xml:space="preserve">28.1390533447266</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2888298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4854125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3637161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7849597930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8785724639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0002613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3934230804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2359085083008</t>
+    <t xml:space="preserve">28.2888317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.485408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3637180328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7849617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8785705566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0002632141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3934211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2359104156494</t>
   </si>
   <si>
     <t xml:space="preserve">30.3201580047607</t>
@@ -3647,16 +3647,16 @@
     <t xml:space="preserve">30.179744720459</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8146686553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.992525100708</t>
+    <t xml:space="preserve">29.8146667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9925270080566</t>
   </si>
   <si>
     <t xml:space="preserve">29.9550819396973</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8989162445068</t>
+    <t xml:space="preserve">29.8989143371582</t>
   </si>
   <si>
     <t xml:space="preserve">29.5619220733643</t>
@@ -3671,19 +3671,19 @@
     <t xml:space="preserve">29.805305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5806427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8708343505859</t>
+    <t xml:space="preserve">29.5806407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8708324432373</t>
   </si>
   <si>
     <t xml:space="preserve">29.9082775115967</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8333911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2171878814697</t>
+    <t xml:space="preserve">29.8333892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2171859741211</t>
   </si>
   <si>
     <t xml:space="preserve">30.4044075012207</t>
@@ -3710,13 +3710,13 @@
     <t xml:space="preserve">30.4699325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">30.713321685791</t>
+    <t xml:space="preserve">30.7133178710938</t>
   </si>
   <si>
     <t xml:space="preserve">30.1142158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1891059875488</t>
+    <t xml:space="preserve">30.1891040802002</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461696624756</t>
@@ -3725,25 +3725,25 @@
     <t xml:space="preserve">29.3185348510742</t>
   </si>
   <si>
-    <t xml:space="preserve">30.029972076416</t>
+    <t xml:space="preserve">30.0299682617188</t>
   </si>
   <si>
     <t xml:space="preserve">30.348237991333</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6742515563965</t>
+    <t xml:space="preserve">29.6742534637451</t>
   </si>
   <si>
     <t xml:space="preserve">28.9534587860107</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8130435943604</t>
+    <t xml:space="preserve">28.813045501709</t>
   </si>
   <si>
     <t xml:space="preserve">28.2420253753662</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5212287902832</t>
+    <t xml:space="preserve">27.5212306976318</t>
   </si>
   <si>
     <t xml:space="preserve">27.4837875366211</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">27.5773963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">27.661642074585</t>
+    <t xml:space="preserve">27.6616439819336</t>
   </si>
   <si>
     <t xml:space="preserve">28.6445465087891</t>
@@ -3770,64 +3770,64 @@
     <t xml:space="preserve">29.2623691558838</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5244789123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7304172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1610221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4792976379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.591625213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.36696434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6384315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6103496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7694854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3030567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9286231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1626472473145</t>
+    <t xml:space="preserve">29.5244770050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7304191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1610240936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4792957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5916290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3669624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6384296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6103477478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7694835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3030586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9286212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1626453399658</t>
   </si>
   <si>
     <t xml:space="preserve">31.668140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8553581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4341144561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1813678741455</t>
+    <t xml:space="preserve">31.8553562164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4341163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1813716888428</t>
   </si>
   <si>
     <t xml:space="preserve">31.2749767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8179187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9302406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.810173034668</t>
+    <t xml:space="preserve">31.8179130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9302444458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8101692199707</t>
   </si>
   <si>
     <t xml:space="preserve">32.7633666992188</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">32.6416778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9489669799805</t>
+    <t xml:space="preserve">31.9489707946777</t>
   </si>
   <si>
     <t xml:space="preserve">31.6962203979492</t>
@@ -3845,37 +3845,37 @@
     <t xml:space="preserve">32.1081008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6945972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3124198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7320442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5822658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8911800384521</t>
+    <t xml:space="preserve">30.6945991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3124217987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7320423126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5822639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8911762237549</t>
   </si>
   <si>
     <t xml:space="preserve">31.752384185791</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9473438262939</t>
+    <t xml:space="preserve">30.9473457336426</t>
   </si>
   <si>
     <t xml:space="preserve">30.7039566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3576011657715</t>
+    <t xml:space="preserve">30.3576030731201</t>
   </si>
   <si>
     <t xml:space="preserve">30.0861339569092</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1516609191895</t>
+    <t xml:space="preserve">30.1516590118408</t>
   </si>
   <si>
     <t xml:space="preserve">29.5525588989258</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">30.7507629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9754276275635</t>
+    <t xml:space="preserve">30.9754257202148</t>
   </si>
   <si>
     <t xml:space="preserve">30.9379806518555</t>
@@ -3896,10 +3896,10 @@
     <t xml:space="preserve">31.069034576416</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9567050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9941482543945</t>
+    <t xml:space="preserve">30.9567031860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9941501617432</t>
   </si>
   <si>
     <t xml:space="preserve">30.9660682678223</t>
@@ -3908,25 +3908,25 @@
     <t xml:space="preserve">31.2936992645264</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2468948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2656154632568</t>
+    <t xml:space="preserve">31.2468929290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2656192779541</t>
   </si>
   <si>
     <t xml:space="preserve">31.602611541748</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7804718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3779468536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5073776245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9721794128418</t>
+    <t xml:space="preserve">31.7804679870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3779487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5073757171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9721813201904</t>
   </si>
   <si>
     <t xml:space="preserve">27.6335620880127</t>
@@ -3935,13 +3935,13 @@
     <t xml:space="preserve">27.0063800811768</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0454425811768</t>
+    <t xml:space="preserve">28.0454444885254</t>
   </si>
   <si>
     <t xml:space="preserve">26.8378810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2045822143555</t>
+    <t xml:space="preserve">28.2045803070068</t>
   </si>
   <si>
     <t xml:space="preserve">28.0548057556152</t>
@@ -3953,19 +3953,19 @@
     <t xml:space="preserve">25.9298667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0421962738037</t>
+    <t xml:space="preserve">26.042200088501</t>
   </si>
   <si>
     <t xml:space="preserve">26.8191566467285</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5664100646973</t>
+    <t xml:space="preserve">26.5664119720459</t>
   </si>
   <si>
     <t xml:space="preserve">26.248140335083</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7800922393799</t>
+    <t xml:space="preserve">25.7800941467285</t>
   </si>
   <si>
     <t xml:space="preserve">26.5102462768555</t>
@@ -3974,10 +3974,10 @@
     <t xml:space="preserve">27.3152904510498</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9970149993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1264476776123</t>
+    <t xml:space="preserve">26.9970169067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1264457702637</t>
   </si>
   <si>
     <t xml:space="preserve">26.229419708252</t>
@@ -3989,19 +3989,19 @@
     <t xml:space="preserve">27.5399532318115</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5415744781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4463405609131</t>
+    <t xml:space="preserve">28.541576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4463424682617</t>
   </si>
   <si>
     <t xml:space="preserve">25.9766712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">27.13743019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9502124786377</t>
+    <t xml:space="preserve">27.1374320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9502105712891</t>
   </si>
   <si>
     <t xml:space="preserve">28.728796005249</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">27.5961170196533</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8863105773926</t>
+    <t xml:space="preserve">27.8863086700439</t>
   </si>
   <si>
     <t xml:space="preserve">28.6258239746094</t>
@@ -4019,16 +4019,16 @@
     <t xml:space="preserve">28.7100734710693</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0377082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.121955871582</t>
+    <t xml:space="preserve">29.0377063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1219577789307</t>
   </si>
   <si>
     <t xml:space="preserve">29.1406764984131</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8598480224609</t>
+    <t xml:space="preserve">28.8598499298096</t>
   </si>
   <si>
     <t xml:space="preserve">28.6071033477783</t>
@@ -4043,10 +4043,10 @@
     <t xml:space="preserve">29.0096225738525</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2904529571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9815406799316</t>
+    <t xml:space="preserve">29.2904510498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.981538772583</t>
   </si>
   <si>
     <t xml:space="preserve">29.515115737915</t>
@@ -4058,22 +4058,22 @@
     <t xml:space="preserve">27.0531826019287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5586757659912</t>
+    <t xml:space="preserve">27.5586738586426</t>
   </si>
   <si>
     <t xml:space="preserve">28.8972930908203</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4666900634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4831771850586</t>
+    <t xml:space="preserve">28.4666881561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4831790924072</t>
   </si>
   <si>
     <t xml:space="preserve">29.32204246521</t>
   </si>
   <si>
-    <t xml:space="preserve">28.931209564209</t>
+    <t xml:space="preserve">28.9312076568604</t>
   </si>
   <si>
     <t xml:space="preserve">28.8549480438232</t>
@@ -4091,10 +4091,10 @@
     <t xml:space="preserve">29.7605361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6452312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0265350341797</t>
+    <t xml:space="preserve">28.6452331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0265331268311</t>
   </si>
   <si>
     <t xml:space="preserve">29.045597076416</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">26.7482604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0247058868408</t>
+    <t xml:space="preserve">27.0247020721436</t>
   </si>
   <si>
     <t xml:space="preserve">27.1104965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052722930908</t>
+    <t xml:space="preserve">26.6052742004395</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101306915283</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">26.9675102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">27.215353012085</t>
+    <t xml:space="preserve">27.2153549194336</t>
   </si>
   <si>
     <t xml:space="preserve">27.7682399749756</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">27.8635654449463</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7301082611084</t>
+    <t xml:space="preserve">27.730110168457</t>
   </si>
   <si>
     <t xml:space="preserve">28.2829971313477</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">27.9684238433838</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1304759979248</t>
+    <t xml:space="preserve">28.1304779052734</t>
   </si>
   <si>
     <t xml:space="preserve">28.4450492858887</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">26.1667785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5280990600586</t>
+    <t xml:space="preserve">25.52809715271</t>
   </si>
   <si>
     <t xml:space="preserve">25.0133419036865</t>
@@ -4226,22 +4226,22 @@
     <t xml:space="preserve">24.765495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3937282562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6987686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3374462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9189300537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1658592224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2993183135986</t>
+    <t xml:space="preserve">24.393726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.698766708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3374481201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9189319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1658611297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.29931640625</t>
   </si>
   <si>
     <t xml:space="preserve">25.2230548858643</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">24.9084815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">25.346981048584</t>
+    <t xml:space="preserve">25.3469791412354</t>
   </si>
   <si>
     <t xml:space="preserve">26.2144393920898</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">25.9093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4908847808838</t>
+    <t xml:space="preserve">26.4908828735352</t>
   </si>
   <si>
     <t xml:space="preserve">27.0532989501953</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">27.0437698364258</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6815338134766</t>
+    <t xml:space="preserve">26.6815319061279</t>
   </si>
   <si>
     <t xml:space="preserve">27.2630176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7882232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5031585693359</t>
+    <t xml:space="preserve">28.7882213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5031604766846</t>
   </si>
   <si>
     <t xml:space="preserve">29.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5508213043213</t>
+    <t xml:space="preserve">29.5508232116699</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461486816406</t>
@@ -4301,16 +4301,16 @@
     <t xml:space="preserve">29.9797859191895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8939933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0760269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.705171585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7995853424072</t>
+    <t xml:space="preserve">29.8939952850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0760250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7051696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7995834350586</t>
   </si>
   <si>
     <t xml:space="preserve">31.0283622741699</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">30.4468803405762</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9997673034668</t>
+    <t xml:space="preserve">30.9997653961182</t>
   </si>
   <si>
     <t xml:space="preserve">30.551736831665</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">30.0274486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2371616363525</t>
+    <t xml:space="preserve">30.2371635437012</t>
   </si>
   <si>
     <t xml:space="preserve">30.5993995666504</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">29.5317573547363</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1790542602539</t>
+    <t xml:space="preserve">29.1790561676025</t>
   </si>
   <si>
     <t xml:space="preserve">29.1885871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4554958343506</t>
+    <t xml:space="preserve">29.4554977416992</t>
   </si>
   <si>
     <t xml:space="preserve">30.3610877990723</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">31.0664920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5907802581787</t>
+    <t xml:space="preserve">31.590784072876</t>
   </si>
   <si>
     <t xml:space="preserve">30.5326709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3515529632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.389684677124</t>
+    <t xml:space="preserve">30.3515567779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3896827697754</t>
   </si>
   <si>
     <t xml:space="preserve">30.3038921356201</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">29.874927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2362480163574</t>
+    <t xml:space="preserve">29.2362499237061</t>
   </si>
   <si>
     <t xml:space="preserve">28.0160865783691</t>
@@ -4391,34 +4391,34 @@
     <t xml:space="preserve">28.6166362762451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6738319396973</t>
+    <t xml:space="preserve">28.6738300323486</t>
   </si>
   <si>
     <t xml:space="preserve">28.3020629882812</t>
   </si>
   <si>
-    <t xml:space="preserve">26.986572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2353363037109</t>
+    <t xml:space="preserve">26.9865741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2353343963623</t>
   </si>
   <si>
     <t xml:space="preserve">28.492712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0560455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5126914978027</t>
+    <t xml:space="preserve">30.0560474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5126895904541</t>
   </si>
   <si>
     <t xml:space="preserve">29.7128753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6842784881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2648487091064</t>
+    <t xml:space="preserve">29.6842765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2648468017578</t>
   </si>
   <si>
     <t xml:space="preserve">29.7033424377441</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">29.3983020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7700691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7510051727295</t>
+    <t xml:space="preserve">29.7700710296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7510032653809</t>
   </si>
   <si>
     <t xml:space="preserve">30.5422058105469</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">30.9616355895996</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4945411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6661243438721</t>
+    <t xml:space="preserve">30.4945430755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6661262512207</t>
   </si>
   <si>
     <t xml:space="preserve">30.8472461700439</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">31.1236896514893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9434833526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.981616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7242374420166</t>
+    <t xml:space="preserve">31.9434814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9816150665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7242336273193</t>
   </si>
   <si>
     <t xml:space="preserve">31.5717163085938</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">30.5231399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9521026611328</t>
+    <t xml:space="preserve">30.9521045684814</t>
   </si>
   <si>
     <t xml:space="preserve">30.5136051177979</t>
@@ -4487,13 +4487,13 @@
     <t xml:space="preserve">32.5535697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6289100646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8853759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3715324401855</t>
+    <t xml:space="preserve">31.6289119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8853778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3715343475342</t>
   </si>
   <si>
     <t xml:space="preserve">30.7709846496582</t>
@@ -4502,10 +4502,10 @@
     <t xml:space="preserve">31.0950889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0378971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.476390838623</t>
+    <t xml:space="preserve">31.037899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4763946533203</t>
   </si>
   <si>
     <t xml:space="preserve">32.1913299560547</t>
@@ -4514,19 +4514,19 @@
     <t xml:space="preserve">32.0769424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1055374145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1246070861816</t>
+    <t xml:space="preserve">32.105541229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1246032714844</t>
   </si>
   <si>
     <t xml:space="preserve">32.143669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8386287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9244251251221</t>
+    <t xml:space="preserve">31.8386325836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9244213104248</t>
   </si>
   <si>
     <t xml:space="preserve">32.1341361999512</t>
@@ -4538,16 +4538,16 @@
     <t xml:space="preserve">32.8300094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1064491271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.840461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5926170349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9167213439941</t>
+    <t xml:space="preserve">33.1064529418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8404579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5926132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9167175292969</t>
   </si>
   <si>
     <t xml:space="preserve">33.9357833862305</t>
@@ -4562,16 +4562,16 @@
     <t xml:space="preserve">33.6116752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4686889648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6021461486816</t>
+    <t xml:space="preserve">33.468692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6021423339844</t>
   </si>
   <si>
     <t xml:space="preserve">33.3161697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5544853210449</t>
+    <t xml:space="preserve">33.5544815063477</t>
   </si>
   <si>
     <t xml:space="preserve">33.6784057617188</t>
@@ -4595,25 +4595,25 @@
     <t xml:space="preserve">32.2866554260254</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9729995727539</t>
+    <t xml:space="preserve">32.9729957580566</t>
   </si>
   <si>
     <t xml:space="preserve">33.373363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9539337158203</t>
+    <t xml:space="preserve">32.953929901123</t>
   </si>
   <si>
     <t xml:space="preserve">33.3638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4114952087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5830764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0311126708984</t>
+    <t xml:space="preserve">33.411491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0311088562012</t>
   </si>
   <si>
     <t xml:space="preserve">34.7937126159668</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">35.0892181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5649299621582</t>
+    <t xml:space="preserve">34.5649261474609</t>
   </si>
   <si>
     <t xml:space="preserve">35.2512702941895</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">35.8804168701172</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5372467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5753746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7469635009766</t>
+    <t xml:space="preserve">35.5372428894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5753784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7469596862793</t>
   </si>
   <si>
     <t xml:space="preserve">35.3942604064941</t>
@@ -4649,7 +4649,7 @@
     <t xml:space="preserve">35.6516380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1091995239258</t>
+    <t xml:space="preserve">36.109203338623</t>
   </si>
   <si>
     <t xml:space="preserve">35.9852752685547</t>
@@ -4661,13 +4661,13 @@
     <t xml:space="preserve">35.2036094665527</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5944404602051</t>
+    <t xml:space="preserve">35.5944442749023</t>
   </si>
   <si>
     <t xml:space="preserve">34.9843635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5563125610352</t>
+    <t xml:space="preserve">35.5563087463379</t>
   </si>
   <si>
     <t xml:space="preserve">35.3370628356934</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">35.8327560424805</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1568603515625</t>
+    <t xml:space="preserve">36.1568641662598</t>
   </si>
   <si>
     <t xml:space="preserve">35.937614440918</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">34.1454963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8413696289062</t>
+    <t xml:space="preserve">34.8413734436035</t>
   </si>
   <si>
     <t xml:space="preserve">34.6697883605957</t>
@@ -4709,16 +4709,16 @@
     <t xml:space="preserve">34.6888542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1759300231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1282615661621</t>
+    <t xml:space="preserve">36.1759262084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1282653808594</t>
   </si>
   <si>
     <t xml:space="preserve">36.0615386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7097473144531</t>
+    <t xml:space="preserve">36.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">37.8631858825684</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">34.9748268127441</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6707000732422</t>
+    <t xml:space="preserve">35.6707038879395</t>
   </si>
   <si>
     <t xml:space="preserve">33.7546653747559</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">33.8881187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3552169799805</t>
+    <t xml:space="preserve">34.3552131652832</t>
   </si>
   <si>
     <t xml:space="preserve">35.1082878112793</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">36.3761100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5953559875488</t>
+    <t xml:space="preserve">36.5953598022461</t>
   </si>
   <si>
     <t xml:space="preserve">36.8908653259277</t>
@@ -4775,28 +4775,28 @@
     <t xml:space="preserve">34.946231842041</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3656578063965</t>
+    <t xml:space="preserve">35.3656616210938</t>
   </si>
   <si>
     <t xml:space="preserve">35.4037895202637</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5086517333984</t>
+    <t xml:space="preserve">35.5086479187012</t>
   </si>
   <si>
     <t xml:space="preserve">35.3847274780273</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9471473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9090118408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5286254882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4619026184082</t>
+    <t xml:space="preserve">35.9471435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9090156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5286293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4618988037109</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807846069336</t>
@@ -6462,6 +6462,9 @@
   </si>
   <si>
     <t xml:space="preserve">89.9599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.5</t>
   </si>
 </sst>
 </file>
@@ -71722,7 +71725,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912962963</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>730474</v>
@@ -71743,6 +71746,32 @@
         <v>2145</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6931712963</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>610136</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>90</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>90.3399963378906</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>2150</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="2151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2152" uniqueCount="2152">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6851577758789</t>
+    <t xml:space="preserve">15.6851558685303</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">15.8714008331299</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3207597732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.239785194397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.74582862854</t>
+    <t xml:space="preserve">15.3207607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2397871017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7458305358887</t>
   </si>
   <si>
     <t xml:space="preserve">14.964467048645</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2964649200439</t>
+    <t xml:space="preserve">15.2964658737183</t>
   </si>
   <si>
     <t xml:space="preserve">15.4989109039307</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">15.0616369247437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5028991699219</t>
+    <t xml:space="preserve">14.5029001235962</t>
   </si>
   <si>
     <t xml:space="preserve">14.5433893203735</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8510980606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870880126953</t>
+    <t xml:space="preserve">14.8510990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870899200439</t>
   </si>
   <si>
     <t xml:space="preserve">14.9401721954346</t>
@@ -86,67 +86,67 @@
     <t xml:space="preserve">15.409836769104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9239768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2802724838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1831026077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6243648529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936395645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8106088638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7296342849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8996829986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5190944671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.73362159729</t>
+    <t xml:space="preserve">14.923975944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2802715301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1831035614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6243667602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936405181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8106079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7296323776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8996810913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5190935134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7336225509644</t>
   </si>
   <si>
     <t xml:space="preserve">13.3449335098267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0980176925659</t>
+    <t xml:space="preserve">14.0980186462402</t>
   </si>
   <si>
     <t xml:space="preserve">13.3206405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">13.474494934082</t>
+    <t xml:space="preserve">13.4744939804077</t>
   </si>
   <si>
     <t xml:space="preserve">13.8955736160278</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7822065353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3328485488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2194795608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057264328003</t>
+    <t xml:space="preserve">13.782205581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3328475952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2194776535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057283401489</t>
   </si>
   <si>
     <t xml:space="preserve">14.8349018096924</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5514831542969</t>
+    <t xml:space="preserve">14.5514841079712</t>
   </si>
   <si>
     <t xml:space="preserve">14.3409452438354</t>
@@ -155,79 +155,79 @@
     <t xml:space="preserve">14.8672924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021242141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235927581787</t>
+    <t xml:space="preserve">15.1021251678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2235908508301</t>
   </si>
   <si>
     <t xml:space="preserve">15.4827156066895</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3774461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017391204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4665193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4908123016357</t>
+    <t xml:space="preserve">15.3774442672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.401741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4665212631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4908132553101</t>
   </si>
   <si>
     <t xml:space="preserve">15.5232028961182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5636901855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1426124572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742290496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8390111923218</t>
+    <t xml:space="preserve">15.5636911392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426115036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8390102386475</t>
   </si>
   <si>
     <t xml:space="preserve">15.5879812240601</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6365671157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9199876785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8309116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8795003890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8228168487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8956928253174</t>
+    <t xml:space="preserve">15.636570930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9199886322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8309135437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8794994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8228149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.895694732666</t>
   </si>
   <si>
     <t xml:space="preserve">16.2762813568115</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1224269866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8471097946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8875970840454</t>
+    <t xml:space="preserve">16.1224308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8471088409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8875999450684</t>
   </si>
   <si>
     <t xml:space="preserve">15.4422273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3855419158936</t>
+    <t xml:space="preserve">15.3855409622192</t>
   </si>
   <si>
     <t xml:space="preserve">16.3086738586426</t>
@@ -236,46 +236,46 @@
     <t xml:space="preserve">16.2276973724365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7135543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6568756103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.430139541626</t>
+    <t xml:space="preserve">16.7135581970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6568737030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4301376342773</t>
   </si>
   <si>
     <t xml:space="preserve">16.6120548248291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.918004989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0254936218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9758815765381</t>
+    <t xml:space="preserve">16.9180011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0254955291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9758834838867</t>
   </si>
   <si>
     <t xml:space="preserve">16.9924201965332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.628589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7774314880371</t>
+    <t xml:space="preserve">16.6285915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7774295806885</t>
   </si>
   <si>
     <t xml:space="preserve">16.98415184021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1081809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9345397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5541725158691</t>
+    <t xml:space="preserve">17.1081829071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9345417022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">16.595516204834</t>
@@ -284,37 +284,37 @@
     <t xml:space="preserve">16.7608909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7030124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8766555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4058609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7696895599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.009485244751</t>
+    <t xml:space="preserve">16.703010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8766574859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4058570861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696914672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0094833374023</t>
   </si>
   <si>
     <t xml:space="preserve">17.9681396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8606452941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7779560089111</t>
+    <t xml:space="preserve">17.8606472015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7779598236084</t>
   </si>
   <si>
     <t xml:space="preserve">17.8854503631592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6952705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1087093353271</t>
+    <t xml:space="preserve">17.6952724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1087074279785</t>
   </si>
   <si>
     <t xml:space="preserve">17.9598712921143</t>
@@ -323,73 +323,73 @@
     <t xml:space="preserve">18.2658195495605</t>
   </si>
   <si>
-    <t xml:space="preserve">18.174861907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2823600769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2988910675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4725360870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1831302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1335144042969</t>
+    <t xml:space="preserve">18.1748600006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.282356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2988929748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.472541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1831321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1335124969482</t>
   </si>
   <si>
     <t xml:space="preserve">18.0425586700439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8027648925781</t>
+    <t xml:space="preserve">17.8027610778809</t>
   </si>
   <si>
     <t xml:space="preserve">18.092170715332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9185276031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0012149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3149013519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9097309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6368637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8022403717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7366142272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5712394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3479785919189</t>
+    <t xml:space="preserve">17.918529510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0012168884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3149032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9097328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6368618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8022365570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7366123199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5712375640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3479766845703</t>
   </si>
   <si>
     <t xml:space="preserve">17.9102592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6694087982178</t>
+    <t xml:space="preserve">15.6694097518921</t>
   </si>
   <si>
     <t xml:space="preserve">14.8342580795288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1402044296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2559680938721</t>
+    <t xml:space="preserve">15.1402053833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2559690475464</t>
   </si>
   <si>
     <t xml:space="preserve">16.2399597167969</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">15.5867233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2311592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6115293502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2813014984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6533985137939</t>
+    <t xml:space="preserve">15.2311601638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6115283966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2813034057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4632167816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6533966064453</t>
   </si>
   <si>
     <t xml:space="preserve">16.6864738464355</t>
@@ -425,40 +425,40 @@
     <t xml:space="preserve">16.6782035827637</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7443542480469</t>
+    <t xml:space="preserve">16.7443561553955</t>
   </si>
   <si>
     <t xml:space="preserve">16.6699352264404</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8435802459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8187732696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9510765075684</t>
+    <t xml:space="preserve">16.8435840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.818775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9510746002197</t>
   </si>
   <si>
     <t xml:space="preserve">17.0999126434326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.116455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2983665466309</t>
+    <t xml:space="preserve">17.1164512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2983684539795</t>
   </si>
   <si>
     <t xml:space="preserve">17.2404842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0751113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3314418792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6208477020264</t>
+    <t xml:space="preserve">17.0751075744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3314437866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6208515167236</t>
   </si>
   <si>
     <t xml:space="preserve">18.1004409790039</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">17.5960445404053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0756359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7944946289062</t>
+    <t xml:space="preserve">18.0756320953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7944927215576</t>
   </si>
   <si>
     <t xml:space="preserve">17.8771858215332</t>
@@ -485,43 +485,43 @@
     <t xml:space="preserve">18.2492828369141</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0839023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2906246185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1665916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9929447174072</t>
+    <t xml:space="preserve">18.0839042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2906227111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1665935516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9929466247559</t>
   </si>
   <si>
     <t xml:space="preserve">17.8441066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7200736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.728343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8937225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0673675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3733139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9438629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4317226409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3573036193848</t>
+    <t xml:space="preserve">17.7200775146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7283458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8937206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0673637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3733100891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9438610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4317207336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3573017120361</t>
   </si>
   <si>
     <t xml:space="preserve">19.1009693145752</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">19.1340446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3490314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7624740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6549835205078</t>
+    <t xml:space="preserve">19.3490295410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7624759674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6549797058105</t>
   </si>
   <si>
     <t xml:space="preserve">19.7045917510986</t>
@@ -566,28 +566,28 @@
     <t xml:space="preserve">18.6461811065674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1175060272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1588516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0100135803223</t>
+    <t xml:space="preserve">19.1175079345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1588535308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.010009765625</t>
   </si>
   <si>
     <t xml:space="preserve">18.7536773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9025192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0844306945801</t>
+    <t xml:space="preserve">18.9025173187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0844287872314</t>
   </si>
   <si>
     <t xml:space="preserve">18.9934749603271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7950229644775</t>
+    <t xml:space="preserve">18.7950210571289</t>
   </si>
   <si>
     <t xml:space="preserve">18.7867546081543</t>
@@ -596,37 +596,37 @@
     <t xml:space="preserve">18.7454090118408</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3319664001465</t>
+    <t xml:space="preserve">18.3319683074951</t>
   </si>
   <si>
     <t xml:space="preserve">17.6291217803955</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8694400787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1505813598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3485069274902</t>
+    <t xml:space="preserve">18.8694438934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1505794525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3485088348389</t>
   </si>
   <si>
     <t xml:space="preserve">18.6627197265625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7288703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6875286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8942451477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4229259490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.480806350708</t>
+    <t xml:space="preserve">18.7288722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6875267028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8942489624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.422924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4808101654053</t>
   </si>
   <si>
     <t xml:space="preserve">18.2327423095703</t>
@@ -635,46 +635,46 @@
     <t xml:space="preserve">18.3237018585205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0590953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.670991897583</t>
+    <t xml:space="preserve">18.0590991973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6709899902344</t>
   </si>
   <si>
     <t xml:space="preserve">18.9355926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4399909973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8782386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6797866821289</t>
+    <t xml:space="preserve">19.4399890899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8782348632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6797847747803</t>
   </si>
   <si>
     <t xml:space="preserve">20.1676425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8451614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7790126800537</t>
+    <t xml:space="preserve">19.8451633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7790107727051</t>
   </si>
   <si>
     <t xml:space="preserve">20.1428375244141</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9113121032715</t>
+    <t xml:space="preserve">19.9113159179688</t>
   </si>
   <si>
     <t xml:space="preserve">20.1759166717529</t>
   </si>
   <si>
-    <t xml:space="preserve">20.002269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9278526306152</t>
+    <t xml:space="preserve">20.0022678375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9278507232666</t>
   </si>
   <si>
     <t xml:space="preserve">20.0105381011963</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">20.1014938354492</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1263008117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1097660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1924495697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6389713287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1345691680908</t>
+    <t xml:space="preserve">20.1263027191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1097621917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1924514770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6389675140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1345710754395</t>
   </si>
   <si>
     <t xml:space="preserve">20.2751407623291</t>
@@ -707,31 +707,31 @@
     <t xml:space="preserve">20.2172603607178</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3164863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2420635223389</t>
+    <t xml:space="preserve">20.3164844512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2420654296875</t>
   </si>
   <si>
     <t xml:space="preserve">20.3330230712891</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2255306243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6555061340332</t>
+    <t xml:space="preserve">20.2255249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6555042266846</t>
   </si>
   <si>
     <t xml:space="preserve">20.5066661834717</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3578319549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4818630218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0849590301514</t>
+    <t xml:space="preserve">20.3578281402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.481861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0849552154541</t>
   </si>
   <si>
     <t xml:space="preserve">20.3991718292236</t>
@@ -743,43 +743,43 @@
     <t xml:space="preserve">20.5397415161133</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6885776519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.894775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4074382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7133846282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9697208404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3495616912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.423978805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3082160949707</t>
+    <t xml:space="preserve">20.6885814666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8947772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4074401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7133865356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9697227478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3495597839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4239807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3082180023193</t>
   </si>
   <si>
     <t xml:space="preserve">20.754732131958</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9609260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8865051269531</t>
+    <t xml:space="preserve">19.9609222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8865089416504</t>
   </si>
   <si>
     <t xml:space="preserve">19.8286247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8534278869629</t>
+    <t xml:space="preserve">19.8534317016602</t>
   </si>
   <si>
     <t xml:space="preserve">20.1180324554443</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">19.5722923278809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2994174957275</t>
+    <t xml:space="preserve">19.2994194030762</t>
   </si>
   <si>
     <t xml:space="preserve">19.5144081115723</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5474815368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4234523773193</t>
+    <t xml:space="preserve">19.5474834442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.423454284668</t>
   </si>
   <si>
     <t xml:space="preserve">19.6136379241943</t>
@@ -806,40 +806,40 @@
     <t xml:space="preserve">19.564022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3821105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7376670837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3661003112793</t>
+    <t xml:space="preserve">19.3821086883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7376689910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3660984039307</t>
   </si>
   <si>
     <t xml:space="preserve">19.9361190795898</t>
   </si>
   <si>
-    <t xml:space="preserve">20.200719833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4901313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7381935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2922058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1516342163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.085485458374</t>
+    <t xml:space="preserve">20.2007179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4901294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7381954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2922019958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1516380310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0854835510254</t>
   </si>
   <si>
     <t xml:space="preserve">20.9366436004639</t>
   </si>
   <si>
-    <t xml:space="preserve">20.779541015625</t>
+    <t xml:space="preserve">20.7795391082764</t>
   </si>
   <si>
     <t xml:space="preserve">20.4570541381836</t>
@@ -848,10 +848,10 @@
     <t xml:space="preserve">20.7051200866699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1268272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0435562133789</t>
+    <t xml:space="preserve">21.1268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0435581207275</t>
   </si>
   <si>
     <t xml:space="preserve">22.1192512512207</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">21.8669395446777</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9846858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2958698272705</t>
+    <t xml:space="preserve">21.9846878051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2958679199219</t>
   </si>
   <si>
     <t xml:space="preserve">22.4724864959717</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2201766967773</t>
+    <t xml:space="preserve">22.2201747894287</t>
   </si>
   <si>
     <t xml:space="preserve">22.262228012085</t>
@@ -878,16 +878,16 @@
     <t xml:space="preserve">22.5397701263428</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5734081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.808069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6987323760986</t>
+    <t xml:space="preserve">22.5734100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8080673217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6987361907959</t>
   </si>
   <si>
     <t xml:space="preserve">21.0847778320312</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">20.9502086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6390285491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4203605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5549221038818</t>
+    <t xml:space="preserve">20.6390247344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4203586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5549240112305</t>
   </si>
   <si>
     <t xml:space="preserve">20.4540004730225</t>
@@ -920,49 +920,49 @@
     <t xml:space="preserve">20.8576965332031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1688823699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8324661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9586181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156452178955</t>
+    <t xml:space="preserve">21.1688785552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.832462310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9586200714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8156471252441</t>
   </si>
   <si>
     <t xml:space="preserve">21.5978088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2613964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1016006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6819133758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.614631652832</t>
+    <t xml:space="preserve">21.2613945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1015968322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6819114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6146259307861</t>
   </si>
   <si>
     <t xml:space="preserve">21.816478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.656681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8248920440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5473461151123</t>
+    <t xml:space="preserve">21.6566791534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8248901367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5473442077637</t>
   </si>
   <si>
     <t xml:space="preserve">21.5725803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0351505279541</t>
+    <t xml:space="preserve">22.0351486206055</t>
   </si>
   <si>
     <t xml:space="preserve">21.8585300445557</t>
@@ -971,40 +971,40 @@
     <t xml:space="preserve">21.9258117675781</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7828388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3210983276367</t>
+    <t xml:space="preserve">21.7828369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3211002349854</t>
   </si>
   <si>
     <t xml:space="preserve">21.4884738922119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3875522613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1949462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8501224517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2454051971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0015048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3883857727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538166046143</t>
+    <t xml:space="preserve">21.3875503540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1949443817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.850118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2454090118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0015068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3883819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538185119629</t>
   </si>
   <si>
     <t xml:space="preserve">22.5481815338135</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5313606262207</t>
+    <t xml:space="preserve">22.5313568115234</t>
   </si>
   <si>
     <t xml:space="preserve">22.7668476104736</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">23.0696220397949</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5818176269531</t>
+    <t xml:space="preserve">22.5818195343018</t>
   </si>
   <si>
     <t xml:space="preserve">22.8425426483154</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">22.1444816589355</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2117652893066</t>
+    <t xml:space="preserve">22.211763381958</t>
   </si>
   <si>
     <t xml:space="preserve">22.1865329742432</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5229511260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7920780181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4220218658447</t>
+    <t xml:space="preserve">22.5229473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7920761108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4220237731934</t>
   </si>
   <si>
     <t xml:space="preserve">22.7500267028809</t>
@@ -1046,16 +1046,16 @@
     <t xml:space="preserve">22.9266452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9350566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8593616485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7079772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416172027588</t>
+    <t xml:space="preserve">22.9350547790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8593635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7079753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416191101074</t>
   </si>
   <si>
     <t xml:space="preserve">22.5902309417725</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">21.8417091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1612987518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3547401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3042793273926</t>
+    <t xml:space="preserve">22.1613006591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3547420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3042774200439</t>
   </si>
   <si>
     <t xml:space="preserve">21.9594535827637</t>
@@ -1082,28 +1082,28 @@
     <t xml:space="preserve">22.2285861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.11083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9174003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3463306427002</t>
+    <t xml:space="preserve">22.1108417510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9174022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3463325500488</t>
   </si>
   <si>
     <t xml:space="preserve">22.4304351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8257217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4649085998535</t>
+    <t xml:space="preserve">22.825719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4649105072021</t>
   </si>
   <si>
     <t xml:space="preserve">23.6331157684326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6751689910889</t>
+    <t xml:space="preserve">23.6751670837402</t>
   </si>
   <si>
     <t xml:space="preserve">23.6835765838623</t>
@@ -1115,34 +1115,34 @@
     <t xml:space="preserve">23.9106578826904</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9190673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7508602142334</t>
+    <t xml:space="preserve">23.9190692901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.750862121582</t>
   </si>
   <si>
     <t xml:space="preserve">23.8770160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9863529205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8938388824463</t>
+    <t xml:space="preserve">23.9863510131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8938369750977</t>
   </si>
   <si>
     <t xml:space="preserve">23.9527072906494</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9779396057129</t>
+    <t xml:space="preserve">23.9779376983643</t>
   </si>
   <si>
     <t xml:space="preserve">23.8517875671387</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0368118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4741516113281</t>
+    <t xml:space="preserve">24.0368137359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4741535186768</t>
   </si>
   <si>
     <t xml:space="preserve">24.3311767578125</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">24.3143558502197</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0536346435547</t>
+    <t xml:space="preserve">24.0536365509033</t>
   </si>
   <si>
     <t xml:space="preserve">23.9358901977539</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">24.0199928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1040992736816</t>
+    <t xml:space="preserve">24.104097366333</t>
   </si>
   <si>
     <t xml:space="preserve">24.558256149292</t>
@@ -1178,46 +1178,46 @@
     <t xml:space="preserve">24.3564071655273</t>
   </si>
   <si>
-    <t xml:space="preserve">24.398458480835</t>
+    <t xml:space="preserve">24.3984622955322</t>
   </si>
   <si>
     <t xml:space="preserve">24.919900894165</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7937469482422</t>
+    <t xml:space="preserve">24.7937450408936</t>
   </si>
   <si>
     <t xml:space="preserve">24.6928234100342</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8946666717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2310829162598</t>
+    <t xml:space="preserve">24.8946685791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2310848236084</t>
   </si>
   <si>
     <t xml:space="preserve">25.1217498779297</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1890316009521</t>
+    <t xml:space="preserve">25.1890296936035</t>
   </si>
   <si>
     <t xml:space="preserve">24.8526191711426</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4489231109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5574245452881</t>
+    <t xml:space="preserve">24.4489212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5574226379395</t>
   </si>
   <si>
     <t xml:space="preserve">23.389217376709</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5994720458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2125968933105</t>
+    <t xml:space="preserve">23.5994739532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2125988006592</t>
   </si>
   <si>
     <t xml:space="preserve">23.9274787902832</t>
@@ -1226,43 +1226,43 @@
     <t xml:space="preserve">23.6919860839844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5406017303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5742435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3808078765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4144477844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.532190322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9695320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9939308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6911582946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014148712158</t>
+    <t xml:space="preserve">23.540599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5742416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3808059692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4144458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5321922302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9695301055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9939289093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6911563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014167785645</t>
   </si>
   <si>
     <t xml:space="preserve">22.9771099090576</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0443878173828</t>
+    <t xml:space="preserve">23.0443916320801</t>
   </si>
   <si>
     <t xml:space="preserve">23.0275688171387</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0359783172607</t>
+    <t xml:space="preserve">23.0359802246094</t>
   </si>
   <si>
     <t xml:space="preserve">22.8930053710938</t>
@@ -1271,22 +1271,22 @@
     <t xml:space="preserve">22.6827449798584</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1789588928223</t>
+    <t xml:space="preserve">23.1789569854736</t>
   </si>
   <si>
     <t xml:space="preserve">23.2546501159668</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2210083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1621360778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2294178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0780334472656</t>
+    <t xml:space="preserve">23.2210102081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1621379852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.229419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.078031539917</t>
   </si>
   <si>
     <t xml:space="preserve">22.8677730560303</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">23.0107498168945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1881980895996</t>
+    <t xml:space="preserve">24.1881999969482</t>
   </si>
   <si>
     <t xml:space="preserve">24.0031700134277</t>
@@ -1304,22 +1304,22 @@
     <t xml:space="preserve">24.1713790893555</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2218437194824</t>
+    <t xml:space="preserve">24.2218399047852</t>
   </si>
   <si>
     <t xml:space="preserve">24.3900489807129</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4909725189209</t>
+    <t xml:space="preserve">24.4909744262695</t>
   </si>
   <si>
     <t xml:space="preserve">24.8273868560791</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5246143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3395900726318</t>
+    <t xml:space="preserve">24.5246124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3395862579346</t>
   </si>
   <si>
     <t xml:space="preserve">24.3059463500977</t>
@@ -1331,22 +1331,22 @@
     <t xml:space="preserve">23.8349628448486</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2882881164551</t>
+    <t xml:space="preserve">23.2882919311523</t>
   </si>
   <si>
     <t xml:space="preserve">22.9602870941162</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6070518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4564952850342</t>
+    <t xml:space="preserve">22.6070556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4564990997314</t>
   </si>
   <si>
     <t xml:space="preserve">22.7163867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4556674957275</t>
+    <t xml:space="preserve">22.4556655883789</t>
   </si>
   <si>
     <t xml:space="preserve">22.0687885284424</t>
@@ -1358,10 +1358,10 @@
     <t xml:space="preserve">22.0940189361572</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9089908599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7996578216553</t>
+    <t xml:space="preserve">21.908992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7996559143066</t>
   </si>
   <si>
     <t xml:space="preserve">21.6314487457275</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">22.363151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3967933654785</t>
+    <t xml:space="preserve">22.3967952728271</t>
   </si>
   <si>
     <t xml:space="preserve">22.2874603271484</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">22.0856094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6230430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3454990386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4043712615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4464206695557</t>
+    <t xml:space="preserve">21.6230411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3454971313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.404369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4464225769043</t>
   </si>
   <si>
     <t xml:space="preserve">21.2950325012207</t>
@@ -1403,67 +1403,67 @@
     <t xml:space="preserve">21.7407855987549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7904109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3194332122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7988204956055</t>
+    <t xml:space="preserve">20.7904148101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3194351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7988262176514</t>
   </si>
   <si>
     <t xml:space="preserve">20.4035358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5717468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7735919952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9249820709229</t>
+    <t xml:space="preserve">20.5717430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7735939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9249801635742</t>
   </si>
   <si>
     <t xml:space="preserve">20.8072338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0288734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8919334411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6351661682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.618049621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.746431350708</t>
+    <t xml:space="preserve">21.0288715362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8919315338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6351699829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6180515289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7464332580566</t>
   </si>
   <si>
     <t xml:space="preserve">20.8662548065186</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3883419036865</t>
+    <t xml:space="preserve">21.3883399963379</t>
   </si>
   <si>
     <t xml:space="preserve">20.9604015350342</t>
   </si>
   <si>
-    <t xml:space="preserve">21.362663269043</t>
+    <t xml:space="preserve">21.3626613616943</t>
   </si>
   <si>
     <t xml:space="preserve">21.5081615447998</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8847503662109</t>
+    <t xml:space="preserve">21.8847465515137</t>
   </si>
   <si>
     <t xml:space="preserve">21.7563667297363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2270984649658</t>
+    <t xml:space="preserve">22.2271003723145</t>
   </si>
   <si>
     <t xml:space="preserve">22.9203586578369</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">22.4153919219971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4239521026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8077182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0987186431885</t>
+    <t xml:space="preserve">22.4239501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8077163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0987148284912</t>
   </si>
   <si>
     <t xml:space="preserve">22.1072731018066</t>
@@ -1499,76 +1499,76 @@
     <t xml:space="preserve">20.9432849884033</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1302032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1216449737549</t>
+    <t xml:space="preserve">20.1302013397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1216430664062</t>
   </si>
   <si>
     <t xml:space="preserve">20.3698482513428</t>
   </si>
   <si>
-    <t xml:space="preserve">21.268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3968963623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.336986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3797779083252</t>
+    <t xml:space="preserve">21.2685165405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3968982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3369846343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3797798156738</t>
   </si>
   <si>
     <t xml:space="preserve">21.011754989624</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779651641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1743698120117</t>
+    <t xml:space="preserve">20.6779613494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1743679046631</t>
   </si>
   <si>
     <t xml:space="preserve">20.8063449859619</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7977867126465</t>
+    <t xml:space="preserve">20.7977886199951</t>
   </si>
   <si>
     <t xml:space="preserve">21.9960136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5424003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1914882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9090461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4554328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6509132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8563213348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8706893920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9305992126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.27294921875</t>
+    <t xml:space="preserve">21.5423984527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1914901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9090480804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4554347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6509113311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8563232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8706874847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9306030273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2729511260986</t>
   </si>
   <si>
     <t xml:space="preserve">17.4427509307861</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2558345794678</t>
+    <t xml:space="preserve">18.2558307647705</t>
   </si>
   <si>
     <t xml:space="preserve">17.9355735778809</t>
@@ -1580,22 +1580,22 @@
     <t xml:space="preserve">18.245418548584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1657428741455</t>
+    <t xml:space="preserve">18.1657447814941</t>
   </si>
   <si>
     <t xml:space="preserve">18.156888961792</t>
   </si>
   <si>
-    <t xml:space="preserve">18.811990737915</t>
+    <t xml:space="preserve">18.8119926452637</t>
   </si>
   <si>
     <t xml:space="preserve">19.2280673980713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9978981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359283447266</t>
+    <t xml:space="preserve">18.997896194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359264373779</t>
   </si>
   <si>
     <t xml:space="preserve">19.2988872528076</t>
@@ -1604,10 +1604,10 @@
     <t xml:space="preserve">19.1838035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2103614807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4139747619629</t>
+    <t xml:space="preserve">19.2103633880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4139728546143</t>
   </si>
   <si>
     <t xml:space="preserve">19.5202045440674</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">19.5113544464111</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5644702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.723819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6352920532227</t>
+    <t xml:space="preserve">19.5644721984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7238178253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.635290145874</t>
   </si>
   <si>
     <t xml:space="preserve">19.4316806793213</t>
@@ -1634,25 +1634,25 @@
     <t xml:space="preserve">19.0687217712402</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2369194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6972618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7503757476807</t>
+    <t xml:space="preserve">19.2369174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6972599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7503776550293</t>
   </si>
   <si>
     <t xml:space="preserve">19.8034954071045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4405326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0333080291748</t>
+    <t xml:space="preserve">19.4405307769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2900371551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0333061218262</t>
   </si>
   <si>
     <t xml:space="preserve">18.5109977722168</t>
@@ -1661,25 +1661,25 @@
     <t xml:space="preserve">18.3516502380371</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8208408355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7765789031982</t>
+    <t xml:space="preserve">18.8208427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7765808105469</t>
   </si>
   <si>
     <t xml:space="preserve">18.7942848205566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9182243347168</t>
+    <t xml:space="preserve">18.9182281494141</t>
   </si>
   <si>
     <t xml:space="preserve">19.1129817962646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4847965240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6707019805908</t>
+    <t xml:space="preserve">19.4847927093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6707038879395</t>
   </si>
   <si>
     <t xml:space="preserve">19.5733242034912</t>
@@ -1688,37 +1688,37 @@
     <t xml:space="preserve">19.201509475708</t>
   </si>
   <si>
-    <t xml:space="preserve">19.219217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0952777862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.696907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1218338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2546234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5906715393066</t>
+    <t xml:space="preserve">19.2192153930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0952758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6969051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1218357086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2546272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5906734466553</t>
   </si>
   <si>
     <t xml:space="preserve">18.4136199951172</t>
   </si>
   <si>
-    <t xml:space="preserve">18.67919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6880550384521</t>
+    <t xml:space="preserve">18.6792030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6880512237549</t>
   </si>
   <si>
     <t xml:space="preserve">19.1483936309814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9890441894531</t>
+    <t xml:space="preserve">18.9890480041504</t>
   </si>
   <si>
     <t xml:space="preserve">19.0510139465332</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">18.5995254516602</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3428001403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.431324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3693542480469</t>
+    <t xml:space="preserve">18.3427982330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4313220977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3693561553955</t>
   </si>
   <si>
     <t xml:space="preserve">17.7585182189941</t>
@@ -1754,28 +1754,28 @@
     <t xml:space="preserve">17.0325965881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6342258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4527435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9392871856689</t>
+    <t xml:space="preserve">16.6342277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4527416229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9392862319946</t>
   </si>
   <si>
     <t xml:space="preserve">15.5719022750854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4346828460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4656705856323</t>
+    <t xml:space="preserve">15.434684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4656686782837</t>
   </si>
   <si>
     <t xml:space="preserve">16.7316055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2712631225586</t>
+    <t xml:space="preserve">16.2712650299072</t>
   </si>
   <si>
     <t xml:space="preserve">15.766658782959</t>
@@ -1787,67 +1787,67 @@
     <t xml:space="preserve">15.1735305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6777811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2262907028198</t>
+    <t xml:space="preserve">14.6777772903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2262897491455</t>
   </si>
   <si>
     <t xml:space="preserve">14.7840127944946</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6290903091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9743461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.071722984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1912326812744</t>
+    <t xml:space="preserve">14.6290893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743452072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0717248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1912355422974</t>
   </si>
   <si>
     <t xml:space="preserve">15.7179698944092</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2933979034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171571731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8596153259277</t>
+    <t xml:space="preserve">16.293399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8596172332764</t>
   </si>
   <si>
     <t xml:space="preserve">16.0986366271973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1030654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7755146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4169807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7887897491455</t>
+    <t xml:space="preserve">16.103063583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7755126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4169816970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7887926101685</t>
   </si>
   <si>
     <t xml:space="preserve">15.4833755493164</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6910572052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2882595062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.204158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943138122559</t>
+    <t xml:space="preserve">14.6910581588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2882604598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2041597366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943147659302</t>
   </si>
   <si>
     <t xml:space="preserve">13.9739894866943</t>
@@ -1856,100 +1856,100 @@
     <t xml:space="preserve">13.8766098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0802221298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9916944503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7880830764771</t>
+    <t xml:space="preserve">14.0802211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9916954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7880821228027</t>
   </si>
   <si>
     <t xml:space="preserve">13.6243076324463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1554698944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3148174285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0451650619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4254760742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1112060546875</t>
+    <t xml:space="preserve">14.1554708480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3148183822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0451669692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4254770278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1112070083618</t>
   </si>
   <si>
     <t xml:space="preserve">13.4959440231323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.367579460144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.252495765686</t>
+    <t xml:space="preserve">13.3675804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2524948120117</t>
   </si>
   <si>
     <t xml:space="preserve">14.0669441223145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7707319259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8415536880493</t>
+    <t xml:space="preserve">14.7707328796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.841552734375</t>
   </si>
   <si>
     <t xml:space="preserve">14.6954851150513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.651219367981</t>
+    <t xml:space="preserve">14.6512203216553</t>
   </si>
   <si>
     <t xml:space="preserve">14.8946704864502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0628719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8813915252686</t>
+    <t xml:space="preserve">15.0628709793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8813905715942</t>
   </si>
   <si>
     <t xml:space="preserve">14.8282737731934</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9345064163208</t>
+    <t xml:space="preserve">14.9345083236694</t>
   </si>
   <si>
     <t xml:space="preserve">15.4479646682739</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7131910324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558237075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2886171340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6958389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3155307769775</t>
+    <t xml:space="preserve">14.713189125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2886142730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6958379745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3155269622803</t>
   </si>
   <si>
     <t xml:space="preserve">16.4129085540771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1163425445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0145359039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8020706176758</t>
+    <t xml:space="preserve">16.116340637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.014533996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8020715713501</t>
   </si>
   <si>
     <t xml:space="preserve">16.1340503692627</t>
@@ -1961,157 +1961,157 @@
     <t xml:space="preserve">16.4793033599854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4748783111572</t>
+    <t xml:space="preserve">16.4748802185059</t>
   </si>
   <si>
     <t xml:space="preserve">16.3376617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2181510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2889709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5811080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5412731170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7758693695068</t>
+    <t xml:space="preserve">16.2181491851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2889747619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5811100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5412750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7758712768555</t>
   </si>
   <si>
     <t xml:space="preserve">16.4881572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7935752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6298007965088</t>
+    <t xml:space="preserve">16.7935733795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6297988891602</t>
   </si>
   <si>
     <t xml:space="preserve">16.9263648986816</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9481401443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9304370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9614229202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5279941558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5368461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6784896850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5855350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7138996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1292667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5763282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8197774887085</t>
+    <t xml:space="preserve">15.9481420516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9304389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9614238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5279922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5368499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6784915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5855369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7139015197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1292676925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5763254165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8197803497314</t>
   </si>
   <si>
     <t xml:space="preserve">16.0101089477539</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8905992507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8463344573975</t>
+    <t xml:space="preserve">15.8906011581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8463354110718</t>
   </si>
   <si>
     <t xml:space="preserve">15.3992757797241</t>
   </si>
   <si>
-    <t xml:space="preserve">15.293041229248</t>
+    <t xml:space="preserve">15.2930402755737</t>
   </si>
   <si>
     <t xml:space="preserve">14.9610662460327</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9876260757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8858184814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3767871856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4874458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6069564819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5626945495605</t>
+    <t xml:space="preserve">14.9876251220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8858194351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3767862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4874467849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6069574356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5626964569092</t>
   </si>
   <si>
     <t xml:space="preserve">14.7795848846436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4125518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2222194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0540199279785</t>
+    <t xml:space="preserve">15.4125528335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2222185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0540189743042</t>
   </si>
   <si>
     <t xml:space="preserve">14.9212293624878</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6423683166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300813674927</t>
+    <t xml:space="preserve">14.6423673629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9300804138184</t>
   </si>
   <si>
     <t xml:space="preserve">14.8592596054077</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1868104934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0230331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9477863311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476079940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2436408996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5534868240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6552925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6420135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1997346878052</t>
+    <t xml:space="preserve">15.1868114471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0230340957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9477872848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2436418533325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5534858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.655291557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.642014503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1997337341309</t>
   </si>
   <si>
     <t xml:space="preserve">14.4564619064331</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">14.4431829452515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6822032928467</t>
+    <t xml:space="preserve">14.682204246521</t>
   </si>
   <si>
     <t xml:space="preserve">14.8459806442261</t>
@@ -2129,43 +2129,43 @@
     <t xml:space="preserve">15.2177934646606</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0495920181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2089424133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0318880081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1823825836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.496298789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1820268630981</t>
+    <t xml:space="preserve">15.0495910644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2089433670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.031886100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1823835372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4962978363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1820287704468</t>
   </si>
   <si>
     <t xml:space="preserve">15.2000885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1381216049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3151731491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3063230514526</t>
+    <t xml:space="preserve">15.1381196975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3151741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.306321144104</t>
   </si>
   <si>
     <t xml:space="preserve">14.6467933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3723621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8589029312134</t>
+    <t xml:space="preserve">14.3723611831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589038848877</t>
   </si>
   <si>
     <t xml:space="preserve">13.7748041152954</t>
@@ -2174,94 +2174,94 @@
     <t xml:space="preserve">13.5977487564087</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7792291641235</t>
+    <t xml:space="preserve">13.7792301177979</t>
   </si>
   <si>
     <t xml:space="preserve">13.5888967514038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6774225234985</t>
+    <t xml:space="preserve">13.6774244308472</t>
   </si>
   <si>
     <t xml:space="preserve">13.2170848846436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5313539505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.350227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3192453384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2705554962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6999130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353229522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9256544113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6600723266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7486000061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9079504013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2266454696655</t>
+    <t xml:space="preserve">13.5313549041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3502283096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3192443847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2705535888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6999101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353239059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9256553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6600732803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7486009597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9079513549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2266464233398</t>
   </si>
   <si>
     <t xml:space="preserve">15.5807542800903</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9127311706543</t>
+    <t xml:space="preserve">15.9127292633057</t>
   </si>
   <si>
     <t xml:space="preserve">16.0942115783691</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8584642410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9808712005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8675317764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2302207946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4568977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5838394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5929012298584</t>
+    <t xml:space="preserve">15.8584671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9808721542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8675327301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2302188873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4568996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5838375091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5929069519043</t>
   </si>
   <si>
     <t xml:space="preserve">16.66090965271</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7243785858154</t>
+    <t xml:space="preserve">16.7243766784668</t>
   </si>
   <si>
     <t xml:space="preserve">16.7425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4115600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6427764892578</t>
+    <t xml:space="preserve">16.4115619659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6427745819092</t>
   </si>
   <si>
     <t xml:space="preserve">16.9827919006348</t>
@@ -2288,46 +2288,46 @@
     <t xml:space="preserve">17.0462646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0436534881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0935192108154</t>
+    <t xml:space="preserve">18.0436515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0935211181641</t>
   </si>
   <si>
     <t xml:space="preserve">18.1116542816162</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7263011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1414699554443</t>
+    <t xml:space="preserve">17.7262992858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1414661407471</t>
   </si>
   <si>
     <t xml:space="preserve">16.7833156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9283905029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5268230438232</t>
+    <t xml:space="preserve">16.9283885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5268249511719</t>
   </si>
   <si>
     <t xml:space="preserve">17.1505355834961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.996395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8875885009766</t>
+    <t xml:space="preserve">16.9963932037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8875904083252</t>
   </si>
   <si>
     <t xml:space="preserve">16.9601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3726787567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7787818908691</t>
+    <t xml:space="preserve">17.3726806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7787799835205</t>
   </si>
   <si>
     <t xml:space="preserve">16.7923831939697</t>
@@ -2336,37 +2336,37 @@
     <t xml:space="preserve">16.7017097473145</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0307426452637</t>
+    <t xml:space="preserve">16.0307388305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.0715427398682</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6473121643066</t>
+    <t xml:space="preserve">16.6473083496094</t>
   </si>
   <si>
     <t xml:space="preserve">16.8150501251221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5948257446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3862819671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0054607391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9782638549805</t>
+    <t xml:space="preserve">17.5948276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3862838745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0054626464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9782600402832</t>
   </si>
   <si>
     <t xml:space="preserve">17.2774753570557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2276058197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0209827423096</t>
+    <t xml:space="preserve">17.2276077270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0209808349609</t>
   </si>
   <si>
     <t xml:space="preserve">18.0481853485107</t>
@@ -2378,31 +2378,31 @@
     <t xml:space="preserve">18.2068614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7508926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2975330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3519344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2884654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4244709014893</t>
+    <t xml:space="preserve">18.7508907318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2975311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3519325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2884635925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4244728088379</t>
   </si>
   <si>
     <t xml:space="preserve">18.9775695800781</t>
   </si>
   <si>
-    <t xml:space="preserve">19.050106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.041036605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3156661987305</t>
+    <t xml:space="preserve">19.0501079559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0410385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3156642913818</t>
   </si>
   <si>
     <t xml:space="preserve">17.7716369628906</t>
@@ -2417,19 +2417,19 @@
     <t xml:space="preserve">18.0889892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9756488800049</t>
+    <t xml:space="preserve">17.9756469726562</t>
   </si>
   <si>
     <t xml:space="preserve">17.7353668212891</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7217655181885</t>
+    <t xml:space="preserve">17.7217693328857</t>
   </si>
   <si>
     <t xml:space="preserve">17.8623104095459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7127017974854</t>
+    <t xml:space="preserve">17.7126998901367</t>
   </si>
   <si>
     <t xml:space="preserve">17.0598640441895</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">17.0961322784424</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8921203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2366752624512</t>
+    <t xml:space="preserve">16.8921184539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2366733551025</t>
   </si>
   <si>
     <t xml:space="preserve">17.7671012878418</t>
@@ -2459,19 +2459,19 @@
     <t xml:space="preserve">18.4698085784912</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5060768127441</t>
+    <t xml:space="preserve">18.5060749053955</t>
   </si>
   <si>
     <t xml:space="preserve">18.7236881256104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.71462059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2703323364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1887226104736</t>
+    <t xml:space="preserve">18.7146224975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2703304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1887245178223</t>
   </si>
   <si>
     <t xml:space="preserve">18.57861328125</t>
@@ -2483,49 +2483,49 @@
     <t xml:space="preserve">18.7690238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7418231964111</t>
+    <t xml:space="preserve">18.7418212890625</t>
   </si>
   <si>
     <t xml:space="preserve">18.7780895233154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2223796844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7120094299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.521598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8117446899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4490604400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3130531311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7962265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4970111846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1732044219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4225482940674</t>
+    <t xml:space="preserve">19.2223815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.712007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5215969085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8117485046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4490642547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3130550384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7962245941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4970092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1732025146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4225521087646</t>
   </si>
   <si>
     <t xml:space="preserve">17.8033714294434</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9121742248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0391159057617</t>
+    <t xml:space="preserve">17.9121780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0391178131104</t>
   </si>
   <si>
     <t xml:space="preserve">17.9892482757568</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">18.0663185119629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8596973419189</t>
+    <t xml:space="preserve">18.8596954345703</t>
   </si>
   <si>
     <t xml:space="preserve">18.9050312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7599563598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3791351318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4399948120117</t>
+    <t xml:space="preserve">18.7599601745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3791370391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4399929046631</t>
   </si>
   <si>
     <t xml:space="preserve">18.9685020446777</t>
@@ -2558,46 +2558,46 @@
     <t xml:space="preserve">19.195182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">19.576000213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6394710540771</t>
+    <t xml:space="preserve">19.5760021209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6394729614258</t>
   </si>
   <si>
     <t xml:space="preserve">19.4218597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7392120361328</t>
+    <t xml:space="preserve">19.7392101287842</t>
   </si>
   <si>
     <t xml:space="preserve">19.9477558135986</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0021572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.866153717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4853324890137</t>
+    <t xml:space="preserve">20.0021591186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8661499023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4853286743164</t>
   </si>
   <si>
     <t xml:space="preserve">19.6757411956787</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2133159637451</t>
+    <t xml:space="preserve">19.2133140563965</t>
   </si>
   <si>
     <t xml:space="preserve">19.1679801940918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3221225738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0319709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2949199676514</t>
+    <t xml:space="preserve">19.3221206665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0319690704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2949180603027</t>
   </si>
   <si>
     <t xml:space="preserve">19.2677192687988</t>
@@ -2609,16 +2609,16 @@
     <t xml:space="preserve">19.8570823669434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4127941131592</t>
+    <t xml:space="preserve">19.4127922058105</t>
   </si>
   <si>
     <t xml:space="preserve">18.9957027435303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6602191925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5332794189453</t>
+    <t xml:space="preserve">18.6602153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.533275604248</t>
   </si>
   <si>
     <t xml:space="preserve">18.9322338104248</t>
@@ -2633,25 +2633,25 @@
     <t xml:space="preserve">20.0112266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9658908843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3376426696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9088726043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3259620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.552640914917</t>
+    <t xml:space="preserve">19.9658889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3376445770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9088745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.325963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5526428222656</t>
   </si>
   <si>
     <t xml:space="preserve">22.0332012176514</t>
   </si>
   <si>
-    <t xml:space="preserve">21.697717666626</t>
+    <t xml:space="preserve">21.6977157592773</t>
   </si>
   <si>
     <t xml:space="preserve">22.4049549102783</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">21.8337249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9814128875732</t>
+    <t xml:space="preserve">20.9814109802246</t>
   </si>
   <si>
     <t xml:space="preserve">19.9930896759033</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">19.3039894104004</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3855895996094</t>
+    <t xml:space="preserve">19.3855934143066</t>
   </si>
   <si>
     <t xml:space="preserve">18.4607410430908</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">18.6511497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6239490509033</t>
+    <t xml:space="preserve">18.623950958252</t>
   </si>
   <si>
     <t xml:space="preserve">18.03005027771</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">16.8195819854736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4685764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6842670440674</t>
+    <t xml:space="preserve">15.4685754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6842679977417</t>
   </si>
   <si>
     <t xml:space="preserve">14.811206817627</t>
@@ -2702,22 +2702,22 @@
     <t xml:space="preserve">12.653223991394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7412824630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7775526046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3170471191406</t>
+    <t xml:space="preserve">13.741283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.777551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3170480728149</t>
   </si>
   <si>
     <t xml:space="preserve">14.7341375350952</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1648283004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6914138793945</t>
+    <t xml:space="preserve">15.1648292541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6914148330688</t>
   </si>
   <si>
     <t xml:space="preserve">14.090368270874</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">14.2354431152344</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8863573074341</t>
+    <t xml:space="preserve">13.8863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">13.2380561828613</t>
@@ -2744,16 +2744,16 @@
     <t xml:space="preserve">13.4783344268799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5327377319336</t>
+    <t xml:space="preserve">13.5327386856079</t>
   </si>
   <si>
     <t xml:space="preserve">12.9660415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4511337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8092861175537</t>
+    <t xml:space="preserve">13.4511346817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.809287071228</t>
   </si>
   <si>
     <t xml:space="preserve">14.1901073455811</t>
@@ -2765,10 +2765,10 @@
     <t xml:space="preserve">13.3695306777954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8727579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9634284973145</t>
+    <t xml:space="preserve">13.8727569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9634294509888</t>
   </si>
   <si>
     <t xml:space="preserve">13.7820854187012</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">14.2943801879883</t>
   </si>
   <si>
-    <t xml:space="preserve">14.448522567749</t>
+    <t xml:space="preserve">14.4485216140747</t>
   </si>
   <si>
     <t xml:space="preserve">14.5346603393555</t>
@@ -2786,46 +2786,46 @@
     <t xml:space="preserve">15.1512250900269</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3643026351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6544542312622</t>
+    <t xml:space="preserve">15.3643035888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6544532775879</t>
   </si>
   <si>
     <t xml:space="preserve">15.5683155059814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3461694717407</t>
+    <t xml:space="preserve">15.3461713790894</t>
   </si>
   <si>
     <t xml:space="preserve">16.6291732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7768602371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7904644012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4478302001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3752937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1097354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0398082733154</t>
+    <t xml:space="preserve">15.7768592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7904624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4478282928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3752918243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1097316741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0398101806641</t>
   </si>
   <si>
     <t xml:space="preserve">17.2446327209473</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4030952453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8813457489014</t>
+    <t xml:space="preserve">16.4030933380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.88134765625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7066020965576</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">17.6998920440674</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9896030426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4515705108643</t>
+    <t xml:space="preserve">17.9896011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4515686035156</t>
   </si>
   <si>
     <t xml:space="preserve">17.658504486084</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">17.6079216003418</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3549995422363</t>
+    <t xml:space="preserve">17.3549976348877</t>
   </si>
   <si>
     <t xml:space="preserve">17.6309127807617</t>
@@ -2861,13 +2861,13 @@
     <t xml:space="preserve">17.8884353637695</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6334018707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.752965927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8081493377686</t>
+    <t xml:space="preserve">18.6333999633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7529640197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8081474304199</t>
   </si>
   <si>
     <t xml:space="preserve">18.6701889038086</t>
@@ -2876,7 +2876,7 @@
     <t xml:space="preserve">17.7090873718262</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6631050109863</t>
+    <t xml:space="preserve">17.6631031036377</t>
   </si>
   <si>
     <t xml:space="preserve">17.4745635986328</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">18.3482913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2885074615479</t>
+    <t xml:space="preserve">18.2885093688965</t>
   </si>
   <si>
     <t xml:space="preserve">18.5874137878418</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">19.222017288208</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7161750793457</t>
+    <t xml:space="preserve">18.7161769866943</t>
   </si>
   <si>
     <t xml:space="preserve">18.9645004272461</t>
@@ -2912,13 +2912,13 @@
     <t xml:space="preserve">19.0104827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0748634338379</t>
+    <t xml:space="preserve">19.0748615264893</t>
   </si>
   <si>
     <t xml:space="preserve">19.5715084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3507766723633</t>
+    <t xml:space="preserve">19.3507785797119</t>
   </si>
   <si>
     <t xml:space="preserve">19.9761829376221</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">19.7278633117676</t>
   </si>
   <si>
-    <t xml:space="preserve">19.930196762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4703407287598</t>
+    <t xml:space="preserve">19.9301948547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4703426361084</t>
   </si>
   <si>
     <t xml:space="preserve">20.0957469940186</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2704925537109</t>
+    <t xml:space="preserve">20.2704906463623</t>
   </si>
   <si>
     <t xml:space="preserve">20.3256740570068</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">20.9602756500244</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3281631469727</t>
+    <t xml:space="preserve">21.328161239624</t>
   </si>
   <si>
     <t xml:space="preserve">21.0154609680176</t>
@@ -2963,19 +2963,19 @@
     <t xml:space="preserve">21.0430507659912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4912223815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2245063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2337017059326</t>
+    <t xml:space="preserve">20.4912242889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2245082855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2337036132812</t>
   </si>
   <si>
     <t xml:space="preserve">19.8934078216553</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8223209381104</t>
+    <t xml:space="preserve">20.8223190307617</t>
   </si>
   <si>
     <t xml:space="preserve">20.4176464080811</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">20.5556011199951</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8775024414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0614452362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7303485870361</t>
+    <t xml:space="preserve">20.8775043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0614433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7303504943848</t>
   </si>
   <si>
     <t xml:space="preserve">20.7579383850098</t>
@@ -3008,13 +3008,13 @@
     <t xml:space="preserve">20.6291809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2453880310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3649501800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4201354980469</t>
+    <t xml:space="preserve">21.2453861236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3649520874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4201374053955</t>
   </si>
   <si>
     <t xml:space="preserve">21.4937133789062</t>
@@ -3032,25 +3032,25 @@
     <t xml:space="preserve">22.0271453857422</t>
   </si>
   <si>
-    <t xml:space="preserve">21.604076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8156108856201</t>
+    <t xml:space="preserve">21.6040782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8156089782715</t>
   </si>
   <si>
     <t xml:space="preserve">21.4109363555908</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7420310974121</t>
+    <t xml:space="preserve">21.7420330047607</t>
   </si>
   <si>
     <t xml:space="preserve">22.1191158294678</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5145950317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6341590881348</t>
+    <t xml:space="preserve">22.5145931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6341571807861</t>
   </si>
   <si>
     <t xml:space="preserve">22.5421867370605</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">22.8456916809082</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2135753631592</t>
+    <t xml:space="preserve">23.2135734558105</t>
   </si>
   <si>
     <t xml:space="preserve">23.2411670684814</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">23.5722637176514</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0045280456543</t>
+    <t xml:space="preserve">24.0045299530029</t>
   </si>
   <si>
     <t xml:space="preserve">23.7194194793701</t>
@@ -3110,25 +3110,25 @@
     <t xml:space="preserve">24.3264312744141</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8757667541504</t>
+    <t xml:space="preserve">23.875768661499</t>
   </si>
   <si>
     <t xml:space="preserve">24.1700801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5998573303223</t>
+    <t xml:space="preserve">23.5998554229736</t>
   </si>
   <si>
     <t xml:space="preserve">22.6525478363037</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7261276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9560565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1926956176758</t>
+    <t xml:space="preserve">22.7261257171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1926937103271</t>
   </si>
   <si>
     <t xml:space="preserve">21.66845703125</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">21.1994018554688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6500644683838</t>
+    <t xml:space="preserve">21.6500625610352</t>
   </si>
   <si>
     <t xml:space="preserve">21.4661197662354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0823287963867</t>
+    <t xml:space="preserve">22.0823268890381</t>
   </si>
   <si>
     <t xml:space="preserve">22.5881690979004</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">24.0413188934326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0112400054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.121603012085</t>
+    <t xml:space="preserve">23.0112380981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1216049194336</t>
   </si>
   <si>
     <t xml:space="preserve">23.6274471282959</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">24.7403011322021</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2277507781982</t>
+    <t xml:space="preserve">25.2277488708496</t>
   </si>
   <si>
     <t xml:space="preserve">24.8966522216797</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">24.4092044830322</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5471611022949</t>
+    <t xml:space="preserve">24.5471630096436</t>
   </si>
   <si>
     <t xml:space="preserve">25.0622005462646</t>
@@ -3212,22 +3212,22 @@
     <t xml:space="preserve">24.6023426055908</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8874549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3105220794678</t>
+    <t xml:space="preserve">24.8874530792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3105239868164</t>
   </si>
   <si>
     <t xml:space="preserve">25.5680408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0805950164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3840999603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.503662109375</t>
+    <t xml:space="preserve">25.0805931091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3841018676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5036640167236</t>
   </si>
   <si>
     <t xml:space="preserve">25.3749046325684</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">25.9359302520752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6257152557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5613327026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7452774047852</t>
+    <t xml:space="preserve">26.6257133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5613346099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7452754974365</t>
   </si>
   <si>
     <t xml:space="preserve">26.8740367889404</t>
@@ -3254,16 +3254,16 @@
     <t xml:space="preserve">27.0119953155518</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5546245574951</t>
+    <t xml:space="preserve">27.5546264648438</t>
   </si>
   <si>
     <t xml:space="preserve">28.2811985015869</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9225120544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0880603790283</t>
+    <t xml:space="preserve">27.9225101470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0880584716797</t>
   </si>
   <si>
     <t xml:space="preserve">26.3957862854004</t>
@@ -3284,10 +3284,10 @@
     <t xml:space="preserve">26.0278987884521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7519874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6876049041748</t>
+    <t xml:space="preserve">25.7519855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6876068115234</t>
   </si>
   <si>
     <t xml:space="preserve">24.7127094268799</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">24.2804431915283</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1449756622314</t>
+    <t xml:space="preserve">25.1449737548828</t>
   </si>
   <si>
     <t xml:space="preserve">24.5011749267578</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">24.593147277832</t>
   </si>
   <si>
-    <t xml:space="preserve">24.390811920166</t>
+    <t xml:space="preserve">24.3908100128174</t>
   </si>
   <si>
     <t xml:space="preserve">24.1608810424805</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">24.9150466918945</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9058494567871</t>
+    <t xml:space="preserve">24.9058475494385</t>
   </si>
   <si>
     <t xml:space="preserve">24.0137271881104</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2712478637695</t>
+    <t xml:space="preserve">24.2712459564209</t>
   </si>
   <si>
     <t xml:space="preserve">25.2001552581787</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">24.2620487213135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.673433303833</t>
+    <t xml:space="preserve">23.6734352111816</t>
   </si>
   <si>
     <t xml:space="preserve">23.5446739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6918258666992</t>
+    <t xml:space="preserve">23.6918277740479</t>
   </si>
   <si>
     <t xml:space="preserve">23.4251098632812</t>
@@ -3398,37 +3398,37 @@
     <t xml:space="preserve">23.7837982177734</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1056976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.151683807373</t>
+    <t xml:space="preserve">24.1056995391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1516819000244</t>
   </si>
   <si>
     <t xml:space="preserve">24.5287666320801</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8138771057129</t>
+    <t xml:space="preserve">24.8138790130615</t>
   </si>
   <si>
     <t xml:space="preserve">24.8322734832764</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9886226654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4852676391602</t>
+    <t xml:space="preserve">24.9886245727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4852695465088</t>
   </si>
   <si>
     <t xml:space="preserve">25.7703800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6416206359863</t>
+    <t xml:space="preserve">25.6416187286377</t>
   </si>
   <si>
     <t xml:space="preserve">24.8414688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">24.694314956665</t>
+    <t xml:space="preserve">24.6943168640137</t>
   </si>
   <si>
     <t xml:space="preserve">25.1081867218018</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">24.5379638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4367923736572</t>
+    <t xml:space="preserve">24.4367942810059</t>
   </si>
   <si>
     <t xml:space="preserve">23.9861354827881</t>
@@ -3458,13 +3458,13 @@
     <t xml:space="preserve">24.4000072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">23.949348449707</t>
+    <t xml:space="preserve">23.9493465423584</t>
   </si>
   <si>
     <t xml:space="preserve">24.7954845428467</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2252578735352</t>
+    <t xml:space="preserve">24.2252597808838</t>
   </si>
   <si>
     <t xml:space="preserve">25.3197212219238</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">26.332389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5476913452148</t>
+    <t xml:space="preserve">26.5476894378662</t>
   </si>
   <si>
     <t xml:space="preserve">26.1826114654541</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">26.8753242492676</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3901786804199</t>
+    <t xml:space="preserve">27.3901767730713</t>
   </si>
   <si>
     <t xml:space="preserve">27.5867576599121</t>
@@ -3515,19 +3515,19 @@
     <t xml:space="preserve">27.7084503173828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8769454956055</t>
+    <t xml:space="preserve">27.8769474029541</t>
   </si>
   <si>
     <t xml:space="preserve">27.3340110778809</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2872066497803</t>
+    <t xml:space="preserve">27.2872047424316</t>
   </si>
   <si>
     <t xml:space="preserve">27.3808155059814</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6990871429443</t>
+    <t xml:space="preserve">27.699089050293</t>
   </si>
   <si>
     <t xml:space="preserve">27.1935977935791</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">27.1655158996582</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9237518310547</t>
+    <t xml:space="preserve">27.9237537384033</t>
   </si>
   <si>
     <t xml:space="preserve">27.8395042419434</t>
   </si>
   <si>
-    <t xml:space="preserve">27.802059173584</t>
+    <t xml:space="preserve">27.8020610809326</t>
   </si>
   <si>
     <t xml:space="preserve">28.401159286499</t>
@@ -3563,16 +3563,16 @@
     <t xml:space="preserve">28.3169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5041351318359</t>
+    <t xml:space="preserve">28.5041332244873</t>
   </si>
   <si>
     <t xml:space="preserve">28.382438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4479656219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7568759918213</t>
+    <t xml:space="preserve">28.4479675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7568778991699</t>
   </si>
   <si>
     <t xml:space="preserve">27.9799175262451</t>
@@ -3581,13 +3581,13 @@
     <t xml:space="preserve">28.5696601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8317642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7943210601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.691349029541</t>
+    <t xml:space="preserve">28.83176612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7943229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6913509368896</t>
   </si>
   <si>
     <t xml:space="preserve">28.4198837280273</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">28.2701072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1390533447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2888317108154</t>
+    <t xml:space="preserve">28.1390514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2888298034668</t>
   </si>
   <si>
     <t xml:space="preserve">28.485408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3637180328369</t>
+    <t xml:space="preserve">28.3637161254883</t>
   </si>
   <si>
     <t xml:space="preserve">28.7849617004395</t>
@@ -3632,25 +3632,25 @@
     <t xml:space="preserve">28.8785705566406</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0002632141113</t>
+    <t xml:space="preserve">29.0002613067627</t>
   </si>
   <si>
     <t xml:space="preserve">29.3934211730957</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2359104156494</t>
+    <t xml:space="preserve">30.2359085083008</t>
   </si>
   <si>
     <t xml:space="preserve">30.3201580047607</t>
   </si>
   <si>
-    <t xml:space="preserve">30.179744720459</t>
+    <t xml:space="preserve">30.1797466278076</t>
   </si>
   <si>
     <t xml:space="preserve">29.8146667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9925270080566</t>
+    <t xml:space="preserve">29.992525100708</t>
   </si>
   <si>
     <t xml:space="preserve">29.9550819396973</t>
@@ -3662,19 +3662,19 @@
     <t xml:space="preserve">29.5619220733643</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5057544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7585029602051</t>
+    <t xml:space="preserve">29.5057563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7585048675537</t>
   </si>
   <si>
     <t xml:space="preserve">29.805305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5806407928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8708324432373</t>
+    <t xml:space="preserve">29.5806427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8708305358887</t>
   </si>
   <si>
     <t xml:space="preserve">29.9082775115967</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">30.2171859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4044075012207</t>
+    <t xml:space="preserve">30.4044094085693</t>
   </si>
   <si>
     <t xml:space="preserve">30.385684967041</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">30.8630962371826</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8537330627441</t>
+    <t xml:space="preserve">30.8537311553955</t>
   </si>
   <si>
     <t xml:space="preserve">30.0018844604492</t>
@@ -3704,7 +3704,7 @@
     <t xml:space="preserve">30.5448246002197</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4980182647705</t>
+    <t xml:space="preserve">30.4980201721191</t>
   </si>
   <si>
     <t xml:space="preserve">30.4699325561523</t>
@@ -3722,19 +3722,19 @@
     <t xml:space="preserve">29.6461696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3185348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0299682617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.348237991333</t>
+    <t xml:space="preserve">29.3185329437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0299701690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3482398986816</t>
   </si>
   <si>
     <t xml:space="preserve">29.6742534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9534587860107</t>
+    <t xml:space="preserve">28.9534568786621</t>
   </si>
   <si>
     <t xml:space="preserve">28.813045501709</t>
@@ -3746,10 +3746,10 @@
     <t xml:space="preserve">27.5212306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4837875366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0267238616943</t>
+    <t xml:space="preserve">27.4837894439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.026725769043</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">29.2249240875244</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2717323303223</t>
+    <t xml:space="preserve">29.2717304229736</t>
   </si>
   <si>
     <t xml:space="preserve">29.2623691558838</t>
@@ -3773,13 +3773,13 @@
     <t xml:space="preserve">29.5244770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7304191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1610240936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4792957305908</t>
+    <t xml:space="preserve">29.7304210662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1610221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4792976379395</t>
   </si>
   <si>
     <t xml:space="preserve">30.5916290283203</t>
@@ -3788,28 +3788,28 @@
     <t xml:space="preserve">30.3669624328613</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6384296417236</t>
+    <t xml:space="preserve">30.6384315490723</t>
   </si>
   <si>
     <t xml:space="preserve">30.6103477478027</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7694835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3030586242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9286212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1626453399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.668140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8553562164307</t>
+    <t xml:space="preserve">30.7694816589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3030567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9286193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1626472473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6681365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.855354309082</t>
   </si>
   <si>
     <t xml:space="preserve">31.4341163635254</t>
@@ -3827,31 +3827,31 @@
     <t xml:space="preserve">31.9302444458008</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8101692199707</t>
+    <t xml:space="preserve">32.810173034668</t>
   </si>
   <si>
     <t xml:space="preserve">32.7633666992188</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6416778564453</t>
+    <t xml:space="preserve">32.6416816711426</t>
   </si>
   <si>
     <t xml:space="preserve">31.9489707946777</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6962203979492</t>
+    <t xml:space="preserve">31.6962223052979</t>
   </si>
   <si>
     <t xml:space="preserve">32.1081008911133</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6945991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3124217987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7320423126221</t>
+    <t xml:space="preserve">30.6945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3124237060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7320404052734</t>
   </si>
   <si>
     <t xml:space="preserve">30.5822639465332</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">30.8911762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">31.752384185791</t>
+    <t xml:space="preserve">31.7523860931396</t>
   </si>
   <si>
     <t xml:space="preserve">30.9473457336426</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">30.3576030731201</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0861339569092</t>
+    <t xml:space="preserve">30.0861320495605</t>
   </si>
   <si>
     <t xml:space="preserve">30.1516590118408</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">30.7507629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9754257202148</t>
+    <t xml:space="preserve">30.9754238128662</t>
   </si>
   <si>
     <t xml:space="preserve">30.9379806518555</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">31.2656192779541</t>
   </si>
   <si>
-    <t xml:space="preserve">31.602611541748</t>
+    <t xml:space="preserve">31.6026096343994</t>
   </si>
   <si>
     <t xml:space="preserve">31.7804679870605</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">30.5073757171631</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9721813201904</t>
+    <t xml:space="preserve">28.9721794128418</t>
   </si>
   <si>
     <t xml:space="preserve">27.6335620880127</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">26.8378810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2045803070068</t>
+    <t xml:space="preserve">28.2045783996582</t>
   </si>
   <si>
     <t xml:space="preserve">28.0548057556152</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">26.248140335083</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7800941467285</t>
+    <t xml:space="preserve">25.7800922393799</t>
   </si>
   <si>
     <t xml:space="preserve">26.5102462768555</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3152904510498</t>
+    <t xml:space="preserve">27.3152885437012</t>
   </si>
   <si>
     <t xml:space="preserve">26.9970169067383</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">26.1077251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5399532318115</t>
+    <t xml:space="preserve">27.5399513244629</t>
   </si>
   <si>
     <t xml:space="preserve">28.541576385498</t>
@@ -3998,10 +3998,10 @@
     <t xml:space="preserve">25.9766712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1374320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9502105712891</t>
+    <t xml:space="preserve">27.1374340057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9502124786377</t>
   </si>
   <si>
     <t xml:space="preserve">28.728796005249</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">29.0377063751221</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1219577789307</t>
+    <t xml:space="preserve">29.121955871582</t>
   </si>
   <si>
     <t xml:space="preserve">29.1406764984131</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">28.2326622009277</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8692092895508</t>
+    <t xml:space="preserve">28.8692111968994</t>
   </si>
   <si>
     <t xml:space="preserve">29.0096225738525</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2904510498047</t>
+    <t xml:space="preserve">29.2904529571533</t>
   </si>
   <si>
     <t xml:space="preserve">28.981538772583</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">27.0531826019287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5586738586426</t>
+    <t xml:space="preserve">27.5586757659912</t>
   </si>
   <si>
     <t xml:space="preserve">28.8972930908203</t>
@@ -4091,10 +4091,10 @@
     <t xml:space="preserve">29.7605361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6452331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0265331268311</t>
+    <t xml:space="preserve">28.6452312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0265350341797</t>
   </si>
   <si>
     <t xml:space="preserve">29.045597076416</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">28.3211250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7482604980469</t>
+    <t xml:space="preserve">26.7482585906982</t>
   </si>
   <si>
     <t xml:space="preserve">27.0247020721436</t>
@@ -4115,22 +4115,22 @@
     <t xml:space="preserve">27.1104965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052742004395</t>
+    <t xml:space="preserve">26.6052722930908</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101306915283</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4146213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9675102233887</t>
+    <t xml:space="preserve">26.414623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.96750831604</t>
   </si>
   <si>
     <t xml:space="preserve">27.2153549194336</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7682399749756</t>
+    <t xml:space="preserve">27.768238067627</t>
   </si>
   <si>
     <t xml:space="preserve">27.5299263000488</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">27.8635654449463</t>
   </si>
   <si>
-    <t xml:space="preserve">27.730110168457</t>
+    <t xml:space="preserve">27.7301120758057</t>
   </si>
   <si>
     <t xml:space="preserve">28.2829971313477</t>
@@ -4151,16 +4151,16 @@
     <t xml:space="preserve">28.9788703918457</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4459648132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.654764175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9207630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2258014678955</t>
+    <t xml:space="preserve">29.4459629058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6547660827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9207611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2258033752441</t>
   </si>
   <si>
     <t xml:space="preserve">27.8063697814941</t>
@@ -4175,7 +4175,7 @@
     <t xml:space="preserve">28.1304779052734</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4450492858887</t>
+    <t xml:space="preserve">28.4450511932373</t>
   </si>
   <si>
     <t xml:space="preserve">26.643404006958</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">26.3860263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6243381500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7950077056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.481351852417</t>
+    <t xml:space="preserve">26.6243362426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7950057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">26.2430381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1667785644531</t>
+    <t xml:space="preserve">26.1667766571045</t>
   </si>
   <si>
     <t xml:space="preserve">25.52809715271</t>
@@ -4211,10 +4211,10 @@
     <t xml:space="preserve">26.3002319335938</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9761257171631</t>
+    <t xml:space="preserve">26.4050884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9761276245117</t>
   </si>
   <si>
     <t xml:space="preserve">24.9847431182861</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">24.698766708374</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3374481201172</t>
+    <t xml:space="preserve">25.3374462127686</t>
   </si>
   <si>
     <t xml:space="preserve">25.9189319610596</t>
@@ -4241,19 +4241,19 @@
     <t xml:space="preserve">25.1658611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">25.29931640625</t>
+    <t xml:space="preserve">25.2993183135986</t>
   </si>
   <si>
     <t xml:space="preserve">25.2230548858643</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4795207977295</t>
+    <t xml:space="preserve">24.4795188903809</t>
   </si>
   <si>
     <t xml:space="preserve">24.9084815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3469791412354</t>
+    <t xml:space="preserve">25.346981048584</t>
   </si>
   <si>
     <t xml:space="preserve">26.2144393920898</t>
@@ -4262,19 +4262,19 @@
     <t xml:space="preserve">25.9093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4908828735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0532989501953</t>
+    <t xml:space="preserve">26.4908809661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0533008575439</t>
   </si>
   <si>
     <t xml:space="preserve">27.0437698364258</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6815319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2630176544189</t>
+    <t xml:space="preserve">26.6815338134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2630157470703</t>
   </si>
   <si>
     <t xml:space="preserve">28.7882213592529</t>
@@ -4283,13 +4283,13 @@
     <t xml:space="preserve">29.5031604766846</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4745616912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5508232116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6461486816406</t>
+    <t xml:space="preserve">29.4745597839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5508213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.646146774292</t>
   </si>
   <si>
     <t xml:space="preserve">30.9044380187988</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">29.9797859191895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8939952850342</t>
+    <t xml:space="preserve">29.8939933776855</t>
   </si>
   <si>
     <t xml:space="preserve">31.0760250091553</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">29.5317573547363</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1790561676025</t>
+    <t xml:space="preserve">29.1790542602539</t>
   </si>
   <si>
     <t xml:space="preserve">29.1885871887207</t>
@@ -4361,13 +4361,13 @@
     <t xml:space="preserve">31.0664920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">31.590784072876</t>
+    <t xml:space="preserve">31.5907821655273</t>
   </si>
   <si>
     <t xml:space="preserve">30.5326709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3515567779541</t>
+    <t xml:space="preserve">30.3515548706055</t>
   </si>
   <si>
     <t xml:space="preserve">30.3896827697754</t>
@@ -4388,10 +4388,10 @@
     <t xml:space="preserve">28.0160865783691</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6166362762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6738300323486</t>
+    <t xml:space="preserve">28.6166343688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.673828125</t>
   </si>
   <si>
     <t xml:space="preserve">28.3020629882812</t>
@@ -4409,7 +4409,7 @@
     <t xml:space="preserve">30.0560474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5126895904541</t>
+    <t xml:space="preserve">29.5126914978027</t>
   </si>
   <si>
     <t xml:space="preserve">29.7128753662109</t>
@@ -4418,25 +4418,25 @@
     <t xml:space="preserve">29.6842765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2648468017578</t>
+    <t xml:space="preserve">29.2648487091064</t>
   </si>
   <si>
     <t xml:space="preserve">29.7033424377441</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3983020782471</t>
+    <t xml:space="preserve">29.3983039855957</t>
   </si>
   <si>
     <t xml:space="preserve">29.7700710296631</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7510032653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5422058105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9616355895996</t>
+    <t xml:space="preserve">29.7510051727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5422077178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.961633682251</t>
   </si>
   <si>
     <t xml:space="preserve">30.4945430755615</t>
@@ -4454,13 +4454,13 @@
     <t xml:space="preserve">31.9434814453125</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9816150665283</t>
+    <t xml:space="preserve">31.981616973877</t>
   </si>
   <si>
     <t xml:space="preserve">31.7242336273193</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5717163085938</t>
+    <t xml:space="preserve">31.5717182159424</t>
   </si>
   <si>
     <t xml:space="preserve">31.4477977752686</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">31.6289119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8853778839111</t>
+    <t xml:space="preserve">30.8853759765625</t>
   </si>
   <si>
     <t xml:space="preserve">31.3715343475342</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">32.143669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8386325836182</t>
+    <t xml:space="preserve">31.8386287689209</t>
   </si>
   <si>
     <t xml:space="preserve">31.9244213104248</t>
@@ -4544,10 +4544,10 @@
     <t xml:space="preserve">33.8404579162598</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5926132202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9167175292969</t>
+    <t xml:space="preserve">33.5926170349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9167213439941</t>
   </si>
   <si>
     <t xml:space="preserve">33.9357833862305</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">33.1445846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3543014526367</t>
+    <t xml:space="preserve">33.354305267334</t>
   </si>
   <si>
     <t xml:space="preserve">33.6116752624512</t>
@@ -4583,10 +4583,10 @@
     <t xml:space="preserve">33.6593399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0397262573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7260704040527</t>
+    <t xml:space="preserve">33.039722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7260665893555</t>
   </si>
   <si>
     <t xml:space="preserve">33.0587921142578</t>
@@ -4601,19 +4601,19 @@
     <t xml:space="preserve">33.373363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.953929901123</t>
+    <t xml:space="preserve">32.9539337158203</t>
   </si>
   <si>
     <t xml:space="preserve">33.3638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">33.411491394043</t>
+    <t xml:space="preserve">33.4114952087402</t>
   </si>
   <si>
     <t xml:space="preserve">33.583080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0311088562012</t>
+    <t xml:space="preserve">34.0311126708984</t>
   </si>
   <si>
     <t xml:space="preserve">34.7937126159668</t>
@@ -4622,10 +4622,10 @@
     <t xml:space="preserve">35.0892181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5649261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2512702941895</t>
+    <t xml:space="preserve">34.5649299621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2512741088867</t>
   </si>
   <si>
     <t xml:space="preserve">35.4323883056641</t>
@@ -4634,10 +4634,10 @@
     <t xml:space="preserve">35.8804168701172</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5372428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5753784179688</t>
+    <t xml:space="preserve">35.5372467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5753746032715</t>
   </si>
   <si>
     <t xml:space="preserve">35.7469596862793</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">36.109203338623</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9852752685547</t>
+    <t xml:space="preserve">35.985279083252</t>
   </si>
   <si>
     <t xml:space="preserve">35.7088317871094</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">36.1568641662598</t>
   </si>
   <si>
-    <t xml:space="preserve">35.937614440918</t>
+    <t xml:space="preserve">35.9376182556152</t>
   </si>
   <si>
     <t xml:space="preserve">35.270336151123</t>
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">34.5839920043945</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1454963684082</t>
+    <t xml:space="preserve">34.1455001831055</t>
   </si>
   <si>
     <t xml:space="preserve">34.8413734436035</t>
@@ -4703,7 +4703,7 @@
     <t xml:space="preserve">34.6697883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9557609558105</t>
+    <t xml:space="preserve">34.9557647705078</t>
   </si>
   <si>
     <t xml:space="preserve">34.6888542175293</t>
@@ -4715,10 +4715,10 @@
     <t xml:space="preserve">36.1282653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0615386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7097434997559</t>
+    <t xml:space="preserve">36.0615348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7097473144531</t>
   </si>
   <si>
     <t xml:space="preserve">37.8631858825684</t>
@@ -4739,16 +4739,16 @@
     <t xml:space="preserve">34.2312927246094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8881187438965</t>
+    <t xml:space="preserve">33.8881225585938</t>
   </si>
   <si>
     <t xml:space="preserve">34.3552131652832</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1082878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1178169250488</t>
+    <t xml:space="preserve">35.108283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1178131103516</t>
   </si>
   <si>
     <t xml:space="preserve">34.7746429443359</t>
@@ -4760,19 +4760,19 @@
     <t xml:space="preserve">36.3761100769043</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5953598022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8908653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2235870361328</t>
+    <t xml:space="preserve">36.5953559875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8908615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2235908508301</t>
   </si>
   <si>
     <t xml:space="preserve">35.9566802978516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.946231842041</t>
+    <t xml:space="preserve">34.9462280273438</t>
   </si>
   <si>
     <t xml:space="preserve">35.3656616210938</t>
@@ -4784,7 +4784,7 @@
     <t xml:space="preserve">35.5086479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3847274780273</t>
+    <t xml:space="preserve">35.3847236633301</t>
   </si>
   <si>
     <t xml:space="preserve">35.9471435546875</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">36.5286293029785</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4618988037109</t>
+    <t xml:space="preserve">36.4619026184082</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807846069336</t>
@@ -4814,7 +4814,7 @@
     <t xml:space="preserve">35.0516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9039649963379</t>
+    <t xml:space="preserve">35.9039688110352</t>
   </si>
   <si>
     <t xml:space="preserve">36.2139015197754</t>
@@ -4832,16 +4832,16 @@
     <t xml:space="preserve">36.4947814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6521453857422</t>
+    <t xml:space="preserve">35.6521492004395</t>
   </si>
   <si>
     <t xml:space="preserve">35.3809509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0249900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2477531433105</t>
+    <t xml:space="preserve">34.0249938964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2477569580078</t>
   </si>
   <si>
     <t xml:space="preserve">34.6739158630371</t>
@@ -4883,25 +4883,25 @@
     <t xml:space="preserve">33.5794563293457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6642303466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3518981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4995765686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4027214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4705200195312</t>
+    <t xml:space="preserve">34.664234161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3518943786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4995727539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4027252197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4705238342285</t>
   </si>
   <si>
     <t xml:space="preserve">34.62548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5770645141602</t>
+    <t xml:space="preserve">34.5770606994629</t>
   </si>
   <si>
     <t xml:space="preserve">35.6618309020996</t>
@@ -4919,28 +4919,28 @@
     <t xml:space="preserve">35.9620819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5649795532227</t>
+    <t xml:space="preserve">35.5649757385254</t>
   </si>
   <si>
     <t xml:space="preserve">34.9354209899902</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8579444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8312797546387</t>
+    <t xml:space="preserve">34.8579406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8312835693359</t>
   </si>
   <si>
     <t xml:space="preserve">34.8676261901855</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9523963928223</t>
+    <t xml:space="preserve">35.952392578125</t>
   </si>
   <si>
     <t xml:space="preserve">35.855541229248</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0759048461914</t>
+    <t xml:space="preserve">37.0759086608887</t>
   </si>
   <si>
     <t xml:space="preserve">36.8240852355957</t>
@@ -4955,10 +4955,10 @@
     <t xml:space="preserve">35.1678733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6812019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5456085205078</t>
+    <t xml:space="preserve">35.6812057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5456047058105</t>
   </si>
   <si>
     <t xml:space="preserve">36.5432052612305</t>
@@ -4967,13 +4967,13 @@
     <t xml:space="preserve">36.349494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8942832946777</t>
+    <t xml:space="preserve">35.894287109375</t>
   </si>
   <si>
     <t xml:space="preserve">35.739315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6230850219727</t>
+    <t xml:space="preserve">35.6230888366699</t>
   </si>
   <si>
     <t xml:space="preserve">35.5359191894531</t>
@@ -4982,7 +4982,7 @@
     <t xml:space="preserve">35.2259864807129</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2550430297852</t>
+    <t xml:space="preserve">35.2550468444824</t>
   </si>
   <si>
     <t xml:space="preserve">34.7513999938965</t>
@@ -5003,19 +5003,19 @@
     <t xml:space="preserve">36.0492515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7029762268066</t>
+    <t xml:space="preserve">34.7029724121094</t>
   </si>
   <si>
     <t xml:space="preserve">34.4802055358887</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5383224487305</t>
+    <t xml:space="preserve">34.5383186340332</t>
   </si>
   <si>
     <t xml:space="preserve">34.2671279907227</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5480041503906</t>
+    <t xml:space="preserve">34.5480003356934</t>
   </si>
   <si>
     <t xml:space="preserve">33.8700256347656</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">34.7901382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1872482299805</t>
+    <t xml:space="preserve">35.1872444152832</t>
   </si>
   <si>
     <t xml:space="preserve">36.4463539123535</t>
@@ -5042,10 +5042,10 @@
     <t xml:space="preserve">36.6013221740723</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5625801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1364212036133</t>
+    <t xml:space="preserve">36.5625762939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.136417388916</t>
   </si>
   <si>
     <t xml:space="preserve">36.3010711669922</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">36.3398132324219</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5044631958008</t>
+    <t xml:space="preserve">36.504467010498</t>
   </si>
   <si>
     <t xml:space="preserve">36.7078590393066</t>
@@ -5069,22 +5069,22 @@
     <t xml:space="preserve">36.6497497558594</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7732620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9282302856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5408096313477</t>
+    <t xml:space="preserve">37.7732582092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9282264709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5408058166504</t>
   </si>
   <si>
     <t xml:space="preserve">37.4633255004883</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7635726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.359188079834</t>
+    <t xml:space="preserve">37.7635765075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3591842651367</t>
   </si>
   <si>
     <t xml:space="preserve">36.020191192627</t>
@@ -5096,16 +5096,16 @@
     <t xml:space="preserve">35.061336517334</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2913856506348</t>
+    <t xml:space="preserve">36.291389465332</t>
   </si>
   <si>
     <t xml:space="preserve">36.9499969482422</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0274772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1194458007812</t>
+    <t xml:space="preserve">37.0274810791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.119441986084</t>
   </si>
   <si>
     <t xml:space="preserve">36.0008201599121</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">34.3930358886719</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1000785827637</t>
+    <t xml:space="preserve">35.1000747680664</t>
   </si>
   <si>
     <t xml:space="preserve">34.4608383178711</t>
@@ -5141,13 +5141,13 @@
     <t xml:space="preserve">33.7150573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5310325622559</t>
+    <t xml:space="preserve">33.5310287475586</t>
   </si>
   <si>
     <t xml:space="preserve">32.7755661010742</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7271423339844</t>
+    <t xml:space="preserve">32.7271385192871</t>
   </si>
   <si>
     <t xml:space="preserve">32.7174530029297</t>
@@ -5159,16 +5159,16 @@
     <t xml:space="preserve">34.1799583435059</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8022232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6836013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9547958374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7441139221191</t>
+    <t xml:space="preserve">33.8022270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6836051940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9547920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7441101074219</t>
   </si>
   <si>
     <t xml:space="preserve">33.8990783691406</t>
@@ -5186,16 +5186,16 @@
     <t xml:space="preserve">35.1581878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8482513427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3155555725098</t>
+    <t xml:space="preserve">34.8482551574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3155517578125</t>
   </si>
   <si>
     <t xml:space="preserve">33.8409652709961</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4729194641113</t>
+    <t xml:space="preserve">33.4729232788086</t>
   </si>
   <si>
     <t xml:space="preserve">34.160587310791</t>
@@ -5210,10 +5210,10 @@
     <t xml:space="preserve">36.1945304870605</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3083572387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5795516967773</t>
+    <t xml:space="preserve">37.3083610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5795478820801</t>
   </si>
   <si>
     <t xml:space="preserve">37.6473503112793</t>
@@ -5234,7 +5234,7 @@
     <t xml:space="preserve">39.3713607788086</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3229293823242</t>
+    <t xml:space="preserve">39.3229331970215</t>
   </si>
   <si>
     <t xml:space="preserve">39.410099029541</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">39.4585304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6134948730469</t>
+    <t xml:space="preserve">39.6134986877441</t>
   </si>
   <si>
     <t xml:space="preserve">39.1389083862305</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">39.8846893310547</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5553855895996</t>
+    <t xml:space="preserve">39.5553817749023</t>
   </si>
   <si>
     <t xml:space="preserve">39.4682159423828</t>
@@ -5285,7 +5285,7 @@
     <t xml:space="preserve">38.8870887756348</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4197845458984</t>
+    <t xml:space="preserve">39.4197883605957</t>
   </si>
   <si>
     <t xml:space="preserve">38.8677177429199</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">39.264820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8096008300781</t>
+    <t xml:space="preserve">38.8096046447754</t>
   </si>
   <si>
     <t xml:space="preserve">39.4972686767578</t>
@@ -5303,7 +5303,7 @@
     <t xml:space="preserve">39.2745056152344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.749095916748</t>
+    <t xml:space="preserve">39.7490921020508</t>
   </si>
   <si>
     <t xml:space="preserve">38.9355125427246</t>
@@ -5312,13 +5312,13 @@
     <t xml:space="preserve">39.6425514221191</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7006645202637</t>
+    <t xml:space="preserve">39.7006683349609</t>
   </si>
   <si>
     <t xml:space="preserve">39.8168907165527</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0009155273438</t>
+    <t xml:space="preserve">40.0009117126465</t>
   </si>
   <si>
     <t xml:space="preserve">40.4173889160156</t>
@@ -5330,7 +5330,7 @@
     <t xml:space="preserve">40.707950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6110992431641</t>
+    <t xml:space="preserve">40.6110954284668</t>
   </si>
   <si>
     <t xml:space="preserve">39.7103500366211</t>
@@ -5339,16 +5339,16 @@
     <t xml:space="preserve">41.5796432495117</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3254203796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8798904418945</t>
+    <t xml:space="preserve">42.3254241943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8798942565918</t>
   </si>
   <si>
     <t xml:space="preserve">42.257625579834</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6934700012207</t>
+    <t xml:space="preserve">42.693473815918</t>
   </si>
   <si>
     <t xml:space="preserve">43.2358551025391</t>
@@ -5357,7 +5357,7 @@
     <t xml:space="preserve">43.8072967529297</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8968620300293</t>
+    <t xml:space="preserve">42.8968658447266</t>
   </si>
   <si>
     <t xml:space="preserve">42.906551361084</t>
@@ -5366,7 +5366,7 @@
     <t xml:space="preserve">43.4779891967773</t>
   </si>
   <si>
-    <t xml:space="preserve">44.601505279541</t>
+    <t xml:space="preserve">44.6015014648438</t>
   </si>
   <si>
     <t xml:space="preserve">44.5627593994141</t>
@@ -5381,10 +5381,10 @@
     <t xml:space="preserve">45.5022506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4925689697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3763389587402</t>
+    <t xml:space="preserve">45.4925651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.376335144043</t>
   </si>
   <si>
     <t xml:space="preserve">44.4465370178223</t>
@@ -5396,7 +5396,7 @@
     <t xml:space="preserve">45.8896713256836</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5870208740234</t>
+    <t xml:space="preserve">46.5870170593262</t>
   </si>
   <si>
     <t xml:space="preserve">46.112434387207</t>
@@ -5405,7 +5405,7 @@
     <t xml:space="preserve">46.4514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1875228881836</t>
+    <t xml:space="preserve">47.1875190734863</t>
   </si>
   <si>
     <t xml:space="preserve">47.8558158874512</t>
@@ -5414,10 +5414,10 @@
     <t xml:space="preserve">47.4683952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8364448547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2141761779785</t>
+    <t xml:space="preserve">47.8364410400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2141723632812</t>
   </si>
   <si>
     <t xml:space="preserve">48.1560668945312</t>
@@ -5426,28 +5426,28 @@
     <t xml:space="preserve">47.1487770080566</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8679008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4126777648926</t>
+    <t xml:space="preserve">46.8678970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4126815795898</t>
   </si>
   <si>
     <t xml:space="preserve">46.548282623291</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7322998046875</t>
+    <t xml:space="preserve">46.7323036193848</t>
   </si>
   <si>
     <t xml:space="preserve">46.7226181030273</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6039962768555</t>
+    <t xml:space="preserve">47.6039924621582</t>
   </si>
   <si>
     <t xml:space="preserve">46.8097877502441</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9938125610352</t>
+    <t xml:space="preserve">46.9938087463379</t>
   </si>
   <si>
     <t xml:space="preserve">46.6838760375977</t>
@@ -5459,10 +5459,10 @@
     <t xml:space="preserve">47.8654975891113</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6403388977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8146781921387</t>
+    <t xml:space="preserve">48.6403350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8146743774414</t>
   </si>
   <si>
     <t xml:space="preserve">48.6968154907227</t>
@@ -6465,6 +6465,9 @@
   </si>
   <si>
     <t xml:space="preserve">91.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6999969482422</t>
   </si>
 </sst>
 </file>
@@ -71751,7 +71754,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6931712963</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>610136</v>
@@ -71772,6 +71775,32 @@
         <v>2150</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6912037037</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>1038295</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>93.0599975585938</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>91.0999984741211</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>91.7399978637695</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>91.6999969482422</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>2151</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="2153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="2154">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,199 +44,199 @@
     <t xml:space="preserve">PRY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8714027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3207635879517</t>
+    <t xml:space="preserve">15.8714008331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3207597732544</t>
   </si>
   <si>
     <t xml:space="preserve">15.2397832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7458267211914</t>
+    <t xml:space="preserve">14.74582862854</t>
   </si>
   <si>
     <t xml:space="preserve">14.9644641876221</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2964677810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.498911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.061637878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5028991699219</t>
+    <t xml:space="preserve">15.2964658737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4989109039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.061635017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5029001235962</t>
   </si>
   <si>
     <t xml:space="preserve">14.5433874130249</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8510980606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870880126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9401712417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.409836769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.923975944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2802753448486</t>
+    <t xml:space="preserve">14.8510961532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9401731491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4098377227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9239778518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2802734375</t>
   </si>
   <si>
     <t xml:space="preserve">15.1831035614014</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6243648529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8106079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7296352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8996839523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5190935134888</t>
+    <t xml:space="preserve">14.6243619918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936414718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8106098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7296333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8996829986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5190954208374</t>
   </si>
   <si>
     <t xml:space="preserve">13.7336206436157</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3449335098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0980167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3206396102905</t>
+    <t xml:space="preserve">13.344934463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.098014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3206415176392</t>
   </si>
   <si>
     <t xml:space="preserve">13.4744958877563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8955755233765</t>
+    <t xml:space="preserve">13.8955745697021</t>
   </si>
   <si>
     <t xml:space="preserve">13.7822046279907</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3328475952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2194805145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057283401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8349018096924</t>
+    <t xml:space="preserve">14.3328485488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2194786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057264328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8348999023438</t>
   </si>
   <si>
     <t xml:space="preserve">14.5514841079712</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3409471511841</t>
+    <t xml:space="preserve">14.3409452438354</t>
   </si>
   <si>
     <t xml:space="preserve">14.8672914505005</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1021213531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235908508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4827136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3774461746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4017362594604</t>
+    <t xml:space="preserve">15.1021223068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.223593711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4827117919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3774471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4017372131348</t>
   </si>
   <si>
     <t xml:space="preserve">15.4665193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4908113479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5232038497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5636920928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.142614364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742261886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8390130996704</t>
+    <t xml:space="preserve">15.4908132553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5232009887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5636873245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426134109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742300033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8390083312988</t>
   </si>
   <si>
     <t xml:space="preserve">15.5879831314087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6365690231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9199848175049</t>
+    <t xml:space="preserve">15.636570930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9199867248535</t>
   </si>
   <si>
     <t xml:space="preserve">15.8309135437012</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8795003890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8228139877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.895694732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2762851715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.122428894043</t>
+    <t xml:space="preserve">15.8794975280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8228158950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8956956863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2762870788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1224308013916</t>
   </si>
   <si>
     <t xml:space="preserve">15.8471088409424</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8875951766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4422245025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3855419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3086738586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2276973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7135543823242</t>
+    <t xml:space="preserve">15.8875942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4422264099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3855400085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3086757659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2277011871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7135581970215</t>
   </si>
   <si>
     <t xml:space="preserve">16.6568717956543</t>
@@ -245,16 +245,16 @@
     <t xml:space="preserve">16.430139541626</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6120529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9180030822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0254955291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9758834838867</t>
+    <t xml:space="preserve">16.6120548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9180011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0254936218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9758796691895</t>
   </si>
   <si>
     <t xml:space="preserve">16.9924201965332</t>
@@ -263,46 +263,46 @@
     <t xml:space="preserve">16.6285915374756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7774314880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9841499328613</t>
+    <t xml:space="preserve">16.7774295806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9841537475586</t>
   </si>
   <si>
     <t xml:space="preserve">17.1081829071045</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9345378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5541763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5955181121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7608909606934</t>
+    <t xml:space="preserve">16.9345397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5541744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5955142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.760892868042</t>
   </si>
   <si>
     <t xml:space="preserve">16.7030124664307</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8766555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4058609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7696895599365</t>
+    <t xml:space="preserve">16.8766574859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4058628082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696914672852</t>
   </si>
   <si>
     <t xml:space="preserve">18.0094833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9681415557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8606452941895</t>
+    <t xml:space="preserve">17.9681396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8606491088867</t>
   </si>
   <si>
     <t xml:space="preserve">17.7779579162598</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">17.8854522705078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6952686309814</t>
+    <t xml:space="preserve">17.6952705383301</t>
   </si>
   <si>
     <t xml:space="preserve">18.1087093353271</t>
@@ -329,34 +329,34 @@
     <t xml:space="preserve">18.282356262207</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2988929748535</t>
+    <t xml:space="preserve">18.2988948822021</t>
   </si>
   <si>
     <t xml:space="preserve">18.4725379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1831302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1335163116455</t>
+    <t xml:space="preserve">18.1831321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1335182189941</t>
   </si>
   <si>
     <t xml:space="preserve">18.0425605773926</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8027610778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0921745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9185256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0012149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3149013519287</t>
+    <t xml:space="preserve">17.8027648925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0921726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9185237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0012168884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.314905166626</t>
   </si>
   <si>
     <t xml:space="preserve">16.9097309112549</t>
@@ -368,112 +368,112 @@
     <t xml:space="preserve">16.8022403717041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7366142272949</t>
+    <t xml:space="preserve">17.7366123199463</t>
   </si>
   <si>
     <t xml:space="preserve">17.5712375640869</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3479785919189</t>
+    <t xml:space="preserve">17.3479804992676</t>
   </si>
   <si>
     <t xml:space="preserve">17.9102592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6694087982178</t>
+    <t xml:space="preserve">15.6694059371948</t>
   </si>
   <si>
     <t xml:space="preserve">14.8342590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1402053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2559680938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399597167969</t>
+    <t xml:space="preserve">15.1402044296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399578094482</t>
   </si>
   <si>
     <t xml:space="preserve">16.2978382110596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7272891998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5867214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2311601638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6115245819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2813034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6533985137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6864738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6782035827637</t>
+    <t xml:space="preserve">15.7272901535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5867233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2311573028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6115293502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2813053131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4632167816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6534004211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6864719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.678201675415</t>
   </si>
   <si>
     <t xml:space="preserve">16.7443542480469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6699352264404</t>
+    <t xml:space="preserve">16.6699371337891</t>
   </si>
   <si>
     <t xml:space="preserve">16.8435821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8187713623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.951078414917</t>
+    <t xml:space="preserve">16.818775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9510746002197</t>
   </si>
   <si>
     <t xml:space="preserve">17.0999126434326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1164531707764</t>
+    <t xml:space="preserve">17.1164512634277</t>
   </si>
   <si>
     <t xml:space="preserve">17.2983684539795</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2404823303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0751113891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3314437866211</t>
+    <t xml:space="preserve">17.2404842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0751094818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3314418792725</t>
   </si>
   <si>
     <t xml:space="preserve">17.620849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1004447937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125793457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5960445404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0756378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7944965362549</t>
+    <t xml:space="preserve">18.1004428863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125812530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5960426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0756359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7944927215576</t>
   </si>
   <si>
     <t xml:space="preserve">17.8771839141846</t>
@@ -482,73 +482,73 @@
     <t xml:space="preserve">18.1913986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2492809295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0839023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2906246185303</t>
+    <t xml:space="preserve">18.2492790222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0839061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.290620803833</t>
   </si>
   <si>
     <t xml:space="preserve">18.1665916442871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9929504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.844108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7200736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.728343963623</t>
+    <t xml:space="preserve">17.9929466247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8441047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7200756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7283458709717</t>
   </si>
   <si>
     <t xml:space="preserve">17.8937225341797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0673675537109</t>
+    <t xml:space="preserve">18.0673656463623</t>
   </si>
   <si>
     <t xml:space="preserve">18.3733139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9438610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4317207336426</t>
+    <t xml:space="preserve">18.9438571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4317245483398</t>
   </si>
   <si>
     <t xml:space="preserve">19.3572998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1009674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1257762908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1919269561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.175386428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2828807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1340408325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3490352630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.76247215271</t>
+    <t xml:space="preserve">19.1009712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1257743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1919288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1753883361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2828845977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1340427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3490333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978675842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7624759674072</t>
   </si>
   <si>
     <t xml:space="preserve">19.6549797058105</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">19.7045917510986</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4647979736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0596218109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6461849212646</t>
+    <t xml:space="preserve">19.4647960662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0596237182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.646183013916</t>
   </si>
   <si>
     <t xml:space="preserve">19.1175060272217</t>
@@ -578,22 +578,22 @@
     <t xml:space="preserve">18.7536773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9025173187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0844345092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9934749603271</t>
+    <t xml:space="preserve">18.902515411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0844287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9934730529785</t>
   </si>
   <si>
     <t xml:space="preserve">18.7950210571289</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7867546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7454090118408</t>
+    <t xml:space="preserve">18.7867527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7454109191895</t>
   </si>
   <si>
     <t xml:space="preserve">18.3319683074951</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">17.6291198730469</t>
   </si>
   <si>
-    <t xml:space="preserve">18.869441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1505851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3485069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6627197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.728874206543</t>
+    <t xml:space="preserve">18.8694400787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1505813598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3485050201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6627235412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7288722991943</t>
   </si>
   <si>
     <t xml:space="preserve">18.6875286102295</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">18.8942489624023</t>
   </si>
   <si>
-    <t xml:space="preserve">18.422924041748</t>
+    <t xml:space="preserve">18.4229259490967</t>
   </si>
   <si>
     <t xml:space="preserve">18.4808082580566</t>
@@ -632,28 +632,28 @@
     <t xml:space="preserve">18.2327442169189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3236980438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0590953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.670991897583</t>
+    <t xml:space="preserve">18.3236999511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0590972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6709861755371</t>
   </si>
   <si>
     <t xml:space="preserve">18.9355907440186</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4399890899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8782329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6797847747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1676483154297</t>
+    <t xml:space="preserve">19.4399909973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8782367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6797866821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1676445007324</t>
   </si>
   <si>
     <t xml:space="preserve">19.8451633453369</t>
@@ -662,16 +662,16 @@
     <t xml:space="preserve">19.7790126800537</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1428413391113</t>
+    <t xml:space="preserve">20.1428394317627</t>
   </si>
   <si>
     <t xml:space="preserve">19.9113121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1759128570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.002269744873</t>
+    <t xml:space="preserve">20.1759166717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0022659301758</t>
   </si>
   <si>
     <t xml:space="preserve">19.9278507232666</t>
@@ -680,64 +680,64 @@
     <t xml:space="preserve">20.0105381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8038158416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1014957427979</t>
+    <t xml:space="preserve">19.8038177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1014938354492</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263027191162</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1097621917725</t>
+    <t xml:space="preserve">20.1097640991211</t>
   </si>
   <si>
     <t xml:space="preserve">20.1924514770508</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6389675140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1345691680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2751445770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2172565460205</t>
+    <t xml:space="preserve">20.6389694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1345729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2751407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2172603607178</t>
   </si>
   <si>
     <t xml:space="preserve">20.3164863586426</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2420654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3330211639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2255268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6555042266846</t>
+    <t xml:space="preserve">20.2420635223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3330192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.225528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6555061340332</t>
   </si>
   <si>
     <t xml:space="preserve">20.5066680908203</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3578281402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4818630218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0849590301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3991737365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5645503997803</t>
+    <t xml:space="preserve">20.3578319549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4818572998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0849571228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3991718292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5645484924316</t>
   </si>
   <si>
     <t xml:space="preserve">20.5397434234619</t>
@@ -749,31 +749,31 @@
     <t xml:space="preserve">19.8947772979736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4074401855469</t>
+    <t xml:space="preserve">20.4074440002441</t>
   </si>
   <si>
     <t xml:space="preserve">20.7133865356445</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9697208404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3495635986328</t>
+    <t xml:space="preserve">20.9697189331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3495616912842</t>
   </si>
   <si>
     <t xml:space="preserve">20.423978805542</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3082141876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.754732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9609260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8865070343018</t>
+    <t xml:space="preserve">20.3082180023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7547340393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9609241485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8865051269531</t>
   </si>
   <si>
     <t xml:space="preserve">19.8286266326904</t>
@@ -788,40 +788,40 @@
     <t xml:space="preserve">19.5722923278809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2994194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5144081115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5474853515625</t>
+    <t xml:space="preserve">19.2994213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5144119262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5474815368652</t>
   </si>
   <si>
     <t xml:space="preserve">19.423454284668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6136341094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5640201568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3821105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7376689910889</t>
+    <t xml:space="preserve">19.6136379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.564022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3821086883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7376651763916</t>
   </si>
   <si>
     <t xml:space="preserve">20.3660984039307</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9361209869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2007236480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4901275634766</t>
+    <t xml:space="preserve">19.9361190795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.200719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4901313781738</t>
   </si>
   <si>
     <t xml:space="preserve">20.7381935119629</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">21.0854835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9366493225098</t>
+    <t xml:space="preserve">20.9366455078125</t>
   </si>
   <si>
     <t xml:space="preserve">20.7795391082764</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">20.7051200866699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1268272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0435562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1192493438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8669414520264</t>
+    <t xml:space="preserve">21.1268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0435600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1192474365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.866943359375</t>
   </si>
   <si>
     <t xml:space="preserve">21.9846858978271</t>
@@ -869,79 +869,79 @@
     <t xml:space="preserve">22.4724864959717</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2201766967773</t>
+    <t xml:space="preserve">22.2201728820801</t>
   </si>
   <si>
     <t xml:space="preserve">22.2622261047363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5397682189941</t>
+    <t xml:space="preserve">22.5397720336914</t>
   </si>
   <si>
     <t xml:space="preserve">22.5734100341797</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5986423492432</t>
+    <t xml:space="preserve">22.5986404418945</t>
   </si>
   <si>
     <t xml:space="preserve">21.8080673217773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6987323760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0847778320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3202686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9502105712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6390247344971</t>
+    <t xml:space="preserve">21.6987342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0847759246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3202667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9502086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6390266418457</t>
   </si>
   <si>
     <t xml:space="preserve">20.4203586578369</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5549221038818</t>
+    <t xml:space="preserve">20.5549240112305</t>
   </si>
   <si>
     <t xml:space="preserve">20.4539985656738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9670314788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1941089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8576946258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1688804626465</t>
+    <t xml:space="preserve">20.9670295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1941108703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8576984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1688823699951</t>
   </si>
   <si>
     <t xml:space="preserve">20.8324642181396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9586181640625</t>
+    <t xml:space="preserve">20.9586219787598</t>
   </si>
   <si>
     <t xml:space="preserve">20.8156433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.597806930542</t>
+    <t xml:space="preserve">21.5978088378906</t>
   </si>
   <si>
     <t xml:space="preserve">21.2613945007324</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1015949249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6819114685059</t>
+    <t xml:space="preserve">21.101598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6819133758545</t>
   </si>
   <si>
     <t xml:space="preserve">21.6146297454834</t>
@@ -956,76 +956,76 @@
     <t xml:space="preserve">21.8248882293701</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5473442077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5725765228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0351486206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.858528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9258117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7828369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.321102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4884700775146</t>
+    <t xml:space="preserve">21.5473461151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5725784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0351505279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8585300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9258098602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7828350067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3211002349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4884757995605</t>
   </si>
   <si>
     <t xml:space="preserve">21.3875484466553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1949424743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8501205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2454051971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0015029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3883819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2538166046143</t>
+    <t xml:space="preserve">22.1949443817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.850118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2454090118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0015048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3883857727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2538185119629</t>
   </si>
   <si>
     <t xml:space="preserve">22.5481796264648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5313587188721</t>
+    <t xml:space="preserve">22.5313625335693</t>
   </si>
   <si>
     <t xml:space="preserve">22.7668495178223</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0696220397949</t>
+    <t xml:space="preserve">23.0696239471436</t>
   </si>
   <si>
     <t xml:space="preserve">22.5818214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8425426483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5649967193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1444816589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.211763381958</t>
+    <t xml:space="preserve">22.8425407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5650024414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1444835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2117652893066</t>
   </si>
   <si>
     <t xml:space="preserve">22.1865329742432</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">22.52294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7920818328857</t>
+    <t xml:space="preserve">22.7920780181885</t>
   </si>
   <si>
     <t xml:space="preserve">22.4220237731934</t>
@@ -1043,25 +1043,25 @@
     <t xml:space="preserve">22.7500286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9266471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9350566864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8593635559082</t>
+    <t xml:space="preserve">22.9266452789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.93505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8593616485596</t>
   </si>
   <si>
     <t xml:space="preserve">22.7079772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7416172027588</t>
+    <t xml:space="preserve">22.7416191101074</t>
   </si>
   <si>
     <t xml:space="preserve">22.5902309417725</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2369956970215</t>
+    <t xml:space="preserve">22.2369995117188</t>
   </si>
   <si>
     <t xml:space="preserve">21.8417091369629</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">22.1613025665283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3547401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3042793273926</t>
+    <t xml:space="preserve">22.3547420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3042774200439</t>
   </si>
   <si>
     <t xml:space="preserve">21.959451675415</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">22.2285861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1108379364014</t>
+    <t xml:space="preserve">22.11083984375</t>
   </si>
   <si>
     <t xml:space="preserve">21.9174003601074</t>
@@ -1100,22 +1100,22 @@
     <t xml:space="preserve">23.4649085998535</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6331176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6751689910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6835803985596</t>
+    <t xml:space="preserve">23.633113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6751670837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6835784912109</t>
   </si>
   <si>
     <t xml:space="preserve">23.8097343444824</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9106597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9190692901611</t>
+    <t xml:space="preserve">23.9106616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9190673828125</t>
   </si>
   <si>
     <t xml:space="preserve">23.7508602142334</t>
@@ -1124,19 +1124,19 @@
     <t xml:space="preserve">23.8770179748535</t>
   </si>
   <si>
-    <t xml:space="preserve">23.986349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8938407897949</t>
+    <t xml:space="preserve">23.9863471984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8938369750977</t>
   </si>
   <si>
     <t xml:space="preserve">23.952709197998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9779415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8517875671387</t>
+    <t xml:space="preserve">23.9779396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8517837524414</t>
   </si>
   <si>
     <t xml:space="preserve">24.0368137359619</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">24.4741535186768</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3311786651611</t>
+    <t xml:space="preserve">24.3311748504639</t>
   </si>
   <si>
     <t xml:space="preserve">24.314359664917</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0536365509033</t>
+    <t xml:space="preserve">24.0536346435547</t>
   </si>
   <si>
     <t xml:space="preserve">23.9358901977539</t>
@@ -1160,82 +1160,82 @@
     <t xml:space="preserve">23.8013229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9611225128174</t>
+    <t xml:space="preserve">23.9611206054688</t>
   </si>
   <si>
     <t xml:space="preserve">24.0199947357178</t>
   </si>
   <si>
-    <t xml:space="preserve">24.104097366333</t>
+    <t xml:space="preserve">24.1040992736816</t>
   </si>
   <si>
     <t xml:space="preserve">24.5582580566406</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5077934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.356409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3984603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9199066162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7937488555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6928195953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8946704864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.231086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1217498779297</t>
+    <t xml:space="preserve">24.5077953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3564071655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.398458480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.919900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7937450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6928215026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8946685791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2310848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1217517852783</t>
   </si>
   <si>
     <t xml:space="preserve">25.1890316009521</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8526229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4489231109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5574264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.389217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5994758605957</t>
+    <t xml:space="preserve">24.8526210784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4489192962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5574245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3892154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5994739532471</t>
   </si>
   <si>
     <t xml:space="preserve">23.2125988006592</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9274787902832</t>
+    <t xml:space="preserve">23.9274768829346</t>
   </si>
   <si>
     <t xml:space="preserve">23.691987991333</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5406036376953</t>
+    <t xml:space="preserve">23.5406017303467</t>
   </si>
   <si>
     <t xml:space="preserve">23.5742454528809</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3808040618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4144458770752</t>
+    <t xml:space="preserve">23.3808078765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4144477844238</t>
   </si>
   <si>
     <t xml:space="preserve">23.532190322876</t>
@@ -1247,25 +1247,25 @@
     <t xml:space="preserve">22.9939289093018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6911582946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9014148712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.977108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0443916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0275707244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0359783172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8930072784424</t>
+    <t xml:space="preserve">22.6911544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9014186859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9771118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0443897247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0275688171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0359802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8930034637451</t>
   </si>
   <si>
     <t xml:space="preserve">22.6827449798584</t>
@@ -1274,25 +1274,25 @@
     <t xml:space="preserve">23.1789569854736</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2546482086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2210083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1621379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.229419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0780334472656</t>
+    <t xml:space="preserve">23.2546501159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2210102081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1621341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2294178009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0780353546143</t>
   </si>
   <si>
     <t xml:space="preserve">22.8677730560303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0107498168945</t>
+    <t xml:space="preserve">23.0107517242432</t>
   </si>
   <si>
     <t xml:space="preserve">24.1881999969482</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">24.003173828125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1713809967041</t>
+    <t xml:space="preserve">24.1713790893555</t>
   </si>
   <si>
     <t xml:space="preserve">24.2218418121338</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">24.3900508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4909706115723</t>
+    <t xml:space="preserve">24.4909725189209</t>
   </si>
   <si>
     <t xml:space="preserve">24.8273887634277</t>
@@ -1325,49 +1325,49 @@
     <t xml:space="preserve">24.3059463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8686065673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8349666595459</t>
+    <t xml:space="preserve">23.8686084747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8349647521973</t>
   </si>
   <si>
     <t xml:space="preserve">23.2882919311523</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9602870941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6070518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4564990997314</t>
+    <t xml:space="preserve">22.9602832794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6070537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4564971923828</t>
   </si>
   <si>
     <t xml:space="preserve">22.7163867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4556674957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0687885284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1781215667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0940170288086</t>
+    <t xml:space="preserve">22.4556636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.068790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1781253814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0940208435059</t>
   </si>
   <si>
     <t xml:space="preserve">21.9089889526367</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7996559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6314487457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7912445068359</t>
+    <t xml:space="preserve">21.7996597290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6314506530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7912464141846</t>
   </si>
   <si>
     <t xml:space="preserve">22.3631496429443</t>
@@ -1376,148 +1376,148 @@
     <t xml:space="preserve">22.3967933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2874603271484</t>
+    <t xml:space="preserve">22.2874584197998</t>
   </si>
   <si>
     <t xml:space="preserve">22.0856094360352</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6230373382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3454990386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4043712615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.446418762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.295036315918</t>
+    <t xml:space="preserve">21.6230392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3455009460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4043731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4464206695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2950344085693</t>
   </si>
   <si>
     <t xml:space="preserve">21.337085723877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7407836914062</t>
+    <t xml:space="preserve">21.7407855987549</t>
   </si>
   <si>
     <t xml:space="preserve">20.790412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3194313049316</t>
+    <t xml:space="preserve">20.3194332122803</t>
   </si>
   <si>
     <t xml:space="preserve">20.7988243103027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4035377502441</t>
+    <t xml:space="preserve">20.4035396575928</t>
   </si>
   <si>
     <t xml:space="preserve">20.5717449188232</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7735939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9249782562256</t>
+    <t xml:space="preserve">20.7735919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9249801635742</t>
   </si>
   <si>
     <t xml:space="preserve">20.8072338104248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0288715362549</t>
+    <t xml:space="preserve">21.0288734436035</t>
   </si>
   <si>
     <t xml:space="preserve">20.8919315338135</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6351661682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6180534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.746431350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8662528991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3883399963379</t>
+    <t xml:space="preserve">20.6351699829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.618049621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7464332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8662548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3883419036865</t>
   </si>
   <si>
     <t xml:space="preserve">20.9604015350342</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3626613616943</t>
+    <t xml:space="preserve">21.3626651763916</t>
   </si>
   <si>
     <t xml:space="preserve">21.5081634521484</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8847465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7563667297363</t>
+    <t xml:space="preserve">21.8847484588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7563648223877</t>
   </si>
   <si>
     <t xml:space="preserve">22.2270965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9203567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4153919219971</t>
+    <t xml:space="preserve">22.9203586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4153938293457</t>
   </si>
   <si>
     <t xml:space="preserve">22.4239501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8077163696289</t>
+    <t xml:space="preserve">21.8077182769775</t>
   </si>
   <si>
     <t xml:space="preserve">22.0987167358398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1072750091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7392482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2428398132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4568099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4054584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9432849884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.130199432373</t>
+    <t xml:space="preserve">22.1072731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7392501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2428436279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.45680809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4054565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.943286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1302032470703</t>
   </si>
   <si>
     <t xml:space="preserve">20.1216430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3698482513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2685165405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3968963623047</t>
+    <t xml:space="preserve">20.3698463439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2685203552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.396900177002</t>
   </si>
   <si>
     <t xml:space="preserve">21.336986541748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3797817230225</t>
+    <t xml:space="preserve">21.3797779083252</t>
   </si>
   <si>
     <t xml:space="preserve">21.0117530822754</t>
@@ -1526,40 +1526,40 @@
     <t xml:space="preserve">20.6779632568359</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1743717193604</t>
+    <t xml:space="preserve">21.1743679046631</t>
   </si>
   <si>
     <t xml:space="preserve">20.8063430786133</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7977848052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9960136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5424022674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1914863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.909049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4554328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6509132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8563213348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8706893920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9305992126465</t>
+    <t xml:space="preserve">20.7977828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9960117340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5424003601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1914901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9090480804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.455436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6509113311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8563232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8706912994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9306011199951</t>
   </si>
   <si>
     <t xml:space="preserve">18.2729511260986</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">17.4427490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2558326721191</t>
+    <t xml:space="preserve">18.2558307647705</t>
   </si>
   <si>
     <t xml:space="preserve">17.9355735778809</t>
@@ -1577,19 +1577,19 @@
     <t xml:space="preserve">18.6260833740234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.245418548584</t>
+    <t xml:space="preserve">18.2454166412354</t>
   </si>
   <si>
     <t xml:space="preserve">18.1657447814941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1568927764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8119888305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2280673980713</t>
+    <t xml:space="preserve">18.1568908691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8119926452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2280654907227</t>
   </si>
   <si>
     <t xml:space="preserve">18.9978981018066</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">18.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2988872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1838035583496</t>
+    <t xml:space="preserve">19.2988891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1838054656982</t>
   </si>
   <si>
     <t xml:space="preserve">19.2103633880615</t>
@@ -1610,43 +1610,43 @@
     <t xml:space="preserve">19.4139747619629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.520206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5113563537598</t>
+    <t xml:space="preserve">19.5202045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5113544464111</t>
   </si>
   <si>
     <t xml:space="preserve">19.5644721984863</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7238178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.635290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4316787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1395397186279</t>
+    <t xml:space="preserve">19.723819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6352920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4316806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1395435333252</t>
   </si>
   <si>
     <t xml:space="preserve">19.0687217712402</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2369232177734</t>
+    <t xml:space="preserve">19.2369213104248</t>
   </si>
   <si>
     <t xml:space="preserve">19.6972599029541</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7503757476807</t>
+    <t xml:space="preserve">19.7503776550293</t>
   </si>
   <si>
     <t xml:space="preserve">19.8034934997559</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4405326843262</t>
+    <t xml:space="preserve">19.4405307769775</t>
   </si>
   <si>
     <t xml:space="preserve">19.2900371551514</t>
@@ -1655,28 +1655,28 @@
     <t xml:space="preserve">19.0333080291748</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5109977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3516483306885</t>
+    <t xml:space="preserve">18.5109996795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3516502380371</t>
   </si>
   <si>
     <t xml:space="preserve">18.8208427429199</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7765808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7942848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9182243347168</t>
+    <t xml:space="preserve">18.7765789031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.794282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9182262420654</t>
   </si>
   <si>
     <t xml:space="preserve">19.1129837036133</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4847984313965</t>
+    <t xml:space="preserve">19.4847965240479</t>
   </si>
   <si>
     <t xml:space="preserve">19.6707019805908</t>
@@ -1694,13 +1694,13 @@
     <t xml:space="preserve">19.0952758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">18.696907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1218338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2546253204346</t>
+    <t xml:space="preserve">18.6969051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1218357086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2546234130859</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906734466553</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">18.4136199951172</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6792011260986</t>
+    <t xml:space="preserve">18.6791973114014</t>
   </si>
   <si>
     <t xml:space="preserve">18.6880512237549</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">19.1483917236328</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9890441894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0510158538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5995235443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3427963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.431324005127</t>
+    <t xml:space="preserve">18.9890480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0510139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5995273590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3427982330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4313220977783</t>
   </si>
   <si>
     <t xml:space="preserve">18.3693561553955</t>
@@ -1739,40 +1739,40 @@
     <t xml:space="preserve">17.7585182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6965522766113</t>
+    <t xml:space="preserve">17.6965503692627</t>
   </si>
   <si>
     <t xml:space="preserve">17.4840850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9001598358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.417688369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.032600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6342258453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4527454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9392890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5719022750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346866607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4656715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7316055297852</t>
+    <t xml:space="preserve">17.9001636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4176902770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0325946807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6342277526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4527473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9392881393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5719032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346828460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4656686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7316036224365</t>
   </si>
   <si>
     <t xml:space="preserve">16.2712650299072</t>
@@ -1781,28 +1781,28 @@
     <t xml:space="preserve">15.7666606903076</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2133674621582</t>
+    <t xml:space="preserve">15.2133655548096</t>
   </si>
   <si>
     <t xml:space="preserve">15.1735305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6777801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2262907028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7840127944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6290884017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9743452072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0717258453369</t>
+    <t xml:space="preserve">14.6777791976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2262897491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7840118408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6290893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0717239379883</t>
   </si>
   <si>
     <t xml:space="preserve">15.1912364959717</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">15.7179718017578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.293399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171571731567</t>
+    <t xml:space="preserve">16.2933979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171581268311</t>
   </si>
   <si>
     <t xml:space="preserve">15.8596153259277</t>
@@ -1823,58 +1823,58 @@
     <t xml:space="preserve">16.0986366271973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1030616760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7755136489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4169807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7887945175171</t>
+    <t xml:space="preserve">16.1030654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7755146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4169797897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7887926101685</t>
   </si>
   <si>
     <t xml:space="preserve">15.4833745956421</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6910581588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2882595062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.204158782959</t>
+    <t xml:space="preserve">14.6910572052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2882604598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2041606903076</t>
   </si>
   <si>
     <t xml:space="preserve">13.8943147659302</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9739904403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8766107559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0802211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9916954040527</t>
+    <t xml:space="preserve">13.9739894866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8766098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0802221298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9916944503784</t>
   </si>
   <si>
     <t xml:space="preserve">13.7880830764771</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6243085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1554698944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3148193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.045166015625</t>
+    <t xml:space="preserve">13.6243076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1554689407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3148174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0451669692993</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254770278931</t>
@@ -1883,58 +1883,58 @@
     <t xml:space="preserve">14.1112060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.495943069458</t>
+    <t xml:space="preserve">13.4959449768066</t>
   </si>
   <si>
     <t xml:space="preserve">13.367579460144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2524938583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0669422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7707319259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.841552734375</t>
+    <t xml:space="preserve">13.2524948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0669431686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7707328796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8415536880493</t>
   </si>
   <si>
     <t xml:space="preserve">14.6954851150513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6512203216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8946723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0628709793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8813905715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.828275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9345064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4479627609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7131910324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1558256149292</t>
+    <t xml:space="preserve">14.651219367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8946704864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0628700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8813915252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8282737731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9345073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4479675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7131900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1558246612549</t>
   </si>
   <si>
     <t xml:space="preserve">15.2886161804199</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6958408355713</t>
+    <t xml:space="preserve">15.6958389282227</t>
   </si>
   <si>
     <t xml:space="preserve">16.3155288696289</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">16.0145359039307</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8020734786987</t>
+    <t xml:space="preserve">15.8020725250244</t>
   </si>
   <si>
     <t xml:space="preserve">16.1340484619141</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">16.2358531951904</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4793033599854</t>
+    <t xml:space="preserve">16.479305267334</t>
   </si>
   <si>
     <t xml:space="preserve">16.4748783111572</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">16.3376617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2181510925293</t>
+    <t xml:space="preserve">16.2181491851807</t>
   </si>
   <si>
     <t xml:space="preserve">16.288969039917</t>
@@ -1976,43 +1976,43 @@
     <t xml:space="preserve">16.5811100006104</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5412712097168</t>
+    <t xml:space="preserve">16.5412731170654</t>
   </si>
   <si>
     <t xml:space="preserve">16.7758693695068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4881572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7935752868652</t>
+    <t xml:space="preserve">16.4881553649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7935733795166</t>
   </si>
   <si>
     <t xml:space="preserve">16.6297988891602</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9263668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9481439590454</t>
+    <t xml:space="preserve">16.9263648986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9481401443481</t>
   </si>
   <si>
     <t xml:space="preserve">15.9304361343384</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9614219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5279941558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5368480682373</t>
+    <t xml:space="preserve">15.9614200592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5279960632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5368461608887</t>
   </si>
   <si>
     <t xml:space="preserve">16.6784896850586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5855369567871</t>
+    <t xml:space="preserve">16.5855388641357</t>
   </si>
   <si>
     <t xml:space="preserve">16.7138996124268</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">15.8197784423828</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0101108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8905992507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8463344573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3992738723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2930421829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9610643386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.987624168396</t>
+    <t xml:space="preserve">16.0101089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8906011581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8463373184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3992767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2930431365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9610662460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876251220703</t>
   </si>
   <si>
     <t xml:space="preserve">14.885817527771</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">14.3767871856689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4874448776245</t>
+    <t xml:space="preserve">14.4874467849731</t>
   </si>
   <si>
     <t xml:space="preserve">14.6069574356079</t>
@@ -2066,31 +2066,31 @@
     <t xml:space="preserve">14.7795848846436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4125518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2222204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0540180206299</t>
+    <t xml:space="preserve">15.4125528335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2222185134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0540189743042</t>
   </si>
   <si>
     <t xml:space="preserve">14.9212274551392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6423692703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9300813674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8592596054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1868095397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0230350494385</t>
+    <t xml:space="preserve">14.6423673629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.930079460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8592586517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1868085861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0230340957642</t>
   </si>
   <si>
     <t xml:space="preserve">14.9477872848511</t>
@@ -2099,19 +2099,19 @@
     <t xml:space="preserve">14.4476079940796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2436418533325</t>
+    <t xml:space="preserve">13.2436408996582</t>
   </si>
   <si>
     <t xml:space="preserve">13.5534858703613</t>
   </si>
   <si>
-    <t xml:space="preserve">13.655291557312</t>
+    <t xml:space="preserve">13.6552925109863</t>
   </si>
   <si>
     <t xml:space="preserve">13.6420125961304</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1997337341309</t>
+    <t xml:space="preserve">14.1997346878052</t>
   </si>
   <si>
     <t xml:space="preserve">14.4564619064331</t>
@@ -2126,118 +2126,118 @@
     <t xml:space="preserve">14.8459806442261</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2177963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0495929718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2089424133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0318880081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1823816299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.496298789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1820287704468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2000904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1381196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3151712417603</t>
+    <t xml:space="preserve">15.2177934646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0495910644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2089414596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0318870544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1823835372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4962997436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1820278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2000894546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1381187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">15.3063220977783</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6467952728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3723611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8589038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7748041152954</t>
+    <t xml:space="preserve">14.6467943191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3723621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8589029312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7748031616211</t>
   </si>
   <si>
     <t xml:space="preserve">13.597749710083</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7792282104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5888957977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6774225234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2170829772949</t>
+    <t xml:space="preserve">13.7792291641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5888977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6774234771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2170848846436</t>
   </si>
   <si>
     <t xml:space="preserve">13.5313529968262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.350227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3192434310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2705564498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6999101638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7353219985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9256553649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6600732803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7486009597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9079484939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2266473770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5807552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9127311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0942115783691</t>
+    <t xml:space="preserve">14.3502283096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3192443847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2705554962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.699912071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7353229522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9256544113159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6600742340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7486000061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9079523086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2266454696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.580756187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9127283096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0942134857178</t>
   </si>
   <si>
     <t xml:space="preserve">15.8584651947021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9808702468872</t>
+    <t xml:space="preserve">15.9808712005615</t>
   </si>
   <si>
     <t xml:space="preserve">15.8675327301025</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2302207946777</t>
+    <t xml:space="preserve">16.2302188873291</t>
   </si>
   <si>
     <t xml:space="preserve">16.4568958282471</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">16.5838394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5929069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6609115600586</t>
+    <t xml:space="preserve">16.592903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6609077453613</t>
   </si>
   <si>
     <t xml:space="preserve">16.7243785858154</t>
@@ -2258,88 +2258,88 @@
     <t xml:space="preserve">16.7425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4115619659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6427745819092</t>
+    <t xml:space="preserve">16.4115600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6427764892578</t>
   </si>
   <si>
     <t xml:space="preserve">16.9827938079834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9419898986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0326614379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.309211730957</t>
+    <t xml:space="preserve">16.9419918060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0326633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3092098236084</t>
   </si>
   <si>
     <t xml:space="preserve">17.4542846679688</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9646587371826</t>
+    <t xml:space="preserve">16.964656829834</t>
   </si>
   <si>
     <t xml:space="preserve">16.9555931091309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0462627410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0436496734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0935192108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1116542816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7262992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.141471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7833194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9283905029297</t>
+    <t xml:space="preserve">17.0462646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0436515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0935211181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1116561889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7263011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1414680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7833137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9283885955811</t>
   </si>
   <si>
     <t xml:space="preserve">17.5268230438232</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1505355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9963932037354</t>
+    <t xml:space="preserve">17.1505374908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9963970184326</t>
   </si>
   <si>
     <t xml:space="preserve">16.8875885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9601249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3726806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7787799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7923831939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7017097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.030740737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0715427398682</t>
+    <t xml:space="preserve">16.9601230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3726787567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7787818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7923851013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7017135620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0307426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0715446472168</t>
   </si>
   <si>
     <t xml:space="preserve">16.647310256958</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">16.8150501251221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5948257446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3862819671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0054626464844</t>
+    <t xml:space="preserve">17.5948276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3862838745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0054607391357</t>
   </si>
   <si>
     <t xml:space="preserve">16.9782600402832</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">17.2774753570557</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2276058197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0209846496582</t>
+    <t xml:space="preserve">17.2276077270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0209827423096</t>
   </si>
   <si>
     <t xml:space="preserve">18.0481853485107</t>
@@ -2375,37 +2375,37 @@
     <t xml:space="preserve">18.0073833465576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.206859588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7508907318115</t>
+    <t xml:space="preserve">18.2068614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7508888244629</t>
   </si>
   <si>
     <t xml:space="preserve">18.2975311279297</t>
   </si>
   <si>
-    <t xml:space="preserve">18.351936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2884616851807</t>
+    <t xml:space="preserve">18.3519344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2884654998779</t>
   </si>
   <si>
     <t xml:space="preserve">18.4244728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9775714874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.050106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0410404205322</t>
+    <t xml:space="preserve">18.9775695800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0501041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0410385131836</t>
   </si>
   <si>
     <t xml:space="preserve">18.3156661987305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7716388702393</t>
+    <t xml:space="preserve">17.7716369628906</t>
   </si>
   <si>
     <t xml:space="preserve">18.0617847442627</t>
@@ -2414,31 +2414,31 @@
     <t xml:space="preserve">17.8804416656494</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0889873504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9756488800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7353649139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7217655181885</t>
+    <t xml:space="preserve">18.0889892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9756507873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7353668212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7217674255371</t>
   </si>
   <si>
     <t xml:space="preserve">17.8623085021973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7126979827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0598659515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0508003234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9737243652344</t>
+    <t xml:space="preserve">17.7126998901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0598621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0507984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.973726272583</t>
   </si>
   <si>
     <t xml:space="preserve">17.096134185791</t>
@@ -2450,31 +2450,31 @@
     <t xml:space="preserve">17.2366752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7671051025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0753841400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4698104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5060749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7236881256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7146224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2703285217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1887264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5786113739014</t>
+    <t xml:space="preserve">17.7670993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0753860473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4698066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5060768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.723690032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.71462059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2703304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1887245178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5786151885986</t>
   </si>
   <si>
     <t xml:space="preserve">18.9594345092773</t>
@@ -2483,67 +2483,67 @@
     <t xml:space="preserve">18.7690238952637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7418212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7780914306641</t>
+    <t xml:space="preserve">18.7418251037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7780895233154</t>
   </si>
   <si>
     <t xml:space="preserve">19.2223815917969</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7120113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5216007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8117485046387</t>
+    <t xml:space="preserve">19.712007522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.521598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.81174659729</t>
   </si>
   <si>
     <t xml:space="preserve">19.4490623474121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3130550384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7962245941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4970092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1732025146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4225521087646</t>
+    <t xml:space="preserve">19.3130531311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7962265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4970073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1732044219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.422550201416</t>
   </si>
   <si>
     <t xml:space="preserve">17.8033695220947</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9121761322021</t>
+    <t xml:space="preserve">17.9121742248535</t>
   </si>
   <si>
     <t xml:space="preserve">18.0391178131104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9892482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0663204193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8596935272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9050331115723</t>
+    <t xml:space="preserve">17.9892501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0663166046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8596954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.905029296875</t>
   </si>
   <si>
     <t xml:space="preserve">18.7599582672119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3791332244873</t>
+    <t xml:space="preserve">18.3791370391846</t>
   </si>
   <si>
     <t xml:space="preserve">19.4399948120117</t>
@@ -2561,19 +2561,19 @@
     <t xml:space="preserve">19.5760021209717</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6394710540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4218578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7392101287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9477519989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0021591186523</t>
+    <t xml:space="preserve">19.6394729614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4218597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7392120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9477558135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0021553039551</t>
   </si>
   <si>
     <t xml:space="preserve">19.8661499023438</t>
@@ -2582,28 +2582,28 @@
     <t xml:space="preserve">19.485330581665</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6757392883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2133140563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1679782867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3221206665039</t>
+    <t xml:space="preserve">19.6757411956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2133159637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1679801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3221225738525</t>
   </si>
   <si>
     <t xml:space="preserve">19.0319728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2949199676514</t>
+    <t xml:space="preserve">19.2949180603027</t>
   </si>
   <si>
     <t xml:space="preserve">19.2677173614502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5941390991211</t>
+    <t xml:space="preserve">19.5941352844238</t>
   </si>
   <si>
     <t xml:space="preserve">19.8570823669434</t>
@@ -2612,16 +2612,16 @@
     <t xml:space="preserve">19.4127922058105</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9957065582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6602172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5332794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9322319030762</t>
+    <t xml:space="preserve">18.9957027435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6602191925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5332775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9322338104248</t>
   </si>
   <si>
     <t xml:space="preserve">19.4762630462646</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">20.0112247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9658908843994</t>
+    <t xml:space="preserve">19.9658889770508</t>
   </si>
   <si>
     <t xml:space="preserve">20.3376445770264</t>
@@ -2642,10 +2642,10 @@
     <t xml:space="preserve">20.9088726043701</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3259658813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5526428222656</t>
+    <t xml:space="preserve">21.325963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.552640914917</t>
   </si>
   <si>
     <t xml:space="preserve">22.0332012176514</t>
@@ -2657,22 +2657,22 @@
     <t xml:space="preserve">22.4049549102783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8337249755859</t>
+    <t xml:space="preserve">21.8337230682373</t>
   </si>
   <si>
     <t xml:space="preserve">20.9814109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">19.993091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1925716400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3039855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3855895996094</t>
+    <t xml:space="preserve">19.9930896759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.192569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3039875030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.385591506958</t>
   </si>
   <si>
     <t xml:space="preserve">18.4607391357422</t>
@@ -2690,52 +2690,52 @@
     <t xml:space="preserve">16.8195819854736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.468578338623</t>
+    <t xml:space="preserve">15.4685764312744</t>
   </si>
   <si>
     <t xml:space="preserve">14.6842670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8112077713013</t>
+    <t xml:space="preserve">14.811206817627</t>
   </si>
   <si>
     <t xml:space="preserve">12.653223991394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7412815093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.777551651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3170490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7341384887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1648263931274</t>
+    <t xml:space="preserve">13.741283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7775526046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3170480728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7341375350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1648283004761</t>
   </si>
   <si>
     <t xml:space="preserve">13.6914138793945</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0903692245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2690992355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0242862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0061511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2354440689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8863573074341</t>
+    <t xml:space="preserve">14.090368270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2691020965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0242853164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0061502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2354431152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">13.238055229187</t>
@@ -2744,67 +2744,67 @@
     <t xml:space="preserve">13.4783344268799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5327396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9660415649414</t>
+    <t xml:space="preserve">13.5327377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9660406112671</t>
   </si>
   <si>
     <t xml:space="preserve">13.4511346817017</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8092880249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1901082992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2581119537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3695297241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8727569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9634265899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7820844650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.294379234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.448522567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5346603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1512269973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3643054962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6544542312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5683145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346170425415</t>
+    <t xml:space="preserve">13.8092851638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1901073455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.258111000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3695306777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8727579116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9634284973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7820854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2943801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4485235214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5346593856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1512241363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3643045425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6544532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5683164596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3461713790894</t>
   </si>
   <si>
     <t xml:space="preserve">16.6291732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7768611907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7904605865479</t>
+    <t xml:space="preserve">15.7768592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7904634475708</t>
   </si>
   <si>
     <t xml:space="preserve">16.4478302001953</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">16.3752918243408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1097354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0398101806641</t>
+    <t xml:space="preserve">17.109733581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0398082733154</t>
   </si>
   <si>
     <t xml:space="preserve">17.2446327209473</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">16.4030952453613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8813438415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7066020965576</t>
+    <t xml:space="preserve">16.8813457489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7066040039062</t>
   </si>
   <si>
     <t xml:space="preserve">17.2906188964844</t>
@@ -2840,34 +2840,34 @@
     <t xml:space="preserve">17.9896011352539</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4515705108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.658504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6079216003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.355001449585</t>
+    <t xml:space="preserve">17.4515686035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6585063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6079196929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3549995422363</t>
   </si>
   <si>
     <t xml:space="preserve">17.6309127807617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9850025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8884334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6334018707275</t>
+    <t xml:space="preserve">17.9850044250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8884353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6333999633789</t>
   </si>
   <si>
     <t xml:space="preserve">18.7529640197754</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8081455230713</t>
+    <t xml:space="preserve">18.8081474304199</t>
   </si>
   <si>
     <t xml:space="preserve">18.67018699646</t>
@@ -2876,25 +2876,25 @@
     <t xml:space="preserve">17.7090873718262</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6631031036377</t>
+    <t xml:space="preserve">17.6631050109863</t>
   </si>
   <si>
     <t xml:space="preserve">17.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3482894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2885093688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5874156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9093132019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8173446655273</t>
+    <t xml:space="preserve">18.3482913970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2885055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5874137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9093151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8173427581787</t>
   </si>
   <si>
     <t xml:space="preserve">19.2220191955566</t>
@@ -2903,13 +2903,13 @@
     <t xml:space="preserve">18.7161750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9645004272461</t>
+    <t xml:space="preserve">18.9644985198975</t>
   </si>
   <si>
     <t xml:space="preserve">18.7897529602051</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0104846954346</t>
+    <t xml:space="preserve">19.0104827880859</t>
   </si>
   <si>
     <t xml:space="preserve">19.0748634338379</t>
@@ -2921,22 +2921,22 @@
     <t xml:space="preserve">19.3507766723633</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9761829376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9577865600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6542835235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7278614044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9301986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4703407287598</t>
+    <t xml:space="preserve">19.9761848449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9577903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6542854309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7278633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.930196762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4703388214111</t>
   </si>
   <si>
     <t xml:space="preserve">20.0957450866699</t>
@@ -2945,19 +2945,19 @@
     <t xml:space="preserve">20.2704906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3256740570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1534175872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9602756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3281650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0154609680176</t>
+    <t xml:space="preserve">20.3256759643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1534156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.960277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3281631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0154628753662</t>
   </si>
   <si>
     <t xml:space="preserve">21.0430507659912</t>
@@ -2972,22 +2972,22 @@
     <t xml:space="preserve">20.2337036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8934097290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8223190307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4176483154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3808574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.206111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5556030273438</t>
+    <t xml:space="preserve">19.8934078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8223209381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4176464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2061138153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5556049346924</t>
   </si>
   <si>
     <t xml:space="preserve">20.8775024414062</t>
@@ -2996,19 +2996,19 @@
     <t xml:space="preserve">21.0614452362061</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7303504943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7579402923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7395458221436</t>
+    <t xml:space="preserve">20.7303466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7579383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7395439147949</t>
   </si>
   <si>
     <t xml:space="preserve">20.6291809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2453880310059</t>
+    <t xml:space="preserve">21.2453899383545</t>
   </si>
   <si>
     <t xml:space="preserve">21.3649501800537</t>
@@ -3017,22 +3017,22 @@
     <t xml:space="preserve">21.4201354980469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4937133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.944372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5580921173096</t>
+    <t xml:space="preserve">21.4937114715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9443702697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5580902099609</t>
   </si>
   <si>
     <t xml:space="preserve">21.5213012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0271472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6040782928467</t>
+    <t xml:space="preserve">22.0271453857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.604076385498</t>
   </si>
   <si>
     <t xml:space="preserve">21.8156108856201</t>
@@ -3044,19 +3044,19 @@
     <t xml:space="preserve">21.7420330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1191177368164</t>
+    <t xml:space="preserve">22.1191158294678</t>
   </si>
   <si>
     <t xml:space="preserve">22.5145931243896</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6341571807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5421867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6433544158936</t>
+    <t xml:space="preserve">22.6341552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5421848297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6433525085449</t>
   </si>
   <si>
     <t xml:space="preserve">22.3674392700195</t>
@@ -3074,19 +3074,19 @@
     <t xml:space="preserve">22.4870014190674</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9008731842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8732833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8456916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2135753631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2411670684814</t>
+    <t xml:space="preserve">22.9008712768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8732795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8456935882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2135734558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2411689758301</t>
   </si>
   <si>
     <t xml:space="preserve">23.6550388336182</t>
@@ -3095,109 +3095,109 @@
     <t xml:space="preserve">23.5262794494629</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5722618103027</t>
+    <t xml:space="preserve">23.5722637176514</t>
   </si>
   <si>
     <t xml:space="preserve">24.0045299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7194194793701</t>
+    <t xml:space="preserve">23.7194213867188</t>
   </si>
   <si>
     <t xml:space="preserve">24.3356246948242</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3264293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.875768661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1700801849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.599853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6525497436523</t>
+    <t xml:space="preserve">24.3264312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8757705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1700782775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5998554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6525478363037</t>
   </si>
   <si>
     <t xml:space="preserve">22.7261257171631</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1926956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.66845703125</t>
+    <t xml:space="preserve">22.9560565948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1926918029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6684551239014</t>
   </si>
   <si>
     <t xml:space="preserve">21.1994018554688</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6500625610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4661197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0823268890381</t>
+    <t xml:space="preserve">21.6500644683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.466121673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0823287963867</t>
   </si>
   <si>
     <t xml:space="preserve">22.5881690979004</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0413188934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0112380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1216049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6274471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2988376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9677410125732</t>
+    <t xml:space="preserve">24.041316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0112400054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.121603012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2988395690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9677391052246</t>
   </si>
   <si>
     <t xml:space="preserve">23.3607292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8665752410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9217567443848</t>
+    <t xml:space="preserve">23.8665714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9217548370361</t>
   </si>
   <si>
     <t xml:space="preserve">23.9033603668213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4459915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0965023040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7403011322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2277507781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8966541290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4092063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5471630096436</t>
+    <t xml:space="preserve">24.4459934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0965003967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7402992248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2277488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8966484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4092044830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5471611022949</t>
   </si>
   <si>
     <t xml:space="preserve">25.0622005462646</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">25.3105239868164</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5680446624756</t>
+    <t xml:space="preserve">25.568042755127</t>
   </si>
   <si>
     <t xml:space="preserve">25.0805950164795</t>
@@ -3233,28 +3233,28 @@
     <t xml:space="preserve">25.3749027252197</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7151947021484</t>
+    <t xml:space="preserve">25.7151966094971</t>
   </si>
   <si>
     <t xml:space="preserve">25.9359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6257152557373</t>
+    <t xml:space="preserve">26.6257133483887</t>
   </si>
   <si>
     <t xml:space="preserve">26.5613327026367</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7452774047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8740367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0119934082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5546226501465</t>
+    <t xml:space="preserve">26.7452754974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8740348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0119972229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5546245574951</t>
   </si>
   <si>
     <t xml:space="preserve">28.2811985015869</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">25.8715476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1106758117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.843957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0278987884521</t>
+    <t xml:space="preserve">26.1106739044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8439559936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0279006958008</t>
   </si>
   <si>
     <t xml:space="preserve">25.7519855499268</t>
@@ -3293,13 +3293,13 @@
     <t xml:space="preserve">24.7127094268799</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2804412841797</t>
+    <t xml:space="preserve">24.2804431915283</t>
   </si>
   <si>
     <t xml:space="preserve">25.1449737548828</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5011749267578</t>
+    <t xml:space="preserve">24.5011730194092</t>
   </si>
   <si>
     <t xml:space="preserve">25.0346088409424</t>
@@ -3308,34 +3308,34 @@
     <t xml:space="preserve">25.236946105957</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6968040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.046293258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9175357818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.28542137146</t>
+    <t xml:space="preserve">25.6968021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0462951660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9175338745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2854194641113</t>
   </si>
   <si>
     <t xml:space="preserve">25.9267311096191</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9083385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1198711395264</t>
+    <t xml:space="preserve">25.9083366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.119873046875</t>
   </si>
   <si>
     <t xml:space="preserve">26.0003089904785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9635181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6600151062012</t>
+    <t xml:space="preserve">25.9635200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6600131988525</t>
   </si>
   <si>
     <t xml:space="preserve">25.0530033111572</t>
@@ -3347,25 +3347,25 @@
     <t xml:space="preserve">24.3908100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1608791351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.556360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5195693969727</t>
+    <t xml:space="preserve">24.1608810424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5563583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5195713043213</t>
   </si>
   <si>
     <t xml:space="preserve">25.0162162780762</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9150447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9058513641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0137252807617</t>
+    <t xml:space="preserve">24.9150485992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9058475494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0137271881104</t>
   </si>
   <si>
     <t xml:space="preserve">24.2712478637695</t>
@@ -3380,52 +3380,52 @@
     <t xml:space="preserve">23.6734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5446739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6918277740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4251079559326</t>
+    <t xml:space="preserve">23.5446720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6918258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4251098632812</t>
   </si>
   <si>
     <t xml:space="preserve">23.3055477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5170822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7838020324707</t>
+    <t xml:space="preserve">23.5170783996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7838001251221</t>
   </si>
   <si>
     <t xml:space="preserve">24.1056976318359</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1516857147217</t>
+    <t xml:space="preserve">24.151683807373</t>
   </si>
   <si>
     <t xml:space="preserve">24.5287666320801</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8138790130615</t>
+    <t xml:space="preserve">24.8138771057129</t>
   </si>
   <si>
     <t xml:space="preserve">24.8322734832764</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9886226654053</t>
+    <t xml:space="preserve">24.9886264801025</t>
   </si>
   <si>
     <t xml:space="preserve">25.4852695465088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7703819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6416168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8414688110352</t>
+    <t xml:space="preserve">25.770378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6416187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8414707183838</t>
   </si>
   <si>
     <t xml:space="preserve">24.6943168640137</t>
@@ -3437,13 +3437,13 @@
     <t xml:space="preserve">24.9518337249756</t>
   </si>
   <si>
-    <t xml:space="preserve">25.33811378479</t>
+    <t xml:space="preserve">25.3381156921387</t>
   </si>
   <si>
     <t xml:space="preserve">24.4919757843018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5379619598389</t>
+    <t xml:space="preserve">24.5379638671875</t>
   </si>
   <si>
     <t xml:space="preserve">24.4367942810059</t>
@@ -3452,31 +3452,31 @@
     <t xml:space="preserve">23.9861354827881</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9585456848145</t>
+    <t xml:space="preserve">23.9585437774658</t>
   </si>
   <si>
     <t xml:space="preserve">24.4000072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9493465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7954807281494</t>
+    <t xml:space="preserve">23.949348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7954845428467</t>
   </si>
   <si>
     <t xml:space="preserve">24.2252616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3197231292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4693622589111</t>
+    <t xml:space="preserve">25.3197212219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4693641662598</t>
   </si>
   <si>
     <t xml:space="preserve">26.4325752258301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2762203216553</t>
+    <t xml:space="preserve">26.2762222290039</t>
   </si>
   <si>
     <t xml:space="preserve">26.3323879241943</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">26.1826133728027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1919746398926</t>
+    <t xml:space="preserve">26.1919727325439</t>
   </si>
   <si>
     <t xml:space="preserve">26.5196075439453</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">27.3901786804199</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5867576599121</t>
+    <t xml:space="preserve">27.5867595672607</t>
   </si>
   <si>
     <t xml:space="preserve">27.7926998138428</t>
@@ -3515,22 +3515,22 @@
     <t xml:space="preserve">27.7084503173828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8769454956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3340129852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2872066497803</t>
+    <t xml:space="preserve">27.8769474029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3340110778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2872047424316</t>
   </si>
   <si>
     <t xml:space="preserve">27.3808155059814</t>
   </si>
   <si>
-    <t xml:space="preserve">27.699089050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1935958862305</t>
+    <t xml:space="preserve">27.6990909576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1935977935791</t>
   </si>
   <si>
     <t xml:space="preserve">27.1655139923096</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">27.8395023345947</t>
   </si>
   <si>
-    <t xml:space="preserve">27.802059173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.401159286499</t>
+    <t xml:space="preserve">27.8020610809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4011611938477</t>
   </si>
   <si>
     <t xml:space="preserve">28.5602989196777</t>
@@ -3563,28 +3563,28 @@
     <t xml:space="preserve">28.3169136047363</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5041332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.382438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4479637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7568759918213</t>
+    <t xml:space="preserve">28.5041313171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3824367523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4479656219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7568778991699</t>
   </si>
   <si>
     <t xml:space="preserve">27.9799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5696582794189</t>
+    <t xml:space="preserve">28.5696563720703</t>
   </si>
   <si>
     <t xml:space="preserve">28.8317642211914</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7943210601807</t>
+    <t xml:space="preserve">28.7943229675293</t>
   </si>
   <si>
     <t xml:space="preserve">28.691349029541</t>
@@ -3614,13 +3614,13 @@
     <t xml:space="preserve">28.2701091766357</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1390533447266</t>
+    <t xml:space="preserve">28.1390514373779</t>
   </si>
   <si>
     <t xml:space="preserve">28.2888298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4854125976562</t>
+    <t xml:space="preserve">28.4854106903076</t>
   </si>
   <si>
     <t xml:space="preserve">28.3637161254883</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">28.7849597930908</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8785724639893</t>
+    <t xml:space="preserve">28.8785705566406</t>
   </si>
   <si>
     <t xml:space="preserve">29.0002613067627</t>
@@ -3638,22 +3638,22 @@
     <t xml:space="preserve">29.3934230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2359085083008</t>
+    <t xml:space="preserve">30.2359104156494</t>
   </si>
   <si>
     <t xml:space="preserve">30.3201580047607</t>
   </si>
   <si>
-    <t xml:space="preserve">30.179744720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8146686553955</t>
+    <t xml:space="preserve">30.1797466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8146648406982</t>
   </si>
   <si>
     <t xml:space="preserve">29.992525100708</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9550819396973</t>
+    <t xml:space="preserve">29.9550800323486</t>
   </si>
   <si>
     <t xml:space="preserve">29.8989162445068</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">29.5619220733643</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5057544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7585029602051</t>
+    <t xml:space="preserve">29.5057563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7585010528564</t>
   </si>
   <si>
     <t xml:space="preserve">29.805305480957</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">29.8708343505859</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9082775115967</t>
+    <t xml:space="preserve">29.908275604248</t>
   </si>
   <si>
     <t xml:space="preserve">29.8333911895752</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">30.8537330627441</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0018844604492</t>
+    <t xml:space="preserve">30.0018863677979</t>
   </si>
   <si>
     <t xml:space="preserve">30.5448246002197</t>
@@ -3722,16 +3722,16 @@
     <t xml:space="preserve">29.6461696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3185348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.029972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.348237991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6742515563965</t>
+    <t xml:space="preserve">29.3185367584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0299701690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3482398986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6742534637451</t>
   </si>
   <si>
     <t xml:space="preserve">28.9534587860107</t>
@@ -3743,13 +3743,13 @@
     <t xml:space="preserve">28.2420253753662</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5212287902832</t>
+    <t xml:space="preserve">27.5212306976318</t>
   </si>
   <si>
     <t xml:space="preserve">27.4837875366211</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0267238616943</t>
+    <t xml:space="preserve">28.0267219543457</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773963928223</t>
@@ -3761,16 +3761,16 @@
     <t xml:space="preserve">28.6445465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2249240875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2717323303223</t>
+    <t xml:space="preserve">29.224925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2717304229736</t>
   </si>
   <si>
     <t xml:space="preserve">29.2623691558838</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5244789123535</t>
+    <t xml:space="preserve">29.5244770050049</t>
   </si>
   <si>
     <t xml:space="preserve">29.7304172515869</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">30.4792976379395</t>
   </si>
   <si>
-    <t xml:space="preserve">30.591625213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.36696434021</t>
+    <t xml:space="preserve">30.5916271209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3669624328613</t>
   </si>
   <si>
     <t xml:space="preserve">30.6384315490723</t>
@@ -3794,55 +3794,55 @@
     <t xml:space="preserve">30.6103496551514</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7694854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3030567169189</t>
+    <t xml:space="preserve">30.7694835662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3030586242676</t>
   </si>
   <si>
     <t xml:space="preserve">30.9286231994629</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1626472473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.668140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8553581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4341144561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1813678741455</t>
+    <t xml:space="preserve">31.1626491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6681385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.855354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4341163635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1813659667969</t>
   </si>
   <si>
     <t xml:space="preserve">31.2749767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8179187774658</t>
+    <t xml:space="preserve">31.8179168701172</t>
   </si>
   <si>
     <t xml:space="preserve">31.9302406311035</t>
   </si>
   <si>
-    <t xml:space="preserve">32.810173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7633666992188</t>
+    <t xml:space="preserve">32.8101768493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.763370513916</t>
   </si>
   <si>
     <t xml:space="preserve">32.6416778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9489669799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6962203979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1081008911133</t>
+    <t xml:space="preserve">31.9489688873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6962184906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1081047058105</t>
   </si>
   <si>
     <t xml:space="preserve">30.6945972442627</t>
@@ -3854,28 +3854,28 @@
     <t xml:space="preserve">30.7320442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5822658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8911800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.752384185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9473438262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7039566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3576011657715</t>
+    <t xml:space="preserve">30.5822639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8911781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7523822784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9473457336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7039585113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3576049804688</t>
   </si>
   <si>
     <t xml:space="preserve">30.0861339569092</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1516609191895</t>
+    <t xml:space="preserve">30.1516590118408</t>
   </si>
   <si>
     <t xml:space="preserve">29.5525588989258</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">29.702335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7507629394531</t>
+    <t xml:space="preserve">30.7507610321045</t>
   </si>
   <si>
     <t xml:space="preserve">30.9754276275635</t>
@@ -3893,16 +3893,16 @@
     <t xml:space="preserve">30.9379806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">31.069034576416</t>
+    <t xml:space="preserve">31.0690364837646</t>
   </si>
   <si>
     <t xml:space="preserve">30.9567050933838</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9941482543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9660682678223</t>
+    <t xml:space="preserve">30.9941463470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9660663604736</t>
   </si>
   <si>
     <t xml:space="preserve">31.2936992645264</t>
@@ -3911,25 +3911,25 @@
     <t xml:space="preserve">31.2468948364258</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2656154632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.602611541748</t>
+    <t xml:space="preserve">31.2656173706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6026096343994</t>
   </si>
   <si>
     <t xml:space="preserve">31.7804718017578</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3779468536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5073776245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9721794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6335620880127</t>
+    <t xml:space="preserve">31.377950668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5073757171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9721813201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6335639953613</t>
   </si>
   <si>
     <t xml:space="preserve">27.0063800811768</t>
@@ -3941,22 +3941,22 @@
     <t xml:space="preserve">26.8378810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2045822143555</t>
+    <t xml:space="preserve">28.2045803070068</t>
   </si>
   <si>
     <t xml:space="preserve">28.0548057556152</t>
   </si>
   <si>
-    <t xml:space="preserve">27.118709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9298667907715</t>
+    <t xml:space="preserve">27.1187076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9298686981201</t>
   </si>
   <si>
     <t xml:space="preserve">26.0421962738037</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8191566467285</t>
+    <t xml:space="preserve">26.8191604614258</t>
   </si>
   <si>
     <t xml:space="preserve">26.5664100646973</t>
@@ -3968,19 +3968,19 @@
     <t xml:space="preserve">25.7800922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5102462768555</t>
+    <t xml:space="preserve">26.5102481842041</t>
   </si>
   <si>
     <t xml:space="preserve">27.3152904510498</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9970149993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1264476776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.229419708252</t>
+    <t xml:space="preserve">26.9970169067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1264495849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2294178009033</t>
   </si>
   <si>
     <t xml:space="preserve">26.1077251434326</t>
@@ -3995,10 +3995,10 @@
     <t xml:space="preserve">27.4463405609131</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9766712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.13743019104</t>
+    <t xml:space="preserve">25.9766731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1374282836914</t>
   </si>
   <si>
     <t xml:space="preserve">26.9502124786377</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">29.121955871582</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1406764984131</t>
+    <t xml:space="preserve">29.1406784057617</t>
   </si>
   <si>
     <t xml:space="preserve">28.8598480224609</t>
@@ -4034,16 +4034,16 @@
     <t xml:space="preserve">28.6071033477783</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2326622009277</t>
+    <t xml:space="preserve">28.2326641082764</t>
   </si>
   <si>
     <t xml:space="preserve">28.8692092895508</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0096225738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2904529571533</t>
+    <t xml:space="preserve">29.0096244812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.290454864502</t>
   </si>
   <si>
     <t xml:space="preserve">28.9815406799316</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">27.0531826019287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5586757659912</t>
+    <t xml:space="preserve">27.5586776733398</t>
   </si>
   <si>
     <t xml:space="preserve">28.8972930908203</t>
@@ -4082,19 +4082,19 @@
     <t xml:space="preserve">29.1981182098389</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2171840667725</t>
+    <t xml:space="preserve">29.2171821594238</t>
   </si>
   <si>
     <t xml:space="preserve">29.5222244262695</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7605361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6452312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0265350341797</t>
+    <t xml:space="preserve">29.7605381011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6452331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0265331268311</t>
   </si>
   <si>
     <t xml:space="preserve">29.045597076416</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">26.7482604980469</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0247058868408</t>
+    <t xml:space="preserve">27.0247039794922</t>
   </si>
   <si>
     <t xml:space="preserve">27.1104965209961</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052722930908</t>
+    <t xml:space="preserve">26.6052742004395</t>
   </si>
   <si>
     <t xml:space="preserve">26.7101306915283</t>
@@ -4127,13 +4127,13 @@
     <t xml:space="preserve">26.9675102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">27.215353012085</t>
+    <t xml:space="preserve">27.2153549194336</t>
   </si>
   <si>
     <t xml:space="preserve">27.7682399749756</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5299263000488</t>
+    <t xml:space="preserve">27.5299282073975</t>
   </si>
   <si>
     <t xml:space="preserve">27.8635654449463</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">29.4459648132324</t>
   </si>
   <si>
-    <t xml:space="preserve">28.654764175415</t>
+    <t xml:space="preserve">28.6547622680664</t>
   </si>
   <si>
     <t xml:space="preserve">27.9207630157471</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">28.397388458252</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9684238433838</t>
+    <t xml:space="preserve">27.9684257507324</t>
   </si>
   <si>
     <t xml:space="preserve">28.1304759979248</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">28.4450492858887</t>
   </si>
   <si>
-    <t xml:space="preserve">26.643404006958</t>
+    <t xml:space="preserve">26.6434020996094</t>
   </si>
   <si>
     <t xml:space="preserve">26.3860263824463</t>
@@ -4193,13 +4193,13 @@
     <t xml:space="preserve">26.481351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2430381774902</t>
+    <t xml:space="preserve">26.2430362701416</t>
   </si>
   <si>
     <t xml:space="preserve">26.1667785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5280990600586</t>
+    <t xml:space="preserve">25.52809715271</t>
   </si>
   <si>
     <t xml:space="preserve">25.0133419036865</t>
@@ -4220,25 +4220,25 @@
     <t xml:space="preserve">24.9847431182861</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7464294433594</t>
+    <t xml:space="preserve">24.746431350708</t>
   </si>
   <si>
     <t xml:space="preserve">24.765495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3937282562256</t>
+    <t xml:space="preserve">24.393726348877</t>
   </si>
   <si>
     <t xml:space="preserve">24.6987686157227</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3374462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9189300537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1658592224121</t>
+    <t xml:space="preserve">25.3374481201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9189319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1658611297607</t>
   </si>
   <si>
     <t xml:space="preserve">25.2993183135986</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">24.9084815979004</t>
   </si>
   <si>
-    <t xml:space="preserve">25.346981048584</t>
+    <t xml:space="preserve">25.3469791412354</t>
   </si>
   <si>
     <t xml:space="preserve">26.2144393920898</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">25.9093990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4908847808838</t>
+    <t xml:space="preserve">26.4908828735352</t>
   </si>
   <si>
     <t xml:space="preserve">27.0532989501953</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">27.0437698364258</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6815338134766</t>
+    <t xml:space="preserve">26.6815319061279</t>
   </si>
   <si>
     <t xml:space="preserve">27.2630176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7882232666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5031585693359</t>
+    <t xml:space="preserve">28.7882213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5031604766846</t>
   </si>
   <si>
     <t xml:space="preserve">29.4745616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5508213043213</t>
+    <t xml:space="preserve">29.5508232116699</t>
   </si>
   <si>
     <t xml:space="preserve">29.6461486816406</t>
@@ -4298,19 +4298,19 @@
     <t xml:space="preserve">29.9893169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9797859191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8939933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0760269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.705171585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7995853424072</t>
+    <t xml:space="preserve">29.9797878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8939952850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0760250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7051734924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7995834350586</t>
   </si>
   <si>
     <t xml:space="preserve">31.0283622741699</t>
@@ -4340,19 +4340,19 @@
     <t xml:space="preserve">29.3792362213135</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5317573547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1790542602539</t>
+    <t xml:space="preserve">29.5317554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1790561676025</t>
   </si>
   <si>
     <t xml:space="preserve">29.1885871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4554958343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3610877990723</t>
+    <t xml:space="preserve">29.4554977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3610858917236</t>
   </si>
   <si>
     <t xml:space="preserve">30.7328567504883</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">30.5326709747314</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3515529632568</t>
+    <t xml:space="preserve">30.3515548706055</t>
   </si>
   <si>
     <t xml:space="preserve">30.389684677124</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">29.874927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2362480163574</t>
+    <t xml:space="preserve">29.2362499237061</t>
   </si>
   <si>
     <t xml:space="preserve">28.0160865783691</t>
@@ -4415,10 +4415,10 @@
     <t xml:space="preserve">29.7128753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6842784881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2648487091064</t>
+    <t xml:space="preserve">29.6842765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2648468017578</t>
   </si>
   <si>
     <t xml:space="preserve">29.7033424377441</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">29.3983020782471</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7700691223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7510051727295</t>
+    <t xml:space="preserve">29.7700710296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7510032653809</t>
   </si>
   <si>
     <t xml:space="preserve">30.5422058105469</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">30.4945411682129</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6661243438721</t>
+    <t xml:space="preserve">30.6661262512207</t>
   </si>
   <si>
     <t xml:space="preserve">30.8472461700439</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">31.1236896514893</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9434833526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.981616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7242374420166</t>
+    <t xml:space="preserve">31.9434814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9816188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7242336273193</t>
   </si>
   <si>
     <t xml:space="preserve">31.5717163085938</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">30.9521026611328</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5136051177979</t>
+    <t xml:space="preserve">30.5136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">30.942569732666</t>
@@ -4487,13 +4487,13 @@
     <t xml:space="preserve">32.5535697937012</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6289100646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8853759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3715324401855</t>
+    <t xml:space="preserve">31.6289119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8853778839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3715343475342</t>
   </si>
   <si>
     <t xml:space="preserve">30.7709846496582</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">31.0950889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">31.0378971099854</t>
+    <t xml:space="preserve">31.037899017334</t>
   </si>
   <si>
     <t xml:space="preserve">31.476390838623</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">32.1055374145508</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1246070861816</t>
+    <t xml:space="preserve">32.1246032714844</t>
   </si>
   <si>
     <t xml:space="preserve">32.143669128418</t>
@@ -4526,13 +4526,13 @@
     <t xml:space="preserve">31.8386287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9244251251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1341361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2675895690918</t>
+    <t xml:space="preserve">31.9244213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1341323852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2675933837891</t>
   </si>
   <si>
     <t xml:space="preserve">32.8300094604492</t>
@@ -4541,10 +4541,10 @@
     <t xml:space="preserve">33.1064491271973</t>
   </si>
   <si>
-    <t xml:space="preserve">33.840461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5926170349121</t>
+    <t xml:space="preserve">33.8404579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5926132202148</t>
   </si>
   <si>
     <t xml:space="preserve">33.9167213439941</t>
@@ -4553,19 +4553,19 @@
     <t xml:space="preserve">33.9357833862305</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1445846557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3543014526367</t>
+    <t xml:space="preserve">33.144588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3542976379395</t>
   </si>
   <si>
     <t xml:space="preserve">33.6116752624512</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4686889648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6021461486816</t>
+    <t xml:space="preserve">33.468692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6021423339844</t>
   </si>
   <si>
     <t xml:space="preserve">33.3161697387695</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">33.3066368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6593399047852</t>
+    <t xml:space="preserve">33.6593437194824</t>
   </si>
   <si>
     <t xml:space="preserve">33.0397262573242</t>
@@ -4601,7 +4601,7 @@
     <t xml:space="preserve">33.373363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9539337158203</t>
+    <t xml:space="preserve">32.953929901123</t>
   </si>
   <si>
     <t xml:space="preserve">33.3638305664062</t>
@@ -4610,10 +4610,10 @@
     <t xml:space="preserve">33.4114952087402</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5830764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0311126708984</t>
+    <t xml:space="preserve">33.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0311088562012</t>
   </si>
   <si>
     <t xml:space="preserve">34.7937126159668</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">35.0892181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5649299621582</t>
+    <t xml:space="preserve">34.5649261474609</t>
   </si>
   <si>
     <t xml:space="preserve">35.2512702941895</t>
@@ -4637,10 +4637,10 @@
     <t xml:space="preserve">35.5372467041016</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5753746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7469635009766</t>
+    <t xml:space="preserve">35.5753784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7469596862793</t>
   </si>
   <si>
     <t xml:space="preserve">35.3942604064941</t>
@@ -4667,19 +4667,19 @@
     <t xml:space="preserve">34.9843635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5563125610352</t>
+    <t xml:space="preserve">35.5563087463379</t>
   </si>
   <si>
     <t xml:space="preserve">35.3370628356934</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8327560424805</t>
+    <t xml:space="preserve">35.8327522277832</t>
   </si>
   <si>
     <t xml:space="preserve">36.1568603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">35.937614440918</t>
+    <t xml:space="preserve">35.9376106262207</t>
   </si>
   <si>
     <t xml:space="preserve">35.270336151123</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">34.8413696289062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6697883605957</t>
+    <t xml:space="preserve">34.6697845458984</t>
   </si>
   <si>
     <t xml:space="preserve">34.9557609558105</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">34.6888542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1759300231934</t>
+    <t xml:space="preserve">36.1759262084961</t>
   </si>
   <si>
     <t xml:space="preserve">36.1282615661621</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">36.0615386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7097473144531</t>
+    <t xml:space="preserve">36.7097434997559</t>
   </si>
   <si>
     <t xml:space="preserve">37.8631858825684</t>
@@ -4730,13 +4730,13 @@
     <t xml:space="preserve">34.9748268127441</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6707000732422</t>
+    <t xml:space="preserve">35.6707038879395</t>
   </si>
   <si>
     <t xml:space="preserve">33.7546653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2312927246094</t>
+    <t xml:space="preserve">34.2312889099121</t>
   </si>
   <si>
     <t xml:space="preserve">33.8881187438965</t>
@@ -4745,10 +4745,10 @@
     <t xml:space="preserve">34.3552169799805</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1082878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1178169250488</t>
+    <t xml:space="preserve">35.108283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1178131103516</t>
   </si>
   <si>
     <t xml:space="preserve">34.7746429443359</t>
@@ -4757,13 +4757,13 @@
     <t xml:space="preserve">34.8509063720703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3761100769043</t>
+    <t xml:space="preserve">36.376106262207</t>
   </si>
   <si>
     <t xml:space="preserve">36.5953559875488</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8908653259277</t>
+    <t xml:space="preserve">36.890869140625</t>
   </si>
   <si>
     <t xml:space="preserve">36.2235870361328</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">35.9090118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5286254882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4619026184082</t>
+    <t xml:space="preserve">36.5286293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4618988037109</t>
   </si>
   <si>
     <t xml:space="preserve">36.2807846069336</t>
@@ -6471,6 +6471,9 @@
   </si>
   <si>
     <t xml:space="preserve">88.0199966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0199966430664</t>
   </si>
 </sst>
 </file>
@@ -71835,7 +71838,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6940972222</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>1158584</v>
@@ -71856,6 +71859,32 @@
         <v>2141</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6912847222</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>868452</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>88.0199966430664</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>90.3399963378906</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>89.0199966430664</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>2153</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRY.MI.xlsx
+++ b/data/PRY.MI.xlsx
@@ -38,88 +38,88 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6851577758789</t>
+    <t xml:space="preserve">15.6851558685303</t>
   </si>
   <si>
     <t xml:space="preserve">PRY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8714027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3207607269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2397832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.74582862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9644641876221</t>
+    <t xml:space="preserve">15.8714017868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.320761680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2397842407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7458295822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9644632339478</t>
   </si>
   <si>
     <t xml:space="preserve">15.2964668273926</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4989137649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0616359710693</t>
+    <t xml:space="preserve">15.498911857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.061637878418</t>
   </si>
   <si>
     <t xml:space="preserve">14.5029001235962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5433893203735</t>
+    <t xml:space="preserve">14.5433883666992</t>
   </si>
   <si>
     <t xml:space="preserve">14.8510980606079</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1870899200439</t>
+    <t xml:space="preserve">14.1870889663696</t>
   </si>
   <si>
     <t xml:space="preserve">14.9401721954346</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4098377227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9239768981934</t>
+    <t xml:space="preserve">15.4098339080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9239749908447</t>
   </si>
   <si>
     <t xml:space="preserve">15.2802753448486</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1831007003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.624363899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936395645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8106079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7296314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8996829986572</t>
+    <t xml:space="preserve">15.1831035614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.624361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936405181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8106098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7296333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8996820449829</t>
   </si>
   <si>
     <t xml:space="preserve">14.5190944671631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7336225509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.344934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0980157852173</t>
+    <t xml:space="preserve">13.73362159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3449325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0980176925659</t>
   </si>
   <si>
     <t xml:space="preserve">13.3206405639648</t>
@@ -131,100 +131,100 @@
     <t xml:space="preserve">13.8955745697021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7822046279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3328466415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2194805145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.405725479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8348999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5514822006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3409471511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8672924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1021223068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2235908508301</t>
+    <t xml:space="preserve">13.782205581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3328485488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2194786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057273864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8349027633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5514869689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3409490585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8672895431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1021270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.223593711853</t>
   </si>
   <si>
     <t xml:space="preserve">15.4827146530151</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3774452209473</t>
+    <t xml:space="preserve">15.3774480819702</t>
   </si>
   <si>
     <t xml:space="preserve">15.4017362594604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4665203094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4908103942871</t>
+    <t xml:space="preserve">15.4665222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4908123016357</t>
   </si>
   <si>
     <t xml:space="preserve">15.5232038497925</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5636892318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.142614364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7742280960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8390130996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.587984085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6365699768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9199867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8309106826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8794975280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8228139877319</t>
+    <t xml:space="preserve">15.5636901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1426115036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7742319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8390083312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5879850387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.636570930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9199876785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8309154510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8795013427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8228158950806</t>
   </si>
   <si>
     <t xml:space="preserve">15.8956937789917</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2762813568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1224269866943</t>
+    <t xml:space="preserve">16.2762851715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1224308013916</t>
   </si>
   <si>
     <t xml:space="preserve">15.8471059799194</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8876008987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4422273635864</t>
+    <t xml:space="preserve">15.8875961303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4422254562378</t>
   </si>
   <si>
     <t xml:space="preserve">15.3855419158936</t>
@@ -239,40 +239,40 @@
     <t xml:space="preserve">16.7135581970215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6568737030029</t>
+    <t xml:space="preserve">16.6568756103516</t>
   </si>
   <si>
     <t xml:space="preserve">16.430139541626</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6120529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9180011749268</t>
+    <t xml:space="preserve">16.6120548248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9179992675781</t>
   </si>
   <si>
     <t xml:space="preserve">17.0254955291748</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9758815765381</t>
+    <t xml:space="preserve">16.9758796691895</t>
   </si>
   <si>
     <t xml:space="preserve">16.9924201965332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6285915374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7774295806885</t>
+    <t xml:space="preserve">16.6285934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7774314880371</t>
   </si>
   <si>
     <t xml:space="preserve">16.9841499328613</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1081848144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9345397949219</t>
+    <t xml:space="preserve">17.1081809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9345378875732</t>
   </si>
   <si>
     <t xml:space="preserve">16.5541744232178</t>
@@ -281,43 +281,43 @@
     <t xml:space="preserve">16.595516204834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.760892868042</t>
+    <t xml:space="preserve">16.7608909606934</t>
   </si>
   <si>
     <t xml:space="preserve">16.7030086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8766574859619</t>
+    <t xml:space="preserve">16.8766593933105</t>
   </si>
   <si>
     <t xml:space="preserve">17.4058609008789</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7696857452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0094871520996</t>
+    <t xml:space="preserve">17.7696876525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0094833374023</t>
   </si>
   <si>
     <t xml:space="preserve">17.9681396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8606452941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7779598236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8854503631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6952705383301</t>
+    <t xml:space="preserve">17.8606472015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7779560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8854522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6952686309814</t>
   </si>
   <si>
     <t xml:space="preserve">18.1087093353271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9598731994629</t>
+    <t xml:space="preserve">17.9598693847656</t>
   </si>
   <si>
     <t xml:space="preserve">18.2658176422119</t>
@@ -332,106 +332,106 @@
     <t xml:space="preserve">18.2988929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4725379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1831321716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1335163116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0425624847412</t>
+    <t xml:space="preserve">18.4725399017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1831283569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1335182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0425605773926</t>
   </si>
   <si>
     <t xml:space="preserve">17.8027648925781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0921726226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9185256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0012111663818</t>
+    <t xml:space="preserve">18.0921745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9185276031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0012130737305</t>
   </si>
   <si>
     <t xml:space="preserve">17.3149032592773</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9097290039062</t>
+    <t xml:space="preserve">16.9097309112549</t>
   </si>
   <si>
     <t xml:space="preserve">16.6368637084961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8022365570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7366123199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5712413787842</t>
+    <t xml:space="preserve">16.8022384643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7366161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5712375640869</t>
   </si>
   <si>
     <t xml:space="preserve">17.3479785919189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9102592468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6694049835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8342580795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1402044296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2399578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2978382110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7272901535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5867195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2311611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6115255355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2812995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6533966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6864738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6782035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7443542480469</t>
+    <t xml:space="preserve">17.9102573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6694078445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8342599868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1402072906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2559671401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2399616241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2978363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7272920608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.586724281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2311592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6115274429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2813014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4632129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6533985137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6864719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.678201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7443561553955</t>
   </si>
   <si>
     <t xml:space="preserve">16.6699371337891</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8435840606689</t>
+    <t xml:space="preserve">16.8435821533203</t>
   </si>
   <si>
     <t xml:space="preserve">16.8187732696533</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">16.9510765075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0999126434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1164493560791</t>
+    <t xml:space="preserve">17.0999164581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1164531707764</t>
   </si>
   <si>
     <t xml:space="preserve">17.2983684539795</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2404842376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0751113891602</t>
+    <t xml:space="preserve">17.2404823303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0751094818115</t>
   </si>
   <si>
     <t xml:space="preserve">17.3314418792725</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">17.620849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1004428863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125793457031</t>
+    <t xml:space="preserve">18.1004409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125831604004</t>
   </si>
   <si>
     <t xml:space="preserve">17.5960426330566</t>
@@ -479,22 +479,22 @@
     <t xml:space="preserve">17.8771839141846</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1914005279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2492790222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0839061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2906227111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1665916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9929447174072</t>
+    <t xml:space="preserve">18.1913986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2492809295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0839023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2906246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1665897369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9929466247559</t>
   </si>
   <si>
     <t xml:space="preserve">17.8441066741943</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">17.7200756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7283458709717</t>
+    <t xml:space="preserve">17.728343963623</t>
   </si>
   <si>
     <t xml:space="preserve">17.8937225341797</t>
@@ -512,79 +512,79 @@
     <t xml:space="preserve">18.0673675537109</t>
   </si>
   <si>
-    <t xml:space="preserve">18.37331199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9438629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4317188262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3573017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1009693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1257762908936</t>
+    <t xml:space="preserve">18.3733158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9438591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4317207336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3573036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1009674072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1257743835449</t>
   </si>
   <si>
     <t xml:space="preserve">19.1919250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1753902435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2828807830811</t>
+    <t xml:space="preserve">19.175386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2828826904297</t>
   </si>
   <si>
     <t xml:space="preserve">19.1340427398682</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3490333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.76247215271</t>
+    <t xml:space="preserve">19.3490314483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7624759674072</t>
   </si>
   <si>
     <t xml:space="preserve">19.6549777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7045936584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4647998809814</t>
+    <t xml:space="preserve">19.7045917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4647960662842</t>
   </si>
   <si>
     <t xml:space="preserve">19.0596237182617</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6461772918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1175079345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1588497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.010009765625</t>
+    <t xml:space="preserve">18.6461811065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1175060272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1588516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0100116729736</t>
   </si>
   <si>
     <t xml:space="preserve">18.7536792755127</t>
   </si>
   <si>
-    <t xml:space="preserve">18.902515411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0844287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9934730529785</t>
+    <t xml:space="preserve">18.9025173187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0844345092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9934749603271</t>
   </si>
   <si>
     <t xml:space="preserve">18.7950229644775</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">18.7867527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7454071044922</t>
+    <t xml:space="preserve">18.7454090118408</t>
   </si>
   <si>
     <t xml:space="preserve">18.3319683074951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6291198730469</t>
+    <t xml:space="preserve">17.6291217803955</t>
   </si>
   <si>
     <t xml:space="preserve">18.869441986084</t>
@@ -608,37 +608,37 @@
     <t xml:space="preserve">19.1505794525146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.348503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6627254486084</t>
+    <t xml:space="preserve">18.3485088348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6627178192139</t>
   </si>
   <si>
     <t xml:space="preserve">18.7288722991943</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6875286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8942489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4229259490967</t>
+    <t xml:space="preserve">18.6875305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8942451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4229221343994</t>
   </si>
   <si>
     <t xml:space="preserve">18.4808082580566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2327423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3236999511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0590972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6709899902344</t>
+    <t xml:space="preserve">18.2327442169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3237018585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0590991973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6709880828857</t>
   </si>
   <si>
     <t xml:space="preserve">18.9355907440186</t>
@@ -650,28 +650,28 @@
     <t xml:space="preserve">19.8782367706299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6797866821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1676425933838</t>
+    <t xml:space="preserve">19.6797847747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1676445007324</t>
   </si>
   <si>
     <t xml:space="preserve">19.8451614379883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7790126800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1428413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9113159179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1759128570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0022716522217</t>
+    <t xml:space="preserve">19.7790107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1428394317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9113121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1759147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.002269744873</t>
   </si>
   <si>
     <t xml:space="preserve">19.9278507232666</t>
@@ -680,49 +680,49 @@
     <t xml:space="preserve">20.0105381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8038196563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1014938354492</t>
+    <t xml:space="preserve">19.8038177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1014976501465</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263008117676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1097621917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1924533843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6389694213867</t>
+    <t xml:space="preserve">20.1097640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1924514770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6389656066895</t>
   </si>
   <si>
     <t xml:space="preserve">20.1345710754395</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2751407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2172565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3164863586426</t>
+    <t xml:space="preserve">20.2751426696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2172584533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3164844512939</t>
   </si>
   <si>
     <t xml:space="preserve">20.2420635223389</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3330211639404</t>
+    <t xml:space="preserve">20.3330230712891</t>
   </si>
   <si>
     <t xml:space="preserve">20.2255268096924</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6555042266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5066661834717</t>
+    <t xml:space="preserve">20.6555061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5066680908203</t>
   </si>
   <si>
     <t xml:space="preserve">20.3578300476074</t>
@@ -731,37 +731,37 @@
     <t xml:space="preserve">20.481861114502</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0849590301514</t>
+    <t xml:space="preserve">20.0849552154541</t>
   </si>
   <si>
     <t xml:space="preserve">20.3991718292236</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5645484924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5397396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6885795593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8947734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4074401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7133903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9697208404541</t>
+    <t xml:space="preserve">20.5645523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5397434234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6885814666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.894775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4074420928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7133884429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9697246551514</t>
   </si>
   <si>
     <t xml:space="preserve">20.3495616912842</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4239807128906</t>
+    <t xml:space="preserve">20.423978805542</t>
   </si>
   <si>
     <t xml:space="preserve">20.3082160949707</t>
@@ -770,22 +770,22 @@
     <t xml:space="preserve">20.754732131958</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9609260559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8865070343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8286285400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8534317016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.118034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5722923278809</t>
+    <t xml:space="preserve">19.9609241485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8865051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8286247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8534297943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1180305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5722904205322</t>
   </si>
   <si>
     <t xml:space="preserve">19.2994194030762</t>
@@ -794,16 +794,16 @@
     <t xml:space="preserve">19.5144100189209</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5474834442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.423454284668</t>
+    <t xml:space="preserve">19.5474853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4234523773193</t>
   </si>
   <si>
     <t xml:space="preserve">19.6136360168457</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5640239715576</t>
+    <t xml:space="preserve">19.564022064209</t>
   </si>
   <si>
     <t xml:space="preserve">19.3821086883545</t>
@@ -812,43 +812,43 @@
     <t xml:space="preserve">19.7376670837402</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3660984039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9361209869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2007217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4901313781738</t>
+    <t xml:space="preserve">20.3660945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9361190795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.200719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4901275634766</t>
   </si>
   <si>
     <t xml:space="preserve">20.7381935119629</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2922039031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1516342163086</t>
+    <t xml:space="preserve">21.2922058105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.15163230896</t>
   </si>
   <si>
     <t xml:space="preserve">21.0854835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9366474151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7795372009277</t>
+    <t xml:space="preserve">20.9366455078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7795391082764</t>
   </si>
   <si>
     <t xml:space="preserve">20.4570541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7051200866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1268272399902</t>
+    <t xml:space="preserve">20.7051162719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1268310546875</t>
   </si>
   <si>
     <t xml:space="preserve">22.0435562133789</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">21.8669414520264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9846839904785</t>
+    <t xml:space="preserve">21.9846858978271</t>
   </si>
   <si>
     <t xml:space="preserve">22.2958679199219</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4724884033203</t>
+    <t xml:space="preserve">22.4724864959717</t>
   </si>
   <si>
     <t xml:space="preserve">22.2201747894287</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">22.262228012085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.53977394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5734119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5986404418945</t>
+    <t xml:space="preserve">22.5397701263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5734100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5986423492432</t>
   </si>
   <si>
     <t xml:space="preserve">21.808069229126</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">21.0847759246826</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3202686309814</t>
+    <t xml:space="preserve">21.3202667236328</t>
   </si>
   <si>
     <t xml:space="preserve">20.9502086639404</t>
@@ -902,34 +902,34 @@
     <t xml:space="preserve">20.6390285491943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4203586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5549259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4540004730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9670295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1941089630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8576965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1688823699951</t>
+    <t xml:space="preserve">20.4203624725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5549221038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4539985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9670314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1941108703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8576984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1688842773438</t>
   </si>
   <si>
     <t xml:space="preserve">20.8324661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9586219787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156452178955</t>
+    <t xml:space="preserve">20.9586200714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8156433105469</t>
   </si>
   <si>
     <t xml:space="preserve">21.5978088378906</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">21.6819133758545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6146297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.816478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6566791534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8248882293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5473461151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5725784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0351448059082</t>
+    <t xml:space="preserve">21.614631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8164806365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.656681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8248901367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5473480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5725803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0351486206055</t>
   </si>
   <si>
     <t xml:space="preserve">21.8585300445557</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">21.7828350067139</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3211002349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4884738922119</t>
+    <t xml:space="preserve">22.3210983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4884757995605</t>
   </si>
   <si>
     <t xml:space="preserve">21.3875484466553</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">22.1949443817139</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8501205444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2454071044922</t>
+    <t xml:space="preserve">21.8501167297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2454032897949</t>
   </si>
   <si>
     <t xml:space="preserve">22.0015048980713</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">22.3883838653564</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2538185119629</t>
+    <t xml:space="preserve">22.2538166046143</t>
   </si>
   <si>
     <t xml:space="preserve">22.5481796264648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5313625335693</t>
+    <t xml:space="preserve">22.5313587188721</t>
   </si>
   <si>
     <t xml:space="preserve">22.7668495178223</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">23.0696201324463</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5818195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8425445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5650005340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1444835662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2117671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1865348815918</t>
+    <t xml:space="preserve">22.5818214416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8425407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5649967193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1444854736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.211763381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1865310668945</t>
   </si>
   <si>
     <t xml:space="preserve">22.52294921875</t>
@@ -1046,70 +1046,70 @@
     <t xml:space="preserve">22.9266471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.93505859375</t>
+    <t xml:space="preserve">22.9350566864014</t>
   </si>
   <si>
     <t xml:space="preserve">22.8593635559082</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7079772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7416152954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5902309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2369976043701</t>
+    <t xml:space="preserve">22.7079753875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7416191101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5902290344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2369956970215</t>
   </si>
   <si>
     <t xml:space="preserve">21.8417072296143</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1613025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3547401428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3042774200439</t>
+    <t xml:space="preserve">22.1613006591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3547439575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3042793273926</t>
   </si>
   <si>
     <t xml:space="preserve">21.9594535827637</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2285861968994</t>
+    <t xml:space="preserve">22.228588104248</t>
   </si>
   <si>
     <t xml:space="preserve">22.11083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9173984527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3463325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4304351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8257217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4649066925049</t>
+    <t xml:space="preserve">21.9174022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3463306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4304332733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.825719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4649047851562</t>
   </si>
   <si>
     <t xml:space="preserve">23.6331157684326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6751689910889</t>
+    <t xml:space="preserve">23.6751708984375</t>
   </si>
   <si>
     <t xml:space="preserve">23.6835784912109</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8097362518311</t>
+    <t xml:space="preserve">23.8097343444824</t>
   </si>
   <si>
     <t xml:space="preserve">23.9106578826904</t>
@@ -1124,52 +1124,52 @@
     <t xml:space="preserve">23.8770160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">23.986349105835</t>
+    <t xml:space="preserve">23.9863510131836</t>
   </si>
   <si>
     <t xml:space="preserve">23.8938369750977</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9527130126953</t>
+    <t xml:space="preserve">23.9527111053467</t>
   </si>
   <si>
     <t xml:space="preserve">23.9779396057129</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8517818450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0368137359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4741554260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3311786651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3143577575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0536346435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9358921051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8013229370117</t>
+    <t xml:space="preserve">23.85178565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0368099212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4741516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3311767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3143539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0536365509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9358901977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8013248443604</t>
   </si>
   <si>
     <t xml:space="preserve">23.9611225128174</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0199966430664</t>
+    <t xml:space="preserve">24.0199928283691</t>
   </si>
   <si>
     <t xml:space="preserve">24.104097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">24.558256149292</t>
+    <t xml:space="preserve">24.5582542419434</t>
   </si>
   <si>
     <t xml:space="preserve">24.5077934265137</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">25.2310829162598</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1217498779297</t>
+    <t xml:space="preserve">25.1217517852783</t>
   </si>
   <si>
     <t xml:space="preserve">25.1890316009521</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">24.4489212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5574207305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3892154693604</t>
+    <t xml:space="preserve">23.5574226379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.389217376709</t>
   </si>
   <si>
     <t xml:space="preserve">23.5994739532471</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2125968933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9274806976318</t>
+    <t xml:space="preserve">23.2126007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9274787902832</t>
   </si>
   <si>
     <t xml:space="preserve">23.691987991333</t>
@@ -1229,46 +1229,46 @@
     <t xml:space="preserve">23.5406036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5742435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3808078765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4144439697266</t>
+    <t xml:space="preserve">23.5742416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.380802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4144477844238</t>
   </si>
   <si>
     <t xml:space="preserve">23.532190322876</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9695301055908</t>
+    <t xml:space="preserve">23.9695320129395</t>
   </si>
   <si>
     <t xml:space="preserve">22.9939289093018</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6911563873291</t>
+    <t xml:space="preserve">22.6911582946777</t>
   </si>
   <si>
     <t xml:space="preserve">22.9014167785645</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9771118164062</t>
+    <t xml:space="preserve">22.9771060943604</t>
   </si>
   <si>
     <t xml:space="preserve">23.0443897247314</t>
   </si>
   <si>
-    <t xml:space="preserve">23.02756690979</t>
+    <t xml:space="preserve">23.0275688171387</t>
   </si>
   <si>
     <t xml:space="preserve">23.0359783172607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8930034637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.682746887207</t>
+    <t xml:space="preserve">22.8930053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6827449798584</t>
   </si>
   <si>
     <t xml:space="preserve">23.1789588928223</t>
@@ -1277,22 +1277,22 @@
     <t xml:space="preserve">23.2546482086182</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2210102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1621341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.229419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.078031539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8677711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0107479095459</t>
+    <t xml:space="preserve">23.2210063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1621360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2294178009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0780334472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8677749633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0107517242432</t>
   </si>
   <si>
     <t xml:space="preserve">24.1881999969482</t>
@@ -1304,13 +1304,13 @@
     <t xml:space="preserve">24.1713809967041</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2218437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3900489807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4909744262695</t>
+    <t xml:space="preserve">24.2218418121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3900508880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4909725189209</t>
   </si>
   <si>
     <t xml:space="preserve">24.8273868560791</t>
@@ -1319,49 +1319,49 @@
     <t xml:space="preserve">24.5246143341064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3395881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3059463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8686046600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8349628448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2882919311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9602870941162</t>
+    <t xml:space="preserve">24.3395862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3059482574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8686065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8349647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2882900238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9602890014648</t>
   </si>
   <si>
     <t xml:space="preserve">22.6070537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4564971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7163848876953</t>
+    <t xml:space="preserve">23.4564990997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7163829803467</t>
   </si>
   <si>
     <t xml:space="preserve">22.4556655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0687885284424</t>
+    <t xml:space="preserve">22.068790435791</t>
   </si>
   <si>
     <t xml:space="preserve">22.1781234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0940189361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9089889526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7996559143066</t>
+    <t xml:space="preserve">22.0940208435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9089908599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7996578216553</t>
   </si>
   <si>
     <t xml:space="preserve">21.6314487457275</t>
@@ -1370,22 +1370,22 @@
     <t xml:space="preserve">21.7912464141846</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3631496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3967952728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2874603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0856113433838</t>
+    <t xml:space="preserve">22.3631534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3967914581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2874584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0856094360352</t>
   </si>
   <si>
     <t xml:space="preserve">21.6230392456055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3454971313477</t>
+    <t xml:space="preserve">21.3454990386963</t>
   </si>
   <si>
     <t xml:space="preserve">21.4043731689453</t>
@@ -1394,61 +1394,61 @@
     <t xml:space="preserve">21.4464206695557</t>
   </si>
   <si>
-    <t xml:space="preserve">21.295036315918</t>
+    <t xml:space="preserve">21.2950344085693</t>
   </si>
   <si>
     <t xml:space="preserve">21.337085723877</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7407836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.790412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3194370269775</t>
+    <t xml:space="preserve">21.7407855987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7904109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3194332122803</t>
   </si>
   <si>
     <t xml:space="preserve">20.7988243103027</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4035377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5717449188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7735939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9249782562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8072319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0288753509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8919315338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6351699829102</t>
+    <t xml:space="preserve">20.4035358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5717430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7735919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9249801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8072338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0288734436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8919334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6351680755615</t>
   </si>
   <si>
     <t xml:space="preserve">20.618049621582</t>
   </si>
   <si>
-    <t xml:space="preserve">20.746431350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8662567138672</t>
+    <t xml:space="preserve">20.7464332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8662548065186</t>
   </si>
   <si>
     <t xml:space="preserve">21.3883399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9604015350342</t>
+    <t xml:space="preserve">20.9603996276855</t>
   </si>
   <si>
     <t xml:space="preserve">21.3626613616943</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">21.5081634521484</t>
   </si>
   <si>
-    <t xml:space="preserve">21.884744644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7563648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2270965576172</t>
+    <t xml:space="preserve">21.8847465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.756368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2270984649658</t>
   </si>
   <si>
     <t xml:space="preserve">22.9203586578369</t>
@@ -1472,43 +1472,43 @@
     <t xml:space="preserve">22.4153900146484</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4239482879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8077163696289</t>
+    <t xml:space="preserve">22.4239521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8077182769775</t>
   </si>
   <si>
     <t xml:space="preserve">22.0987167358398</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1072750091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7392501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2428398132324</t>
+    <t xml:space="preserve">22.1072731018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7392482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2428417205811</t>
   </si>
   <si>
     <t xml:space="preserve">21.45680809021</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4054565429688</t>
+    <t xml:space="preserve">21.4054584503174</t>
   </si>
   <si>
     <t xml:space="preserve">20.9432849884033</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1302032470703</t>
+    <t xml:space="preserve">20.1302013397217</t>
   </si>
   <si>
     <t xml:space="preserve">20.1216430664062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3698501586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.268518447876</t>
+    <t xml:space="preserve">20.3698463439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2685146331787</t>
   </si>
   <si>
     <t xml:space="preserve">21.3968982696533</t>
@@ -1517,43 +1517,43 @@
     <t xml:space="preserve">21.336986541748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3797798156738</t>
+    <t xml:space="preserve">21.3797779083252</t>
   </si>
   <si>
     <t xml:space="preserve">21.0117530822754</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6779651641846</t>
+    <t xml:space="preserve">20.6779632568359</t>
   </si>
   <si>
     <t xml:space="preserve">21.1743698120117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8063430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7977848052979</t>
+    <t xml:space="preserve">20.8063449859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7977828979492</t>
   </si>
   <si>
     <t xml:space="preserve">21.9960136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5423965454102</t>
+    <t xml:space="preserve">21.5424003601074</t>
   </si>
   <si>
     <t xml:space="preserve">21.1914901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">20.909049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4554328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6509132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8563232421875</t>
+    <t xml:space="preserve">20.9090461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.455436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6509094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8563194274902</t>
   </si>
   <si>
     <t xml:space="preserve">17.8706874847412</t>
@@ -1562,49 +1562,49 @@
     <t xml:space="preserve">17.9305992126465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2729511260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4427490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2558326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9355735778809</t>
+    <t xml:space="preserve">18.27294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4427509307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2558345794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9355754852295</t>
   </si>
   <si>
     <t xml:space="preserve">18.6260852813721</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2454166412354</t>
+    <t xml:space="preserve">18.245418548584</t>
   </si>
   <si>
     <t xml:space="preserve">18.1657447814941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.156888961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8119926452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2280673980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9978981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9359283447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2988910675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1838054656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2103652954102</t>
+    <t xml:space="preserve">18.1568927764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.811990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.228063583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9978942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9359302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2988872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1838035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2103633880615</t>
   </si>
   <si>
     <t xml:space="preserve">19.4139766693115</t>
@@ -1616,25 +1616,25 @@
     <t xml:space="preserve">19.5113544464111</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5644721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.723819732666</t>
+    <t xml:space="preserve">19.5644702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7238216400146</t>
   </si>
   <si>
     <t xml:space="preserve">19.6352920532227</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4316825866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1395416259766</t>
+    <t xml:space="preserve">19.4316806793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1395435333252</t>
   </si>
   <si>
     <t xml:space="preserve">19.0687198638916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2369213104248</t>
+    <t xml:space="preserve">19.2369194030762</t>
   </si>
   <si>
     <t xml:space="preserve">19.6972637176514</t>
@@ -1649,22 +1649,22 @@
     <t xml:space="preserve">19.4405326843262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2900352478027</t>
+    <t xml:space="preserve">19.2900390625</t>
   </si>
   <si>
     <t xml:space="preserve">19.0333099365234</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5109996795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3516540527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8208446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7765808105469</t>
+    <t xml:space="preserve">18.5109977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3516502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8208408355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7765769958496</t>
   </si>
   <si>
     <t xml:space="preserve">18.7942848205566</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">19.4847965240479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6707019805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5733222961426</t>
+    <t xml:space="preserve">19.6707038879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5733242034912</t>
   </si>
   <si>
     <t xml:space="preserve">19.201509475708</t>
@@ -1694,25 +1694,25 @@
     <t xml:space="preserve">19.0952777862549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.696907043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1218357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2546253204346</t>
+    <t xml:space="preserve">18.6969051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1218376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2546234130859</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906734466553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4136180877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6791973114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6880531311035</t>
+    <t xml:space="preserve">18.4136199951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6792030334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6880569458008</t>
   </si>
   <si>
     <t xml:space="preserve">19.1483936309814</t>
@@ -1721,16 +1721,16 @@
     <t xml:space="preserve">18.9890441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0510120391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5995292663574</t>
+    <t xml:space="preserve">19.0510139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5995273590088</t>
   </si>
   <si>
     <t xml:space="preserve">18.3427963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4313220977783</t>
+    <t xml:space="preserve">18.431324005127</t>
   </si>
   <si>
     <t xml:space="preserve">18.3693561553955</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">17.7585201263428</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6965503692627</t>
+    <t xml:space="preserve">17.6965484619141</t>
   </si>
   <si>
     <t xml:space="preserve">17.4840869903564</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">17.417688369751</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0325984954834</t>
+    <t xml:space="preserve">17.0325965881348</t>
   </si>
   <si>
     <t xml:space="preserve">16.6342258453369</t>
@@ -1760,121 +1760,121 @@
     <t xml:space="preserve">16.4527435302734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9392890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5719041824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4346857070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4656667709351</t>
+    <t xml:space="preserve">15.9392910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5719003677368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4346828460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4656715393066</t>
   </si>
   <si>
     <t xml:space="preserve">16.7316055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2712631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7666625976562</t>
+    <t xml:space="preserve">16.2712650299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7666635513306</t>
   </si>
   <si>
     <t xml:space="preserve">15.2133684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1735305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6777791976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2262916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7840127944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6290893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.97434425354</t>
+    <t xml:space="preserve">15.1735286712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6777801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2262907028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7840137481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6290884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9743452072144</t>
   </si>
   <si>
     <t xml:space="preserve">15.0717239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.191234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7179708480835</t>
+    <t xml:space="preserve">15.1912355422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7179698944092</t>
   </si>
   <si>
     <t xml:space="preserve">16.2933979034424</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9171562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8596143722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0986385345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1030654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7755136489868</t>
+    <t xml:space="preserve">15.9171590805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8596153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0986366271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1030616760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7755126953125</t>
   </si>
   <si>
     <t xml:space="preserve">15.4169816970825</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7887935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4833755493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6910581588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2882595062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2041597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943147659302</t>
+    <t xml:space="preserve">15.7887916564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4833745956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6910591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2882604598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.204158782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943157196045</t>
   </si>
   <si>
     <t xml:space="preserve">13.97398853302</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8766098022461</t>
+    <t xml:space="preserve">13.8766107559204</t>
   </si>
   <si>
     <t xml:space="preserve">14.0802221298218</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9916944503784</t>
+    <t xml:space="preserve">13.9916954040527</t>
   </si>
   <si>
     <t xml:space="preserve">13.7880821228027</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6243085861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1554708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3148174285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0451650619507</t>
+    <t xml:space="preserve">13.6243076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1554698944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3148183822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0451688766479</t>
   </si>
   <si>
     <t xml:space="preserve">14.4254770278931</t>
@@ -1883,46 +1883,46 @@
     <t xml:space="preserve">14.1112060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4959440231323</t>
+    <t xml:space="preserve">13.495943069458</t>
   </si>
   <si>
     <t xml:space="preserve">13.367579460144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2524938583374</t>
+    <t xml:space="preserve">13.2524948120117</t>
   </si>
   <si>
     <t xml:space="preserve">14.0669431686401</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7707328796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8415546417236</t>
+    <t xml:space="preserve">14.7707319259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8415555953979</t>
   </si>
   <si>
     <t xml:space="preserve">14.6954870223999</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6512203216553</t>
+    <t xml:space="preserve">14.651219367981</t>
   </si>
   <si>
     <t xml:space="preserve">14.8946714401245</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0628709793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8813905715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8282737731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9345083236694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4479646682739</t>
+    <t xml:space="preserve">15.0628719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8813896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.828275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9345054626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4479656219482</t>
   </si>
   <si>
     <t xml:space="preserve">14.7131910324097</t>
@@ -1931,28 +1931,28 @@
     <t xml:space="preserve">15.1558256149292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2886152267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6958379745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3155288696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4129085540771</t>
+    <t xml:space="preserve">15.2886171340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6958389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.